--- a/docs/downloads/2026-10-09/bursa-report-2026-10-09.xlsx
+++ b/docs/downloads/2026-10-09/bursa-report-2026-10-09.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-09" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-09'!$A$1:$M$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-09'!$A$1:$M$75</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -35,13 +35,13 @@
       <color rgb="00FFFFFF"/>
     </font>
     <font>
-      <color rgb="00D03B3B"/>
+      <color rgb="00898781"/>
     </font>
     <font>
       <color rgb="000CA30C"/>
     </font>
     <font>
-      <color rgb="00898781"/>
+      <color rgb="00D03B3B"/>
     </font>
   </fonts>
   <fills count="3">
@@ -83,8 +83,8 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -543,28 +543,28 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.39</v>
+        <v>0.525</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>-0.0127</v>
+        <v>0</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>33900900</v>
+        <v>53102100</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.8</v>
+        <v>1.86</v>
       </c>
       <c r="H2" t="n">
-        <v>70.36</v>
+        <v>65.31</v>
       </c>
       <c r="I2" s="6" t="inlineStr">
         <is>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0.354</v>
+        <v>0.491</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0.23</v>
+        <v>0.479</v>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" s="7" t="inlineStr"/>
@@ -588,28 +588,28 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>5156</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>XDL</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.615</v>
+        <v>0.01</v>
       </c>
       <c r="E3" s="8" t="n">
-        <v>0.0424</v>
+        <v>1</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>31160300</v>
+        <v>39409400</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>1.22</v>
+        <v>105.52</v>
       </c>
       <c r="H3" t="n">
-        <v>69.42</v>
+        <v>54.97</v>
       </c>
       <c r="I3" s="6" t="inlineStr">
         <is>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.578</v>
+        <v>0.008</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0.505</v>
+        <v>0.007</v>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" s="7" t="inlineStr"/>
@@ -633,39 +633,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>5156</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>XDL</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="E4" s="9" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="E4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>22712800</v>
+        <v>21007900</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>60.81</v>
+        <v>0.9</v>
       </c>
       <c r="H4" t="n">
-        <v>43</v>
-      </c>
-      <c r="I4" s="10" t="inlineStr">
+        <v>47.95</v>
+      </c>
+      <c r="I4" s="9" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.007</v>
+        <v>0.195</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.007</v>
+        <v>0.183</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" s="7" t="inlineStr"/>
@@ -678,28 +678,28 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="E5" s="8" t="n">
-        <v>0.0095</v>
+        <v>0.855</v>
+      </c>
+      <c r="E5" s="10" t="n">
+        <v>-0.0229</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>10707700</v>
+        <v>14386300</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.38</v>
+        <v>0.19</v>
       </c>
       <c r="H5" t="n">
-        <v>66.54000000000001</v>
+        <v>65.68000000000001</v>
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
@@ -707,10 +707,10 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.492</v>
+        <v>0.783</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.479</v>
+        <v>0.71</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" s="7" t="inlineStr"/>
@@ -723,28 +723,28 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>7020</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ASTEEL</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="E6" s="8" t="n">
-        <v>0.0476</v>
+        <v>0.39</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>4012000</v>
+        <v>12649600</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>1.81</v>
+        <v>0.3</v>
       </c>
       <c r="H6" t="n">
-        <v>62.74</v>
+        <v>70.36</v>
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
@@ -752,10 +752,10 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.096</v>
+        <v>0.358</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.236</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" s="7" t="inlineStr"/>
@@ -768,39 +768,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5195</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CENSOF</t>
+          <t>JAKS</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="E7" s="9" t="n">
-        <v>0</v>
+        <v>0.18</v>
+      </c>
+      <c r="E7" s="10" t="n">
+        <v>-0.027</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>2080000</v>
+        <v>8349500</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>1.54</v>
+        <v>0.13</v>
       </c>
       <c r="H7" t="n">
-        <v>68.81</v>
-      </c>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>60.1</v>
+      </c>
+      <c r="I7" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.22</v>
+        <v>0.167</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.206</v>
+        <v>0.132</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" s="7" t="inlineStr"/>
@@ -813,28 +813,28 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>5260</t>
+          <t>5195</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>OWG</t>
+          <t>CENSOF</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E8" s="8" t="n">
-        <v>0.0526</v>
+        <v>0.24</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>1137100</v>
+        <v>6599000</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>1.78</v>
+        <v>4.89</v>
       </c>
       <c r="H8" t="n">
-        <v>61.12</v>
+        <v>68.81</v>
       </c>
       <c r="I8" s="6" t="inlineStr">
         <is>
@@ -842,16 +842,3016 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.186</v>
+        <v>0.22</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.188</v>
+        <v>0.206</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="7" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>0270</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NATGATE</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="E9" s="8" t="n">
+        <v>0.0153</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>5564400</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H9" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>1.809</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>1.636</v>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" s="7" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>6963</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>VS</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>0.0303</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>5487200</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H10" t="n">
+        <v>77.59999999999999</v>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>0.278</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>0.245</v>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" s="7" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>7192</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>GIIB</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="E11" s="8" t="n">
+        <v>0.008100000000000001</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>5467400</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H11" t="n">
+        <v>70.55</v>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="n">
+        <v>0.582</v>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>0.508</v>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" s="7" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>0471</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>PIONEER</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="E12" s="8" t="n">
+        <v>0.08960000000000001</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>5462300</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="H12" t="n">
+        <v>76.05</v>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="n"/>
+      <c r="K12" s="2" t="n"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" s="7" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>0193</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>KINERGY</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>5096000</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="H13" t="n">
+        <v>38.47</v>
+      </c>
+      <c r="I13" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>0.402</v>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" s="7" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>7020</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ASTEEL</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>5022200</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="H14" t="n">
+        <v>59.81</v>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>0.096</v>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" s="7" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>0476</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>SLGC Berhad</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>4629000</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="n"/>
+      <c r="K15" s="2" t="n"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" s="7" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>5238</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>AAGB</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>0.465</v>
+      </c>
+      <c r="E16" s="10" t="n">
+        <v>-0.0211</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>4351900</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H16" t="n">
+        <v>25.65</v>
+      </c>
+      <c r="I16" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="n">
+        <v>0.548</v>
+      </c>
+      <c r="K16" s="2" t="n">
+        <v>0.749</v>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" s="7" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>5259</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>AVANGAAD</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>4240200</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="H17" t="n">
+        <v>49.15</v>
+      </c>
+      <c r="I17" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="K17" s="2" t="n">
+        <v>0.296</v>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" s="7" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>7106</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>SUPERMX</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>0.435</v>
+      </c>
+      <c r="E18" s="10" t="n">
+        <v>-0.0225</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>3963100</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H18" t="n">
+        <v>60.91</v>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="K18" s="2" t="n">
+        <v>0.346</v>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" s="7" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0262</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>SUNVIEW</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="E19" s="8" t="n">
+        <v>0.08220000000000001</v>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>3939600</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="H19" t="n">
+        <v>55.1</v>
+      </c>
+      <c r="I19" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="n">
+        <v>0.384</v>
+      </c>
+      <c r="K19" s="2" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" s="7" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0198</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>GDB</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="E20" s="10" t="n">
+        <v>-0.0723</v>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>3879400</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="H20" t="n">
+        <v>27.42</v>
+      </c>
+      <c r="I20" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="K20" s="2" t="n">
+        <v>0.441</v>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" s="7" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>0111</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="E21" s="8" t="n">
+        <v>0.0313</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>3228600</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="H21" t="n">
+        <v>59.38</v>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="n">
+        <v>0.156</v>
+      </c>
+      <c r="K21" s="2" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" s="7" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>0376</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>IAB</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="E22" s="10" t="n">
+        <v>-0.0074</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>2429100</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H22" t="n">
+        <v>56.55</v>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="n">
+        <v>1.277</v>
+      </c>
+      <c r="K22" s="2" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" s="7" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>0024</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>JAG</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>2196900</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="H23" t="n">
+        <v>53.56</v>
+      </c>
+      <c r="I23" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="K23" s="2" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" s="7" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>0278</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>EDELTEQ</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>0.425</v>
+      </c>
+      <c r="E24" s="10" t="n">
+        <v>-0.023</v>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>2189100</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="H24" t="n">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="n">
+        <v>0.354</v>
+      </c>
+      <c r="K24" s="2" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" s="7" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>0455</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>BUSCAP</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>0.985</v>
+      </c>
+      <c r="E25" s="10" t="n">
+        <v>-0.0101</v>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>2179400</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="H25" t="n">
+        <v>84.86</v>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="n">
+        <v>0.657</v>
+      </c>
+      <c r="K25" s="2" t="n">
+        <v>0.479</v>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" s="7" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>0248</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>YEWLEE</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="E26" s="8" t="n">
+        <v>0.008100000000000001</v>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>2023700</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H26" t="n">
+        <v>58.16</v>
+      </c>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="n">
+        <v>0.611</v>
+      </c>
+      <c r="K26" s="2" t="n">
+        <v>0.611</v>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" s="7" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>0470</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>BFIELD</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>0.485</v>
+      </c>
+      <c r="E27" s="8" t="n">
+        <v>0.0104</v>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>2012800</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H27" t="n">
+        <v>68.69</v>
+      </c>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="n"/>
+      <c r="K27" s="2" t="n"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" s="7" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>4324</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>HENGYUAN</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="E28" s="8" t="n">
+        <v>0.0027</v>
+      </c>
+      <c r="F28" s="4" t="n">
+        <v>1994000</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H28" t="n">
+        <v>58.44</v>
+      </c>
+      <c r="I28" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="n">
+        <v>3.608</v>
+      </c>
+      <c r="K28" s="2" t="n">
+        <v>2.741</v>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" s="7" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>5286</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="E29" s="8" t="n">
+        <v>0.09380000000000001</v>
+      </c>
+      <c r="F29" s="4" t="n">
+        <v>1913600</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="H29" t="n">
+        <v>64.86</v>
+      </c>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="n">
+        <v>5.827</v>
+      </c>
+      <c r="K29" s="2" t="n">
+        <v>5.777</v>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" s="7" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>0338</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>KOPI</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>0.925</v>
+      </c>
+      <c r="E30" s="8" t="n">
+        <v>0.0393</v>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>1564700</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="H30" t="n">
+        <v>51.74</v>
+      </c>
+      <c r="I30" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="n">
+        <v>0.913</v>
+      </c>
+      <c r="K30" s="2" t="n">
+        <v>0.965</v>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" s="7" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>1651</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>MRCB</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="E31" s="8" t="n">
+        <v>0.0182</v>
+      </c>
+      <c r="F31" s="4" t="n">
+        <v>1557800</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H31" t="n">
+        <v>37.22</v>
+      </c>
+      <c r="I31" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="n">
+        <v>0.289</v>
+      </c>
+      <c r="K31" s="2" t="n">
+        <v>0.307</v>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" s="7" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>5260</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>OWG</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E32" s="8" t="n">
+        <v>0.0526</v>
+      </c>
+      <c r="F32" s="4" t="n">
+        <v>1552800</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="H32" t="n">
+        <v>61.12</v>
+      </c>
+      <c r="I32" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="n">
+        <v>0.186</v>
+      </c>
+      <c r="K32" s="2" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" s="7" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>5161</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>JCY</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="E33" s="8" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="F33" s="4" t="n">
+        <v>1529400</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H33" t="n">
+        <v>63.49</v>
+      </c>
+      <c r="I33" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="n">
+        <v>0.581</v>
+      </c>
+      <c r="K33" s="2" t="n">
+        <v>0.518</v>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" s="7" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>5099</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>CAPITALA</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>0.225</v>
+      </c>
+      <c r="E34" s="8" t="n">
+        <v>0.0227</v>
+      </c>
+      <c r="F34" s="4" t="n">
+        <v>1516500</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H34" t="n">
+        <v>33.07</v>
+      </c>
+      <c r="I34" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="n">
+        <v>0.249</v>
+      </c>
+      <c r="K34" s="2" t="n">
+        <v>0.304</v>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" s="7" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>5327</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>MEGAFB</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="E35" s="8" t="n">
+        <v>0.0035</v>
+      </c>
+      <c r="F35" s="4" t="n">
+        <v>1384600</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="H35" t="n">
+        <v>75.53</v>
+      </c>
+      <c r="I35" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="n">
+        <v>2.638</v>
+      </c>
+      <c r="K35" s="2" t="n">
+        <v>2.285</v>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" s="7" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>1155</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>MAYBANK</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>9.81</v>
+      </c>
+      <c r="E36" s="8" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="F36" s="4" t="n">
+        <v>1383800</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H36" t="n">
+        <v>31.22</v>
+      </c>
+      <c r="I36" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="n">
+        <v>10.022</v>
+      </c>
+      <c r="K36" s="2" t="n">
+        <v>10.213</v>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" s="7" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>0236</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>RAMSSOL</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>0.785</v>
+      </c>
+      <c r="E37" s="10" t="n">
+        <v>-0.0063</v>
+      </c>
+      <c r="F37" s="4" t="n">
+        <v>1359000</v>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H37" t="n">
+        <v>52.68</v>
+      </c>
+      <c r="I37" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="n">
+        <v>0.778</v>
+      </c>
+      <c r="K37" s="2" t="n">
+        <v>0.773</v>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" s="7" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>5151</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>HEXTAR</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="E38" s="8" t="n">
+        <v>0.006500000000000001</v>
+      </c>
+      <c r="F38" s="4" t="n">
+        <v>1320800</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H38" t="n">
+        <v>50.25</v>
+      </c>
+      <c r="I38" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="K38" s="2" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" s="7" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>0267</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>ECA</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="E39" s="8" t="n">
+        <v>0.0411</v>
+      </c>
+      <c r="F39" s="4" t="n">
+        <v>1288900</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="H39" t="n">
+        <v>53.04</v>
+      </c>
+      <c r="I39" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="n">
+        <v>0.366</v>
+      </c>
+      <c r="K39" s="2" t="n">
+        <v>0.374</v>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" s="7" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>0453</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>EIPOWER</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="E40" s="8" t="n">
+        <v>0.0155</v>
+      </c>
+      <c r="F40" s="4" t="n">
+        <v>1236500</v>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H40" t="n">
+        <v>57.2</v>
+      </c>
+      <c r="I40" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="n">
+        <v>0.963</v>
+      </c>
+      <c r="K40" s="2" t="n">
+        <v>0.821</v>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" s="7" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>7121</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="E41" s="8" t="n">
+        <v>0.0062</v>
+      </c>
+      <c r="F41" s="4" t="n">
+        <v>1151000</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H41" t="n">
+        <v>54.76</v>
+      </c>
+      <c r="I41" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="K41" s="2" t="n">
+        <v>0.806</v>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" s="7" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>0246</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>CNERGEN</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E42" s="8" t="n">
+        <v>0.0331</v>
+      </c>
+      <c r="F42" s="4" t="n">
+        <v>1073400</v>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="H42" t="n">
+        <v>76.55</v>
+      </c>
+      <c r="I42" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="n">
+        <v>1.025</v>
+      </c>
+      <c r="K42" s="2" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" s="7" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>0450</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>MFGROUP</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>0.265</v>
+      </c>
+      <c r="E43" s="10" t="n">
+        <v>-0.0185</v>
+      </c>
+      <c r="F43" s="4" t="n">
+        <v>1062000</v>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="H43" t="n">
+        <v>54.17</v>
+      </c>
+      <c r="I43" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="n">
+        <v>0.262</v>
+      </c>
+      <c r="K43" s="2" t="n">
+        <v>0.264</v>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" s="7" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>0104</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>GENETEC</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="E44" s="10" t="n">
+        <v>-0.0149</v>
+      </c>
+      <c r="F44" s="4" t="n">
+        <v>1049300</v>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H44" t="n">
+        <v>52.01</v>
+      </c>
+      <c r="I44" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="K44" s="2" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" s="7" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>0166</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>INARI</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="E45" s="10" t="n">
+        <v>-0.0036</v>
+      </c>
+      <c r="F45" s="4" t="n">
+        <v>1043500</v>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H45" t="n">
+        <v>64.19</v>
+      </c>
+      <c r="I45" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="K45" s="2" t="n">
+        <v>2.497</v>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" s="7" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>0249</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>LGMS</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="E46" s="8" t="n">
+        <v>0.0175</v>
+      </c>
+      <c r="F46" s="4" t="n">
+        <v>1012600</v>
+      </c>
+      <c r="G46" s="5" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="H46" t="n">
+        <v>73.84</v>
+      </c>
+      <c r="I46" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="n">
+        <v>0.524</v>
+      </c>
+      <c r="K46" s="2" t="n">
+        <v>0.504</v>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" s="7" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>5398</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>GAMUDA</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E47" s="8" t="n">
+        <v>0.0101</v>
+      </c>
+      <c r="F47" s="4" t="n">
+        <v>998100</v>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H47" t="n">
+        <v>58.12</v>
+      </c>
+      <c r="I47" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="n">
+        <v>4.917</v>
+      </c>
+      <c r="K47" s="2" t="n">
+        <v>4.651</v>
+      </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" s="7" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>0045</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>SSB8</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="E48" s="8" t="n">
+        <v>0.0149</v>
+      </c>
+      <c r="F48" s="4" t="n">
+        <v>965100</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H48" t="n">
+        <v>66.18000000000001</v>
+      </c>
+      <c r="I48" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="n">
+        <v>0.638</v>
+      </c>
+      <c r="K48" s="2" t="n">
+        <v>0.601</v>
+      </c>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" s="7" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>7204</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>D&amp;O</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="E49" s="8" t="n">
+        <v>0.0294</v>
+      </c>
+      <c r="F49" s="4" t="n">
+        <v>964000</v>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H49" t="n">
+        <v>55.9</v>
+      </c>
+      <c r="I49" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="n">
+        <v>0.512</v>
+      </c>
+      <c r="K49" s="2" t="n">
+        <v>0.436</v>
+      </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" s="7" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>0271</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>WELLS</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="E50" s="8" t="n">
+        <v>0.0291</v>
+      </c>
+      <c r="F50" s="4" t="n">
+        <v>963600</v>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="H50" t="n">
+        <v>26.64</v>
+      </c>
+      <c r="I50" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="n">
+        <v>0.582</v>
+      </c>
+      <c r="K50" s="2" t="n">
+        <v>0.622</v>
+      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" s="7" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>3336</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>IJM</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E51" s="8" t="n">
+        <v>0.0072</v>
+      </c>
+      <c r="F51" s="4" t="n">
+        <v>957700</v>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H51" t="n">
+        <v>52.82</v>
+      </c>
+      <c r="I51" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="n">
+        <v>2.791</v>
+      </c>
+      <c r="K51" s="2" t="n">
+        <v>2.693</v>
+      </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" s="7" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>5296</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>MRDIY</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="E52" s="10" t="n">
+        <v>-0.008100000000000001</v>
+      </c>
+      <c r="F52" s="4" t="n">
+        <v>928500</v>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H52" t="n">
+        <v>32.43</v>
+      </c>
+      <c r="I52" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="n">
+        <v>1.284</v>
+      </c>
+      <c r="K52" s="2" t="n">
+        <v>1.386</v>
+      </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" s="7" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>0273</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>VLB</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="E53" s="8" t="n">
+        <v>0.0108</v>
+      </c>
+      <c r="F53" s="4" t="n">
+        <v>915000</v>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="H53" t="n">
+        <v>55.4</v>
+      </c>
+      <c r="I53" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="n">
+        <v>0.923</v>
+      </c>
+      <c r="K53" s="2" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" s="7" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>0339</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>CBHB</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="E54" s="8" t="n">
+        <v>0.0273</v>
+      </c>
+      <c r="F54" s="4" t="n">
+        <v>895500</v>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H54" t="n">
+        <v>66.05</v>
+      </c>
+      <c r="I54" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="K54" s="2" t="n">
+        <v>0.917</v>
+      </c>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" s="7" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>5183</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>PCHEM</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="E55" s="10" t="n">
+        <v>-0.0211</v>
+      </c>
+      <c r="F55" s="4" t="n">
+        <v>861800</v>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H55" t="n">
+        <v>41.58</v>
+      </c>
+      <c r="I55" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="n">
+        <v>4.363</v>
+      </c>
+      <c r="K55" s="2" t="n">
+        <v>4.463</v>
+      </c>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" s="7" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>0310</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>UUE</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="n">
+        <v>0.805</v>
+      </c>
+      <c r="E56" s="8" t="n">
+        <v>0.0321</v>
+      </c>
+      <c r="F56" s="4" t="n">
+        <v>839100</v>
+      </c>
+      <c r="G56" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H56" t="n">
+        <v>65.55</v>
+      </c>
+      <c r="I56" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="n">
+        <v>0.736</v>
+      </c>
+      <c r="K56" s="2" t="n">
+        <v>0.652</v>
+      </c>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" s="7" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>0359</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>HKB</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="E57" s="8" t="n">
+        <v>0.0124</v>
+      </c>
+      <c r="F57" s="4" t="n">
+        <v>818300</v>
+      </c>
+      <c r="G57" s="5" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="H57" t="n">
+        <v>81.81</v>
+      </c>
+      <c r="I57" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="n">
+        <v>0.679</v>
+      </c>
+      <c r="K57" s="2" t="n">
+        <v>0.622</v>
+      </c>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" s="7" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>5141</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>DAYANG</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="E58" s="10" t="n">
+        <v>-0.0069</v>
+      </c>
+      <c r="F58" s="4" t="n">
+        <v>800800</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="H58" t="n">
+        <v>41.86</v>
+      </c>
+      <c r="I58" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="n">
+        <v>1.461</v>
+      </c>
+      <c r="K58" s="2" t="n">
+        <v>1.495</v>
+      </c>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" s="7" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>7081</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>PHARMA</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="n">
+        <v>0.925</v>
+      </c>
+      <c r="E59" s="8" t="n">
+        <v>0.0054</v>
+      </c>
+      <c r="F59" s="4" t="n">
+        <v>798100</v>
+      </c>
+      <c r="G59" s="5" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H59" t="n">
+        <v>22.43</v>
+      </c>
+      <c r="I59" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="n">
+        <v>1.037</v>
+      </c>
+      <c r="K59" s="2" t="n">
+        <v>1.119</v>
+      </c>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" s="7" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>5168</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>HARTA</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="E60" s="10" t="n">
+        <v>-0.009300000000000001</v>
+      </c>
+      <c r="F60" s="4" t="n">
+        <v>783700</v>
+      </c>
+      <c r="G60" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H60" t="n">
+        <v>48.94</v>
+      </c>
+      <c r="I60" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="n">
+        <v>1.071</v>
+      </c>
+      <c r="K60" s="2" t="n">
+        <v>1.037</v>
+      </c>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" s="7" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>0318</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>ELRIDGE</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="n">
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="E61" s="8" t="n">
+        <v>0.0054</v>
+      </c>
+      <c r="F61" s="4" t="n">
+        <v>776700</v>
+      </c>
+      <c r="G61" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H61" t="n">
+        <v>65.34999999999999</v>
+      </c>
+      <c r="I61" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="n">
+        <v>0.909</v>
+      </c>
+      <c r="K61" s="2" t="n">
+        <v>0.863</v>
+      </c>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" s="7" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>5326</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>99SMART</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="E62" s="8" t="n">
+        <v>0.0288</v>
+      </c>
+      <c r="F62" s="4" t="n">
+        <v>776300</v>
+      </c>
+      <c r="G62" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H62" t="n">
+        <v>47.87</v>
+      </c>
+      <c r="I62" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="n">
+        <v>3.194</v>
+      </c>
+      <c r="K62" s="2" t="n">
+        <v>3.389</v>
+      </c>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" s="7" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>4677</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>YTL</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="E63" s="8" t="n">
+        <v>0.004699999999999999</v>
+      </c>
+      <c r="F63" s="4" t="n">
+        <v>760700</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H63" t="n">
+        <v>42.31</v>
+      </c>
+      <c r="I63" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="n">
+        <v>2.226</v>
+      </c>
+      <c r="K63" s="2" t="n">
+        <v>2.213</v>
+      </c>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" s="7" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>0208</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>GREATEC</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="E64" s="8" t="n">
+        <v>0.0187</v>
+      </c>
+      <c r="F64" s="4" t="n">
+        <v>737100</v>
+      </c>
+      <c r="G64" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H64" t="n">
+        <v>59.25</v>
+      </c>
+      <c r="I64" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="n">
+        <v>2.631</v>
+      </c>
+      <c r="K64" s="2" t="n">
+        <v>2.581</v>
+      </c>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" s="7" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>1066</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>RHBBANK</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="n">
+        <v>7.11</v>
+      </c>
+      <c r="E65" s="10" t="n">
+        <v>-0.005600000000000001</v>
+      </c>
+      <c r="F65" s="4" t="n">
+        <v>734800</v>
+      </c>
+      <c r="G65" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H65" t="n">
+        <v>18.64</v>
+      </c>
+      <c r="I65" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="n">
+        <v>7.595</v>
+      </c>
+      <c r="K65" s="2" t="n">
+        <v>8.089</v>
+      </c>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" s="7" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>0120</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>VIS</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="E66" s="8" t="n">
+        <v>0.0388</v>
+      </c>
+      <c r="F66" s="4" t="n">
+        <v>712300</v>
+      </c>
+      <c r="G66" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H66" t="n">
+        <v>84.47</v>
+      </c>
+      <c r="I66" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="n">
+        <v>0.516</v>
+      </c>
+      <c r="K66" s="2" t="n">
+        <v>0.443</v>
+      </c>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" s="7" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>0083</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>NOTION</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="n">
+        <v>0.715</v>
+      </c>
+      <c r="E67" s="8" t="n">
+        <v>0.0214</v>
+      </c>
+      <c r="F67" s="4" t="n">
+        <v>658100</v>
+      </c>
+      <c r="G67" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H67" t="n">
+        <v>62.82</v>
+      </c>
+      <c r="I67" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="n">
+        <v>0.671</v>
+      </c>
+      <c r="K67" s="2" t="n">
+        <v>0.607</v>
+      </c>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" s="7" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>7579</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>AWC</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="E68" s="10" t="n">
+        <v>-0.007900000000000001</v>
+      </c>
+      <c r="F68" s="4" t="n">
+        <v>621100</v>
+      </c>
+      <c r="G68" s="5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H68" t="n">
+        <v>56.48</v>
+      </c>
+      <c r="I68" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="n">
+        <v>0.619</v>
+      </c>
+      <c r="K68" s="2" t="n">
+        <v>0.529</v>
+      </c>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" s="7" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>1023</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>CIMB</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="E69" s="10" t="n">
+        <v>-0.0014</v>
+      </c>
+      <c r="F69" s="4" t="n">
+        <v>609400</v>
+      </c>
+      <c r="G69" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H69" t="n">
+        <v>31.19</v>
+      </c>
+      <c r="I69" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="n">
+        <v>7.639</v>
+      </c>
+      <c r="K69" s="2" t="n">
+        <v>7.729</v>
+      </c>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" s="7" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>0112</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>MIKROMB</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" s="4" t="n">
+        <v>579500</v>
+      </c>
+      <c r="G70" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H70" t="n">
+        <v>54.4</v>
+      </c>
+      <c r="I70" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="n">
+        <v>0.639</v>
+      </c>
+      <c r="K70" s="2" t="n">
+        <v>0.611</v>
+      </c>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" s="7" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>5555</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>SUNMED</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" s="4" t="n">
+        <v>576000</v>
+      </c>
+      <c r="G71" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H71" t="n">
+        <v>50.69</v>
+      </c>
+      <c r="I71" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="n">
+        <v>2.098</v>
+      </c>
+      <c r="K71" s="2" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" s="7" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>9792</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>SEG</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="E72" s="10" t="n">
+        <v>-0.007900000000000001</v>
+      </c>
+      <c r="F72" s="4" t="n">
+        <v>550100</v>
+      </c>
+      <c r="G72" s="5" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="H72" t="n">
+        <v>37.72</v>
+      </c>
+      <c r="I72" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="n">
+        <v>0.632</v>
+      </c>
+      <c r="K72" s="2" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" s="7" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>5317</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>CPETECH</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="E73" s="8" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="F73" s="4" t="n">
+        <v>541200</v>
+      </c>
+      <c r="G73" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H73" t="n">
+        <v>57.71</v>
+      </c>
+      <c r="I73" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="n">
+        <v>1.294</v>
+      </c>
+      <c r="K73" s="2" t="n">
+        <v>1.194</v>
+      </c>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" s="7" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>5162</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>VSTECS</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="E74" s="8" t="n">
+        <v>0.0299</v>
+      </c>
+      <c r="F74" s="4" t="n">
+        <v>533500</v>
+      </c>
+      <c r="G74" s="5" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="H74" t="n">
+        <v>56.36</v>
+      </c>
+      <c r="I74" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="n">
+        <v>1.663</v>
+      </c>
+      <c r="K74" s="2" t="n">
+        <v>1.678</v>
+      </c>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" s="7" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>5102</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>GCB</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" s="4" t="n">
+        <v>513400</v>
+      </c>
+      <c r="G75" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H75" t="n">
+        <v>43.08</v>
+      </c>
+      <c r="I75" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="n">
+        <v>1.322</v>
+      </c>
+      <c r="K75" s="2" t="n">
+        <v>1.305</v>
+      </c>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M8"/>
+  <autoFilter ref="A1:M75"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-09/bursa-report-2026-10-09.xlsx
+++ b/docs/downloads/2026-10-09/bursa-report-2026-10-09.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-09" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-09'!$A$1:$M$75</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-09'!$A$1:$M$114</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -35,13 +35,13 @@
       <color rgb="00FFFFFF"/>
     </font>
     <font>
-      <color rgb="00898781"/>
+      <color rgb="00D03B3B"/>
     </font>
     <font>
       <color rgb="000CA30C"/>
     </font>
     <font>
-      <color rgb="00D03B3B"/>
+      <color rgb="00898781"/>
     </font>
   </fonts>
   <fills count="3">
@@ -82,9 +82,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M75"/>
+  <dimension ref="A1:M114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -552,19 +552,19 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.525</v>
+        <v>0.515</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0</v>
+        <v>-0.019</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>53102100</v>
+        <v>69250300</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>1.86</v>
+        <v>2.43</v>
       </c>
       <c r="H2" t="n">
-        <v>65.31</v>
+        <v>60.83</v>
       </c>
       <c r="I2" s="6" t="inlineStr">
         <is>
@@ -572,7 +572,7 @@
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0.491</v>
+        <v>0.49</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0.479</v>
@@ -597,27 +597,27 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="E3" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>39409400</v>
+        <v>39809700</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>105.52</v>
+        <v>106.59</v>
       </c>
       <c r="H3" t="n">
-        <v>54.97</v>
-      </c>
-      <c r="I3" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43</v>
+      </c>
+      <c r="I3" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.008</v>
+        <v>0.007</v>
       </c>
       <c r="K3" s="2" t="n">
         <v>0.007</v>
@@ -644,11 +644,11 @@
       <c r="D4" s="2" t="n">
         <v>0.19</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="E4" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>21007900</v>
+        <v>21145000</v>
       </c>
       <c r="G4" s="5" t="n">
         <v>0.9</v>
@@ -687,19 +687,19 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.855</v>
-      </c>
-      <c r="E5" s="10" t="n">
-        <v>-0.0229</v>
+        <v>0.845</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>-0.0343</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>14386300</v>
+        <v>20487200</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.19</v>
+        <v>0.27</v>
       </c>
       <c r="H5" t="n">
-        <v>65.68000000000001</v>
+        <v>63.57</v>
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.783</v>
+        <v>0.782</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>0.71</v>
@@ -723,39 +723,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>0138</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>ZETRIX</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>0</v>
+        <v>0.08</v>
+      </c>
+      <c r="E6" s="10" t="n">
+        <v>0.0667</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>12649600</v>
+        <v>17207600</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.3</v>
+        <v>0.04</v>
       </c>
       <c r="H6" t="n">
-        <v>70.36</v>
-      </c>
-      <c r="I6" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>22.11</v>
+      </c>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.358</v>
+        <v>0.175</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.236</v>
+        <v>0.397</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" s="7" t="inlineStr"/>
@@ -779,14 +779,14 @@
       <c r="D7" s="2" t="n">
         <v>0.18</v>
       </c>
-      <c r="E7" s="10" t="n">
+      <c r="E7" s="3" t="n">
         <v>-0.027</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>8349500</v>
+        <v>16799600</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.13</v>
+        <v>0.26</v>
       </c>
       <c r="H7" t="n">
         <v>60.1</v>
@@ -813,28 +813,28 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>5195</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CENSOF</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>0</v>
+        <v>2.01</v>
+      </c>
+      <c r="E8" s="10" t="n">
+        <v>0.0255</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>6599000</v>
+        <v>15251600</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>4.89</v>
+        <v>0.61</v>
       </c>
       <c r="H8" t="n">
-        <v>68.81</v>
+        <v>71.48</v>
       </c>
       <c r="I8" s="6" t="inlineStr">
         <is>
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.22</v>
+        <v>1.811</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.206</v>
+        <v>1.636</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="7" t="inlineStr"/>
@@ -858,28 +858,28 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1.99</v>
+        <v>0.39</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>0.0153</v>
+        <v>0</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>5564400</v>
+        <v>15111700</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.22</v>
+        <v>0.36</v>
       </c>
       <c r="H9" t="n">
-        <v>70.5</v>
+        <v>70.36</v>
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
@@ -887,10 +887,10 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>1.809</v>
+        <v>0.358</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>1.636</v>
+        <v>0.236</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="7" t="inlineStr"/>
@@ -914,14 +914,14 @@
       <c r="D10" s="2" t="n">
         <v>0.34</v>
       </c>
-      <c r="E10" s="8" t="n">
+      <c r="E10" s="10" t="n">
         <v>0.0303</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>5487200</v>
+        <v>14741100</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.09</v>
+        <v>0.25</v>
       </c>
       <c r="H10" t="n">
         <v>77.59999999999999</v>
@@ -948,40 +948,36 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>0471</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>PIONEER</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="E11" s="8" t="n">
-        <v>0.008100000000000001</v>
+        <v>0.35</v>
+      </c>
+      <c r="E11" s="10" t="n">
+        <v>0.04480000000000001</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>5467400</v>
+        <v>11802300</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.21</v>
+        <v>1.26</v>
       </c>
       <c r="H11" t="n">
-        <v>70.55</v>
+        <v>72.73999999999999</v>
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J11" s="2" t="n">
-        <v>0.582</v>
-      </c>
-      <c r="K11" s="2" t="n">
-        <v>0.508</v>
-      </c>
+      <c r="J11" s="2" t="n"/>
+      <c r="K11" s="2" t="n"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="7" t="inlineStr"/>
     </row>
@@ -993,36 +989,40 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0471</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>PIONEER</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0.365</v>
-      </c>
-      <c r="E12" s="8" t="n">
-        <v>0.08960000000000001</v>
+        <v>0.62</v>
+      </c>
+      <c r="E12" s="10" t="n">
+        <v>0.008100000000000001</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>5462300</v>
+        <v>9824400</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.58</v>
+        <v>0.38</v>
       </c>
       <c r="H12" t="n">
-        <v>76.05</v>
+        <v>70.55</v>
       </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J12" s="2" t="n"/>
-      <c r="K12" s="2" t="n"/>
+      <c r="J12" s="2" t="n">
+        <v>0.582</v>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>0.508</v>
+      </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="7" t="inlineStr"/>
     </row>
@@ -1034,39 +1034,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>5195</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>CENSOF</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0.395</v>
-      </c>
-      <c r="E13" s="3" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="E13" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>5096000</v>
+        <v>7225200</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.47</v>
+        <v>5.36</v>
       </c>
       <c r="H13" t="n">
-        <v>38.47</v>
-      </c>
-      <c r="I13" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>68.81</v>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.402</v>
+        <v>0.22</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0.41</v>
+        <v>0.206</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="7" t="inlineStr"/>
@@ -1079,28 +1079,28 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>7020</t>
+          <t>0278</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ASTEEL</t>
+          <t>EDELTEQ</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0.105</v>
-      </c>
-      <c r="E14" s="3" t="n">
-        <v>0</v>
+        <v>0.47</v>
+      </c>
+      <c r="E14" s="10" t="n">
+        <v>0.0805</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>5022200</v>
+        <v>6914700</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>2.27</v>
+        <v>3.01</v>
       </c>
       <c r="H14" t="n">
-        <v>59.81</v>
+        <v>79.16</v>
       </c>
       <c r="I14" s="6" t="inlineStr">
         <is>
@@ -1108,10 +1108,10 @@
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.096</v>
+        <v>0.359</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.349</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="7" t="inlineStr"/>
@@ -1124,33 +1124,40 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0476</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SLGC Berhad</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E15" s="3" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="E15" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>4629000</v>
+        <v>6215100</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="I15" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="n"/>
-      <c r="K15" s="2" t="n"/>
+        <v>2.36</v>
+      </c>
+      <c r="H15" t="n">
+        <v>49.15</v>
+      </c>
+      <c r="I15" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="K15" s="2" t="n">
+        <v>0.296</v>
+      </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="7" t="inlineStr"/>
     </row>
@@ -1162,28 +1169,28 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>0.465</v>
-      </c>
-      <c r="E16" s="10" t="n">
-        <v>-0.0211</v>
+        <v>0.395</v>
+      </c>
+      <c r="E16" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>4351900</v>
+        <v>5460200</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.11</v>
+        <v>0.51</v>
       </c>
       <c r="H16" t="n">
-        <v>25.65</v>
+        <v>38.47</v>
       </c>
       <c r="I16" s="9" t="inlineStr">
         <is>
@@ -1191,10 +1198,10 @@
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.548</v>
+        <v>0.402</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0.749</v>
+        <v>0.41</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="7" t="inlineStr"/>
@@ -1207,39 +1214,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>7020</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AVANGAAD</t>
+          <t>ASTEEL</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E17" s="3" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="E17" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>4240200</v>
+        <v>5271800</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>1.61</v>
+        <v>2.38</v>
       </c>
       <c r="H17" t="n">
-        <v>49.15</v>
-      </c>
-      <c r="I17" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.81</v>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.295</v>
+        <v>0.096</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0.296</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="7" t="inlineStr"/>
@@ -1252,40 +1259,36 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>0470</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>BFIELD</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>0.435</v>
+        <v>0.485</v>
       </c>
       <c r="E18" s="10" t="n">
-        <v>-0.0225</v>
+        <v>0.0104</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>3963100</v>
+        <v>5231600</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.15</v>
+        <v>0.44</v>
       </c>
       <c r="H18" t="n">
-        <v>60.91</v>
+        <v>68.69</v>
       </c>
       <c r="I18" s="6" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J18" s="2" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="K18" s="2" t="n">
-        <v>0.346</v>
-      </c>
+      <c r="J18" s="2" t="n"/>
+      <c r="K18" s="2" t="n"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="7" t="inlineStr"/>
     </row>
@@ -1297,40 +1300,33 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>0476</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>SLGC Berhad</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>0.395</v>
+        <v>0.25</v>
       </c>
       <c r="E19" s="8" t="n">
-        <v>0.08220000000000001</v>
+        <v>0</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>3939600</v>
+        <v>5145400</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="H19" t="n">
-        <v>55.1</v>
-      </c>
-      <c r="I19" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="n">
-        <v>0.384</v>
-      </c>
-      <c r="K19" s="2" t="n">
-        <v>0.375</v>
-      </c>
+        <v>0.12</v>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="n"/>
+      <c r="K19" s="2" t="n"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="7" t="inlineStr"/>
     </row>
@@ -1342,39 +1338,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0198</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>GDB</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="E20" s="10" t="n">
-        <v>-0.0723</v>
+        <v>0.43</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>-0.0337</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>3879400</v>
+        <v>5085800</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>3.44</v>
+        <v>0.19</v>
       </c>
       <c r="H20" t="n">
-        <v>27.42</v>
-      </c>
-      <c r="I20" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.31</v>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.42</v>
+        <v>0.409</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0.441</v>
+        <v>0.346</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="7" t="inlineStr"/>
@@ -1387,39 +1383,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0111</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>K1</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>0.165</v>
-      </c>
-      <c r="E21" s="8" t="n">
-        <v>0.0313</v>
+        <v>0.39</v>
+      </c>
+      <c r="E21" s="10" t="n">
+        <v>0.06849999999999999</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>3228600</v>
+        <v>4949000</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.98</v>
+        <v>0.41</v>
       </c>
       <c r="H21" t="n">
-        <v>59.38</v>
-      </c>
-      <c r="I21" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.45</v>
+      </c>
+      <c r="I21" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.156</v>
+        <v>0.384</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0.145</v>
+        <v>0.375</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="7" t="inlineStr"/>
@@ -1432,39 +1428,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0376</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>IAB</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="E22" s="10" t="n">
-        <v>-0.0074</v>
+        <v>0.46</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>-0.0316</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>2429100</v>
+        <v>4866400</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>1.4</v>
+        <v>0.13</v>
       </c>
       <c r="H22" t="n">
-        <v>56.55</v>
-      </c>
-      <c r="I22" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>25.19</v>
+      </c>
+      <c r="I22" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>1.277</v>
+        <v>0.548</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>1.32</v>
+        <v>0.749</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="7" t="inlineStr"/>
@@ -1477,28 +1473,28 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0</v>
+        <v>-0.0843</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>2196900</v>
+        <v>4016800</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.33</v>
+        <v>3.56</v>
       </c>
       <c r="H23" t="n">
-        <v>53.56</v>
+        <v>26.04</v>
       </c>
       <c r="I23" s="9" t="inlineStr">
         <is>
@@ -1506,10 +1502,10 @@
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.368</v>
+        <v>0.419</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0.368</v>
+        <v>0.441</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="7" t="inlineStr"/>
@@ -1522,28 +1518,28 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0278</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>EDELTEQ</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>0.425</v>
+        <v>0.625</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>-0.023</v>
+        <v>0.008100000000000001</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>2189100</v>
+        <v>3713700</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.95</v>
+        <v>0.36</v>
       </c>
       <c r="H24" t="n">
-        <v>71.09999999999999</v>
+        <v>58.16</v>
       </c>
       <c r="I24" s="6" t="inlineStr">
         <is>
@@ -1551,10 +1547,10 @@
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.354</v>
+        <v>0.611</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0.348</v>
+        <v>0.611</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="7" t="inlineStr"/>
@@ -1567,28 +1563,28 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>0.985</v>
+        <v>0.725</v>
       </c>
       <c r="E25" s="10" t="n">
-        <v>-0.0101</v>
+        <v>0.0357</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>2179400</v>
+        <v>3671600</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.68</v>
+        <v>0.48</v>
       </c>
       <c r="H25" t="n">
-        <v>84.86</v>
+        <v>58.51</v>
       </c>
       <c r="I25" s="6" t="inlineStr">
         <is>
@@ -1596,10 +1592,10 @@
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.657</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0.479</v>
+        <v>0.678</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="7" t="inlineStr"/>
@@ -1612,28 +1608,28 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>0111</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E26" s="8" t="n">
-        <v>0.008100000000000001</v>
+        <v>0.165</v>
+      </c>
+      <c r="E26" s="10" t="n">
+        <v>0.0313</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>2023700</v>
+        <v>3667800</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.19</v>
+        <v>1.12</v>
       </c>
       <c r="H26" t="n">
-        <v>58.16</v>
+        <v>59.38</v>
       </c>
       <c r="I26" s="6" t="inlineStr">
         <is>
@@ -1641,10 +1637,10 @@
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.611</v>
+        <v>0.156</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0.611</v>
+        <v>0.145</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="7" t="inlineStr"/>
@@ -1657,36 +1653,40 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0470</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>BFIELD</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>0.485</v>
-      </c>
-      <c r="E27" s="8" t="n">
-        <v>0.0104</v>
+        <v>0.775</v>
+      </c>
+      <c r="E27" s="10" t="n">
+        <v>0.006500000000000001</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>2012800</v>
+        <v>3200800</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.17</v>
+        <v>0.22</v>
       </c>
       <c r="H27" t="n">
-        <v>68.69</v>
+        <v>50.25</v>
       </c>
       <c r="I27" s="6" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J27" s="2" t="n"/>
-      <c r="K27" s="2" t="n"/>
+      <c r="J27" s="2" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="K27" s="2" t="n">
+        <v>0.775</v>
+      </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="7" t="inlineStr"/>
     </row>
@@ -1698,39 +1698,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>5253</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>ECONBHD</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>3.78</v>
+        <v>0.125</v>
       </c>
       <c r="E28" s="8" t="n">
-        <v>0.0027</v>
+        <v>0</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>1994000</v>
+        <v>3095700</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.17</v>
+        <v>0.68</v>
       </c>
       <c r="H28" t="n">
-        <v>58.44</v>
-      </c>
-      <c r="I28" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.25</v>
+      </c>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>3.608</v>
+        <v>0.122</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>2.741</v>
+        <v>0.125</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="7" t="inlineStr"/>
@@ -1743,28 +1743,28 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>0376</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>IAB</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="E29" s="8" t="n">
-        <v>0.09380000000000001</v>
+        <v>1.32</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>-0.0222</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>1913600</v>
+        <v>3049100</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.43</v>
+        <v>1.76</v>
       </c>
       <c r="H29" t="n">
-        <v>64.86</v>
+        <v>54.18</v>
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
@@ -1772,10 +1772,10 @@
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>5.827</v>
+        <v>1.275</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>5.777</v>
+        <v>1.32</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="7" t="inlineStr"/>
@@ -1788,28 +1788,28 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>0.925</v>
-      </c>
-      <c r="E30" s="8" t="n">
-        <v>0.0393</v>
+        <v>3.7</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>-0.0186</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>1564700</v>
+        <v>2840100</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.54</v>
+        <v>0.25</v>
       </c>
       <c r="H30" t="n">
-        <v>51.74</v>
+        <v>56.35</v>
       </c>
       <c r="I30" s="9" t="inlineStr">
         <is>
@@ -1817,10 +1817,10 @@
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.913</v>
+        <v>3.6</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0.965</v>
+        <v>2.739</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="7" t="inlineStr"/>
@@ -1833,39 +1833,39 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>MRCB</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="E31" s="8" t="n">
-        <v>0.0182</v>
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="E31" s="10" t="n">
+        <v>0.0062</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>1557800</v>
+        <v>2763000</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.22</v>
+        <v>0.17</v>
       </c>
       <c r="H31" t="n">
-        <v>37.22</v>
-      </c>
-      <c r="I31" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.76</v>
+      </c>
+      <c r="I31" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.289</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0.307</v>
+        <v>0.806</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="7" t="inlineStr"/>
@@ -1878,28 +1878,28 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>5260</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>OWG</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E32" s="8" t="n">
-        <v>0.0526</v>
+        <v>0.64</v>
+      </c>
+      <c r="E32" s="10" t="n">
+        <v>0.024</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>1552800</v>
+        <v>2706400</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>2.43</v>
+        <v>0.14</v>
       </c>
       <c r="H32" t="n">
-        <v>61.12</v>
+        <v>64.14</v>
       </c>
       <c r="I32" s="6" t="inlineStr">
         <is>
@@ -1907,10 +1907,10 @@
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.186</v>
+        <v>0.582</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0.188</v>
+        <v>0.519</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="7" t="inlineStr"/>
@@ -1923,28 +1923,28 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E33" s="8" t="n">
-        <v>0.016</v>
+        <v>6.7</v>
+      </c>
+      <c r="E33" s="10" t="n">
+        <v>0.102</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>1529400</v>
+        <v>2702900</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.08</v>
+        <v>0.6</v>
       </c>
       <c r="H33" t="n">
-        <v>63.49</v>
+        <v>65.41</v>
       </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
@@ -1952,10 +1952,10 @@
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.581</v>
+        <v>5.832</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0.518</v>
+        <v>5.778</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="7" t="inlineStr"/>
@@ -1968,40 +1968,36 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>0468</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>UNIPAC</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>0.225</v>
+        <v>0.25</v>
       </c>
       <c r="E34" s="8" t="n">
-        <v>0.0227</v>
+        <v>0</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>1516500</v>
+        <v>2499400</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.06</v>
+        <v>0.21</v>
       </c>
       <c r="H34" t="n">
-        <v>33.07</v>
-      </c>
-      <c r="I34" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="n">
-        <v>0.249</v>
-      </c>
-      <c r="K34" s="2" t="n">
-        <v>0.304</v>
-      </c>
+        <v>28.11</v>
+      </c>
+      <c r="I34" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="n"/>
+      <c r="K34" s="2" t="n"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="7" t="inlineStr"/>
     </row>
@@ -2013,39 +2009,39 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="E35" s="8" t="n">
-        <v>0.0035</v>
+        <v>9.789999999999999</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>-0.001</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>1384600</v>
+        <v>2475400</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.44</v>
+        <v>0.2</v>
       </c>
       <c r="H35" t="n">
-        <v>75.53</v>
-      </c>
-      <c r="I35" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>29.86</v>
+      </c>
+      <c r="I35" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>2.638</v>
+        <v>10.02</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>2.285</v>
+        <v>10.213</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="7" t="inlineStr"/>
@@ -2058,39 +2054,39 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>9.81</v>
-      </c>
-      <c r="E36" s="8" t="n">
-        <v>0.001</v>
+        <v>1.14</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>-0.0256</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>1383800</v>
+        <v>2461000</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.11</v>
+        <v>0.22</v>
       </c>
       <c r="H36" t="n">
-        <v>31.22</v>
-      </c>
-      <c r="I36" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.21</v>
+      </c>
+      <c r="I36" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>10.022</v>
+        <v>1.162</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>10.213</v>
+        <v>1.119</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="7" t="inlineStr"/>
@@ -2103,39 +2099,39 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>0338</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>KOPI</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>0.785</v>
+        <v>0.93</v>
       </c>
       <c r="E37" s="10" t="n">
-        <v>-0.0063</v>
+        <v>0.0449</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>1359000</v>
+        <v>2442000</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.17</v>
+        <v>0.85</v>
       </c>
       <c r="H37" t="n">
-        <v>52.68</v>
-      </c>
-      <c r="I37" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.36</v>
+      </c>
+      <c r="I37" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.778</v>
+        <v>0.913</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0.773</v>
+        <v>0.965</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="7" t="inlineStr"/>
@@ -2148,28 +2144,28 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E38" s="8" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.98</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>-0.0151</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>1320800</v>
+        <v>2430600</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.09</v>
+        <v>0.75</v>
       </c>
       <c r="H38" t="n">
-        <v>50.25</v>
+        <v>84.12</v>
       </c>
       <c r="I38" s="6" t="inlineStr">
         <is>
@@ -2177,10 +2173,10 @@
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.775</v>
+        <v>0.656</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>0.775</v>
+        <v>0.479</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="7" t="inlineStr"/>
@@ -2193,39 +2189,39 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0267</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ECA</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="E39" s="8" t="n">
-        <v>0.0411</v>
+        <v>5.01</v>
+      </c>
+      <c r="E39" s="10" t="n">
+        <v>0.0121</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>1288900</v>
+        <v>2256700</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.38</v>
+        <v>0.09</v>
       </c>
       <c r="H39" t="n">
-        <v>53.04</v>
-      </c>
-      <c r="I39" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.56</v>
+      </c>
+      <c r="I39" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.366</v>
+        <v>4.918</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0.374</v>
+        <v>4.651</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="7" t="inlineStr"/>
@@ -2238,39 +2234,39 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>5326</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>99SMART</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="E40" s="8" t="n">
-        <v>0.0155</v>
+        <v>3.29</v>
+      </c>
+      <c r="E40" s="10" t="n">
+        <v>0.0545</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>1236500</v>
+        <v>2203100</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.15</v>
+        <v>0.52</v>
       </c>
       <c r="H40" t="n">
-        <v>57.2</v>
-      </c>
-      <c r="I40" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.26</v>
+      </c>
+      <c r="I40" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.963</v>
+        <v>3.202</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0.821</v>
+        <v>3.391</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="7" t="inlineStr"/>
@@ -2283,39 +2279,39 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.37</v>
       </c>
       <c r="E41" s="8" t="n">
-        <v>0.0062</v>
+        <v>0</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>1151000</v>
+        <v>2196900</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.33</v>
       </c>
       <c r="H41" t="n">
-        <v>54.76</v>
-      </c>
-      <c r="I41" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.56</v>
+      </c>
+      <c r="I41" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.368</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>0.806</v>
+        <v>0.368</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="7" t="inlineStr"/>
@@ -2328,28 +2324,28 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="E42" s="8" t="n">
-        <v>0.0331</v>
+        <v>2.75</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>-0.0108</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>1073400</v>
+        <v>2190700</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.32</v>
+        <v>0.12</v>
       </c>
       <c r="H42" t="n">
-        <v>76.55</v>
+        <v>62.29</v>
       </c>
       <c r="I42" s="6" t="inlineStr">
         <is>
@@ -2357,10 +2353,10 @@
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>1.025</v>
+        <v>2.624</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0.86</v>
+        <v>2.496</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="7" t="inlineStr"/>
@@ -2373,28 +2369,28 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0450</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>MFGROUP</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="E43" s="10" t="n">
-        <v>-0.0185</v>
+        <v>0.22</v>
+      </c>
+      <c r="E43" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>1062000</v>
+        <v>2064900</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>1.09</v>
+        <v>0.08</v>
       </c>
       <c r="H43" t="n">
-        <v>54.17</v>
+        <v>29.99</v>
       </c>
       <c r="I43" s="9" t="inlineStr">
         <is>
@@ -2402,10 +2398,10 @@
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.262</v>
+        <v>0.249</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>0.264</v>
+        <v>0.304</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="7" t="inlineStr"/>
@@ -2418,28 +2414,28 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0104</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>GENETEC</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="E44" s="10" t="n">
-        <v>-0.0149</v>
+        <v>0.0388</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>1049300</v>
+        <v>2057000</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.19</v>
+        <v>0.45</v>
       </c>
       <c r="H44" t="n">
-        <v>52.01</v>
+        <v>84.47</v>
       </c>
       <c r="I44" s="6" t="inlineStr">
         <is>
@@ -2447,10 +2443,10 @@
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.326</v>
+        <v>0.516</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0.338</v>
+        <v>0.443</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="7" t="inlineStr"/>
@@ -2463,39 +2459,39 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>2.77</v>
+        <v>0.97</v>
       </c>
       <c r="E45" s="10" t="n">
-        <v>-0.0036</v>
+        <v>0.0052</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>1043500</v>
+        <v>1981300</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.06</v>
+        <v>0.24</v>
       </c>
       <c r="H45" t="n">
-        <v>64.19</v>
-      </c>
-      <c r="I45" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>55.95</v>
+      </c>
+      <c r="I45" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>2.625</v>
+        <v>0.962</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>2.497</v>
+        <v>0.821</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="7" t="inlineStr"/>
@@ -2508,39 +2504,39 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0249</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>LGMS</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="E46" s="8" t="n">
-        <v>0.0175</v>
+        <v>2.83</v>
+      </c>
+      <c r="E46" s="10" t="n">
+        <v>0.018</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>1012600</v>
+        <v>1966200</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>1.13</v>
+        <v>0.14</v>
       </c>
       <c r="H46" t="n">
-        <v>73.84</v>
-      </c>
-      <c r="I46" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>55.1</v>
+      </c>
+      <c r="I46" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.524</v>
+        <v>2.793</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>0.504</v>
+        <v>2.693</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="7" t="inlineStr"/>
@@ -2553,39 +2549,39 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="E47" s="8" t="n">
-        <v>0.0101</v>
+        <v>1.27</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>-0.007800000000000001</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>998100</v>
+        <v>1943300</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.04</v>
+        <v>0.18</v>
       </c>
       <c r="H47" t="n">
-        <v>58.12</v>
-      </c>
-      <c r="I47" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.81</v>
+      </c>
+      <c r="I47" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>4.917</v>
+        <v>1.321</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>4.651</v>
+        <v>1.305</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="7" t="inlineStr"/>
@@ -2598,28 +2594,28 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0045</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>SSB8</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>0.68</v>
+        <v>0.79</v>
       </c>
       <c r="E48" s="8" t="n">
-        <v>0.0149</v>
+        <v>0</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>965100</v>
+        <v>1824000</v>
       </c>
       <c r="G48" s="5" t="n">
         <v>0.23</v>
       </c>
       <c r="H48" t="n">
-        <v>66.18000000000001</v>
+        <v>54.24</v>
       </c>
       <c r="I48" s="6" t="inlineStr">
         <is>
@@ -2627,10 +2623,10 @@
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.638</v>
+        <v>0.779</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0.601</v>
+        <v>0.773</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="7" t="inlineStr"/>
@@ -2643,28 +2639,28 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>0.525</v>
-      </c>
-      <c r="E49" s="8" t="n">
-        <v>0.0294</v>
+        <v>4.56</v>
+      </c>
+      <c r="E49" s="10" t="n">
+        <v>0.0022</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>964000</v>
+        <v>1810800</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.06</v>
+        <v>0.12</v>
       </c>
       <c r="H49" t="n">
-        <v>55.9</v>
+        <v>27.57</v>
       </c>
       <c r="I49" s="9" t="inlineStr">
         <is>
@@ -2672,10 +2668,10 @@
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.512</v>
+        <v>4.721</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0.436</v>
+        <v>4.891</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="7" t="inlineStr"/>
@@ -2688,39 +2684,39 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0271</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>WELLS</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="E50" s="8" t="n">
-        <v>0.0291</v>
+        <v>0.455</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>-0.0109</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>963600</v>
+        <v>1777100</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.87</v>
+        <v>0.26</v>
       </c>
       <c r="H50" t="n">
-        <v>26.64</v>
-      </c>
-      <c r="I50" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.71</v>
+      </c>
+      <c r="I50" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.582</v>
+        <v>0.426</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>0.622</v>
+        <v>0.413</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="7" t="inlineStr"/>
@@ -2733,28 +2729,28 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="E51" s="8" t="n">
-        <v>0.0072</v>
+        <v>0.525</v>
+      </c>
+      <c r="E51" s="10" t="n">
+        <v>0.0294</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>957700</v>
+        <v>1739500</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="H51" t="n">
-        <v>52.82</v>
+        <v>55.9</v>
       </c>
       <c r="I51" s="9" t="inlineStr">
         <is>
@@ -2762,10 +2758,10 @@
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>2.791</v>
+        <v>0.512</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>2.693</v>
+        <v>0.436</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="7" t="inlineStr"/>
@@ -2778,39 +2774,39 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>0268</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>L&amp;PBHD</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>1.23</v>
+        <v>0.24</v>
       </c>
       <c r="E52" s="10" t="n">
-        <v>-0.008100000000000001</v>
+        <v>0.09089999999999999</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>928500</v>
+        <v>1719600</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.1</v>
+        <v>0.86</v>
       </c>
       <c r="H52" t="n">
-        <v>32.43</v>
-      </c>
-      <c r="I52" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>77.70999999999999</v>
+      </c>
+      <c r="I52" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>1.284</v>
+        <v>0.206</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>1.386</v>
+        <v>0.171</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="7" t="inlineStr"/>
@@ -2823,39 +2819,39 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="E53" s="8" t="n">
-        <v>0.0108</v>
+        <v>2.86</v>
+      </c>
+      <c r="E53" s="10" t="n">
+        <v>0.0035</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>915000</v>
+        <v>1715200</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
       <c r="H53" t="n">
-        <v>55.4</v>
-      </c>
-      <c r="I53" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>75.53</v>
+      </c>
+      <c r="I53" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.923</v>
+        <v>2.638</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0.85</v>
+        <v>2.285</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="7" t="inlineStr"/>
@@ -2868,28 +2864,28 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>CNERGEN</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="E54" s="8" t="n">
-        <v>0.0273</v>
+        <v>1.25</v>
+      </c>
+      <c r="E54" s="10" t="n">
+        <v>0.0331</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>895500</v>
+        <v>1698500</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.09</v>
+        <v>0.5</v>
       </c>
       <c r="H54" t="n">
-        <v>66.05</v>
+        <v>76.55</v>
       </c>
       <c r="I54" s="6" t="inlineStr">
         <is>
@@ -2897,10 +2893,10 @@
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>1.07</v>
+        <v>1.025</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>0.917</v>
+        <v>0.86</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="7" t="inlineStr"/>
@@ -2913,28 +2909,28 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>MRCB</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>4.17</v>
+        <v>0.28</v>
       </c>
       <c r="E55" s="10" t="n">
-        <v>-0.0211</v>
+        <v>0.0182</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>861800</v>
+        <v>1600800</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.11</v>
+        <v>0.23</v>
       </c>
       <c r="H55" t="n">
-        <v>41.58</v>
+        <v>37.22</v>
       </c>
       <c r="I55" s="9" t="inlineStr">
         <is>
@@ -2942,10 +2938,10 @@
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>4.363</v>
+        <v>0.289</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>4.463</v>
+        <v>0.307</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="7" t="inlineStr"/>
@@ -2958,39 +2954,39 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>0267</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>ECA</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>0.805</v>
-      </c>
-      <c r="E56" s="8" t="n">
-        <v>0.0321</v>
+        <v>0.38</v>
+      </c>
+      <c r="E56" s="10" t="n">
+        <v>0.0411</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>839100</v>
+        <v>1569100</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.12</v>
+        <v>0.47</v>
       </c>
       <c r="H56" t="n">
-        <v>65.55</v>
-      </c>
-      <c r="I56" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.04</v>
+      </c>
+      <c r="I56" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.736</v>
+        <v>0.366</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>0.652</v>
+        <v>0.374</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="7" t="inlineStr"/>
@@ -3003,28 +2999,28 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0359</t>
+          <t>5260</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>HKB</t>
+          <t>OWG</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>0.8149999999999999</v>
-      </c>
-      <c r="E57" s="8" t="n">
-        <v>0.0124</v>
+        <v>0.2</v>
+      </c>
+      <c r="E57" s="10" t="n">
+        <v>0.0526</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>818300</v>
+        <v>1563300</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.37</v>
+        <v>2.45</v>
       </c>
       <c r="H57" t="n">
-        <v>81.81</v>
+        <v>61.12</v>
       </c>
       <c r="I57" s="6" t="inlineStr">
         <is>
@@ -3032,10 +3028,10 @@
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.679</v>
+        <v>0.186</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>0.622</v>
+        <v>0.188</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="7" t="inlineStr"/>
@@ -3048,39 +3044,39 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>5141</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>DAYANG</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="E58" s="10" t="n">
-        <v>-0.0069</v>
+        <v>0.33</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>-0.0149</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>800800</v>
+        <v>1561200</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.36</v>
+        <v>0.28</v>
       </c>
       <c r="H58" t="n">
-        <v>41.86</v>
-      </c>
-      <c r="I58" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.01</v>
+      </c>
+      <c r="I58" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>1.461</v>
+        <v>0.326</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>1.495</v>
+        <v>0.338</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="7" t="inlineStr"/>
@@ -3093,39 +3089,39 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>7081</t>
+          <t>0045</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>SSB8</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>0.925</v>
+        <v>0.67</v>
       </c>
       <c r="E59" s="8" t="n">
-        <v>0.0054</v>
+        <v>0</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>798100</v>
+        <v>1559700</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.34</v>
+        <v>0.38</v>
       </c>
       <c r="H59" t="n">
-        <v>22.43</v>
-      </c>
-      <c r="I59" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64</v>
+      </c>
+      <c r="I59" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>1.037</v>
+        <v>0.637</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>1.119</v>
+        <v>0.601</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="7" t="inlineStr"/>
@@ -3138,39 +3134,39 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>IOICORP</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>1.06</v>
+        <v>4.59</v>
       </c>
       <c r="E60" s="10" t="n">
-        <v>-0.009300000000000001</v>
+        <v>0.0066</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>783700</v>
+        <v>1550500</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.05</v>
+        <v>0.16</v>
       </c>
       <c r="H60" t="n">
-        <v>48.94</v>
-      </c>
-      <c r="I60" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.75</v>
+      </c>
+      <c r="I60" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>1.071</v>
+        <v>4.676</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>1.037</v>
+        <v>4.62</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="7" t="inlineStr"/>
@@ -3183,28 +3179,28 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>0.9350000000000001</v>
-      </c>
-      <c r="E61" s="8" t="n">
-        <v>0.0054</v>
+        <v>7.25</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>-0.0014</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>776700</v>
+        <v>1484400</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.15</v>
+        <v>0.11</v>
       </c>
       <c r="H61" t="n">
-        <v>65.34999999999999</v>
+        <v>31.19</v>
       </c>
       <c r="I61" s="9" t="inlineStr">
         <is>
@@ -3212,10 +3208,10 @@
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.909</v>
+        <v>7.639</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>0.863</v>
+        <v>7.729</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="7" t="inlineStr"/>
@@ -3228,28 +3224,28 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>5326</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>99SMART</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="E62" s="8" t="n">
-        <v>0.0288</v>
+        <v>1.12</v>
+      </c>
+      <c r="E62" s="10" t="n">
+        <v>0.0182</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>776300</v>
+        <v>1459100</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.18</v>
+        <v>0.15</v>
       </c>
       <c r="H62" t="n">
-        <v>47.87</v>
+        <v>64.88</v>
       </c>
       <c r="I62" s="6" t="inlineStr">
         <is>
@@ -3257,10 +3253,10 @@
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>3.194</v>
+        <v>1.069</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>3.389</v>
+        <v>0.916</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="7" t="inlineStr"/>
@@ -3273,39 +3269,39 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>NEXG</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="E63" s="8" t="n">
-        <v>0.004699999999999999</v>
+        <v>0.3</v>
+      </c>
+      <c r="E63" s="10" t="n">
+        <v>0.0345</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>760700</v>
+        <v>1454500</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.05</v>
+        <v>0.12</v>
       </c>
       <c r="H63" t="n">
-        <v>42.31</v>
-      </c>
-      <c r="I63" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.14</v>
+      </c>
+      <c r="I63" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>2.226</v>
+        <v>0.292</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>2.213</v>
+        <v>0.281</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="7" t="inlineStr"/>
@@ -3318,28 +3314,28 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="E64" s="8" t="n">
-        <v>0.0187</v>
+        <v>0.45</v>
+      </c>
+      <c r="E64" s="10" t="n">
+        <v>0.0227</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>737100</v>
+        <v>1426700</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
       <c r="H64" t="n">
-        <v>59.25</v>
+        <v>51.11</v>
       </c>
       <c r="I64" s="6" t="inlineStr">
         <is>
@@ -3347,10 +3343,10 @@
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>2.631</v>
+        <v>0.45</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>2.581</v>
+        <v>0.426</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="7" t="inlineStr"/>
@@ -3363,28 +3359,28 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>0273</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>VLB</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>7.11</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E65" s="10" t="n">
-        <v>-0.005600000000000001</v>
+        <v>0.0108</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>734800</v>
+        <v>1391600</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>0.08</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H65" t="n">
-        <v>18.64</v>
+        <v>55.4</v>
       </c>
       <c r="I65" s="9" t="inlineStr">
         <is>
@@ -3392,10 +3388,10 @@
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>7.595</v>
+        <v>0.923</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>8.089</v>
+        <v>0.85</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="7" t="inlineStr"/>
@@ -3408,39 +3404,39 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>0.67</v>
+        <v>1.24</v>
       </c>
       <c r="E66" s="8" t="n">
-        <v>0.0388</v>
+        <v>0</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>712300</v>
+        <v>1362500</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="H66" t="n">
-        <v>84.47</v>
-      </c>
-      <c r="I66" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.91</v>
+      </c>
+      <c r="I66" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.516</v>
+        <v>1.285</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>0.443</v>
+        <v>1.386</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="7" t="inlineStr"/>
@@ -3453,28 +3449,28 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>0359</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>HKB</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>0.715</v>
-      </c>
-      <c r="E67" s="8" t="n">
-        <v>0.0214</v>
+        <v>0.825</v>
+      </c>
+      <c r="E67" s="10" t="n">
+        <v>0.0248</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>658100</v>
+        <v>1283400</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="H67" t="n">
-        <v>62.82</v>
+        <v>82.5</v>
       </c>
       <c r="I67" s="6" t="inlineStr">
         <is>
@@ -3482,10 +3478,10 @@
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.671</v>
+        <v>0.68</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>0.607</v>
+        <v>0.622</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="7" t="inlineStr"/>
@@ -3498,28 +3494,28 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>AWC</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="E68" s="10" t="n">
-        <v>-0.007900000000000001</v>
+        <v>7.11</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>-0.005600000000000001</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>621100</v>
+        <v>1253100</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>0.28</v>
+        <v>0.13</v>
       </c>
       <c r="H68" t="n">
-        <v>56.48</v>
+        <v>18.64</v>
       </c>
       <c r="I68" s="9" t="inlineStr">
         <is>
@@ -3527,10 +3523,10 @@
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.619</v>
+        <v>7.595</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>0.529</v>
+        <v>8.089</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="7" t="inlineStr"/>
@@ -3543,39 +3539,39 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>7.25</v>
-      </c>
-      <c r="E69" s="10" t="n">
-        <v>-0.0014</v>
+        <v>0.35</v>
+      </c>
+      <c r="E69" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>609400</v>
+        <v>1218500</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>0.04</v>
+        <v>0.16</v>
       </c>
       <c r="H69" t="n">
-        <v>31.19</v>
-      </c>
-      <c r="I69" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.58</v>
+      </c>
+      <c r="I69" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>7.639</v>
+        <v>0.343</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>7.729</v>
+        <v>0.324</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="7" t="inlineStr"/>
@@ -3588,39 +3584,39 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="E70" s="3" t="n">
-        <v>0</v>
+        <v>0.385</v>
+      </c>
+      <c r="E70" s="10" t="n">
+        <v>0.0267</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>579500</v>
+        <v>1200900</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="H70" t="n">
-        <v>54.4</v>
-      </c>
-      <c r="I70" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>69.33</v>
+      </c>
+      <c r="I70" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.639</v>
+        <v>0.354</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>0.611</v>
+        <v>0.322</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="7" t="inlineStr"/>
@@ -3633,39 +3629,39 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>0296</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>HEGROUP</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>2.1</v>
+        <v>1.12</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>0</v>
+        <v>-0.0175</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>576000</v>
+        <v>1186900</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>0.03</v>
+        <v>0.24</v>
       </c>
       <c r="H71" t="n">
-        <v>50.69</v>
-      </c>
-      <c r="I71" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66.73</v>
+      </c>
+      <c r="I71" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>2.098</v>
+        <v>1.057</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>2.08</v>
+        <v>0.891</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="7" t="inlineStr"/>
@@ -3678,28 +3674,28 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>SEG</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E72" s="10" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.55</v>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>-0.009000000000000001</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>550100</v>
+        <v>1186500</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>0.43</v>
+        <v>0.22</v>
       </c>
       <c r="H72" t="n">
-        <v>37.72</v>
+        <v>33.2</v>
       </c>
       <c r="I72" s="9" t="inlineStr">
         <is>
@@ -3707,10 +3703,10 @@
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.632</v>
+        <v>0.592</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>0.63</v>
+        <v>0.641</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="7" t="inlineStr"/>
@@ -3723,28 +3719,28 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>CPETECH</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="E73" s="8" t="n">
-        <v>0.015</v>
+        <v>0.71</v>
+      </c>
+      <c r="E73" s="10" t="n">
+        <v>0.0143</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>541200</v>
+        <v>1179600</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="H73" t="n">
-        <v>57.71</v>
+        <v>62.05</v>
       </c>
       <c r="I73" s="6" t="inlineStr">
         <is>
@@ -3752,10 +3748,10 @@
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>1.294</v>
+        <v>0.671</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>1.194</v>
+        <v>0.607</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="7" t="inlineStr"/>
@@ -3768,28 +3764,28 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>5162</t>
+          <t>0249</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>VSTECS</t>
+          <t>LGMS</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="E74" s="8" t="n">
-        <v>0.0299</v>
+        <v>0.58</v>
+      </c>
+      <c r="E74" s="10" t="n">
+        <v>0.0175</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>533500</v>
+        <v>1168900</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>0.31</v>
+        <v>1.3</v>
       </c>
       <c r="H74" t="n">
-        <v>56.36</v>
+        <v>73.84</v>
       </c>
       <c r="I74" s="6" t="inlineStr">
         <is>
@@ -3797,10 +3793,10 @@
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>1.663</v>
+        <v>0.524</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>1.678</v>
+        <v>0.504</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="7" t="inlineStr"/>
@@ -3813,28 +3809,28 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>1.28</v>
+        <v>4.22</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>0</v>
+        <v>-0.009399999999999999</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>513400</v>
+        <v>1165300</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>0.05</v>
+        <v>0.15</v>
       </c>
       <c r="H75" t="n">
-        <v>43.08</v>
+        <v>43.07</v>
       </c>
       <c r="I75" s="9" t="inlineStr">
         <is>
@@ -3842,16 +3838,1771 @@
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>1.322</v>
+        <v>4.368</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>1.305</v>
+        <v>4.464</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="7" t="inlineStr"/>
     </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>0310</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>UUE</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="E76" s="10" t="n">
+        <v>0.0385</v>
+      </c>
+      <c r="F76" s="4" t="n">
+        <v>1153900</v>
+      </c>
+      <c r="G76" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H76" t="n">
+        <v>66.09999999999999</v>
+      </c>
+      <c r="I76" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="n">
+        <v>0.737</v>
+      </c>
+      <c r="K76" s="2" t="n">
+        <v>0.652</v>
+      </c>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" s="7" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>5555</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>SUNMED</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="E77" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" s="4" t="n">
+        <v>1123600</v>
+      </c>
+      <c r="G77" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H77" t="n">
+        <v>50.69</v>
+      </c>
+      <c r="I77" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="n">
+        <v>2.098</v>
+      </c>
+      <c r="K77" s="2" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" s="7" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>5078</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>M&amp;G</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="E78" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F78" s="4" t="n">
+        <v>1107600</v>
+      </c>
+      <c r="G78" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H78" t="n">
+        <v>57.67</v>
+      </c>
+      <c r="I78" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="K78" s="2" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" s="7" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>0251</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>SFPTECH</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="E79" s="10" t="n">
+        <v>0.0172</v>
+      </c>
+      <c r="F79" s="4" t="n">
+        <v>1104200</v>
+      </c>
+      <c r="G79" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H79" t="n">
+        <v>57.36</v>
+      </c>
+      <c r="I79" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="n">
+        <v>0.278</v>
+      </c>
+      <c r="K79" s="2" t="n">
+        <v>0.303</v>
+      </c>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" s="7" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>0208</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>GREATEC</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="E80" s="10" t="n">
+        <v>0.0149</v>
+      </c>
+      <c r="F80" s="4" t="n">
+        <v>1079400</v>
+      </c>
+      <c r="G80" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H80" t="n">
+        <v>58.63</v>
+      </c>
+      <c r="I80" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="K80" s="2" t="n">
+        <v>2.581</v>
+      </c>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" s="7" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>4677</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>YTL</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="E81" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F81" s="4" t="n">
+        <v>1075100</v>
+      </c>
+      <c r="G81" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H81" t="n">
+        <v>41.24</v>
+      </c>
+      <c r="I81" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="n">
+        <v>2.225</v>
+      </c>
+      <c r="K81" s="2" t="n">
+        <v>2.212</v>
+      </c>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" s="7" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>0321</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>SDCG</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="n">
+        <v>0.805</v>
+      </c>
+      <c r="E82" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" s="4" t="n">
+        <v>1071700</v>
+      </c>
+      <c r="G82" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H82" t="n">
+        <v>70.15000000000001</v>
+      </c>
+      <c r="I82" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="n">
+        <v>0.785</v>
+      </c>
+      <c r="K82" s="2" t="n">
+        <v>0.764</v>
+      </c>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" s="7" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>7579</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>AWC</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="E83" s="3" t="n">
+        <v>-0.007900000000000001</v>
+      </c>
+      <c r="F83" s="4" t="n">
+        <v>1064800</v>
+      </c>
+      <c r="G83" s="5" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="H83" t="n">
+        <v>56.48</v>
+      </c>
+      <c r="I83" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="n">
+        <v>0.619</v>
+      </c>
+      <c r="K83" s="2" t="n">
+        <v>0.529</v>
+      </c>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" s="7" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>0450</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>MFGROUP</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="n">
+        <v>0.265</v>
+      </c>
+      <c r="E84" s="3" t="n">
+        <v>-0.0185</v>
+      </c>
+      <c r="F84" s="4" t="n">
+        <v>1062000</v>
+      </c>
+      <c r="G84" s="5" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="H84" t="n">
+        <v>54.17</v>
+      </c>
+      <c r="I84" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="n">
+        <v>0.262</v>
+      </c>
+      <c r="K84" s="2" t="n">
+        <v>0.264</v>
+      </c>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" s="7" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>5168</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>HARTA</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="E85" s="3" t="n">
+        <v>-0.009300000000000001</v>
+      </c>
+      <c r="F85" s="4" t="n">
+        <v>1028100</v>
+      </c>
+      <c r="G85" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H85" t="n">
+        <v>48.94</v>
+      </c>
+      <c r="I85" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="n">
+        <v>1.071</v>
+      </c>
+      <c r="K85" s="2" t="n">
+        <v>1.037</v>
+      </c>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" s="7" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>0259</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>SNS</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="n">
+        <v>0.535</v>
+      </c>
+      <c r="E86" s="10" t="n">
+        <v>0.009399999999999999</v>
+      </c>
+      <c r="F86" s="4" t="n">
+        <v>998500</v>
+      </c>
+      <c r="G86" s="5" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H86" t="n">
+        <v>55.09</v>
+      </c>
+      <c r="I86" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="n">
+        <v>0.522</v>
+      </c>
+      <c r="K86" s="2" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" s="7" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>0271</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>WELLS</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="E87" s="10" t="n">
+        <v>0.0291</v>
+      </c>
+      <c r="F87" s="4" t="n">
+        <v>963600</v>
+      </c>
+      <c r="G87" s="5" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="H87" t="n">
+        <v>26.64</v>
+      </c>
+      <c r="I87" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="n">
+        <v>0.582</v>
+      </c>
+      <c r="K87" s="2" t="n">
+        <v>0.622</v>
+      </c>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" s="7" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>5337</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>ECOSHOP</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="E88" s="10" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="F88" s="4" t="n">
+        <v>943700</v>
+      </c>
+      <c r="G88" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H88" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="I88" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="n">
+        <v>1.461</v>
+      </c>
+      <c r="K88" s="2" t="n">
+        <v>1.469</v>
+      </c>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" s="7" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>0318</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>ELRIDGE</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="E89" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" s="4" t="n">
+        <v>930100</v>
+      </c>
+      <c r="G89" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H89" t="n">
+        <v>63.88</v>
+      </c>
+      <c r="I89" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="n">
+        <v>0.908</v>
+      </c>
+      <c r="K89" s="2" t="n">
+        <v>0.863</v>
+      </c>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" s="7" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>5184</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>CYPARK</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E90" s="10" t="n">
+        <v>0.0191</v>
+      </c>
+      <c r="F90" s="4" t="n">
+        <v>915100</v>
+      </c>
+      <c r="G90" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H90" t="n">
+        <v>57.83</v>
+      </c>
+      <c r="I90" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="n">
+        <v>0.768</v>
+      </c>
+      <c r="K90" s="2" t="n">
+        <v>0.712</v>
+      </c>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" s="7" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>3182</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>GENTING</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="E91" s="3" t="n">
+        <v>-0.0054</v>
+      </c>
+      <c r="F91" s="4" t="n">
+        <v>895800</v>
+      </c>
+      <c r="G91" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H91" t="n">
+        <v>36</v>
+      </c>
+      <c r="I91" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="n">
+        <v>1.894</v>
+      </c>
+      <c r="K91" s="2" t="n">
+        <v>2.026</v>
+      </c>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" s="7" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>5141</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>DAYANG</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="E92" s="3" t="n">
+        <v>-0.0069</v>
+      </c>
+      <c r="F92" s="4" t="n">
+        <v>877500</v>
+      </c>
+      <c r="G92" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H92" t="n">
+        <v>41.86</v>
+      </c>
+      <c r="I92" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="n">
+        <v>1.461</v>
+      </c>
+      <c r="K92" s="2" t="n">
+        <v>1.495</v>
+      </c>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" s="7" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>0196</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>QES</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="E93" s="10" t="n">
+        <v>0.0157</v>
+      </c>
+      <c r="F93" s="4" t="n">
+        <v>855000</v>
+      </c>
+      <c r="G93" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H93" t="n">
+        <v>64.34999999999999</v>
+      </c>
+      <c r="I93" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="n">
+        <v>0.597</v>
+      </c>
+      <c r="K93" s="2" t="n">
+        <v>0.582</v>
+      </c>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" s="7" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>7081</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>PHARMA</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="E94" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F94" s="4" t="n">
+        <v>800100</v>
+      </c>
+      <c r="G94" s="5" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H94" t="n">
+        <v>20.91</v>
+      </c>
+      <c r="I94" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="n">
+        <v>1.037</v>
+      </c>
+      <c r="K94" s="2" t="n">
+        <v>1.119</v>
+      </c>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" s="7" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>8052</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>CGB</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="n">
+        <v>0.865</v>
+      </c>
+      <c r="E95" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F95" s="4" t="n">
+        <v>799500</v>
+      </c>
+      <c r="G95" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H95" t="n">
+        <v>46.68</v>
+      </c>
+      <c r="I95" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="n">
+        <v>0.868</v>
+      </c>
+      <c r="K95" s="2" t="n">
+        <v>0.869</v>
+      </c>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" s="7" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>6742</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>YTLPOWR</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="E96" s="10" t="n">
+        <v>0.0036</v>
+      </c>
+      <c r="F96" s="4" t="n">
+        <v>790900</v>
+      </c>
+      <c r="G96" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H96" t="n">
+        <v>49.97</v>
+      </c>
+      <c r="I96" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="n">
+        <v>5.634</v>
+      </c>
+      <c r="K96" s="2" t="n">
+        <v>5.307</v>
+      </c>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" s="7" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>8583</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>MAHSING</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="n">
+        <v>0.955</v>
+      </c>
+      <c r="E97" s="10" t="n">
+        <v>0.0106</v>
+      </c>
+      <c r="F97" s="4" t="n">
+        <v>786000</v>
+      </c>
+      <c r="G97" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H97" t="n">
+        <v>32.16</v>
+      </c>
+      <c r="I97" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="n">
+        <v>0.996</v>
+      </c>
+      <c r="K97" s="2" t="n">
+        <v>1.066</v>
+      </c>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" s="7" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>5162</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>VSTECS</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="E98" s="10" t="n">
+        <v>0.0359</v>
+      </c>
+      <c r="F98" s="4" t="n">
+        <v>732100</v>
+      </c>
+      <c r="G98" s="5" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="H98" t="n">
+        <v>57.25</v>
+      </c>
+      <c r="I98" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="n">
+        <v>1.664</v>
+      </c>
+      <c r="K98" s="2" t="n">
+        <v>1.678</v>
+      </c>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" s="7" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>0215</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>SLVEST</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="E99" s="10" t="n">
+        <v>0.0144</v>
+      </c>
+      <c r="F99" s="4" t="n">
+        <v>723700</v>
+      </c>
+      <c r="G99" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H99" t="n">
+        <v>64.02</v>
+      </c>
+      <c r="I99" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="n">
+        <v>3.963</v>
+      </c>
+      <c r="K99" s="2" t="n">
+        <v>3.442</v>
+      </c>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" s="7" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>0277</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>CLOUDPT</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="n">
+        <v>0.515</v>
+      </c>
+      <c r="E100" s="10" t="n">
+        <v>0.0098</v>
+      </c>
+      <c r="F100" s="4" t="n">
+        <v>715000</v>
+      </c>
+      <c r="G100" s="5" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="H100" t="n">
+        <v>62.85</v>
+      </c>
+      <c r="I100" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="n">
+        <v>0.489</v>
+      </c>
+      <c r="K100" s="2" t="n">
+        <v>0.479</v>
+      </c>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" s="7" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>5347</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>TENAGA</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="n">
+        <v>12.98</v>
+      </c>
+      <c r="E101" s="10" t="n">
+        <v>0.0062</v>
+      </c>
+      <c r="F101" s="4" t="n">
+        <v>708300</v>
+      </c>
+      <c r="G101" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H101" t="n">
+        <v>43.26</v>
+      </c>
+      <c r="I101" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="n">
+        <v>13.038</v>
+      </c>
+      <c r="K101" s="2" t="n">
+        <v>13.573</v>
+      </c>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" s="7" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>5317</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>CPETECH</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="E102" s="10" t="n">
+        <v>0.0226</v>
+      </c>
+      <c r="F102" s="4" t="n">
+        <v>699800</v>
+      </c>
+      <c r="G102" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H102" t="n">
+        <v>58.46</v>
+      </c>
+      <c r="I102" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="n">
+        <v>1.295</v>
+      </c>
+      <c r="K102" s="2" t="n">
+        <v>1.194</v>
+      </c>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" s="7" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>7233</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>DUFU</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="E103" s="3" t="n">
+        <v>-0.0031</v>
+      </c>
+      <c r="F103" s="4" t="n">
+        <v>654700</v>
+      </c>
+      <c r="G103" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H103" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="I103" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="n">
+        <v>3.003</v>
+      </c>
+      <c r="K103" s="2" t="n">
+        <v>2.804</v>
+      </c>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" s="7" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>9792</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>SEG</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="E104" s="3" t="n">
+        <v>-0.007900000000000001</v>
+      </c>
+      <c r="F104" s="4" t="n">
+        <v>615100</v>
+      </c>
+      <c r="G104" s="5" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="H104" t="n">
+        <v>37.72</v>
+      </c>
+      <c r="I104" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="n">
+        <v>0.632</v>
+      </c>
+      <c r="K104" s="2" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" s="7" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>0368</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>OXB</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E105" s="10" t="n">
+        <v>0.0092</v>
+      </c>
+      <c r="F105" s="4" t="n">
+        <v>599000</v>
+      </c>
+      <c r="G105" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H105" t="n">
+        <v>71.79000000000001</v>
+      </c>
+      <c r="I105" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="n">
+        <v>0.477</v>
+      </c>
+      <c r="K105" s="2" t="n">
+        <v>0.451</v>
+      </c>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" s="7" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>0223</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>SAMAIDEN</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="E106" s="10" t="n">
+        <v>0.0199</v>
+      </c>
+      <c r="F106" s="4" t="n">
+        <v>594700</v>
+      </c>
+      <c r="G106" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H106" t="n">
+        <v>69.84999999999999</v>
+      </c>
+      <c r="I106" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="n">
+        <v>2.695</v>
+      </c>
+      <c r="K106" s="2" t="n">
+        <v>2.043</v>
+      </c>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" s="7" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>0112</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>MIKROMB</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="E107" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F107" s="4" t="n">
+        <v>592700</v>
+      </c>
+      <c r="G107" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H107" t="n">
+        <v>54.4</v>
+      </c>
+      <c r="I107" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="n">
+        <v>0.639</v>
+      </c>
+      <c r="K107" s="2" t="n">
+        <v>0.611</v>
+      </c>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" s="7" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>2852</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>CMSB</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="n">
+        <v>0.915</v>
+      </c>
+      <c r="E108" s="10" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="F108" s="4" t="n">
+        <v>587300</v>
+      </c>
+      <c r="G108" s="5" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H108" t="n">
+        <v>31.21</v>
+      </c>
+      <c r="I108" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="n">
+        <v>0.959</v>
+      </c>
+      <c r="K108" s="2" t="n">
+        <v>0.993</v>
+      </c>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" s="7" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>4197</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>SIME</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E109" s="10" t="n">
+        <v>0.008100000000000001</v>
+      </c>
+      <c r="F109" s="4" t="n">
+        <v>580100</v>
+      </c>
+      <c r="G109" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H109" t="n">
+        <v>58.18</v>
+      </c>
+      <c r="I109" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="n">
+        <v>2.463</v>
+      </c>
+      <c r="K109" s="2" t="n">
+        <v>2.344</v>
+      </c>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" s="7" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>5323</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>JPG</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="E110" s="10" t="n">
+        <v>0.0172</v>
+      </c>
+      <c r="F110" s="4" t="n">
+        <v>563600</v>
+      </c>
+      <c r="G110" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H110" t="n">
+        <v>40.32</v>
+      </c>
+      <c r="I110" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="n">
+        <v>1.824</v>
+      </c>
+      <c r="K110" s="2" t="n">
+        <v>1.927</v>
+      </c>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" s="7" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>7160</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>PENTA</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="n">
+        <v>5.98</v>
+      </c>
+      <c r="E111" s="10" t="n">
+        <v>0.0205</v>
+      </c>
+      <c r="F111" s="4" t="n">
+        <v>554800</v>
+      </c>
+      <c r="G111" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H111" t="n">
+        <v>64.55</v>
+      </c>
+      <c r="I111" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J111" s="2" t="n">
+        <v>5.485</v>
+      </c>
+      <c r="K111" s="2" t="n">
+        <v>5.357</v>
+      </c>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" s="7" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>0390</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>ISF</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="n">
+        <v>0.835</v>
+      </c>
+      <c r="E112" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F112" s="4" t="n">
+        <v>542200</v>
+      </c>
+      <c r="G112" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H112" t="n">
+        <v>58.39</v>
+      </c>
+      <c r="I112" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J112" s="2" t="n">
+        <v>0.819</v>
+      </c>
+      <c r="K112" s="2" t="n">
+        <v>0.756</v>
+      </c>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" s="7" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>5352</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>MTTSL</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="E113" s="10" t="n">
+        <v>0.0259</v>
+      </c>
+      <c r="F113" s="4" t="n">
+        <v>525200</v>
+      </c>
+      <c r="G113" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H113" t="n">
+        <v>55.65</v>
+      </c>
+      <c r="I113" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J113" s="2" t="n">
+        <v>1.154</v>
+      </c>
+      <c r="K113" s="2" t="n">
+        <v>1.165</v>
+      </c>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" s="7" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>0146</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>JFTECH</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="E114" s="10" t="n">
+        <v>0.0197</v>
+      </c>
+      <c r="F114" s="4" t="n">
+        <v>510700</v>
+      </c>
+      <c r="G114" s="5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H114" t="n">
+        <v>63.64</v>
+      </c>
+      <c r="I114" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J114" s="2" t="n">
+        <v>0.712</v>
+      </c>
+      <c r="K114" s="2" t="n">
+        <v>0.6909999999999999</v>
+      </c>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M75"/>
+  <autoFilter ref="A1:M114"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-09/bursa-report-2026-10-09.xlsx
+++ b/docs/downloads/2026-10-09/bursa-report-2026-10-09.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-09" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-09'!$A$1:$M$114</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-09'!$A$1:$M$137</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M114"/>
+  <dimension ref="A1:M137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -552,19 +552,19 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.515</v>
+        <v>0.51</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>-0.019</v>
+        <v>-0.0286</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>69250300</v>
+        <v>77848400</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>2.43</v>
+        <v>2.73</v>
       </c>
       <c r="H2" t="n">
-        <v>60.83</v>
+        <v>58.81</v>
       </c>
       <c r="I2" s="6" t="inlineStr">
         <is>
@@ -575,7 +575,7 @@
         <v>0.49</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0.479</v>
+        <v>0.478</v>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" s="7" t="inlineStr"/>
@@ -633,39 +633,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="E4" s="8" t="n">
-        <v>0</v>
+        <v>0.85</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>-0.0286</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>21145000</v>
+        <v>25910000</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.9</v>
+        <v>0.34</v>
       </c>
       <c r="H4" t="n">
-        <v>47.95</v>
-      </c>
-      <c r="I4" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.59999999999999</v>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.195</v>
+        <v>0.783</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.183</v>
+        <v>0.71</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" s="7" t="inlineStr"/>
@@ -678,39 +678,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>0138</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>ZETRIX</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.845</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>-0.0343</v>
+        <v>0.075</v>
+      </c>
+      <c r="E5" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>20487200</v>
+        <v>22298800</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.27</v>
+        <v>0.05</v>
       </c>
       <c r="H5" t="n">
-        <v>63.57</v>
-      </c>
-      <c r="I5" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>20.62</v>
+      </c>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.782</v>
+        <v>0.174</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.71</v>
+        <v>0.397</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" s="7" t="inlineStr"/>
@@ -723,28 +723,28 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0138</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ZETRIX</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="E6" s="10" t="n">
-        <v>0.0667</v>
+        <v>0.19</v>
+      </c>
+      <c r="E6" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>17207600</v>
+        <v>21894000</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.04</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>22.11</v>
+        <v>47.95</v>
       </c>
       <c r="I6" s="9" t="inlineStr">
         <is>
@@ -752,10 +752,10 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.175</v>
+        <v>0.195</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.397</v>
+        <v>0.183</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" s="7" t="inlineStr"/>
@@ -768,39 +768,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>JAKS</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>-0.027</v>
+        <v>2</v>
+      </c>
+      <c r="E7" s="10" t="n">
+        <v>0.0204</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>16799600</v>
+        <v>21210400</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.26</v>
+        <v>0.85</v>
       </c>
       <c r="H7" t="n">
-        <v>60.1</v>
-      </c>
-      <c r="I7" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>71</v>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.167</v>
+        <v>1.81</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.132</v>
+        <v>1.636</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" s="7" t="inlineStr"/>
@@ -813,28 +813,28 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>2.01</v>
+        <v>0.34</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>0.0255</v>
+        <v>0.0303</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>15251600</v>
+        <v>18193900</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.61</v>
+        <v>0.31</v>
       </c>
       <c r="H8" t="n">
-        <v>71.48</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="I8" s="6" t="inlineStr">
         <is>
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>1.811</v>
+        <v>0.278</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>1.636</v>
+        <v>0.245</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="7" t="inlineStr"/>
@@ -858,39 +858,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>JAKS</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="E9" s="8" t="n">
-        <v>0</v>
+        <v>0.18</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>-0.027</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>15111700</v>
+        <v>17474600</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.36</v>
+        <v>0.27</v>
       </c>
       <c r="H9" t="n">
-        <v>70.36</v>
-      </c>
-      <c r="I9" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>60.1</v>
+      </c>
+      <c r="I9" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.358</v>
+        <v>0.167</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.236</v>
+        <v>0.132</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="7" t="inlineStr"/>
@@ -903,28 +903,28 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="E10" s="10" t="n">
-        <v>0.0303</v>
+        <v>0.385</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>-0.0128</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>14741100</v>
+        <v>15169200</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.25</v>
+        <v>0.36</v>
       </c>
       <c r="H10" t="n">
-        <v>77.59999999999999</v>
+        <v>68.02</v>
       </c>
       <c r="I10" s="6" t="inlineStr">
         <is>
@@ -932,10 +932,10 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.278</v>
+        <v>0.357</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0.245</v>
+        <v>0.236</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="7" t="inlineStr"/>
@@ -948,36 +948,40 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0471</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>PIONEER</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0.35</v>
+        <v>0.62</v>
       </c>
       <c r="E11" s="10" t="n">
-        <v>0.04480000000000001</v>
+        <v>0.008100000000000001</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>11802300</v>
+        <v>14861500</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>1.26</v>
+        <v>0.57</v>
       </c>
       <c r="H11" t="n">
-        <v>72.73999999999999</v>
+        <v>70.55</v>
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J11" s="2" t="n"/>
-      <c r="K11" s="2" t="n"/>
+      <c r="J11" s="2" t="n">
+        <v>0.582</v>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>0.508</v>
+      </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="7" t="inlineStr"/>
     </row>
@@ -989,40 +993,36 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>0471</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>PIONEER</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0.62</v>
+        <v>0.34</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>0.008100000000000001</v>
+        <v>0.0149</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>9824400</v>
+        <v>13705100</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.38</v>
+        <v>1.46</v>
       </c>
       <c r="H12" t="n">
-        <v>70.55</v>
+        <v>69.98</v>
       </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J12" s="2" t="n">
-        <v>0.582</v>
-      </c>
-      <c r="K12" s="2" t="n">
-        <v>0.508</v>
-      </c>
+      <c r="J12" s="2" t="n"/>
+      <c r="K12" s="2" t="n"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="7" t="inlineStr"/>
     </row>
@@ -1034,39 +1034,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>5195</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CENSOF</t>
+          <t>MALAKOF</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="E13" s="8" t="n">
-        <v>0</v>
+        <v>0.8</v>
+      </c>
+      <c r="E13" s="10" t="n">
+        <v>0.0256</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>7225200</v>
+        <v>9254500</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>5.36</v>
+        <v>2.5</v>
       </c>
       <c r="H13" t="n">
-        <v>68.81</v>
-      </c>
-      <c r="I13" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>51.34</v>
+      </c>
+      <c r="I13" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.22</v>
+        <v>0.792</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0.206</v>
+        <v>0.806</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="7" t="inlineStr"/>
@@ -1094,10 +1094,10 @@
         <v>0.0805</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>6914700</v>
+        <v>8474000</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>3.01</v>
+        <v>3.69</v>
       </c>
       <c r="H14" t="n">
         <v>79.16</v>
@@ -1124,39 +1124,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AVANGAAD</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E15" s="8" t="n">
-        <v>0</v>
+        <v>0.74</v>
+      </c>
+      <c r="E15" s="10" t="n">
+        <v>0.0571</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>6215100</v>
+        <v>8249400</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>2.36</v>
+        <v>1.08</v>
       </c>
       <c r="H15" t="n">
-        <v>49.15</v>
-      </c>
-      <c r="I15" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.01</v>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.295</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0.296</v>
+        <v>0.678</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="7" t="inlineStr"/>
@@ -1169,39 +1169,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>5195</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>CENSOF</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>0.395</v>
-      </c>
-      <c r="E16" s="8" t="n">
-        <v>0</v>
+        <v>0.235</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>-0.0208</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>5460200</v>
+        <v>8228300</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.51</v>
+        <v>6.1</v>
       </c>
       <c r="H16" t="n">
-        <v>38.47</v>
-      </c>
-      <c r="I16" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.08</v>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.402</v>
+        <v>0.219</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0.41</v>
+        <v>0.206</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="7" t="inlineStr"/>
@@ -1214,28 +1214,28 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>7020</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ASTEEL</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>0.105</v>
-      </c>
-      <c r="E17" s="8" t="n">
-        <v>0</v>
+        <v>0.43</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>-0.0337</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>5271800</v>
+        <v>7275100</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>2.38</v>
+        <v>0.27</v>
       </c>
       <c r="H17" t="n">
-        <v>59.81</v>
+        <v>59.31</v>
       </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
@@ -1243,10 +1243,10 @@
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.096</v>
+        <v>0.409</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.346</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="7" t="inlineStr"/>
@@ -1259,36 +1259,40 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0470</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>BFIELD</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>0.485</v>
+        <v>0.39</v>
       </c>
       <c r="E18" s="10" t="n">
-        <v>0.0104</v>
+        <v>0.06849999999999999</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>5231600</v>
+        <v>6851900</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.44</v>
+        <v>0.57</v>
       </c>
       <c r="H18" t="n">
-        <v>68.69</v>
-      </c>
-      <c r="I18" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="n"/>
-      <c r="K18" s="2" t="n"/>
+        <v>53.45</v>
+      </c>
+      <c r="I18" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="n">
+        <v>0.384</v>
+      </c>
+      <c r="K18" s="2" t="n">
+        <v>0.375</v>
+      </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="7" t="inlineStr"/>
     </row>
@@ -1300,33 +1304,40 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0476</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SLGC Berhad</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>0.25</v>
+        <v>0.295</v>
       </c>
       <c r="E19" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>5145400</v>
+        <v>6215100</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="I19" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="n"/>
-      <c r="K19" s="2" t="n"/>
+        <v>2.36</v>
+      </c>
+      <c r="H19" t="n">
+        <v>49.15</v>
+      </c>
+      <c r="I19" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="K19" s="2" t="n">
+        <v>0.296</v>
+      </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="7" t="inlineStr"/>
     </row>
@@ -1338,39 +1349,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>0.43</v>
+        <v>0.405</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>-0.0337</v>
+        <v>-0.0241</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>5085800</v>
+        <v>5983800</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.19</v>
+        <v>5.31</v>
       </c>
       <c r="H20" t="n">
-        <v>59.31</v>
-      </c>
-      <c r="I20" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.82</v>
+      </c>
+      <c r="I20" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.409</v>
+        <v>0.422</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0.346</v>
+        <v>0.441</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="7" t="inlineStr"/>
@@ -1383,28 +1394,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="E21" s="10" t="n">
-        <v>0.06849999999999999</v>
+        <v>0.46</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>-0.0316</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>4949000</v>
+        <v>5974400</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.41</v>
+        <v>0.16</v>
       </c>
       <c r="H21" t="n">
-        <v>53.45</v>
+        <v>25.19</v>
       </c>
       <c r="I21" s="9" t="inlineStr">
         <is>
@@ -1412,10 +1423,10 @@
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.384</v>
+        <v>0.548</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0.375</v>
+        <v>0.749</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="7" t="inlineStr"/>
@@ -1428,39 +1439,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>7020</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>ASTEEL</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="E22" s="3" t="n">
-        <v>-0.0316</v>
+        <v>0.105</v>
+      </c>
+      <c r="E22" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>4866400</v>
+        <v>5830800</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.13</v>
+        <v>2.63</v>
       </c>
       <c r="H22" t="n">
-        <v>25.19</v>
-      </c>
-      <c r="I22" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.81</v>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.548</v>
+        <v>0.096</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0.749</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="7" t="inlineStr"/>
@@ -1473,40 +1484,33 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0198</t>
+          <t>0476</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>GDB</t>
+          <t>SLGC Berhad</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="E23" s="3" t="n">
-        <v>-0.0843</v>
+        <v>0.25</v>
+      </c>
+      <c r="E23" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>4016800</v>
+        <v>5501700</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="H23" t="n">
-        <v>26.04</v>
-      </c>
-      <c r="I23" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="n">
-        <v>0.419</v>
-      </c>
-      <c r="K23" s="2" t="n">
-        <v>0.441</v>
-      </c>
+        <v>0.13</v>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="n"/>
+      <c r="K23" s="2" t="n"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="7" t="inlineStr"/>
     </row>
@@ -1518,39 +1522,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E24" s="10" t="n">
-        <v>0.008100000000000001</v>
+        <v>0.39</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>-0.0127</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>3713700</v>
+        <v>5471000</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.36</v>
+        <v>0.51</v>
       </c>
       <c r="H24" t="n">
-        <v>58.16</v>
-      </c>
-      <c r="I24" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.12</v>
+      </c>
+      <c r="I24" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.611</v>
+        <v>0.402</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0.611</v>
+        <v>0.41</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="7" t="inlineStr"/>
@@ -1563,40 +1567,36 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>0470</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>BFIELD</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>0.725</v>
+        <v>0.485</v>
       </c>
       <c r="E25" s="10" t="n">
-        <v>0.0357</v>
+        <v>0.0104</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>3671600</v>
+        <v>5371600</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.48</v>
+        <v>0.45</v>
       </c>
       <c r="H25" t="n">
-        <v>58.51</v>
+        <v>68.69</v>
       </c>
       <c r="I25" s="6" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J25" s="2" t="n">
-        <v>0.6919999999999999</v>
-      </c>
-      <c r="K25" s="2" t="n">
-        <v>0.678</v>
-      </c>
+      <c r="J25" s="2" t="n"/>
+      <c r="K25" s="2" t="n"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="7" t="inlineStr"/>
     </row>
@@ -1608,28 +1608,28 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0111</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>K1</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>0.165</v>
+        <v>0.625</v>
       </c>
       <c r="E26" s="10" t="n">
-        <v>0.0313</v>
+        <v>0.008100000000000001</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>3667800</v>
+        <v>4707600</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>1.12</v>
+        <v>0.45</v>
       </c>
       <c r="H26" t="n">
-        <v>59.38</v>
+        <v>58.16</v>
       </c>
       <c r="I26" s="6" t="inlineStr">
         <is>
@@ -1637,10 +1637,10 @@
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.156</v>
+        <v>0.611</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0.145</v>
+        <v>0.611</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="7" t="inlineStr"/>
@@ -1653,39 +1653,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>0.775</v>
+        <v>2.82</v>
       </c>
       <c r="E27" s="10" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.0144</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>3200800</v>
+        <v>4580400</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.22</v>
+        <v>0.33</v>
       </c>
       <c r="H27" t="n">
-        <v>50.25</v>
-      </c>
-      <c r="I27" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>54.37</v>
+      </c>
+      <c r="I27" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.775</v>
+        <v>2.792</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0.775</v>
+        <v>2.693</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="7" t="inlineStr"/>
@@ -1698,39 +1698,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>5253</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ECONBHD</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>0.125</v>
+        <v>0.37</v>
       </c>
       <c r="E28" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>3095700</v>
+        <v>4571200</v>
       </c>
       <c r="G28" s="5" t="n">
         <v>0.68</v>
       </c>
       <c r="H28" t="n">
-        <v>55.25</v>
-      </c>
-      <c r="I28" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.56</v>
+      </c>
+      <c r="I28" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.122</v>
+        <v>0.368</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0.125</v>
+        <v>0.368</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="7" t="inlineStr"/>
@@ -1743,28 +1743,28 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0376</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>IAB</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="E29" s="3" t="n">
-        <v>-0.0222</v>
+        <v>0.775</v>
+      </c>
+      <c r="E29" s="10" t="n">
+        <v>0.006500000000000001</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>3049100</v>
+        <v>4570800</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>1.76</v>
+        <v>0.31</v>
       </c>
       <c r="H29" t="n">
-        <v>54.18</v>
+        <v>50.25</v>
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
@@ -1772,10 +1772,10 @@
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>1.275</v>
+        <v>0.775</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>1.32</v>
+        <v>0.775</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="7" t="inlineStr"/>
@@ -1788,28 +1788,28 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>0358</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>ICTZONE</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="E30" s="3" t="n">
-        <v>-0.0186</v>
+        <v>0.24</v>
+      </c>
+      <c r="E30" s="10" t="n">
+        <v>0.0667</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>2840100</v>
+        <v>4425600</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.25</v>
+        <v>1.59</v>
       </c>
       <c r="H30" t="n">
-        <v>56.35</v>
+        <v>48.47</v>
       </c>
       <c r="I30" s="9" t="inlineStr">
         <is>
@@ -1817,10 +1817,10 @@
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>3.6</v>
+        <v>0.241</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>2.739</v>
+        <v>0.249</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="7" t="inlineStr"/>
@@ -1833,28 +1833,28 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>0.8149999999999999</v>
-      </c>
-      <c r="E31" s="10" t="n">
-        <v>0.0062</v>
+        <v>0.31</v>
+      </c>
+      <c r="E31" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>2763000</v>
+        <v>4040400</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.17</v>
+        <v>0.21</v>
       </c>
       <c r="H31" t="n">
-        <v>54.76</v>
+        <v>57.67</v>
       </c>
       <c r="I31" s="6" t="inlineStr">
         <is>
@@ -1862,10 +1862,10 @@
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.305</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0.806</v>
+        <v>0.295</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="7" t="inlineStr"/>
@@ -1893,10 +1893,10 @@
         <v>0.024</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>2706400</v>
+        <v>3986000</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.14</v>
+        <v>0.21</v>
       </c>
       <c r="H32" t="n">
         <v>64.14</v>
@@ -1932,19 +1932,19 @@
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>6.7</v>
+        <v>6.77</v>
       </c>
       <c r="E33" s="10" t="n">
-        <v>0.102</v>
+        <v>0.1135</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>2702900</v>
+        <v>3920600</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.6</v>
+        <v>0.88</v>
       </c>
       <c r="H33" t="n">
-        <v>65.41</v>
+        <v>66.16</v>
       </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
@@ -1952,10 +1952,10 @@
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>5.832</v>
+        <v>5.838</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>5.778</v>
+        <v>5.78</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="7" t="inlineStr"/>
@@ -1968,36 +1968,40 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0468</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>UNIPAC</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E34" s="8" t="n">
-        <v>0</v>
+        <v>5.05</v>
+      </c>
+      <c r="E34" s="10" t="n">
+        <v>0.0202</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>2499400</v>
+        <v>3826500</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.21</v>
+        <v>0.16</v>
       </c>
       <c r="H34" t="n">
-        <v>28.11</v>
+        <v>60.26</v>
       </c>
       <c r="I34" s="6" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J34" s="2" t="n"/>
-      <c r="K34" s="2" t="n"/>
+      <c r="J34" s="2" t="n">
+        <v>4.922</v>
+      </c>
+      <c r="K34" s="2" t="n">
+        <v>4.652</v>
+      </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="7" t="inlineStr"/>
     </row>
@@ -2009,39 +2013,39 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>9.789999999999999</v>
-      </c>
-      <c r="E35" s="3" t="n">
-        <v>-0.001</v>
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="E35" s="10" t="n">
+        <v>0.0062</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>2475400</v>
+        <v>3780000</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.2</v>
+        <v>0.24</v>
       </c>
       <c r="H35" t="n">
-        <v>29.86</v>
-      </c>
-      <c r="I35" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.76</v>
+      </c>
+      <c r="I35" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>10.02</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>10.213</v>
+        <v>0.806</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="7" t="inlineStr"/>
@@ -2054,28 +2058,28 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>0376</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>IAB</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>1.14</v>
+        <v>1.32</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>-0.0256</v>
+        <v>-0.0222</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>2461000</v>
+        <v>3726300</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.22</v>
+        <v>2.15</v>
       </c>
       <c r="H36" t="n">
-        <v>48.21</v>
+        <v>54.18</v>
       </c>
       <c r="I36" s="6" t="inlineStr">
         <is>
@@ -2083,10 +2087,10 @@
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>1.162</v>
+        <v>1.275</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>1.119</v>
+        <v>1.32</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="7" t="inlineStr"/>
@@ -2099,39 +2103,39 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>0111</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>0.93</v>
+        <v>0.165</v>
       </c>
       <c r="E37" s="10" t="n">
-        <v>0.0449</v>
+        <v>0.0313</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>2442000</v>
+        <v>3667800</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.85</v>
+        <v>1.12</v>
       </c>
       <c r="H37" t="n">
-        <v>53.36</v>
-      </c>
-      <c r="I37" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.38</v>
+      </c>
+      <c r="I37" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.913</v>
+        <v>0.156</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0.965</v>
+        <v>0.145</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="7" t="inlineStr"/>
@@ -2144,28 +2148,28 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>0050</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>SYSTECH</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="E38" s="3" t="n">
-        <v>-0.0151</v>
+        <v>0.19</v>
+      </c>
+      <c r="E38" s="10" t="n">
+        <v>0.0857</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>2430600</v>
+        <v>3570000</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.75</v>
+        <v>0.66</v>
       </c>
       <c r="H38" t="n">
-        <v>84.12</v>
+        <v>67.38</v>
       </c>
       <c r="I38" s="6" t="inlineStr">
         <is>
@@ -2173,10 +2177,10 @@
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.656</v>
+        <v>0.165</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>0.479</v>
+        <v>0.166</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="7" t="inlineStr"/>
@@ -2189,28 +2193,28 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>5253</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>ECONBHD</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>5.01</v>
-      </c>
-      <c r="E39" s="10" t="n">
-        <v>0.0121</v>
+        <v>0.125</v>
+      </c>
+      <c r="E39" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>2256700</v>
+        <v>3288700</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.09</v>
+        <v>0.72</v>
       </c>
       <c r="H39" t="n">
-        <v>58.56</v>
+        <v>55.25</v>
       </c>
       <c r="I39" s="6" t="inlineStr">
         <is>
@@ -2218,10 +2222,10 @@
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>4.918</v>
+        <v>0.122</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>4.651</v>
+        <v>0.125</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="7" t="inlineStr"/>
@@ -2234,39 +2238,39 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>5326</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>99SMART</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="E40" s="10" t="n">
-        <v>0.0545</v>
+        <v>9.789999999999999</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>-0.001</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>2203100</v>
+        <v>3272900</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.52</v>
+        <v>0.26</v>
       </c>
       <c r="H40" t="n">
-        <v>54.26</v>
-      </c>
-      <c r="I40" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>29.86</v>
+      </c>
+      <c r="I40" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>3.202</v>
+        <v>10.02</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>3.391</v>
+        <v>10.213</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="7" t="inlineStr"/>
@@ -2279,40 +2283,36 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>0468</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>UNIPAC</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>0.37</v>
+        <v>0.25</v>
       </c>
       <c r="E41" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>2196900</v>
+        <v>3083100</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.33</v>
+        <v>0.26</v>
       </c>
       <c r="H41" t="n">
-        <v>53.56</v>
-      </c>
-      <c r="I41" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="n">
-        <v>0.368</v>
-      </c>
-      <c r="K41" s="2" t="n">
-        <v>0.368</v>
-      </c>
+        <v>28.11</v>
+      </c>
+      <c r="I41" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="n"/>
+      <c r="K41" s="2" t="n"/>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="7" t="inlineStr"/>
     </row>
@@ -2324,39 +2324,39 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>2.75</v>
+        <v>3.73</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>-0.0108</v>
+        <v>-0.0106</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>2190700</v>
+        <v>3064100</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.12</v>
+        <v>0.27</v>
       </c>
       <c r="H42" t="n">
-        <v>62.29</v>
-      </c>
-      <c r="I42" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>57.15</v>
+      </c>
+      <c r="I42" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>2.624</v>
+        <v>3.603</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>2.496</v>
+        <v>2.74</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="7" t="inlineStr"/>
@@ -2369,28 +2369,28 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>SPSETIA</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="E43" s="8" t="n">
-        <v>0</v>
+        <v>0.715</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>-0.0138</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>2064900</v>
+        <v>3034500</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.08</v>
+        <v>0.51</v>
       </c>
       <c r="H43" t="n">
-        <v>29.99</v>
+        <v>32.64</v>
       </c>
       <c r="I43" s="9" t="inlineStr">
         <is>
@@ -2398,10 +2398,10 @@
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.249</v>
+        <v>0.756</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>0.304</v>
+        <v>0.819</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="7" t="inlineStr"/>
@@ -2414,28 +2414,28 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="E44" s="10" t="n">
-        <v>0.0388</v>
+        <v>1.14</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>-0.0256</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>2057000</v>
+        <v>2969600</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.45</v>
+        <v>0.26</v>
       </c>
       <c r="H44" t="n">
-        <v>84.47</v>
+        <v>48.21</v>
       </c>
       <c r="I44" s="6" t="inlineStr">
         <is>
@@ -2443,10 +2443,10 @@
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.516</v>
+        <v>1.162</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0.443</v>
+        <v>1.119</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="7" t="inlineStr"/>
@@ -2459,28 +2459,28 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="E45" s="10" t="n">
-        <v>0.0052</v>
+        <v>0.34</v>
+      </c>
+      <c r="E45" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>1981300</v>
+        <v>2911600</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.24</v>
+        <v>0.73</v>
       </c>
       <c r="H45" t="n">
-        <v>55.95</v>
+        <v>32.2</v>
       </c>
       <c r="I45" s="9" t="inlineStr">
         <is>
@@ -2488,10 +2488,10 @@
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.962</v>
+        <v>0.363</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0.821</v>
+        <v>0.383</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="7" t="inlineStr"/>
@@ -2504,39 +2504,39 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>2.83</v>
+        <v>0.675</v>
       </c>
       <c r="E46" s="10" t="n">
-        <v>0.018</v>
+        <v>0.04650000000000001</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>1966200</v>
+        <v>2854000</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.14</v>
+        <v>0.63</v>
       </c>
       <c r="H46" t="n">
-        <v>55.1</v>
-      </c>
-      <c r="I46" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>84.73999999999999</v>
+      </c>
+      <c r="I46" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>2.793</v>
+        <v>0.516</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>2.693</v>
+        <v>0.443</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="7" t="inlineStr"/>
@@ -2549,39 +2549,39 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>5326</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>99SMART</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="E47" s="3" t="n">
-        <v>-0.007800000000000001</v>
+        <v>3.26</v>
+      </c>
+      <c r="E47" s="10" t="n">
+        <v>0.0449</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>1943300</v>
+        <v>2824700</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.18</v>
+        <v>0.66</v>
       </c>
       <c r="H47" t="n">
-        <v>41.81</v>
-      </c>
-      <c r="I47" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.06</v>
+      </c>
+      <c r="I47" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>1.321</v>
+        <v>3.199</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>1.305</v>
+        <v>3.39</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="7" t="inlineStr"/>
@@ -2603,19 +2603,19 @@
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="E48" s="8" t="n">
-        <v>0</v>
+        <v>0.8</v>
+      </c>
+      <c r="E48" s="10" t="n">
+        <v>0.0127</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>1824000</v>
+        <v>2778900</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.23</v>
+        <v>0.35</v>
       </c>
       <c r="H48" t="n">
-        <v>54.24</v>
+        <v>56.78</v>
       </c>
       <c r="I48" s="6" t="inlineStr">
         <is>
@@ -2623,7 +2623,7 @@
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.779</v>
+        <v>0.78</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>0.773</v>
@@ -2639,39 +2639,39 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>4.56</v>
-      </c>
-      <c r="E49" s="10" t="n">
-        <v>0.0022</v>
+        <v>2.75</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>-0.0108</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>1810800</v>
+        <v>2681800</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="H49" t="n">
-        <v>27.57</v>
-      </c>
-      <c r="I49" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.29</v>
+      </c>
+      <c r="I49" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>4.721</v>
+        <v>2.624</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>4.891</v>
+        <v>2.496</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="7" t="inlineStr"/>
@@ -2684,39 +2684,39 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>0338</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>KOPI</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>0.455</v>
-      </c>
-      <c r="E50" s="3" t="n">
-        <v>-0.0109</v>
+        <v>0.92</v>
+      </c>
+      <c r="E50" s="10" t="n">
+        <v>0.0337</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>1777100</v>
+        <v>2660100</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.26</v>
+        <v>0.92</v>
       </c>
       <c r="H50" t="n">
-        <v>60.71</v>
-      </c>
-      <c r="I50" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.01</v>
+      </c>
+      <c r="I50" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.426</v>
+        <v>0.912</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>0.413</v>
+        <v>0.965</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="7" t="inlineStr"/>
@@ -2729,39 +2729,39 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>0.525</v>
-      </c>
-      <c r="E51" s="10" t="n">
-        <v>0.0294</v>
+        <v>0.46</v>
+      </c>
+      <c r="E51" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>1739500</v>
+        <v>2654000</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.1</v>
+        <v>0.38</v>
       </c>
       <c r="H51" t="n">
-        <v>55.9</v>
-      </c>
-      <c r="I51" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.48</v>
+      </c>
+      <c r="I51" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.512</v>
+        <v>0.427</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0.436</v>
+        <v>0.413</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="7" t="inlineStr"/>
@@ -2774,39 +2774,39 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0268</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>L&amp;PBHD</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>0.24</v>
+        <v>4.56</v>
       </c>
       <c r="E52" s="10" t="n">
-        <v>0.09089999999999999</v>
+        <v>0.0022</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>1719600</v>
+        <v>2587100</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.86</v>
+        <v>0.16</v>
       </c>
       <c r="H52" t="n">
-        <v>77.70999999999999</v>
-      </c>
-      <c r="I52" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>27.57</v>
+      </c>
+      <c r="I52" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.206</v>
+        <v>4.721</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>0.171</v>
+        <v>4.891</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="7" t="inlineStr"/>
@@ -2819,28 +2819,28 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="E53" s="10" t="n">
-        <v>0.0035</v>
+        <v>0.975</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>-0.0201</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>1715200</v>
+        <v>2533800</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.55</v>
+        <v>0.79</v>
       </c>
       <c r="H53" t="n">
-        <v>75.53</v>
+        <v>83.41</v>
       </c>
       <c r="I53" s="6" t="inlineStr">
         <is>
@@ -2848,10 +2848,10 @@
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>2.638</v>
+        <v>0.656</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>2.285</v>
+        <v>0.479</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="7" t="inlineStr"/>
@@ -2864,39 +2864,39 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="E54" s="10" t="n">
-        <v>0.0331</v>
+        <v>1.27</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>-0.007800000000000001</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>1698500</v>
+        <v>2497100</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.5</v>
+        <v>0.23</v>
       </c>
       <c r="H54" t="n">
-        <v>76.55</v>
-      </c>
-      <c r="I54" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.81</v>
+      </c>
+      <c r="I54" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>1.025</v>
+        <v>1.321</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>0.86</v>
+        <v>1.305</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="7" t="inlineStr"/>
@@ -2909,28 +2909,28 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>MRCB</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="E55" s="10" t="n">
-        <v>0.0182</v>
+        <v>0.965</v>
+      </c>
+      <c r="E55" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>1600800</v>
+        <v>2474600</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.23</v>
+        <v>0.3</v>
       </c>
       <c r="H55" t="n">
-        <v>37.22</v>
+        <v>55.29</v>
       </c>
       <c r="I55" s="9" t="inlineStr">
         <is>
@@ -2938,10 +2938,10 @@
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.289</v>
+        <v>0.961</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>0.307</v>
+        <v>0.821</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="7" t="inlineStr"/>
@@ -2954,28 +2954,28 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0267</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ECA</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="E56" s="10" t="n">
-        <v>0.0411</v>
+        <v>0.22</v>
+      </c>
+      <c r="E56" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>1569100</v>
+        <v>2458300</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.47</v>
+        <v>0.09</v>
       </c>
       <c r="H56" t="n">
-        <v>53.04</v>
+        <v>29.99</v>
       </c>
       <c r="I56" s="9" t="inlineStr">
         <is>
@@ -2983,10 +2983,10 @@
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.366</v>
+        <v>0.249</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>0.374</v>
+        <v>0.304</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="7" t="inlineStr"/>
@@ -2999,28 +2999,28 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>5260</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>OWG</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>0.2</v>
+        <v>1.12</v>
       </c>
       <c r="E57" s="10" t="n">
-        <v>0.0526</v>
+        <v>0.0182</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>1563300</v>
+        <v>2431400</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>2.45</v>
+        <v>0.25</v>
       </c>
       <c r="H57" t="n">
-        <v>61.12</v>
+        <v>64.88</v>
       </c>
       <c r="I57" s="6" t="inlineStr">
         <is>
@@ -3028,10 +3028,10 @@
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.186</v>
+        <v>1.069</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>0.188</v>
+        <v>0.916</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="7" t="inlineStr"/>
@@ -3044,28 +3044,28 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0104</t>
+          <t>0268</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>GENETEC</t>
+          <t>L&amp;PBHD</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="E58" s="3" t="n">
-        <v>-0.0149</v>
+        <v>0.24</v>
+      </c>
+      <c r="E58" s="10" t="n">
+        <v>0.09089999999999999</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>1561200</v>
+        <v>2403100</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.28</v>
+        <v>1.2</v>
       </c>
       <c r="H58" t="n">
-        <v>52.01</v>
+        <v>77.70999999999999</v>
       </c>
       <c r="I58" s="6" t="inlineStr">
         <is>
@@ -3073,10 +3073,10 @@
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.326</v>
+        <v>0.206</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>0.338</v>
+        <v>0.171</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="7" t="inlineStr"/>
@@ -3089,39 +3089,39 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0045</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>SSB8</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="E59" s="8" t="n">
-        <v>0</v>
+        <v>0.53</v>
+      </c>
+      <c r="E59" s="10" t="n">
+        <v>0.0392</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>1559700</v>
+        <v>2371800</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.38</v>
+        <v>0.14</v>
       </c>
       <c r="H59" t="n">
-        <v>64</v>
-      </c>
-      <c r="I59" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>56.74</v>
+      </c>
+      <c r="I59" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.637</v>
+        <v>0.512</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0.601</v>
+        <v>0.436</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="7" t="inlineStr"/>
@@ -3134,28 +3134,28 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>IOICORP</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>4.59</v>
+        <v>1.2</v>
       </c>
       <c r="E60" s="10" t="n">
-        <v>0.0066</v>
+        <v>0.0345</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>1550500</v>
+        <v>2316800</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.16</v>
+        <v>0.4</v>
       </c>
       <c r="H60" t="n">
-        <v>42.75</v>
+        <v>56.94</v>
       </c>
       <c r="I60" s="9" t="inlineStr">
         <is>
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>4.676</v>
+        <v>1.155</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>4.62</v>
+        <v>1.165</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="7" t="inlineStr"/>
@@ -3179,28 +3179,28 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>7.25</v>
+        <v>2.12</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>-0.0014</v>
+        <v>-0.009300000000000001</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>1484400</v>
+        <v>2304800</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="H61" t="n">
-        <v>31.19</v>
+        <v>39.76</v>
       </c>
       <c r="I61" s="9" t="inlineStr">
         <is>
@@ -3208,10 +3208,10 @@
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>7.639</v>
+        <v>2.223</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>7.729</v>
+        <v>2.212</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="7" t="inlineStr"/>
@@ -3224,28 +3224,28 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>1.12</v>
+        <v>0.455</v>
       </c>
       <c r="E62" s="10" t="n">
-        <v>0.0182</v>
+        <v>0.0341</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>1459100</v>
+        <v>2245300</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.15</v>
+        <v>0.21</v>
       </c>
       <c r="H62" t="n">
-        <v>64.88</v>
+        <v>52.28</v>
       </c>
       <c r="I62" s="6" t="inlineStr">
         <is>
@@ -3253,10 +3253,10 @@
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>1.069</v>
+        <v>0.451</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>0.916</v>
+        <v>0.426</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="7" t="inlineStr"/>
@@ -3269,28 +3269,28 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>NEXG</t>
+          <t>CNERGEN</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>0.3</v>
+        <v>1.25</v>
       </c>
       <c r="E63" s="10" t="n">
-        <v>0.0345</v>
+        <v>0.0331</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>1454500</v>
+        <v>2243500</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.12</v>
+        <v>0.67</v>
       </c>
       <c r="H63" t="n">
-        <v>54.14</v>
+        <v>76.55</v>
       </c>
       <c r="I63" s="6" t="inlineStr">
         <is>
@@ -3298,10 +3298,10 @@
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.292</v>
+        <v>1.025</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>0.281</v>
+        <v>0.86</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="7" t="inlineStr"/>
@@ -3314,28 +3314,28 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0345</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>SUNLOGY</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="E64" s="10" t="n">
-        <v>0.0227</v>
+        <v>0.865</v>
+      </c>
+      <c r="E64" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>1426700</v>
+        <v>2127700</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0.14</v>
+        <v>0.11</v>
       </c>
       <c r="H64" t="n">
-        <v>51.11</v>
+        <v>46.68</v>
       </c>
       <c r="I64" s="6" t="inlineStr">
         <is>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.45</v>
+        <v>0.868</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>0.426</v>
+        <v>0.869</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="7" t="inlineStr"/>
@@ -3359,39 +3359,39 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="E65" s="10" t="n">
-        <v>0.0108</v>
+        <v>0.33</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>-0.0149</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>1391600</v>
+        <v>2110000</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.37</v>
       </c>
       <c r="H65" t="n">
-        <v>55.4</v>
-      </c>
-      <c r="I65" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.01</v>
+      </c>
+      <c r="I65" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.923</v>
+        <v>0.326</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>0.85</v>
+        <v>0.338</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="7" t="inlineStr"/>
@@ -3404,28 +3404,28 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="E66" s="8" t="n">
-        <v>0</v>
+        <v>0.55</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>-0.009000000000000001</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>1362500</v>
+        <v>2097200</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>0.15</v>
+        <v>0.39</v>
       </c>
       <c r="H66" t="n">
-        <v>33.91</v>
+        <v>33.2</v>
       </c>
       <c r="I66" s="9" t="inlineStr">
         <is>
@@ -3433,10 +3433,10 @@
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>1.285</v>
+        <v>0.592</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>1.386</v>
+        <v>0.641</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="7" t="inlineStr"/>
@@ -3449,28 +3449,28 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0359</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>HKB</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>0.825</v>
+        <v>0.72</v>
       </c>
       <c r="E67" s="10" t="n">
-        <v>0.0248</v>
+        <v>0.0286</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>1283400</v>
+        <v>1916200</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>0.57</v>
+        <v>0.21</v>
       </c>
       <c r="H67" t="n">
-        <v>82.5</v>
+        <v>63.57</v>
       </c>
       <c r="I67" s="6" t="inlineStr">
         <is>
@@ -3478,10 +3478,10 @@
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.68</v>
+        <v>0.672</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>0.622</v>
+        <v>0.607</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="7" t="inlineStr"/>
@@ -3494,39 +3494,39 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>0267</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>ECA</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>7.11</v>
-      </c>
-      <c r="E68" s="3" t="n">
-        <v>-0.005600000000000001</v>
+        <v>0.385</v>
+      </c>
+      <c r="E68" s="10" t="n">
+        <v>0.0548</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>1253100</v>
+        <v>1891000</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>0.13</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H68" t="n">
-        <v>18.64</v>
-      </c>
-      <c r="I68" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.15</v>
+      </c>
+      <c r="I68" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>7.595</v>
+        <v>0.367</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>8.089</v>
+        <v>0.374</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="7" t="inlineStr"/>
@@ -3539,39 +3539,39 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="E69" s="8" t="n">
-        <v>0</v>
+        <v>7.12</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>-0.0042</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>1218500</v>
+        <v>1858600</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>0.16</v>
+        <v>0.19</v>
       </c>
       <c r="H69" t="n">
-        <v>56.58</v>
-      </c>
-      <c r="I69" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>18.83</v>
+      </c>
+      <c r="I69" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.343</v>
+        <v>7.596</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>0.324</v>
+        <v>8.09</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="7" t="inlineStr"/>
@@ -3584,39 +3584,39 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>SKPRES</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="E70" s="10" t="n">
-        <v>0.0267</v>
+        <v>7.25</v>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>-0.0014</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>1200900</v>
+        <v>1848300</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>0.15</v>
+        <v>0.13</v>
       </c>
       <c r="H70" t="n">
-        <v>69.33</v>
-      </c>
-      <c r="I70" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>31.19</v>
+      </c>
+      <c r="I70" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.354</v>
+        <v>7.639</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>0.322</v>
+        <v>7.729</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="7" t="inlineStr"/>
@@ -3629,39 +3629,39 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0296</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>HEGROUP</t>
+          <t>MRCB</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="E71" s="3" t="n">
-        <v>-0.0175</v>
+        <v>0.28</v>
+      </c>
+      <c r="E71" s="10" t="n">
+        <v>0.0182</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>1186900</v>
+        <v>1778500</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="H71" t="n">
-        <v>66.73</v>
-      </c>
-      <c r="I71" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.22</v>
+      </c>
+      <c r="I71" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>1.057</v>
+        <v>0.289</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>0.891</v>
+        <v>0.307</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="7" t="inlineStr"/>
@@ -3674,39 +3674,39 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="E72" s="3" t="n">
-        <v>-0.009000000000000001</v>
+        <v>2.86</v>
+      </c>
+      <c r="E72" s="10" t="n">
+        <v>0.0035</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>1186500</v>
+        <v>1770600</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>0.22</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H72" t="n">
-        <v>33.2</v>
-      </c>
-      <c r="I72" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>75.53</v>
+      </c>
+      <c r="I72" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.592</v>
+        <v>2.638</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>0.641</v>
+        <v>2.285</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="7" t="inlineStr"/>
@@ -3719,39 +3719,39 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>0.71</v>
+        <v>1.26</v>
       </c>
       <c r="E73" s="10" t="n">
-        <v>0.0143</v>
+        <v>0.0161</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>1179600</v>
+        <v>1762400</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>0.13</v>
+        <v>0.2</v>
       </c>
       <c r="H73" t="n">
-        <v>62.05</v>
-      </c>
-      <c r="I73" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.42</v>
+      </c>
+      <c r="I73" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.671</v>
+        <v>1.286</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>0.607</v>
+        <v>1.387</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="7" t="inlineStr"/>
@@ -3764,39 +3764,39 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0249</t>
+          <t>7225</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>LGMS</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="E74" s="10" t="n">
-        <v>0.0175</v>
+        <v>0.2</v>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>-0.0244</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>1168900</v>
+        <v>1720500</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>1.3</v>
+        <v>0.37</v>
       </c>
       <c r="H74" t="n">
-        <v>73.84</v>
-      </c>
-      <c r="I74" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.79</v>
+      </c>
+      <c r="I74" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.524</v>
+        <v>0.207</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>0.504</v>
+        <v>0.208</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="7" t="inlineStr"/>
@@ -3809,39 +3809,39 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>4.22</v>
-      </c>
-      <c r="E75" s="3" t="n">
-        <v>-0.009399999999999999</v>
+        <v>0.295</v>
+      </c>
+      <c r="E75" s="10" t="n">
+        <v>0.0172</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>1165300</v>
+        <v>1702500</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="H75" t="n">
-        <v>43.07</v>
-      </c>
-      <c r="I75" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.36</v>
+      </c>
+      <c r="I75" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>4.368</v>
+        <v>0.278</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>4.464</v>
+        <v>0.303</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="7" t="inlineStr"/>
@@ -3854,28 +3854,28 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>2.72</v>
       </c>
       <c r="E76" s="10" t="n">
-        <v>0.0385</v>
+        <v>0.0149</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>1153900</v>
+        <v>1672100</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>0.16</v>
+        <v>0.28</v>
       </c>
       <c r="H76" t="n">
-        <v>66.09999999999999</v>
+        <v>58.63</v>
       </c>
       <c r="I76" s="6" t="inlineStr">
         <is>
@@ -3883,10 +3883,10 @@
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.737</v>
+        <v>2.63</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>0.652</v>
+        <v>2.581</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="7" t="inlineStr"/>
@@ -3899,28 +3899,28 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>0273</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>VLB</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="E77" s="8" t="n">
-        <v>0</v>
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="E77" s="10" t="n">
+        <v>0.0108</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>1123600</v>
+        <v>1588800</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>0.06</v>
+        <v>0.93</v>
       </c>
       <c r="H77" t="n">
-        <v>50.69</v>
+        <v>55.4</v>
       </c>
       <c r="I77" s="9" t="inlineStr">
         <is>
@@ -3928,10 +3928,10 @@
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>2.098</v>
+        <v>0.923</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>2.08</v>
+        <v>0.85</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="7" t="inlineStr"/>
@@ -3944,39 +3944,39 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>IOICORP</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="E78" s="8" t="n">
-        <v>0</v>
+        <v>4.58</v>
+      </c>
+      <c r="E78" s="10" t="n">
+        <v>0.0044</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>1107600</v>
+        <v>1582900</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>0.06</v>
+        <v>0.17</v>
       </c>
       <c r="H78" t="n">
-        <v>57.67</v>
-      </c>
-      <c r="I78" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.8</v>
+      </c>
+      <c r="I78" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.305</v>
+        <v>4.675</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>0.295</v>
+        <v>4.62</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="7" t="inlineStr"/>
@@ -3989,28 +3989,28 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>0045</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>SSB8</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E79" s="10" t="n">
-        <v>0.0172</v>
+        <v>0.67</v>
+      </c>
+      <c r="E79" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>1104200</v>
+        <v>1564400</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>0.12</v>
+        <v>0.38</v>
       </c>
       <c r="H79" t="n">
-        <v>57.36</v>
+        <v>64</v>
       </c>
       <c r="I79" s="6" t="inlineStr">
         <is>
@@ -4018,10 +4018,10 @@
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.278</v>
+        <v>0.637</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>0.303</v>
+        <v>0.601</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="7" t="inlineStr"/>
@@ -4034,28 +4034,28 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>5260</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>OWG</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>2.72</v>
+        <v>0.2</v>
       </c>
       <c r="E80" s="10" t="n">
-        <v>0.0149</v>
+        <v>0.0526</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>1079400</v>
+        <v>1563300</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>0.18</v>
+        <v>2.45</v>
       </c>
       <c r="H80" t="n">
-        <v>58.63</v>
+        <v>61.12</v>
       </c>
       <c r="I80" s="6" t="inlineStr">
         <is>
@@ -4063,10 +4063,10 @@
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>2.63</v>
+        <v>0.186</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>2.581</v>
+        <v>0.188</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="7" t="inlineStr"/>
@@ -4079,39 +4079,39 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>NEXG</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="E81" s="8" t="n">
-        <v>0</v>
+        <v>0.295</v>
+      </c>
+      <c r="E81" s="10" t="n">
+        <v>0.0172</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>1075100</v>
+        <v>1548900</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="H81" t="n">
-        <v>41.24</v>
-      </c>
-      <c r="I81" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.49</v>
+      </c>
+      <c r="I81" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J81" s="2" t="n">
-        <v>2.225</v>
+        <v>0.291</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>2.212</v>
+        <v>0.281</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="7" t="inlineStr"/>
@@ -4124,28 +4124,28 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>0359</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>HKB</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>0.805</v>
-      </c>
-      <c r="E82" s="8" t="n">
-        <v>0</v>
+        <v>0.82</v>
+      </c>
+      <c r="E82" s="10" t="n">
+        <v>0.0186</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>1071700</v>
+        <v>1518100</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>0.17</v>
+        <v>0.68</v>
       </c>
       <c r="H82" t="n">
-        <v>70.15000000000001</v>
+        <v>82.16</v>
       </c>
       <c r="I82" s="6" t="inlineStr">
         <is>
@@ -4153,10 +4153,10 @@
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.785</v>
+        <v>0.679</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>0.764</v>
+        <v>0.622</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="7" t="inlineStr"/>
@@ -4169,28 +4169,28 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>5141</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>AWC</t>
+          <t>DAYANG</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>0.63</v>
+        <v>1.43</v>
       </c>
       <c r="E83" s="3" t="n">
-        <v>-0.007900000000000001</v>
+        <v>-0.0138</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>1064800</v>
+        <v>1435300</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>0.48</v>
+        <v>0.65</v>
       </c>
       <c r="H83" t="n">
-        <v>56.48</v>
+        <v>39.83</v>
       </c>
       <c r="I83" s="9" t="inlineStr">
         <is>
@@ -4198,10 +4198,10 @@
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.619</v>
+        <v>1.46</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>0.529</v>
+        <v>1.495</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="7" t="inlineStr"/>
@@ -4214,39 +4214,39 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0450</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>MFGROUP</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="E84" s="3" t="n">
-        <v>-0.0185</v>
+        <v>0.35</v>
+      </c>
+      <c r="E84" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>1062000</v>
+        <v>1428900</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>1.09</v>
+        <v>0.18</v>
       </c>
       <c r="H84" t="n">
-        <v>54.17</v>
-      </c>
-      <c r="I84" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.58</v>
+      </c>
+      <c r="I84" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.262</v>
+        <v>0.343</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>0.264</v>
+        <v>0.324</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="7" t="inlineStr"/>
@@ -4274,10 +4274,10 @@
         <v>-0.009300000000000001</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>1028100</v>
+        <v>1412800</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="H85" t="n">
         <v>48.94</v>
@@ -4304,39 +4304,39 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>0.535</v>
+        <v>0.385</v>
       </c>
       <c r="E86" s="10" t="n">
-        <v>0.009399999999999999</v>
+        <v>0.0267</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>998500</v>
+        <v>1400200</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>0.13</v>
+        <v>0.17</v>
       </c>
       <c r="H86" t="n">
-        <v>55.09</v>
-      </c>
-      <c r="I86" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>69.33</v>
+      </c>
+      <c r="I86" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.522</v>
+        <v>0.354</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>0.531</v>
+        <v>0.322</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="7" t="inlineStr"/>
@@ -4349,39 +4349,39 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0271</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>WELLS</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>0.53</v>
+        <v>0.805</v>
       </c>
       <c r="E87" s="10" t="n">
-        <v>0.0291</v>
+        <v>0.0321</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v>963600</v>
+        <v>1392000</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>0.87</v>
+        <v>0.2</v>
       </c>
       <c r="H87" t="n">
-        <v>26.64</v>
-      </c>
-      <c r="I87" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>65.55</v>
+      </c>
+      <c r="I87" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.582</v>
+        <v>0.736</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>0.622</v>
+        <v>0.652</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="7" t="inlineStr"/>
@@ -4394,39 +4394,39 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>5337</t>
+          <t>0249</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>ECOSHOP</t>
+          <t>LGMS</t>
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>1.46</v>
+        <v>0.58</v>
       </c>
       <c r="E88" s="10" t="n">
-        <v>0.021</v>
+        <v>0.0175</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>943700</v>
+        <v>1347000</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>0.2</v>
+        <v>1.5</v>
       </c>
       <c r="H88" t="n">
-        <v>49.32</v>
-      </c>
-      <c r="I88" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>73.84</v>
+      </c>
+      <c r="I88" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>1.461</v>
+        <v>0.524</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>1.469</v>
+        <v>0.504</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="7" t="inlineStr"/>
@@ -4439,39 +4439,39 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>0296</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>HEGROUP</t>
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="E89" s="8" t="n">
-        <v>0</v>
+        <v>1.13</v>
+      </c>
+      <c r="E89" s="3" t="n">
+        <v>-0.008800000000000001</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>930100</v>
+        <v>1324000</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>0.18</v>
+        <v>0.27</v>
       </c>
       <c r="H89" t="n">
-        <v>63.88</v>
-      </c>
-      <c r="I89" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>68.90000000000001</v>
+      </c>
+      <c r="I89" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.908</v>
+        <v>1.058</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>0.863</v>
+        <v>0.892</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="7" t="inlineStr"/>
@@ -4484,28 +4484,28 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>TENAGA</t>
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>0.8</v>
+        <v>13</v>
       </c>
       <c r="E90" s="10" t="n">
-        <v>0.0191</v>
+        <v>0.007800000000000001</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>915100</v>
+        <v>1286700</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="H90" t="n">
-        <v>57.83</v>
+        <v>44.16</v>
       </c>
       <c r="I90" s="6" t="inlineStr">
         <is>
@@ -4513,10 +4513,10 @@
         </is>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.768</v>
+        <v>13.039</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>0.712</v>
+        <v>13.573</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="7" t="inlineStr"/>
@@ -4529,28 +4529,28 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="E91" s="3" t="n">
-        <v>-0.0054</v>
+        <v>2.1</v>
+      </c>
+      <c r="E91" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F91" s="4" t="n">
-        <v>895800</v>
+        <v>1279700</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>0.21</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H91" t="n">
-        <v>36</v>
+        <v>50.69</v>
       </c>
       <c r="I91" s="9" t="inlineStr">
         <is>
@@ -4558,10 +4558,10 @@
         </is>
       </c>
       <c r="J91" s="2" t="n">
-        <v>1.894</v>
+        <v>2.098</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>2.026</v>
+        <v>2.08</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="7" t="inlineStr"/>
@@ -4574,28 +4574,28 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>5141</t>
+          <t>0172</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>DAYANG</t>
+          <t>OCK</t>
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="E92" s="3" t="n">
-        <v>-0.0069</v>
+        <v>0.45</v>
+      </c>
+      <c r="E92" s="10" t="n">
+        <v>0.0112</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v>877500</v>
+        <v>1248300</v>
       </c>
       <c r="G92" s="5" t="n">
-        <v>0.4</v>
+        <v>0.35</v>
       </c>
       <c r="H92" t="n">
-        <v>41.86</v>
+        <v>49.83</v>
       </c>
       <c r="I92" s="9" t="inlineStr">
         <is>
@@ -4603,10 +4603,10 @@
         </is>
       </c>
       <c r="J92" s="2" t="n">
-        <v>1.461</v>
+        <v>0.457</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>1.495</v>
+        <v>0.42</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="7" t="inlineStr"/>
@@ -4619,40 +4619,33 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>0475</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>GBBOND</t>
         </is>
       </c>
       <c r="D93" s="2" t="n">
-        <v>0.645</v>
+        <v>0.23</v>
       </c>
       <c r="E93" s="10" t="n">
-        <v>0.0157</v>
+        <v>0.0455</v>
       </c>
       <c r="F93" s="4" t="n">
-        <v>855000</v>
+        <v>1243500</v>
       </c>
       <c r="G93" s="5" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="H93" t="n">
-        <v>64.34999999999999</v>
-      </c>
-      <c r="I93" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J93" s="2" t="n">
-        <v>0.597</v>
-      </c>
-      <c r="K93" s="2" t="n">
-        <v>0.582</v>
-      </c>
+        <v>0.06</v>
+      </c>
+      <c r="I93" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="n"/>
+      <c r="K93" s="2" t="n"/>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="7" t="inlineStr"/>
     </row>
@@ -4664,28 +4657,28 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>7081</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D94" s="2" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="E94" s="8" t="n">
-        <v>0</v>
+        <v>0.535</v>
+      </c>
+      <c r="E94" s="10" t="n">
+        <v>0.009399999999999999</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>800100</v>
+        <v>1234800</v>
       </c>
       <c r="G94" s="5" t="n">
-        <v>0.34</v>
+        <v>0.16</v>
       </c>
       <c r="H94" t="n">
-        <v>20.91</v>
+        <v>55.09</v>
       </c>
       <c r="I94" s="9" t="inlineStr">
         <is>
@@ -4693,10 +4686,10 @@
         </is>
       </c>
       <c r="J94" s="2" t="n">
-        <v>1.037</v>
+        <v>0.522</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>1.119</v>
+        <v>0.531</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="7" t="inlineStr"/>
@@ -4709,39 +4702,39 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>5337</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>ECOSHOP</t>
         </is>
       </c>
       <c r="D95" s="2" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E95" s="8" t="n">
-        <v>0</v>
+        <v>1.46</v>
+      </c>
+      <c r="E95" s="10" t="n">
+        <v>0.021</v>
       </c>
       <c r="F95" s="4" t="n">
-        <v>799500</v>
+        <v>1228100</v>
       </c>
       <c r="G95" s="5" t="n">
-        <v>0.04</v>
+        <v>0.27</v>
       </c>
       <c r="H95" t="n">
-        <v>46.68</v>
-      </c>
-      <c r="I95" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.32</v>
+      </c>
+      <c r="I95" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.868</v>
+        <v>1.461</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>0.869</v>
+        <v>1.469</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="7" t="inlineStr"/>
@@ -4754,28 +4747,28 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D96" s="2" t="n">
-        <v>5.58</v>
-      </c>
-      <c r="E96" s="10" t="n">
-        <v>0.0036</v>
+        <v>4.22</v>
+      </c>
+      <c r="E96" s="3" t="n">
+        <v>-0.009399999999999999</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>790900</v>
+        <v>1181200</v>
       </c>
       <c r="G96" s="5" t="n">
-        <v>0.06</v>
+        <v>0.15</v>
       </c>
       <c r="H96" t="n">
-        <v>49.97</v>
+        <v>43.07</v>
       </c>
       <c r="I96" s="9" t="inlineStr">
         <is>
@@ -4783,10 +4776,10 @@
         </is>
       </c>
       <c r="J96" s="2" t="n">
-        <v>5.634</v>
+        <v>4.368</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>5.307</v>
+        <v>4.464</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="7" t="inlineStr"/>
@@ -4799,39 +4792,39 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>0277</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>MAHSING</t>
+          <t>CLOUDPT</t>
         </is>
       </c>
       <c r="D97" s="2" t="n">
-        <v>0.955</v>
+        <v>0.515</v>
       </c>
       <c r="E97" s="10" t="n">
-        <v>0.0106</v>
+        <v>0.0098</v>
       </c>
       <c r="F97" s="4" t="n">
-        <v>786000</v>
+        <v>1143900</v>
       </c>
       <c r="G97" s="5" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="H97" t="n">
-        <v>32.16</v>
-      </c>
-      <c r="I97" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.85</v>
+      </c>
+      <c r="I97" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.996</v>
+        <v>0.489</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>1.066</v>
+        <v>0.479</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="7" t="inlineStr"/>
@@ -4844,28 +4837,28 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>5162</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>VSTECS</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D98" s="2" t="n">
-        <v>1.73</v>
+        <v>0.55</v>
       </c>
       <c r="E98" s="10" t="n">
-        <v>0.0359</v>
+        <v>0.0092</v>
       </c>
       <c r="F98" s="4" t="n">
-        <v>732100</v>
+        <v>1092700</v>
       </c>
       <c r="G98" s="5" t="n">
-        <v>0.43</v>
+        <v>0.26</v>
       </c>
       <c r="H98" t="n">
-        <v>57.25</v>
+        <v>71.79000000000001</v>
       </c>
       <c r="I98" s="6" t="inlineStr">
         <is>
@@ -4873,10 +4866,10 @@
         </is>
       </c>
       <c r="J98" s="2" t="n">
-        <v>1.664</v>
+        <v>0.477</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>1.678</v>
+        <v>0.451</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="7" t="inlineStr"/>
@@ -4889,39 +4882,39 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D99" s="2" t="n">
-        <v>4.22</v>
+        <v>5.58</v>
       </c>
       <c r="E99" s="10" t="n">
-        <v>0.0144</v>
+        <v>0.0036</v>
       </c>
       <c r="F99" s="4" t="n">
-        <v>723700</v>
+        <v>1092600</v>
       </c>
       <c r="G99" s="5" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="H99" t="n">
-        <v>64.02</v>
-      </c>
-      <c r="I99" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.97</v>
+      </c>
+      <c r="I99" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J99" s="2" t="n">
-        <v>3.963</v>
+        <v>5.634</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>3.442</v>
+        <v>5.307</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="7" t="inlineStr"/>
@@ -4934,39 +4927,39 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>0277</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>CLOUDPT</t>
+          <t>AWC</t>
         </is>
       </c>
       <c r="D100" s="2" t="n">
-        <v>0.515</v>
-      </c>
-      <c r="E100" s="10" t="n">
-        <v>0.0098</v>
+        <v>0.635</v>
+      </c>
+      <c r="E100" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F100" s="4" t="n">
-        <v>715000</v>
+        <v>1089800</v>
       </c>
       <c r="G100" s="5" t="n">
-        <v>0.44</v>
+        <v>0.49</v>
       </c>
       <c r="H100" t="n">
-        <v>62.85</v>
-      </c>
-      <c r="I100" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>57.68</v>
+      </c>
+      <c r="I100" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.489</v>
+        <v>0.62</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>0.479</v>
+        <v>0.529</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="7" t="inlineStr"/>
@@ -4979,39 +4972,39 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>TENAGA</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D101" s="2" t="n">
-        <v>12.98</v>
-      </c>
-      <c r="E101" s="10" t="n">
-        <v>0.0062</v>
+        <v>0.93</v>
+      </c>
+      <c r="E101" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F101" s="4" t="n">
-        <v>708300</v>
+        <v>1088100</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>0.08</v>
+        <v>0.21</v>
       </c>
       <c r="H101" t="n">
-        <v>43.26</v>
-      </c>
-      <c r="I101" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>63.88</v>
+      </c>
+      <c r="I101" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J101" s="2" t="n">
-        <v>13.038</v>
+        <v>0.908</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>13.573</v>
+        <v>0.863</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="7" t="inlineStr"/>
@@ -5024,39 +5017,39 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>0450</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>CPETECH</t>
+          <t>MFGROUP</t>
         </is>
       </c>
       <c r="D102" s="2" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="E102" s="10" t="n">
-        <v>0.0226</v>
+        <v>0.265</v>
+      </c>
+      <c r="E102" s="3" t="n">
+        <v>-0.0185</v>
       </c>
       <c r="F102" s="4" t="n">
-        <v>699800</v>
+        <v>1082000</v>
       </c>
       <c r="G102" s="5" t="n">
-        <v>0.18</v>
+        <v>1.11</v>
       </c>
       <c r="H102" t="n">
-        <v>58.46</v>
-      </c>
-      <c r="I102" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>54.17</v>
+      </c>
+      <c r="I102" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J102" s="2" t="n">
-        <v>1.295</v>
+        <v>0.262</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>1.194</v>
+        <v>0.264</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="7" t="inlineStr"/>
@@ -5069,28 +5062,28 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>7233</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>DUFU</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D103" s="2" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="E103" s="3" t="n">
-        <v>-0.0031</v>
+        <v>0.805</v>
+      </c>
+      <c r="E103" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F103" s="4" t="n">
-        <v>654700</v>
+        <v>1071700</v>
       </c>
       <c r="G103" s="5" t="n">
-        <v>0.21</v>
+        <v>0.17</v>
       </c>
       <c r="H103" t="n">
-        <v>63.5</v>
+        <v>70.15000000000001</v>
       </c>
       <c r="I103" s="6" t="inlineStr">
         <is>
@@ -5098,10 +5091,10 @@
         </is>
       </c>
       <c r="J103" s="2" t="n">
-        <v>3.003</v>
+        <v>0.785</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>2.804</v>
+        <v>0.764</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="7" t="inlineStr"/>
@@ -5114,39 +5107,39 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>SEG</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D104" s="2" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E104" s="3" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.64</v>
+      </c>
+      <c r="E104" s="10" t="n">
+        <v>0.007900000000000001</v>
       </c>
       <c r="F104" s="4" t="n">
-        <v>615100</v>
+        <v>1056600</v>
       </c>
       <c r="G104" s="5" t="n">
-        <v>0.49</v>
+        <v>0.28</v>
       </c>
       <c r="H104" t="n">
-        <v>37.72</v>
-      </c>
-      <c r="I104" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.45</v>
+      </c>
+      <c r="I104" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.632</v>
+        <v>0.596</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>0.63</v>
+        <v>0.582</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="7" t="inlineStr"/>
@@ -5159,28 +5152,28 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D105" s="2" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="E105" s="10" t="n">
-        <v>0.0092</v>
+        <v>0.82</v>
+      </c>
+      <c r="E105" s="3" t="n">
+        <v>-0.0238</v>
       </c>
       <c r="F105" s="4" t="n">
-        <v>599000</v>
+        <v>1033500</v>
       </c>
       <c r="G105" s="5" t="n">
-        <v>0.14</v>
+        <v>0.16</v>
       </c>
       <c r="H105" t="n">
-        <v>71.79000000000001</v>
+        <v>69.3</v>
       </c>
       <c r="I105" s="6" t="inlineStr">
         <is>
@@ -5188,10 +5181,10 @@
         </is>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.477</v>
+        <v>0.749</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>0.451</v>
+        <v>0.663</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="7" t="inlineStr"/>
@@ -5204,39 +5197,39 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>0223</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>SAMAIDEN</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D106" s="2" t="n">
-        <v>3.07</v>
+        <v>0.49</v>
       </c>
       <c r="E106" s="10" t="n">
-        <v>0.0199</v>
+        <v>0.0103</v>
       </c>
       <c r="F106" s="4" t="n">
-        <v>594700</v>
+        <v>1015800</v>
       </c>
       <c r="G106" s="5" t="n">
         <v>0.14</v>
       </c>
       <c r="H106" t="n">
-        <v>69.84999999999999</v>
-      </c>
-      <c r="I106" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>28.72</v>
+      </c>
+      <c r="I106" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J106" s="2" t="n">
-        <v>2.695</v>
+        <v>0.524</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>2.043</v>
+        <v>0.571</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="7" t="inlineStr"/>
@@ -5249,28 +5242,28 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>3662</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>MFLOUR</t>
         </is>
       </c>
       <c r="D107" s="2" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="E107" s="8" t="n">
-        <v>0</v>
+        <v>0.6</v>
+      </c>
+      <c r="E107" s="10" t="n">
+        <v>0.0256</v>
       </c>
       <c r="F107" s="4" t="n">
-        <v>592700</v>
+        <v>1009000</v>
       </c>
       <c r="G107" s="5" t="n">
-        <v>0.2</v>
+        <v>0.43</v>
       </c>
       <c r="H107" t="n">
-        <v>54.4</v>
+        <v>40.75</v>
       </c>
       <c r="I107" s="9" t="inlineStr">
         <is>
@@ -5278,10 +5271,10 @@
         </is>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.639</v>
+        <v>0.617</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>0.611</v>
+        <v>0.635</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="7" t="inlineStr"/>
@@ -5294,39 +5287,39 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>0272</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>CMSB</t>
+          <t>TTVHB</t>
         </is>
       </c>
       <c r="D108" s="2" t="n">
-        <v>0.915</v>
+        <v>0.26</v>
       </c>
       <c r="E108" s="10" t="n">
-        <v>0.011</v>
+        <v>0.0612</v>
       </c>
       <c r="F108" s="4" t="n">
-        <v>587300</v>
+        <v>1005600</v>
       </c>
       <c r="G108" s="5" t="n">
-        <v>0.29</v>
+        <v>0.5</v>
       </c>
       <c r="H108" t="n">
-        <v>31.21</v>
-      </c>
-      <c r="I108" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.07</v>
+      </c>
+      <c r="I108" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.959</v>
+        <v>0.249</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>0.993</v>
+        <v>0.253</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="7" t="inlineStr"/>
@@ -5339,28 +5332,28 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>MAHSING</t>
         </is>
       </c>
       <c r="D109" s="2" t="n">
-        <v>2.5</v>
+        <v>0.95</v>
       </c>
       <c r="E109" s="10" t="n">
-        <v>0.008100000000000001</v>
+        <v>0.0053</v>
       </c>
       <c r="F109" s="4" t="n">
-        <v>580100</v>
+        <v>983000</v>
       </c>
       <c r="G109" s="5" t="n">
-        <v>0.04</v>
+        <v>0.25</v>
       </c>
       <c r="H109" t="n">
-        <v>58.18</v>
+        <v>30.03</v>
       </c>
       <c r="I109" s="9" t="inlineStr">
         <is>
@@ -5368,10 +5361,10 @@
         </is>
       </c>
       <c r="J109" s="2" t="n">
-        <v>2.463</v>
+        <v>0.996</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>2.344</v>
+        <v>1.066</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="7" t="inlineStr"/>
@@ -5384,28 +5377,28 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>5323</t>
+          <t>0271</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>JPG</t>
+          <t>WELLS</t>
         </is>
       </c>
       <c r="D110" s="2" t="n">
-        <v>1.77</v>
+        <v>0.53</v>
       </c>
       <c r="E110" s="10" t="n">
-        <v>0.0172</v>
+        <v>0.0291</v>
       </c>
       <c r="F110" s="4" t="n">
-        <v>563600</v>
+        <v>963600</v>
       </c>
       <c r="G110" s="5" t="n">
-        <v>0.09</v>
+        <v>0.87</v>
       </c>
       <c r="H110" t="n">
-        <v>40.32</v>
+        <v>26.64</v>
       </c>
       <c r="I110" s="9" t="inlineStr">
         <is>
@@ -5413,10 +5406,10 @@
         </is>
       </c>
       <c r="J110" s="2" t="n">
-        <v>1.824</v>
+        <v>0.582</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>1.927</v>
+        <v>0.622</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="7" t="inlineStr"/>
@@ -5429,39 +5422,39 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>7160</t>
+          <t>5306</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>PENTA</t>
+          <t>FFB</t>
         </is>
       </c>
       <c r="D111" s="2" t="n">
-        <v>5.98</v>
+        <v>1.79</v>
       </c>
       <c r="E111" s="10" t="n">
-        <v>0.0205</v>
+        <v>0.0229</v>
       </c>
       <c r="F111" s="4" t="n">
-        <v>554800</v>
+        <v>942500</v>
       </c>
       <c r="G111" s="5" t="n">
-        <v>0.16</v>
+        <v>0.32</v>
       </c>
       <c r="H111" t="n">
-        <v>64.55</v>
-      </c>
-      <c r="I111" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>30.67</v>
+      </c>
+      <c r="I111" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J111" s="2" t="n">
-        <v>5.485</v>
+        <v>1.879</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>5.357</v>
+        <v>2.017</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="7" t="inlineStr"/>
@@ -5474,28 +5467,28 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D112" s="2" t="n">
-        <v>0.835</v>
-      </c>
-      <c r="E112" s="8" t="n">
-        <v>0</v>
+        <v>1.83</v>
+      </c>
+      <c r="E112" s="3" t="n">
+        <v>-0.0054</v>
       </c>
       <c r="F112" s="4" t="n">
-        <v>542200</v>
+        <v>940500</v>
       </c>
       <c r="G112" s="5" t="n">
-        <v>0.17</v>
+        <v>0.22</v>
       </c>
       <c r="H112" t="n">
-        <v>58.39</v>
+        <v>36</v>
       </c>
       <c r="I112" s="9" t="inlineStr">
         <is>
@@ -5503,10 +5496,10 @@
         </is>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.819</v>
+        <v>1.894</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>0.756</v>
+        <v>2.026</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="7" t="inlineStr"/>
@@ -5519,28 +5512,28 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D113" s="2" t="n">
-        <v>1.19</v>
+        <v>2.49</v>
       </c>
       <c r="E113" s="10" t="n">
-        <v>0.0259</v>
+        <v>0.004</v>
       </c>
       <c r="F113" s="4" t="n">
-        <v>525200</v>
+        <v>933600</v>
       </c>
       <c r="G113" s="5" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H113" t="n">
-        <v>55.65</v>
+        <v>57.08</v>
       </c>
       <c r="I113" s="9" t="inlineStr">
         <is>
@@ -5548,10 +5541,10 @@
         </is>
       </c>
       <c r="J113" s="2" t="n">
-        <v>1.154</v>
+        <v>2.462</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>1.165</v>
+        <v>2.344</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="7" t="inlineStr"/>
@@ -5564,28 +5557,28 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D114" s="2" t="n">
-        <v>0.775</v>
+        <v>4.23</v>
       </c>
       <c r="E114" s="10" t="n">
-        <v>0.0197</v>
+        <v>0.0168</v>
       </c>
       <c r="F114" s="4" t="n">
-        <v>510700</v>
+        <v>929300</v>
       </c>
       <c r="G114" s="5" t="n">
-        <v>0.28</v>
+        <v>0.11</v>
       </c>
       <c r="H114" t="n">
-        <v>63.64</v>
+        <v>64.26000000000001</v>
       </c>
       <c r="I114" s="6" t="inlineStr">
         <is>
@@ -5593,16 +5586,1051 @@
         </is>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.712</v>
+        <v>3.964</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>0.6909999999999999</v>
+        <v>3.443</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="7" t="inlineStr"/>
     </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>5317</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>CPETECH</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="E115" s="10" t="n">
+        <v>0.0226</v>
+      </c>
+      <c r="F115" s="4" t="n">
+        <v>924700</v>
+      </c>
+      <c r="G115" s="5" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H115" t="n">
+        <v>58.46</v>
+      </c>
+      <c r="I115" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J115" s="2" t="n">
+        <v>1.295</v>
+      </c>
+      <c r="K115" s="2" t="n">
+        <v>1.194</v>
+      </c>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" s="7" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>5184</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>CYPARK</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="n">
+        <v>0.795</v>
+      </c>
+      <c r="E116" s="10" t="n">
+        <v>0.0127</v>
+      </c>
+      <c r="F116" s="4" t="n">
+        <v>916300</v>
+      </c>
+      <c r="G116" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H116" t="n">
+        <v>57.16</v>
+      </c>
+      <c r="I116" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J116" s="2" t="n">
+        <v>0.767</v>
+      </c>
+      <c r="K116" s="2" t="n">
+        <v>0.712</v>
+      </c>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" s="7" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>7233</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>DUFU</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="E117" s="3" t="n">
+        <v>-0.009300000000000001</v>
+      </c>
+      <c r="F117" s="4" t="n">
+        <v>895200</v>
+      </c>
+      <c r="G117" s="5" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H117" t="n">
+        <v>62.41</v>
+      </c>
+      <c r="I117" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J117" s="2" t="n">
+        <v>3.002</v>
+      </c>
+      <c r="K117" s="2" t="n">
+        <v>2.804</v>
+      </c>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" s="7" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>5162</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>VSTECS</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="E118" s="10" t="n">
+        <v>0.0359</v>
+      </c>
+      <c r="F118" s="4" t="n">
+        <v>848600</v>
+      </c>
+      <c r="G118" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H118" t="n">
+        <v>57.25</v>
+      </c>
+      <c r="I118" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J118" s="2" t="n">
+        <v>1.664</v>
+      </c>
+      <c r="K118" s="2" t="n">
+        <v>1.678</v>
+      </c>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" s="7" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>7081</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>PHARMA</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="n">
+        <v>0.925</v>
+      </c>
+      <c r="E119" s="10" t="n">
+        <v>0.0054</v>
+      </c>
+      <c r="F119" s="4" t="n">
+        <v>818800</v>
+      </c>
+      <c r="G119" s="5" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H119" t="n">
+        <v>22.43</v>
+      </c>
+      <c r="I119" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J119" s="2" t="n">
+        <v>1.037</v>
+      </c>
+      <c r="K119" s="2" t="n">
+        <v>1.119</v>
+      </c>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" s="7" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>2852</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>CMSB</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="n">
+        <v>0.915</v>
+      </c>
+      <c r="E120" s="10" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="F120" s="4" t="n">
+        <v>787700</v>
+      </c>
+      <c r="G120" s="5" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="H120" t="n">
+        <v>31.21</v>
+      </c>
+      <c r="I120" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J120" s="2" t="n">
+        <v>0.959</v>
+      </c>
+      <c r="K120" s="2" t="n">
+        <v>0.993</v>
+      </c>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" s="7" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>6633</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>LHI</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="E121" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F121" s="4" t="n">
+        <v>730700</v>
+      </c>
+      <c r="G121" s="5" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="H121" t="n">
+        <v>47.32</v>
+      </c>
+      <c r="I121" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J121" s="2" t="n">
+        <v>0.735</v>
+      </c>
+      <c r="K121" s="2" t="n">
+        <v>0.749</v>
+      </c>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" s="7" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>5302</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>ATECH</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="n">
+        <v>0.805</v>
+      </c>
+      <c r="E122" s="10" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="F122" s="4" t="n">
+        <v>705900</v>
+      </c>
+      <c r="G122" s="5" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="H122" t="n">
+        <v>59.79</v>
+      </c>
+      <c r="I122" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J122" s="2" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="K122" s="2" t="n">
+        <v>0.761</v>
+      </c>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" s="7" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>7160</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>PENTA</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="n">
+        <v>5.91</v>
+      </c>
+      <c r="E123" s="10" t="n">
+        <v>0.008500000000000001</v>
+      </c>
+      <c r="F123" s="4" t="n">
+        <v>683300</v>
+      </c>
+      <c r="G123" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H123" t="n">
+        <v>63.28</v>
+      </c>
+      <c r="I123" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J123" s="2" t="n">
+        <v>5.479</v>
+      </c>
+      <c r="K123" s="2" t="n">
+        <v>5.356</v>
+      </c>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" s="7" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>0223</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>SAMAIDEN</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="E124" s="10" t="n">
+        <v>0.0166</v>
+      </c>
+      <c r="F124" s="4" t="n">
+        <v>676300</v>
+      </c>
+      <c r="G124" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H124" t="n">
+        <v>69.63</v>
+      </c>
+      <c r="I124" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J124" s="2" t="n">
+        <v>2.694</v>
+      </c>
+      <c r="K124" s="2" t="n">
+        <v>2.043</v>
+      </c>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" s="7" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>5323</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>JPG</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="E125" s="10" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="F125" s="4" t="n">
+        <v>650300</v>
+      </c>
+      <c r="G125" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H125" t="n">
+        <v>41.73</v>
+      </c>
+      <c r="I125" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J125" s="2" t="n">
+        <v>1.825</v>
+      </c>
+      <c r="K125" s="2" t="n">
+        <v>1.927</v>
+      </c>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" s="7" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>0292</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>JTGROUP</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="E126" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F126" s="4" t="n">
+        <v>643400</v>
+      </c>
+      <c r="G126" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H126" t="n">
+        <v>72.14</v>
+      </c>
+      <c r="I126" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J126" s="2" t="n">
+        <v>1.237</v>
+      </c>
+      <c r="K126" s="2" t="n">
+        <v>1.008</v>
+      </c>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" s="7" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>0127</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>JHM</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="n">
+        <v>0.605</v>
+      </c>
+      <c r="E127" s="10" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="F127" s="4" t="n">
+        <v>635900</v>
+      </c>
+      <c r="G127" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H127" t="n">
+        <v>70.43000000000001</v>
+      </c>
+      <c r="I127" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J127" s="2" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="K127" s="2" t="n">
+        <v>0.493</v>
+      </c>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" s="7" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>0167</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>MCLEAN</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="n">
+        <v>0.735</v>
+      </c>
+      <c r="E128" s="10" t="n">
+        <v>0.0068</v>
+      </c>
+      <c r="F128" s="4" t="n">
+        <v>620200</v>
+      </c>
+      <c r="G128" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H128" t="n">
+        <v>44.96</v>
+      </c>
+      <c r="I128" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J128" s="2" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="K128" s="2" t="n">
+        <v>0.747</v>
+      </c>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" s="7" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>9792</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>SEG</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="E129" s="3" t="n">
+        <v>-0.007900000000000001</v>
+      </c>
+      <c r="F129" s="4" t="n">
+        <v>615100</v>
+      </c>
+      <c r="G129" s="5" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="H129" t="n">
+        <v>37.72</v>
+      </c>
+      <c r="I129" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J129" s="2" t="n">
+        <v>0.632</v>
+      </c>
+      <c r="K129" s="2" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" s="7" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>0146</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>JFTECH</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="E130" s="10" t="n">
+        <v>0.0197</v>
+      </c>
+      <c r="F130" s="4" t="n">
+        <v>601200</v>
+      </c>
+      <c r="G130" s="5" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="H130" t="n">
+        <v>63.64</v>
+      </c>
+      <c r="I130" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J130" s="2" t="n">
+        <v>0.712</v>
+      </c>
+      <c r="K130" s="2" t="n">
+        <v>0.6909999999999999</v>
+      </c>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" s="7" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>0390</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>ISF</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="E131" s="10" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="F131" s="4" t="n">
+        <v>600800</v>
+      </c>
+      <c r="G131" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H131" t="n">
+        <v>59.49</v>
+      </c>
+      <c r="I131" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J131" s="2" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="K131" s="2" t="n">
+        <v>0.756</v>
+      </c>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" s="7" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>0112</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>MIKROMB</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="E132" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F132" s="4" t="n">
+        <v>592700</v>
+      </c>
+      <c r="G132" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H132" t="n">
+        <v>54.4</v>
+      </c>
+      <c r="I132" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J132" s="2" t="n">
+        <v>0.639</v>
+      </c>
+      <c r="K132" s="2" t="n">
+        <v>0.611</v>
+      </c>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" s="7" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>0217</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>PWRWELL</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="E133" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F133" s="4" t="n">
+        <v>583200</v>
+      </c>
+      <c r="G133" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H133" t="n">
+        <v>58.23</v>
+      </c>
+      <c r="I133" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J133" s="2" t="n">
+        <v>1.152</v>
+      </c>
+      <c r="K133" s="2" t="n">
+        <v>1.066</v>
+      </c>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" s="7" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>5357</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>SKYECHIP</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="E134" s="10" t="n">
+        <v>0.0034</v>
+      </c>
+      <c r="F134" s="4" t="n">
+        <v>549500</v>
+      </c>
+      <c r="G134" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H134" t="n">
+        <v>45.93</v>
+      </c>
+      <c r="I134" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J134" s="2" t="n">
+        <v>2.975</v>
+      </c>
+      <c r="K134" s="2" t="n">
+        <v>3.034</v>
+      </c>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" s="7" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>5199</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>HIBISCS</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="E135" s="3" t="n">
+        <v>-0.0225</v>
+      </c>
+      <c r="F135" s="4" t="n">
+        <v>536600</v>
+      </c>
+      <c r="G135" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H135" t="n">
+        <v>49.02</v>
+      </c>
+      <c r="I135" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J135" s="2" t="n">
+        <v>2.188</v>
+      </c>
+      <c r="K135" s="2" t="n">
+        <v>2.127</v>
+      </c>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" s="7" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>0225</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>SCGBHD</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="E136" s="10" t="n">
+        <v>0.0035</v>
+      </c>
+      <c r="F136" s="4" t="n">
+        <v>523500</v>
+      </c>
+      <c r="G136" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H136" t="n">
+        <v>56.65</v>
+      </c>
+      <c r="I136" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J136" s="2" t="n">
+        <v>2.776</v>
+      </c>
+      <c r="K136" s="2" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" s="7" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>6888</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>AXIATA</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="E137" s="3" t="n">
+        <v>-0.0063</v>
+      </c>
+      <c r="F137" s="4" t="n">
+        <v>513800</v>
+      </c>
+      <c r="G137" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H137" t="n">
+        <v>32.03</v>
+      </c>
+      <c r="I137" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J137" s="2" t="n">
+        <v>1.666</v>
+      </c>
+      <c r="K137" s="2" t="n">
+        <v>1.786</v>
+      </c>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M114"/>
+  <autoFilter ref="A1:M137"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-09/bursa-report-2026-10-09.xlsx
+++ b/docs/downloads/2026-10-09/bursa-report-2026-10-09.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-09" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-09'!$A$1:$M$137</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-09'!$A$1:$M$152</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M137"/>
+  <dimension ref="A1:M152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -552,19 +552,19 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.51</v>
+        <v>0.515</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>-0.0286</v>
+        <v>-0.019</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>77848400</v>
+        <v>80258600</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>2.73</v>
+        <v>2.82</v>
       </c>
       <c r="H2" t="n">
-        <v>58.81</v>
+        <v>60.83</v>
       </c>
       <c r="I2" s="6" t="inlineStr">
         <is>
@@ -575,7 +575,7 @@
         <v>0.49</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0.478</v>
+        <v>0.479</v>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" s="7" t="inlineStr"/>
@@ -633,39 +633,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>0138</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>ZETRIX</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>-0.0286</v>
+        <v>0.08</v>
+      </c>
+      <c r="E4" s="10" t="n">
+        <v>0.0667</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>25910000</v>
+        <v>38259700</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.34</v>
+        <v>0.09</v>
       </c>
       <c r="H4" t="n">
-        <v>64.59999999999999</v>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>22.11</v>
+      </c>
+      <c r="I4" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.783</v>
+        <v>0.175</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.71</v>
+        <v>0.397</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" s="7" t="inlineStr"/>
@@ -678,39 +678,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0138</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ZETRIX</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="E5" s="8" t="n">
-        <v>0</v>
+        <v>0.345</v>
+      </c>
+      <c r="E5" s="10" t="n">
+        <v>0.0455</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>22298800</v>
+        <v>30655300</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.05</v>
+        <v>0.52</v>
       </c>
       <c r="H5" t="n">
-        <v>20.62</v>
-      </c>
-      <c r="I5" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>78.38</v>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.174</v>
+        <v>0.279</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.397</v>
+        <v>0.245</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" s="7" t="inlineStr"/>
@@ -723,39 +723,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="E6" s="8" t="n">
-        <v>0</v>
+        <v>0.85</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>-0.0286</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>21894000</v>
+        <v>28255300</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.37</v>
       </c>
       <c r="H6" t="n">
-        <v>47.95</v>
-      </c>
-      <c r="I6" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.59999999999999</v>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.195</v>
+        <v>0.783</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.183</v>
+        <v>0.71</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" s="7" t="inlineStr"/>
@@ -777,19 +777,19 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.0204</v>
+        <v>0.0255</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>21210400</v>
+        <v>25313000</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.85</v>
+        <v>1.01</v>
       </c>
       <c r="H7" t="n">
-        <v>71</v>
+        <v>71.48</v>
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>1.81</v>
+        <v>1.811</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>1.636</v>
@@ -813,39 +813,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="E8" s="10" t="n">
-        <v>0.0303</v>
+        <v>0.19</v>
+      </c>
+      <c r="E8" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>18193900</v>
+        <v>22020200</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.31</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>77.59999999999999</v>
-      </c>
-      <c r="I8" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.95</v>
+      </c>
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.278</v>
+        <v>0.195</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.245</v>
+        <v>0.183</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="7" t="inlineStr"/>
@@ -873,7 +873,7 @@
         <v>-0.027</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>17474600</v>
+        <v>17598100</v>
       </c>
       <c r="G9" s="5" t="n">
         <v>0.27</v>
@@ -912,19 +912,19 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="E10" s="3" t="n">
-        <v>-0.0128</v>
+        <v>0.39</v>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>15169200</v>
+        <v>16578400</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.36</v>
+        <v>0.39</v>
       </c>
       <c r="H10" t="n">
-        <v>68.02</v>
+        <v>70.36</v>
       </c>
       <c r="I10" s="6" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.357</v>
+        <v>0.358</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>0.236</v>
@@ -963,10 +963,10 @@
         <v>0.008100000000000001</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>14861500</v>
+        <v>15277600</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.57</v>
+        <v>0.59</v>
       </c>
       <c r="H11" t="n">
         <v>70.55</v>
@@ -1002,19 +1002,19 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>0.0149</v>
+        <v>0.04480000000000001</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>13705100</v>
+        <v>14701700</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="H12" t="n">
-        <v>69.98</v>
+        <v>72.73999999999999</v>
       </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
@@ -1034,39 +1034,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>0278</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MALAKOF</t>
+          <t>EDELTEQ</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0.8</v>
+        <v>0.48</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>0.0256</v>
+        <v>0.1034</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>9254500</v>
+        <v>10839500</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>2.5</v>
+        <v>4.72</v>
       </c>
       <c r="H13" t="n">
-        <v>51.34</v>
-      </c>
-      <c r="I13" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>80.09</v>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.792</v>
+        <v>0.36</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0.806</v>
+        <v>0.349</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="7" t="inlineStr"/>
@@ -1079,28 +1079,28 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0278</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>EDELTEQ</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0.47</v>
+        <v>0.735</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>0.0805</v>
+        <v>0.05</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>8474000</v>
+        <v>9661500</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>3.69</v>
+        <v>1.27</v>
       </c>
       <c r="H14" t="n">
-        <v>79.16</v>
+        <v>60.21</v>
       </c>
       <c r="I14" s="6" t="inlineStr">
         <is>
@@ -1108,10 +1108,10 @@
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.359</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0.349</v>
+        <v>0.678</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="7" t="inlineStr"/>
@@ -1124,39 +1124,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>MALAKOF</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0.74</v>
+        <v>0.8</v>
       </c>
       <c r="E15" s="10" t="n">
-        <v>0.0571</v>
+        <v>0.0256</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>8249400</v>
+        <v>9375400</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>1.08</v>
+        <v>2.54</v>
       </c>
       <c r="H15" t="n">
-        <v>61.01</v>
-      </c>
-      <c r="I15" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>51.34</v>
+      </c>
+      <c r="I15" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.792</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0.678</v>
+        <v>0.806</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="7" t="inlineStr"/>
@@ -1169,39 +1169,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>5195</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CENSOF</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>0.235</v>
-      </c>
-      <c r="E16" s="3" t="n">
-        <v>-0.0208</v>
+        <v>0.405</v>
+      </c>
+      <c r="E16" s="10" t="n">
+        <v>0.1096</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>8228300</v>
+        <v>9201700</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>6.1</v>
+        <v>0.77</v>
       </c>
       <c r="H16" t="n">
-        <v>64.08</v>
-      </c>
-      <c r="I16" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>58.07</v>
+      </c>
+      <c r="I16" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.219</v>
+        <v>0.385</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0.206</v>
+        <v>0.375</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="7" t="inlineStr"/>
@@ -1214,28 +1214,28 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>5195</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>CENSOF</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>0.43</v>
+        <v>0.23</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-0.0337</v>
+        <v>-0.0417</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>7275100</v>
+        <v>8496300</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.27</v>
+        <v>6.3</v>
       </c>
       <c r="H17" t="n">
-        <v>59.31</v>
+        <v>59.96</v>
       </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
@@ -1243,10 +1243,10 @@
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.409</v>
+        <v>0.219</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0.346</v>
+        <v>0.206</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="7" t="inlineStr"/>
@@ -1259,39 +1259,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="E18" s="10" t="n">
-        <v>0.06849999999999999</v>
+        <v>0.435</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>-0.0225</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>6851900</v>
+        <v>7991300</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.57</v>
+        <v>0.3</v>
       </c>
       <c r="H18" t="n">
-        <v>53.45</v>
-      </c>
-      <c r="I18" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.91</v>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.384</v>
+        <v>0.41</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0.375</v>
+        <v>0.346</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="7" t="inlineStr"/>
@@ -1304,28 +1304,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AVANGAAD</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E19" s="8" t="n">
-        <v>0</v>
+        <v>0.465</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>-0.0211</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>6215100</v>
+        <v>6531300</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>2.36</v>
+        <v>0.17</v>
       </c>
       <c r="H19" t="n">
-        <v>49.15</v>
+        <v>25.65</v>
       </c>
       <c r="I19" s="9" t="inlineStr">
         <is>
@@ -1333,10 +1333,10 @@
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.295</v>
+        <v>0.548</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0.296</v>
+        <v>0.749</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="7" t="inlineStr"/>
@@ -1349,39 +1349,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0198</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>GDB</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>0.405</v>
-      </c>
-      <c r="E20" s="3" t="n">
-        <v>-0.0241</v>
+        <v>0.31</v>
+      </c>
+      <c r="E20" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>5983800</v>
+        <v>6470400</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>5.31</v>
+        <v>0.34</v>
       </c>
       <c r="H20" t="n">
-        <v>34.82</v>
-      </c>
-      <c r="I20" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.67</v>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.422</v>
+        <v>0.305</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0.441</v>
+        <v>0.295</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="7" t="inlineStr"/>
@@ -1394,28 +1394,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="E21" s="3" t="n">
-        <v>-0.0316</v>
+        <v>0.295</v>
+      </c>
+      <c r="E21" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>5974400</v>
+        <v>6215100</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.16</v>
+        <v>2.36</v>
       </c>
       <c r="H21" t="n">
-        <v>25.19</v>
+        <v>49.15</v>
       </c>
       <c r="I21" s="9" t="inlineStr">
         <is>
@@ -1423,10 +1423,10 @@
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.548</v>
+        <v>0.295</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0.749</v>
+        <v>0.296</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="7" t="inlineStr"/>
@@ -1439,40 +1439,33 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>7020</t>
+          <t>0476</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ASTEEL</t>
+          <t>SLGC Berhad</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>0.105</v>
+        <v>0.25</v>
       </c>
       <c r="E22" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>5830800</v>
+        <v>6133500</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="H22" t="n">
-        <v>59.81</v>
+        <v>0.14</v>
       </c>
       <c r="I22" s="6" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J22" s="2" t="n">
-        <v>0.096</v>
-      </c>
-      <c r="K22" s="2" t="n">
-        <v>0.08500000000000001</v>
-      </c>
+      <c r="J22" s="2" t="n"/>
+      <c r="K22" s="2" t="n"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="7" t="inlineStr"/>
     </row>
@@ -1484,33 +1477,40 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0476</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>SLGC Berhad</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E23" s="8" t="n">
-        <v>0</v>
+        <v>0.4</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>-0.0361</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>5501700</v>
+        <v>6099500</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="I23" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="n"/>
-      <c r="K23" s="2" t="n"/>
+        <v>5.41</v>
+      </c>
+      <c r="H23" t="n">
+        <v>32.62</v>
+      </c>
+      <c r="I23" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="n">
+        <v>0.421</v>
+      </c>
+      <c r="K23" s="2" t="n">
+        <v>0.441</v>
+      </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="7" t="inlineStr"/>
     </row>
@@ -1522,39 +1522,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="E24" s="3" t="n">
-        <v>-0.0127</v>
+        <v>0.775</v>
+      </c>
+      <c r="E24" s="10" t="n">
+        <v>0.006500000000000001</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>5471000</v>
+        <v>6030800</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.51</v>
+        <v>0.41</v>
       </c>
       <c r="H24" t="n">
-        <v>34.12</v>
-      </c>
-      <c r="I24" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.25</v>
+      </c>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.402</v>
+        <v>0.775</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0.41</v>
+        <v>0.775</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="7" t="inlineStr"/>
@@ -1567,36 +1567,40 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0470</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>BFIELD</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>0.485</v>
+        <v>2.82</v>
       </c>
       <c r="E25" s="10" t="n">
-        <v>0.0104</v>
+        <v>0.0144</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>5371600</v>
+        <v>5985600</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="H25" t="n">
-        <v>68.69</v>
-      </c>
-      <c r="I25" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="n"/>
-      <c r="K25" s="2" t="n"/>
+        <v>54.37</v>
+      </c>
+      <c r="I25" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="n">
+        <v>2.792</v>
+      </c>
+      <c r="K25" s="2" t="n">
+        <v>2.693</v>
+      </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="7" t="inlineStr"/>
     </row>
@@ -1608,40 +1612,36 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>0470</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>BFIELD</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E26" s="10" t="n">
-        <v>0.008100000000000001</v>
+        <v>0.48</v>
+      </c>
+      <c r="E26" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>4707600</v>
+        <v>5983300</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="H26" t="n">
-        <v>58.16</v>
+        <v>63.39</v>
       </c>
       <c r="I26" s="6" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J26" s="2" t="n">
-        <v>0.611</v>
-      </c>
-      <c r="K26" s="2" t="n">
-        <v>0.611</v>
-      </c>
+      <c r="J26" s="2" t="n"/>
+      <c r="K26" s="2" t="n"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="7" t="inlineStr"/>
     </row>
@@ -1653,39 +1653,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>7020</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>ASTEEL</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="E27" s="10" t="n">
-        <v>0.0144</v>
+        <v>0.105</v>
+      </c>
+      <c r="E27" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>4580400</v>
+        <v>5968100</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.33</v>
+        <v>2.69</v>
       </c>
       <c r="H27" t="n">
-        <v>54.37</v>
-      </c>
-      <c r="I27" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.81</v>
+      </c>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>2.792</v>
+        <v>0.096</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>2.693</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="7" t="inlineStr"/>
@@ -1698,28 +1698,28 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>0358</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>ICTZONE</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="E28" s="8" t="n">
-        <v>0</v>
+        <v>0.235</v>
+      </c>
+      <c r="E28" s="10" t="n">
+        <v>0.0444</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>4571200</v>
+        <v>5740900</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.68</v>
+        <v>2.06</v>
       </c>
       <c r="H28" t="n">
-        <v>53.56</v>
+        <v>46.06</v>
       </c>
       <c r="I28" s="9" t="inlineStr">
         <is>
@@ -1727,10 +1727,10 @@
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.368</v>
+        <v>0.241</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0.368</v>
+        <v>0.249</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="7" t="inlineStr"/>
@@ -1743,39 +1743,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E29" s="10" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.39</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>-0.0127</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>4570800</v>
+        <v>5698600</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.31</v>
+        <v>0.53</v>
       </c>
       <c r="H29" t="n">
-        <v>50.25</v>
-      </c>
-      <c r="I29" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.12</v>
+      </c>
+      <c r="I29" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.775</v>
+        <v>0.402</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0.775</v>
+        <v>0.41</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="7" t="inlineStr"/>
@@ -1788,28 +1788,28 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0358</t>
+          <t>7139</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ICTZONE</t>
+          <t>NICE</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="E30" s="10" t="n">
-        <v>0.0667</v>
+        <v>0.08</v>
+      </c>
+      <c r="E30" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>4425600</v>
+        <v>5595200</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>1.59</v>
+        <v>5.91</v>
       </c>
       <c r="H30" t="n">
-        <v>48.47</v>
+        <v>37.6</v>
       </c>
       <c r="I30" s="9" t="inlineStr">
         <is>
@@ -1817,10 +1817,10 @@
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.241</v>
+        <v>0.083</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0.249</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="7" t="inlineStr"/>
@@ -1833,28 +1833,28 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="E31" s="8" t="n">
-        <v>0</v>
+        <v>0.625</v>
+      </c>
+      <c r="E31" s="10" t="n">
+        <v>0.008100000000000001</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>4040400</v>
+        <v>5581800</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.21</v>
+        <v>0.53</v>
       </c>
       <c r="H31" t="n">
-        <v>57.67</v>
+        <v>58.16</v>
       </c>
       <c r="I31" s="6" t="inlineStr">
         <is>
@@ -1862,10 +1862,10 @@
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.305</v>
+        <v>0.611</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0.295</v>
+        <v>0.611</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="7" t="inlineStr"/>
@@ -1878,28 +1878,28 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>0.64</v>
+        <v>5.05</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>0.024</v>
+        <v>0.0202</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>3986000</v>
+        <v>5332900</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="H32" t="n">
-        <v>64.14</v>
+        <v>60.26</v>
       </c>
       <c r="I32" s="6" t="inlineStr">
         <is>
@@ -1907,10 +1907,10 @@
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.582</v>
+        <v>4.922</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0.519</v>
+        <v>4.652</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="7" t="inlineStr"/>
@@ -1923,28 +1923,28 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>6.77</v>
+        <v>0.64</v>
       </c>
       <c r="E33" s="10" t="n">
-        <v>0.1135</v>
+        <v>0.024</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>3920600</v>
+        <v>5011700</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.88</v>
+        <v>0.27</v>
       </c>
       <c r="H33" t="n">
-        <v>66.16</v>
+        <v>64.14</v>
       </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
@@ -1952,10 +1952,10 @@
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>5.838</v>
+        <v>0.582</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>5.78</v>
+        <v>0.519</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="7" t="inlineStr"/>
@@ -1968,28 +1968,28 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>5.05</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="E34" s="10" t="n">
-        <v>0.0202</v>
+        <v>0.0062</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>3826500</v>
+        <v>4934900</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.16</v>
+        <v>0.31</v>
       </c>
       <c r="H34" t="n">
-        <v>60.26</v>
+        <v>54.76</v>
       </c>
       <c r="I34" s="6" t="inlineStr">
         <is>
@@ -1997,10 +1997,10 @@
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>4.922</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>4.652</v>
+        <v>0.806</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="7" t="inlineStr"/>
@@ -2013,28 +2013,28 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>0.8149999999999999</v>
+        <v>6.73</v>
       </c>
       <c r="E35" s="10" t="n">
-        <v>0.0062</v>
+        <v>0.1069</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>3780000</v>
+        <v>4824600</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.24</v>
+        <v>1.08</v>
       </c>
       <c r="H35" t="n">
-        <v>54.76</v>
+        <v>65.73999999999999</v>
       </c>
       <c r="I35" s="6" t="inlineStr">
         <is>
@@ -2042,10 +2042,10 @@
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>5.834</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0.806</v>
+        <v>5.779</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="7" t="inlineStr"/>
@@ -2058,39 +2058,39 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0376</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>IAB</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="E36" s="3" t="n">
-        <v>-0.0222</v>
+        <v>0.37</v>
+      </c>
+      <c r="E36" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>3726300</v>
+        <v>4701200</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>2.15</v>
+        <v>0.7</v>
       </c>
       <c r="H36" t="n">
-        <v>54.18</v>
-      </c>
-      <c r="I36" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.56</v>
+      </c>
+      <c r="I36" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>1.275</v>
+        <v>0.368</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>1.32</v>
+        <v>0.368</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="7" t="inlineStr"/>
@@ -2103,28 +2103,28 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0111</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>K1</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>0.165</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E37" s="10" t="n">
-        <v>0.0313</v>
+        <v>0.0698</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>3667800</v>
+        <v>4636100</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>1.12</v>
+        <v>1.02</v>
       </c>
       <c r="H37" t="n">
-        <v>59.38</v>
+        <v>85.51000000000001</v>
       </c>
       <c r="I37" s="6" t="inlineStr">
         <is>
@@ -2132,10 +2132,10 @@
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.156</v>
+        <v>0.518</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0.145</v>
+        <v>0.443</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="7" t="inlineStr"/>
@@ -2163,10 +2163,10 @@
         <v>0.0857</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>3570000</v>
+        <v>4612900</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.66</v>
+        <v>0.85</v>
       </c>
       <c r="H38" t="n">
         <v>67.38</v>
@@ -2193,28 +2193,28 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>5253</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ECONBHD</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>0.125</v>
+        <v>0.865</v>
       </c>
       <c r="E39" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>3288700</v>
+        <v>3912700</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.72</v>
+        <v>0.21</v>
       </c>
       <c r="H39" t="n">
-        <v>55.25</v>
+        <v>46.68</v>
       </c>
       <c r="I39" s="6" t="inlineStr">
         <is>
@@ -2222,10 +2222,10 @@
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.122</v>
+        <v>0.868</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0.125</v>
+        <v>0.869</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="7" t="inlineStr"/>
@@ -2238,39 +2238,39 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>9.789999999999999</v>
-      </c>
-      <c r="E40" s="3" t="n">
-        <v>-0.001</v>
+        <v>0.795</v>
+      </c>
+      <c r="E40" s="10" t="n">
+        <v>0.0063</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>3272900</v>
+        <v>3907800</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.26</v>
+        <v>0.49</v>
       </c>
       <c r="H40" t="n">
-        <v>29.86</v>
-      </c>
-      <c r="I40" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.55</v>
+      </c>
+      <c r="I40" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>10.02</v>
+        <v>0.779</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>10.213</v>
+        <v>0.773</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="7" t="inlineStr"/>
@@ -2283,36 +2283,40 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0468</t>
+          <t>0376</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>UNIPAC</t>
+          <t>IAB</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E41" s="8" t="n">
-        <v>0</v>
+        <v>1.32</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>-0.0222</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>3083100</v>
+        <v>3871100</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.26</v>
+        <v>2.23</v>
       </c>
       <c r="H41" t="n">
-        <v>28.11</v>
+        <v>54.18</v>
       </c>
       <c r="I41" s="6" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J41" s="2" t="n"/>
-      <c r="K41" s="2" t="n"/>
+      <c r="J41" s="2" t="n">
+        <v>1.275</v>
+      </c>
+      <c r="K41" s="2" t="n">
+        <v>1.32</v>
+      </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="7" t="inlineStr"/>
     </row>
@@ -2324,39 +2328,39 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>0111</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>3.73</v>
-      </c>
-      <c r="E42" s="3" t="n">
-        <v>-0.0106</v>
+        <v>0.165</v>
+      </c>
+      <c r="E42" s="10" t="n">
+        <v>0.0313</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>3064100</v>
+        <v>3780100</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.27</v>
+        <v>1.15</v>
       </c>
       <c r="H42" t="n">
-        <v>57.15</v>
-      </c>
-      <c r="I42" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.38</v>
+      </c>
+      <c r="I42" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>3.603</v>
+        <v>0.156</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>2.74</v>
+        <v>0.145</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="7" t="inlineStr"/>
@@ -2369,28 +2373,28 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>SPSETIA</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>0.715</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>-0.0138</v>
+        <v>-0.001</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>3034500</v>
+        <v>3728300</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.51</v>
+        <v>0.3</v>
       </c>
       <c r="H43" t="n">
-        <v>32.64</v>
+        <v>29.86</v>
       </c>
       <c r="I43" s="9" t="inlineStr">
         <is>
@@ -2398,10 +2402,10 @@
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.756</v>
+        <v>10.02</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>0.819</v>
+        <v>10.213</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="7" t="inlineStr"/>
@@ -2414,39 +2418,39 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="E44" s="3" t="n">
-        <v>-0.0256</v>
+        <v>4.56</v>
+      </c>
+      <c r="E44" s="10" t="n">
+        <v>0.0022</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>2969600</v>
+        <v>3706300</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="H44" t="n">
-        <v>48.21</v>
-      </c>
-      <c r="I44" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>27.57</v>
+      </c>
+      <c r="I44" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>1.162</v>
+        <v>4.721</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>1.119</v>
+        <v>4.891</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="7" t="inlineStr"/>
@@ -2459,28 +2463,28 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>WCT</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="E45" s="8" t="n">
-        <v>0</v>
+        <v>2.13</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>-0.004699999999999999</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>2911600</v>
+        <v>3489100</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.73</v>
+        <v>0.24</v>
       </c>
       <c r="H45" t="n">
-        <v>32.2</v>
+        <v>40.49</v>
       </c>
       <c r="I45" s="9" t="inlineStr">
         <is>
@@ -2488,10 +2492,10 @@
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.363</v>
+        <v>2.224</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0.383</v>
+        <v>2.212</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="7" t="inlineStr"/>
@@ -2504,39 +2508,39 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>SPSETIA</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>0.675</v>
-      </c>
-      <c r="E46" s="10" t="n">
-        <v>0.04650000000000001</v>
+        <v>0.72</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>-0.0069</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>2854000</v>
+        <v>3423700</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.63</v>
+        <v>0.58</v>
       </c>
       <c r="H46" t="n">
-        <v>84.73999999999999</v>
-      </c>
-      <c r="I46" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.63</v>
+      </c>
+      <c r="I46" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.516</v>
+        <v>0.756</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>0.443</v>
+        <v>0.819</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="7" t="inlineStr"/>
@@ -2549,28 +2553,28 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>5326</t>
+          <t>5253</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>99SMART</t>
+          <t>ECONBHD</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="E47" s="10" t="n">
-        <v>0.0449</v>
+        <v>0.125</v>
+      </c>
+      <c r="E47" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>2824700</v>
+        <v>3288700</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.66</v>
+        <v>0.72</v>
       </c>
       <c r="H47" t="n">
-        <v>52.06</v>
+        <v>55.25</v>
       </c>
       <c r="I47" s="6" t="inlineStr">
         <is>
@@ -2578,10 +2582,10 @@
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>3.199</v>
+        <v>0.122</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>3.39</v>
+        <v>0.125</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="7" t="inlineStr"/>
@@ -2594,39 +2598,39 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E48" s="10" t="n">
-        <v>0.0127</v>
+        <v>3.73</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>-0.0106</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>2778900</v>
+        <v>3203000</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.35</v>
+        <v>0.28</v>
       </c>
       <c r="H48" t="n">
-        <v>56.78</v>
-      </c>
-      <c r="I48" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>57.15</v>
+      </c>
+      <c r="I48" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.78</v>
+        <v>3.603</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0.773</v>
+        <v>2.74</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="7" t="inlineStr"/>
@@ -2639,39 +2643,39 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="E49" s="3" t="n">
-        <v>-0.0108</v>
+        <v>0.34</v>
+      </c>
+      <c r="E49" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>2681800</v>
+        <v>3199900</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.15</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H49" t="n">
-        <v>62.29</v>
-      </c>
-      <c r="I49" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>32.2</v>
+      </c>
+      <c r="I49" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>2.624</v>
+        <v>0.363</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>2.496</v>
+        <v>0.383</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="7" t="inlineStr"/>
@@ -2684,39 +2688,39 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>5326</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>99SMART</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>0.92</v>
+        <v>3.25</v>
       </c>
       <c r="E50" s="10" t="n">
-        <v>0.0337</v>
+        <v>0.0417</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>2660100</v>
+        <v>3135600</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.92</v>
+        <v>0.74</v>
       </c>
       <c r="H50" t="n">
-        <v>50.01</v>
-      </c>
-      <c r="I50" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.28</v>
+      </c>
+      <c r="I50" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.912</v>
+        <v>3.198</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>0.965</v>
+        <v>3.39</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="7" t="inlineStr"/>
@@ -2744,10 +2748,10 @@
         <v>0</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>2654000</v>
+        <v>3117500</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.38</v>
+        <v>0.45</v>
       </c>
       <c r="H51" t="n">
         <v>62.48</v>
@@ -2774,40 +2778,36 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>0468</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>UNIPAC</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>4.56</v>
-      </c>
-      <c r="E52" s="10" t="n">
-        <v>0.0022</v>
+        <v>0.25</v>
+      </c>
+      <c r="E52" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>2587100</v>
+        <v>3109500</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.16</v>
+        <v>0.26</v>
       </c>
       <c r="H52" t="n">
-        <v>27.57</v>
-      </c>
-      <c r="I52" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J52" s="2" t="n">
-        <v>4.721</v>
-      </c>
-      <c r="K52" s="2" t="n">
-        <v>4.891</v>
-      </c>
+        <v>28.11</v>
+      </c>
+      <c r="I52" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="n"/>
+      <c r="K52" s="2" t="n"/>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="7" t="inlineStr"/>
     </row>
@@ -2819,28 +2819,28 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>0.975</v>
+        <v>1.14</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>-0.0201</v>
+        <v>-0.0256</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>2533800</v>
+        <v>3064600</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.79</v>
+        <v>0.27</v>
       </c>
       <c r="H53" t="n">
-        <v>83.41</v>
+        <v>48.21</v>
       </c>
       <c r="I53" s="6" t="inlineStr">
         <is>
@@ -2848,10 +2848,10 @@
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.656</v>
+        <v>1.162</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0.479</v>
+        <v>1.119</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="7" t="inlineStr"/>
@@ -2864,28 +2864,28 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>MRCB</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="E54" s="3" t="n">
-        <v>-0.007800000000000001</v>
+        <v>0.28</v>
+      </c>
+      <c r="E54" s="10" t="n">
+        <v>0.0182</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>2497100</v>
+        <v>2914700</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.23</v>
+        <v>0.41</v>
       </c>
       <c r="H54" t="n">
-        <v>41.81</v>
+        <v>37.22</v>
       </c>
       <c r="I54" s="9" t="inlineStr">
         <is>
@@ -2893,10 +2893,10 @@
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>1.321</v>
+        <v>0.289</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>1.305</v>
+        <v>0.307</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="7" t="inlineStr"/>
@@ -2909,39 +2909,39 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>0338</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>KOPI</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="E55" s="10" t="n">
+        <v>0.0337</v>
+      </c>
+      <c r="F55" s="4" t="n">
+        <v>2813100</v>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="H55" t="n">
+        <v>50.01</v>
+      </c>
+      <c r="I55" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="n">
+        <v>0.912</v>
+      </c>
+      <c r="K55" s="2" t="n">
         <v>0.965</v>
-      </c>
-      <c r="E55" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F55" s="4" t="n">
-        <v>2474600</v>
-      </c>
-      <c r="G55" s="5" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="H55" t="n">
-        <v>55.29</v>
-      </c>
-      <c r="I55" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J55" s="2" t="n">
-        <v>0.961</v>
-      </c>
-      <c r="K55" s="2" t="n">
-        <v>0.821</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="7" t="inlineStr"/>
@@ -2954,39 +2954,39 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="E56" s="8" t="n">
-        <v>0</v>
+        <v>2.75</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>-0.0108</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>2458300</v>
+        <v>2794300</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.09</v>
+        <v>0.16</v>
       </c>
       <c r="H56" t="n">
-        <v>29.99</v>
-      </c>
-      <c r="I56" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.29</v>
+      </c>
+      <c r="I56" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.249</v>
+        <v>2.624</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>0.304</v>
+        <v>2.496</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="7" t="inlineStr"/>
@@ -2999,39 +2999,39 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>1.12</v>
+        <v>1.29</v>
       </c>
       <c r="E57" s="10" t="n">
-        <v>0.0182</v>
+        <v>0.007800000000000001</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>2431400</v>
+        <v>2790000</v>
       </c>
       <c r="G57" s="5" t="n">
         <v>0.25</v>
       </c>
       <c r="H57" t="n">
-        <v>64.88</v>
-      </c>
-      <c r="I57" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.76</v>
+      </c>
+      <c r="I57" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>1.069</v>
+        <v>1.323</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>0.916</v>
+        <v>1.306</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="7" t="inlineStr"/>
@@ -3044,39 +3044,39 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0268</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>L&amp;PBHD</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="E58" s="10" t="n">
-        <v>0.09089999999999999</v>
+        <v>7.25</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>-0.0014</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>2403100</v>
+        <v>2758100</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="H58" t="n">
-        <v>77.70999999999999</v>
-      </c>
-      <c r="I58" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>31.19</v>
+      </c>
+      <c r="I58" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.206</v>
+        <v>7.639</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>0.171</v>
+        <v>7.729</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="7" t="inlineStr"/>
@@ -3089,28 +3089,28 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>0.53</v>
+        <v>1.19</v>
       </c>
       <c r="E59" s="10" t="n">
-        <v>0.0392</v>
+        <v>0.0259</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>2371800</v>
+        <v>2702600</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.14</v>
+        <v>0.47</v>
       </c>
       <c r="H59" t="n">
-        <v>56.74</v>
+        <v>55.65</v>
       </c>
       <c r="I59" s="9" t="inlineStr">
         <is>
@@ -3118,10 +3118,10 @@
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.512</v>
+        <v>1.154</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0.436</v>
+        <v>1.165</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="7" t="inlineStr"/>
@@ -3134,28 +3134,28 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="E60" s="10" t="n">
-        <v>0.0345</v>
+        <v>0.965</v>
+      </c>
+      <c r="E60" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>2316800</v>
+        <v>2701400</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="H60" t="n">
-        <v>56.94</v>
+        <v>55.29</v>
       </c>
       <c r="I60" s="9" t="inlineStr">
         <is>
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>1.155</v>
+        <v>0.961</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>1.165</v>
+        <v>0.821</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="7" t="inlineStr"/>
@@ -3179,39 +3179,39 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="E61" s="3" t="n">
-        <v>-0.009300000000000001</v>
+        <v>0.795</v>
+      </c>
+      <c r="E61" s="10" t="n">
+        <v>0.0127</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>2304800</v>
+        <v>2684400</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="H61" t="n">
-        <v>39.76</v>
-      </c>
-      <c r="I61" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.16</v>
+      </c>
+      <c r="I61" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>2.223</v>
+        <v>0.767</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>2.212</v>
+        <v>0.712</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="7" t="inlineStr"/>
@@ -3224,39 +3224,39 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0345</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>SUNLOGY</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>0.455</v>
+        <v>0.53</v>
       </c>
       <c r="E62" s="10" t="n">
-        <v>0.0341</v>
+        <v>0.0392</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>2245300</v>
+        <v>2661500</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.21</v>
+        <v>0.16</v>
       </c>
       <c r="H62" t="n">
-        <v>52.28</v>
-      </c>
-      <c r="I62" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>56.74</v>
+      </c>
+      <c r="I62" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.451</v>
+        <v>0.512</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>0.426</v>
+        <v>0.436</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="7" t="inlineStr"/>
@@ -3269,28 +3269,28 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="E63" s="10" t="n">
-        <v>0.0331</v>
+        <v>0.98</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>-0.0151</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>2243500</v>
+        <v>2560900</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.67</v>
+        <v>0.79</v>
       </c>
       <c r="H63" t="n">
-        <v>76.55</v>
+        <v>84.12</v>
       </c>
       <c r="I63" s="6" t="inlineStr">
         <is>
@@ -3298,10 +3298,10 @@
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>1.025</v>
+        <v>0.656</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>0.86</v>
+        <v>0.479</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="7" t="inlineStr"/>
@@ -3314,39 +3314,39 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E64" s="8" t="n">
-        <v>0</v>
+        <v>0.225</v>
+      </c>
+      <c r="E64" s="10" t="n">
+        <v>0.0227</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>2127700</v>
+        <v>2516300</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="H64" t="n">
-        <v>46.68</v>
-      </c>
-      <c r="I64" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.07</v>
+      </c>
+      <c r="I64" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.868</v>
+        <v>0.249</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>0.869</v>
+        <v>0.304</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="7" t="inlineStr"/>
@@ -3359,28 +3359,28 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0104</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>GENETEC</t>
+          <t>CNERGEN</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="E65" s="3" t="n">
-        <v>-0.0149</v>
+        <v>1.25</v>
+      </c>
+      <c r="E65" s="10" t="n">
+        <v>0.0331</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>2110000</v>
+        <v>2491700</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>0.37</v>
+        <v>0.74</v>
       </c>
       <c r="H65" t="n">
-        <v>52.01</v>
+        <v>76.55</v>
       </c>
       <c r="I65" s="6" t="inlineStr">
         <is>
@@ -3388,10 +3388,10 @@
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.326</v>
+        <v>1.025</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>0.338</v>
+        <v>0.86</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="7" t="inlineStr"/>
@@ -3404,39 +3404,39 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>0268</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>L&amp;PBHD</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="E66" s="3" t="n">
-        <v>-0.009000000000000001</v>
+        <v>0.235</v>
+      </c>
+      <c r="E66" s="10" t="n">
+        <v>0.0682</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>2097200</v>
+        <v>2483500</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>0.39</v>
+        <v>1.24</v>
       </c>
       <c r="H66" t="n">
-        <v>33.2</v>
-      </c>
-      <c r="I66" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>76.23999999999999</v>
+      </c>
+      <c r="I66" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.592</v>
+        <v>0.205</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>0.641</v>
+        <v>0.171</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="7" t="inlineStr"/>
@@ -3449,28 +3449,28 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>0.72</v>
+        <v>1.12</v>
       </c>
       <c r="E67" s="10" t="n">
-        <v>0.0286</v>
+        <v>0.0182</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>1916200</v>
+        <v>2437500</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="H67" t="n">
-        <v>63.57</v>
+        <v>64.88</v>
       </c>
       <c r="I67" s="6" t="inlineStr">
         <is>
@@ -3478,10 +3478,10 @@
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.672</v>
+        <v>1.069</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>0.607</v>
+        <v>0.916</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="7" t="inlineStr"/>
@@ -3494,28 +3494,28 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0267</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>ECA</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>0.385</v>
+        <v>0.455</v>
       </c>
       <c r="E68" s="10" t="n">
-        <v>0.0548</v>
+        <v>0.0341</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>1891000</v>
+        <v>2377200</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.23</v>
       </c>
       <c r="H68" t="n">
-        <v>54.15</v>
+        <v>52.28</v>
       </c>
       <c r="I68" s="6" t="inlineStr">
         <is>
@@ -3523,10 +3523,10 @@
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.367</v>
+        <v>0.451</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>0.374</v>
+        <v>0.426</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="7" t="inlineStr"/>
@@ -3539,39 +3539,39 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>7.12</v>
-      </c>
-      <c r="E69" s="3" t="n">
-        <v>-0.0042</v>
+        <v>2.86</v>
+      </c>
+      <c r="E69" s="10" t="n">
+        <v>0.0035</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>1858600</v>
+        <v>2344000</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>0.19</v>
+        <v>0.75</v>
       </c>
       <c r="H69" t="n">
-        <v>18.83</v>
-      </c>
-      <c r="I69" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>75.53</v>
+      </c>
+      <c r="I69" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>7.596</v>
+        <v>2.638</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>8.09</v>
+        <v>2.285</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="7" t="inlineStr"/>
@@ -3584,28 +3584,28 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>7.25</v>
+        <v>0.55</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>-0.0014</v>
+        <v>-0.009000000000000001</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>1848300</v>
+        <v>2334200</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>0.13</v>
+        <v>0.43</v>
       </c>
       <c r="H70" t="n">
-        <v>31.19</v>
+        <v>33.2</v>
       </c>
       <c r="I70" s="9" t="inlineStr">
         <is>
@@ -3613,10 +3613,10 @@
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>7.639</v>
+        <v>0.592</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>7.729</v>
+        <v>0.641</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="7" t="inlineStr"/>
@@ -3629,39 +3629,39 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>MRCB</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>0.28</v>
+        <v>0.72</v>
       </c>
       <c r="E71" s="10" t="n">
-        <v>0.0182</v>
+        <v>0.0286</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>1778500</v>
+        <v>2214600</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="H71" t="n">
-        <v>37.22</v>
-      </c>
-      <c r="I71" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.57</v>
+      </c>
+      <c r="I71" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.289</v>
+        <v>0.672</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>0.307</v>
+        <v>0.607</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="7" t="inlineStr"/>
@@ -3674,39 +3674,39 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="E72" s="10" t="n">
-        <v>0.0035</v>
+        <v>7.12</v>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>-0.0042</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>1770600</v>
+        <v>2201700</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.23</v>
       </c>
       <c r="H72" t="n">
-        <v>75.53</v>
-      </c>
-      <c r="I72" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>18.83</v>
+      </c>
+      <c r="I72" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>2.638</v>
+        <v>7.596</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>2.285</v>
+        <v>8.09</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="7" t="inlineStr"/>
@@ -3719,39 +3719,39 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="E73" s="10" t="n">
-        <v>0.0161</v>
+        <v>0.33</v>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>-0.0149</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>1762400</v>
+        <v>2153300</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>0.2</v>
+        <v>0.38</v>
       </c>
       <c r="H73" t="n">
-        <v>39.42</v>
-      </c>
-      <c r="I73" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.01</v>
+      </c>
+      <c r="I73" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>1.286</v>
+        <v>0.326</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>1.387</v>
+        <v>0.338</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="7" t="inlineStr"/>
@@ -3764,39 +3764,39 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>7225</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E74" s="3" t="n">
-        <v>-0.0244</v>
+        <v>0.295</v>
+      </c>
+      <c r="E74" s="10" t="n">
+        <v>0.0172</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>1720500</v>
+        <v>2135200</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>0.37</v>
+        <v>0.24</v>
       </c>
       <c r="H74" t="n">
-        <v>42.79</v>
-      </c>
-      <c r="I74" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.36</v>
+      </c>
+      <c r="I74" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.207</v>
+        <v>0.278</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>0.208</v>
+        <v>0.303</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="7" t="inlineStr"/>
@@ -3809,12 +3809,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>NEXG</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
@@ -3824,13 +3824,13 @@
         <v>0.0172</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>1702500</v>
+        <v>2085900</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="H75" t="n">
-        <v>57.36</v>
+        <v>52.49</v>
       </c>
       <c r="I75" s="6" t="inlineStr">
         <is>
@@ -3838,10 +3838,10 @@
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.278</v>
+        <v>0.291</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>0.303</v>
+        <v>0.281</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="7" t="inlineStr"/>
@@ -3854,39 +3854,39 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>5141</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>DAYANG</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="E76" s="10" t="n">
-        <v>0.0149</v>
+        <v>1.42</v>
+      </c>
+      <c r="E76" s="3" t="n">
+        <v>-0.0207</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>1672100</v>
+        <v>2064900</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>0.28</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H76" t="n">
-        <v>58.63</v>
-      </c>
-      <c r="I76" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.98</v>
+      </c>
+      <c r="I76" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>2.63</v>
+        <v>1.459</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>2.581</v>
+        <v>1.495</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="7" t="inlineStr"/>
@@ -3899,39 +3899,39 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>2.71</v>
       </c>
       <c r="E77" s="10" t="n">
-        <v>0.0108</v>
+        <v>0.0112</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>1588800</v>
+        <v>2006000</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>0.93</v>
+        <v>0.33</v>
       </c>
       <c r="H77" t="n">
-        <v>55.4</v>
-      </c>
-      <c r="I77" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.99</v>
+      </c>
+      <c r="I77" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.923</v>
+        <v>2.629</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>0.85</v>
+        <v>2.581</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="7" t="inlineStr"/>
@@ -3944,39 +3944,39 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>0267</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>IOICORP</t>
+          <t>ECA</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>4.58</v>
+        <v>0.385</v>
       </c>
       <c r="E78" s="10" t="n">
-        <v>0.0044</v>
+        <v>0.0548</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>1582900</v>
+        <v>1973200</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>0.17</v>
+        <v>0.59</v>
       </c>
       <c r="H78" t="n">
-        <v>41.8</v>
-      </c>
-      <c r="I78" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.15</v>
+      </c>
+      <c r="I78" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>4.675</v>
+        <v>0.367</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>4.62</v>
+        <v>0.374</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="7" t="inlineStr"/>
@@ -3989,28 +3989,28 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0045</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>SSB8</t>
+          <t>TENAGA</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="E79" s="8" t="n">
-        <v>0</v>
+        <v>12.96</v>
+      </c>
+      <c r="E79" s="10" t="n">
+        <v>0.004699999999999999</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>1564400</v>
+        <v>1934900</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>0.38</v>
+        <v>0.21</v>
       </c>
       <c r="H79" t="n">
-        <v>64</v>
+        <v>42.32</v>
       </c>
       <c r="I79" s="6" t="inlineStr">
         <is>
@@ -4018,10 +4018,10 @@
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.637</v>
+        <v>13.036</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>0.601</v>
+        <v>13.573</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="7" t="inlineStr"/>
@@ -4034,28 +4034,28 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>5260</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>OWG</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="E80" s="10" t="n">
-        <v>0.0526</v>
+        <v>0.0256</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>1563300</v>
+        <v>1917200</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>2.45</v>
+        <v>0.27</v>
       </c>
       <c r="H80" t="n">
-        <v>61.12</v>
+        <v>64.98</v>
       </c>
       <c r="I80" s="6" t="inlineStr">
         <is>
@@ -4063,10 +4063,10 @@
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.186</v>
+        <v>0.736</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>0.188</v>
+        <v>0.652</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="7" t="inlineStr"/>
@@ -4079,28 +4079,28 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>NEXG</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>0.295</v>
+        <v>0.38</v>
       </c>
       <c r="E81" s="10" t="n">
-        <v>0.0172</v>
+        <v>0.0133</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>1548900</v>
+        <v>1873200</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>0.13</v>
+        <v>0.23</v>
       </c>
       <c r="H81" t="n">
-        <v>52.49</v>
+        <v>67.83</v>
       </c>
       <c r="I81" s="6" t="inlineStr">
         <is>
@@ -4108,10 +4108,10 @@
         </is>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.291</v>
+        <v>0.354</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>0.281</v>
+        <v>0.322</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="7" t="inlineStr"/>
@@ -4124,39 +4124,39 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0359</t>
+          <t>7225</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>HKB</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="E82" s="10" t="n">
-        <v>0.0186</v>
+        <v>0.205</v>
+      </c>
+      <c r="E82" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>1518100</v>
+        <v>1796000</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>0.68</v>
+        <v>0.39</v>
       </c>
       <c r="H82" t="n">
-        <v>82.16</v>
-      </c>
-      <c r="I82" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.55</v>
+      </c>
+      <c r="I82" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.679</v>
+        <v>0.207</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>0.622</v>
+        <v>0.208</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="7" t="inlineStr"/>
@@ -4169,28 +4169,28 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>5141</t>
+          <t>0273</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>DAYANG</t>
+          <t>VLB</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="E83" s="3" t="n">
-        <v>-0.0138</v>
+        <v>0.945</v>
+      </c>
+      <c r="E83" s="10" t="n">
+        <v>0.0161</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>1435300</v>
+        <v>1778300</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>0.65</v>
+        <v>1.04</v>
       </c>
       <c r="H83" t="n">
-        <v>39.83</v>
+        <v>56.09</v>
       </c>
       <c r="I83" s="9" t="inlineStr">
         <is>
@@ -4198,10 +4198,10 @@
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>1.46</v>
+        <v>0.924</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>1.495</v>
+        <v>0.85</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="7" t="inlineStr"/>
@@ -4214,39 +4214,39 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="E84" s="8" t="n">
-        <v>0</v>
+        <v>1.25</v>
+      </c>
+      <c r="E84" s="10" t="n">
+        <v>0.008100000000000001</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>1428900</v>
+        <v>1771800</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
       <c r="H84" t="n">
-        <v>56.58</v>
-      </c>
-      <c r="I84" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.79</v>
+      </c>
+      <c r="I84" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.343</v>
+        <v>1.286</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>0.324</v>
+        <v>1.387</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="7" t="inlineStr"/>
@@ -4259,28 +4259,28 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>0249</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>LGMS</t>
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="E85" s="3" t="n">
-        <v>-0.009300000000000001</v>
+        <v>0.57</v>
+      </c>
+      <c r="E85" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>1412800</v>
+        <v>1748400</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>0.1</v>
+        <v>1.94</v>
       </c>
       <c r="H85" t="n">
-        <v>48.94</v>
+        <v>71.84</v>
       </c>
       <c r="I85" s="6" t="inlineStr">
         <is>
@@ -4288,10 +4288,10 @@
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>1.071</v>
+        <v>0.523</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>1.037</v>
+        <v>0.504</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="7" t="inlineStr"/>
@@ -4304,39 +4304,39 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>0239</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>SKPRES</t>
+          <t>ECOMATE</t>
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="E86" s="10" t="n">
-        <v>0.0267</v>
+        <v>0.865</v>
+      </c>
+      <c r="E86" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>1400200</v>
+        <v>1741000</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>0.17</v>
+        <v>0.54</v>
       </c>
       <c r="H86" t="n">
-        <v>69.33</v>
-      </c>
-      <c r="I86" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.86</v>
+      </c>
+      <c r="I86" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.354</v>
+        <v>0.864</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>0.322</v>
+        <v>0.858</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="7" t="inlineStr"/>
@@ -4349,39 +4349,39 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>IOICORP</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>0.805</v>
+        <v>4.58</v>
       </c>
       <c r="E87" s="10" t="n">
-        <v>0.0321</v>
+        <v>0.0044</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v>1392000</v>
+        <v>1739900</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="H87" t="n">
-        <v>65.55</v>
-      </c>
-      <c r="I87" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.8</v>
+      </c>
+      <c r="I87" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.736</v>
+        <v>4.675</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>0.652</v>
+        <v>4.62</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="7" t="inlineStr"/>
@@ -4394,28 +4394,28 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0249</t>
+          <t>0359</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>LGMS</t>
+          <t>HKB</t>
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>0.58</v>
+        <v>0.82</v>
       </c>
       <c r="E88" s="10" t="n">
-        <v>0.0175</v>
+        <v>0.0186</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>1347000</v>
+        <v>1735400</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>1.5</v>
+        <v>0.78</v>
       </c>
       <c r="H88" t="n">
-        <v>73.84</v>
+        <v>82.16</v>
       </c>
       <c r="I88" s="6" t="inlineStr">
         <is>
@@ -4423,10 +4423,10 @@
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.524</v>
+        <v>0.679</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>0.504</v>
+        <v>0.622</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="7" t="inlineStr"/>
@@ -4439,28 +4439,28 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0296</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>HEGROUP</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="E89" s="3" t="n">
-        <v>-0.008800000000000001</v>
+        <v>0.805</v>
+      </c>
+      <c r="E89" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>1324000</v>
+        <v>1708700</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="H89" t="n">
-        <v>68.90000000000001</v>
+        <v>70.15000000000001</v>
       </c>
       <c r="I89" s="6" t="inlineStr">
         <is>
@@ -4468,10 +4468,10 @@
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>1.058</v>
+        <v>0.785</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>0.892</v>
+        <v>0.764</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="7" t="inlineStr"/>
@@ -4484,39 +4484,39 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>TENAGA</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="E90" s="10" t="n">
-        <v>0.007800000000000001</v>
+        <v>2.1</v>
+      </c>
+      <c r="E90" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>1286700</v>
+        <v>1653200</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>0.14</v>
+        <v>0.08</v>
       </c>
       <c r="H90" t="n">
-        <v>44.16</v>
-      </c>
-      <c r="I90" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.69</v>
+      </c>
+      <c r="I90" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J90" s="2" t="n">
-        <v>13.039</v>
+        <v>2.098</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>13.573</v>
+        <v>2.08</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="7" t="inlineStr"/>
@@ -4529,39 +4529,39 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>0045</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>SSB8</t>
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>2.1</v>
+        <v>0.67</v>
       </c>
       <c r="E91" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F91" s="4" t="n">
-        <v>1279700</v>
+        <v>1613800</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.39</v>
       </c>
       <c r="H91" t="n">
-        <v>50.69</v>
-      </c>
-      <c r="I91" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64</v>
+      </c>
+      <c r="I91" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J91" s="2" t="n">
-        <v>2.098</v>
+        <v>0.637</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>2.08</v>
+        <v>0.601</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="7" t="inlineStr"/>
@@ -4574,28 +4574,28 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0172</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>OCK</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>0.45</v>
+        <v>2.5</v>
       </c>
       <c r="E92" s="10" t="n">
-        <v>0.0112</v>
+        <v>0.008100000000000001</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v>1248300</v>
+        <v>1543100</v>
       </c>
       <c r="G92" s="5" t="n">
-        <v>0.35</v>
+        <v>0.11</v>
       </c>
       <c r="H92" t="n">
-        <v>49.83</v>
+        <v>58.18</v>
       </c>
       <c r="I92" s="9" t="inlineStr">
         <is>
@@ -4603,10 +4603,10 @@
         </is>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.457</v>
+        <v>2.463</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>0.42</v>
+        <v>2.344</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="7" t="inlineStr"/>
@@ -4619,33 +4619,40 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0475</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>GBBOND</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D93" s="2" t="n">
-        <v>0.23</v>
+        <v>0.535</v>
       </c>
       <c r="E93" s="10" t="n">
-        <v>0.0455</v>
+        <v>0.009399999999999999</v>
       </c>
       <c r="F93" s="4" t="n">
-        <v>1243500</v>
+        <v>1508100</v>
       </c>
       <c r="G93" s="5" t="n">
-        <v>0.06</v>
+        <v>0.2</v>
+      </c>
+      <c r="H93" t="n">
+        <v>55.09</v>
       </c>
       <c r="I93" s="9" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J93" s="2" t="n"/>
-      <c r="K93" s="2" t="n"/>
+      <c r="J93" s="2" t="n">
+        <v>0.522</v>
+      </c>
+      <c r="K93" s="2" t="n">
+        <v>0.531</v>
+      </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="7" t="inlineStr"/>
     </row>
@@ -4657,39 +4664,39 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D94" s="2" t="n">
-        <v>0.535</v>
-      </c>
-      <c r="E94" s="10" t="n">
-        <v>0.009399999999999999</v>
+        <v>1.07</v>
+      </c>
+      <c r="E94" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>1234800</v>
+        <v>1499200</v>
       </c>
       <c r="G94" s="5" t="n">
-        <v>0.16</v>
+        <v>0.1</v>
       </c>
       <c r="H94" t="n">
-        <v>55.09</v>
-      </c>
-      <c r="I94" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.51</v>
+      </c>
+      <c r="I94" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.522</v>
+        <v>1.072</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>0.531</v>
+        <v>1.037</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="7" t="inlineStr"/>
@@ -4702,39 +4709,39 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>5337</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>ECOSHOP</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D95" s="2" t="n">
-        <v>1.46</v>
+        <v>0.355</v>
       </c>
       <c r="E95" s="10" t="n">
-        <v>0.021</v>
+        <v>0.0143</v>
       </c>
       <c r="F95" s="4" t="n">
-        <v>1228100</v>
+        <v>1494900</v>
       </c>
       <c r="G95" s="5" t="n">
-        <v>0.27</v>
+        <v>0.19</v>
       </c>
       <c r="H95" t="n">
-        <v>49.32</v>
-      </c>
-      <c r="I95" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.58</v>
+      </c>
+      <c r="I95" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J95" s="2" t="n">
-        <v>1.461</v>
+        <v>0.344</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>1.469</v>
+        <v>0.324</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="7" t="inlineStr"/>
@@ -4747,39 +4754,39 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D96" s="2" t="n">
-        <v>4.22</v>
-      </c>
-      <c r="E96" s="3" t="n">
-        <v>-0.009399999999999999</v>
+        <v>0.545</v>
+      </c>
+      <c r="E96" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>1181200</v>
+        <v>1479000</v>
       </c>
       <c r="G96" s="5" t="n">
-        <v>0.15</v>
+        <v>0.36</v>
       </c>
       <c r="H96" t="n">
-        <v>43.07</v>
-      </c>
-      <c r="I96" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>71.06999999999999</v>
+      </c>
+      <c r="I96" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J96" s="2" t="n">
-        <v>4.368</v>
+        <v>0.477</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>4.464</v>
+        <v>0.451</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="7" t="inlineStr"/>
@@ -4792,39 +4799,39 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0277</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>CLOUDPT</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D97" s="2" t="n">
-        <v>0.515</v>
+        <v>5.59</v>
       </c>
       <c r="E97" s="10" t="n">
-        <v>0.0098</v>
+        <v>0.0054</v>
       </c>
       <c r="F97" s="4" t="n">
-        <v>1143900</v>
+        <v>1442200</v>
       </c>
       <c r="G97" s="5" t="n">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="H97" t="n">
-        <v>62.85</v>
-      </c>
-      <c r="I97" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.41</v>
+      </c>
+      <c r="I97" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.489</v>
+        <v>5.635</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>0.479</v>
+        <v>5.307</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="7" t="inlineStr"/>
@@ -4837,39 +4844,39 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D98" s="2" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="E98" s="10" t="n">
-        <v>0.0092</v>
+        <v>4.23</v>
+      </c>
+      <c r="E98" s="3" t="n">
+        <v>-0.006999999999999999</v>
       </c>
       <c r="F98" s="4" t="n">
-        <v>1092700</v>
+        <v>1406600</v>
       </c>
       <c r="G98" s="5" t="n">
-        <v>0.26</v>
+        <v>0.18</v>
       </c>
       <c r="H98" t="n">
-        <v>71.79000000000001</v>
-      </c>
-      <c r="I98" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.38</v>
+      </c>
+      <c r="I98" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.477</v>
+        <v>4.369</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>0.451</v>
+        <v>4.464</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="7" t="inlineStr"/>
@@ -4882,28 +4889,28 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D99" s="2" t="n">
-        <v>5.58</v>
-      </c>
-      <c r="E99" s="10" t="n">
-        <v>0.0036</v>
+        <v>1.84</v>
+      </c>
+      <c r="E99" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F99" s="4" t="n">
-        <v>1092600</v>
+        <v>1376100</v>
       </c>
       <c r="G99" s="5" t="n">
-        <v>0.08</v>
+        <v>0.33</v>
       </c>
       <c r="H99" t="n">
-        <v>49.97</v>
+        <v>37.05</v>
       </c>
       <c r="I99" s="9" t="inlineStr">
         <is>
@@ -4911,10 +4918,10 @@
         </is>
       </c>
       <c r="J99" s="2" t="n">
-        <v>5.634</v>
+        <v>1.895</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>5.307</v>
+        <v>2.026</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="7" t="inlineStr"/>
@@ -4927,28 +4934,28 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>0172</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>AWC</t>
+          <t>OCK</t>
         </is>
       </c>
       <c r="D100" s="2" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E100" s="8" t="n">
-        <v>0</v>
+        <v>0.45</v>
+      </c>
+      <c r="E100" s="10" t="n">
+        <v>0.0112</v>
       </c>
       <c r="F100" s="4" t="n">
-        <v>1089800</v>
+        <v>1372000</v>
       </c>
       <c r="G100" s="5" t="n">
-        <v>0.49</v>
+        <v>0.39</v>
       </c>
       <c r="H100" t="n">
-        <v>57.68</v>
+        <v>49.83</v>
       </c>
       <c r="I100" s="9" t="inlineStr">
         <is>
@@ -4956,10 +4963,10 @@
         </is>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.62</v>
+        <v>0.457</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>0.529</v>
+        <v>0.42</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="7" t="inlineStr"/>
@@ -4972,39 +4979,39 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>0296</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>HEGROUP</t>
         </is>
       </c>
       <c r="D101" s="2" t="n">
-        <v>0.93</v>
+        <v>1.14</v>
       </c>
       <c r="E101" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F101" s="4" t="n">
-        <v>1088100</v>
+        <v>1360400</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>0.21</v>
+        <v>0.28</v>
       </c>
       <c r="H101" t="n">
-        <v>63.88</v>
-      </c>
-      <c r="I101" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>71.20999999999999</v>
+      </c>
+      <c r="I101" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.908</v>
+        <v>1.059</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>0.863</v>
+        <v>0.892</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="7" t="inlineStr"/>
@@ -5017,40 +5024,33 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>0450</t>
+          <t>0475</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>MFGROUP</t>
+          <t>GBBOND</t>
         </is>
       </c>
       <c r="D102" s="2" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="E102" s="3" t="n">
-        <v>-0.0185</v>
+        <v>0.23</v>
+      </c>
+      <c r="E102" s="10" t="n">
+        <v>0.0455</v>
       </c>
       <c r="F102" s="4" t="n">
-        <v>1082000</v>
+        <v>1360100</v>
       </c>
       <c r="G102" s="5" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="H102" t="n">
-        <v>54.17</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I102" s="9" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J102" s="2" t="n">
-        <v>0.262</v>
-      </c>
-      <c r="K102" s="2" t="n">
-        <v>0.264</v>
-      </c>
+      <c r="J102" s="2" t="n"/>
+      <c r="K102" s="2" t="n"/>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="7" t="inlineStr"/>
     </row>
@@ -5062,39 +5062,39 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>AWC</t>
         </is>
       </c>
       <c r="D103" s="2" t="n">
-        <v>0.805</v>
+        <v>0.635</v>
       </c>
       <c r="E103" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F103" s="4" t="n">
-        <v>1071700</v>
+        <v>1293700</v>
       </c>
       <c r="G103" s="5" t="n">
-        <v>0.17</v>
+        <v>0.59</v>
       </c>
       <c r="H103" t="n">
-        <v>70.15000000000001</v>
-      </c>
-      <c r="I103" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>57.68</v>
+      </c>
+      <c r="I103" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.785</v>
+        <v>0.62</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>0.764</v>
+        <v>0.529</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="7" t="inlineStr"/>
@@ -5107,28 +5107,28 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>0277</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>CLOUDPT</t>
         </is>
       </c>
       <c r="D104" s="2" t="n">
-        <v>0.64</v>
+        <v>0.515</v>
       </c>
       <c r="E104" s="10" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.0098</v>
       </c>
       <c r="F104" s="4" t="n">
-        <v>1056600</v>
+        <v>1277600</v>
       </c>
       <c r="G104" s="5" t="n">
-        <v>0.28</v>
+        <v>0.78</v>
       </c>
       <c r="H104" t="n">
-        <v>63.45</v>
+        <v>62.85</v>
       </c>
       <c r="I104" s="6" t="inlineStr">
         <is>
@@ -5136,10 +5136,10 @@
         </is>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.596</v>
+        <v>0.489</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>0.582</v>
+        <v>0.479</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="7" t="inlineStr"/>
@@ -5152,28 +5152,28 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>0272</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>TTVHB</t>
         </is>
       </c>
       <c r="D105" s="2" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="E105" s="3" t="n">
-        <v>-0.0238</v>
+        <v>0.255</v>
+      </c>
+      <c r="E105" s="10" t="n">
+        <v>0.0408</v>
       </c>
       <c r="F105" s="4" t="n">
-        <v>1033500</v>
+        <v>1263900</v>
       </c>
       <c r="G105" s="5" t="n">
-        <v>0.16</v>
+        <v>0.63</v>
       </c>
       <c r="H105" t="n">
-        <v>69.3</v>
+        <v>52.98</v>
       </c>
       <c r="I105" s="6" t="inlineStr">
         <is>
@@ -5181,10 +5181,10 @@
         </is>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.749</v>
+        <v>0.248</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>0.663</v>
+        <v>0.253</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="7" t="inlineStr"/>
@@ -5197,28 +5197,28 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>5337</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>ECOSHOP</t>
         </is>
       </c>
       <c r="D106" s="2" t="n">
-        <v>0.49</v>
+        <v>1.45</v>
       </c>
       <c r="E106" s="10" t="n">
-        <v>0.0103</v>
+        <v>0.014</v>
       </c>
       <c r="F106" s="4" t="n">
-        <v>1015800</v>
+        <v>1256000</v>
       </c>
       <c r="G106" s="5" t="n">
-        <v>0.14</v>
+        <v>0.27</v>
       </c>
       <c r="H106" t="n">
-        <v>28.72</v>
+        <v>46.32</v>
       </c>
       <c r="I106" s="9" t="inlineStr">
         <is>
@@ -5226,10 +5226,10 @@
         </is>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.524</v>
+        <v>1.46</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>0.571</v>
+        <v>1.468</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="7" t="inlineStr"/>
@@ -5242,28 +5242,28 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>3662</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>MFLOUR</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D107" s="2" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E107" s="10" t="n">
-        <v>0.0256</v>
+        <v>0.925</v>
+      </c>
+      <c r="E107" s="3" t="n">
+        <v>-0.0054</v>
       </c>
       <c r="F107" s="4" t="n">
-        <v>1009000</v>
+        <v>1255700</v>
       </c>
       <c r="G107" s="5" t="n">
-        <v>0.43</v>
+        <v>0.24</v>
       </c>
       <c r="H107" t="n">
-        <v>40.75</v>
+        <v>61.28</v>
       </c>
       <c r="I107" s="9" t="inlineStr">
         <is>
@@ -5271,10 +5271,10 @@
         </is>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.617</v>
+        <v>0.908</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>0.635</v>
+        <v>0.863</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="7" t="inlineStr"/>
@@ -5287,28 +5287,28 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>0272</t>
+          <t>6633</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>TTVHB</t>
+          <t>LHI</t>
         </is>
       </c>
       <c r="D108" s="2" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E108" s="10" t="n">
-        <v>0.0612</v>
+        <v>0.73</v>
+      </c>
+      <c r="E108" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F108" s="4" t="n">
-        <v>1005600</v>
+        <v>1255700</v>
       </c>
       <c r="G108" s="5" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="H108" t="n">
-        <v>55.07</v>
+        <v>47.32</v>
       </c>
       <c r="I108" s="6" t="inlineStr">
         <is>
@@ -5316,10 +5316,10 @@
         </is>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.249</v>
+        <v>0.735</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>0.253</v>
+        <v>0.749</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="7" t="inlineStr"/>
@@ -5332,28 +5332,28 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>5306</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>MAHSING</t>
+          <t>FFB</t>
         </is>
       </c>
       <c r="D109" s="2" t="n">
-        <v>0.95</v>
+        <v>1.79</v>
       </c>
       <c r="E109" s="10" t="n">
-        <v>0.0053</v>
+        <v>0.0229</v>
       </c>
       <c r="F109" s="4" t="n">
-        <v>983000</v>
+        <v>1181200</v>
       </c>
       <c r="G109" s="5" t="n">
-        <v>0.25</v>
+        <v>0.41</v>
       </c>
       <c r="H109" t="n">
-        <v>30.03</v>
+        <v>30.67</v>
       </c>
       <c r="I109" s="9" t="inlineStr">
         <is>
@@ -5361,10 +5361,10 @@
         </is>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.996</v>
+        <v>1.879</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>1.066</v>
+        <v>2.017</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="7" t="inlineStr"/>
@@ -5377,28 +5377,28 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>0271</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>WELLS</t>
+          <t>CMSB</t>
         </is>
       </c>
       <c r="D110" s="2" t="n">
-        <v>0.53</v>
+        <v>0.92</v>
       </c>
       <c r="E110" s="10" t="n">
-        <v>0.0291</v>
+        <v>0.0166</v>
       </c>
       <c r="F110" s="4" t="n">
-        <v>963600</v>
+        <v>1175900</v>
       </c>
       <c r="G110" s="5" t="n">
-        <v>0.87</v>
+        <v>0.57</v>
       </c>
       <c r="H110" t="n">
-        <v>26.64</v>
+        <v>33.38</v>
       </c>
       <c r="I110" s="9" t="inlineStr">
         <is>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.582</v>
+        <v>0.96</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>0.622</v>
+        <v>0.993</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="7" t="inlineStr"/>
@@ -5422,39 +5422,39 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>5306</t>
+          <t>0056</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>FFB</t>
+          <t>NCT</t>
         </is>
       </c>
       <c r="D111" s="2" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="E111" s="10" t="n">
-        <v>0.0229</v>
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="E111" s="3" t="n">
+        <v>-0.008800000000000001</v>
       </c>
       <c r="F111" s="4" t="n">
-        <v>942500</v>
+        <v>1153200</v>
       </c>
       <c r="G111" s="5" t="n">
-        <v>0.32</v>
+        <v>0.53</v>
       </c>
       <c r="H111" t="n">
-        <v>30.67</v>
-      </c>
-      <c r="I111" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.06</v>
+      </c>
+      <c r="I111" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J111" s="2" t="n">
-        <v>1.879</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>2.017</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="7" t="inlineStr"/>
@@ -5467,39 +5467,39 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D112" s="2" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="E112" s="3" t="n">
-        <v>-0.0054</v>
+        <v>0.64</v>
+      </c>
+      <c r="E112" s="10" t="n">
+        <v>0.007900000000000001</v>
       </c>
       <c r="F112" s="4" t="n">
-        <v>940500</v>
+        <v>1149200</v>
       </c>
       <c r="G112" s="5" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="H112" t="n">
-        <v>36</v>
-      </c>
-      <c r="I112" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.45</v>
+      </c>
+      <c r="I112" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J112" s="2" t="n">
-        <v>1.894</v>
+        <v>0.596</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>2.026</v>
+        <v>0.582</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="7" t="inlineStr"/>
@@ -5512,28 +5512,28 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>0373</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>VERDANT</t>
         </is>
       </c>
       <c r="D113" s="2" t="n">
-        <v>2.49</v>
+        <v>0.28</v>
       </c>
       <c r="E113" s="10" t="n">
-        <v>0.004</v>
+        <v>0.0182</v>
       </c>
       <c r="F113" s="4" t="n">
-        <v>933600</v>
+        <v>1143000</v>
       </c>
       <c r="G113" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.26</v>
       </c>
       <c r="H113" t="n">
-        <v>57.08</v>
+        <v>69.36</v>
       </c>
       <c r="I113" s="9" t="inlineStr">
         <is>
@@ -5541,10 +5541,10 @@
         </is>
       </c>
       <c r="J113" s="2" t="n">
-        <v>2.462</v>
+        <v>0.252</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>2.344</v>
+        <v>0.22</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="7" t="inlineStr"/>
@@ -5557,28 +5557,28 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D114" s="2" t="n">
-        <v>4.23</v>
-      </c>
-      <c r="E114" s="10" t="n">
-        <v>0.0168</v>
+        <v>0.83</v>
+      </c>
+      <c r="E114" s="3" t="n">
+        <v>-0.0119</v>
       </c>
       <c r="F114" s="4" t="n">
-        <v>929300</v>
+        <v>1122400</v>
       </c>
       <c r="G114" s="5" t="n">
-        <v>0.11</v>
+        <v>0.17</v>
       </c>
       <c r="H114" t="n">
-        <v>64.26000000000001</v>
+        <v>72.09</v>
       </c>
       <c r="I114" s="6" t="inlineStr">
         <is>
@@ -5586,10 +5586,10 @@
         </is>
       </c>
       <c r="J114" s="2" t="n">
-        <v>3.964</v>
+        <v>0.75</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>3.443</v>
+        <v>0.663</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="7" t="inlineStr"/>
@@ -5611,19 +5611,19 @@
         </is>
       </c>
       <c r="D115" s="2" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="E115" s="10" t="n">
-        <v>0.0226</v>
+        <v>0.015</v>
       </c>
       <c r="F115" s="4" t="n">
-        <v>924700</v>
+        <v>1095500</v>
       </c>
       <c r="G115" s="5" t="n">
-        <v>0.24</v>
+        <v>0.29</v>
       </c>
       <c r="H115" t="n">
-        <v>58.46</v>
+        <v>57.71</v>
       </c>
       <c r="I115" s="6" t="inlineStr">
         <is>
@@ -5631,7 +5631,7 @@
         </is>
       </c>
       <c r="J115" s="2" t="n">
-        <v>1.295</v>
+        <v>1.294</v>
       </c>
       <c r="K115" s="2" t="n">
         <v>1.194</v>
@@ -5647,39 +5647,39 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D116" s="2" t="n">
-        <v>0.795</v>
+        <v>1.61</v>
       </c>
       <c r="E116" s="10" t="n">
-        <v>0.0127</v>
+        <v>0.0126</v>
       </c>
       <c r="F116" s="4" t="n">
-        <v>916300</v>
+        <v>1082400</v>
       </c>
       <c r="G116" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="H116" t="n">
-        <v>57.16</v>
-      </c>
-      <c r="I116" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.89</v>
+      </c>
+      <c r="I116" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.767</v>
+        <v>1.668</v>
       </c>
       <c r="K116" s="2" t="n">
-        <v>0.712</v>
+        <v>1.786</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="7" t="inlineStr"/>
@@ -5692,39 +5692,39 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>7233</t>
+          <t>0450</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>DUFU</t>
+          <t>MFGROUP</t>
         </is>
       </c>
       <c r="D117" s="2" t="n">
-        <v>3.21</v>
+        <v>0.265</v>
       </c>
       <c r="E117" s="3" t="n">
-        <v>-0.009300000000000001</v>
+        <v>-0.0185</v>
       </c>
       <c r="F117" s="4" t="n">
-        <v>895200</v>
+        <v>1082000</v>
       </c>
       <c r="G117" s="5" t="n">
-        <v>0.29</v>
+        <v>1.11</v>
       </c>
       <c r="H117" t="n">
-        <v>62.41</v>
-      </c>
-      <c r="I117" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>54.17</v>
+      </c>
+      <c r="I117" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J117" s="2" t="n">
-        <v>3.002</v>
+        <v>0.262</v>
       </c>
       <c r="K117" s="2" t="n">
-        <v>2.804</v>
+        <v>0.264</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="7" t="inlineStr"/>
@@ -5737,39 +5737,39 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>5162</t>
+          <t>7081</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>VSTECS</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D118" s="2" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="E118" s="10" t="n">
-        <v>0.0359</v>
+        <v>0.91</v>
+      </c>
+      <c r="E118" s="3" t="n">
+        <v>-0.0109</v>
       </c>
       <c r="F118" s="4" t="n">
-        <v>848600</v>
+        <v>1057700</v>
       </c>
       <c r="G118" s="5" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="H118" t="n">
-        <v>57.25</v>
-      </c>
-      <c r="I118" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>20.11</v>
+      </c>
+      <c r="I118" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J118" s="2" t="n">
-        <v>1.664</v>
+        <v>1.036</v>
       </c>
       <c r="K118" s="2" t="n">
-        <v>1.678</v>
+        <v>1.119</v>
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" s="7" t="inlineStr"/>
@@ -5782,39 +5782,39 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>7081</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D119" s="2" t="n">
-        <v>0.925</v>
+        <v>4.24</v>
       </c>
       <c r="E119" s="10" t="n">
-        <v>0.0054</v>
+        <v>0.0192</v>
       </c>
       <c r="F119" s="4" t="n">
-        <v>818800</v>
+        <v>1040000</v>
       </c>
       <c r="G119" s="5" t="n">
-        <v>0.35</v>
+        <v>0.12</v>
       </c>
       <c r="H119" t="n">
-        <v>22.43</v>
-      </c>
-      <c r="I119" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.51000000000001</v>
+      </c>
+      <c r="I119" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J119" s="2" t="n">
-        <v>1.037</v>
+        <v>3.965</v>
       </c>
       <c r="K119" s="2" t="n">
-        <v>1.119</v>
+        <v>3.443</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="7" t="inlineStr"/>
@@ -5827,28 +5827,28 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>3662</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>CMSB</t>
+          <t>MFLOUR</t>
         </is>
       </c>
       <c r="D120" s="2" t="n">
-        <v>0.915</v>
+        <v>0.595</v>
       </c>
       <c r="E120" s="10" t="n">
-        <v>0.011</v>
+        <v>0.0171</v>
       </c>
       <c r="F120" s="4" t="n">
-        <v>787700</v>
+        <v>1036800</v>
       </c>
       <c r="G120" s="5" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="H120" t="n">
-        <v>31.21</v>
+        <v>38.12</v>
       </c>
       <c r="I120" s="9" t="inlineStr">
         <is>
@@ -5856,10 +5856,10 @@
         </is>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.959</v>
+        <v>0.616</v>
       </c>
       <c r="K120" s="2" t="n">
-        <v>0.993</v>
+        <v>0.635</v>
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="7" t="inlineStr"/>
@@ -5872,39 +5872,39 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>6633</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>LHI</t>
+          <t>MAHSING</t>
         </is>
       </c>
       <c r="D121" s="2" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="E121" s="8" t="n">
-        <v>0</v>
+        <v>0.95</v>
+      </c>
+      <c r="E121" s="10" t="n">
+        <v>0.0053</v>
       </c>
       <c r="F121" s="4" t="n">
-        <v>730700</v>
+        <v>1036700</v>
       </c>
       <c r="G121" s="5" t="n">
-        <v>0.44</v>
+        <v>0.27</v>
       </c>
       <c r="H121" t="n">
-        <v>47.32</v>
-      </c>
-      <c r="I121" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>30.03</v>
+      </c>
+      <c r="I121" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0.735</v>
+        <v>0.996</v>
       </c>
       <c r="K121" s="2" t="n">
-        <v>0.749</v>
+        <v>1.066</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" s="7" t="inlineStr"/>
@@ -5917,39 +5917,39 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>ATECH</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D122" s="2" t="n">
-        <v>0.805</v>
+        <v>0.49</v>
       </c>
       <c r="E122" s="10" t="n">
-        <v>0.019</v>
+        <v>0.0103</v>
       </c>
       <c r="F122" s="4" t="n">
-        <v>705900</v>
+        <v>1017100</v>
       </c>
       <c r="G122" s="5" t="n">
-        <v>0.39</v>
+        <v>0.14</v>
       </c>
       <c r="H122" t="n">
-        <v>59.79</v>
-      </c>
-      <c r="I122" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>28.72</v>
+      </c>
+      <c r="I122" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J122" s="2" t="n">
-        <v>0.77</v>
+        <v>0.524</v>
       </c>
       <c r="K122" s="2" t="n">
-        <v>0.761</v>
+        <v>0.571</v>
       </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="7" t="inlineStr"/>
@@ -5962,28 +5962,28 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>7160</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>PENTA</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D123" s="2" t="n">
-        <v>5.91</v>
+        <v>0.605</v>
       </c>
       <c r="E123" s="10" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.0168</v>
       </c>
       <c r="F123" s="4" t="n">
-        <v>683300</v>
+        <v>990200</v>
       </c>
       <c r="G123" s="5" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="H123" t="n">
-        <v>63.28</v>
+        <v>70.43000000000001</v>
       </c>
       <c r="I123" s="6" t="inlineStr">
         <is>
@@ -5991,10 +5991,10 @@
         </is>
       </c>
       <c r="J123" s="2" t="n">
-        <v>5.479</v>
+        <v>0.55</v>
       </c>
       <c r="K123" s="2" t="n">
-        <v>5.356</v>
+        <v>0.493</v>
       </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" s="7" t="inlineStr"/>
@@ -6007,39 +6007,39 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>0223</t>
+          <t>0271</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>SAMAIDEN</t>
+          <t>WELLS</t>
         </is>
       </c>
       <c r="D124" s="2" t="n">
-        <v>3.06</v>
+        <v>0.53</v>
       </c>
       <c r="E124" s="10" t="n">
-        <v>0.0166</v>
+        <v>0.0291</v>
       </c>
       <c r="F124" s="4" t="n">
-        <v>676300</v>
+        <v>963600</v>
       </c>
       <c r="G124" s="5" t="n">
-        <v>0.16</v>
+        <v>0.87</v>
       </c>
       <c r="H124" t="n">
-        <v>69.63</v>
-      </c>
-      <c r="I124" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>26.64</v>
+      </c>
+      <c r="I124" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J124" s="2" t="n">
-        <v>2.694</v>
+        <v>0.582</v>
       </c>
       <c r="K124" s="2" t="n">
-        <v>2.043</v>
+        <v>0.622</v>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" s="7" t="inlineStr"/>
@@ -6052,39 +6052,39 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>5323</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>JPG</t>
+          <t>DUFU</t>
         </is>
       </c>
       <c r="D125" s="2" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="E125" s="10" t="n">
-        <v>0.023</v>
+        <v>3.21</v>
+      </c>
+      <c r="E125" s="3" t="n">
+        <v>-0.009300000000000001</v>
       </c>
       <c r="F125" s="4" t="n">
-        <v>650300</v>
+        <v>929800</v>
       </c>
       <c r="G125" s="5" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="H125" t="n">
-        <v>41.73</v>
-      </c>
-      <c r="I125" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.41</v>
+      </c>
+      <c r="I125" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J125" s="2" t="n">
-        <v>1.825</v>
+        <v>3.002</v>
       </c>
       <c r="K125" s="2" t="n">
-        <v>1.927</v>
+        <v>2.804</v>
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" s="7" t="inlineStr"/>
@@ -6097,28 +6097,28 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D126" s="2" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="E126" s="8" t="n">
-        <v>0</v>
+        <v>7.19</v>
+      </c>
+      <c r="E126" s="10" t="n">
+        <v>0.0098</v>
       </c>
       <c r="F126" s="4" t="n">
-        <v>643400</v>
+        <v>918300</v>
       </c>
       <c r="G126" s="5" t="n">
-        <v>0.2</v>
+        <v>0.12</v>
       </c>
       <c r="H126" t="n">
-        <v>72.14</v>
+        <v>34.49</v>
       </c>
       <c r="I126" s="9" t="inlineStr">
         <is>
@@ -6126,10 +6126,10 @@
         </is>
       </c>
       <c r="J126" s="2" t="n">
-        <v>1.237</v>
+        <v>7.408</v>
       </c>
       <c r="K126" s="2" t="n">
-        <v>1.008</v>
+        <v>7.724</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="7" t="inlineStr"/>
@@ -6142,28 +6142,28 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>5162</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>VSTECS</t>
         </is>
       </c>
       <c r="D127" s="2" t="n">
-        <v>0.605</v>
+        <v>1.73</v>
       </c>
       <c r="E127" s="10" t="n">
-        <v>0.0168</v>
+        <v>0.0359</v>
       </c>
       <c r="F127" s="4" t="n">
-        <v>635900</v>
+        <v>916700</v>
       </c>
       <c r="G127" s="5" t="n">
-        <v>0.11</v>
+        <v>0.54</v>
       </c>
       <c r="H127" t="n">
-        <v>70.43000000000001</v>
+        <v>57.25</v>
       </c>
       <c r="I127" s="6" t="inlineStr">
         <is>
@@ -6171,10 +6171,10 @@
         </is>
       </c>
       <c r="J127" s="2" t="n">
-        <v>0.55</v>
+        <v>1.664</v>
       </c>
       <c r="K127" s="2" t="n">
-        <v>0.493</v>
+        <v>1.678</v>
       </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" s="7" t="inlineStr"/>
@@ -6187,28 +6187,28 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>SKYECHIP</t>
         </is>
       </c>
       <c r="D128" s="2" t="n">
-        <v>0.735</v>
-      </c>
-      <c r="E128" s="10" t="n">
-        <v>0.0068</v>
+        <v>2.92</v>
+      </c>
+      <c r="E128" s="3" t="n">
+        <v>-0.0034</v>
       </c>
       <c r="F128" s="4" t="n">
-        <v>620200</v>
+        <v>871000</v>
       </c>
       <c r="G128" s="5" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="H128" t="n">
-        <v>44.96</v>
+        <v>44.13</v>
       </c>
       <c r="I128" s="9" t="inlineStr">
         <is>
@@ -6216,10 +6216,10 @@
         </is>
       </c>
       <c r="J128" s="2" t="n">
-        <v>0.76</v>
+        <v>2.973</v>
       </c>
       <c r="K128" s="2" t="n">
-        <v>0.747</v>
+        <v>3.033</v>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" s="7" t="inlineStr"/>
@@ -6232,39 +6232,39 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>7160</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>SEG</t>
+          <t>PENTA</t>
         </is>
       </c>
       <c r="D129" s="2" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E129" s="3" t="n">
-        <v>-0.007900000000000001</v>
+        <v>5.9</v>
+      </c>
+      <c r="E129" s="10" t="n">
+        <v>0.0068</v>
       </c>
       <c r="F129" s="4" t="n">
-        <v>615100</v>
+        <v>840300</v>
       </c>
       <c r="G129" s="5" t="n">
-        <v>0.49</v>
+        <v>0.25</v>
       </c>
       <c r="H129" t="n">
-        <v>37.72</v>
-      </c>
-      <c r="I129" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.09</v>
+      </c>
+      <c r="I129" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J129" s="2" t="n">
-        <v>0.632</v>
+        <v>5.478</v>
       </c>
       <c r="K129" s="2" t="n">
-        <v>0.63</v>
+        <v>5.356</v>
       </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" s="7" t="inlineStr"/>
@@ -6277,28 +6277,28 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>5302</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>ATECH</t>
         </is>
       </c>
       <c r="D130" s="2" t="n">
-        <v>0.775</v>
+        <v>0.805</v>
       </c>
       <c r="E130" s="10" t="n">
-        <v>0.0197</v>
+        <v>0.019</v>
       </c>
       <c r="F130" s="4" t="n">
-        <v>601200</v>
+        <v>839500</v>
       </c>
       <c r="G130" s="5" t="n">
-        <v>0.33</v>
+        <v>0.46</v>
       </c>
       <c r="H130" t="n">
-        <v>63.64</v>
+        <v>59.79</v>
       </c>
       <c r="I130" s="6" t="inlineStr">
         <is>
@@ -6306,10 +6306,10 @@
         </is>
       </c>
       <c r="J130" s="2" t="n">
-        <v>0.712</v>
+        <v>0.77</v>
       </c>
       <c r="K130" s="2" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.761</v>
       </c>
       <c r="L130" t="inlineStr"/>
       <c r="M130" s="7" t="inlineStr"/>
@@ -6322,28 +6322,28 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>5180</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>CLMT</t>
         </is>
       </c>
       <c r="D131" s="2" t="n">
-        <v>0.84</v>
+        <v>0.555</v>
       </c>
       <c r="E131" s="10" t="n">
-        <v>0.006</v>
+        <v>0.0091</v>
       </c>
       <c r="F131" s="4" t="n">
-        <v>600800</v>
+        <v>820200</v>
       </c>
       <c r="G131" s="5" t="n">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="H131" t="n">
-        <v>59.49</v>
+        <v>35.64</v>
       </c>
       <c r="I131" s="9" t="inlineStr">
         <is>
@@ -6351,10 +6351,10 @@
         </is>
       </c>
       <c r="J131" s="2" t="n">
-        <v>0.82</v>
+        <v>0.571</v>
       </c>
       <c r="K131" s="2" t="n">
-        <v>0.756</v>
+        <v>0.582</v>
       </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" s="7" t="inlineStr"/>
@@ -6367,39 +6367,39 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>0223</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>SAMAIDEN</t>
         </is>
       </c>
       <c r="D132" s="2" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="E132" s="8" t="n">
-        <v>0</v>
+        <v>3.06</v>
+      </c>
+      <c r="E132" s="10" t="n">
+        <v>0.0166</v>
       </c>
       <c r="F132" s="4" t="n">
-        <v>592700</v>
+        <v>758300</v>
       </c>
       <c r="G132" s="5" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="H132" t="n">
-        <v>54.4</v>
-      </c>
-      <c r="I132" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>69.63</v>
+      </c>
+      <c r="I132" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J132" s="2" t="n">
-        <v>0.639</v>
+        <v>2.694</v>
       </c>
       <c r="K132" s="2" t="n">
-        <v>0.611</v>
+        <v>2.043</v>
       </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" s="7" t="inlineStr"/>
@@ -6412,28 +6412,28 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>0217</t>
+          <t>5878</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>PWRWELL</t>
+          <t>KPJ</t>
         </is>
       </c>
       <c r="D133" s="2" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="E133" s="8" t="n">
-        <v>0</v>
+        <v>2.51</v>
+      </c>
+      <c r="E133" s="3" t="n">
+        <v>-0.004</v>
       </c>
       <c r="F133" s="4" t="n">
-        <v>583200</v>
+        <v>741700</v>
       </c>
       <c r="G133" s="5" t="n">
         <v>0.14</v>
       </c>
       <c r="H133" t="n">
-        <v>58.23</v>
+        <v>35.17</v>
       </c>
       <c r="I133" s="9" t="inlineStr">
         <is>
@@ -6441,10 +6441,10 @@
         </is>
       </c>
       <c r="J133" s="2" t="n">
-        <v>1.152</v>
+        <v>2.613</v>
       </c>
       <c r="K133" s="2" t="n">
-        <v>1.066</v>
+        <v>2.79</v>
       </c>
       <c r="L133" t="inlineStr"/>
       <c r="M133" s="7" t="inlineStr"/>
@@ -6457,28 +6457,28 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>0167</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>MCLEAN</t>
         </is>
       </c>
       <c r="D134" s="2" t="n">
-        <v>2.94</v>
+        <v>0.735</v>
       </c>
       <c r="E134" s="10" t="n">
-        <v>0.0034</v>
+        <v>0.0068</v>
       </c>
       <c r="F134" s="4" t="n">
-        <v>549500</v>
+        <v>736400</v>
       </c>
       <c r="G134" s="5" t="n">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="H134" t="n">
-        <v>45.93</v>
+        <v>44.96</v>
       </c>
       <c r="I134" s="9" t="inlineStr">
         <is>
@@ -6486,10 +6486,10 @@
         </is>
       </c>
       <c r="J134" s="2" t="n">
-        <v>2.975</v>
+        <v>0.76</v>
       </c>
       <c r="K134" s="2" t="n">
-        <v>3.034</v>
+        <v>0.747</v>
       </c>
       <c r="L134" t="inlineStr"/>
       <c r="M134" s="7" t="inlineStr"/>
@@ -6502,28 +6502,28 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D135" s="2" t="n">
-        <v>2.17</v>
+        <v>1.36</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>-0.0225</v>
+        <v>-0.0073</v>
       </c>
       <c r="F135" s="4" t="n">
-        <v>536600</v>
+        <v>710900</v>
       </c>
       <c r="G135" s="5" t="n">
-        <v>0.1</v>
+        <v>0.22</v>
       </c>
       <c r="H135" t="n">
-        <v>49.02</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="I135" s="9" t="inlineStr">
         <is>
@@ -6531,10 +6531,10 @@
         </is>
       </c>
       <c r="J135" s="2" t="n">
-        <v>2.188</v>
+        <v>1.236</v>
       </c>
       <c r="K135" s="2" t="n">
-        <v>2.127</v>
+        <v>1.008</v>
       </c>
       <c r="L135" t="inlineStr"/>
       <c r="M135" s="7" t="inlineStr"/>
@@ -6547,39 +6547,39 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D136" s="2" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="E136" s="10" t="n">
-        <v>0.0035</v>
+        <v>2.89</v>
+      </c>
+      <c r="E136" s="3" t="n">
+        <v>-0.0103</v>
       </c>
       <c r="F136" s="4" t="n">
-        <v>523500</v>
+        <v>700800</v>
       </c>
       <c r="G136" s="5" t="n">
-        <v>0.06</v>
+        <v>0.15</v>
       </c>
       <c r="H136" t="n">
-        <v>56.65</v>
-      </c>
-      <c r="I136" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.26</v>
+      </c>
+      <c r="I136" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J136" s="2" t="n">
-        <v>2.776</v>
+        <v>2.967</v>
       </c>
       <c r="K136" s="2" t="n">
-        <v>2.6</v>
+        <v>2.819</v>
       </c>
       <c r="L136" t="inlineStr"/>
       <c r="M136" s="7" t="inlineStr"/>
@@ -6592,45 +6592,720 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>0146</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>JFTECH</t>
         </is>
       </c>
       <c r="D137" s="2" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="E137" s="3" t="n">
-        <v>-0.0063</v>
+        <v>0.77</v>
+      </c>
+      <c r="E137" s="10" t="n">
+        <v>0.0132</v>
       </c>
       <c r="F137" s="4" t="n">
-        <v>513800</v>
+        <v>690700</v>
       </c>
       <c r="G137" s="5" t="n">
-        <v>0.08</v>
+        <v>0.37</v>
       </c>
       <c r="H137" t="n">
-        <v>32.03</v>
-      </c>
-      <c r="I137" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.99</v>
+      </c>
+      <c r="I137" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J137" s="2" t="n">
-        <v>1.666</v>
+        <v>0.712</v>
       </c>
       <c r="K137" s="2" t="n">
-        <v>1.786</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="L137" t="inlineStr"/>
       <c r="M137" s="7" t="inlineStr"/>
     </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>5323</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>JPG</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="E138" s="10" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="F138" s="4" t="n">
+        <v>678200</v>
+      </c>
+      <c r="G138" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H138" t="n">
+        <v>41.73</v>
+      </c>
+      <c r="I138" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J138" s="2" t="n">
+        <v>1.825</v>
+      </c>
+      <c r="K138" s="2" t="n">
+        <v>1.927</v>
+      </c>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" s="7" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>5053</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>OSK</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="E139" s="10" t="n">
+        <v>0.0124</v>
+      </c>
+      <c r="F139" s="4" t="n">
+        <v>677900</v>
+      </c>
+      <c r="G139" s="5" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="H139" t="n">
+        <v>23.55</v>
+      </c>
+      <c r="I139" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J139" s="2" t="n">
+        <v>1.784</v>
+      </c>
+      <c r="K139" s="2" t="n">
+        <v>1.918</v>
+      </c>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" s="7" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>0225</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>SCGBHD</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="E140" s="10" t="n">
+        <v>0.0035</v>
+      </c>
+      <c r="F140" s="4" t="n">
+        <v>639700</v>
+      </c>
+      <c r="G140" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H140" t="n">
+        <v>56.65</v>
+      </c>
+      <c r="I140" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J140" s="2" t="n">
+        <v>2.776</v>
+      </c>
+      <c r="K140" s="2" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" s="7" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>5199</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>HIBISCS</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="E141" s="3" t="n">
+        <v>-0.0225</v>
+      </c>
+      <c r="F141" s="4" t="n">
+        <v>635600</v>
+      </c>
+      <c r="G141" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H141" t="n">
+        <v>49.02</v>
+      </c>
+      <c r="I141" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J141" s="2" t="n">
+        <v>2.188</v>
+      </c>
+      <c r="K141" s="2" t="n">
+        <v>2.127</v>
+      </c>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" s="7" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>5212</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>PAVREIT</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="E142" s="10" t="n">
+        <v>0.006500000000000001</v>
+      </c>
+      <c r="F142" s="4" t="n">
+        <v>624100</v>
+      </c>
+      <c r="G142" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H142" t="n">
+        <v>45.12</v>
+      </c>
+      <c r="I142" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J142" s="2" t="n">
+        <v>1.562</v>
+      </c>
+      <c r="K142" s="2" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" s="7" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>0390</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>ISF</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="E143" s="10" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="F143" s="4" t="n">
+        <v>620500</v>
+      </c>
+      <c r="G143" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H143" t="n">
+        <v>59.49</v>
+      </c>
+      <c r="I143" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J143" s="2" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="K143" s="2" t="n">
+        <v>0.756</v>
+      </c>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" s="7" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>9792</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>SEG</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="E144" s="3" t="n">
+        <v>-0.007900000000000001</v>
+      </c>
+      <c r="F144" s="4" t="n">
+        <v>615100</v>
+      </c>
+      <c r="G144" s="5" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="H144" t="n">
+        <v>37.72</v>
+      </c>
+      <c r="I144" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J144" s="2" t="n">
+        <v>0.632</v>
+      </c>
+      <c r="K144" s="2" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" s="7" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>0217</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>PWRWELL</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="E145" s="10" t="n">
+        <v>0.008500000000000001</v>
+      </c>
+      <c r="F145" s="4" t="n">
+        <v>594500</v>
+      </c>
+      <c r="G145" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H145" t="n">
+        <v>59.85</v>
+      </c>
+      <c r="I145" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J145" s="2" t="n">
+        <v>1.153</v>
+      </c>
+      <c r="K145" s="2" t="n">
+        <v>1.066</v>
+      </c>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" s="7" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>0112</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>MIKROMB</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="E146" s="3" t="n">
+        <v>-0.007800000000000001</v>
+      </c>
+      <c r="F146" s="4" t="n">
+        <v>593400</v>
+      </c>
+      <c r="G146" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H146" t="n">
+        <v>51.42</v>
+      </c>
+      <c r="I146" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J146" s="2" t="n">
+        <v>0.638</v>
+      </c>
+      <c r="K146" s="2" t="n">
+        <v>0.611</v>
+      </c>
+      <c r="L146" t="inlineStr"/>
+      <c r="M146" s="7" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>5331</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>PGLOBAL</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="E147" s="10" t="n">
+        <v>0.0179</v>
+      </c>
+      <c r="F147" s="4" t="n">
+        <v>590700</v>
+      </c>
+      <c r="G147" s="5" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="H147" t="n">
+        <v>68.42</v>
+      </c>
+      <c r="I147" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J147" s="2" t="n">
+        <v>0.539</v>
+      </c>
+      <c r="K147" s="2" t="n">
+        <v>0.511</v>
+      </c>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" s="7" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>6947</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>CDB</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="E148" s="10" t="n">
+        <v>0.0162</v>
+      </c>
+      <c r="F148" s="4" t="n">
+        <v>568800</v>
+      </c>
+      <c r="G148" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H148" t="n">
+        <v>35.71</v>
+      </c>
+      <c r="I148" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J148" s="2" t="n">
+        <v>2.582</v>
+      </c>
+      <c r="K148" s="2" t="n">
+        <v>2.731</v>
+      </c>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" s="7" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>0240</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>CORAZA</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="E149" s="3" t="n">
+        <v>-0.0211</v>
+      </c>
+      <c r="F149" s="4" t="n">
+        <v>567700</v>
+      </c>
+      <c r="G149" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H149" t="n">
+        <v>72.58</v>
+      </c>
+      <c r="I149" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J149" s="2" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="K149" s="2" t="n">
+        <v>1.151</v>
+      </c>
+      <c r="L149" t="inlineStr"/>
+      <c r="M149" s="7" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>1171</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>MBSB</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="n">
+        <v>0.535</v>
+      </c>
+      <c r="E150" s="10" t="n">
+        <v>0.009399999999999999</v>
+      </c>
+      <c r="F150" s="4" t="n">
+        <v>563100</v>
+      </c>
+      <c r="G150" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H150" t="n">
+        <v>35.78</v>
+      </c>
+      <c r="I150" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J150" s="2" t="n">
+        <v>0.552</v>
+      </c>
+      <c r="K150" s="2" t="n">
+        <v>0.582</v>
+      </c>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" s="7" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>0391</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>AMBEST</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="E151" s="3" t="n">
+        <v>-0.0149</v>
+      </c>
+      <c r="F151" s="4" t="n">
+        <v>537700</v>
+      </c>
+      <c r="G151" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H151" t="n">
+        <v>48.88</v>
+      </c>
+      <c r="I151" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J151" s="2" t="n">
+        <v>1.348</v>
+      </c>
+      <c r="K151" s="2" t="n">
+        <v>1.235</v>
+      </c>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" s="7" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>7293</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>YINSON</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="E152" s="10" t="n">
+        <v>0.0142</v>
+      </c>
+      <c r="F152" s="4" t="n">
+        <v>516800</v>
+      </c>
+      <c r="G152" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H152" t="n">
+        <v>56.49</v>
+      </c>
+      <c r="I152" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J152" s="2" t="n">
+        <v>2.091</v>
+      </c>
+      <c r="K152" s="2" t="n">
+        <v>2.037</v>
+      </c>
+      <c r="L152" t="inlineStr"/>
+      <c r="M152" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M137"/>
+  <autoFilter ref="A1:M152"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-09/bursa-report-2026-10-09.xlsx
+++ b/docs/downloads/2026-10-09/bursa-report-2026-10-09.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-09" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-09'!$A$1:$M$152</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-09'!$A$1:$M$174</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -35,10 +35,10 @@
       <color rgb="00FFFFFF"/>
     </font>
     <font>
-      <color rgb="00D03B3B"/>
+      <color rgb="000CA30C"/>
     </font>
     <font>
-      <color rgb="000CA30C"/>
+      <color rgb="00D03B3B"/>
     </font>
     <font>
       <color rgb="00898781"/>
@@ -82,9 +82,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M152"/>
+  <dimension ref="A1:M174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -543,39 +543,39 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>0138</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>ZETRIX</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.515</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>-0.019</v>
+        <v>0.1333</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>80258600</v>
+        <v>115736500</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>2.82</v>
+        <v>0.26</v>
       </c>
       <c r="H2" t="n">
-        <v>60.83</v>
+        <v>23.54</v>
       </c>
       <c r="I2" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0.49</v>
+        <v>0.175</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0.479</v>
+        <v>0.397</v>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" s="7" t="inlineStr"/>
@@ -588,39 +588,39 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>5156</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>XDL</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.005</v>
+        <v>0.52</v>
       </c>
       <c r="E3" s="8" t="n">
-        <v>0</v>
+        <v>-0.0095</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>39809700</v>
+        <v>80394800</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>106.59</v>
+        <v>2.82</v>
       </c>
       <c r="H3" t="n">
-        <v>43</v>
+        <v>62.99</v>
       </c>
       <c r="I3" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.007</v>
+        <v>0.491</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0.007</v>
+        <v>0.479</v>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" s="7" t="inlineStr"/>
@@ -633,39 +633,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0138</t>
+          <t>5156</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ZETRIX</t>
+          <t>XDL</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.08</v>
+        <v>0.005</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>0.0667</v>
+        <v>0</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>38259700</v>
+        <v>39809700</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.09</v>
+        <v>106.59</v>
       </c>
       <c r="H4" t="n">
-        <v>22.11</v>
-      </c>
-      <c r="I4" s="9" t="inlineStr">
+        <v>43</v>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.175</v>
+        <v>0.007</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.397</v>
+        <v>0.007</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" s="7" t="inlineStr"/>
@@ -678,39 +678,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.345</v>
-      </c>
-      <c r="E5" s="10" t="n">
-        <v>0.0455</v>
+        <v>0.84</v>
+      </c>
+      <c r="E5" s="8" t="n">
+        <v>-0.04</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>30655300</v>
+        <v>35033300</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.52</v>
+        <v>0.45</v>
       </c>
       <c r="H5" t="n">
-        <v>78.38</v>
-      </c>
-      <c r="I5" s="6" t="inlineStr">
+        <v>62.57</v>
+      </c>
+      <c r="I5" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.279</v>
+        <v>0.782</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.245</v>
+        <v>0.71</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" s="7" t="inlineStr"/>
@@ -723,39 +723,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.85</v>
+        <v>0.345</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>-0.0286</v>
+        <v>0.0455</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>28255300</v>
+        <v>33754500</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.37</v>
+        <v>0.58</v>
       </c>
       <c r="H6" t="n">
-        <v>64.59999999999999</v>
-      </c>
-      <c r="I6" s="6" t="inlineStr">
+        <v>78.38</v>
+      </c>
+      <c r="I6" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.783</v>
+        <v>0.279</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.71</v>
+        <v>0.245</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" s="7" t="inlineStr"/>
@@ -777,27 +777,27 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="E7" s="10" t="n">
-        <v>0.0255</v>
+        <v>2.02</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>0.0306</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>25313000</v>
+        <v>27513700</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="H7" t="n">
-        <v>71.48</v>
-      </c>
-      <c r="I7" s="6" t="inlineStr">
+        <v>71.94</v>
+      </c>
+      <c r="I7" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>1.811</v>
+        <v>1.812</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>1.636</v>
@@ -822,27 +822,27 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="E8" s="8" t="n">
-        <v>0</v>
+        <v>0.195</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>0.0263</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>22020200</v>
+        <v>25404600</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.09</v>
       </c>
       <c r="H8" t="n">
-        <v>47.95</v>
-      </c>
-      <c r="I8" s="9" t="inlineStr">
+        <v>51.06</v>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.195</v>
+        <v>0.196</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>0.183</v>
@@ -858,39 +858,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>0095</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>JAKS</t>
+          <t>MAG</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>-0.027</v>
+        <v>0.155</v>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>17598100</v>
+        <v>22615500</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.27</v>
+        <v>0.71</v>
       </c>
       <c r="H9" t="n">
-        <v>60.1</v>
+        <v>46.07</v>
       </c>
       <c r="I9" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.167</v>
+        <v>0.156</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.132</v>
+        <v>0.157</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="7" t="inlineStr"/>
@@ -903,39 +903,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="E10" s="8" t="n">
-        <v>0</v>
+        <v>0.625</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>0.0163</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>16578400</v>
+        <v>18173400</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.39</v>
+        <v>0.7</v>
       </c>
       <c r="H10" t="n">
-        <v>70.36</v>
-      </c>
-      <c r="I10" s="6" t="inlineStr">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="I10" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.358</v>
+        <v>0.582</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0.236</v>
+        <v>0.508</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="7" t="inlineStr"/>
@@ -948,39 +948,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>JAKS</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="E11" s="10" t="n">
-        <v>0.008100000000000001</v>
+        <v>0.18</v>
+      </c>
+      <c r="E11" s="8" t="n">
+        <v>-0.027</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>15277600</v>
+        <v>17917200</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.59</v>
+        <v>0.28</v>
       </c>
       <c r="H11" t="n">
-        <v>70.55</v>
+        <v>60.1</v>
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.582</v>
+        <v>0.167</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0.508</v>
+        <v>0.132</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="7" t="inlineStr"/>
@@ -993,36 +993,40 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0471</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>PIONEER</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0.35</v>
+        <v>0.39</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>0.04480000000000001</v>
+        <v>0</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>14701700</v>
+        <v>17090200</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>1.57</v>
+        <v>0.41</v>
       </c>
       <c r="H12" t="n">
-        <v>72.73999999999999</v>
-      </c>
-      <c r="I12" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="n"/>
-      <c r="K12" s="2" t="n"/>
+        <v>70.36</v>
+      </c>
+      <c r="I12" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>0.358</v>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>0.236</v>
+      </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="7" t="inlineStr"/>
     </row>
@@ -1034,40 +1038,36 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0278</t>
+          <t>0471</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>EDELTEQ</t>
+          <t>PIONEER</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="E13" s="10" t="n">
-        <v>0.1034</v>
+        <v>0.35</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>0.04480000000000001</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>10839500</v>
+        <v>15323200</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>4.72</v>
+        <v>1.63</v>
       </c>
       <c r="H13" t="n">
-        <v>80.09</v>
-      </c>
-      <c r="I13" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="K13" s="2" t="n">
-        <v>0.349</v>
-      </c>
+        <v>72.73999999999999</v>
+      </c>
+      <c r="I13" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="n"/>
+      <c r="K13" s="2" t="n"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="7" t="inlineStr"/>
     </row>
@@ -1088,27 +1088,27 @@
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0.735</v>
-      </c>
-      <c r="E14" s="10" t="n">
-        <v>0.05</v>
+        <v>0.75</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>0.07139999999999999</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>9661500</v>
+        <v>14339400</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>1.27</v>
+        <v>1.88</v>
       </c>
       <c r="H14" t="n">
-        <v>60.21</v>
-      </c>
-      <c r="I14" s="6" t="inlineStr">
+        <v>62.52</v>
+      </c>
+      <c r="I14" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.694</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>0.678</v>
@@ -1124,39 +1124,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>0278</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MALAKOF</t>
+          <t>EDELTEQ</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E15" s="10" t="n">
-        <v>0.0256</v>
+        <v>0.48</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>0.1034</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>9375400</v>
+        <v>13905300</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>2.54</v>
+        <v>6.06</v>
       </c>
       <c r="H15" t="n">
-        <v>51.34</v>
+        <v>80.09</v>
       </c>
       <c r="I15" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.792</v>
+        <v>0.36</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0.806</v>
+        <v>0.349</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="7" t="inlineStr"/>
@@ -1178,27 +1178,27 @@
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>0.405</v>
-      </c>
-      <c r="E16" s="10" t="n">
-        <v>0.1096</v>
+        <v>0.4</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>0.0959</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>9201700</v>
+        <v>10118700</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.77</v>
+        <v>0.85</v>
       </c>
       <c r="H16" t="n">
-        <v>58.07</v>
-      </c>
-      <c r="I16" s="9" t="inlineStr">
+        <v>56.64</v>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.385</v>
+        <v>0.384</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>0.375</v>
@@ -1223,27 +1223,27 @@
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="E17" s="3" t="n">
-        <v>-0.0417</v>
+        <v>0.24</v>
+      </c>
+      <c r="E17" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>8496300</v>
+        <v>9781700</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>6.3</v>
+        <v>7.25</v>
       </c>
       <c r="H17" t="n">
-        <v>59.96</v>
-      </c>
-      <c r="I17" s="6" t="inlineStr">
+        <v>68.81</v>
+      </c>
+      <c r="I17" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.219</v>
+        <v>0.22</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>0.206</v>
@@ -1259,39 +1259,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>MALAKOF</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>0.435</v>
+        <v>0.79</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>-0.0225</v>
+        <v>0.0128</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>7991300</v>
+        <v>9500000</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.3</v>
+        <v>2.57</v>
       </c>
       <c r="H18" t="n">
-        <v>60.91</v>
+        <v>48.72</v>
       </c>
       <c r="I18" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.41</v>
+        <v>0.791</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0.346</v>
+        <v>0.806</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="7" t="inlineStr"/>
@@ -1304,39 +1304,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>0.465</v>
-      </c>
-      <c r="E19" s="3" t="n">
-        <v>-0.0211</v>
+        <v>0.44</v>
+      </c>
+      <c r="E19" s="8" t="n">
+        <v>-0.0112</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>6531300</v>
+        <v>8544100</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.17</v>
+        <v>0.32</v>
       </c>
       <c r="H19" t="n">
-        <v>25.65</v>
+        <v>62.6</v>
       </c>
       <c r="I19" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.548</v>
+        <v>0.41</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0.749</v>
+        <v>0.347</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="7" t="inlineStr"/>
@@ -1360,19 +1360,19 @@
       <c r="D20" s="2" t="n">
         <v>0.31</v>
       </c>
-      <c r="E20" s="8" t="n">
+      <c r="E20" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>6470400</v>
+        <v>7960400</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.34</v>
+        <v>0.41</v>
       </c>
       <c r="H20" t="n">
         <v>57.67</v>
       </c>
-      <c r="I20" s="6" t="inlineStr">
+      <c r="I20" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -1394,39 +1394,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AVANGAAD</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E21" s="8" t="n">
-        <v>0</v>
+        <v>0.625</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>0.008100000000000001</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>6215100</v>
+        <v>7684700</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>2.36</v>
+        <v>0.74</v>
       </c>
       <c r="H21" t="n">
-        <v>49.15</v>
+        <v>58.16</v>
       </c>
       <c r="I21" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.295</v>
+        <v>0.611</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0.296</v>
+        <v>0.611</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="7" t="inlineStr"/>
@@ -1439,33 +1439,40 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0476</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>SLGC Berhad</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E22" s="8" t="n">
-        <v>0</v>
+        <v>0.775</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>0.006500000000000001</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>6133500</v>
+        <v>7514800</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="I22" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="n"/>
-      <c r="K22" s="2" t="n"/>
+        <v>0.51</v>
+      </c>
+      <c r="H22" t="n">
+        <v>50.25</v>
+      </c>
+      <c r="I22" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="K22" s="2" t="n">
+        <v>0.775</v>
+      </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="7" t="inlineStr"/>
     </row>
@@ -1477,39 +1484,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0198</t>
+          <t>0358</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>GDB</t>
+          <t>ICTZONE</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>0.4</v>
+        <v>0.24</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>-0.0361</v>
+        <v>0.0667</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>6099500</v>
+        <v>7009600</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>5.41</v>
+        <v>2.52</v>
       </c>
       <c r="H23" t="n">
-        <v>32.62</v>
-      </c>
-      <c r="I23" s="9" t="inlineStr">
+        <v>48.47</v>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.421</v>
+        <v>0.241</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0.441</v>
+        <v>0.249</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="7" t="inlineStr"/>
@@ -1522,39 +1529,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E24" s="10" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.465</v>
+      </c>
+      <c r="E24" s="8" t="n">
+        <v>-0.0211</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>6030800</v>
+        <v>6942500</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.41</v>
+        <v>0.18</v>
       </c>
       <c r="H24" t="n">
-        <v>50.25</v>
+        <v>25.65</v>
       </c>
       <c r="I24" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.775</v>
+        <v>0.548</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0.775</v>
+        <v>0.749</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="7" t="inlineStr"/>
@@ -1567,39 +1574,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="E25" s="10" t="n">
-        <v>0.0144</v>
+        <v>5.05</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>0.0202</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>5985600</v>
+        <v>6794100</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.43</v>
+        <v>0.28</v>
       </c>
       <c r="H25" t="n">
-        <v>54.37</v>
+        <v>60.26</v>
       </c>
       <c r="I25" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>2.792</v>
+        <v>4.922</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>2.693</v>
+        <v>4.652</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="7" t="inlineStr"/>
@@ -1612,36 +1619,40 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0470</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>BFIELD</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="E26" s="8" t="n">
-        <v>0</v>
+        <v>2.82</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>0.0144</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>5983300</v>
+        <v>6506000</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="H26" t="n">
-        <v>63.39</v>
+        <v>54.37</v>
       </c>
       <c r="I26" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="n"/>
-      <c r="K26" s="2" t="n"/>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="n">
+        <v>2.792</v>
+      </c>
+      <c r="K26" s="2" t="n">
+        <v>2.693</v>
+      </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="7" t="inlineStr"/>
     </row>
@@ -1653,40 +1664,33 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>7020</t>
+          <t>0476</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ASTEEL</t>
+          <t>SLGC Berhad</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>0.105</v>
+        <v>0.245</v>
       </c>
       <c r="E27" s="8" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>5968100</v>
+        <v>6492500</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="H27" t="n">
-        <v>59.81</v>
-      </c>
-      <c r="I27" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="n">
-        <v>0.096</v>
-      </c>
-      <c r="K27" s="2" t="n">
-        <v>0.08500000000000001</v>
-      </c>
+        <v>0.15</v>
+      </c>
+      <c r="I27" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="n"/>
+      <c r="K27" s="2" t="n"/>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="7" t="inlineStr"/>
     </row>
@@ -1698,39 +1702,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0358</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ICTZONE</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>0.235</v>
-      </c>
-      <c r="E28" s="10" t="n">
-        <v>0.0444</v>
+        <v>0.29</v>
+      </c>
+      <c r="E28" s="8" t="n">
+        <v>-0.0169</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>5740900</v>
+        <v>6245100</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>2.06</v>
+        <v>2.38</v>
       </c>
       <c r="H28" t="n">
-        <v>46.06</v>
-      </c>
-      <c r="I28" s="9" t="inlineStr">
+        <v>32.74</v>
+      </c>
+      <c r="I28" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.241</v>
+        <v>0.295</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0.249</v>
+        <v>0.296</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="7" t="inlineStr"/>
@@ -1743,39 +1747,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="E29" s="3" t="n">
-        <v>-0.0127</v>
+        <v>0.37</v>
+      </c>
+      <c r="E29" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>5698600</v>
+        <v>6140200</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.53</v>
+        <v>0.91</v>
       </c>
       <c r="H29" t="n">
-        <v>34.12</v>
-      </c>
-      <c r="I29" s="9" t="inlineStr">
+        <v>53.56</v>
+      </c>
+      <c r="I29" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.402</v>
+        <v>0.368</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0.41</v>
+        <v>0.368</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="7" t="inlineStr"/>
@@ -1788,39 +1792,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>7139</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>NICE</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>0.08</v>
+        <v>0.4</v>
       </c>
       <c r="E30" s="8" t="n">
-        <v>0</v>
+        <v>-0.0361</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>5595200</v>
+        <v>6124500</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>5.91</v>
+        <v>5.43</v>
       </c>
       <c r="H30" t="n">
-        <v>37.6</v>
-      </c>
-      <c r="I30" s="9" t="inlineStr">
+        <v>32.62</v>
+      </c>
+      <c r="I30" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.083</v>
+        <v>0.421</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.441</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="7" t="inlineStr"/>
@@ -1833,39 +1837,39 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E31" s="10" t="n">
-        <v>0.008100000000000001</v>
+        <v>0.39</v>
+      </c>
+      <c r="E31" s="8" t="n">
+        <v>-0.0127</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>5581800</v>
+        <v>6025000</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H31" t="n">
-        <v>58.16</v>
+        <v>34.12</v>
       </c>
       <c r="I31" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.611</v>
+        <v>0.402</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0.611</v>
+        <v>0.41</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="7" t="inlineStr"/>
@@ -1878,40 +1882,36 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>0470</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>BFIELD</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>5.05</v>
+        <v>0.48</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>0.0202</v>
+        <v>0</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>5332900</v>
+        <v>6021000</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.22</v>
+        <v>0.51</v>
       </c>
       <c r="H32" t="n">
-        <v>60.26</v>
-      </c>
-      <c r="I32" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="n">
-        <v>4.922</v>
-      </c>
-      <c r="K32" s="2" t="n">
-        <v>4.652</v>
-      </c>
+        <v>63.39</v>
+      </c>
+      <c r="I32" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="n"/>
+      <c r="K32" s="2" t="n"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="7" t="inlineStr"/>
     </row>
@@ -1923,39 +1923,39 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>7020</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>ASTEEL</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>0.64</v>
+        <v>0.105</v>
       </c>
       <c r="E33" s="10" t="n">
-        <v>0.024</v>
+        <v>0</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>5011700</v>
+        <v>5983100</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.27</v>
+        <v>2.7</v>
       </c>
       <c r="H33" t="n">
-        <v>64.14</v>
-      </c>
-      <c r="I33" s="6" t="inlineStr">
+        <v>59.81</v>
+      </c>
+      <c r="I33" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.582</v>
+        <v>0.096</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0.519</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="7" t="inlineStr"/>
@@ -1968,39 +1968,39 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>7139</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>NICE</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.08</v>
       </c>
       <c r="E34" s="10" t="n">
-        <v>0.0062</v>
+        <v>0</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>4934900</v>
+        <v>5705300</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.31</v>
+        <v>6.03</v>
       </c>
       <c r="H34" t="n">
-        <v>54.76</v>
+        <v>37.6</v>
       </c>
       <c r="I34" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.083</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0.806</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="7" t="inlineStr"/>
@@ -2013,39 +2013,39 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>6.73</v>
+        <v>0.865</v>
       </c>
       <c r="E35" s="10" t="n">
-        <v>0.1069</v>
+        <v>0</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>4824600</v>
+        <v>5700200</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>1.08</v>
+        <v>0.3</v>
       </c>
       <c r="H35" t="n">
-        <v>65.73999999999999</v>
-      </c>
-      <c r="I35" s="6" t="inlineStr">
+        <v>46.68</v>
+      </c>
+      <c r="I35" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>5.834</v>
+        <v>0.868</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>5.779</v>
+        <v>0.869</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="7" t="inlineStr"/>
@@ -2058,39 +2058,39 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="E36" s="8" t="n">
-        <v>0</v>
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>0.0062</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>4701200</v>
+        <v>5687900</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.7</v>
+        <v>0.36</v>
       </c>
       <c r="H36" t="n">
-        <v>53.56</v>
+        <v>54.76</v>
       </c>
       <c r="I36" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.368</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>0.368</v>
+        <v>0.806</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="7" t="inlineStr"/>
@@ -2112,21 +2112,21 @@
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="E37" s="10" t="n">
-        <v>0.0698</v>
+        <v>0.695</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>0.0775</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>4636100</v>
+        <v>5590300</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>1.02</v>
+        <v>1.23</v>
       </c>
       <c r="H37" t="n">
-        <v>85.51000000000001</v>
-      </c>
-      <c r="I37" s="6" t="inlineStr">
+        <v>85.75</v>
+      </c>
+      <c r="I37" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -2148,39 +2148,39 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0050</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>SYSTECH</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>0.19</v>
+        <v>2.14</v>
       </c>
       <c r="E38" s="10" t="n">
-        <v>0.0857</v>
+        <v>0</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>4612900</v>
+        <v>5378900</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.85</v>
+        <v>0.36</v>
       </c>
       <c r="H38" t="n">
-        <v>67.38</v>
+        <v>41.24</v>
       </c>
       <c r="I38" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.165</v>
+        <v>2.225</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>0.166</v>
+        <v>2.212</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="7" t="inlineStr"/>
@@ -2193,39 +2193,39 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E39" s="8" t="n">
-        <v>0</v>
+        <v>0.635</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>0.016</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>3912700</v>
+        <v>5271000</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.21</v>
+        <v>0.28</v>
       </c>
       <c r="H39" t="n">
-        <v>46.68</v>
-      </c>
-      <c r="I39" s="6" t="inlineStr">
+        <v>63.49</v>
+      </c>
+      <c r="I39" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.868</v>
+        <v>0.581</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0.869</v>
+        <v>0.518</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="7" t="inlineStr"/>
@@ -2238,39 +2238,39 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>0.795</v>
-      </c>
-      <c r="E40" s="10" t="n">
-        <v>0.0063</v>
+        <v>4.57</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>0.0044</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>3907800</v>
+        <v>5154800</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.49</v>
+        <v>0.33</v>
       </c>
       <c r="H40" t="n">
-        <v>55.55</v>
+        <v>29.08</v>
       </c>
       <c r="I40" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.779</v>
+        <v>4.722</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0.773</v>
+        <v>4.891</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="7" t="inlineStr"/>
@@ -2283,39 +2283,39 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0376</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>IAB</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>1.32</v>
+        <v>6.67</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>-0.0222</v>
+        <v>0.09699999999999999</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>3871100</v>
+        <v>5151200</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>2.23</v>
+        <v>1.15</v>
       </c>
       <c r="H41" t="n">
-        <v>54.18</v>
-      </c>
-      <c r="I41" s="6" t="inlineStr">
+        <v>65.08</v>
+      </c>
+      <c r="I41" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>1.275</v>
+        <v>5.829</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>1.32</v>
+        <v>5.778</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="7" t="inlineStr"/>
@@ -2328,39 +2328,39 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0111</t>
+          <t>0050</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>K1</t>
+          <t>SYSTECH</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>0.0857</v>
+      </c>
+      <c r="F42" s="4" t="n">
+        <v>5120500</v>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="H42" t="n">
+        <v>67.38</v>
+      </c>
+      <c r="I42" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="n">
         <v>0.165</v>
       </c>
-      <c r="E42" s="10" t="n">
-        <v>0.0313</v>
-      </c>
-      <c r="F42" s="4" t="n">
-        <v>3780100</v>
-      </c>
-      <c r="G42" s="5" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="H42" t="n">
-        <v>59.38</v>
-      </c>
-      <c r="I42" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="n">
-        <v>0.156</v>
-      </c>
       <c r="K42" s="2" t="n">
-        <v>0.145</v>
+        <v>0.166</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="7" t="inlineStr"/>
@@ -2373,39 +2373,39 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>IOICORP</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>9.789999999999999</v>
+        <v>4.57</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>-0.001</v>
+        <v>0.0022</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>3728300</v>
+        <v>4971300</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.3</v>
+        <v>0.53</v>
       </c>
       <c r="H43" t="n">
-        <v>29.86</v>
-      </c>
-      <c r="I43" s="9" t="inlineStr">
+        <v>40.81</v>
+      </c>
+      <c r="I43" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>10.02</v>
+        <v>4.674</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>10.213</v>
+        <v>4.619</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="7" t="inlineStr"/>
@@ -2418,39 +2418,39 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>4.56</v>
+        <v>0.34</v>
       </c>
       <c r="E44" s="10" t="n">
-        <v>0.0022</v>
+        <v>0</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>3706300</v>
+        <v>4575400</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.24</v>
+        <v>1.15</v>
       </c>
       <c r="H44" t="n">
-        <v>27.57</v>
-      </c>
-      <c r="I44" s="9" t="inlineStr">
+        <v>32.2</v>
+      </c>
+      <c r="I44" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>4.721</v>
+        <v>0.363</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>4.891</v>
+        <v>0.383</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="7" t="inlineStr"/>
@@ -2463,39 +2463,39 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="E45" s="3" t="n">
-        <v>-0.004699999999999999</v>
+        <v>0.79</v>
+      </c>
+      <c r="E45" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>3489100</v>
+        <v>4513000</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.24</v>
+        <v>0.57</v>
       </c>
       <c r="H45" t="n">
-        <v>40.49</v>
+        <v>54.24</v>
       </c>
       <c r="I45" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>2.224</v>
+        <v>0.779</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>2.212</v>
+        <v>0.773</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="7" t="inlineStr"/>
@@ -2508,39 +2508,39 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>SPSETIA</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>0.72</v>
+        <v>0.39</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>-0.0069</v>
+        <v>0.04</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>3423700</v>
+        <v>4492200</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="H46" t="n">
-        <v>33.63</v>
+        <v>70.7</v>
       </c>
       <c r="I46" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.756</v>
+        <v>0.355</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>0.819</v>
+        <v>0.322</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="7" t="inlineStr"/>
@@ -2553,39 +2553,39 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>5253</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ECONBHD</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="E47" s="8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="E47" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>3288700</v>
+        <v>4387600</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.72</v>
+        <v>0.35</v>
       </c>
       <c r="H47" t="n">
-        <v>55.25</v>
+        <v>30.27</v>
       </c>
       <c r="I47" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.122</v>
+        <v>10.021</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0.125</v>
+        <v>10.213</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="7" t="inlineStr"/>
@@ -2598,39 +2598,39 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>MRCB</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>3.73</v>
+        <v>0.28</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>-0.0106</v>
+        <v>0.0182</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>3203000</v>
+        <v>4139800</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.28</v>
+        <v>0.59</v>
       </c>
       <c r="H48" t="n">
-        <v>57.15</v>
-      </c>
-      <c r="I48" s="9" t="inlineStr">
+        <v>37.22</v>
+      </c>
+      <c r="I48" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>3.603</v>
+        <v>0.289</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>2.74</v>
+        <v>0.307</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="7" t="inlineStr"/>
@@ -2643,39 +2643,39 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>0376</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>WCT</t>
+          <t>IAB</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>0.34</v>
+        <v>1.31</v>
       </c>
       <c r="E49" s="8" t="n">
-        <v>0</v>
+        <v>-0.0296</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>3199900</v>
+        <v>4115500</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.8100000000000001</v>
+        <v>2.38</v>
       </c>
       <c r="H49" t="n">
-        <v>32.2</v>
+        <v>53.07</v>
       </c>
       <c r="I49" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.363</v>
+        <v>1.274</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0.383</v>
+        <v>1.319</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="7" t="inlineStr"/>
@@ -2688,39 +2688,39 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>5326</t>
+          <t>0111</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>99SMART</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="E50" s="10" t="n">
-        <v>0.0417</v>
+        <v>0.165</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>0.0313</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>3135600</v>
+        <v>3810200</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.74</v>
+        <v>1.16</v>
       </c>
       <c r="H50" t="n">
-        <v>51.28</v>
-      </c>
-      <c r="I50" s="6" t="inlineStr">
+        <v>59.38</v>
+      </c>
+      <c r="I50" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>3.198</v>
+        <v>0.156</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>3.39</v>
+        <v>0.145</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="7" t="inlineStr"/>
@@ -2733,39 +2733,39 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>SPSETIA</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>0.46</v>
+        <v>0.72</v>
       </c>
       <c r="E51" s="8" t="n">
-        <v>0</v>
+        <v>-0.0069</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>3117500</v>
+        <v>3583400</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.45</v>
+        <v>0.6</v>
       </c>
       <c r="H51" t="n">
-        <v>62.48</v>
+        <v>33.63</v>
       </c>
       <c r="I51" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.427</v>
+        <v>0.756</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0.413</v>
+        <v>0.819</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="7" t="inlineStr"/>
@@ -2778,36 +2778,40 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0468</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>UNIPAC</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>0.25</v>
+        <v>7.25</v>
       </c>
       <c r="E52" s="8" t="n">
-        <v>0</v>
+        <v>-0.0014</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>3109500</v>
+        <v>3571100</v>
       </c>
       <c r="G52" s="5" t="n">
         <v>0.26</v>
       </c>
       <c r="H52" t="n">
-        <v>28.11</v>
+        <v>31.19</v>
       </c>
       <c r="I52" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J52" s="2" t="n"/>
-      <c r="K52" s="2" t="n"/>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="n">
+        <v>7.639</v>
+      </c>
+      <c r="K52" s="2" t="n">
+        <v>7.729</v>
+      </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="7" t="inlineStr"/>
     </row>
@@ -2819,39 +2823,39 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>2429</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>TANCO</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="E53" s="3" t="n">
-        <v>-0.0256</v>
+        <v>0.145</v>
+      </c>
+      <c r="E53" s="8" t="n">
+        <v>-0.0333</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>3064600</v>
+        <v>3516700</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.27</v>
+        <v>0.2</v>
       </c>
       <c r="H53" t="n">
-        <v>48.21</v>
+        <v>28.09</v>
       </c>
       <c r="I53" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>1.162</v>
+        <v>0.164</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>1.119</v>
+        <v>0.201</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="7" t="inlineStr"/>
@@ -2864,39 +2868,39 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>MRCB</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="E54" s="10" t="n">
-        <v>0.0182</v>
+        <v>1.14</v>
+      </c>
+      <c r="E54" s="8" t="n">
+        <v>-0.0256</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>2914700</v>
+        <v>3489600</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.41</v>
+        <v>0.31</v>
       </c>
       <c r="H54" t="n">
-        <v>37.22</v>
+        <v>48.21</v>
       </c>
       <c r="I54" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.289</v>
+        <v>1.162</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>0.307</v>
+        <v>1.119</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="7" t="inlineStr"/>
@@ -2909,39 +2913,39 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>5326</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>99SMART</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="E55" s="10" t="n">
-        <v>0.0337</v>
+        <v>3.26</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>0.0449</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>2813100</v>
+        <v>3433200</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.97</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H55" t="n">
-        <v>50.01</v>
+        <v>52.06</v>
       </c>
       <c r="I55" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.912</v>
+        <v>3.199</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>0.965</v>
+        <v>3.39</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="7" t="inlineStr"/>
@@ -2963,27 +2967,27 @@
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="E56" s="3" t="n">
-        <v>-0.0108</v>
+        <v>2.74</v>
+      </c>
+      <c r="E56" s="8" t="n">
+        <v>-0.0144</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>2794300</v>
+        <v>3423500</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.16</v>
+        <v>0.19</v>
       </c>
       <c r="H56" t="n">
-        <v>62.29</v>
-      </c>
-      <c r="I56" s="6" t="inlineStr">
+        <v>61.38</v>
+      </c>
+      <c r="I56" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>2.624</v>
+        <v>2.623</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>2.496</v>
@@ -3008,30 +3012,30 @@
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="E57" s="10" t="n">
-        <v>0.007800000000000001</v>
+        <v>0</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>2790000</v>
+        <v>3404700</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="H57" t="n">
-        <v>44.76</v>
-      </c>
-      <c r="I57" s="9" t="inlineStr">
+        <v>43.08</v>
+      </c>
+      <c r="I57" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>1.323</v>
+        <v>1.322</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>1.306</v>
+        <v>1.305</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="7" t="inlineStr"/>
@@ -3044,39 +3048,39 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>7.25</v>
+        <v>1.2</v>
       </c>
       <c r="E58" s="3" t="n">
-        <v>-0.0014</v>
+        <v>0.0345</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>2758100</v>
+        <v>3369900</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.2</v>
+        <v>0.59</v>
       </c>
       <c r="H58" t="n">
-        <v>31.19</v>
-      </c>
-      <c r="I58" s="9" t="inlineStr">
+        <v>56.94</v>
+      </c>
+      <c r="I58" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>7.639</v>
+        <v>1.155</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>7.729</v>
+        <v>1.165</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="7" t="inlineStr"/>
@@ -3089,39 +3093,39 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>5253</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>ECONBHD</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>1.19</v>
+        <v>0.125</v>
       </c>
       <c r="E59" s="10" t="n">
-        <v>0.0259</v>
+        <v>0</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>2702600</v>
+        <v>3369000</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.47</v>
+        <v>0.74</v>
       </c>
       <c r="H59" t="n">
-        <v>55.65</v>
+        <v>55.25</v>
       </c>
       <c r="I59" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>1.154</v>
+        <v>0.122</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>1.165</v>
+        <v>0.125</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="7" t="inlineStr"/>
@@ -3134,39 +3138,39 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>0.965</v>
+        <v>3.72</v>
       </c>
       <c r="E60" s="8" t="n">
-        <v>0</v>
+        <v>-0.0133</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>2701400</v>
+        <v>3319200</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="H60" t="n">
-        <v>55.29</v>
-      </c>
-      <c r="I60" s="9" t="inlineStr">
+        <v>56.88</v>
+      </c>
+      <c r="I60" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.961</v>
+        <v>3.602</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>0.821</v>
+        <v>2.74</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="7" t="inlineStr"/>
@@ -3179,40 +3183,36 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>0468</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>UNIPAC</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>0.795</v>
+        <v>0.25</v>
       </c>
       <c r="E61" s="10" t="n">
-        <v>0.0127</v>
+        <v>0</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>2684400</v>
+        <v>3193700</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="H61" t="n">
-        <v>57.16</v>
-      </c>
-      <c r="I61" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J61" s="2" t="n">
-        <v>0.767</v>
-      </c>
-      <c r="K61" s="2" t="n">
-        <v>0.712</v>
-      </c>
+        <v>28.11</v>
+      </c>
+      <c r="I61" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="n"/>
+      <c r="K61" s="2" t="n"/>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="7" t="inlineStr"/>
     </row>
@@ -3224,39 +3224,39 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="E62" s="10" t="n">
-        <v>0.0392</v>
+        <v>0.45</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>0.0227</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>2661500</v>
+        <v>3191800</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.16</v>
+        <v>0.3</v>
       </c>
       <c r="H62" t="n">
-        <v>56.74</v>
+        <v>51.11</v>
       </c>
       <c r="I62" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.512</v>
+        <v>0.45</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>0.436</v>
+        <v>0.426</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="7" t="inlineStr"/>
@@ -3269,39 +3269,39 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="E63" s="3" t="n">
-        <v>-0.0151</v>
+        <v>0.46</v>
+      </c>
+      <c r="E63" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>2560900</v>
+        <v>3154700</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.79</v>
+        <v>0.46</v>
       </c>
       <c r="H63" t="n">
-        <v>84.12</v>
-      </c>
-      <c r="I63" s="6" t="inlineStr">
+        <v>62.48</v>
+      </c>
+      <c r="I63" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.656</v>
+        <v>0.427</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>0.479</v>
+        <v>0.413</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="7" t="inlineStr"/>
@@ -3314,39 +3314,39 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="E64" s="10" t="n">
-        <v>0.0227</v>
+        <v>7.13</v>
+      </c>
+      <c r="E64" s="8" t="n">
+        <v>-0.0028</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>2516300</v>
+        <v>3118800</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0.1</v>
+        <v>0.32</v>
       </c>
       <c r="H64" t="n">
-        <v>33.07</v>
-      </c>
-      <c r="I64" s="9" t="inlineStr">
+        <v>19.02</v>
+      </c>
+      <c r="I64" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.249</v>
+        <v>7.597</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>0.304</v>
+        <v>8.09</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="7" t="inlineStr"/>
@@ -3359,39 +3359,39 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="E65" s="10" t="n">
-        <v>0.0331</v>
+        <v>0.795</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>0.0127</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>2491700</v>
+        <v>3110300</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>0.74</v>
+        <v>0.23</v>
       </c>
       <c r="H65" t="n">
-        <v>76.55</v>
-      </c>
-      <c r="I65" s="6" t="inlineStr">
+        <v>57.16</v>
+      </c>
+      <c r="I65" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>1.025</v>
+        <v>0.767</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>0.86</v>
+        <v>0.712</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="7" t="inlineStr"/>
@@ -3404,39 +3404,39 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0268</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>L&amp;PBHD</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>0.235</v>
-      </c>
-      <c r="E66" s="10" t="n">
-        <v>0.0682</v>
+        <v>0.525</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>0.0294</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>2483500</v>
+        <v>2982100</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>1.24</v>
+        <v>0.18</v>
       </c>
       <c r="H66" t="n">
-        <v>76.23999999999999</v>
+        <v>55.9</v>
       </c>
       <c r="I66" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.205</v>
+        <v>0.512</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>0.171</v>
+        <v>0.436</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="7" t="inlineStr"/>
@@ -3449,39 +3449,39 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>0338</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>KOPI</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="E67" s="10" t="n">
-        <v>0.0182</v>
+        <v>0.915</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>0.0281</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>2437500</v>
+        <v>2980800</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>0.25</v>
+        <v>1.03</v>
       </c>
       <c r="H67" t="n">
-        <v>64.88</v>
+        <v>48.14</v>
       </c>
       <c r="I67" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>1.069</v>
+        <v>0.912</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>0.916</v>
+        <v>0.964</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="7" t="inlineStr"/>
@@ -3494,39 +3494,39 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0345</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>SUNLOGY</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>0.455</v>
+        <v>0.965</v>
       </c>
       <c r="E68" s="10" t="n">
-        <v>0.0341</v>
+        <v>0</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>2377200</v>
+        <v>2818300</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>0.23</v>
+        <v>0.35</v>
       </c>
       <c r="H68" t="n">
-        <v>52.28</v>
+        <v>55.29</v>
       </c>
       <c r="I68" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.451</v>
+        <v>0.961</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>0.426</v>
+        <v>0.821</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="7" t="inlineStr"/>
@@ -3539,39 +3539,39 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="E69" s="10" t="n">
-        <v>0.0035</v>
+        <v>1.11</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>0.0091</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>2344000</v>
+        <v>2791500</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>0.75</v>
+        <v>0.29</v>
       </c>
       <c r="H69" t="n">
-        <v>75.53</v>
-      </c>
-      <c r="I69" s="6" t="inlineStr">
+        <v>63.64</v>
+      </c>
+      <c r="I69" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>2.638</v>
+        <v>1.068</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>2.285</v>
+        <v>0.916</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="7" t="inlineStr"/>
@@ -3584,39 +3584,39 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>0.55</v>
+        <v>0.225</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>-0.009000000000000001</v>
+        <v>0.0227</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>2334200</v>
+        <v>2715400</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>0.43</v>
+        <v>0.1</v>
       </c>
       <c r="H70" t="n">
-        <v>33.2</v>
-      </c>
-      <c r="I70" s="9" t="inlineStr">
+        <v>33.07</v>
+      </c>
+      <c r="I70" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.592</v>
+        <v>0.249</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>0.641</v>
+        <v>0.304</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="7" t="inlineStr"/>
@@ -3629,39 +3629,39 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="E71" s="10" t="n">
-        <v>0.0286</v>
+        <v>2.88</v>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>0.0105</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>2214600</v>
+        <v>2694700</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>0.24</v>
+        <v>0.86</v>
       </c>
       <c r="H71" t="n">
-        <v>63.57</v>
-      </c>
-      <c r="I71" s="6" t="inlineStr">
+        <v>76.28</v>
+      </c>
+      <c r="I71" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.672</v>
+        <v>2.64</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>0.607</v>
+        <v>2.286</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="7" t="inlineStr"/>
@@ -3674,39 +3674,39 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>7.12</v>
-      </c>
-      <c r="E72" s="3" t="n">
-        <v>-0.0042</v>
+        <v>0.545</v>
+      </c>
+      <c r="E72" s="8" t="n">
+        <v>-0.018</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>2201700</v>
+        <v>2623800</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>0.23</v>
+        <v>0.49</v>
       </c>
       <c r="H72" t="n">
-        <v>18.83</v>
-      </c>
-      <c r="I72" s="9" t="inlineStr">
+        <v>32.26</v>
+      </c>
+      <c r="I72" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>7.596</v>
+        <v>0.592</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>8.09</v>
+        <v>0.641</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="7" t="inlineStr"/>
@@ -3719,39 +3719,39 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0104</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>GENETEC</t>
+          <t>CNERGEN</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>0.33</v>
+        <v>1.24</v>
       </c>
       <c r="E73" s="3" t="n">
-        <v>-0.0149</v>
+        <v>0.0248</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>2153300</v>
+        <v>2604000</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>0.38</v>
+        <v>0.77</v>
       </c>
       <c r="H73" t="n">
-        <v>52.01</v>
-      </c>
-      <c r="I73" s="6" t="inlineStr">
+        <v>76.11</v>
+      </c>
+      <c r="I73" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.326</v>
+        <v>1.024</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>0.338</v>
+        <v>0.86</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="7" t="inlineStr"/>
@@ -3764,39 +3764,39 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E74" s="10" t="n">
-        <v>0.0172</v>
+        <v>0.975</v>
+      </c>
+      <c r="E74" s="8" t="n">
+        <v>-0.0201</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>2135200</v>
+        <v>2590900</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>0.24</v>
+        <v>0.8</v>
       </c>
       <c r="H74" t="n">
-        <v>57.36</v>
-      </c>
-      <c r="I74" s="6" t="inlineStr">
+        <v>83.41</v>
+      </c>
+      <c r="I74" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.278</v>
+        <v>0.656</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>0.303</v>
+        <v>0.479</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="7" t="inlineStr"/>
@@ -3809,39 +3809,39 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>0268</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>NEXG</t>
+          <t>L&amp;PBHD</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E75" s="10" t="n">
-        <v>0.0172</v>
+        <v>0.24</v>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>0.09089999999999999</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>2085900</v>
+        <v>2578600</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>0.17</v>
+        <v>1.29</v>
       </c>
       <c r="H75" t="n">
-        <v>52.49</v>
-      </c>
-      <c r="I75" s="6" t="inlineStr">
+        <v>77.70999999999999</v>
+      </c>
+      <c r="I75" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.291</v>
+        <v>0.206</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>0.281</v>
+        <v>0.171</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="7" t="inlineStr"/>
@@ -3854,39 +3854,39 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>5141</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>DAYANG</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>1.42</v>
+        <v>0.72</v>
       </c>
       <c r="E76" s="3" t="n">
-        <v>-0.0207</v>
+        <v>0.0286</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>2064900</v>
+        <v>2522000</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.27</v>
       </c>
       <c r="H76" t="n">
-        <v>37.98</v>
+        <v>63.57</v>
       </c>
       <c r="I76" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>1.459</v>
+        <v>0.672</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>1.495</v>
+        <v>0.607</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="7" t="inlineStr"/>
@@ -3899,39 +3899,39 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>NEXG</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="E77" s="10" t="n">
-        <v>0.0112</v>
+        <v>0.295</v>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>0.0172</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>2006000</v>
+        <v>2508400</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>0.33</v>
+        <v>0.21</v>
       </c>
       <c r="H77" t="n">
-        <v>57.99</v>
-      </c>
-      <c r="I77" s="6" t="inlineStr">
+        <v>52.49</v>
+      </c>
+      <c r="I77" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>2.629</v>
+        <v>0.291</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>2.581</v>
+        <v>0.281</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="7" t="inlineStr"/>
@@ -3944,39 +3944,39 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0267</t>
+          <t>5141</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>ECA</t>
+          <t>DAYANG</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="E78" s="10" t="n">
-        <v>0.0548</v>
+        <v>1.41</v>
+      </c>
+      <c r="E78" s="8" t="n">
+        <v>-0.0276</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>1973200</v>
+        <v>2486400</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>0.59</v>
+        <v>1.13</v>
       </c>
       <c r="H78" t="n">
-        <v>54.15</v>
+        <v>36.3</v>
       </c>
       <c r="I78" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.367</v>
+        <v>1.458</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>0.374</v>
+        <v>1.495</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="7" t="inlineStr"/>
@@ -3989,39 +3989,39 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>TENAGA</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>12.96</v>
-      </c>
-      <c r="E79" s="10" t="n">
-        <v>0.004699999999999999</v>
+        <v>1.27</v>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>0.0242</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>1934900</v>
+        <v>2476700</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>0.21</v>
+        <v>0.28</v>
       </c>
       <c r="H79" t="n">
-        <v>42.32</v>
+        <v>41.85</v>
       </c>
       <c r="I79" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>13.036</v>
+        <v>1.287</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>13.573</v>
+        <v>1.387</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="7" t="inlineStr"/>
@@ -4034,39 +4034,39 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E80" s="10" t="n">
-        <v>0.0256</v>
+        <v>2.69</v>
+      </c>
+      <c r="E80" s="3" t="n">
+        <v>0.0037</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>1917200</v>
+        <v>2442000</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>0.27</v>
+        <v>0.41</v>
       </c>
       <c r="H80" t="n">
-        <v>64.98</v>
-      </c>
-      <c r="I80" s="6" t="inlineStr">
+        <v>56.64</v>
+      </c>
+      <c r="I80" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.736</v>
+        <v>2.628</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>0.652</v>
+        <v>2.58</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="7" t="inlineStr"/>
@@ -4079,39 +4079,39 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>0296</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>SKPRES</t>
+          <t>HEGROUP</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="E81" s="10" t="n">
-        <v>0.0133</v>
+        <v>1.1</v>
+      </c>
+      <c r="E81" s="8" t="n">
+        <v>-0.0351</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>1873200</v>
+        <v>2383600</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>0.23</v>
+        <v>0.49</v>
       </c>
       <c r="H81" t="n">
-        <v>67.83</v>
-      </c>
-      <c r="I81" s="6" t="inlineStr">
+        <v>62.77</v>
+      </c>
+      <c r="I81" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.354</v>
+        <v>1.056</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>0.322</v>
+        <v>0.891</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="7" t="inlineStr"/>
@@ -4124,39 +4124,39 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>7225</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>TENAGA</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>0.205</v>
-      </c>
-      <c r="E82" s="8" t="n">
-        <v>0</v>
+        <v>13</v>
+      </c>
+      <c r="E82" s="3" t="n">
+        <v>0.007800000000000001</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>1796000</v>
+        <v>2358000</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>0.39</v>
+        <v>0.26</v>
       </c>
       <c r="H82" t="n">
-        <v>47.55</v>
+        <v>44.16</v>
       </c>
       <c r="I82" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.207</v>
+        <v>13.039</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>0.208</v>
+        <v>13.573</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="7" t="inlineStr"/>
@@ -4169,39 +4169,39 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>0.945</v>
-      </c>
-      <c r="E83" s="10" t="n">
-        <v>0.0161</v>
+        <v>0.795</v>
+      </c>
+      <c r="E83" s="3" t="n">
+        <v>0.0192</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>1778300</v>
+        <v>2302700</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>1.04</v>
+        <v>0.33</v>
       </c>
       <c r="H83" t="n">
-        <v>56.09</v>
+        <v>64.39</v>
       </c>
       <c r="I83" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.924</v>
+        <v>0.735</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>0.85</v>
+        <v>0.652</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="7" t="inlineStr"/>
@@ -4214,39 +4214,39 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="E84" s="10" t="n">
-        <v>0.008100000000000001</v>
+        <v>5.6</v>
+      </c>
+      <c r="E84" s="3" t="n">
+        <v>0.0072</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>1771800</v>
+        <v>2238300</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
       <c r="H84" t="n">
-        <v>36.79</v>
-      </c>
-      <c r="I84" s="9" t="inlineStr">
+        <v>50.83</v>
+      </c>
+      <c r="I84" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>1.286</v>
+        <v>5.636</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>1.387</v>
+        <v>5.308</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="7" t="inlineStr"/>
@@ -4259,39 +4259,39 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0249</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>LGMS</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>0.57</v>
+        <v>0.33</v>
       </c>
       <c r="E85" s="8" t="n">
-        <v>0</v>
+        <v>-0.0149</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>1748400</v>
+        <v>2203000</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>1.94</v>
+        <v>0.39</v>
       </c>
       <c r="H85" t="n">
-        <v>71.84</v>
-      </c>
-      <c r="I85" s="6" t="inlineStr">
+        <v>52.01</v>
+      </c>
+      <c r="I85" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.523</v>
+        <v>0.326</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>0.504</v>
+        <v>0.338</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="7" t="inlineStr"/>
@@ -4304,39 +4304,39 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0239</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>ECOMATE</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E86" s="8" t="n">
-        <v>0</v>
+        <v>0.295</v>
+      </c>
+      <c r="E86" s="3" t="n">
+        <v>0.0172</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>1741000</v>
+        <v>2202200</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>0.54</v>
+        <v>0.25</v>
       </c>
       <c r="H86" t="n">
-        <v>52.86</v>
+        <v>57.36</v>
       </c>
       <c r="I86" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.864</v>
+        <v>0.278</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>0.858</v>
+        <v>0.303</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="7" t="inlineStr"/>
@@ -4349,39 +4349,39 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>0239</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>IOICORP</t>
+          <t>ECOMATE</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>4.58</v>
+        <v>0.865</v>
       </c>
       <c r="E87" s="10" t="n">
-        <v>0.0044</v>
+        <v>0</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v>1739900</v>
+        <v>2152900</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>0.18</v>
+        <v>0.67</v>
       </c>
       <c r="H87" t="n">
-        <v>41.8</v>
-      </c>
-      <c r="I87" s="9" t="inlineStr">
+        <v>52.86</v>
+      </c>
+      <c r="I87" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>4.675</v>
+        <v>0.864</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>4.62</v>
+        <v>0.858</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="7" t="inlineStr"/>
@@ -4394,39 +4394,39 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0359</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>HKB</t>
+          <t>CPETECH</t>
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="E88" s="10" t="n">
-        <v>0.0186</v>
+        <v>1.34</v>
+      </c>
+      <c r="E88" s="3" t="n">
+        <v>0.0075</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>1735400</v>
+        <v>2121100</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>0.78</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H88" t="n">
-        <v>82.16</v>
-      </c>
-      <c r="I88" s="6" t="inlineStr">
+        <v>56.94</v>
+      </c>
+      <c r="I88" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.679</v>
+        <v>1.293</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>0.622</v>
+        <v>1.194</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="7" t="inlineStr"/>
@@ -4439,39 +4439,39 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>0.805</v>
-      </c>
-      <c r="E89" s="8" t="n">
-        <v>0</v>
+        <v>2.11</v>
+      </c>
+      <c r="E89" s="3" t="n">
+        <v>0.0048</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>1708700</v>
+        <v>2120100</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>0.28</v>
+        <v>0.11</v>
       </c>
       <c r="H89" t="n">
-        <v>70.15000000000001</v>
+        <v>52.16</v>
       </c>
       <c r="I89" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.785</v>
+        <v>2.099</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>0.764</v>
+        <v>2.081</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="7" t="inlineStr"/>
@@ -4484,39 +4484,39 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="E90" s="8" t="n">
-        <v>0</v>
+        <v>1.64</v>
+      </c>
+      <c r="E90" s="3" t="n">
+        <v>0.0314</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>1653200</v>
+        <v>2085700</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>0.08</v>
+        <v>0.31</v>
       </c>
       <c r="H90" t="n">
-        <v>50.69</v>
+        <v>41.93</v>
       </c>
       <c r="I90" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J90" s="2" t="n">
-        <v>2.098</v>
+        <v>1.671</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>2.08</v>
+        <v>1.787</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="7" t="inlineStr"/>
@@ -4529,39 +4529,39 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0045</t>
+          <t>0267</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>SSB8</t>
+          <t>ECA</t>
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="E91" s="8" t="n">
-        <v>0</v>
+        <v>0.385</v>
+      </c>
+      <c r="E91" s="3" t="n">
+        <v>0.0548</v>
       </c>
       <c r="F91" s="4" t="n">
-        <v>1613800</v>
+        <v>2020900</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>0.39</v>
+        <v>0.6</v>
       </c>
       <c r="H91" t="n">
-        <v>64</v>
-      </c>
-      <c r="I91" s="6" t="inlineStr">
+        <v>54.15</v>
+      </c>
+      <c r="I91" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.637</v>
+        <v>0.367</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>0.601</v>
+        <v>0.374</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="7" t="inlineStr"/>
@@ -4574,39 +4574,39 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>2.5</v>
+        <v>0.545</v>
       </c>
       <c r="E92" s="10" t="n">
-        <v>0.008100000000000001</v>
+        <v>0</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v>1543100</v>
+        <v>1914400</v>
       </c>
       <c r="G92" s="5" t="n">
-        <v>0.11</v>
+        <v>0.46</v>
       </c>
       <c r="H92" t="n">
-        <v>58.18</v>
+        <v>71.06999999999999</v>
       </c>
       <c r="I92" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J92" s="2" t="n">
-        <v>2.463</v>
+        <v>0.477</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>2.344</v>
+        <v>0.451</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="7" t="inlineStr"/>
@@ -4619,39 +4619,39 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>0359</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>HKB</t>
         </is>
       </c>
       <c r="D93" s="2" t="n">
-        <v>0.535</v>
-      </c>
-      <c r="E93" s="10" t="n">
-        <v>0.009399999999999999</v>
+        <v>0.82</v>
+      </c>
+      <c r="E93" s="3" t="n">
+        <v>0.0186</v>
       </c>
       <c r="F93" s="4" t="n">
-        <v>1508100</v>
+        <v>1876600</v>
       </c>
       <c r="G93" s="5" t="n">
-        <v>0.2</v>
+        <v>0.84</v>
       </c>
       <c r="H93" t="n">
-        <v>55.09</v>
+        <v>82.16</v>
       </c>
       <c r="I93" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.522</v>
+        <v>0.679</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>0.531</v>
+        <v>0.622</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="7" t="inlineStr"/>
@@ -4664,39 +4664,39 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>0249</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>LGMS</t>
         </is>
       </c>
       <c r="D94" s="2" t="n">
-        <v>1.07</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="E94" s="8" t="n">
-        <v>0</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>1499200</v>
+        <v>1827200</v>
       </c>
       <c r="G94" s="5" t="n">
-        <v>0.1</v>
+        <v>2.03</v>
       </c>
       <c r="H94" t="n">
-        <v>50.51</v>
-      </c>
-      <c r="I94" s="6" t="inlineStr">
+        <v>69.2</v>
+      </c>
+      <c r="I94" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J94" s="2" t="n">
-        <v>1.072</v>
+        <v>0.523</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>1.037</v>
+        <v>0.504</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="7" t="inlineStr"/>
@@ -4709,39 +4709,39 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>0272</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>TTVHB</t>
         </is>
       </c>
       <c r="D95" s="2" t="n">
-        <v>0.355</v>
-      </c>
-      <c r="E95" s="10" t="n">
-        <v>0.0143</v>
+        <v>0.26</v>
+      </c>
+      <c r="E95" s="3" t="n">
+        <v>0.0612</v>
       </c>
       <c r="F95" s="4" t="n">
-        <v>1494900</v>
+        <v>1822700</v>
       </c>
       <c r="G95" s="5" t="n">
-        <v>0.19</v>
+        <v>0.91</v>
       </c>
       <c r="H95" t="n">
-        <v>58.58</v>
-      </c>
-      <c r="I95" s="6" t="inlineStr">
+        <v>55.07</v>
+      </c>
+      <c r="I95" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.344</v>
+        <v>0.249</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>0.324</v>
+        <v>0.253</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="7" t="inlineStr"/>
@@ -4754,39 +4754,39 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D96" s="2" t="n">
-        <v>0.545</v>
-      </c>
-      <c r="E96" s="8" t="n">
-        <v>0</v>
+        <v>2.49</v>
+      </c>
+      <c r="E96" s="3" t="n">
+        <v>0.004</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>1479000</v>
+        <v>1818400</v>
       </c>
       <c r="G96" s="5" t="n">
-        <v>0.36</v>
+        <v>0.14</v>
       </c>
       <c r="H96" t="n">
-        <v>71.06999999999999</v>
+        <v>57.08</v>
       </c>
       <c r="I96" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.477</v>
+        <v>2.462</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>0.451</v>
+        <v>2.344</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="7" t="inlineStr"/>
@@ -4799,39 +4799,39 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>0273</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>VLB</t>
         </is>
       </c>
       <c r="D97" s="2" t="n">
-        <v>5.59</v>
-      </c>
-      <c r="E97" s="10" t="n">
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="E97" s="3" t="n">
         <v>0.0054</v>
       </c>
       <c r="F97" s="4" t="n">
-        <v>1442200</v>
+        <v>1815300</v>
       </c>
       <c r="G97" s="5" t="n">
-        <v>0.1</v>
+        <v>1.06</v>
       </c>
       <c r="H97" t="n">
-        <v>50.41</v>
-      </c>
-      <c r="I97" s="9" t="inlineStr">
+        <v>54.68</v>
+      </c>
+      <c r="I97" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J97" s="2" t="n">
-        <v>5.635</v>
+        <v>0.923</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>5.307</v>
+        <v>0.85</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="7" t="inlineStr"/>
@@ -4844,39 +4844,39 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D98" s="2" t="n">
-        <v>4.23</v>
-      </c>
-      <c r="E98" s="3" t="n">
-        <v>-0.006999999999999999</v>
+        <v>0.8</v>
+      </c>
+      <c r="E98" s="8" t="n">
+        <v>-0.0062</v>
       </c>
       <c r="F98" s="4" t="n">
-        <v>1406600</v>
+        <v>1808200</v>
       </c>
       <c r="G98" s="5" t="n">
-        <v>0.18</v>
+        <v>0.29</v>
       </c>
       <c r="H98" t="n">
-        <v>43.38</v>
+        <v>65.37</v>
       </c>
       <c r="I98" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J98" s="2" t="n">
-        <v>4.369</v>
+        <v>0.785</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>4.464</v>
+        <v>0.764</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="7" t="inlineStr"/>
@@ -4889,39 +4889,39 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>CMSB</t>
         </is>
       </c>
       <c r="D99" s="2" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="E99" s="8" t="n">
-        <v>0</v>
+        <v>0.92</v>
+      </c>
+      <c r="E99" s="3" t="n">
+        <v>0.0166</v>
       </c>
       <c r="F99" s="4" t="n">
-        <v>1376100</v>
+        <v>1805100</v>
       </c>
       <c r="G99" s="5" t="n">
-        <v>0.33</v>
+        <v>0.88</v>
       </c>
       <c r="H99" t="n">
-        <v>37.05</v>
-      </c>
-      <c r="I99" s="9" t="inlineStr">
+        <v>33.38</v>
+      </c>
+      <c r="I99" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J99" s="2" t="n">
-        <v>1.895</v>
+        <v>0.96</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>2.026</v>
+        <v>0.993</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="7" t="inlineStr"/>
@@ -4934,39 +4934,39 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>0172</t>
+          <t>7225</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>OCK</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="D100" s="2" t="n">
-        <v>0.45</v>
+        <v>0.205</v>
       </c>
       <c r="E100" s="10" t="n">
-        <v>0.0112</v>
+        <v>0</v>
       </c>
       <c r="F100" s="4" t="n">
-        <v>1372000</v>
+        <v>1804100</v>
       </c>
       <c r="G100" s="5" t="n">
         <v>0.39</v>
       </c>
       <c r="H100" t="n">
-        <v>49.83</v>
-      </c>
-      <c r="I100" s="9" t="inlineStr">
+        <v>47.55</v>
+      </c>
+      <c r="I100" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.457</v>
+        <v>0.207</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>0.42</v>
+        <v>0.208</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="7" t="inlineStr"/>
@@ -4979,39 +4979,39 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>0296</t>
+          <t>5337</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>HEGROUP</t>
+          <t>ECOSHOP</t>
         </is>
       </c>
       <c r="D101" s="2" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="E101" s="8" t="n">
-        <v>0</v>
+        <v>1.46</v>
+      </c>
+      <c r="E101" s="3" t="n">
+        <v>0.021</v>
       </c>
       <c r="F101" s="4" t="n">
-        <v>1360400</v>
+        <v>1736500</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>0.28</v>
+        <v>0.38</v>
       </c>
       <c r="H101" t="n">
-        <v>71.20999999999999</v>
+        <v>49.32</v>
       </c>
       <c r="I101" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J101" s="2" t="n">
-        <v>1.059</v>
+        <v>1.461</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>0.892</v>
+        <v>1.469</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="7" t="inlineStr"/>
@@ -5024,33 +5024,40 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>0475</t>
+          <t>0045</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>GBBOND</t>
+          <t>SSB8</t>
         </is>
       </c>
       <c r="D102" s="2" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="E102" s="10" t="n">
-        <v>0.0455</v>
+        <v>0.665</v>
+      </c>
+      <c r="E102" s="8" t="n">
+        <v>-0.0075</v>
       </c>
       <c r="F102" s="4" t="n">
-        <v>1360100</v>
+        <v>1724300</v>
       </c>
       <c r="G102" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.41</v>
+      </c>
+      <c r="H102" t="n">
+        <v>62</v>
       </c>
       <c r="I102" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J102" s="2" t="n"/>
-      <c r="K102" s="2" t="n"/>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="n">
+        <v>0.637</v>
+      </c>
+      <c r="K102" s="2" t="n">
+        <v>0.601</v>
+      </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="7" t="inlineStr"/>
     </row>
@@ -5062,39 +5069,39 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>AWC</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D103" s="2" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E103" s="8" t="n">
-        <v>0</v>
+        <v>0.535</v>
+      </c>
+      <c r="E103" s="3" t="n">
+        <v>0.009399999999999999</v>
       </c>
       <c r="F103" s="4" t="n">
-        <v>1293700</v>
+        <v>1655700</v>
       </c>
       <c r="G103" s="5" t="n">
-        <v>0.59</v>
+        <v>0.22</v>
       </c>
       <c r="H103" t="n">
-        <v>57.68</v>
-      </c>
-      <c r="I103" s="9" t="inlineStr">
+        <v>55.09</v>
+      </c>
+      <c r="I103" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.62</v>
+        <v>0.522</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>0.529</v>
+        <v>0.531</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="7" t="inlineStr"/>
@@ -5107,39 +5114,39 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>0277</t>
+          <t>5210</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>CLOUDPT</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="D104" s="2" t="n">
-        <v>0.515</v>
-      </c>
-      <c r="E104" s="10" t="n">
-        <v>0.0098</v>
+        <v>0.325</v>
+      </c>
+      <c r="E104" s="8" t="n">
+        <v>-0.0152</v>
       </c>
       <c r="F104" s="4" t="n">
-        <v>1277600</v>
+        <v>1601300</v>
       </c>
       <c r="G104" s="5" t="n">
-        <v>0.78</v>
+        <v>0.27</v>
       </c>
       <c r="H104" t="n">
-        <v>62.85</v>
+        <v>32.41</v>
       </c>
       <c r="I104" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.489</v>
+        <v>0.339</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>0.479</v>
+        <v>0.345</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="7" t="inlineStr"/>
@@ -5152,39 +5159,39 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>0272</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>TTVHB</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D105" s="2" t="n">
-        <v>0.255</v>
-      </c>
-      <c r="E105" s="10" t="n">
-        <v>0.0408</v>
+        <v>4.23</v>
+      </c>
+      <c r="E105" s="8" t="n">
+        <v>-0.006999999999999999</v>
       </c>
       <c r="F105" s="4" t="n">
-        <v>1263900</v>
+        <v>1563500</v>
       </c>
       <c r="G105" s="5" t="n">
-        <v>0.63</v>
+        <v>0.2</v>
       </c>
       <c r="H105" t="n">
-        <v>52.98</v>
+        <v>43.38</v>
       </c>
       <c r="I105" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.248</v>
+        <v>4.369</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>0.253</v>
+        <v>4.464</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="7" t="inlineStr"/>
@@ -5197,39 +5204,39 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>5337</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>ECOSHOP</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D106" s="2" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="E106" s="10" t="n">
-        <v>0.014</v>
+        <v>1.06</v>
+      </c>
+      <c r="E106" s="8" t="n">
+        <v>-0.009300000000000001</v>
       </c>
       <c r="F106" s="4" t="n">
-        <v>1256000</v>
+        <v>1557900</v>
       </c>
       <c r="G106" s="5" t="n">
-        <v>0.27</v>
+        <v>0.11</v>
       </c>
       <c r="H106" t="n">
-        <v>46.32</v>
+        <v>48.94</v>
       </c>
       <c r="I106" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J106" s="2" t="n">
-        <v>1.46</v>
+        <v>1.071</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>1.468</v>
+        <v>1.037</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="7" t="inlineStr"/>
@@ -5242,39 +5249,39 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D107" s="2" t="n">
-        <v>0.925</v>
-      </c>
-      <c r="E107" s="3" t="n">
-        <v>-0.0054</v>
+        <v>0.35</v>
+      </c>
+      <c r="E107" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F107" s="4" t="n">
-        <v>1255700</v>
+        <v>1519900</v>
       </c>
       <c r="G107" s="5" t="n">
-        <v>0.24</v>
+        <v>0.2</v>
       </c>
       <c r="H107" t="n">
-        <v>61.28</v>
+        <v>56.58</v>
       </c>
       <c r="I107" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.908</v>
+        <v>0.343</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>0.863</v>
+        <v>0.324</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="7" t="inlineStr"/>
@@ -5287,39 +5294,39 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>6633</t>
+          <t>5306</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>LHI</t>
+          <t>FFB</t>
         </is>
       </c>
       <c r="D108" s="2" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="E108" s="8" t="n">
-        <v>0</v>
+        <v>1.8</v>
+      </c>
+      <c r="E108" s="3" t="n">
+        <v>0.0286</v>
       </c>
       <c r="F108" s="4" t="n">
-        <v>1255700</v>
+        <v>1489500</v>
       </c>
       <c r="G108" s="5" t="n">
-        <v>0.75</v>
+        <v>0.51</v>
       </c>
       <c r="H108" t="n">
-        <v>47.32</v>
+        <v>32.69</v>
       </c>
       <c r="I108" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.735</v>
+        <v>1.88</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>0.749</v>
+        <v>2.017</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="7" t="inlineStr"/>
@@ -5332,39 +5339,39 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>5306</t>
+          <t>6947</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>FFB</t>
+          <t>CDB</t>
         </is>
       </c>
       <c r="D109" s="2" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="E109" s="10" t="n">
-        <v>0.0229</v>
+        <v>2.55</v>
+      </c>
+      <c r="E109" s="3" t="n">
+        <v>0.03240000000000001</v>
       </c>
       <c r="F109" s="4" t="n">
-        <v>1181200</v>
+        <v>1441000</v>
       </c>
       <c r="G109" s="5" t="n">
-        <v>0.41</v>
+        <v>0.46</v>
       </c>
       <c r="H109" t="n">
-        <v>30.67</v>
+        <v>41.75</v>
       </c>
       <c r="I109" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J109" s="2" t="n">
-        <v>1.879</v>
+        <v>2.586</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>2.017</v>
+        <v>2.731</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="7" t="inlineStr"/>
@@ -5377,39 +5384,39 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>CMSB</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D110" s="2" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="E110" s="10" t="n">
-        <v>0.0166</v>
+        <v>4.27</v>
+      </c>
+      <c r="E110" s="3" t="n">
+        <v>0.0264</v>
       </c>
       <c r="F110" s="4" t="n">
-        <v>1175900</v>
+        <v>1423200</v>
       </c>
       <c r="G110" s="5" t="n">
-        <v>0.57</v>
+        <v>0.17</v>
       </c>
       <c r="H110" t="n">
-        <v>33.38</v>
+        <v>65.23</v>
       </c>
       <c r="I110" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.96</v>
+        <v>3.968</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>0.993</v>
+        <v>3.443</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="7" t="inlineStr"/>
@@ -5422,39 +5429,39 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>0056</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>NCT</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D111" s="2" t="n">
-        <v>0.5649999999999999</v>
+        <v>1.85</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>-0.008800000000000001</v>
+        <v>0.0054</v>
       </c>
       <c r="F111" s="4" t="n">
-        <v>1153200</v>
+        <v>1395600</v>
       </c>
       <c r="G111" s="5" t="n">
-        <v>0.53</v>
+        <v>0.33</v>
       </c>
       <c r="H111" t="n">
-        <v>51.06</v>
+        <v>38.83</v>
       </c>
       <c r="I111" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.5629999999999999</v>
+        <v>1.896</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>0.5620000000000001</v>
+        <v>2.026</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="7" t="inlineStr"/>
@@ -5467,39 +5474,39 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>5322</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>FEYTECH</t>
         </is>
       </c>
       <c r="D112" s="2" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="E112" s="10" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.225</v>
+      </c>
+      <c r="E112" s="8" t="n">
+        <v>-0.0426</v>
       </c>
       <c r="F112" s="4" t="n">
-        <v>1149200</v>
+        <v>1394100</v>
       </c>
       <c r="G112" s="5" t="n">
-        <v>0.3</v>
+        <v>2.01</v>
       </c>
       <c r="H112" t="n">
-        <v>63.45</v>
+        <v>44.59</v>
       </c>
       <c r="I112" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.596</v>
+        <v>0.231</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>0.582</v>
+        <v>0.234</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="7" t="inlineStr"/>
@@ -5512,39 +5519,39 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>0373</t>
+          <t>0328</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>VERDANT</t>
+          <t>3REN</t>
         </is>
       </c>
       <c r="D113" s="2" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="E113" s="10" t="n">
-        <v>0.0182</v>
+        <v>0.4</v>
+      </c>
+      <c r="E113" s="3" t="n">
+        <v>0.039</v>
       </c>
       <c r="F113" s="4" t="n">
-        <v>1143000</v>
+        <v>1387000</v>
       </c>
       <c r="G113" s="5" t="n">
-        <v>0.26</v>
+        <v>0.7</v>
       </c>
       <c r="H113" t="n">
-        <v>69.36</v>
+        <v>56.15</v>
       </c>
       <c r="I113" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.252</v>
+        <v>0.386</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>0.22</v>
+        <v>0.391</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="7" t="inlineStr"/>
@@ -5557,39 +5564,39 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>0172</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>OCK</t>
         </is>
       </c>
       <c r="D114" s="2" t="n">
-        <v>0.83</v>
+        <v>0.45</v>
       </c>
       <c r="E114" s="3" t="n">
-        <v>-0.0119</v>
+        <v>0.0112</v>
       </c>
       <c r="F114" s="4" t="n">
-        <v>1122400</v>
+        <v>1385300</v>
       </c>
       <c r="G114" s="5" t="n">
-        <v>0.17</v>
+        <v>0.39</v>
       </c>
       <c r="H114" t="n">
-        <v>72.09</v>
+        <v>49.83</v>
       </c>
       <c r="I114" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.75</v>
+        <v>0.457</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>0.663</v>
+        <v>0.42</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="7" t="inlineStr"/>
@@ -5602,40 +5609,33 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>0475</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>CPETECH</t>
+          <t>GBBOND</t>
         </is>
       </c>
       <c r="D115" s="2" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="E115" s="10" t="n">
-        <v>0.015</v>
+        <v>0.23</v>
+      </c>
+      <c r="E115" s="3" t="n">
+        <v>0.0455</v>
       </c>
       <c r="F115" s="4" t="n">
-        <v>1095500</v>
+        <v>1360200</v>
       </c>
       <c r="G115" s="5" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="H115" t="n">
-        <v>57.71</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I115" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J115" s="2" t="n">
-        <v>1.294</v>
-      </c>
-      <c r="K115" s="2" t="n">
-        <v>1.194</v>
-      </c>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J115" s="2" t="n"/>
+      <c r="K115" s="2" t="n"/>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="7" t="inlineStr"/>
     </row>
@@ -5647,39 +5647,39 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>0056</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>NCT</t>
         </is>
       </c>
       <c r="D116" s="2" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="E116" s="10" t="n">
-        <v>0.0126</v>
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E116" s="8" t="n">
+        <v>-0.0175</v>
       </c>
       <c r="F116" s="4" t="n">
-        <v>1082400</v>
+        <v>1353400</v>
       </c>
       <c r="G116" s="5" t="n">
-        <v>0.16</v>
+        <v>0.62</v>
       </c>
       <c r="H116" t="n">
-        <v>36.89</v>
+        <v>48.28</v>
       </c>
       <c r="I116" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J116" s="2" t="n">
-        <v>1.668</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="K116" s="2" t="n">
-        <v>1.786</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="7" t="inlineStr"/>
@@ -5692,39 +5692,39 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>0450</t>
+          <t>3662</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>MFGROUP</t>
+          <t>MFLOUR</t>
         </is>
       </c>
       <c r="D117" s="2" t="n">
-        <v>0.265</v>
+        <v>0.6</v>
       </c>
       <c r="E117" s="3" t="n">
-        <v>-0.0185</v>
+        <v>0.0256</v>
       </c>
       <c r="F117" s="4" t="n">
-        <v>1082000</v>
+        <v>1331600</v>
       </c>
       <c r="G117" s="5" t="n">
-        <v>1.11</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H117" t="n">
-        <v>54.17</v>
-      </c>
-      <c r="I117" s="9" t="inlineStr">
+        <v>40.75</v>
+      </c>
+      <c r="I117" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.262</v>
+        <v>0.617</v>
       </c>
       <c r="K117" s="2" t="n">
-        <v>0.264</v>
+        <v>0.635</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="7" t="inlineStr"/>
@@ -5737,39 +5737,39 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>7081</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D118" s="2" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="E118" s="3" t="n">
-        <v>-0.0109</v>
+        <v>0.92</v>
+      </c>
+      <c r="E118" s="8" t="n">
+        <v>-0.0108</v>
       </c>
       <c r="F118" s="4" t="n">
-        <v>1057700</v>
+        <v>1331100</v>
       </c>
       <c r="G118" s="5" t="n">
-        <v>0.45</v>
+        <v>0.26</v>
       </c>
       <c r="H118" t="n">
-        <v>20.11</v>
-      </c>
-      <c r="I118" s="9" t="inlineStr">
+        <v>58.88</v>
+      </c>
+      <c r="I118" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J118" s="2" t="n">
-        <v>1.036</v>
+        <v>0.907</v>
       </c>
       <c r="K118" s="2" t="n">
-        <v>1.119</v>
+        <v>0.863</v>
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" s="7" t="inlineStr"/>
@@ -5782,39 +5782,39 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>0373</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>VERDANT</t>
         </is>
       </c>
       <c r="D119" s="2" t="n">
-        <v>4.24</v>
-      </c>
-      <c r="E119" s="10" t="n">
-        <v>0.0192</v>
+        <v>0.28</v>
+      </c>
+      <c r="E119" s="3" t="n">
+        <v>0.0182</v>
       </c>
       <c r="F119" s="4" t="n">
-        <v>1040000</v>
+        <v>1324100</v>
       </c>
       <c r="G119" s="5" t="n">
-        <v>0.12</v>
+        <v>0.3</v>
       </c>
       <c r="H119" t="n">
-        <v>64.51000000000001</v>
+        <v>69.36</v>
       </c>
       <c r="I119" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J119" s="2" t="n">
-        <v>3.965</v>
+        <v>0.252</v>
       </c>
       <c r="K119" s="2" t="n">
-        <v>3.443</v>
+        <v>0.22</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="7" t="inlineStr"/>
@@ -5827,39 +5827,39 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>3662</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>MFLOUR</t>
+          <t>AWC</t>
         </is>
       </c>
       <c r="D120" s="2" t="n">
-        <v>0.595</v>
+        <v>0.635</v>
       </c>
       <c r="E120" s="10" t="n">
-        <v>0.0171</v>
+        <v>0</v>
       </c>
       <c r="F120" s="4" t="n">
-        <v>1036800</v>
+        <v>1309700</v>
       </c>
       <c r="G120" s="5" t="n">
-        <v>0.44</v>
+        <v>0.59</v>
       </c>
       <c r="H120" t="n">
-        <v>38.12</v>
-      </c>
-      <c r="I120" s="9" t="inlineStr">
+        <v>57.68</v>
+      </c>
+      <c r="I120" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.616</v>
+        <v>0.62</v>
       </c>
       <c r="K120" s="2" t="n">
-        <v>0.635</v>
+        <v>0.529</v>
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="7" t="inlineStr"/>
@@ -5872,39 +5872,39 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>0277</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>MAHSING</t>
+          <t>CLOUDPT</t>
         </is>
       </c>
       <c r="D121" s="2" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="E121" s="10" t="n">
-        <v>0.0053</v>
+        <v>0.515</v>
+      </c>
+      <c r="E121" s="3" t="n">
+        <v>0.0098</v>
       </c>
       <c r="F121" s="4" t="n">
-        <v>1036700</v>
+        <v>1288100</v>
       </c>
       <c r="G121" s="5" t="n">
-        <v>0.27</v>
+        <v>0.79</v>
       </c>
       <c r="H121" t="n">
-        <v>30.03</v>
+        <v>62.85</v>
       </c>
       <c r="I121" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0.996</v>
+        <v>0.489</v>
       </c>
       <c r="K121" s="2" t="n">
-        <v>1.066</v>
+        <v>0.479</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" s="7" t="inlineStr"/>
@@ -5917,39 +5917,39 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D122" s="2" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="E122" s="10" t="n">
-        <v>0.0103</v>
+        <v>7.23</v>
+      </c>
+      <c r="E122" s="3" t="n">
+        <v>0.0154</v>
       </c>
       <c r="F122" s="4" t="n">
-        <v>1017100</v>
+        <v>1265600</v>
       </c>
       <c r="G122" s="5" t="n">
-        <v>0.14</v>
+        <v>0.16</v>
       </c>
       <c r="H122" t="n">
-        <v>28.72</v>
-      </c>
-      <c r="I122" s="9" t="inlineStr">
+        <v>36.97</v>
+      </c>
+      <c r="I122" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J122" s="2" t="n">
-        <v>0.524</v>
+        <v>7.412</v>
       </c>
       <c r="K122" s="2" t="n">
-        <v>0.571</v>
+        <v>7.724</v>
       </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="7" t="inlineStr"/>
@@ -5962,39 +5962,39 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>6633</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>LHI</t>
         </is>
       </c>
       <c r="D123" s="2" t="n">
-        <v>0.605</v>
+        <v>0.73</v>
       </c>
       <c r="E123" s="10" t="n">
-        <v>0.0168</v>
+        <v>0</v>
       </c>
       <c r="F123" s="4" t="n">
-        <v>990200</v>
+        <v>1265300</v>
       </c>
       <c r="G123" s="5" t="n">
-        <v>0.17</v>
+        <v>0.76</v>
       </c>
       <c r="H123" t="n">
-        <v>70.43000000000001</v>
-      </c>
-      <c r="I123" s="6" t="inlineStr">
+        <v>47.32</v>
+      </c>
+      <c r="I123" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J123" s="2" t="n">
-        <v>0.55</v>
+        <v>0.735</v>
       </c>
       <c r="K123" s="2" t="n">
-        <v>0.493</v>
+        <v>0.749</v>
       </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" s="7" t="inlineStr"/>
@@ -6007,39 +6007,39 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>0271</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>WELLS</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D124" s="2" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="E124" s="10" t="n">
-        <v>0.0291</v>
+        <v>0.825</v>
+      </c>
+      <c r="E124" s="8" t="n">
+        <v>-0.0179</v>
       </c>
       <c r="F124" s="4" t="n">
-        <v>963600</v>
+        <v>1250700</v>
       </c>
       <c r="G124" s="5" t="n">
-        <v>0.87</v>
+        <v>0.19</v>
       </c>
       <c r="H124" t="n">
-        <v>26.64</v>
+        <v>70.67</v>
       </c>
       <c r="I124" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J124" s="2" t="n">
-        <v>0.582</v>
+        <v>0.75</v>
       </c>
       <c r="K124" s="2" t="n">
-        <v>0.622</v>
+        <v>0.663</v>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" s="7" t="inlineStr"/>
@@ -6052,39 +6052,39 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>7233</t>
+          <t>0219</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>DUFU</t>
+          <t>RL</t>
         </is>
       </c>
       <c r="D125" s="2" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="E125" s="3" t="n">
-        <v>-0.009300000000000001</v>
+        <v>0.295</v>
+      </c>
+      <c r="E125" s="8" t="n">
+        <v>-0.0167</v>
       </c>
       <c r="F125" s="4" t="n">
-        <v>929800</v>
+        <v>1216200</v>
       </c>
       <c r="G125" s="5" t="n">
-        <v>0.3</v>
+        <v>0.19</v>
       </c>
       <c r="H125" t="n">
-        <v>62.41</v>
+        <v>40.45</v>
       </c>
       <c r="I125" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J125" s="2" t="n">
-        <v>3.002</v>
+        <v>0.304</v>
       </c>
       <c r="K125" s="2" t="n">
-        <v>2.804</v>
+        <v>0.299</v>
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" s="7" t="inlineStr"/>
@@ -6097,39 +6097,39 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D126" s="2" t="n">
-        <v>7.19</v>
-      </c>
-      <c r="E126" s="10" t="n">
-        <v>0.0098</v>
+        <v>0.64</v>
+      </c>
+      <c r="E126" s="3" t="n">
+        <v>0.007900000000000001</v>
       </c>
       <c r="F126" s="4" t="n">
-        <v>918300</v>
+        <v>1171100</v>
       </c>
       <c r="G126" s="5" t="n">
-        <v>0.12</v>
+        <v>0.3</v>
       </c>
       <c r="H126" t="n">
-        <v>34.49</v>
+        <v>63.45</v>
       </c>
       <c r="I126" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J126" s="2" t="n">
-        <v>7.408</v>
+        <v>0.596</v>
       </c>
       <c r="K126" s="2" t="n">
-        <v>7.724</v>
+        <v>0.582</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="7" t="inlineStr"/>
@@ -6142,39 +6142,39 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>5162</t>
+          <t>7081</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>VSTECS</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D127" s="2" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="E127" s="10" t="n">
-        <v>0.0359</v>
+        <v>0.91</v>
+      </c>
+      <c r="E127" s="8" t="n">
+        <v>-0.0109</v>
       </c>
       <c r="F127" s="4" t="n">
-        <v>916700</v>
+        <v>1165100</v>
       </c>
       <c r="G127" s="5" t="n">
-        <v>0.54</v>
+        <v>0.49</v>
       </c>
       <c r="H127" t="n">
-        <v>57.25</v>
+        <v>20.11</v>
       </c>
       <c r="I127" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J127" s="2" t="n">
-        <v>1.664</v>
+        <v>1.036</v>
       </c>
       <c r="K127" s="2" t="n">
-        <v>1.678</v>
+        <v>1.119</v>
       </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" s="7" t="inlineStr"/>
@@ -6198,19 +6198,19 @@
       <c r="D128" s="2" t="n">
         <v>2.92</v>
       </c>
-      <c r="E128" s="3" t="n">
+      <c r="E128" s="8" t="n">
         <v>-0.0034</v>
       </c>
       <c r="F128" s="4" t="n">
-        <v>871000</v>
+        <v>1120700</v>
       </c>
       <c r="G128" s="5" t="n">
-        <v>0.27</v>
+        <v>0.35</v>
       </c>
       <c r="H128" t="n">
         <v>44.13</v>
       </c>
-      <c r="I128" s="9" t="inlineStr">
+      <c r="I128" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -6232,39 +6232,39 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>7160</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>PENTA</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D129" s="2" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="E129" s="10" t="n">
-        <v>0.0068</v>
+        <v>0.605</v>
+      </c>
+      <c r="E129" s="3" t="n">
+        <v>0.0168</v>
       </c>
       <c r="F129" s="4" t="n">
-        <v>840300</v>
+        <v>1092300</v>
       </c>
       <c r="G129" s="5" t="n">
-        <v>0.25</v>
+        <v>0.19</v>
       </c>
       <c r="H129" t="n">
-        <v>63.09</v>
-      </c>
-      <c r="I129" s="6" t="inlineStr">
+        <v>70.43000000000001</v>
+      </c>
+      <c r="I129" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J129" s="2" t="n">
-        <v>5.478</v>
+        <v>0.55</v>
       </c>
       <c r="K129" s="2" t="n">
-        <v>5.356</v>
+        <v>0.493</v>
       </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" s="7" t="inlineStr"/>
@@ -6277,39 +6277,39 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>ATECH</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D130" s="2" t="n">
-        <v>0.805</v>
-      </c>
-      <c r="E130" s="10" t="n">
-        <v>0.019</v>
+        <v>0.49</v>
+      </c>
+      <c r="E130" s="3" t="n">
+        <v>0.0103</v>
       </c>
       <c r="F130" s="4" t="n">
-        <v>839500</v>
+        <v>1084900</v>
       </c>
       <c r="G130" s="5" t="n">
-        <v>0.46</v>
+        <v>0.15</v>
       </c>
       <c r="H130" t="n">
-        <v>59.79</v>
+        <v>28.72</v>
       </c>
       <c r="I130" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J130" s="2" t="n">
-        <v>0.77</v>
+        <v>0.524</v>
       </c>
       <c r="K130" s="2" t="n">
-        <v>0.761</v>
+        <v>0.571</v>
       </c>
       <c r="L130" t="inlineStr"/>
       <c r="M130" s="7" t="inlineStr"/>
@@ -6322,39 +6322,39 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>5180</t>
+          <t>0450</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>CLMT</t>
+          <t>MFGROUP</t>
         </is>
       </c>
       <c r="D131" s="2" t="n">
-        <v>0.555</v>
-      </c>
-      <c r="E131" s="10" t="n">
-        <v>0.0091</v>
+        <v>0.265</v>
+      </c>
+      <c r="E131" s="8" t="n">
+        <v>-0.0185</v>
       </c>
       <c r="F131" s="4" t="n">
-        <v>820200</v>
+        <v>1082000</v>
       </c>
       <c r="G131" s="5" t="n">
-        <v>0.2</v>
+        <v>1.11</v>
       </c>
       <c r="H131" t="n">
-        <v>35.64</v>
-      </c>
-      <c r="I131" s="9" t="inlineStr">
+        <v>54.17</v>
+      </c>
+      <c r="I131" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J131" s="2" t="n">
-        <v>0.571</v>
+        <v>0.262</v>
       </c>
       <c r="K131" s="2" t="n">
-        <v>0.582</v>
+        <v>0.264</v>
       </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" s="7" t="inlineStr"/>
@@ -6367,39 +6367,39 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>0223</t>
+          <t>5302</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>SAMAIDEN</t>
+          <t>ATECH</t>
         </is>
       </c>
       <c r="D132" s="2" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="E132" s="10" t="n">
-        <v>0.0166</v>
+        <v>0.8</v>
+      </c>
+      <c r="E132" s="3" t="n">
+        <v>0.0127</v>
       </c>
       <c r="F132" s="4" t="n">
-        <v>758300</v>
+        <v>1080000</v>
       </c>
       <c r="G132" s="5" t="n">
-        <v>0.18</v>
+        <v>0.59</v>
       </c>
       <c r="H132" t="n">
-        <v>69.63</v>
-      </c>
-      <c r="I132" s="6" t="inlineStr">
+        <v>58.78</v>
+      </c>
+      <c r="I132" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J132" s="2" t="n">
-        <v>2.694</v>
+        <v>0.77</v>
       </c>
       <c r="K132" s="2" t="n">
-        <v>2.043</v>
+        <v>0.761</v>
       </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" s="7" t="inlineStr"/>
@@ -6412,39 +6412,39 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>7160</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>KPJ</t>
+          <t>PENTA</t>
         </is>
       </c>
       <c r="D133" s="2" t="n">
-        <v>2.51</v>
+        <v>5.89</v>
       </c>
       <c r="E133" s="3" t="n">
-        <v>-0.004</v>
+        <v>0.0051</v>
       </c>
       <c r="F133" s="4" t="n">
-        <v>741700</v>
+        <v>1052500</v>
       </c>
       <c r="G133" s="5" t="n">
-        <v>0.14</v>
+        <v>0.31</v>
       </c>
       <c r="H133" t="n">
-        <v>35.17</v>
+        <v>62.9</v>
       </c>
       <c r="I133" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J133" s="2" t="n">
-        <v>2.613</v>
+        <v>5.477</v>
       </c>
       <c r="K133" s="2" t="n">
-        <v>2.79</v>
+        <v>5.356</v>
       </c>
       <c r="L133" t="inlineStr"/>
       <c r="M133" s="7" t="inlineStr"/>
@@ -6457,39 +6457,39 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>MAHSING</t>
         </is>
       </c>
       <c r="D134" s="2" t="n">
-        <v>0.735</v>
-      </c>
-      <c r="E134" s="10" t="n">
-        <v>0.0068</v>
+        <v>0.95</v>
+      </c>
+      <c r="E134" s="3" t="n">
+        <v>0.0053</v>
       </c>
       <c r="F134" s="4" t="n">
-        <v>736400</v>
+        <v>1047600</v>
       </c>
       <c r="G134" s="5" t="n">
-        <v>0.23</v>
+        <v>0.27</v>
       </c>
       <c r="H134" t="n">
-        <v>44.96</v>
-      </c>
-      <c r="I134" s="9" t="inlineStr">
+        <v>30.03</v>
+      </c>
+      <c r="I134" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J134" s="2" t="n">
-        <v>0.76</v>
+        <v>0.996</v>
       </c>
       <c r="K134" s="2" t="n">
-        <v>0.747</v>
+        <v>1.066</v>
       </c>
       <c r="L134" t="inlineStr"/>
       <c r="M134" s="7" t="inlineStr"/>
@@ -6502,39 +6502,39 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>5053</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>OSK</t>
         </is>
       </c>
       <c r="D135" s="2" t="n">
-        <v>1.36</v>
+        <v>1.66</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>-0.0073</v>
+        <v>0.0311</v>
       </c>
       <c r="F135" s="4" t="n">
-        <v>710900</v>
+        <v>1030000</v>
       </c>
       <c r="G135" s="5" t="n">
-        <v>0.22</v>
+        <v>0.72</v>
       </c>
       <c r="H135" t="n">
-        <v>70.59999999999999</v>
-      </c>
-      <c r="I135" s="9" t="inlineStr">
+        <v>29.21</v>
+      </c>
+      <c r="I135" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J135" s="2" t="n">
-        <v>1.236</v>
+        <v>1.786</v>
       </c>
       <c r="K135" s="2" t="n">
-        <v>1.008</v>
+        <v>1.919</v>
       </c>
       <c r="L135" t="inlineStr"/>
       <c r="M135" s="7" t="inlineStr"/>
@@ -6547,39 +6547,39 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>DUFU</t>
         </is>
       </c>
       <c r="D136" s="2" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="E136" s="3" t="n">
-        <v>-0.0103</v>
+        <v>3.19</v>
+      </c>
+      <c r="E136" s="8" t="n">
+        <v>-0.0154</v>
       </c>
       <c r="F136" s="4" t="n">
-        <v>700800</v>
+        <v>1002300</v>
       </c>
       <c r="G136" s="5" t="n">
-        <v>0.15</v>
+        <v>0.32</v>
       </c>
       <c r="H136" t="n">
-        <v>47.26</v>
+        <v>61.36</v>
       </c>
       <c r="I136" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J136" s="2" t="n">
-        <v>2.967</v>
+        <v>3</v>
       </c>
       <c r="K136" s="2" t="n">
-        <v>2.819</v>
+        <v>2.804</v>
       </c>
       <c r="L136" t="inlineStr"/>
       <c r="M136" s="7" t="inlineStr"/>
@@ -6592,39 +6592,39 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>5162</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>VSTECS</t>
         </is>
       </c>
       <c r="D137" s="2" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="E137" s="10" t="n">
-        <v>0.0132</v>
+        <v>1.73</v>
+      </c>
+      <c r="E137" s="3" t="n">
+        <v>0.0359</v>
       </c>
       <c r="F137" s="4" t="n">
-        <v>690700</v>
+        <v>999300</v>
       </c>
       <c r="G137" s="5" t="n">
-        <v>0.37</v>
+        <v>0.59</v>
       </c>
       <c r="H137" t="n">
-        <v>62.99</v>
-      </c>
-      <c r="I137" s="6" t="inlineStr">
+        <v>57.25</v>
+      </c>
+      <c r="I137" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J137" s="2" t="n">
-        <v>0.712</v>
+        <v>1.664</v>
       </c>
       <c r="K137" s="2" t="n">
-        <v>0.6909999999999999</v>
+        <v>1.678</v>
       </c>
       <c r="L137" t="inlineStr"/>
       <c r="M137" s="7" t="inlineStr"/>
@@ -6637,39 +6637,39 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>5323</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>JPG</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D138" s="2" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="E138" s="10" t="n">
-        <v>0.023</v>
+        <v>2.9</v>
+      </c>
+      <c r="E138" s="8" t="n">
+        <v>-0.0068</v>
       </c>
       <c r="F138" s="4" t="n">
-        <v>678200</v>
+        <v>990200</v>
       </c>
       <c r="G138" s="5" t="n">
-        <v>0.11</v>
+        <v>0.21</v>
       </c>
       <c r="H138" t="n">
-        <v>41.73</v>
-      </c>
-      <c r="I138" s="9" t="inlineStr">
+        <v>47.73</v>
+      </c>
+      <c r="I138" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J138" s="2" t="n">
-        <v>1.825</v>
+        <v>2.968</v>
       </c>
       <c r="K138" s="2" t="n">
-        <v>1.927</v>
+        <v>2.819</v>
       </c>
       <c r="L138" t="inlineStr"/>
       <c r="M138" s="7" t="inlineStr"/>
@@ -6682,39 +6682,39 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>5053</t>
+          <t>0271</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>OSK</t>
+          <t>WELLS</t>
         </is>
       </c>
       <c r="D139" s="2" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="E139" s="10" t="n">
-        <v>0.0124</v>
+        <v>0.53</v>
+      </c>
+      <c r="E139" s="3" t="n">
+        <v>0.0291</v>
       </c>
       <c r="F139" s="4" t="n">
-        <v>677900</v>
+        <v>963600</v>
       </c>
       <c r="G139" s="5" t="n">
-        <v>0.47</v>
+        <v>0.87</v>
       </c>
       <c r="H139" t="n">
-        <v>23.55</v>
-      </c>
-      <c r="I139" s="9" t="inlineStr">
+        <v>26.64</v>
+      </c>
+      <c r="I139" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J139" s="2" t="n">
-        <v>1.784</v>
+        <v>0.582</v>
       </c>
       <c r="K139" s="2" t="n">
-        <v>1.918</v>
+        <v>0.622</v>
       </c>
       <c r="L139" t="inlineStr"/>
       <c r="M139" s="7" t="inlineStr"/>
@@ -6736,30 +6736,30 @@
         </is>
       </c>
       <c r="D140" s="2" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="E140" s="10" t="n">
-        <v>0.0035</v>
+        <v>2.82</v>
+      </c>
+      <c r="E140" s="8" t="n">
+        <v>-0.0035</v>
       </c>
       <c r="F140" s="4" t="n">
-        <v>639700</v>
+        <v>915000</v>
       </c>
       <c r="G140" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="H140" t="n">
-        <v>56.65</v>
-      </c>
-      <c r="I140" s="6" t="inlineStr">
+        <v>55.48</v>
+      </c>
+      <c r="I140" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J140" s="2" t="n">
-        <v>2.776</v>
+        <v>2.774</v>
       </c>
       <c r="K140" s="2" t="n">
-        <v>2.6</v>
+        <v>2.599</v>
       </c>
       <c r="L140" t="inlineStr"/>
       <c r="M140" s="7" t="inlineStr"/>
@@ -6772,39 +6772,39 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>4863</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>TM</t>
         </is>
       </c>
       <c r="D141" s="2" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="E141" s="3" t="n">
-        <v>-0.0225</v>
+        <v>7.86</v>
+      </c>
+      <c r="E141" s="8" t="n">
+        <v>-0.0013</v>
       </c>
       <c r="F141" s="4" t="n">
-        <v>635600</v>
+        <v>902700</v>
       </c>
       <c r="G141" s="5" t="n">
-        <v>0.12</v>
+        <v>0.3</v>
       </c>
       <c r="H141" t="n">
-        <v>49.02</v>
+        <v>48.99</v>
       </c>
       <c r="I141" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J141" s="2" t="n">
-        <v>2.188</v>
+        <v>7.889</v>
       </c>
       <c r="K141" s="2" t="n">
-        <v>2.127</v>
+        <v>7.849</v>
       </c>
       <c r="L141" t="inlineStr"/>
       <c r="M141" s="7" t="inlineStr"/>
@@ -6817,39 +6817,39 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>5212</t>
+          <t>5180</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>PAVREIT</t>
+          <t>CLMT</t>
         </is>
       </c>
       <c r="D142" s="2" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="E142" s="10" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.555</v>
+      </c>
+      <c r="E142" s="3" t="n">
+        <v>0.0091</v>
       </c>
       <c r="F142" s="4" t="n">
-        <v>624100</v>
+        <v>868600</v>
       </c>
       <c r="G142" s="5" t="n">
-        <v>0.15</v>
+        <v>0.21</v>
       </c>
       <c r="H142" t="n">
-        <v>45.12</v>
-      </c>
-      <c r="I142" s="9" t="inlineStr">
+        <v>35.64</v>
+      </c>
+      <c r="I142" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J142" s="2" t="n">
-        <v>1.562</v>
+        <v>0.571</v>
       </c>
       <c r="K142" s="2" t="n">
-        <v>1.62</v>
+        <v>0.582</v>
       </c>
       <c r="L142" t="inlineStr"/>
       <c r="M142" s="7" t="inlineStr"/>
@@ -6862,39 +6862,39 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>0223</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>SAMAIDEN</t>
         </is>
       </c>
       <c r="D143" s="2" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="E143" s="10" t="n">
-        <v>0.006</v>
+        <v>3.05</v>
+      </c>
+      <c r="E143" s="3" t="n">
+        <v>0.0133</v>
       </c>
       <c r="F143" s="4" t="n">
-        <v>620500</v>
+        <v>857300</v>
       </c>
       <c r="G143" s="5" t="n">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="H143" t="n">
-        <v>59.49</v>
+        <v>69.42</v>
       </c>
       <c r="I143" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J143" s="2" t="n">
-        <v>0.82</v>
+        <v>2.693</v>
       </c>
       <c r="K143" s="2" t="n">
-        <v>0.756</v>
+        <v>2.043</v>
       </c>
       <c r="L143" t="inlineStr"/>
       <c r="M143" s="7" t="inlineStr"/>
@@ -6907,39 +6907,39 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>SEG</t>
+          <t>MBSB</t>
         </is>
       </c>
       <c r="D144" s="2" t="n">
-        <v>0.625</v>
+        <v>0.535</v>
       </c>
       <c r="E144" s="3" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.009399999999999999</v>
       </c>
       <c r="F144" s="4" t="n">
-        <v>615100</v>
+        <v>854500</v>
       </c>
       <c r="G144" s="5" t="n">
-        <v>0.49</v>
+        <v>0.24</v>
       </c>
       <c r="H144" t="n">
-        <v>37.72</v>
-      </c>
-      <c r="I144" s="9" t="inlineStr">
+        <v>35.78</v>
+      </c>
+      <c r="I144" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J144" s="2" t="n">
-        <v>0.632</v>
+        <v>0.552</v>
       </c>
       <c r="K144" s="2" t="n">
-        <v>0.63</v>
+        <v>0.582</v>
       </c>
       <c r="L144" t="inlineStr"/>
       <c r="M144" s="7" t="inlineStr"/>
@@ -6952,39 +6952,39 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>0217</t>
+          <t>5878</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>PWRWELL</t>
+          <t>KPJ</t>
         </is>
       </c>
       <c r="D145" s="2" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="E145" s="10" t="n">
-        <v>0.008500000000000001</v>
+        <v>2.53</v>
+      </c>
+      <c r="E145" s="3" t="n">
+        <v>0.004</v>
       </c>
       <c r="F145" s="4" t="n">
-        <v>594500</v>
+        <v>839500</v>
       </c>
       <c r="G145" s="5" t="n">
-        <v>0.14</v>
+        <v>0.16</v>
       </c>
       <c r="H145" t="n">
-        <v>59.85</v>
-      </c>
-      <c r="I145" s="9" t="inlineStr">
+        <v>37.16</v>
+      </c>
+      <c r="I145" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J145" s="2" t="n">
-        <v>1.153</v>
+        <v>2.615</v>
       </c>
       <c r="K145" s="2" t="n">
-        <v>1.066</v>
+        <v>2.79</v>
       </c>
       <c r="L145" t="inlineStr"/>
       <c r="M145" s="7" t="inlineStr"/>
@@ -6997,39 +6997,39 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D146" s="2" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E146" s="3" t="n">
-        <v>-0.007800000000000001</v>
+        <v>1.37</v>
+      </c>
+      <c r="E146" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F146" s="4" t="n">
-        <v>593400</v>
+        <v>833300</v>
       </c>
       <c r="G146" s="5" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="H146" t="n">
-        <v>51.42</v>
-      </c>
-      <c r="I146" s="9" t="inlineStr">
+        <v>72.14</v>
+      </c>
+      <c r="I146" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J146" s="2" t="n">
-        <v>0.638</v>
+        <v>1.237</v>
       </c>
       <c r="K146" s="2" t="n">
-        <v>0.611</v>
+        <v>1.008</v>
       </c>
       <c r="L146" t="inlineStr"/>
       <c r="M146" s="7" t="inlineStr"/>
@@ -7042,39 +7042,39 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>5331</t>
+          <t>0167</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>PGLOBAL</t>
+          <t>MCLEAN</t>
         </is>
       </c>
       <c r="D147" s="2" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="E147" s="10" t="n">
-        <v>0.0179</v>
+        <v>0.735</v>
+      </c>
+      <c r="E147" s="3" t="n">
+        <v>0.0068</v>
       </c>
       <c r="F147" s="4" t="n">
-        <v>590700</v>
+        <v>832400</v>
       </c>
       <c r="G147" s="5" t="n">
-        <v>1.27</v>
+        <v>0.26</v>
       </c>
       <c r="H147" t="n">
-        <v>68.42</v>
+        <v>44.96</v>
       </c>
       <c r="I147" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J147" s="2" t="n">
-        <v>0.539</v>
+        <v>0.76</v>
       </c>
       <c r="K147" s="2" t="n">
-        <v>0.511</v>
+        <v>0.747</v>
       </c>
       <c r="L147" t="inlineStr"/>
       <c r="M147" s="7" t="inlineStr"/>
@@ -7087,39 +7087,39 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>6947</t>
+          <t>0146</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>CDB</t>
+          <t>JFTECH</t>
         </is>
       </c>
       <c r="D148" s="2" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="E148" s="10" t="n">
-        <v>0.0162</v>
+        <v>0.765</v>
+      </c>
+      <c r="E148" s="3" t="n">
+        <v>0.0066</v>
       </c>
       <c r="F148" s="4" t="n">
-        <v>568800</v>
+        <v>826400</v>
       </c>
       <c r="G148" s="5" t="n">
-        <v>0.18</v>
+        <v>0.45</v>
       </c>
       <c r="H148" t="n">
-        <v>35.71</v>
+        <v>62.31</v>
       </c>
       <c r="I148" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J148" s="2" t="n">
-        <v>2.582</v>
+        <v>0.711</v>
       </c>
       <c r="K148" s="2" t="n">
-        <v>2.731</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="L148" t="inlineStr"/>
       <c r="M148" s="7" t="inlineStr"/>
@@ -7132,39 +7132,39 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>0240</t>
+          <t>5323</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>CORAZA</t>
+          <t>JPG</t>
         </is>
       </c>
       <c r="D149" s="2" t="n">
-        <v>1.39</v>
+        <v>1.78</v>
       </c>
       <c r="E149" s="3" t="n">
-        <v>-0.0211</v>
+        <v>0.023</v>
       </c>
       <c r="F149" s="4" t="n">
-        <v>567700</v>
+        <v>800600</v>
       </c>
       <c r="G149" s="5" t="n">
-        <v>0.21</v>
+        <v>0.13</v>
       </c>
       <c r="H149" t="n">
-        <v>72.58</v>
+        <v>41.73</v>
       </c>
       <c r="I149" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J149" s="2" t="n">
-        <v>1.22</v>
+        <v>1.825</v>
       </c>
       <c r="K149" s="2" t="n">
-        <v>1.151</v>
+        <v>1.927</v>
       </c>
       <c r="L149" t="inlineStr"/>
       <c r="M149" s="7" t="inlineStr"/>
@@ -7177,39 +7177,39 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>0217</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>MBSB</t>
+          <t>PWRWELL</t>
         </is>
       </c>
       <c r="D150" s="2" t="n">
-        <v>0.535</v>
-      </c>
-      <c r="E150" s="10" t="n">
-        <v>0.009399999999999999</v>
+        <v>1.18</v>
+      </c>
+      <c r="E150" s="3" t="n">
+        <v>0.008500000000000001</v>
       </c>
       <c r="F150" s="4" t="n">
-        <v>563100</v>
+        <v>797300</v>
       </c>
       <c r="G150" s="5" t="n">
-        <v>0.16</v>
+        <v>0.19</v>
       </c>
       <c r="H150" t="n">
-        <v>35.78</v>
-      </c>
-      <c r="I150" s="9" t="inlineStr">
+        <v>59.85</v>
+      </c>
+      <c r="I150" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J150" s="2" t="n">
-        <v>0.552</v>
+        <v>1.153</v>
       </c>
       <c r="K150" s="2" t="n">
-        <v>0.582</v>
+        <v>1.066</v>
       </c>
       <c r="L150" t="inlineStr"/>
       <c r="M150" s="7" t="inlineStr"/>
@@ -7222,39 +7222,39 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>0391</t>
+          <t>5212</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>AMBEST</t>
+          <t>PAVREIT</t>
         </is>
       </c>
       <c r="D151" s="2" t="n">
-        <v>1.32</v>
+        <v>1.55</v>
       </c>
       <c r="E151" s="3" t="n">
-        <v>-0.0149</v>
+        <v>0.006500000000000001</v>
       </c>
       <c r="F151" s="4" t="n">
-        <v>537700</v>
+        <v>783600</v>
       </c>
       <c r="G151" s="5" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="H151" t="n">
-        <v>48.88</v>
-      </c>
-      <c r="I151" s="9" t="inlineStr">
+        <v>45.12</v>
+      </c>
+      <c r="I151" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J151" s="2" t="n">
-        <v>1.348</v>
+        <v>1.562</v>
       </c>
       <c r="K151" s="2" t="n">
-        <v>1.235</v>
+        <v>1.62</v>
       </c>
       <c r="L151" t="inlineStr"/>
       <c r="M151" s="7" t="inlineStr"/>
@@ -7267,45 +7267,1035 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>7293</t>
+          <t>0388</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>YINSON</t>
+          <t>SEMICO</t>
         </is>
       </c>
       <c r="D152" s="2" t="n">
-        <v>2.14</v>
+        <v>0.615</v>
       </c>
       <c r="E152" s="10" t="n">
-        <v>0.0142</v>
+        <v>0</v>
       </c>
       <c r="F152" s="4" t="n">
-        <v>516800</v>
+        <v>783100</v>
       </c>
       <c r="G152" s="5" t="n">
-        <v>0.21</v>
+        <v>0.27</v>
       </c>
       <c r="H152" t="n">
-        <v>56.49</v>
-      </c>
-      <c r="I152" s="6" t="inlineStr">
+        <v>59.01</v>
+      </c>
+      <c r="I152" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J152" s="2" t="n">
-        <v>2.091</v>
+        <v>0.612</v>
       </c>
       <c r="K152" s="2" t="n">
-        <v>2.037</v>
+        <v>0.598</v>
       </c>
       <c r="L152" t="inlineStr"/>
       <c r="M152" s="7" t="inlineStr"/>
     </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>9792</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>SEG</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="E153" s="8" t="n">
+        <v>-0.007900000000000001</v>
+      </c>
+      <c r="F153" s="4" t="n">
+        <v>725100</v>
+      </c>
+      <c r="G153" s="5" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="H153" t="n">
+        <v>37.72</v>
+      </c>
+      <c r="I153" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J153" s="2" t="n">
+        <v>0.632</v>
+      </c>
+      <c r="K153" s="2" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="L153" t="inlineStr"/>
+      <c r="M153" s="7" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>5331</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>PGLOBAL</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="E154" s="3" t="n">
+        <v>0.0268</v>
+      </c>
+      <c r="F154" s="4" t="n">
+        <v>706700</v>
+      </c>
+      <c r="G154" s="5" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="H154" t="n">
+        <v>69.77</v>
+      </c>
+      <c r="I154" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J154" s="2" t="n">
+        <v>0.539</v>
+      </c>
+      <c r="K154" s="2" t="n">
+        <v>0.511</v>
+      </c>
+      <c r="L154" t="inlineStr"/>
+      <c r="M154" s="7" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>8907</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="E155" s="3" t="n">
+        <v>0.005699999999999999</v>
+      </c>
+      <c r="F155" s="4" t="n">
+        <v>695900</v>
+      </c>
+      <c r="G155" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H155" t="n">
+        <v>50.39</v>
+      </c>
+      <c r="I155" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J155" s="2" t="n">
+        <v>1.752</v>
+      </c>
+      <c r="K155" s="2" t="n">
+        <v>1.778</v>
+      </c>
+      <c r="L155" t="inlineStr"/>
+      <c r="M155" s="7" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>1015</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>AMBANK</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="n">
+        <v>6.09</v>
+      </c>
+      <c r="E156" s="8" t="n">
+        <v>-0.0016</v>
+      </c>
+      <c r="F156" s="4" t="n">
+        <v>692300</v>
+      </c>
+      <c r="G156" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H156" t="n">
+        <v>22.87</v>
+      </c>
+      <c r="I156" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J156" s="2" t="n">
+        <v>6.473</v>
+      </c>
+      <c r="K156" s="2" t="n">
+        <v>6.826</v>
+      </c>
+      <c r="L156" t="inlineStr"/>
+      <c r="M156" s="7" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>0340</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>NORTHERN</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="E157" s="3" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="F157" s="4" t="n">
+        <v>676100</v>
+      </c>
+      <c r="G157" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H157" t="n">
+        <v>67.31999999999999</v>
+      </c>
+      <c r="I157" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J157" s="2" t="n">
+        <v>1.081</v>
+      </c>
+      <c r="K157" s="2" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" s="7" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>7277</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>DIALOG</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="E158" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F158" s="4" t="n">
+        <v>665600</v>
+      </c>
+      <c r="G158" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H158" t="n">
+        <v>43.39</v>
+      </c>
+      <c r="I158" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J158" s="2" t="n">
+        <v>1.927</v>
+      </c>
+      <c r="K158" s="2" t="n">
+        <v>1.957</v>
+      </c>
+      <c r="L158" t="inlineStr"/>
+      <c r="M158" s="7" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>5199</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>HIBISCS</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="E159" s="8" t="n">
+        <v>-0.0225</v>
+      </c>
+      <c r="F159" s="4" t="n">
+        <v>644900</v>
+      </c>
+      <c r="G159" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H159" t="n">
+        <v>49.02</v>
+      </c>
+      <c r="I159" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J159" s="2" t="n">
+        <v>2.188</v>
+      </c>
+      <c r="K159" s="2" t="n">
+        <v>2.127</v>
+      </c>
+      <c r="L159" t="inlineStr"/>
+      <c r="M159" s="7" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>5211</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>SUNWAY</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="E160" s="3" t="n">
+        <v>0.009300000000000001</v>
+      </c>
+      <c r="F160" s="4" t="n">
+        <v>640800</v>
+      </c>
+      <c r="G160" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H160" t="n">
+        <v>33.97</v>
+      </c>
+      <c r="I160" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J160" s="2" t="n">
+        <v>4.481</v>
+      </c>
+      <c r="K160" s="2" t="n">
+        <v>4.817</v>
+      </c>
+      <c r="L160" t="inlineStr"/>
+      <c r="M160" s="7" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>0391</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>AMBEST</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="E161" s="8" t="n">
+        <v>-0.0149</v>
+      </c>
+      <c r="F161" s="4" t="n">
+        <v>633900</v>
+      </c>
+      <c r="G161" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H161" t="n">
+        <v>48.88</v>
+      </c>
+      <c r="I161" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J161" s="2" t="n">
+        <v>1.348</v>
+      </c>
+      <c r="K161" s="2" t="n">
+        <v>1.235</v>
+      </c>
+      <c r="L161" t="inlineStr"/>
+      <c r="M161" s="7" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>0390</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>ISF</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="E162" s="3" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="F162" s="4" t="n">
+        <v>622200</v>
+      </c>
+      <c r="G162" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H162" t="n">
+        <v>59.49</v>
+      </c>
+      <c r="I162" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J162" s="2" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="K162" s="2" t="n">
+        <v>0.756</v>
+      </c>
+      <c r="L162" t="inlineStr"/>
+      <c r="M162" s="7" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>0097</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>VITROX</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="n">
+        <v>11.08</v>
+      </c>
+      <c r="E163" s="3" t="n">
+        <v>0.0073</v>
+      </c>
+      <c r="F163" s="4" t="n">
+        <v>619700</v>
+      </c>
+      <c r="G163" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H163" t="n">
+        <v>74.28</v>
+      </c>
+      <c r="I163" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J163" s="2" t="n">
+        <v>10.242</v>
+      </c>
+      <c r="K163" s="2" t="n">
+        <v>9.504</v>
+      </c>
+      <c r="L163" t="inlineStr"/>
+      <c r="M163" s="7" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>5236</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>MATRIX</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="E164" s="3" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="F164" s="4" t="n">
+        <v>615200</v>
+      </c>
+      <c r="G164" s="5" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="H164" t="n">
+        <v>38.66</v>
+      </c>
+      <c r="I164" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J164" s="2" t="n">
+        <v>1.102</v>
+      </c>
+      <c r="K164" s="2" t="n">
+        <v>1.147</v>
+      </c>
+      <c r="L164" t="inlineStr"/>
+      <c r="M164" s="7" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>0112</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>MIKROMB</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="E165" s="8" t="n">
+        <v>-0.007800000000000001</v>
+      </c>
+      <c r="F165" s="4" t="n">
+        <v>608300</v>
+      </c>
+      <c r="G165" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H165" t="n">
+        <v>51.42</v>
+      </c>
+      <c r="I165" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J165" s="2" t="n">
+        <v>0.638</v>
+      </c>
+      <c r="K165" s="2" t="n">
+        <v>0.611</v>
+      </c>
+      <c r="L165" t="inlineStr"/>
+      <c r="M165" s="7" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>0240</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>CORAZA</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="E166" s="8" t="n">
+        <v>-0.0141</v>
+      </c>
+      <c r="F166" s="4" t="n">
+        <v>598200</v>
+      </c>
+      <c r="G166" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H166" t="n">
+        <v>74.17</v>
+      </c>
+      <c r="I166" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J166" s="2" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="K166" s="2" t="n">
+        <v>1.151</v>
+      </c>
+      <c r="L166" t="inlineStr"/>
+      <c r="M166" s="7" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>5292</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>UWC</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="n">
+        <v>7.94</v>
+      </c>
+      <c r="E167" s="8" t="n">
+        <v>-0.0063</v>
+      </c>
+      <c r="F167" s="4" t="n">
+        <v>573500</v>
+      </c>
+      <c r="G167" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H167" t="n">
+        <v>71.79000000000001</v>
+      </c>
+      <c r="I167" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J167" s="2" t="n">
+        <v>7.242</v>
+      </c>
+      <c r="K167" s="2" t="n">
+        <v>6.753</v>
+      </c>
+      <c r="L167" t="inlineStr"/>
+      <c r="M167" s="7" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>7293</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>YINSON</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="E168" s="3" t="n">
+        <v>0.0095</v>
+      </c>
+      <c r="F168" s="4" t="n">
+        <v>566400</v>
+      </c>
+      <c r="G168" s="5" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H168" t="n">
+        <v>55.63</v>
+      </c>
+      <c r="I168" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J168" s="2" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="K168" s="2" t="n">
+        <v>2.037</v>
+      </c>
+      <c r="L168" t="inlineStr"/>
+      <c r="M168" s="7" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>5271</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>PECCA</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="E169" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F169" s="4" t="n">
+        <v>541500</v>
+      </c>
+      <c r="G169" s="5" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H169" t="n">
+        <v>53.49</v>
+      </c>
+      <c r="I169" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J169" s="2" t="n">
+        <v>1.369</v>
+      </c>
+      <c r="K169" s="2" t="n">
+        <v>1.337</v>
+      </c>
+      <c r="L169" t="inlineStr"/>
+      <c r="M169" s="7" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>4715</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>GENM</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="E170" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F170" s="4" t="n">
+        <v>528700</v>
+      </c>
+      <c r="G170" s="5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H170" t="n">
+        <v>31.71</v>
+      </c>
+      <c r="I170" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J170" s="2" t="n">
+        <v>1.506</v>
+      </c>
+      <c r="K170" s="2" t="n">
+        <v>1.621</v>
+      </c>
+      <c r="L170" t="inlineStr"/>
+      <c r="M170" s="7" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>5176</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>SUNREIT</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="E171" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F171" s="4" t="n">
+        <v>526600</v>
+      </c>
+      <c r="G171" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H171" t="n">
+        <v>49.54</v>
+      </c>
+      <c r="I171" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J171" s="2" t="n">
+        <v>2.056</v>
+      </c>
+      <c r="K171" s="2" t="n">
+        <v>2.085</v>
+      </c>
+      <c r="L171" t="inlineStr"/>
+      <c r="M171" s="7" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>7195</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>BNASTRA</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="E172" s="3" t="n">
+        <v>0.0114</v>
+      </c>
+      <c r="F172" s="4" t="n">
+        <v>520500</v>
+      </c>
+      <c r="G172" s="5" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="H172" t="n">
+        <v>84.62</v>
+      </c>
+      <c r="I172" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J172" s="2" t="n">
+        <v>2.477</v>
+      </c>
+      <c r="K172" s="2" t="n">
+        <v>2.347</v>
+      </c>
+      <c r="L172" t="inlineStr"/>
+      <c r="M172" s="7" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>0466</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>SRKKAI</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="n">
+        <v>0.515</v>
+      </c>
+      <c r="E173" s="8" t="n">
+        <v>-0.009599999999999999</v>
+      </c>
+      <c r="F173" s="4" t="n">
+        <v>512500</v>
+      </c>
+      <c r="G173" s="5" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H173" t="n">
+        <v>45.34</v>
+      </c>
+      <c r="I173" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J173" s="2" t="n">
+        <v>0.524</v>
+      </c>
+      <c r="K173" s="2" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="L173" t="inlineStr"/>
+      <c r="M173" s="7" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>5227</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>IGBREIT</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="E174" s="8" t="n">
+        <v>-0.0037</v>
+      </c>
+      <c r="F174" s="4" t="n">
+        <v>501900</v>
+      </c>
+      <c r="G174" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H174" t="n">
+        <v>41.62</v>
+      </c>
+      <c r="I174" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J174" s="2" t="n">
+        <v>2.765</v>
+      </c>
+      <c r="K174" s="2" t="n">
+        <v>2.762</v>
+      </c>
+      <c r="L174" t="inlineStr"/>
+      <c r="M174" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M152"/>
+  <autoFilter ref="A1:M174"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-09/bursa-report-2026-10-09.xlsx
+++ b/docs/downloads/2026-10-09/bursa-report-2026-10-09.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-09" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-09'!$A$1:$M$174</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-09'!$A$1:$M$190</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M174"/>
+  <dimension ref="A1:M190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -552,19 +552,19 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0.1333</v>
+        <v>0.0667</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>115736500</v>
+        <v>119161200</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="H2" t="n">
-        <v>23.54</v>
+        <v>22.11</v>
       </c>
       <c r="I2" s="6" t="inlineStr">
         <is>
@@ -597,19 +597,19 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.52</v>
+        <v>0.515</v>
       </c>
       <c r="E3" s="8" t="n">
-        <v>-0.0095</v>
+        <v>-0.019</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>80394800</v>
+        <v>80856500</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="H3" t="n">
-        <v>62.99</v>
+        <v>60.83</v>
       </c>
       <c r="I3" s="9" t="inlineStr">
         <is>
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.491</v>
+        <v>0.49</v>
       </c>
       <c r="K3" s="2" t="n">
         <v>0.479</v>
@@ -648,10 +648,10 @@
         <v>0</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>39809700</v>
+        <v>40309700</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>106.59</v>
+        <v>107.93</v>
       </c>
       <c r="H4" t="n">
         <v>43</v>
@@ -678,28 +678,28 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="E5" s="8" t="n">
-        <v>-0.04</v>
+        <v>0.34</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>0.0303</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>35033300</v>
+        <v>38525000</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.45</v>
+        <v>0.66</v>
       </c>
       <c r="H5" t="n">
-        <v>62.57</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="I5" s="9" t="inlineStr">
         <is>
@@ -707,10 +707,10 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.782</v>
+        <v>0.278</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.71</v>
+        <v>0.245</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" s="7" t="inlineStr"/>
@@ -723,28 +723,28 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.345</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>0.0455</v>
+        <v>0.84</v>
+      </c>
+      <c r="E6" s="8" t="n">
+        <v>-0.04</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>33754500</v>
+        <v>37916000</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.58</v>
+        <v>0.49</v>
       </c>
       <c r="H6" t="n">
-        <v>78.38</v>
+        <v>62.57</v>
       </c>
       <c r="I6" s="9" t="inlineStr">
         <is>
@@ -752,10 +752,10 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.279</v>
+        <v>0.782</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.245</v>
+        <v>0.71</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" s="7" t="inlineStr"/>
@@ -768,39 +768,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>2.02</v>
+        <v>0.195</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.0306</v>
+        <v>0.0263</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>27513700</v>
+        <v>28446100</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="H7" t="n">
-        <v>71.94</v>
-      </c>
-      <c r="I7" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>51.06</v>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>1.812</v>
+        <v>0.196</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>1.636</v>
+        <v>0.183</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" s="7" t="inlineStr"/>
@@ -813,39 +813,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.195</v>
+        <v>2.03</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>0.0263</v>
+        <v>0.0357</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>25404600</v>
+        <v>28297600</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="H8" t="n">
-        <v>51.06</v>
-      </c>
-      <c r="I8" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>72.39</v>
+      </c>
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.196</v>
+        <v>1.813</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.183</v>
+        <v>1.637</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="7" t="inlineStr"/>
@@ -873,10 +873,10 @@
         <v>0</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>22615500</v>
+        <v>25015500</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.71</v>
+        <v>0.78</v>
       </c>
       <c r="H9" t="n">
         <v>46.07</v>
@@ -918,10 +918,10 @@
         <v>0.0163</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>18173400</v>
+        <v>21861400</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.7</v>
+        <v>0.84</v>
       </c>
       <c r="H10" t="n">
         <v>71.59999999999999</v>
@@ -963,10 +963,10 @@
         <v>-0.027</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>17917200</v>
+        <v>18271500</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="H11" t="n">
         <v>60.1</v>
@@ -993,28 +993,28 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>0278</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>EDELTEQ</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="E12" s="10" t="n">
-        <v>0</v>
+        <v>0.45</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>0.0345</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>17090200</v>
+        <v>17232800</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.41</v>
+        <v>7.51</v>
       </c>
       <c r="H12" t="n">
-        <v>70.36</v>
+        <v>77.01000000000001</v>
       </c>
       <c r="I12" s="9" t="inlineStr">
         <is>
@@ -1022,10 +1022,10 @@
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.358</v>
+        <v>0.357</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0.236</v>
+        <v>0.349</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="7" t="inlineStr"/>
@@ -1038,36 +1038,40 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0471</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>PIONEER</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="E13" s="3" t="n">
-        <v>0.04480000000000001</v>
+        <v>0.39</v>
+      </c>
+      <c r="E13" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>15323200</v>
+        <v>17173000</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>1.63</v>
+        <v>0.41</v>
       </c>
       <c r="H13" t="n">
-        <v>72.73999999999999</v>
+        <v>70.36</v>
       </c>
       <c r="I13" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J13" s="2" t="n"/>
-      <c r="K13" s="2" t="n"/>
+      <c r="J13" s="2" t="n">
+        <v>0.358</v>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>0.236</v>
+      </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="7" t="inlineStr"/>
     </row>
@@ -1088,19 +1092,19 @@
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0.75</v>
+        <v>0.74</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>0.07139999999999999</v>
+        <v>0.0571</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>14339400</v>
+        <v>16608700</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>1.88</v>
+        <v>2.18</v>
       </c>
       <c r="H14" t="n">
-        <v>62.52</v>
+        <v>61.01</v>
       </c>
       <c r="I14" s="9" t="inlineStr">
         <is>
@@ -1108,7 +1112,7 @@
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.694</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>0.678</v>
@@ -1124,40 +1128,36 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0278</t>
+          <t>0471</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>EDELTEQ</t>
+          <t>PIONEER</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0.48</v>
+        <v>0.345</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>0.1034</v>
+        <v>0.0299</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>13905300</v>
+        <v>15535200</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>6.06</v>
+        <v>1.66</v>
       </c>
       <c r="H15" t="n">
-        <v>80.09</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="I15" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J15" s="2" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="K15" s="2" t="n">
-        <v>0.349</v>
-      </c>
+      <c r="J15" s="2" t="n"/>
+      <c r="K15" s="2" t="n"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="7" t="inlineStr"/>
     </row>
@@ -1184,10 +1184,10 @@
         <v>0.0959</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>10118700</v>
+        <v>11200100</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.85</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H16" t="n">
         <v>56.64</v>
@@ -1214,28 +1214,28 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>5195</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CENSOF</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>0.24</v>
+        <v>0.31</v>
       </c>
       <c r="E17" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>9781700</v>
+        <v>10835100</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>7.25</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H17" t="n">
-        <v>68.81</v>
+        <v>57.67</v>
       </c>
       <c r="I17" s="9" t="inlineStr">
         <is>
@@ -1243,10 +1243,10 @@
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.22</v>
+        <v>0.305</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0.206</v>
+        <v>0.295</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="7" t="inlineStr"/>
@@ -1259,39 +1259,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>5195</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MALAKOF</t>
+          <t>CENSOF</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="E18" s="3" t="n">
-        <v>0.0128</v>
+        <v>0.24</v>
+      </c>
+      <c r="E18" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>9500000</v>
+        <v>9781700</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>2.57</v>
+        <v>7.25</v>
       </c>
       <c r="H18" t="n">
-        <v>48.72</v>
-      </c>
-      <c r="I18" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>68.81</v>
+      </c>
+      <c r="I18" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.791</v>
+        <v>0.22</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0.806</v>
+        <v>0.206</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="7" t="inlineStr"/>
@@ -1304,39 +1304,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>MALAKOF</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="E19" s="8" t="n">
-        <v>-0.0112</v>
+        <v>0.795</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>0.0192</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>8544100</v>
+        <v>9544700</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.32</v>
+        <v>2.58</v>
       </c>
       <c r="H19" t="n">
-        <v>62.6</v>
-      </c>
-      <c r="I19" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.06</v>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.41</v>
+        <v>0.792</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0.347</v>
+        <v>0.806</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="7" t="inlineStr"/>
@@ -1349,28 +1349,28 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="E20" s="10" t="n">
-        <v>0</v>
+        <v>0.775</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>0.006500000000000001</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>7960400</v>
+        <v>9197600</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.41</v>
+        <v>0.62</v>
       </c>
       <c r="H20" t="n">
-        <v>57.67</v>
+        <v>50.25</v>
       </c>
       <c r="I20" s="9" t="inlineStr">
         <is>
@@ -1378,10 +1378,10 @@
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.305</v>
+        <v>0.775</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0.295</v>
+        <v>0.775</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="7" t="inlineStr"/>
@@ -1409,10 +1409,10 @@
         <v>0.008100000000000001</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>7684700</v>
+        <v>9128300</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.74</v>
+        <v>0.87</v>
       </c>
       <c r="H21" t="n">
         <v>58.16</v>
@@ -1439,28 +1439,28 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>0.775</v>
+        <v>5.03</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.0162</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>7514800</v>
+        <v>9125800</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.51</v>
+        <v>0.37</v>
       </c>
       <c r="H22" t="n">
-        <v>50.25</v>
+        <v>59.43</v>
       </c>
       <c r="I22" s="9" t="inlineStr">
         <is>
@@ -1468,10 +1468,10 @@
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.775</v>
+        <v>4.92</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0.775</v>
+        <v>4.651</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="7" t="inlineStr"/>
@@ -1484,39 +1484,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0358</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ICTZONE</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="E23" s="3" t="n">
-        <v>0.0667</v>
+        <v>0.435</v>
+      </c>
+      <c r="E23" s="8" t="n">
+        <v>-0.0225</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>7009600</v>
+        <v>8822900</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>2.52</v>
+        <v>0.33</v>
       </c>
       <c r="H23" t="n">
-        <v>48.47</v>
-      </c>
-      <c r="I23" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.91</v>
+      </c>
+      <c r="I23" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.241</v>
+        <v>0.41</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0.249</v>
+        <v>0.346</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="7" t="inlineStr"/>
@@ -1529,39 +1529,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>0.465</v>
-      </c>
-      <c r="E24" s="8" t="n">
-        <v>-0.0211</v>
+        <v>0.345</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>0.0299</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>6942500</v>
+        <v>8044400</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.18</v>
+        <v>1.43</v>
       </c>
       <c r="H24" t="n">
-        <v>25.65</v>
-      </c>
-      <c r="I24" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.12</v>
+      </c>
+      <c r="I24" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.548</v>
+        <v>0.327</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0.749</v>
+        <v>0.339</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="7" t="inlineStr"/>
@@ -1574,40 +1574,36 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>0470</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>BFIELD</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="E25" s="3" t="n">
-        <v>0.0202</v>
+        <v>0.47</v>
+      </c>
+      <c r="E25" s="8" t="n">
+        <v>-0.0208</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>6794100</v>
+        <v>8013100</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.28</v>
+        <v>0.67</v>
       </c>
       <c r="H25" t="n">
-        <v>60.26</v>
+        <v>47.36</v>
       </c>
       <c r="I25" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J25" s="2" t="n">
-        <v>4.922</v>
-      </c>
-      <c r="K25" s="2" t="n">
-        <v>4.652</v>
-      </c>
+      <c r="J25" s="2" t="n"/>
+      <c r="K25" s="2" t="n"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="7" t="inlineStr"/>
     </row>
@@ -1619,39 +1615,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="E26" s="3" t="n">
-        <v>0.0144</v>
+        <v>0.865</v>
+      </c>
+      <c r="E26" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>6506000</v>
+        <v>7834400</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.47</v>
+        <v>0.42</v>
       </c>
       <c r="H26" t="n">
-        <v>54.37</v>
-      </c>
-      <c r="I26" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.68</v>
+      </c>
+      <c r="I26" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>2.792</v>
+        <v>0.868</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>2.693</v>
+        <v>0.869</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="7" t="inlineStr"/>
@@ -1664,33 +1660,40 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0476</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>SLGC Berhad</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>0.245</v>
+        <v>0.46</v>
       </c>
       <c r="E27" s="8" t="n">
-        <v>-0.02</v>
+        <v>-0.0316</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>6492500</v>
+        <v>7687400</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="I27" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="n"/>
-      <c r="K27" s="2" t="n"/>
+        <v>0.2</v>
+      </c>
+      <c r="H27" t="n">
+        <v>25.19</v>
+      </c>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="n">
+        <v>0.548</v>
+      </c>
+      <c r="K27" s="2" t="n">
+        <v>0.749</v>
+      </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="7" t="inlineStr"/>
     </row>
@@ -1702,39 +1705,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AVANGAAD</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="E28" s="8" t="n">
-        <v>-0.0169</v>
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>0.0062</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>6245100</v>
+        <v>7641900</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>2.38</v>
+        <v>0.48</v>
       </c>
       <c r="H28" t="n">
-        <v>32.74</v>
-      </c>
-      <c r="I28" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.76</v>
+      </c>
+      <c r="I28" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.295</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0.296</v>
+        <v>0.806</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="7" t="inlineStr"/>
@@ -1747,28 +1750,28 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>0358</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>ICTZONE</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="E29" s="10" t="n">
-        <v>0</v>
+        <v>0.24</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>0.0667</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>6140200</v>
+        <v>7505600</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.91</v>
+        <v>2.69</v>
       </c>
       <c r="H29" t="n">
-        <v>53.56</v>
+        <v>48.47</v>
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
@@ -1776,10 +1779,10 @@
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.368</v>
+        <v>0.241</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0.368</v>
+        <v>0.249</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="7" t="inlineStr"/>
@@ -1792,39 +1795,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0198</t>
+          <t>0131</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>GDB</t>
+          <t>DFX</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E30" s="8" t="n">
-        <v>-0.0361</v>
+        <v>0.155</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>0.06900000000000001</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>6124500</v>
+        <v>7249400</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>5.43</v>
+        <v>0.91</v>
       </c>
       <c r="H30" t="n">
-        <v>32.62</v>
-      </c>
-      <c r="I30" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>77.22</v>
+      </c>
+      <c r="I30" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.421</v>
+        <v>0.118</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0.441</v>
+        <v>0.094</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="7" t="inlineStr"/>
@@ -1837,28 +1840,28 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="E31" s="8" t="n">
-        <v>-0.0127</v>
+        <v>2.81</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>0.0108</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>6025000</v>
+        <v>7156300</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.52</v>
       </c>
       <c r="H31" t="n">
-        <v>34.12</v>
+        <v>53.6</v>
       </c>
       <c r="I31" s="6" t="inlineStr">
         <is>
@@ -1866,10 +1869,10 @@
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.402</v>
+        <v>2.791</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0.41</v>
+        <v>2.693</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="7" t="inlineStr"/>
@@ -1882,36 +1885,40 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0470</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>BFIELD</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="E32" s="10" t="n">
-        <v>0</v>
+        <v>4.57</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>0.0044</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>6021000</v>
+        <v>7102500</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.51</v>
+        <v>0.45</v>
       </c>
       <c r="H32" t="n">
-        <v>63.39</v>
-      </c>
-      <c r="I32" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="n"/>
-      <c r="K32" s="2" t="n"/>
+        <v>29.08</v>
+      </c>
+      <c r="I32" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="n">
+        <v>4.722</v>
+      </c>
+      <c r="K32" s="2" t="n">
+        <v>4.891</v>
+      </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="7" t="inlineStr"/>
     </row>
@@ -1923,40 +1930,33 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>7020</t>
+          <t>0476</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ASTEEL</t>
+          <t>SLGC Berhad</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>0.105</v>
+        <v>0.25</v>
       </c>
       <c r="E33" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>5983100</v>
+        <v>6909000</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="H33" t="n">
-        <v>59.81</v>
+        <v>0.16</v>
       </c>
       <c r="I33" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J33" s="2" t="n">
-        <v>0.096</v>
-      </c>
-      <c r="K33" s="2" t="n">
-        <v>0.08500000000000001</v>
-      </c>
+      <c r="J33" s="2" t="n"/>
+      <c r="K33" s="2" t="n"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="7" t="inlineStr"/>
     </row>
@@ -1968,39 +1968,39 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>7139</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>NICE</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="E34" s="10" t="n">
-        <v>0</v>
+        <v>0.71</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>0.1008</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>5705300</v>
+        <v>6671000</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>6.03</v>
+        <v>1.47</v>
       </c>
       <c r="H34" t="n">
-        <v>37.6</v>
-      </c>
-      <c r="I34" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>86.43000000000001</v>
+      </c>
+      <c r="I34" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.083</v>
+        <v>0.519</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.444</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="7" t="inlineStr"/>
@@ -2013,39 +2013,39 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E35" s="10" t="n">
-        <v>0</v>
+        <v>0.365</v>
+      </c>
+      <c r="E35" s="8" t="n">
+        <v>-0.0135</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>5700200</v>
+        <v>6435300</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.3</v>
+        <v>0.96</v>
       </c>
       <c r="H35" t="n">
-        <v>46.68</v>
-      </c>
-      <c r="I35" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.65</v>
+      </c>
+      <c r="I35" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.868</v>
+        <v>0.367</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0.869</v>
+        <v>0.367</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="7" t="inlineStr"/>
@@ -2058,39 +2058,39 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>0.8149999999999999</v>
-      </c>
-      <c r="E36" s="3" t="n">
-        <v>0.0062</v>
+        <v>2.14</v>
+      </c>
+      <c r="E36" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>5687900</v>
+        <v>6318900</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.36</v>
+        <v>0.43</v>
       </c>
       <c r="H36" t="n">
-        <v>54.76</v>
-      </c>
-      <c r="I36" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.24</v>
+      </c>
+      <c r="I36" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>2.225</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>0.806</v>
+        <v>2.212</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="7" t="inlineStr"/>
@@ -2103,39 +2103,39 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>0.695</v>
-      </c>
-      <c r="E37" s="3" t="n">
-        <v>0.0775</v>
+        <v>0.295</v>
+      </c>
+      <c r="E37" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>5590300</v>
+        <v>6246100</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>1.23</v>
+        <v>2.38</v>
       </c>
       <c r="H37" t="n">
-        <v>85.75</v>
-      </c>
-      <c r="I37" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.15</v>
+      </c>
+      <c r="I37" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.518</v>
+        <v>0.295</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0.443</v>
+        <v>0.296</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="7" t="inlineStr"/>
@@ -2148,28 +2148,28 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="E38" s="10" t="n">
-        <v>0</v>
+        <v>0.4</v>
+      </c>
+      <c r="E38" s="8" t="n">
+        <v>-0.0361</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>5378900</v>
+        <v>6190000</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.36</v>
+        <v>5.49</v>
       </c>
       <c r="H38" t="n">
-        <v>41.24</v>
+        <v>32.62</v>
       </c>
       <c r="I38" s="6" t="inlineStr">
         <is>
@@ -2177,10 +2177,10 @@
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>2.225</v>
+        <v>0.421</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>2.212</v>
+        <v>0.441</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="7" t="inlineStr"/>
@@ -2193,39 +2193,39 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E39" s="3" t="n">
-        <v>0.016</v>
+        <v>0.39</v>
+      </c>
+      <c r="E39" s="8" t="n">
+        <v>-0.0127</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>5271000</v>
+        <v>6025000</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.28</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H39" t="n">
-        <v>63.49</v>
-      </c>
-      <c r="I39" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.12</v>
+      </c>
+      <c r="I39" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.581</v>
+        <v>0.402</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0.518</v>
+        <v>0.41</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="7" t="inlineStr"/>
@@ -2238,39 +2238,39 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>7020</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>ASTEEL</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>4.57</v>
-      </c>
-      <c r="E40" s="3" t="n">
-        <v>0.0044</v>
+        <v>0.105</v>
+      </c>
+      <c r="E40" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>5154800</v>
+        <v>5983100</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.33</v>
+        <v>2.7</v>
       </c>
       <c r="H40" t="n">
-        <v>29.08</v>
-      </c>
-      <c r="I40" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.81</v>
+      </c>
+      <c r="I40" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>4.722</v>
+        <v>0.096</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>4.891</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="7" t="inlineStr"/>
@@ -2283,39 +2283,39 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>7139</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>NICE</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>6.67</v>
-      </c>
-      <c r="E41" s="3" t="n">
-        <v>0.09699999999999999</v>
+        <v>0.08</v>
+      </c>
+      <c r="E41" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>5151200</v>
+        <v>5705300</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>1.15</v>
+        <v>6.03</v>
       </c>
       <c r="H41" t="n">
-        <v>65.08</v>
-      </c>
-      <c r="I41" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.6</v>
+      </c>
+      <c r="I41" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>5.829</v>
+        <v>0.083</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>5.778</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="7" t="inlineStr"/>
@@ -2343,10 +2343,10 @@
         <v>0.0857</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>5120500</v>
+        <v>5688500</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.95</v>
+        <v>1.05</v>
       </c>
       <c r="H42" t="n">
         <v>67.38</v>
@@ -2373,39 +2373,39 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>IOICORP</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>4.57</v>
+        <v>6.7</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>0.0022</v>
+        <v>0.102</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>4971300</v>
+        <v>5655100</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.53</v>
+        <v>1.26</v>
       </c>
       <c r="H43" t="n">
-        <v>40.81</v>
-      </c>
-      <c r="I43" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>65.41</v>
+      </c>
+      <c r="I43" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>4.674</v>
+        <v>5.832</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>4.619</v>
+        <v>5.778</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="7" t="inlineStr"/>
@@ -2418,39 +2418,39 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>WCT</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="E44" s="10" t="n">
-        <v>0</v>
+        <v>0.64</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>0.024</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>4575400</v>
+        <v>5522600</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>1.15</v>
+        <v>0.29</v>
       </c>
       <c r="H44" t="n">
-        <v>32.2</v>
-      </c>
-      <c r="I44" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.14</v>
+      </c>
+      <c r="I44" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.363</v>
+        <v>0.582</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0.383</v>
+        <v>0.519</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="7" t="inlineStr"/>
@@ -2463,39 +2463,39 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>0.79</v>
+        <v>0.34</v>
       </c>
       <c r="E45" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>4513000</v>
+        <v>5430300</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.57</v>
+        <v>1.37</v>
       </c>
       <c r="H45" t="n">
-        <v>54.24</v>
-      </c>
-      <c r="I45" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>32.2</v>
+      </c>
+      <c r="I45" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.779</v>
+        <v>0.363</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0.773</v>
+        <v>0.383</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="7" t="inlineStr"/>
@@ -2517,19 +2517,19 @@
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>0.39</v>
+        <v>0.385</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>0.04</v>
+        <v>0.0267</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>4492200</v>
+        <v>5147600</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.55</v>
+        <v>0.63</v>
       </c>
       <c r="H46" t="n">
-        <v>70.7</v>
+        <v>69.33</v>
       </c>
       <c r="I46" s="9" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.355</v>
+        <v>0.354</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0.322</v>
@@ -2553,28 +2553,28 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>IOICORP</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="E47" s="10" t="n">
-        <v>0</v>
+        <v>4.57</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>0.0022</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>4387600</v>
+        <v>5055700</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.35</v>
+        <v>0.53</v>
       </c>
       <c r="H47" t="n">
-        <v>30.27</v>
+        <v>40.81</v>
       </c>
       <c r="I47" s="6" t="inlineStr">
         <is>
@@ -2582,10 +2582,10 @@
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>10.021</v>
+        <v>4.674</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>10.213</v>
+        <v>4.619</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="7" t="inlineStr"/>
@@ -2598,39 +2598,39 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>MRCB</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="E48" s="3" t="n">
-        <v>0.0182</v>
+        <v>0.79</v>
+      </c>
+      <c r="E48" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>4139800</v>
+        <v>4994600</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.59</v>
+        <v>0.63</v>
       </c>
       <c r="H48" t="n">
-        <v>37.22</v>
-      </c>
-      <c r="I48" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.24</v>
+      </c>
+      <c r="I48" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.289</v>
+        <v>0.779</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0.307</v>
+        <v>0.773</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="7" t="inlineStr"/>
@@ -2643,39 +2643,39 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0376</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>IAB</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="E49" s="8" t="n">
-        <v>-0.0296</v>
+        <v>9.800000000000001</v>
+      </c>
+      <c r="E49" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>4115500</v>
+        <v>4972300</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>2.38</v>
+        <v>0.39</v>
       </c>
       <c r="H49" t="n">
-        <v>53.07</v>
-      </c>
-      <c r="I49" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>30.27</v>
+      </c>
+      <c r="I49" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>1.274</v>
+        <v>10.021</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>1.319</v>
+        <v>10.213</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="7" t="inlineStr"/>
@@ -2688,28 +2688,28 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0111</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>K1</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>0.165</v>
+        <v>1.22</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>0.0313</v>
+        <v>0.0517</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>3810200</v>
+        <v>4780500</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>1.16</v>
+        <v>0.83</v>
       </c>
       <c r="H50" t="n">
-        <v>59.38</v>
+        <v>59.32</v>
       </c>
       <c r="I50" s="9" t="inlineStr">
         <is>
@@ -2717,10 +2717,10 @@
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.156</v>
+        <v>1.157</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>0.145</v>
+        <v>1.166</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="7" t="inlineStr"/>
@@ -2733,39 +2733,39 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>SPSETIA</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>0.72</v>
+        <v>2.74</v>
       </c>
       <c r="E51" s="8" t="n">
-        <v>-0.0069</v>
+        <v>-0.0144</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>3583400</v>
+        <v>4592600</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.6</v>
+        <v>0.26</v>
       </c>
       <c r="H51" t="n">
-        <v>33.63</v>
-      </c>
-      <c r="I51" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.38</v>
+      </c>
+      <c r="I51" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.756</v>
+        <v>2.623</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0.819</v>
+        <v>2.496</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="7" t="inlineStr"/>
@@ -2778,28 +2778,28 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>5141</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>DAYANG</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>7.25</v>
+        <v>1.39</v>
       </c>
       <c r="E52" s="8" t="n">
-        <v>-0.0014</v>
+        <v>-0.0414</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>3571100</v>
+        <v>4574900</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.26</v>
+        <v>2.08</v>
       </c>
       <c r="H52" t="n">
-        <v>31.19</v>
+        <v>33.34</v>
       </c>
       <c r="I52" s="6" t="inlineStr">
         <is>
@@ -2807,10 +2807,10 @@
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>7.639</v>
+        <v>1.456</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>7.729</v>
+        <v>1.494</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="7" t="inlineStr"/>
@@ -2823,28 +2823,28 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>TANCO</t>
+          <t>MRCB</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>0.145</v>
-      </c>
-      <c r="E53" s="8" t="n">
-        <v>-0.0333</v>
+        <v>0.28</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>0.0182</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>3516700</v>
+        <v>4470500</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.2</v>
+        <v>0.63</v>
       </c>
       <c r="H53" t="n">
-        <v>28.09</v>
+        <v>37.22</v>
       </c>
       <c r="I53" s="6" t="inlineStr">
         <is>
@@ -2852,10 +2852,10 @@
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.164</v>
+        <v>0.289</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0.201</v>
+        <v>0.307</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="7" t="inlineStr"/>
@@ -2868,28 +2868,28 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>0376</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>IAB</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>1.14</v>
+        <v>1.32</v>
       </c>
       <c r="E54" s="8" t="n">
-        <v>-0.0256</v>
+        <v>-0.0222</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>3489600</v>
+        <v>4385000</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.31</v>
+        <v>2.53</v>
       </c>
       <c r="H54" t="n">
-        <v>48.21</v>
+        <v>54.18</v>
       </c>
       <c r="I54" s="9" t="inlineStr">
         <is>
@@ -2897,10 +2897,10 @@
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>1.162</v>
+        <v>1.275</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>1.119</v>
+        <v>1.32</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="7" t="inlineStr"/>
@@ -2913,39 +2913,39 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>5326</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>99SMART</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="E55" s="3" t="n">
-        <v>0.0449</v>
+        <v>7.25</v>
+      </c>
+      <c r="E55" s="8" t="n">
+        <v>-0.0014</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>3433200</v>
+        <v>4087000</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="H55" t="n">
-        <v>52.06</v>
-      </c>
-      <c r="I55" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>31.19</v>
+      </c>
+      <c r="I55" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>3.199</v>
+        <v>7.639</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>3.39</v>
+        <v>7.729</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="7" t="inlineStr"/>
@@ -2958,39 +2958,39 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>2.74</v>
+        <v>7.12</v>
       </c>
       <c r="E56" s="8" t="n">
-        <v>-0.0144</v>
+        <v>-0.0042</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>3423500</v>
+        <v>4018500</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.19</v>
+        <v>0.42</v>
       </c>
       <c r="H56" t="n">
-        <v>61.38</v>
-      </c>
-      <c r="I56" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>18.83</v>
+      </c>
+      <c r="I56" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>2.623</v>
+        <v>7.596</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>2.496</v>
+        <v>8.09</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="7" t="inlineStr"/>
@@ -3003,39 +3003,39 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="E57" s="10" t="n">
-        <v>0</v>
+        <v>0.455</v>
+      </c>
+      <c r="E57" s="8" t="n">
+        <v>-0.0109</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>3404700</v>
+        <v>3892300</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.31</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H57" t="n">
-        <v>43.08</v>
-      </c>
-      <c r="I57" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.71</v>
+      </c>
+      <c r="I57" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>1.322</v>
+        <v>0.426</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>1.305</v>
+        <v>0.413</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="7" t="inlineStr"/>
@@ -3048,39 +3048,39 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="E58" s="3" t="n">
-        <v>0.0345</v>
+        <v>1.13</v>
+      </c>
+      <c r="E58" s="8" t="n">
+        <v>-0.0342</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>3369900</v>
+        <v>3871800</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.59</v>
+        <v>0.34</v>
       </c>
       <c r="H58" t="n">
-        <v>56.94</v>
-      </c>
-      <c r="I58" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.14</v>
+      </c>
+      <c r="I58" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>1.155</v>
+        <v>1.161</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>1.165</v>
+        <v>1.119</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="7" t="inlineStr"/>
@@ -3093,28 +3093,28 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>5253</t>
+          <t>0111</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>ECONBHD</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="E59" s="10" t="n">
-        <v>0</v>
+        <v>0.165</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>0.0313</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>3369000</v>
+        <v>3810200</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.74</v>
+        <v>1.16</v>
       </c>
       <c r="H59" t="n">
-        <v>55.25</v>
+        <v>59.38</v>
       </c>
       <c r="I59" s="9" t="inlineStr">
         <is>
@@ -3122,10 +3122,10 @@
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.122</v>
+        <v>0.156</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0.125</v>
+        <v>0.145</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="7" t="inlineStr"/>
@@ -3138,28 +3138,28 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>SPSETIA</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>3.72</v>
+        <v>0.72</v>
       </c>
       <c r="E60" s="8" t="n">
-        <v>-0.0133</v>
+        <v>-0.0069</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>3319200</v>
+        <v>3694300</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.29</v>
+        <v>0.62</v>
       </c>
       <c r="H60" t="n">
-        <v>56.88</v>
+        <v>33.63</v>
       </c>
       <c r="I60" s="6" t="inlineStr">
         <is>
@@ -3167,10 +3167,10 @@
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>3.602</v>
+        <v>0.756</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>2.74</v>
+        <v>0.819</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="7" t="inlineStr"/>
@@ -3183,36 +3183,40 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0468</t>
+          <t>5326</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>UNIPAC</t>
+          <t>99SMART</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E61" s="10" t="n">
-        <v>0</v>
+        <v>3.26</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>0.0449</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>3193700</v>
+        <v>3691800</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.27</v>
+        <v>0.87</v>
       </c>
       <c r="H61" t="n">
-        <v>28.11</v>
+        <v>52.06</v>
       </c>
       <c r="I61" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J61" s="2" t="n"/>
-      <c r="K61" s="2" t="n"/>
+      <c r="J61" s="2" t="n">
+        <v>3.199</v>
+      </c>
+      <c r="K61" s="2" t="n">
+        <v>3.39</v>
+      </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="7" t="inlineStr"/>
     </row>
@@ -3224,39 +3228,39 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0345</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>SUNLOGY</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="E62" s="3" t="n">
-        <v>0.0227</v>
+        <v>3.67</v>
+      </c>
+      <c r="E62" s="8" t="n">
+        <v>-0.0265</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>3191800</v>
+        <v>3668400</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.3</v>
+        <v>0.32</v>
       </c>
       <c r="H62" t="n">
-        <v>51.11</v>
-      </c>
-      <c r="I62" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>55.58</v>
+      </c>
+      <c r="I62" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.45</v>
+        <v>3.597</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>0.426</v>
+        <v>2.739</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="7" t="inlineStr"/>
@@ -3269,28 +3273,28 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="E63" s="10" t="n">
-        <v>0</v>
+        <v>0.455</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>0.0341</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>3154700</v>
+        <v>3581000</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.46</v>
+        <v>0.34</v>
       </c>
       <c r="H63" t="n">
-        <v>62.48</v>
+        <v>52.28</v>
       </c>
       <c r="I63" s="9" t="inlineStr">
         <is>
@@ -3298,10 +3302,10 @@
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.427</v>
+        <v>0.451</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>0.413</v>
+        <v>0.426</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="7" t="inlineStr"/>
@@ -3314,28 +3318,28 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>2429</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>TANCO</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>7.13</v>
-      </c>
-      <c r="E64" s="8" t="n">
-        <v>-0.0028</v>
+        <v>0.15</v>
+      </c>
+      <c r="E64" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>3118800</v>
+        <v>3578900</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0.32</v>
+        <v>0.21</v>
       </c>
       <c r="H64" t="n">
-        <v>19.02</v>
+        <v>30.21</v>
       </c>
       <c r="I64" s="6" t="inlineStr">
         <is>
@@ -3343,10 +3347,10 @@
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>7.597</v>
+        <v>0.165</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>8.09</v>
+        <v>0.201</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="7" t="inlineStr"/>
@@ -3359,39 +3363,39 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>0.795</v>
-      </c>
-      <c r="E65" s="3" t="n">
-        <v>0.0127</v>
+        <v>1.28</v>
+      </c>
+      <c r="E65" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>3110300</v>
+        <v>3559600</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>0.23</v>
+        <v>0.32</v>
       </c>
       <c r="H65" t="n">
-        <v>57.16</v>
-      </c>
-      <c r="I65" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.08</v>
+      </c>
+      <c r="I65" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.767</v>
+        <v>1.322</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>0.712</v>
+        <v>1.305</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="7" t="inlineStr"/>
@@ -3404,39 +3408,39 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>5253</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>ECONBHD</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>0.525</v>
-      </c>
-      <c r="E66" s="3" t="n">
-        <v>0.0294</v>
+        <v>0.125</v>
+      </c>
+      <c r="E66" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>2982100</v>
+        <v>3421000</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>0.18</v>
+        <v>0.75</v>
       </c>
       <c r="H66" t="n">
-        <v>55.9</v>
-      </c>
-      <c r="I66" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.25</v>
+      </c>
+      <c r="I66" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.512</v>
+        <v>0.122</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>0.436</v>
+        <v>0.125</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="7" t="inlineStr"/>
@@ -3449,28 +3453,28 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>0.915</v>
-      </c>
-      <c r="E67" s="3" t="n">
-        <v>0.0281</v>
+        <v>0.96</v>
+      </c>
+      <c r="E67" s="8" t="n">
+        <v>-0.0052</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>2980800</v>
+        <v>3355100</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>1.03</v>
+        <v>0.41</v>
       </c>
       <c r="H67" t="n">
-        <v>48.14</v>
+        <v>54.49</v>
       </c>
       <c r="I67" s="6" t="inlineStr">
         <is>
@@ -3478,10 +3482,10 @@
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.912</v>
+        <v>0.961</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>0.964</v>
+        <v>0.821</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="7" t="inlineStr"/>
@@ -3494,39 +3498,39 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>0.965</v>
-      </c>
-      <c r="E68" s="10" t="n">
-        <v>0</v>
+        <v>0.795</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>0.0127</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>2818300</v>
+        <v>3321800</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>0.35</v>
+        <v>0.25</v>
       </c>
       <c r="H68" t="n">
-        <v>55.29</v>
-      </c>
-      <c r="I68" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.16</v>
+      </c>
+      <c r="I68" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.961</v>
+        <v>0.767</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>0.821</v>
+        <v>0.712</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="7" t="inlineStr"/>
@@ -3539,40 +3543,36 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>0468</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>UNIPAC</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="E69" s="3" t="n">
-        <v>0.0091</v>
+        <v>0.25</v>
+      </c>
+      <c r="E69" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>2791500</v>
+        <v>3272400</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="H69" t="n">
-        <v>63.64</v>
+        <v>28.11</v>
       </c>
       <c r="I69" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J69" s="2" t="n">
-        <v>1.068</v>
-      </c>
-      <c r="K69" s="2" t="n">
-        <v>0.916</v>
-      </c>
+      <c r="J69" s="2" t="n"/>
+      <c r="K69" s="2" t="n"/>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="7" t="inlineStr"/>
     </row>
@@ -3584,39 +3584,39 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>TENAGA</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>0.225</v>
+        <v>12.96</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>0.0227</v>
+        <v>0.004699999999999999</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>2715400</v>
+        <v>3130300</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>0.1</v>
+        <v>0.35</v>
       </c>
       <c r="H70" t="n">
-        <v>33.07</v>
-      </c>
-      <c r="I70" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>42.32</v>
+      </c>
+      <c r="I70" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.249</v>
+        <v>13.036</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>0.304</v>
+        <v>13.573</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="7" t="inlineStr"/>
@@ -3629,28 +3629,28 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>0.0105</v>
+        <v>0.0075</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>2694700</v>
+        <v>3087800</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>0.86</v>
+        <v>0.52</v>
       </c>
       <c r="H71" t="n">
-        <v>76.28</v>
+        <v>57.33</v>
       </c>
       <c r="I71" s="9" t="inlineStr">
         <is>
@@ -3658,10 +3658,10 @@
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>2.64</v>
+        <v>2.628</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>2.286</v>
+        <v>2.581</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="7" t="inlineStr"/>
@@ -3674,39 +3674,39 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>0.545</v>
-      </c>
-      <c r="E72" s="8" t="n">
-        <v>-0.018</v>
+        <v>1.12</v>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>0.0182</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>2623800</v>
+        <v>3084500</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>0.49</v>
+        <v>0.32</v>
       </c>
       <c r="H72" t="n">
-        <v>32.26</v>
-      </c>
-      <c r="I72" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.88</v>
+      </c>
+      <c r="I72" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.592</v>
+        <v>1.069</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>0.641</v>
+        <v>0.916</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="7" t="inlineStr"/>
@@ -3719,39 +3719,39 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>1.24</v>
+        <v>0.53</v>
       </c>
       <c r="E73" s="3" t="n">
-        <v>0.0248</v>
+        <v>0.0392</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>2604000</v>
+        <v>3084400</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>0.77</v>
+        <v>0.19</v>
       </c>
       <c r="H73" t="n">
-        <v>76.11</v>
-      </c>
-      <c r="I73" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>56.74</v>
+      </c>
+      <c r="I73" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>1.024</v>
+        <v>0.512</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>0.86</v>
+        <v>0.436</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="7" t="inlineStr"/>
@@ -3764,39 +3764,39 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>0.975</v>
-      </c>
-      <c r="E74" s="8" t="n">
-        <v>-0.0201</v>
+        <v>0.22</v>
+      </c>
+      <c r="E74" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>2590900</v>
+        <v>3074800</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>0.8</v>
+        <v>0.12</v>
       </c>
       <c r="H74" t="n">
-        <v>83.41</v>
-      </c>
-      <c r="I74" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>29.99</v>
+      </c>
+      <c r="I74" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.656</v>
+        <v>0.249</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>0.479</v>
+        <v>0.304</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="7" t="inlineStr"/>
@@ -3809,39 +3809,39 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0268</t>
+          <t>0338</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>L&amp;PBHD</t>
+          <t>KOPI</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>0.24</v>
+        <v>0.91</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>0.09089999999999999</v>
+        <v>0.0225</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>2578600</v>
+        <v>3045100</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>1.29</v>
+        <v>1.05</v>
       </c>
       <c r="H75" t="n">
-        <v>77.70999999999999</v>
-      </c>
-      <c r="I75" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.13</v>
+      </c>
+      <c r="I75" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.206</v>
+        <v>0.911</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>0.171</v>
+        <v>0.964</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="7" t="inlineStr"/>
@@ -3854,39 +3854,39 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="E76" s="3" t="n">
-        <v>0.0286</v>
+        <v>0.55</v>
+      </c>
+      <c r="E76" s="8" t="n">
+        <v>-0.009000000000000001</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>2522000</v>
+        <v>3041200</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>0.27</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H76" t="n">
-        <v>63.57</v>
-      </c>
-      <c r="I76" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.2</v>
+      </c>
+      <c r="I76" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.672</v>
+        <v>0.592</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>0.607</v>
+        <v>0.641</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="7" t="inlineStr"/>
@@ -3899,39 +3899,39 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>0243</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>NEXG</t>
+          <t>CENGILD</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E77" s="3" t="n">
-        <v>0.0172</v>
+        <v>0.16</v>
+      </c>
+      <c r="E77" s="8" t="n">
+        <v>-0.1351</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>2508400</v>
+        <v>3000700</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>0.21</v>
+        <v>13.35</v>
       </c>
       <c r="H77" t="n">
-        <v>52.49</v>
-      </c>
-      <c r="I77" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>18.12</v>
+      </c>
+      <c r="I77" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.291</v>
+        <v>0.192</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>0.281</v>
+        <v>0.195</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="7" t="inlineStr"/>
@@ -3944,39 +3944,39 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>5141</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>DAYANG</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="E78" s="8" t="n">
-        <v>-0.0276</v>
+        <v>2.87</v>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>0.006999999999999999</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>2486400</v>
+        <v>2977300</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>1.13</v>
+        <v>0.95</v>
       </c>
       <c r="H78" t="n">
-        <v>36.3</v>
-      </c>
-      <c r="I78" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>75.91</v>
+      </c>
+      <c r="I78" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>1.458</v>
+        <v>2.639</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>1.495</v>
+        <v>2.285</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="7" t="inlineStr"/>
@@ -3989,39 +3989,39 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>CNERGEN</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>0.0242</v>
+        <v>0.0165</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>2476700</v>
+        <v>2861600</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>0.28</v>
+        <v>0.85</v>
       </c>
       <c r="H79" t="n">
-        <v>41.85</v>
-      </c>
-      <c r="I79" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>75.64</v>
+      </c>
+      <c r="I79" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>1.287</v>
+        <v>1.023</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>1.387</v>
+        <v>0.86</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="7" t="inlineStr"/>
@@ -4034,28 +4034,28 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>0268</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>L&amp;PBHD</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>2.69</v>
+        <v>0.235</v>
       </c>
       <c r="E80" s="3" t="n">
-        <v>0.0037</v>
+        <v>0.0682</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>2442000</v>
+        <v>2808700</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>0.41</v>
+        <v>1.41</v>
       </c>
       <c r="H80" t="n">
-        <v>56.64</v>
+        <v>76.23999999999999</v>
       </c>
       <c r="I80" s="9" t="inlineStr">
         <is>
@@ -4063,10 +4063,10 @@
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>2.628</v>
+        <v>0.205</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>2.58</v>
+        <v>0.171</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="7" t="inlineStr"/>
@@ -4079,39 +4079,39 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0296</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>HEGROUP</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="E81" s="8" t="n">
-        <v>-0.0351</v>
+        <v>5.6</v>
+      </c>
+      <c r="E81" s="3" t="n">
+        <v>0.0072</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>2383600</v>
+        <v>2782200</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>0.49</v>
+        <v>0.2</v>
       </c>
       <c r="H81" t="n">
-        <v>62.77</v>
-      </c>
-      <c r="I81" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.83</v>
+      </c>
+      <c r="I81" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J81" s="2" t="n">
-        <v>1.056</v>
+        <v>5.636</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>0.891</v>
+        <v>5.308</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="7" t="inlineStr"/>
@@ -4124,28 +4124,28 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>0296</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>TENAGA</t>
+          <t>HEGROUP</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="E82" s="3" t="n">
-        <v>0.007800000000000001</v>
+        <v>1.12</v>
+      </c>
+      <c r="E82" s="8" t="n">
+        <v>-0.0175</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>2358000</v>
+        <v>2707300</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>0.26</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H82" t="n">
-        <v>44.16</v>
+        <v>66.73</v>
       </c>
       <c r="I82" s="9" t="inlineStr">
         <is>
@@ -4153,10 +4153,10 @@
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>13.039</v>
+        <v>1.057</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>13.573</v>
+        <v>0.891</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="7" t="inlineStr"/>
@@ -4169,28 +4169,28 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>0.795</v>
-      </c>
-      <c r="E83" s="3" t="n">
-        <v>0.0192</v>
+        <v>0.975</v>
+      </c>
+      <c r="E83" s="8" t="n">
+        <v>-0.0201</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>2302700</v>
+        <v>2649600</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>0.33</v>
+        <v>0.82</v>
       </c>
       <c r="H83" t="n">
-        <v>64.39</v>
+        <v>83.41</v>
       </c>
       <c r="I83" s="9" t="inlineStr">
         <is>
@@ -4198,10 +4198,10 @@
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.735</v>
+        <v>0.656</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>0.652</v>
+        <v>0.479</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="7" t="inlineStr"/>
@@ -4214,39 +4214,39 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>5.6</v>
+        <v>0.72</v>
       </c>
       <c r="E84" s="3" t="n">
-        <v>0.0072</v>
+        <v>0.0286</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>2238300</v>
+        <v>2642500</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>0.16</v>
+        <v>0.29</v>
       </c>
       <c r="H84" t="n">
-        <v>50.83</v>
-      </c>
-      <c r="I84" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.57</v>
+      </c>
+      <c r="I84" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>5.636</v>
+        <v>0.672</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>5.308</v>
+        <v>0.607</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="7" t="inlineStr"/>
@@ -4259,28 +4259,28 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0104</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>GENETEC</t>
+          <t>NEXG</t>
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="E85" s="8" t="n">
-        <v>-0.0149</v>
+        <v>0.295</v>
+      </c>
+      <c r="E85" s="3" t="n">
+        <v>0.0172</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>2203000</v>
+        <v>2558700</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>0.39</v>
+        <v>0.21</v>
       </c>
       <c r="H85" t="n">
-        <v>52.01</v>
+        <v>52.49</v>
       </c>
       <c r="I85" s="9" t="inlineStr">
         <is>
@@ -4288,10 +4288,10 @@
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.326</v>
+        <v>0.291</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>0.338</v>
+        <v>0.281</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="7" t="inlineStr"/>
@@ -4304,39 +4304,39 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>0.295</v>
+        <v>1.27</v>
       </c>
       <c r="E86" s="3" t="n">
-        <v>0.0172</v>
+        <v>0.0242</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>2202200</v>
+        <v>2556200</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>0.25</v>
+        <v>0.29</v>
       </c>
       <c r="H86" t="n">
-        <v>57.36</v>
-      </c>
-      <c r="I86" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.85</v>
+      </c>
+      <c r="I86" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.278</v>
+        <v>1.287</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>0.303</v>
+        <v>1.387</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="7" t="inlineStr"/>
@@ -4349,28 +4349,28 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0239</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>ECOMATE</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E87" s="10" t="n">
-        <v>0</v>
+        <v>2.11</v>
+      </c>
+      <c r="E87" s="3" t="n">
+        <v>0.0048</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v>2152900</v>
+        <v>2522600</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>0.67</v>
+        <v>0.13</v>
       </c>
       <c r="H87" t="n">
-        <v>52.86</v>
+        <v>52.16</v>
       </c>
       <c r="I87" s="6" t="inlineStr">
         <is>
@@ -4378,10 +4378,10 @@
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.864</v>
+        <v>2.099</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>0.858</v>
+        <v>2.081</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="7" t="inlineStr"/>
@@ -4394,28 +4394,28 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>CPETECH</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>1.34</v>
+        <v>0.795</v>
       </c>
       <c r="E88" s="3" t="n">
-        <v>0.0075</v>
+        <v>0.0192</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>2121100</v>
+        <v>2510700</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.36</v>
       </c>
       <c r="H88" t="n">
-        <v>56.94</v>
+        <v>64.39</v>
       </c>
       <c r="I88" s="9" t="inlineStr">
         <is>
@@ -4423,10 +4423,10 @@
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>1.293</v>
+        <v>0.735</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>1.194</v>
+        <v>0.652</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="7" t="inlineStr"/>
@@ -4439,39 +4439,39 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>2.11</v>
+        <v>1.64</v>
       </c>
       <c r="E89" s="3" t="n">
-        <v>0.0048</v>
+        <v>0.0314</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>2120100</v>
+        <v>2493900</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>0.11</v>
+        <v>0.37</v>
       </c>
       <c r="H89" t="n">
-        <v>52.16</v>
-      </c>
-      <c r="I89" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>41.93</v>
+      </c>
+      <c r="I89" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>2.099</v>
+        <v>1.671</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>2.081</v>
+        <v>1.787</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="7" t="inlineStr"/>
@@ -4484,28 +4484,28 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>1.64</v>
+        <v>0.295</v>
       </c>
       <c r="E90" s="3" t="n">
-        <v>0.0314</v>
+        <v>0.0172</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>2085700</v>
+        <v>2428400</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>0.31</v>
+        <v>0.27</v>
       </c>
       <c r="H90" t="n">
-        <v>41.93</v>
+        <v>57.36</v>
       </c>
       <c r="I90" s="9" t="inlineStr">
         <is>
@@ -4513,10 +4513,10 @@
         </is>
       </c>
       <c r="J90" s="2" t="n">
-        <v>1.671</v>
+        <v>0.278</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>1.787</v>
+        <v>0.303</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="7" t="inlineStr"/>
@@ -4529,28 +4529,28 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0267</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>ECA</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="E91" s="3" t="n">
-        <v>0.0548</v>
+        <v>1.05</v>
+      </c>
+      <c r="E91" s="8" t="n">
+        <v>-0.0187</v>
       </c>
       <c r="F91" s="4" t="n">
-        <v>2020900</v>
+        <v>2424300</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>0.6</v>
+        <v>0.17</v>
       </c>
       <c r="H91" t="n">
-        <v>54.15</v>
+        <v>47.46</v>
       </c>
       <c r="I91" s="9" t="inlineStr">
         <is>
@@ -4558,10 +4558,10 @@
         </is>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.367</v>
+        <v>1.07</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>0.374</v>
+        <v>1.037</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="7" t="inlineStr"/>
@@ -4574,28 +4574,28 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>0272</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>TTVHB</t>
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>0.545</v>
-      </c>
-      <c r="E92" s="10" t="n">
-        <v>0</v>
+        <v>0.255</v>
+      </c>
+      <c r="E92" s="3" t="n">
+        <v>0.0408</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v>1914400</v>
+        <v>2318600</v>
       </c>
       <c r="G92" s="5" t="n">
-        <v>0.46</v>
+        <v>1.15</v>
       </c>
       <c r="H92" t="n">
-        <v>71.06999999999999</v>
+        <v>52.98</v>
       </c>
       <c r="I92" s="9" t="inlineStr">
         <is>
@@ -4603,10 +4603,10 @@
         </is>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.477</v>
+        <v>0.248</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>0.451</v>
+        <v>0.253</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="7" t="inlineStr"/>
@@ -4619,39 +4619,39 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0359</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>HKB</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D93" s="2" t="n">
-        <v>0.82</v>
+        <v>0.535</v>
       </c>
       <c r="E93" s="3" t="n">
-        <v>0.0186</v>
+        <v>0.009399999999999999</v>
       </c>
       <c r="F93" s="4" t="n">
-        <v>1876600</v>
+        <v>2311000</v>
       </c>
       <c r="G93" s="5" t="n">
-        <v>0.84</v>
+        <v>0.3</v>
       </c>
       <c r="H93" t="n">
-        <v>82.16</v>
-      </c>
-      <c r="I93" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>55.09</v>
+      </c>
+      <c r="I93" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.679</v>
+        <v>0.522</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>0.622</v>
+        <v>0.531</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="7" t="inlineStr"/>
@@ -4664,28 +4664,28 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0249</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>LGMS</t>
+          <t>CPETECH</t>
         </is>
       </c>
       <c r="D94" s="2" t="n">
-        <v>0.5649999999999999</v>
-      </c>
-      <c r="E94" s="8" t="n">
-        <v>-0.008800000000000001</v>
+        <v>1.35</v>
+      </c>
+      <c r="E94" s="3" t="n">
+        <v>0.015</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>1827200</v>
+        <v>2185500</v>
       </c>
       <c r="G94" s="5" t="n">
-        <v>2.03</v>
+        <v>0.58</v>
       </c>
       <c r="H94" t="n">
-        <v>69.2</v>
+        <v>57.71</v>
       </c>
       <c r="I94" s="9" t="inlineStr">
         <is>
@@ -4693,10 +4693,10 @@
         </is>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.523</v>
+        <v>1.294</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>0.504</v>
+        <v>1.194</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="7" t="inlineStr"/>
@@ -4709,39 +4709,39 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0272</t>
+          <t>0239</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>TTVHB</t>
+          <t>ECOMATE</t>
         </is>
       </c>
       <c r="D95" s="2" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E95" s="3" t="n">
-        <v>0.0612</v>
+        <v>0.865</v>
+      </c>
+      <c r="E95" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F95" s="4" t="n">
-        <v>1822700</v>
+        <v>2152900</v>
       </c>
       <c r="G95" s="5" t="n">
-        <v>0.91</v>
+        <v>0.67</v>
       </c>
       <c r="H95" t="n">
-        <v>55.07</v>
-      </c>
-      <c r="I95" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.86</v>
+      </c>
+      <c r="I95" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.249</v>
+        <v>0.864</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>0.253</v>
+        <v>0.858</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="7" t="inlineStr"/>
@@ -4754,39 +4754,39 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D96" s="2" t="n">
-        <v>2.49</v>
+        <v>0.355</v>
       </c>
       <c r="E96" s="3" t="n">
-        <v>0.004</v>
+        <v>0.0143</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>1818400</v>
+        <v>2152100</v>
       </c>
       <c r="G96" s="5" t="n">
-        <v>0.14</v>
+        <v>0.28</v>
       </c>
       <c r="H96" t="n">
-        <v>57.08</v>
-      </c>
-      <c r="I96" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.58</v>
+      </c>
+      <c r="I96" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J96" s="2" t="n">
-        <v>2.462</v>
+        <v>0.344</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>2.344</v>
+        <v>0.324</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="7" t="inlineStr"/>
@@ -4799,39 +4799,39 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>0045</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>SSB8</t>
         </is>
       </c>
       <c r="D97" s="2" t="n">
-        <v>0.9350000000000001</v>
-      </c>
-      <c r="E97" s="3" t="n">
-        <v>0.0054</v>
+        <v>0.655</v>
+      </c>
+      <c r="E97" s="8" t="n">
+        <v>-0.0224</v>
       </c>
       <c r="F97" s="4" t="n">
-        <v>1815300</v>
+        <v>2142300</v>
       </c>
       <c r="G97" s="5" t="n">
-        <v>1.06</v>
+        <v>0.52</v>
       </c>
       <c r="H97" t="n">
-        <v>54.68</v>
-      </c>
-      <c r="I97" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.35</v>
+      </c>
+      <c r="I97" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.923</v>
+        <v>0.636</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>0.85</v>
+        <v>0.601</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="7" t="inlineStr"/>
@@ -4844,39 +4844,39 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D98" s="2" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E98" s="8" t="n">
-        <v>-0.0062</v>
+        <v>2.5</v>
+      </c>
+      <c r="E98" s="3" t="n">
+        <v>0.008100000000000001</v>
       </c>
       <c r="F98" s="4" t="n">
-        <v>1808200</v>
+        <v>2090700</v>
       </c>
       <c r="G98" s="5" t="n">
-        <v>0.29</v>
+        <v>0.16</v>
       </c>
       <c r="H98" t="n">
-        <v>65.37</v>
-      </c>
-      <c r="I98" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>58.18</v>
+      </c>
+      <c r="I98" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.785</v>
+        <v>2.463</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>0.764</v>
+        <v>2.344</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="7" t="inlineStr"/>
@@ -4889,28 +4889,28 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>CMSB</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D99" s="2" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="E99" s="3" t="n">
-        <v>0.0166</v>
+        <v>4.2</v>
+      </c>
+      <c r="E99" s="8" t="n">
+        <v>-0.0141</v>
       </c>
       <c r="F99" s="4" t="n">
-        <v>1805100</v>
+        <v>2062200</v>
       </c>
       <c r="G99" s="5" t="n">
-        <v>0.88</v>
+        <v>0.26</v>
       </c>
       <c r="H99" t="n">
-        <v>33.38</v>
+        <v>42.46</v>
       </c>
       <c r="I99" s="6" t="inlineStr">
         <is>
@@ -4918,10 +4918,10 @@
         </is>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.96</v>
+        <v>4.366</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>0.993</v>
+        <v>4.463</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="7" t="inlineStr"/>
@@ -4934,39 +4934,39 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>7225</t>
+          <t>0359</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>HKB</t>
         </is>
       </c>
       <c r="D100" s="2" t="n">
-        <v>0.205</v>
-      </c>
-      <c r="E100" s="10" t="n">
-        <v>0</v>
+        <v>0.82</v>
+      </c>
+      <c r="E100" s="3" t="n">
+        <v>0.0186</v>
       </c>
       <c r="F100" s="4" t="n">
-        <v>1804100</v>
+        <v>2052400</v>
       </c>
       <c r="G100" s="5" t="n">
-        <v>0.39</v>
+        <v>0.92</v>
       </c>
       <c r="H100" t="n">
-        <v>47.55</v>
-      </c>
-      <c r="I100" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>82.16</v>
+      </c>
+      <c r="I100" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.207</v>
+        <v>0.679</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>0.208</v>
+        <v>0.622</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="7" t="inlineStr"/>
@@ -4979,39 +4979,39 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>5337</t>
+          <t>0388</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>ECOSHOP</t>
+          <t>SEMICO</t>
         </is>
       </c>
       <c r="D101" s="2" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="E101" s="3" t="n">
-        <v>0.021</v>
+        <v>0.615</v>
+      </c>
+      <c r="E101" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F101" s="4" t="n">
-        <v>1736500</v>
+        <v>2043100</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>0.38</v>
+        <v>0.7</v>
       </c>
       <c r="H101" t="n">
-        <v>49.32</v>
-      </c>
-      <c r="I101" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.01</v>
+      </c>
+      <c r="I101" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J101" s="2" t="n">
-        <v>1.461</v>
+        <v>0.612</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>1.469</v>
+        <v>0.598</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="7" t="inlineStr"/>
@@ -5024,28 +5024,28 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>0045</t>
+          <t>0267</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>SSB8</t>
+          <t>ECA</t>
         </is>
       </c>
       <c r="D102" s="2" t="n">
-        <v>0.665</v>
-      </c>
-      <c r="E102" s="8" t="n">
-        <v>-0.0075</v>
+        <v>0.385</v>
+      </c>
+      <c r="E102" s="3" t="n">
+        <v>0.0548</v>
       </c>
       <c r="F102" s="4" t="n">
-        <v>1724300</v>
+        <v>2031000</v>
       </c>
       <c r="G102" s="5" t="n">
-        <v>0.41</v>
+        <v>0.6</v>
       </c>
       <c r="H102" t="n">
-        <v>62</v>
+        <v>54.15</v>
       </c>
       <c r="I102" s="9" t="inlineStr">
         <is>
@@ -5053,10 +5053,10 @@
         </is>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.637</v>
+        <v>0.367</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>0.601</v>
+        <v>0.374</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="7" t="inlineStr"/>
@@ -5069,39 +5069,39 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>5302</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>ATECH</t>
         </is>
       </c>
       <c r="D103" s="2" t="n">
-        <v>0.535</v>
+        <v>0.805</v>
       </c>
       <c r="E103" s="3" t="n">
-        <v>0.009399999999999999</v>
+        <v>0.019</v>
       </c>
       <c r="F103" s="4" t="n">
-        <v>1655700</v>
+        <v>2030000</v>
       </c>
       <c r="G103" s="5" t="n">
-        <v>0.22</v>
+        <v>1.11</v>
       </c>
       <c r="H103" t="n">
-        <v>55.09</v>
-      </c>
-      <c r="I103" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.79</v>
+      </c>
+      <c r="I103" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.522</v>
+        <v>0.77</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>0.531</v>
+        <v>0.761</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="7" t="inlineStr"/>
@@ -5114,28 +5114,28 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>5210</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>CMSB</t>
         </is>
       </c>
       <c r="D104" s="2" t="n">
-        <v>0.325</v>
-      </c>
-      <c r="E104" s="8" t="n">
-        <v>-0.0152</v>
+        <v>0.92</v>
+      </c>
+      <c r="E104" s="3" t="n">
+        <v>0.0166</v>
       </c>
       <c r="F104" s="4" t="n">
-        <v>1601300</v>
+        <v>2011400</v>
       </c>
       <c r="G104" s="5" t="n">
-        <v>0.27</v>
+        <v>0.98</v>
       </c>
       <c r="H104" t="n">
-        <v>32.41</v>
+        <v>33.38</v>
       </c>
       <c r="I104" s="6" t="inlineStr">
         <is>
@@ -5143,10 +5143,10 @@
         </is>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.339</v>
+        <v>0.96</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>0.345</v>
+        <v>0.993</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="7" t="inlineStr"/>
@@ -5159,39 +5159,39 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D105" s="2" t="n">
-        <v>4.23</v>
-      </c>
-      <c r="E105" s="8" t="n">
-        <v>-0.006999999999999999</v>
+        <v>0.545</v>
+      </c>
+      <c r="E105" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F105" s="4" t="n">
-        <v>1563500</v>
+        <v>1983200</v>
       </c>
       <c r="G105" s="5" t="n">
-        <v>0.2</v>
+        <v>0.48</v>
       </c>
       <c r="H105" t="n">
-        <v>43.38</v>
-      </c>
-      <c r="I105" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>71.06999999999999</v>
+      </c>
+      <c r="I105" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J105" s="2" t="n">
-        <v>4.369</v>
+        <v>0.477</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>4.464</v>
+        <v>0.451</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="7" t="inlineStr"/>
@@ -5204,28 +5204,28 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>0249</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>LGMS</t>
         </is>
       </c>
       <c r="D106" s="2" t="n">
-        <v>1.06</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E106" s="8" t="n">
-        <v>-0.009300000000000001</v>
+        <v>-0.0175</v>
       </c>
       <c r="F106" s="4" t="n">
-        <v>1557900</v>
+        <v>1976400</v>
       </c>
       <c r="G106" s="5" t="n">
-        <v>0.11</v>
+        <v>2.2</v>
       </c>
       <c r="H106" t="n">
-        <v>48.94</v>
+        <v>66.75</v>
       </c>
       <c r="I106" s="9" t="inlineStr">
         <is>
@@ -5233,10 +5233,10 @@
         </is>
       </c>
       <c r="J106" s="2" t="n">
-        <v>1.071</v>
+        <v>0.522</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>1.037</v>
+        <v>0.504</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="7" t="inlineStr"/>
@@ -5249,28 +5249,28 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>4863</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>TM</t>
         </is>
       </c>
       <c r="D107" s="2" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="E107" s="10" t="n">
-        <v>0</v>
+        <v>7.89</v>
+      </c>
+      <c r="E107" s="3" t="n">
+        <v>0.0025</v>
       </c>
       <c r="F107" s="4" t="n">
-        <v>1519900</v>
+        <v>1965800</v>
       </c>
       <c r="G107" s="5" t="n">
-        <v>0.2</v>
+        <v>0.66</v>
       </c>
       <c r="H107" t="n">
-        <v>56.58</v>
+        <v>50.7</v>
       </c>
       <c r="I107" s="9" t="inlineStr">
         <is>
@@ -5278,10 +5278,10 @@
         </is>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.343</v>
+        <v>7.892</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>0.324</v>
+        <v>7.85</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="7" t="inlineStr"/>
@@ -5294,28 +5294,28 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>5306</t>
+          <t>5210</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>FFB</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="D108" s="2" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="E108" s="3" t="n">
-        <v>0.0286</v>
+        <v>0.325</v>
+      </c>
+      <c r="E108" s="8" t="n">
+        <v>-0.0152</v>
       </c>
       <c r="F108" s="4" t="n">
-        <v>1489500</v>
+        <v>1950500</v>
       </c>
       <c r="G108" s="5" t="n">
-        <v>0.51</v>
+        <v>0.32</v>
       </c>
       <c r="H108" t="n">
-        <v>32.69</v>
+        <v>32.41</v>
       </c>
       <c r="I108" s="6" t="inlineStr">
         <is>
@@ -5323,10 +5323,10 @@
         </is>
       </c>
       <c r="J108" s="2" t="n">
-        <v>1.88</v>
+        <v>0.339</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>2.017</v>
+        <v>0.345</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="7" t="inlineStr"/>
@@ -5339,28 +5339,28 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>6947</t>
+          <t>6633</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>CDB</t>
+          <t>LHI</t>
         </is>
       </c>
       <c r="D109" s="2" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="E109" s="3" t="n">
-        <v>0.03240000000000001</v>
+        <v>0.72</v>
+      </c>
+      <c r="E109" s="8" t="n">
+        <v>-0.0137</v>
       </c>
       <c r="F109" s="4" t="n">
-        <v>1441000</v>
+        <v>1947400</v>
       </c>
       <c r="G109" s="5" t="n">
-        <v>0.46</v>
+        <v>1.16</v>
       </c>
       <c r="H109" t="n">
-        <v>41.75</v>
+        <v>44.17</v>
       </c>
       <c r="I109" s="9" t="inlineStr">
         <is>
@@ -5368,10 +5368,10 @@
         </is>
       </c>
       <c r="J109" s="2" t="n">
-        <v>2.586</v>
+        <v>0.734</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>2.731</v>
+        <v>0.748</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="7" t="inlineStr"/>
@@ -5384,28 +5384,28 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>6947</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>CDB</t>
         </is>
       </c>
       <c r="D110" s="2" t="n">
-        <v>4.27</v>
+        <v>2.53</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>0.0264</v>
+        <v>0.0243</v>
       </c>
       <c r="F110" s="4" t="n">
-        <v>1423200</v>
+        <v>1934000</v>
       </c>
       <c r="G110" s="5" t="n">
-        <v>0.17</v>
+        <v>0.62</v>
       </c>
       <c r="H110" t="n">
-        <v>65.23</v>
+        <v>38.88</v>
       </c>
       <c r="I110" s="9" t="inlineStr">
         <is>
@@ -5413,10 +5413,10 @@
         </is>
       </c>
       <c r="J110" s="2" t="n">
-        <v>3.968</v>
+        <v>2.584</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>3.443</v>
+        <v>2.731</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="7" t="inlineStr"/>
@@ -5429,39 +5429,39 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D111" s="2" t="n">
-        <v>1.85</v>
+        <v>4.24</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0.0054</v>
+        <v>0.0192</v>
       </c>
       <c r="F111" s="4" t="n">
-        <v>1395600</v>
+        <v>1930700</v>
       </c>
       <c r="G111" s="5" t="n">
-        <v>0.33</v>
+        <v>0.23</v>
       </c>
       <c r="H111" t="n">
-        <v>38.83</v>
-      </c>
-      <c r="I111" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.51000000000001</v>
+      </c>
+      <c r="I111" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J111" s="2" t="n">
-        <v>1.896</v>
+        <v>3.965</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>2.026</v>
+        <v>3.443</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="7" t="inlineStr"/>
@@ -5483,19 +5483,19 @@
         </is>
       </c>
       <c r="D112" s="2" t="n">
-        <v>0.225</v>
+        <v>0.23</v>
       </c>
       <c r="E112" s="8" t="n">
-        <v>-0.0426</v>
+        <v>-0.0213</v>
       </c>
       <c r="F112" s="4" t="n">
-        <v>1394100</v>
+        <v>1917500</v>
       </c>
       <c r="G112" s="5" t="n">
-        <v>2.01</v>
+        <v>2.76</v>
       </c>
       <c r="H112" t="n">
-        <v>44.59</v>
+        <v>48.43</v>
       </c>
       <c r="I112" s="6" t="inlineStr">
         <is>
@@ -5503,7 +5503,7 @@
         </is>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.231</v>
+        <v>0.232</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0.234</v>
@@ -5519,39 +5519,39 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>0328</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>3REN</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D113" s="2" t="n">
-        <v>0.4</v>
+        <v>7.18</v>
       </c>
       <c r="E113" s="3" t="n">
-        <v>0.039</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="F113" s="4" t="n">
-        <v>1387000</v>
+        <v>1875900</v>
       </c>
       <c r="G113" s="5" t="n">
-        <v>0.7</v>
+        <v>0.24</v>
       </c>
       <c r="H113" t="n">
-        <v>56.15</v>
-      </c>
-      <c r="I113" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.84</v>
+      </c>
+      <c r="I113" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.386</v>
+        <v>7.407</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>0.391</v>
+        <v>7.723</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="7" t="inlineStr"/>
@@ -5564,39 +5564,39 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>0172</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>OCK</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D114" s="2" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="E114" s="3" t="n">
-        <v>0.0112</v>
+        <v>0.805</v>
+      </c>
+      <c r="E114" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F114" s="4" t="n">
-        <v>1385300</v>
+        <v>1870700</v>
       </c>
       <c r="G114" s="5" t="n">
-        <v>0.39</v>
+        <v>0.3</v>
       </c>
       <c r="H114" t="n">
-        <v>49.83</v>
-      </c>
-      <c r="I114" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>70.15000000000001</v>
+      </c>
+      <c r="I114" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.457</v>
+        <v>0.785</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>0.42</v>
+        <v>0.764</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="7" t="inlineStr"/>
@@ -5609,33 +5609,40 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>0475</t>
+          <t>7225</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>GBBOND</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="D115" s="2" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="E115" s="3" t="n">
-        <v>0.0455</v>
+        <v>0.2</v>
+      </c>
+      <c r="E115" s="8" t="n">
+        <v>-0.0244</v>
       </c>
       <c r="F115" s="4" t="n">
-        <v>1360200</v>
+        <v>1855100</v>
       </c>
       <c r="G115" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.4</v>
+      </c>
+      <c r="H115" t="n">
+        <v>42.79</v>
       </c>
       <c r="I115" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J115" s="2" t="n"/>
-      <c r="K115" s="2" t="n"/>
+      <c r="J115" s="2" t="n">
+        <v>0.207</v>
+      </c>
+      <c r="K115" s="2" t="n">
+        <v>0.208</v>
+      </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="7" t="inlineStr"/>
     </row>
@@ -5647,39 +5654,39 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>0056</t>
+          <t>0273</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>NCT</t>
+          <t>VLB</t>
         </is>
       </c>
       <c r="D116" s="2" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="E116" s="8" t="n">
-        <v>-0.0175</v>
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="E116" s="3" t="n">
+        <v>0.0054</v>
       </c>
       <c r="F116" s="4" t="n">
-        <v>1353400</v>
+        <v>1834800</v>
       </c>
       <c r="G116" s="5" t="n">
-        <v>0.62</v>
+        <v>1.07</v>
       </c>
       <c r="H116" t="n">
-        <v>48.28</v>
-      </c>
-      <c r="I116" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>54.68</v>
+      </c>
+      <c r="I116" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.923</v>
       </c>
       <c r="K116" s="2" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.85</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="7" t="inlineStr"/>
@@ -5692,28 +5699,28 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>3662</t>
+          <t>5337</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>MFLOUR</t>
+          <t>ECOSHOP</t>
         </is>
       </c>
       <c r="D117" s="2" t="n">
-        <v>0.6</v>
+        <v>1.46</v>
       </c>
       <c r="E117" s="3" t="n">
-        <v>0.0256</v>
+        <v>0.021</v>
       </c>
       <c r="F117" s="4" t="n">
-        <v>1331600</v>
+        <v>1798200</v>
       </c>
       <c r="G117" s="5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.39</v>
       </c>
       <c r="H117" t="n">
-        <v>40.75</v>
+        <v>49.32</v>
       </c>
       <c r="I117" s="6" t="inlineStr">
         <is>
@@ -5721,10 +5728,10 @@
         </is>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.617</v>
+        <v>1.461</v>
       </c>
       <c r="K117" s="2" t="n">
-        <v>0.635</v>
+        <v>1.469</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="7" t="inlineStr"/>
@@ -5737,39 +5744,39 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>0056</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>NCT</t>
         </is>
       </c>
       <c r="D118" s="2" t="n">
-        <v>0.92</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="E118" s="8" t="n">
-        <v>-0.0108</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="F118" s="4" t="n">
-        <v>1331100</v>
+        <v>1795400</v>
       </c>
       <c r="G118" s="5" t="n">
-        <v>0.26</v>
+        <v>0.83</v>
       </c>
       <c r="H118" t="n">
-        <v>58.88</v>
-      </c>
-      <c r="I118" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.06</v>
+      </c>
+      <c r="I118" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.907</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="K118" s="2" t="n">
-        <v>0.863</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" s="7" t="inlineStr"/>
@@ -5782,39 +5789,39 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>0373</t>
+          <t>0328</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>VERDANT</t>
+          <t>3REN</t>
         </is>
       </c>
       <c r="D119" s="2" t="n">
-        <v>0.28</v>
+        <v>0.4</v>
       </c>
       <c r="E119" s="3" t="n">
-        <v>0.0182</v>
+        <v>0.039</v>
       </c>
       <c r="F119" s="4" t="n">
-        <v>1324100</v>
+        <v>1737400</v>
       </c>
       <c r="G119" s="5" t="n">
-        <v>0.3</v>
+        <v>0.88</v>
       </c>
       <c r="H119" t="n">
-        <v>69.36</v>
-      </c>
-      <c r="I119" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.15</v>
+      </c>
+      <c r="I119" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.252</v>
+        <v>0.386</v>
       </c>
       <c r="K119" s="2" t="n">
-        <v>0.22</v>
+        <v>0.391</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="7" t="inlineStr"/>
@@ -5827,28 +5834,28 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>AWC</t>
+          <t>AMBANK</t>
         </is>
       </c>
       <c r="D120" s="2" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E120" s="10" t="n">
-        <v>0</v>
+        <v>6.09</v>
+      </c>
+      <c r="E120" s="8" t="n">
+        <v>-0.0016</v>
       </c>
       <c r="F120" s="4" t="n">
-        <v>1309700</v>
+        <v>1710600</v>
       </c>
       <c r="G120" s="5" t="n">
-        <v>0.59</v>
+        <v>0.37</v>
       </c>
       <c r="H120" t="n">
-        <v>57.68</v>
+        <v>22.87</v>
       </c>
       <c r="I120" s="6" t="inlineStr">
         <is>
@@ -5856,10 +5863,10 @@
         </is>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.62</v>
+        <v>6.473</v>
       </c>
       <c r="K120" s="2" t="n">
-        <v>0.529</v>
+        <v>6.826</v>
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="7" t="inlineStr"/>
@@ -5872,39 +5879,39 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>0277</t>
+          <t>5306</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>CLOUDPT</t>
+          <t>FFB</t>
         </is>
       </c>
       <c r="D121" s="2" t="n">
-        <v>0.515</v>
+        <v>1.79</v>
       </c>
       <c r="E121" s="3" t="n">
-        <v>0.0098</v>
+        <v>0.0229</v>
       </c>
       <c r="F121" s="4" t="n">
-        <v>1288100</v>
+        <v>1702100</v>
       </c>
       <c r="G121" s="5" t="n">
-        <v>0.79</v>
+        <v>0.58</v>
       </c>
       <c r="H121" t="n">
-        <v>62.85</v>
-      </c>
-      <c r="I121" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>30.67</v>
+      </c>
+      <c r="I121" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0.489</v>
+        <v>1.879</v>
       </c>
       <c r="K121" s="2" t="n">
-        <v>0.479</v>
+        <v>2.017</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" s="7" t="inlineStr"/>
@@ -5917,28 +5924,28 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D122" s="2" t="n">
-        <v>7.23</v>
+        <v>1.85</v>
       </c>
       <c r="E122" s="3" t="n">
-        <v>0.0154</v>
+        <v>0.0054</v>
       </c>
       <c r="F122" s="4" t="n">
-        <v>1265600</v>
+        <v>1642200</v>
       </c>
       <c r="G122" s="5" t="n">
-        <v>0.16</v>
+        <v>0.39</v>
       </c>
       <c r="H122" t="n">
-        <v>36.97</v>
+        <v>38.83</v>
       </c>
       <c r="I122" s="6" t="inlineStr">
         <is>
@@ -5946,10 +5953,10 @@
         </is>
       </c>
       <c r="J122" s="2" t="n">
-        <v>7.412</v>
+        <v>1.896</v>
       </c>
       <c r="K122" s="2" t="n">
-        <v>7.724</v>
+        <v>2.026</v>
       </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="7" t="inlineStr"/>
@@ -5962,39 +5969,39 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>6633</t>
+          <t>0172</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>LHI</t>
+          <t>OCK</t>
         </is>
       </c>
       <c r="D123" s="2" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="E123" s="10" t="n">
-        <v>0</v>
+        <v>0.455</v>
+      </c>
+      <c r="E123" s="3" t="n">
+        <v>0.0225</v>
       </c>
       <c r="F123" s="4" t="n">
-        <v>1265300</v>
+        <v>1609800</v>
       </c>
       <c r="G123" s="5" t="n">
-        <v>0.76</v>
+        <v>0.45</v>
       </c>
       <c r="H123" t="n">
-        <v>47.32</v>
-      </c>
-      <c r="I123" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>51.75</v>
+      </c>
+      <c r="I123" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J123" s="2" t="n">
-        <v>0.735</v>
+        <v>0.458</v>
       </c>
       <c r="K123" s="2" t="n">
-        <v>0.749</v>
+        <v>0.42</v>
       </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" s="7" t="inlineStr"/>
@@ -6007,28 +6014,28 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>0090</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>ELSOFT</t>
         </is>
       </c>
       <c r="D124" s="2" t="n">
-        <v>0.825</v>
-      </c>
-      <c r="E124" s="8" t="n">
-        <v>-0.0179</v>
+        <v>0.35</v>
+      </c>
+      <c r="E124" s="3" t="n">
+        <v>0.09369999999999999</v>
       </c>
       <c r="F124" s="4" t="n">
-        <v>1250700</v>
+        <v>1475300</v>
       </c>
       <c r="G124" s="5" t="n">
-        <v>0.19</v>
+        <v>2.16</v>
       </c>
       <c r="H124" t="n">
-        <v>70.67</v>
+        <v>76.87</v>
       </c>
       <c r="I124" s="9" t="inlineStr">
         <is>
@@ -6036,10 +6043,10 @@
         </is>
       </c>
       <c r="J124" s="2" t="n">
-        <v>0.75</v>
+        <v>0.284</v>
       </c>
       <c r="K124" s="2" t="n">
-        <v>0.663</v>
+        <v>0.272</v>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" s="7" t="inlineStr"/>
@@ -6052,28 +6059,28 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>0219</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>RL</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D125" s="2" t="n">
-        <v>0.295</v>
+        <v>0.92</v>
       </c>
       <c r="E125" s="8" t="n">
-        <v>-0.0167</v>
+        <v>-0.0108</v>
       </c>
       <c r="F125" s="4" t="n">
-        <v>1216200</v>
+        <v>1461700</v>
       </c>
       <c r="G125" s="5" t="n">
-        <v>0.19</v>
+        <v>0.28</v>
       </c>
       <c r="H125" t="n">
-        <v>40.45</v>
+        <v>58.88</v>
       </c>
       <c r="I125" s="6" t="inlineStr">
         <is>
@@ -6081,10 +6088,10 @@
         </is>
       </c>
       <c r="J125" s="2" t="n">
-        <v>0.304</v>
+        <v>0.907</v>
       </c>
       <c r="K125" s="2" t="n">
-        <v>0.299</v>
+        <v>0.863</v>
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" s="7" t="inlineStr"/>
@@ -6097,12 +6104,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>AWC</t>
         </is>
       </c>
       <c r="D126" s="2" t="n">
@@ -6112,24 +6119,24 @@
         <v>0.007900000000000001</v>
       </c>
       <c r="F126" s="4" t="n">
-        <v>1171100</v>
+        <v>1371700</v>
       </c>
       <c r="G126" s="5" t="n">
-        <v>0.3</v>
+        <v>0.62</v>
       </c>
       <c r="H126" t="n">
-        <v>63.45</v>
-      </c>
-      <c r="I126" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>58.57</v>
+      </c>
+      <c r="I126" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J126" s="2" t="n">
-        <v>0.596</v>
+        <v>0.62</v>
       </c>
       <c r="K126" s="2" t="n">
-        <v>0.582</v>
+        <v>0.529</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="7" t="inlineStr"/>
@@ -6142,28 +6149,28 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>7081</t>
+          <t>3662</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>MFLOUR</t>
         </is>
       </c>
       <c r="D127" s="2" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="E127" s="8" t="n">
-        <v>-0.0109</v>
+        <v>0.6</v>
+      </c>
+      <c r="E127" s="3" t="n">
+        <v>0.0256</v>
       </c>
       <c r="F127" s="4" t="n">
-        <v>1165100</v>
+        <v>1370300</v>
       </c>
       <c r="G127" s="5" t="n">
-        <v>0.49</v>
+        <v>0.58</v>
       </c>
       <c r="H127" t="n">
-        <v>20.11</v>
+        <v>40.75</v>
       </c>
       <c r="I127" s="6" t="inlineStr">
         <is>
@@ -6171,10 +6178,10 @@
         </is>
       </c>
       <c r="J127" s="2" t="n">
-        <v>1.036</v>
+        <v>0.617</v>
       </c>
       <c r="K127" s="2" t="n">
-        <v>1.119</v>
+        <v>0.635</v>
       </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" s="7" t="inlineStr"/>
@@ -6187,40 +6194,33 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>0475</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>GBBOND</t>
         </is>
       </c>
       <c r="D128" s="2" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="E128" s="8" t="n">
-        <v>-0.0034</v>
+        <v>0.23</v>
+      </c>
+      <c r="E128" s="3" t="n">
+        <v>0.0455</v>
       </c>
       <c r="F128" s="4" t="n">
-        <v>1120700</v>
+        <v>1365600</v>
       </c>
       <c r="G128" s="5" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="H128" t="n">
-        <v>44.13</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I128" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J128" s="2" t="n">
-        <v>2.973</v>
-      </c>
-      <c r="K128" s="2" t="n">
-        <v>3.033</v>
-      </c>
+      <c r="J128" s="2" t="n"/>
+      <c r="K128" s="2" t="n"/>
       <c r="L128" t="inlineStr"/>
       <c r="M128" s="7" t="inlineStr"/>
     </row>
@@ -6232,28 +6232,28 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D129" s="2" t="n">
-        <v>0.605</v>
+        <v>0.64</v>
       </c>
       <c r="E129" s="3" t="n">
-        <v>0.0168</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="F129" s="4" t="n">
-        <v>1092300</v>
+        <v>1342900</v>
       </c>
       <c r="G129" s="5" t="n">
-        <v>0.19</v>
+        <v>0.35</v>
       </c>
       <c r="H129" t="n">
-        <v>70.43000000000001</v>
+        <v>63.45</v>
       </c>
       <c r="I129" s="9" t="inlineStr">
         <is>
@@ -6261,10 +6261,10 @@
         </is>
       </c>
       <c r="J129" s="2" t="n">
-        <v>0.55</v>
+        <v>0.596</v>
       </c>
       <c r="K129" s="2" t="n">
-        <v>0.493</v>
+        <v>0.582</v>
       </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" s="7" t="inlineStr"/>
@@ -6277,39 +6277,39 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D130" s="2" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="E130" s="3" t="n">
-        <v>0.0103</v>
+        <v>0.83</v>
+      </c>
+      <c r="E130" s="8" t="n">
+        <v>-0.0119</v>
       </c>
       <c r="F130" s="4" t="n">
-        <v>1084900</v>
+        <v>1337500</v>
       </c>
       <c r="G130" s="5" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="H130" t="n">
-        <v>28.72</v>
-      </c>
-      <c r="I130" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>72.09</v>
+      </c>
+      <c r="I130" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J130" s="2" t="n">
-        <v>0.524</v>
+        <v>0.75</v>
       </c>
       <c r="K130" s="2" t="n">
-        <v>0.571</v>
+        <v>0.663</v>
       </c>
       <c r="L130" t="inlineStr"/>
       <c r="M130" s="7" t="inlineStr"/>
@@ -6322,28 +6322,28 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>0450</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>MFGROUP</t>
+          <t>SKYECHIP</t>
         </is>
       </c>
       <c r="D131" s="2" t="n">
-        <v>0.265</v>
+        <v>2.92</v>
       </c>
       <c r="E131" s="8" t="n">
-        <v>-0.0185</v>
+        <v>-0.0034</v>
       </c>
       <c r="F131" s="4" t="n">
-        <v>1082000</v>
+        <v>1330300</v>
       </c>
       <c r="G131" s="5" t="n">
-        <v>1.11</v>
+        <v>0.42</v>
       </c>
       <c r="H131" t="n">
-        <v>54.17</v>
+        <v>44.13</v>
       </c>
       <c r="I131" s="6" t="inlineStr">
         <is>
@@ -6351,10 +6351,10 @@
         </is>
       </c>
       <c r="J131" s="2" t="n">
-        <v>0.262</v>
+        <v>2.973</v>
       </c>
       <c r="K131" s="2" t="n">
-        <v>0.264</v>
+        <v>3.033</v>
       </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" s="7" t="inlineStr"/>
@@ -6367,39 +6367,39 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>0373</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>ATECH</t>
+          <t>VERDANT</t>
         </is>
       </c>
       <c r="D132" s="2" t="n">
-        <v>0.8</v>
+        <v>0.28</v>
       </c>
       <c r="E132" s="3" t="n">
-        <v>0.0127</v>
+        <v>0.0182</v>
       </c>
       <c r="F132" s="4" t="n">
-        <v>1080000</v>
+        <v>1324100</v>
       </c>
       <c r="G132" s="5" t="n">
-        <v>0.59</v>
+        <v>0.3</v>
       </c>
       <c r="H132" t="n">
-        <v>58.78</v>
-      </c>
-      <c r="I132" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>69.36</v>
+      </c>
+      <c r="I132" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J132" s="2" t="n">
-        <v>0.77</v>
+        <v>0.252</v>
       </c>
       <c r="K132" s="2" t="n">
-        <v>0.761</v>
+        <v>0.22</v>
       </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" s="7" t="inlineStr"/>
@@ -6412,28 +6412,28 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>7160</t>
+          <t>0277</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>PENTA</t>
+          <t>CLOUDPT</t>
         </is>
       </c>
       <c r="D133" s="2" t="n">
-        <v>5.89</v>
+        <v>0.515</v>
       </c>
       <c r="E133" s="3" t="n">
-        <v>0.0051</v>
+        <v>0.0098</v>
       </c>
       <c r="F133" s="4" t="n">
-        <v>1052500</v>
+        <v>1316100</v>
       </c>
       <c r="G133" s="5" t="n">
-        <v>0.31</v>
+        <v>0.8</v>
       </c>
       <c r="H133" t="n">
-        <v>62.9</v>
+        <v>62.85</v>
       </c>
       <c r="I133" s="9" t="inlineStr">
         <is>
@@ -6441,10 +6441,10 @@
         </is>
       </c>
       <c r="J133" s="2" t="n">
-        <v>5.477</v>
+        <v>0.489</v>
       </c>
       <c r="K133" s="2" t="n">
-        <v>5.356</v>
+        <v>0.479</v>
       </c>
       <c r="L133" t="inlineStr"/>
       <c r="M133" s="7" t="inlineStr"/>
@@ -6457,28 +6457,28 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>MAHSING</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D134" s="2" t="n">
-        <v>0.95</v>
+        <v>0.495</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0.0053</v>
+        <v>0.0206</v>
       </c>
       <c r="F134" s="4" t="n">
-        <v>1047600</v>
+        <v>1293400</v>
       </c>
       <c r="G134" s="5" t="n">
-        <v>0.27</v>
+        <v>0.18</v>
       </c>
       <c r="H134" t="n">
-        <v>30.03</v>
+        <v>31.76</v>
       </c>
       <c r="I134" s="6" t="inlineStr">
         <is>
@@ -6486,10 +6486,10 @@
         </is>
       </c>
       <c r="J134" s="2" t="n">
-        <v>0.996</v>
+        <v>0.524</v>
       </c>
       <c r="K134" s="2" t="n">
-        <v>1.066</v>
+        <v>0.571</v>
       </c>
       <c r="L134" t="inlineStr"/>
       <c r="M134" s="7" t="inlineStr"/>
@@ -6502,28 +6502,28 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>5053</t>
+          <t>7081</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>OSK</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D135" s="2" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="E135" s="3" t="n">
-        <v>0.0311</v>
+        <v>0.92</v>
+      </c>
+      <c r="E135" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F135" s="4" t="n">
-        <v>1030000</v>
+        <v>1258400</v>
       </c>
       <c r="G135" s="5" t="n">
-        <v>0.72</v>
+        <v>0.53</v>
       </c>
       <c r="H135" t="n">
-        <v>29.21</v>
+        <v>20.91</v>
       </c>
       <c r="I135" s="6" t="inlineStr">
         <is>
@@ -6531,10 +6531,10 @@
         </is>
       </c>
       <c r="J135" s="2" t="n">
-        <v>1.786</v>
+        <v>1.037</v>
       </c>
       <c r="K135" s="2" t="n">
-        <v>1.919</v>
+        <v>1.119</v>
       </c>
       <c r="L135" t="inlineStr"/>
       <c r="M135" s="7" t="inlineStr"/>
@@ -6547,28 +6547,28 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>7233</t>
+          <t>5331</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>DUFU</t>
+          <t>PGLOBAL</t>
         </is>
       </c>
       <c r="D136" s="2" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="E136" s="8" t="n">
-        <v>-0.0154</v>
+        <v>0.59</v>
+      </c>
+      <c r="E136" s="3" t="n">
+        <v>0.0536</v>
       </c>
       <c r="F136" s="4" t="n">
-        <v>1002300</v>
+        <v>1250100</v>
       </c>
       <c r="G136" s="5" t="n">
-        <v>0.32</v>
+        <v>2.69</v>
       </c>
       <c r="H136" t="n">
-        <v>61.36</v>
+        <v>73.19</v>
       </c>
       <c r="I136" s="9" t="inlineStr">
         <is>
@@ -6576,10 +6576,10 @@
         </is>
       </c>
       <c r="J136" s="2" t="n">
-        <v>3</v>
+        <v>0.541</v>
       </c>
       <c r="K136" s="2" t="n">
-        <v>2.804</v>
+        <v>0.511</v>
       </c>
       <c r="L136" t="inlineStr"/>
       <c r="M136" s="7" t="inlineStr"/>
@@ -6592,28 +6592,28 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>5162</t>
+          <t>7160</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>VSTECS</t>
+          <t>PENTA</t>
         </is>
       </c>
       <c r="D137" s="2" t="n">
-        <v>1.73</v>
+        <v>5.89</v>
       </c>
       <c r="E137" s="3" t="n">
-        <v>0.0359</v>
+        <v>0.0051</v>
       </c>
       <c r="F137" s="4" t="n">
-        <v>999300</v>
+        <v>1245500</v>
       </c>
       <c r="G137" s="5" t="n">
-        <v>0.59</v>
+        <v>0.36</v>
       </c>
       <c r="H137" t="n">
-        <v>57.25</v>
+        <v>62.9</v>
       </c>
       <c r="I137" s="9" t="inlineStr">
         <is>
@@ -6621,10 +6621,10 @@
         </is>
       </c>
       <c r="J137" s="2" t="n">
-        <v>1.664</v>
+        <v>5.477</v>
       </c>
       <c r="K137" s="2" t="n">
-        <v>1.678</v>
+        <v>5.356</v>
       </c>
       <c r="L137" t="inlineStr"/>
       <c r="M137" s="7" t="inlineStr"/>
@@ -6637,39 +6637,39 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D138" s="2" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="E138" s="8" t="n">
-        <v>-0.0068</v>
+        <v>0.605</v>
+      </c>
+      <c r="E138" s="3" t="n">
+        <v>0.0168</v>
       </c>
       <c r="F138" s="4" t="n">
-        <v>990200</v>
+        <v>1233700</v>
       </c>
       <c r="G138" s="5" t="n">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="H138" t="n">
-        <v>47.73</v>
-      </c>
-      <c r="I138" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>70.43000000000001</v>
+      </c>
+      <c r="I138" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J138" s="2" t="n">
-        <v>2.968</v>
+        <v>0.55</v>
       </c>
       <c r="K138" s="2" t="n">
-        <v>2.819</v>
+        <v>0.493</v>
       </c>
       <c r="L138" t="inlineStr"/>
       <c r="M138" s="7" t="inlineStr"/>
@@ -6682,28 +6682,28 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>0271</t>
+          <t>0219</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>WELLS</t>
+          <t>RL</t>
         </is>
       </c>
       <c r="D139" s="2" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="E139" s="3" t="n">
-        <v>0.0291</v>
+        <v>0.295</v>
+      </c>
+      <c r="E139" s="8" t="n">
+        <v>-0.0167</v>
       </c>
       <c r="F139" s="4" t="n">
-        <v>963600</v>
+        <v>1220800</v>
       </c>
       <c r="G139" s="5" t="n">
-        <v>0.87</v>
+        <v>0.19</v>
       </c>
       <c r="H139" t="n">
-        <v>26.64</v>
+        <v>40.45</v>
       </c>
       <c r="I139" s="6" t="inlineStr">
         <is>
@@ -6711,10 +6711,10 @@
         </is>
       </c>
       <c r="J139" s="2" t="n">
-        <v>0.582</v>
+        <v>0.304</v>
       </c>
       <c r="K139" s="2" t="n">
-        <v>0.622</v>
+        <v>0.299</v>
       </c>
       <c r="L139" t="inlineStr"/>
       <c r="M139" s="7" t="inlineStr"/>
@@ -6727,39 +6727,39 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>5180</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>CLMT</t>
         </is>
       </c>
       <c r="D140" s="2" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="E140" s="8" t="n">
-        <v>-0.0035</v>
+        <v>0.555</v>
+      </c>
+      <c r="E140" s="3" t="n">
+        <v>0.0091</v>
       </c>
       <c r="F140" s="4" t="n">
-        <v>915000</v>
+        <v>1203100</v>
       </c>
       <c r="G140" s="5" t="n">
-        <v>0.1</v>
+        <v>0.29</v>
       </c>
       <c r="H140" t="n">
-        <v>55.48</v>
-      </c>
-      <c r="I140" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.64</v>
+      </c>
+      <c r="I140" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J140" s="2" t="n">
-        <v>2.774</v>
+        <v>0.571</v>
       </c>
       <c r="K140" s="2" t="n">
-        <v>2.599</v>
+        <v>0.582</v>
       </c>
       <c r="L140" t="inlineStr"/>
       <c r="M140" s="7" t="inlineStr"/>
@@ -6772,39 +6772,39 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>4863</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>TM</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D141" s="2" t="n">
-        <v>7.86</v>
+        <v>2.86</v>
       </c>
       <c r="E141" s="8" t="n">
-        <v>-0.0013</v>
+        <v>-0.0205</v>
       </c>
       <c r="F141" s="4" t="n">
-        <v>902700</v>
+        <v>1183700</v>
       </c>
       <c r="G141" s="5" t="n">
-        <v>0.3</v>
+        <v>0.26</v>
       </c>
       <c r="H141" t="n">
-        <v>48.99</v>
-      </c>
-      <c r="I141" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.9</v>
+      </c>
+      <c r="I141" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J141" s="2" t="n">
-        <v>7.889</v>
+        <v>2.964</v>
       </c>
       <c r="K141" s="2" t="n">
-        <v>7.849</v>
+        <v>2.819</v>
       </c>
       <c r="L141" t="inlineStr"/>
       <c r="M141" s="7" t="inlineStr"/>
@@ -6817,28 +6817,28 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>5180</t>
+          <t>0369</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>CLMT</t>
+          <t>JSSOLAR</t>
         </is>
       </c>
       <c r="D142" s="2" t="n">
-        <v>0.555</v>
+        <v>0.25</v>
       </c>
       <c r="E142" s="3" t="n">
-        <v>0.0091</v>
+        <v>0.0638</v>
       </c>
       <c r="F142" s="4" t="n">
-        <v>868600</v>
+        <v>1155900</v>
       </c>
       <c r="G142" s="5" t="n">
-        <v>0.21</v>
+        <v>0.73</v>
       </c>
       <c r="H142" t="n">
-        <v>35.64</v>
+        <v>60.92</v>
       </c>
       <c r="I142" s="6" t="inlineStr">
         <is>
@@ -6846,10 +6846,10 @@
         </is>
       </c>
       <c r="J142" s="2" t="n">
-        <v>0.571</v>
+        <v>0.232</v>
       </c>
       <c r="K142" s="2" t="n">
-        <v>0.582</v>
+        <v>0.208</v>
       </c>
       <c r="L142" t="inlineStr"/>
       <c r="M142" s="7" t="inlineStr"/>
@@ -6862,28 +6862,28 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>0223</t>
+          <t>0337</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>SAMAIDEN</t>
+          <t>SET</t>
         </is>
       </c>
       <c r="D143" s="2" t="n">
-        <v>3.05</v>
+        <v>0.245</v>
       </c>
       <c r="E143" s="3" t="n">
-        <v>0.0133</v>
+        <v>0.0426</v>
       </c>
       <c r="F143" s="4" t="n">
-        <v>857300</v>
+        <v>1145000</v>
       </c>
       <c r="G143" s="5" t="n">
-        <v>0.21</v>
+        <v>0.67</v>
       </c>
       <c r="H143" t="n">
-        <v>69.42</v>
+        <v>55.55</v>
       </c>
       <c r="I143" s="9" t="inlineStr">
         <is>
@@ -6891,10 +6891,10 @@
         </is>
       </c>
       <c r="J143" s="2" t="n">
-        <v>2.693</v>
+        <v>0.237</v>
       </c>
       <c r="K143" s="2" t="n">
-        <v>2.043</v>
+        <v>0.243</v>
       </c>
       <c r="L143" t="inlineStr"/>
       <c r="M143" s="7" t="inlineStr"/>
@@ -6907,28 +6907,28 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>5053</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>MBSB</t>
+          <t>OSK</t>
         </is>
       </c>
       <c r="D144" s="2" t="n">
-        <v>0.535</v>
+        <v>1.65</v>
       </c>
       <c r="E144" s="3" t="n">
-        <v>0.009399999999999999</v>
+        <v>0.0248</v>
       </c>
       <c r="F144" s="4" t="n">
-        <v>854500</v>
+        <v>1127000</v>
       </c>
       <c r="G144" s="5" t="n">
-        <v>0.24</v>
+        <v>0.78</v>
       </c>
       <c r="H144" t="n">
-        <v>35.78</v>
+        <v>27.42</v>
       </c>
       <c r="I144" s="6" t="inlineStr">
         <is>
@@ -6936,10 +6936,10 @@
         </is>
       </c>
       <c r="J144" s="2" t="n">
-        <v>0.552</v>
+        <v>1.786</v>
       </c>
       <c r="K144" s="2" t="n">
-        <v>0.582</v>
+        <v>1.919</v>
       </c>
       <c r="L144" t="inlineStr"/>
       <c r="M144" s="7" t="inlineStr"/>
@@ -6952,28 +6952,28 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>0456</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>KPJ</t>
+          <t>MMCS</t>
         </is>
       </c>
       <c r="D145" s="2" t="n">
-        <v>2.53</v>
+        <v>0.345</v>
       </c>
       <c r="E145" s="3" t="n">
-        <v>0.004</v>
+        <v>0.0299</v>
       </c>
       <c r="F145" s="4" t="n">
-        <v>839500</v>
+        <v>1126300</v>
       </c>
       <c r="G145" s="5" t="n">
-        <v>0.16</v>
+        <v>0.88</v>
       </c>
       <c r="H145" t="n">
-        <v>37.16</v>
+        <v>41.57</v>
       </c>
       <c r="I145" s="6" t="inlineStr">
         <is>
@@ -6981,10 +6981,10 @@
         </is>
       </c>
       <c r="J145" s="2" t="n">
-        <v>2.615</v>
+        <v>0.349</v>
       </c>
       <c r="K145" s="2" t="n">
-        <v>2.79</v>
+        <v>0.383</v>
       </c>
       <c r="L145" t="inlineStr"/>
       <c r="M145" s="7" t="inlineStr"/>
@@ -6997,39 +6997,39 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>ALPHA</t>
         </is>
       </c>
       <c r="D146" s="2" t="n">
-        <v>1.37</v>
+        <v>0.275</v>
       </c>
       <c r="E146" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F146" s="4" t="n">
-        <v>833300</v>
+        <v>1122300</v>
       </c>
       <c r="G146" s="5" t="n">
-        <v>0.25</v>
+        <v>0.47</v>
       </c>
       <c r="H146" t="n">
-        <v>72.14</v>
-      </c>
-      <c r="I146" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.87</v>
+      </c>
+      <c r="I146" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J146" s="2" t="n">
-        <v>1.237</v>
+        <v>0.259</v>
       </c>
       <c r="K146" s="2" t="n">
-        <v>1.008</v>
+        <v>0.257</v>
       </c>
       <c r="L146" t="inlineStr"/>
       <c r="M146" s="7" t="inlineStr"/>
@@ -7042,39 +7042,39 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D147" s="2" t="n">
-        <v>0.735</v>
-      </c>
-      <c r="E147" s="3" t="n">
-        <v>0.0068</v>
+        <v>2.82</v>
+      </c>
+      <c r="E147" s="8" t="n">
+        <v>-0.0035</v>
       </c>
       <c r="F147" s="4" t="n">
-        <v>832400</v>
+        <v>1085900</v>
       </c>
       <c r="G147" s="5" t="n">
-        <v>0.26</v>
+        <v>0.12</v>
       </c>
       <c r="H147" t="n">
-        <v>44.96</v>
-      </c>
-      <c r="I147" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.48</v>
+      </c>
+      <c r="I147" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J147" s="2" t="n">
-        <v>0.76</v>
+        <v>2.774</v>
       </c>
       <c r="K147" s="2" t="n">
-        <v>0.747</v>
+        <v>2.599</v>
       </c>
       <c r="L147" t="inlineStr"/>
       <c r="M147" s="7" t="inlineStr"/>
@@ -7087,39 +7087,39 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>0450</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>MFGROUP</t>
         </is>
       </c>
       <c r="D148" s="2" t="n">
-        <v>0.765</v>
-      </c>
-      <c r="E148" s="3" t="n">
-        <v>0.0066</v>
+        <v>0.265</v>
+      </c>
+      <c r="E148" s="8" t="n">
+        <v>-0.0185</v>
       </c>
       <c r="F148" s="4" t="n">
-        <v>826400</v>
+        <v>1082000</v>
       </c>
       <c r="G148" s="5" t="n">
-        <v>0.45</v>
+        <v>1.11</v>
       </c>
       <c r="H148" t="n">
-        <v>62.31</v>
-      </c>
-      <c r="I148" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>54.17</v>
+      </c>
+      <c r="I148" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J148" s="2" t="n">
-        <v>0.711</v>
+        <v>0.262</v>
       </c>
       <c r="K148" s="2" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.264</v>
       </c>
       <c r="L148" t="inlineStr"/>
       <c r="M148" s="7" t="inlineStr"/>
@@ -7132,28 +7132,28 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>5323</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>JPG</t>
+          <t>MAHSING</t>
         </is>
       </c>
       <c r="D149" s="2" t="n">
-        <v>1.78</v>
+        <v>0.95</v>
       </c>
       <c r="E149" s="3" t="n">
-        <v>0.023</v>
+        <v>0.0053</v>
       </c>
       <c r="F149" s="4" t="n">
-        <v>800600</v>
+        <v>1080400</v>
       </c>
       <c r="G149" s="5" t="n">
-        <v>0.13</v>
+        <v>0.28</v>
       </c>
       <c r="H149" t="n">
-        <v>41.73</v>
+        <v>30.03</v>
       </c>
       <c r="I149" s="6" t="inlineStr">
         <is>
@@ -7161,10 +7161,10 @@
         </is>
       </c>
       <c r="J149" s="2" t="n">
-        <v>1.825</v>
+        <v>0.996</v>
       </c>
       <c r="K149" s="2" t="n">
-        <v>1.927</v>
+        <v>1.066</v>
       </c>
       <c r="L149" t="inlineStr"/>
       <c r="M149" s="7" t="inlineStr"/>
@@ -7177,39 +7177,39 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>0217</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>PWRWELL</t>
+          <t>DUFU</t>
         </is>
       </c>
       <c r="D150" s="2" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="E150" s="3" t="n">
-        <v>0.008500000000000001</v>
+        <v>3.19</v>
+      </c>
+      <c r="E150" s="8" t="n">
+        <v>-0.0154</v>
       </c>
       <c r="F150" s="4" t="n">
-        <v>797300</v>
+        <v>1066600</v>
       </c>
       <c r="G150" s="5" t="n">
-        <v>0.19</v>
+        <v>0.34</v>
       </c>
       <c r="H150" t="n">
-        <v>59.85</v>
-      </c>
-      <c r="I150" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.36</v>
+      </c>
+      <c r="I150" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J150" s="2" t="n">
-        <v>1.153</v>
+        <v>3</v>
       </c>
       <c r="K150" s="2" t="n">
-        <v>1.066</v>
+        <v>2.804</v>
       </c>
       <c r="L150" t="inlineStr"/>
       <c r="M150" s="7" t="inlineStr"/>
@@ -7222,39 +7222,39 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>5212</t>
+          <t>5162</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>PAVREIT</t>
+          <t>VSTECS</t>
         </is>
       </c>
       <c r="D151" s="2" t="n">
-        <v>1.55</v>
+        <v>1.72</v>
       </c>
       <c r="E151" s="3" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.0299</v>
       </c>
       <c r="F151" s="4" t="n">
-        <v>783600</v>
+        <v>1041200</v>
       </c>
       <c r="G151" s="5" t="n">
-        <v>0.19</v>
+        <v>0.61</v>
       </c>
       <c r="H151" t="n">
-        <v>45.12</v>
-      </c>
-      <c r="I151" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.36</v>
+      </c>
+      <c r="I151" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J151" s="2" t="n">
-        <v>1.562</v>
+        <v>1.663</v>
       </c>
       <c r="K151" s="2" t="n">
-        <v>1.62</v>
+        <v>1.678</v>
       </c>
       <c r="L151" t="inlineStr"/>
       <c r="M151" s="7" t="inlineStr"/>
@@ -7267,39 +7267,39 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>0388</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>SEMICO</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D152" s="2" t="n">
-        <v>0.615</v>
-      </c>
-      <c r="E152" s="10" t="n">
-        <v>0</v>
+        <v>1.89</v>
+      </c>
+      <c r="E152" s="8" t="n">
+        <v>-0.0053</v>
       </c>
       <c r="F152" s="4" t="n">
-        <v>783100</v>
+        <v>1040400</v>
       </c>
       <c r="G152" s="5" t="n">
-        <v>0.27</v>
+        <v>0.16</v>
       </c>
       <c r="H152" t="n">
-        <v>59.01</v>
-      </c>
-      <c r="I152" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.98</v>
+      </c>
+      <c r="I152" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J152" s="2" t="n">
-        <v>0.612</v>
+        <v>1.927</v>
       </c>
       <c r="K152" s="2" t="n">
-        <v>0.598</v>
+        <v>1.957</v>
       </c>
       <c r="L152" t="inlineStr"/>
       <c r="M152" s="7" t="inlineStr"/>
@@ -7312,39 +7312,39 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>0185</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>SEG</t>
+          <t>HSSEB</t>
         </is>
       </c>
       <c r="D153" s="2" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E153" s="8" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.5</v>
+      </c>
+      <c r="E153" s="3" t="n">
+        <v>0.1364</v>
       </c>
       <c r="F153" s="4" t="n">
-        <v>725100</v>
+        <v>1027200</v>
       </c>
       <c r="G153" s="5" t="n">
-        <v>0.57</v>
+        <v>7.41</v>
       </c>
       <c r="H153" t="n">
-        <v>37.72</v>
-      </c>
-      <c r="I153" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.28</v>
+      </c>
+      <c r="I153" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J153" s="2" t="n">
-        <v>0.632</v>
+        <v>0.469</v>
       </c>
       <c r="K153" s="2" t="n">
-        <v>0.63</v>
+        <v>0.498</v>
       </c>
       <c r="L153" t="inlineStr"/>
       <c r="M153" s="7" t="inlineStr"/>
@@ -7357,39 +7357,39 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>5331</t>
+          <t>5878</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>PGLOBAL</t>
+          <t>KPJ</t>
         </is>
       </c>
       <c r="D154" s="2" t="n">
-        <v>0.575</v>
-      </c>
-      <c r="E154" s="3" t="n">
-        <v>0.0268</v>
+        <v>2.52</v>
+      </c>
+      <c r="E154" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F154" s="4" t="n">
-        <v>706700</v>
+        <v>966800</v>
       </c>
       <c r="G154" s="5" t="n">
-        <v>1.52</v>
+        <v>0.18</v>
       </c>
       <c r="H154" t="n">
-        <v>69.77</v>
-      </c>
-      <c r="I154" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.88</v>
+      </c>
+      <c r="I154" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J154" s="2" t="n">
-        <v>0.539</v>
+        <v>2.614</v>
       </c>
       <c r="K154" s="2" t="n">
-        <v>0.511</v>
+        <v>2.79</v>
       </c>
       <c r="L154" t="inlineStr"/>
       <c r="M154" s="7" t="inlineStr"/>
@@ -7402,28 +7402,28 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>0271</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>WELLS</t>
         </is>
       </c>
       <c r="D155" s="2" t="n">
-        <v>1.76</v>
+        <v>0.53</v>
       </c>
       <c r="E155" s="3" t="n">
-        <v>0.005699999999999999</v>
+        <v>0.0291</v>
       </c>
       <c r="F155" s="4" t="n">
-        <v>695900</v>
+        <v>963600</v>
       </c>
       <c r="G155" s="5" t="n">
-        <v>0.14</v>
+        <v>0.87</v>
       </c>
       <c r="H155" t="n">
-        <v>50.39</v>
+        <v>26.64</v>
       </c>
       <c r="I155" s="6" t="inlineStr">
         <is>
@@ -7431,10 +7431,10 @@
         </is>
       </c>
       <c r="J155" s="2" t="n">
-        <v>1.752</v>
+        <v>0.582</v>
       </c>
       <c r="K155" s="2" t="n">
-        <v>1.778</v>
+        <v>0.622</v>
       </c>
       <c r="L155" t="inlineStr"/>
       <c r="M155" s="7" t="inlineStr"/>
@@ -7447,28 +7447,28 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>AMBANK</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D156" s="2" t="n">
-        <v>6.09</v>
-      </c>
-      <c r="E156" s="8" t="n">
-        <v>-0.0016</v>
+        <v>1.76</v>
+      </c>
+      <c r="E156" s="3" t="n">
+        <v>0.005699999999999999</v>
       </c>
       <c r="F156" s="4" t="n">
-        <v>692300</v>
+        <v>956200</v>
       </c>
       <c r="G156" s="5" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="H156" t="n">
-        <v>22.87</v>
+        <v>50.39</v>
       </c>
       <c r="I156" s="6" t="inlineStr">
         <is>
@@ -7476,10 +7476,10 @@
         </is>
       </c>
       <c r="J156" s="2" t="n">
-        <v>6.473</v>
+        <v>1.752</v>
       </c>
       <c r="K156" s="2" t="n">
-        <v>6.826</v>
+        <v>1.778</v>
       </c>
       <c r="L156" t="inlineStr"/>
       <c r="M156" s="7" t="inlineStr"/>
@@ -7492,39 +7492,39 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>0340</t>
+          <t>0167</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>NORTHERN</t>
+          <t>MCLEAN</t>
         </is>
       </c>
       <c r="D157" s="2" t="n">
-        <v>1.23</v>
+        <v>0.74</v>
       </c>
       <c r="E157" s="3" t="n">
-        <v>0.025</v>
+        <v>0.0137</v>
       </c>
       <c r="F157" s="4" t="n">
-        <v>676100</v>
+        <v>922600</v>
       </c>
       <c r="G157" s="5" t="n">
-        <v>0.09</v>
+        <v>0.29</v>
       </c>
       <c r="H157" t="n">
-        <v>67.31999999999999</v>
-      </c>
-      <c r="I157" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.05</v>
+      </c>
+      <c r="I157" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J157" s="2" t="n">
-        <v>1.081</v>
+        <v>0.761</v>
       </c>
       <c r="K157" s="2" t="n">
-        <v>0.83</v>
+        <v>0.747</v>
       </c>
       <c r="L157" t="inlineStr"/>
       <c r="M157" s="7" t="inlineStr"/>
@@ -7537,39 +7537,39 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>0223</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>SAMAIDEN</t>
         </is>
       </c>
       <c r="D158" s="2" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="E158" s="10" t="n">
-        <v>0</v>
+        <v>3.04</v>
+      </c>
+      <c r="E158" s="3" t="n">
+        <v>0.01</v>
       </c>
       <c r="F158" s="4" t="n">
-        <v>665600</v>
+        <v>903500</v>
       </c>
       <c r="G158" s="5" t="n">
-        <v>0.1</v>
+        <v>0.22</v>
       </c>
       <c r="H158" t="n">
-        <v>43.39</v>
-      </c>
-      <c r="I158" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>69.19</v>
+      </c>
+      <c r="I158" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J158" s="2" t="n">
-        <v>1.927</v>
+        <v>2.692</v>
       </c>
       <c r="K158" s="2" t="n">
-        <v>1.957</v>
+        <v>2.042</v>
       </c>
       <c r="L158" t="inlineStr"/>
       <c r="M158" s="7" t="inlineStr"/>
@@ -7582,28 +7582,28 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>5212</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>PAVREIT</t>
         </is>
       </c>
       <c r="D159" s="2" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="E159" s="8" t="n">
-        <v>-0.0225</v>
+        <v>1.57</v>
+      </c>
+      <c r="E159" s="3" t="n">
+        <v>0.0195</v>
       </c>
       <c r="F159" s="4" t="n">
-        <v>644900</v>
+        <v>895100</v>
       </c>
       <c r="G159" s="5" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="H159" t="n">
-        <v>49.02</v>
+        <v>49.18</v>
       </c>
       <c r="I159" s="6" t="inlineStr">
         <is>
@@ -7611,10 +7611,10 @@
         </is>
       </c>
       <c r="J159" s="2" t="n">
-        <v>2.188</v>
+        <v>1.564</v>
       </c>
       <c r="K159" s="2" t="n">
-        <v>2.127</v>
+        <v>1.62</v>
       </c>
       <c r="L159" t="inlineStr"/>
       <c r="M159" s="7" t="inlineStr"/>
@@ -7627,28 +7627,28 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>5211</t>
+          <t>0217</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>SUNWAY</t>
+          <t>PWRWELL</t>
         </is>
       </c>
       <c r="D160" s="2" t="n">
-        <v>4.35</v>
+        <v>1.18</v>
       </c>
       <c r="E160" s="3" t="n">
-        <v>0.009300000000000001</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="F160" s="4" t="n">
-        <v>640800</v>
+        <v>870500</v>
       </c>
       <c r="G160" s="5" t="n">
-        <v>0.12</v>
+        <v>0.21</v>
       </c>
       <c r="H160" t="n">
-        <v>33.97</v>
+        <v>59.85</v>
       </c>
       <c r="I160" s="6" t="inlineStr">
         <is>
@@ -7656,10 +7656,10 @@
         </is>
       </c>
       <c r="J160" s="2" t="n">
-        <v>4.481</v>
+        <v>1.153</v>
       </c>
       <c r="K160" s="2" t="n">
-        <v>4.817</v>
+        <v>1.066</v>
       </c>
       <c r="L160" t="inlineStr"/>
       <c r="M160" s="7" t="inlineStr"/>
@@ -7672,28 +7672,28 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>0391</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>AMBEST</t>
+          <t>MBSB</t>
         </is>
       </c>
       <c r="D161" s="2" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="E161" s="8" t="n">
-        <v>-0.0149</v>
+        <v>0.535</v>
+      </c>
+      <c r="E161" s="3" t="n">
+        <v>0.009399999999999999</v>
       </c>
       <c r="F161" s="4" t="n">
-        <v>633900</v>
+        <v>866000</v>
       </c>
       <c r="G161" s="5" t="n">
-        <v>0.22</v>
+        <v>0.24</v>
       </c>
       <c r="H161" t="n">
-        <v>48.88</v>
+        <v>35.78</v>
       </c>
       <c r="I161" s="6" t="inlineStr">
         <is>
@@ -7701,10 +7701,10 @@
         </is>
       </c>
       <c r="J161" s="2" t="n">
-        <v>1.348</v>
+        <v>0.552</v>
       </c>
       <c r="K161" s="2" t="n">
-        <v>1.235</v>
+        <v>0.582</v>
       </c>
       <c r="L161" t="inlineStr"/>
       <c r="M161" s="7" t="inlineStr"/>
@@ -7717,28 +7717,28 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>5323</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>JPG</t>
         </is>
       </c>
       <c r="D162" s="2" t="n">
-        <v>0.84</v>
+        <v>1.76</v>
       </c>
       <c r="E162" s="3" t="n">
-        <v>0.006</v>
+        <v>0.0115</v>
       </c>
       <c r="F162" s="4" t="n">
-        <v>622200</v>
+        <v>865000</v>
       </c>
       <c r="G162" s="5" t="n">
-        <v>0.2</v>
+        <v>0.14</v>
       </c>
       <c r="H162" t="n">
-        <v>59.49</v>
+        <v>38.84</v>
       </c>
       <c r="I162" s="6" t="inlineStr">
         <is>
@@ -7746,10 +7746,10 @@
         </is>
       </c>
       <c r="J162" s="2" t="n">
-        <v>0.82</v>
+        <v>1.823</v>
       </c>
       <c r="K162" s="2" t="n">
-        <v>0.756</v>
+        <v>1.927</v>
       </c>
       <c r="L162" t="inlineStr"/>
       <c r="M162" s="7" t="inlineStr"/>
@@ -7762,28 +7762,28 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>0097</t>
+          <t>0146</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>VITROX</t>
+          <t>JFTECH</t>
         </is>
       </c>
       <c r="D163" s="2" t="n">
-        <v>11.08</v>
+        <v>0.765</v>
       </c>
       <c r="E163" s="3" t="n">
-        <v>0.0073</v>
+        <v>0.0066</v>
       </c>
       <c r="F163" s="4" t="n">
-        <v>619700</v>
+        <v>839800</v>
       </c>
       <c r="G163" s="5" t="n">
-        <v>0.19</v>
+        <v>0.46</v>
       </c>
       <c r="H163" t="n">
-        <v>74.28</v>
+        <v>62.31</v>
       </c>
       <c r="I163" s="9" t="inlineStr">
         <is>
@@ -7791,10 +7791,10 @@
         </is>
       </c>
       <c r="J163" s="2" t="n">
-        <v>10.242</v>
+        <v>0.711</v>
       </c>
       <c r="K163" s="2" t="n">
-        <v>9.504</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="L163" t="inlineStr"/>
       <c r="M163" s="7" t="inlineStr"/>
@@ -7807,28 +7807,28 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>5236</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>MATRIX</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D164" s="2" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="E164" s="3" t="n">
-        <v>0.019</v>
+        <v>1.37</v>
+      </c>
+      <c r="E164" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F164" s="4" t="n">
-        <v>615200</v>
+        <v>839600</v>
       </c>
       <c r="G164" s="5" t="n">
-        <v>0.55</v>
+        <v>0.25</v>
       </c>
       <c r="H164" t="n">
-        <v>38.66</v>
+        <v>72.14</v>
       </c>
       <c r="I164" s="6" t="inlineStr">
         <is>
@@ -7836,10 +7836,10 @@
         </is>
       </c>
       <c r="J164" s="2" t="n">
-        <v>1.102</v>
+        <v>1.237</v>
       </c>
       <c r="K164" s="2" t="n">
-        <v>1.147</v>
+        <v>1.008</v>
       </c>
       <c r="L164" t="inlineStr"/>
       <c r="M164" s="7" t="inlineStr"/>
@@ -7852,39 +7852,39 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>5280</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>KIPREIT</t>
         </is>
       </c>
       <c r="D165" s="2" t="n">
-        <v>0.635</v>
+        <v>0.855</v>
       </c>
       <c r="E165" s="8" t="n">
-        <v>-0.007800000000000001</v>
+        <v>-0.0058</v>
       </c>
       <c r="F165" s="4" t="n">
-        <v>608300</v>
+        <v>810700</v>
       </c>
       <c r="G165" s="5" t="n">
-        <v>0.21</v>
+        <v>1.31</v>
       </c>
       <c r="H165" t="n">
-        <v>51.42</v>
-      </c>
-      <c r="I165" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.23</v>
+      </c>
+      <c r="I165" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J165" s="2" t="n">
-        <v>0.638</v>
+        <v>0.856</v>
       </c>
       <c r="K165" s="2" t="n">
-        <v>0.611</v>
+        <v>0.851</v>
       </c>
       <c r="L165" t="inlineStr"/>
       <c r="M165" s="7" t="inlineStr"/>
@@ -7897,28 +7897,28 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>0240</t>
+          <t>0340</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>CORAZA</t>
+          <t>NORTHERN</t>
         </is>
       </c>
       <c r="D166" s="2" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="E166" s="8" t="n">
-        <v>-0.0141</v>
+        <v>1.23</v>
+      </c>
+      <c r="E166" s="3" t="n">
+        <v>0.025</v>
       </c>
       <c r="F166" s="4" t="n">
-        <v>598200</v>
+        <v>785600</v>
       </c>
       <c r="G166" s="5" t="n">
-        <v>0.22</v>
+        <v>0.1</v>
       </c>
       <c r="H166" t="n">
-        <v>74.17</v>
+        <v>67.31999999999999</v>
       </c>
       <c r="I166" s="9" t="inlineStr">
         <is>
@@ -7926,10 +7926,10 @@
         </is>
       </c>
       <c r="J166" s="2" t="n">
-        <v>1.22</v>
+        <v>1.081</v>
       </c>
       <c r="K166" s="2" t="n">
-        <v>1.151</v>
+        <v>0.83</v>
       </c>
       <c r="L166" t="inlineStr"/>
       <c r="M166" s="7" t="inlineStr"/>
@@ -7942,39 +7942,39 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>9792</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>UWC</t>
+          <t>SEG</t>
         </is>
       </c>
       <c r="D167" s="2" t="n">
-        <v>7.94</v>
+        <v>0.625</v>
       </c>
       <c r="E167" s="8" t="n">
-        <v>-0.0063</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="F167" s="4" t="n">
-        <v>573500</v>
+        <v>775100</v>
       </c>
       <c r="G167" s="5" t="n">
-        <v>0.14</v>
+        <v>0.61</v>
       </c>
       <c r="H167" t="n">
-        <v>71.79000000000001</v>
-      </c>
-      <c r="I167" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.72</v>
+      </c>
+      <c r="I167" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J167" s="2" t="n">
-        <v>7.242</v>
+        <v>0.632</v>
       </c>
       <c r="K167" s="2" t="n">
-        <v>6.753</v>
+        <v>0.63</v>
       </c>
       <c r="L167" t="inlineStr"/>
       <c r="M167" s="7" t="inlineStr"/>
@@ -7987,39 +7987,39 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>7293</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>YINSON</t>
+          <t>SUNREIT</t>
         </is>
       </c>
       <c r="D168" s="2" t="n">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="E168" s="3" t="n">
-        <v>0.0095</v>
+        <v>0.0097</v>
       </c>
       <c r="F168" s="4" t="n">
-        <v>566400</v>
+        <v>774600</v>
       </c>
       <c r="G168" s="5" t="n">
         <v>0.23</v>
       </c>
       <c r="H168" t="n">
-        <v>55.63</v>
-      </c>
-      <c r="I168" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.45</v>
+      </c>
+      <c r="I168" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J168" s="2" t="n">
-        <v>2.09</v>
+        <v>2.058</v>
       </c>
       <c r="K168" s="2" t="n">
-        <v>2.037</v>
+        <v>2.086</v>
       </c>
       <c r="L168" t="inlineStr"/>
       <c r="M168" s="7" t="inlineStr"/>
@@ -8032,28 +8032,28 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>5271</t>
+          <t>5211</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>PECCA</t>
+          <t>SUNWAY</t>
         </is>
       </c>
       <c r="D169" s="2" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="E169" s="10" t="n">
-        <v>0</v>
+        <v>4.36</v>
+      </c>
+      <c r="E169" s="3" t="n">
+        <v>0.0116</v>
       </c>
       <c r="F169" s="4" t="n">
-        <v>541500</v>
+        <v>741100</v>
       </c>
       <c r="G169" s="5" t="n">
-        <v>0.27</v>
+        <v>0.14</v>
       </c>
       <c r="H169" t="n">
-        <v>53.49</v>
+        <v>34.94</v>
       </c>
       <c r="I169" s="6" t="inlineStr">
         <is>
@@ -8061,10 +8061,10 @@
         </is>
       </c>
       <c r="J169" s="2" t="n">
-        <v>1.369</v>
+        <v>4.482</v>
       </c>
       <c r="K169" s="2" t="n">
-        <v>1.337</v>
+        <v>4.817</v>
       </c>
       <c r="L169" t="inlineStr"/>
       <c r="M169" s="7" t="inlineStr"/>
@@ -8077,39 +8077,39 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>5263</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>SUNCON</t>
         </is>
       </c>
       <c r="D170" s="2" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="E170" s="10" t="n">
-        <v>0</v>
+        <v>7.58</v>
+      </c>
+      <c r="E170" s="3" t="n">
+        <v>0.0107</v>
       </c>
       <c r="F170" s="4" t="n">
-        <v>528700</v>
+        <v>737400</v>
       </c>
       <c r="G170" s="5" t="n">
-        <v>0.28</v>
+        <v>0.19</v>
       </c>
       <c r="H170" t="n">
-        <v>31.71</v>
-      </c>
-      <c r="I170" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.24</v>
+      </c>
+      <c r="I170" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J170" s="2" t="n">
-        <v>1.506</v>
+        <v>7.608</v>
       </c>
       <c r="K170" s="2" t="n">
-        <v>1.621</v>
+        <v>7.801</v>
       </c>
       <c r="L170" t="inlineStr"/>
       <c r="M170" s="7" t="inlineStr"/>
@@ -8122,39 +8122,39 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>5176</t>
+          <t>0097</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>SUNREIT</t>
+          <t>VITROX</t>
         </is>
       </c>
       <c r="D171" s="2" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="E171" s="10" t="n">
-        <v>0</v>
+        <v>11.08</v>
+      </c>
+      <c r="E171" s="3" t="n">
+        <v>0.0073</v>
       </c>
       <c r="F171" s="4" t="n">
-        <v>526600</v>
+        <v>732000</v>
       </c>
       <c r="G171" s="5" t="n">
-        <v>0.16</v>
+        <v>0.22</v>
       </c>
       <c r="H171" t="n">
-        <v>49.54</v>
-      </c>
-      <c r="I171" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>74.28</v>
+      </c>
+      <c r="I171" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J171" s="2" t="n">
-        <v>2.056</v>
+        <v>10.242</v>
       </c>
       <c r="K171" s="2" t="n">
-        <v>2.085</v>
+        <v>9.504</v>
       </c>
       <c r="L171" t="inlineStr"/>
       <c r="M171" s="7" t="inlineStr"/>
@@ -8167,39 +8167,39 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>7195</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>BNASTRA</t>
+          <t>HIBISCS</t>
         </is>
       </c>
       <c r="D172" s="2" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="E172" s="3" t="n">
-        <v>0.0114</v>
+        <v>2.17</v>
+      </c>
+      <c r="E172" s="8" t="n">
+        <v>-0.0225</v>
       </c>
       <c r="F172" s="4" t="n">
-        <v>520500</v>
+        <v>726400</v>
       </c>
       <c r="G172" s="5" t="n">
-        <v>0.41</v>
+        <v>0.13</v>
       </c>
       <c r="H172" t="n">
-        <v>84.62</v>
-      </c>
-      <c r="I172" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.02</v>
+      </c>
+      <c r="I172" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J172" s="2" t="n">
-        <v>2.477</v>
+        <v>2.188</v>
       </c>
       <c r="K172" s="2" t="n">
-        <v>2.347</v>
+        <v>2.127</v>
       </c>
       <c r="L172" t="inlineStr"/>
       <c r="M172" s="7" t="inlineStr"/>
@@ -8212,28 +8212,28 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>0466</t>
+          <t>0391</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>SRKKAI</t>
+          <t>AMBEST</t>
         </is>
       </c>
       <c r="D173" s="2" t="n">
-        <v>0.515</v>
+        <v>1.32</v>
       </c>
       <c r="E173" s="8" t="n">
-        <v>-0.009599999999999999</v>
+        <v>-0.0149</v>
       </c>
       <c r="F173" s="4" t="n">
-        <v>512500</v>
+        <v>698300</v>
       </c>
       <c r="G173" s="5" t="n">
-        <v>0.45</v>
+        <v>0.24</v>
       </c>
       <c r="H173" t="n">
-        <v>45.34</v>
+        <v>48.88</v>
       </c>
       <c r="I173" s="6" t="inlineStr">
         <is>
@@ -8241,10 +8241,10 @@
         </is>
       </c>
       <c r="J173" s="2" t="n">
-        <v>0.524</v>
+        <v>1.348</v>
       </c>
       <c r="K173" s="2" t="n">
-        <v>0.533</v>
+        <v>1.235</v>
       </c>
       <c r="L173" t="inlineStr"/>
       <c r="M173" s="7" t="inlineStr"/>
@@ -8257,28 +8257,28 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>5227</t>
+          <t>3417</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>IGBREIT</t>
+          <t>E&amp;O</t>
         </is>
       </c>
       <c r="D174" s="2" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="E174" s="8" t="n">
-        <v>-0.0037</v>
+        <v>0.77</v>
+      </c>
+      <c r="E174" s="3" t="n">
+        <v>0.006500000000000001</v>
       </c>
       <c r="F174" s="4" t="n">
-        <v>501900</v>
+        <v>677500</v>
       </c>
       <c r="G174" s="5" t="n">
-        <v>0.17</v>
+        <v>0.37</v>
       </c>
       <c r="H174" t="n">
-        <v>41.62</v>
+        <v>50.06</v>
       </c>
       <c r="I174" s="6" t="inlineStr">
         <is>
@@ -8286,16 +8286,736 @@
         </is>
       </c>
       <c r="J174" s="2" t="n">
-        <v>2.765</v>
+        <v>0.771</v>
       </c>
       <c r="K174" s="2" t="n">
-        <v>2.762</v>
+        <v>0.767</v>
       </c>
       <c r="L174" t="inlineStr"/>
       <c r="M174" s="7" t="inlineStr"/>
     </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>7293</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>YINSON</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="E175" s="3" t="n">
+        <v>0.0095</v>
+      </c>
+      <c r="F175" s="4" t="n">
+        <v>670200</v>
+      </c>
+      <c r="G175" s="5" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H175" t="n">
+        <v>55.63</v>
+      </c>
+      <c r="I175" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J175" s="2" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="K175" s="2" t="n">
+        <v>2.037</v>
+      </c>
+      <c r="L175" t="inlineStr"/>
+      <c r="M175" s="7" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>4715</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>GENM</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="E176" s="3" t="n">
+        <v>0.0068</v>
+      </c>
+      <c r="F176" s="4" t="n">
+        <v>663700</v>
+      </c>
+      <c r="G176" s="5" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H176" t="n">
+        <v>34.88</v>
+      </c>
+      <c r="I176" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J176" s="2" t="n">
+        <v>1.507</v>
+      </c>
+      <c r="K176" s="2" t="n">
+        <v>1.621</v>
+      </c>
+      <c r="L176" t="inlineStr"/>
+      <c r="M176" s="7" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>0240</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>CORAZA</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="E177" s="8" t="n">
+        <v>-0.0211</v>
+      </c>
+      <c r="F177" s="4" t="n">
+        <v>647600</v>
+      </c>
+      <c r="G177" s="5" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H177" t="n">
+        <v>72.58</v>
+      </c>
+      <c r="I177" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J177" s="2" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="K177" s="2" t="n">
+        <v>1.151</v>
+      </c>
+      <c r="L177" t="inlineStr"/>
+      <c r="M177" s="7" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>5292</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>UWC</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="E178" s="8" t="n">
+        <v>-0.008800000000000001</v>
+      </c>
+      <c r="F178" s="4" t="n">
+        <v>646100</v>
+      </c>
+      <c r="G178" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H178" t="n">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="I178" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J178" s="2" t="n">
+        <v>7.24</v>
+      </c>
+      <c r="K178" s="2" t="n">
+        <v>6.753</v>
+      </c>
+      <c r="L178" t="inlineStr"/>
+      <c r="M178" s="7" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>5236</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>MATRIX</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="E179" s="3" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="F179" s="4" t="n">
+        <v>643900</v>
+      </c>
+      <c r="G179" s="5" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="H179" t="n">
+        <v>38.66</v>
+      </c>
+      <c r="I179" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J179" s="2" t="n">
+        <v>1.102</v>
+      </c>
+      <c r="K179" s="2" t="n">
+        <v>1.147</v>
+      </c>
+      <c r="L179" t="inlineStr"/>
+      <c r="M179" s="7" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>0390</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>ISF</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="n">
+        <v>0.835</v>
+      </c>
+      <c r="E180" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F180" s="4" t="n">
+        <v>637900</v>
+      </c>
+      <c r="G180" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H180" t="n">
+        <v>58.39</v>
+      </c>
+      <c r="I180" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J180" s="2" t="n">
+        <v>0.819</v>
+      </c>
+      <c r="K180" s="2" t="n">
+        <v>0.756</v>
+      </c>
+      <c r="L180" t="inlineStr"/>
+      <c r="M180" s="7" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>0112</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>MIKROMB</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="E181" s="8" t="n">
+        <v>-0.007800000000000001</v>
+      </c>
+      <c r="F181" s="4" t="n">
+        <v>609000</v>
+      </c>
+      <c r="G181" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H181" t="n">
+        <v>51.42</v>
+      </c>
+      <c r="I181" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J181" s="2" t="n">
+        <v>0.638</v>
+      </c>
+      <c r="K181" s="2" t="n">
+        <v>0.611</v>
+      </c>
+      <c r="L181" t="inlineStr"/>
+      <c r="M181" s="7" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>0466</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>SRKKAI</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="n">
+        <v>0.515</v>
+      </c>
+      <c r="E182" s="8" t="n">
+        <v>-0.009599999999999999</v>
+      </c>
+      <c r="F182" s="4" t="n">
+        <v>600500</v>
+      </c>
+      <c r="G182" s="5" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="H182" t="n">
+        <v>45.34</v>
+      </c>
+      <c r="I182" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J182" s="2" t="n">
+        <v>0.524</v>
+      </c>
+      <c r="K182" s="2" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="L182" t="inlineStr"/>
+      <c r="M182" s="7" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>5227</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>IGBREIT</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="E183" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F183" s="4" t="n">
+        <v>560900</v>
+      </c>
+      <c r="G183" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H183" t="n">
+        <v>42.84</v>
+      </c>
+      <c r="I183" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J183" s="2" t="n">
+        <v>2.766</v>
+      </c>
+      <c r="K183" s="2" t="n">
+        <v>2.763</v>
+      </c>
+      <c r="L183" t="inlineStr"/>
+      <c r="M183" s="7" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>5288</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>SIMEPROP</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="E184" s="3" t="n">
+        <v>0.0248</v>
+      </c>
+      <c r="F184" s="4" t="n">
+        <v>558800</v>
+      </c>
+      <c r="G184" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H184" t="n">
+        <v>46.82</v>
+      </c>
+      <c r="I184" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J184" s="2" t="n">
+        <v>1.247</v>
+      </c>
+      <c r="K184" s="2" t="n">
+        <v>1.285</v>
+      </c>
+      <c r="L184" t="inlineStr"/>
+      <c r="M184" s="7" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>5271</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>PECCA</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="E185" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F185" s="4" t="n">
+        <v>549100</v>
+      </c>
+      <c r="G185" s="5" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H185" t="n">
+        <v>53.49</v>
+      </c>
+      <c r="I185" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J185" s="2" t="n">
+        <v>1.369</v>
+      </c>
+      <c r="K185" s="2" t="n">
+        <v>1.337</v>
+      </c>
+      <c r="L185" t="inlineStr"/>
+      <c r="M185" s="7" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>7195</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>BNASTRA</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="E186" s="3" t="n">
+        <v>0.0076</v>
+      </c>
+      <c r="F186" s="4" t="n">
+        <v>543700</v>
+      </c>
+      <c r="G186" s="5" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="H186" t="n">
+        <v>84.13</v>
+      </c>
+      <c r="I186" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J186" s="2" t="n">
+        <v>2.476</v>
+      </c>
+      <c r="K186" s="2" t="n">
+        <v>2.347</v>
+      </c>
+      <c r="L186" t="inlineStr"/>
+      <c r="M186" s="7" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>0245</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>MNHLDG</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="E187" s="8" t="n">
+        <v>-0.0077</v>
+      </c>
+      <c r="F187" s="4" t="n">
+        <v>543400</v>
+      </c>
+      <c r="G187" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H187" t="n">
+        <v>54.53</v>
+      </c>
+      <c r="I187" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J187" s="2" t="n">
+        <v>3.859</v>
+      </c>
+      <c r="K187" s="2" t="n">
+        <v>3.569</v>
+      </c>
+      <c r="L187" t="inlineStr"/>
+      <c r="M187" s="7" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>0291</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>CHB</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="E188" s="8" t="n">
+        <v>-0.0106</v>
+      </c>
+      <c r="F188" s="4" t="n">
+        <v>523100</v>
+      </c>
+      <c r="G188" s="5" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="H188" t="n">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I188" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J188" s="2" t="n">
+        <v>2.461</v>
+      </c>
+      <c r="K188" s="2" t="n">
+        <v>2.157</v>
+      </c>
+      <c r="L188" t="inlineStr"/>
+      <c r="M188" s="7" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>5285</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>SDG</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="E189" s="3" t="n">
+        <v>0.0067</v>
+      </c>
+      <c r="F189" s="4" t="n">
+        <v>517600</v>
+      </c>
+      <c r="G189" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H189" t="n">
+        <v>39.88</v>
+      </c>
+      <c r="I189" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J189" s="2" t="n">
+        <v>6.166</v>
+      </c>
+      <c r="K189" s="2" t="n">
+        <v>6.401</v>
+      </c>
+      <c r="L189" t="inlineStr"/>
+      <c r="M189" s="7" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>5031</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>TIMECOM</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="E190" s="3" t="n">
+        <v>0.0072</v>
+      </c>
+      <c r="F190" s="4" t="n">
+        <v>513100</v>
+      </c>
+      <c r="G190" s="5" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="H190" t="n">
+        <v>38.49</v>
+      </c>
+      <c r="I190" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J190" s="2" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="K190" s="2" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="L190" t="inlineStr"/>
+      <c r="M190" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M174"/>
+  <autoFilter ref="A1:M190"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-09/bursa-report-2026-10-09.xlsx
+++ b/docs/downloads/2026-10-09/bursa-report-2026-10-09.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-09" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-09'!$A$1:$M$190</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-09'!$A$1:$M$202</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M190"/>
+  <dimension ref="A1:M202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -558,10 +558,10 @@
         <v>0.0667</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>119161200</v>
+        <v>172900200</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.27</v>
+        <v>0.39</v>
       </c>
       <c r="H2" t="n">
         <v>22.11</v>
@@ -597,19 +597,19 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.515</v>
+        <v>0.52</v>
       </c>
       <c r="E3" s="8" t="n">
-        <v>-0.019</v>
+        <v>-0.0095</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>80856500</v>
+        <v>86229000</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>2.84</v>
+        <v>3.03</v>
       </c>
       <c r="H3" t="n">
-        <v>60.83</v>
+        <v>62.99</v>
       </c>
       <c r="I3" s="9" t="inlineStr">
         <is>
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.49</v>
+        <v>0.491</v>
       </c>
       <c r="K3" s="2" t="n">
         <v>0.479</v>
@@ -648,10 +648,10 @@
         <v>0</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>40309700</v>
+        <v>42110000</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>107.93</v>
+        <v>112.75</v>
       </c>
       <c r="H4" t="n">
         <v>43</v>
@@ -678,28 +678,28 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>0.0303</v>
+        <v>0.845</v>
+      </c>
+      <c r="E5" s="8" t="n">
+        <v>-0.0343</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>38525000</v>
+        <v>38921500</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.66</v>
+        <v>0.5</v>
       </c>
       <c r="H5" t="n">
-        <v>77.59999999999999</v>
+        <v>63.57</v>
       </c>
       <c r="I5" s="9" t="inlineStr">
         <is>
@@ -707,10 +707,10 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.278</v>
+        <v>0.782</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.245</v>
+        <v>0.71</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" s="7" t="inlineStr"/>
@@ -723,28 +723,28 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="E6" s="8" t="n">
-        <v>-0.04</v>
+        <v>0.335</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>0.0152</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>37916000</v>
+        <v>38867600</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.49</v>
+        <v>0.66</v>
       </c>
       <c r="H6" t="n">
-        <v>62.57</v>
+        <v>76.77</v>
       </c>
       <c r="I6" s="9" t="inlineStr">
         <is>
@@ -752,10 +752,10 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.782</v>
+        <v>0.278</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.71</v>
+        <v>0.244</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" s="7" t="inlineStr"/>
@@ -768,39 +768,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>0095</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>MAG</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.195</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>0.0263</v>
+        <v>0.155</v>
+      </c>
+      <c r="E7" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>28446100</v>
+        <v>31365500</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>1.22</v>
+        <v>0.98</v>
       </c>
       <c r="H7" t="n">
-        <v>51.06</v>
-      </c>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.07</v>
+      </c>
+      <c r="I7" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.196</v>
+        <v>0.156</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.183</v>
+        <v>0.157</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" s="7" t="inlineStr"/>
@@ -828,10 +828,10 @@
         <v>0.0357</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>28297600</v>
+        <v>29980100</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="H8" t="n">
         <v>72.39</v>
@@ -858,39 +858,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0095</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MAG</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="E9" s="10" t="n">
-        <v>0</v>
+        <v>0.195</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>0.0263</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>25015500</v>
+        <v>28595600</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.78</v>
+        <v>1.22</v>
       </c>
       <c r="H9" t="n">
-        <v>46.07</v>
-      </c>
-      <c r="I9" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>51.06</v>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.156</v>
+        <v>0.196</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.157</v>
+        <v>0.183</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="7" t="inlineStr"/>
@@ -918,7 +918,7 @@
         <v>0.0163</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>21861400</v>
+        <v>21869800</v>
       </c>
       <c r="G10" s="5" t="n">
         <v>0.84</v>
@@ -948,39 +948,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>0278</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>JAKS</t>
+          <t>EDELTEQ</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="E11" s="8" t="n">
-        <v>-0.027</v>
+        <v>0.465</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>0.06900000000000001</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>18271500</v>
+        <v>18939300</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.29</v>
+        <v>8.25</v>
       </c>
       <c r="H11" t="n">
-        <v>60.1</v>
-      </c>
-      <c r="I11" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>78.66</v>
+      </c>
+      <c r="I11" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.167</v>
+        <v>0.358</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0.132</v>
+        <v>0.349</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="7" t="inlineStr"/>
@@ -993,28 +993,28 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0278</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>EDELTEQ</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="E12" s="3" t="n">
-        <v>0.0345</v>
+        <v>0.39</v>
+      </c>
+      <c r="E12" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>17232800</v>
+        <v>18620100</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>7.51</v>
+        <v>0.44</v>
       </c>
       <c r="H12" t="n">
-        <v>77.01000000000001</v>
+        <v>70.36</v>
       </c>
       <c r="I12" s="9" t="inlineStr">
         <is>
@@ -1022,10 +1022,10 @@
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.357</v>
+        <v>0.358</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0.349</v>
+        <v>0.236</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="7" t="inlineStr"/>
@@ -1038,39 +1038,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>JAKS</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0.39</v>
+        <v>0.185</v>
       </c>
       <c r="E13" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>17173000</v>
+        <v>18528800</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.41</v>
+        <v>0.29</v>
       </c>
       <c r="H13" t="n">
-        <v>70.36</v>
-      </c>
-      <c r="I13" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>63.02</v>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.358</v>
+        <v>0.168</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0.236</v>
+        <v>0.132</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="7" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         <v>0.0571</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>16608700</v>
+        <v>17047600</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="H14" t="n">
         <v>61.01</v>
@@ -1143,10 +1143,10 @@
         <v>0.0299</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>15535200</v>
+        <v>15681100</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="H15" t="n">
         <v>71.43000000000001</v>
@@ -1169,39 +1169,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E16" s="3" t="n">
-        <v>0.0959</v>
+        <v>0.31</v>
+      </c>
+      <c r="E16" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>11200100</v>
+        <v>13865000</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.72</v>
       </c>
       <c r="H16" t="n">
-        <v>56.64</v>
-      </c>
-      <c r="I16" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.67</v>
+      </c>
+      <c r="I16" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.384</v>
+        <v>0.305</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0.375</v>
+        <v>0.295</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="7" t="inlineStr"/>
@@ -1214,39 +1214,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="E17" s="10" t="n">
-        <v>0</v>
+        <v>0.4</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>0.0959</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>10835100</v>
+        <v>11414600</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.96</v>
       </c>
       <c r="H17" t="n">
-        <v>57.67</v>
-      </c>
-      <c r="I17" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>56.64</v>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.305</v>
+        <v>0.384</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0.295</v>
+        <v>0.375</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="7" t="inlineStr"/>
@@ -1259,28 +1259,28 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>5195</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CENSOF</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="E18" s="10" t="n">
-        <v>0</v>
+        <v>5.02</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>0.0141</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>9781700</v>
+        <v>10497100</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>7.25</v>
+        <v>0.43</v>
       </c>
       <c r="H18" t="n">
-        <v>68.81</v>
+        <v>59</v>
       </c>
       <c r="I18" s="9" t="inlineStr">
         <is>
@@ -1288,10 +1288,10 @@
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.22</v>
+        <v>4.919</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0.206</v>
+        <v>4.651</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="7" t="inlineStr"/>
@@ -1304,39 +1304,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>MALAKOF</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>0.795</v>
+        <v>0.775</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>0.0192</v>
+        <v>0.006500000000000001</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>9544700</v>
+        <v>10443200</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>2.58</v>
+        <v>0.71</v>
       </c>
       <c r="H19" t="n">
-        <v>50.06</v>
-      </c>
-      <c r="I19" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.25</v>
+      </c>
+      <c r="I19" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.792</v>
+        <v>0.775</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0.806</v>
+        <v>0.775</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="7" t="inlineStr"/>
@@ -1349,28 +1349,28 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E20" s="3" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.865</v>
+      </c>
+      <c r="E20" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>9197600</v>
+        <v>10369400</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.62</v>
+        <v>0.55</v>
       </c>
       <c r="H20" t="n">
-        <v>50.25</v>
+        <v>46.68</v>
       </c>
       <c r="I20" s="9" t="inlineStr">
         <is>
@@ -1378,10 +1378,10 @@
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.775</v>
+        <v>0.868</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0.775</v>
+        <v>0.869</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="7" t="inlineStr"/>
@@ -1394,28 +1394,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>0.625</v>
+        <v>0.345</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>0.008100000000000001</v>
+        <v>0.0299</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>9128300</v>
+        <v>10242300</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.87</v>
+        <v>1.82</v>
       </c>
       <c r="H21" t="n">
-        <v>58.16</v>
+        <v>59.12</v>
       </c>
       <c r="I21" s="9" t="inlineStr">
         <is>
@@ -1423,10 +1423,10 @@
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.611</v>
+        <v>0.327</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0.611</v>
+        <v>0.339</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="7" t="inlineStr"/>
@@ -1439,28 +1439,28 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>5.03</v>
+        <v>0.625</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>0.0162</v>
+        <v>0.008100000000000001</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>9125800</v>
+        <v>9837500</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.37</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>59.43</v>
+        <v>58.16</v>
       </c>
       <c r="I22" s="9" t="inlineStr">
         <is>
@@ -1468,10 +1468,10 @@
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>4.92</v>
+        <v>0.611</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>4.651</v>
+        <v>0.611</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="7" t="inlineStr"/>
@@ -1484,28 +1484,28 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>5195</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>CENSOF</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>0.435</v>
-      </c>
-      <c r="E23" s="8" t="n">
-        <v>-0.0225</v>
+        <v>0.24</v>
+      </c>
+      <c r="E23" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>8822900</v>
+        <v>9781700</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.33</v>
+        <v>7.25</v>
       </c>
       <c r="H23" t="n">
-        <v>60.91</v>
+        <v>68.81</v>
       </c>
       <c r="I23" s="9" t="inlineStr">
         <is>
@@ -1513,10 +1513,10 @@
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.41</v>
+        <v>0.22</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0.346</v>
+        <v>0.206</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="7" t="inlineStr"/>
@@ -1529,39 +1529,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0104</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>GENETEC</t>
+          <t>MALAKOF</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>0.345</v>
+        <v>0.79</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>0.0299</v>
+        <v>0.0128</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>8044400</v>
+        <v>9689800</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>1.43</v>
+        <v>2.62</v>
       </c>
       <c r="H24" t="n">
-        <v>59.12</v>
-      </c>
-      <c r="I24" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.72</v>
+      </c>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.327</v>
+        <v>0.791</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0.339</v>
+        <v>0.806</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="7" t="inlineStr"/>
@@ -1574,36 +1574,40 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0470</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>BFIELD</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>0.47</v>
+        <v>0.46</v>
       </c>
       <c r="E25" s="8" t="n">
-        <v>-0.0208</v>
+        <v>-0.0316</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>8013100</v>
+        <v>9473100</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.67</v>
+        <v>0.25</v>
       </c>
       <c r="H25" t="n">
-        <v>47.36</v>
-      </c>
-      <c r="I25" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="n"/>
-      <c r="K25" s="2" t="n"/>
+        <v>25.19</v>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="n">
+        <v>0.548</v>
+      </c>
+      <c r="K25" s="2" t="n">
+        <v>0.749</v>
+      </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="7" t="inlineStr"/>
     </row>
@@ -1615,28 +1619,28 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>0131</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>DFX</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E26" s="10" t="n">
-        <v>0</v>
+        <v>0.16</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>0.1034</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>7834400</v>
+        <v>9446000</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.42</v>
+        <v>1.18</v>
       </c>
       <c r="H26" t="n">
-        <v>46.68</v>
+        <v>78.47</v>
       </c>
       <c r="I26" s="9" t="inlineStr">
         <is>
@@ -1644,10 +1648,10 @@
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.868</v>
+        <v>0.118</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0.869</v>
+        <v>0.094</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="7" t="inlineStr"/>
@@ -1660,39 +1664,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="E27" s="8" t="n">
-        <v>-0.0316</v>
+        <v>-0.0337</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>7687400</v>
+        <v>9011500</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="H27" t="n">
-        <v>25.19</v>
-      </c>
-      <c r="I27" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.31</v>
+      </c>
+      <c r="I27" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.548</v>
+        <v>0.409</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0.749</v>
+        <v>0.346</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="7" t="inlineStr"/>
@@ -1705,39 +1709,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>0.8149999999999999</v>
+        <v>2.81</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0.0062</v>
+        <v>0.0108</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>7641900</v>
+        <v>8691200</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.48</v>
+        <v>0.63</v>
       </c>
       <c r="H28" t="n">
-        <v>54.76</v>
-      </c>
-      <c r="I28" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.6</v>
+      </c>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>2.791</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0.806</v>
+        <v>2.693</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="7" t="inlineStr"/>
@@ -1750,39 +1754,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0358</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ICTZONE</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>0.24</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.0667</v>
+        <v>0.0062</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>7505600</v>
+        <v>8538200</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>2.69</v>
+        <v>0.53</v>
       </c>
       <c r="H29" t="n">
-        <v>48.47</v>
-      </c>
-      <c r="I29" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.76</v>
+      </c>
+      <c r="I29" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.241</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0.249</v>
+        <v>0.806</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="7" t="inlineStr"/>
@@ -1795,28 +1799,28 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0131</t>
+          <t>0050</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>DFX</t>
+          <t>SYSTECH</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>0.155</v>
+        <v>0.185</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.0571</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>7249400</v>
+        <v>8237700</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.91</v>
+        <v>1.52</v>
       </c>
       <c r="H30" t="n">
-        <v>77.22</v>
+        <v>65.31999999999999</v>
       </c>
       <c r="I30" s="9" t="inlineStr">
         <is>
@@ -1824,10 +1828,10 @@
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.118</v>
+        <v>0.165</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0.094</v>
+        <v>0.166</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="7" t="inlineStr"/>
@@ -1840,28 +1844,28 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>2.81</v>
+        <v>4.57</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0.0108</v>
+        <v>0.0044</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>7156300</v>
+        <v>8115100</v>
       </c>
       <c r="G31" s="5" t="n">
         <v>0.52</v>
       </c>
       <c r="H31" t="n">
-        <v>53.6</v>
+        <v>29.08</v>
       </c>
       <c r="I31" s="6" t="inlineStr">
         <is>
@@ -1869,10 +1873,10 @@
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>2.791</v>
+        <v>4.722</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>2.693</v>
+        <v>4.891</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="7" t="inlineStr"/>
@@ -1885,40 +1889,36 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>0470</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>BFIELD</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>4.57</v>
-      </c>
-      <c r="E32" s="3" t="n">
-        <v>0.0044</v>
+        <v>0.475</v>
+      </c>
+      <c r="E32" s="8" t="n">
+        <v>-0.0104</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>7102500</v>
+        <v>8113100</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.45</v>
+        <v>0.68</v>
       </c>
       <c r="H32" t="n">
-        <v>29.08</v>
-      </c>
-      <c r="I32" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="n">
-        <v>4.722</v>
-      </c>
-      <c r="K32" s="2" t="n">
-        <v>4.891</v>
-      </c>
+        <v>54.21</v>
+      </c>
+      <c r="I32" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="n"/>
+      <c r="K32" s="2" t="n"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="7" t="inlineStr"/>
     </row>
@@ -1930,33 +1930,40 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0476</t>
+          <t>0358</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>SLGC Berhad</t>
+          <t>ICTZONE</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E33" s="10" t="n">
-        <v>0</v>
+        <v>0.24</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>0.0667</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>6909000</v>
+        <v>7663400</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="I33" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="n"/>
-      <c r="K33" s="2" t="n"/>
+        <v>2.75</v>
+      </c>
+      <c r="H33" t="n">
+        <v>48.47</v>
+      </c>
+      <c r="I33" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="n">
+        <v>0.241</v>
+      </c>
+      <c r="K33" s="2" t="n">
+        <v>0.249</v>
+      </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="7" t="inlineStr"/>
     </row>
@@ -1977,19 +1984,19 @@
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>0.71</v>
+        <v>0.7</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0.1008</v>
+        <v>0.08529999999999999</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>6671000</v>
+        <v>7575700</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>1.47</v>
+        <v>1.67</v>
       </c>
       <c r="H34" t="n">
-        <v>86.43000000000001</v>
+        <v>85.98999999999999</v>
       </c>
       <c r="I34" s="9" t="inlineStr">
         <is>
@@ -1997,10 +2004,10 @@
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.519</v>
+        <v>0.518</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0.444</v>
+        <v>0.443</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="7" t="inlineStr"/>
@@ -2013,28 +2020,28 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>0.365</v>
+        <v>0.39</v>
       </c>
       <c r="E35" s="8" t="n">
-        <v>-0.0135</v>
+        <v>-0.0127</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>6435300</v>
+        <v>7463700</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.96</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H35" t="n">
-        <v>47.65</v>
+        <v>34.12</v>
       </c>
       <c r="I35" s="6" t="inlineStr">
         <is>
@@ -2042,10 +2049,10 @@
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.367</v>
+        <v>0.402</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0.367</v>
+        <v>0.41</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="7" t="inlineStr"/>
@@ -2058,40 +2065,33 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>0476</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>SLGC Berhad</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>2.14</v>
+        <v>0.25</v>
       </c>
       <c r="E36" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>6318900</v>
+        <v>7414600</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="H36" t="n">
-        <v>41.24</v>
-      </c>
-      <c r="I36" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="n">
-        <v>2.225</v>
-      </c>
-      <c r="K36" s="2" t="n">
-        <v>2.212</v>
-      </c>
+        <v>0.17</v>
+      </c>
+      <c r="I36" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="n"/>
+      <c r="K36" s="2" t="n"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="7" t="inlineStr"/>
     </row>
@@ -2103,28 +2103,28 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>AVANGAAD</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E37" s="10" t="n">
-        <v>0</v>
+        <v>2.15</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>0.004699999999999999</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>6246100</v>
+        <v>7180700</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>2.38</v>
+        <v>0.48</v>
       </c>
       <c r="H37" t="n">
-        <v>49.15</v>
+        <v>42.31</v>
       </c>
       <c r="I37" s="6" t="inlineStr">
         <is>
@@ -2132,10 +2132,10 @@
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.295</v>
+        <v>2.226</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0.296</v>
+        <v>2.213</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="7" t="inlineStr"/>
@@ -2148,28 +2148,28 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0198</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>GDB</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>0.4</v>
+        <v>0.365</v>
       </c>
       <c r="E38" s="8" t="n">
-        <v>-0.0361</v>
+        <v>-0.0135</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>6190000</v>
+        <v>6435300</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>5.49</v>
+        <v>0.96</v>
       </c>
       <c r="H38" t="n">
-        <v>32.62</v>
+        <v>47.65</v>
       </c>
       <c r="I38" s="6" t="inlineStr">
         <is>
@@ -2177,10 +2177,10 @@
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.421</v>
+        <v>0.367</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>0.441</v>
+        <v>0.367</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="7" t="inlineStr"/>
@@ -2193,28 +2193,28 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="E39" s="8" t="n">
-        <v>-0.0127</v>
+        <v>-0.0361</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>6025000</v>
+        <v>6280000</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.5600000000000001</v>
+        <v>5.57</v>
       </c>
       <c r="H39" t="n">
-        <v>34.12</v>
+        <v>32.62</v>
       </c>
       <c r="I39" s="6" t="inlineStr">
         <is>
@@ -2222,10 +2222,10 @@
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.402</v>
+        <v>0.421</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0.41</v>
+        <v>0.441</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="7" t="inlineStr"/>
@@ -2238,39 +2238,39 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>7020</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ASTEEL</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>0.105</v>
+        <v>0.295</v>
       </c>
       <c r="E40" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>5983100</v>
+        <v>6246100</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>2.7</v>
+        <v>2.38</v>
       </c>
       <c r="H40" t="n">
-        <v>59.81</v>
-      </c>
-      <c r="I40" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.15</v>
+      </c>
+      <c r="I40" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.096</v>
+        <v>0.295</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.296</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="7" t="inlineStr"/>
@@ -2283,39 +2283,39 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>7139</t>
+          <t>7020</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>NICE</t>
+          <t>ASTEEL</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>0.08</v>
+        <v>0.105</v>
       </c>
       <c r="E41" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>5705300</v>
+        <v>6023100</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>6.03</v>
+        <v>2.72</v>
       </c>
       <c r="H41" t="n">
-        <v>37.6</v>
-      </c>
-      <c r="I41" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.81</v>
+      </c>
+      <c r="I41" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.083</v>
+        <v>0.096</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="7" t="inlineStr"/>
@@ -2328,28 +2328,28 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0050</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>SYSTECH</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>0.19</v>
+        <v>6.7</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>0.0857</v>
+        <v>0.102</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>5688500</v>
+        <v>5978900</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>1.05</v>
+        <v>1.33</v>
       </c>
       <c r="H42" t="n">
-        <v>67.38</v>
+        <v>65.41</v>
       </c>
       <c r="I42" s="9" t="inlineStr">
         <is>
@@ -2357,10 +2357,10 @@
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.165</v>
+        <v>5.832</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0.166</v>
+        <v>5.778</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="7" t="inlineStr"/>
@@ -2373,28 +2373,28 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>6.7</v>
+        <v>0.64</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>0.102</v>
+        <v>0.024</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>5655100</v>
+        <v>5877500</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>1.26</v>
+        <v>0.31</v>
       </c>
       <c r="H43" t="n">
-        <v>65.41</v>
+        <v>64.14</v>
       </c>
       <c r="I43" s="9" t="inlineStr">
         <is>
@@ -2402,10 +2402,10 @@
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>5.832</v>
+        <v>0.582</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>5.778</v>
+        <v>0.519</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="7" t="inlineStr"/>
@@ -2418,39 +2418,39 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="E44" s="3" t="n">
-        <v>0.024</v>
+        <v>7.25</v>
+      </c>
+      <c r="E44" s="8" t="n">
+        <v>-0.0014</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>5522600</v>
+        <v>5737900</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.29</v>
+        <v>0.41</v>
       </c>
       <c r="H44" t="n">
-        <v>64.14</v>
-      </c>
-      <c r="I44" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>31.19</v>
+      </c>
+      <c r="I44" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.582</v>
+        <v>7.639</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0.519</v>
+        <v>7.729</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="7" t="inlineStr"/>
@@ -2463,28 +2463,28 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>5141</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>WCT</t>
+          <t>DAYANG</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="E45" s="10" t="n">
-        <v>0</v>
+        <v>1.39</v>
+      </c>
+      <c r="E45" s="8" t="n">
+        <v>-0.0414</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>5430300</v>
+        <v>5728800</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>1.37</v>
+        <v>2.61</v>
       </c>
       <c r="H45" t="n">
-        <v>32.2</v>
+        <v>33.34</v>
       </c>
       <c r="I45" s="6" t="inlineStr">
         <is>
@@ -2492,10 +2492,10 @@
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.363</v>
+        <v>1.456</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0.383</v>
+        <v>1.494</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="7" t="inlineStr"/>
@@ -2508,39 +2508,39 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>7139</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>SKPRES</t>
+          <t>NICE</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="E46" s="3" t="n">
-        <v>0.0267</v>
+        <v>0.08</v>
+      </c>
+      <c r="E46" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>5147600</v>
+        <v>5705300</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.63</v>
+        <v>6.03</v>
       </c>
       <c r="H46" t="n">
-        <v>69.33</v>
-      </c>
-      <c r="I46" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.6</v>
+      </c>
+      <c r="I46" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.354</v>
+        <v>0.083</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>0.322</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="7" t="inlineStr"/>
@@ -2553,28 +2553,28 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>IOICORP</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>4.57</v>
-      </c>
-      <c r="E47" s="3" t="n">
-        <v>0.0022</v>
+        <v>0.34</v>
+      </c>
+      <c r="E47" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>5055700</v>
+        <v>5657200</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.53</v>
+        <v>1.42</v>
       </c>
       <c r="H47" t="n">
-        <v>40.81</v>
+        <v>32.2</v>
       </c>
       <c r="I47" s="6" t="inlineStr">
         <is>
@@ -2582,10 +2582,10 @@
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>4.674</v>
+        <v>0.363</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>4.619</v>
+        <v>0.383</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="7" t="inlineStr"/>
@@ -2598,28 +2598,28 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="E48" s="10" t="n">
-        <v>0</v>
+        <v>2.76</v>
+      </c>
+      <c r="E48" s="8" t="n">
+        <v>-0.0072</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>4994600</v>
+        <v>5593900</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.63</v>
+        <v>0.31</v>
       </c>
       <c r="H48" t="n">
-        <v>54.24</v>
+        <v>63.23</v>
       </c>
       <c r="I48" s="9" t="inlineStr">
         <is>
@@ -2627,10 +2627,10 @@
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.779</v>
+        <v>2.625</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0.773</v>
+        <v>2.496</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="7" t="inlineStr"/>
@@ -2652,19 +2652,19 @@
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="E49" s="10" t="n">
-        <v>0</v>
+        <v>9.81</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>0.001</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>4972300</v>
+        <v>5545700</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.39</v>
+        <v>0.44</v>
       </c>
       <c r="H49" t="n">
-        <v>30.27</v>
+        <v>31.22</v>
       </c>
       <c r="I49" s="6" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>10.021</v>
+        <v>10.022</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>10.213</v>
@@ -2688,28 +2688,28 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>1.22</v>
+        <v>0.39</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>0.0517</v>
+        <v>0.04</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>4780500</v>
+        <v>5288500</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.83</v>
+        <v>0.64</v>
       </c>
       <c r="H50" t="n">
-        <v>59.32</v>
+        <v>70.7</v>
       </c>
       <c r="I50" s="9" t="inlineStr">
         <is>
@@ -2717,10 +2717,10 @@
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>1.157</v>
+        <v>0.355</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>1.166</v>
+        <v>0.322</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="7" t="inlineStr"/>
@@ -2733,28 +2733,28 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>2.74</v>
+        <v>0.78</v>
       </c>
       <c r="E51" s="8" t="n">
-        <v>-0.0144</v>
+        <v>-0.0127</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>4592600</v>
+        <v>5255200</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.26</v>
+        <v>0.66</v>
       </c>
       <c r="H51" t="n">
-        <v>61.38</v>
+        <v>51.22</v>
       </c>
       <c r="I51" s="9" t="inlineStr">
         <is>
@@ -2762,10 +2762,10 @@
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>2.623</v>
+        <v>0.778</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>2.496</v>
+        <v>0.773</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="7" t="inlineStr"/>
@@ -2778,39 +2778,39 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>5141</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>DAYANG</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="E52" s="8" t="n">
-        <v>-0.0414</v>
+        <v>1.23</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>0.0603</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>4574900</v>
+        <v>5242000</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>2.08</v>
+        <v>0.91</v>
       </c>
       <c r="H52" t="n">
-        <v>33.34</v>
-      </c>
-      <c r="I52" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.41</v>
+      </c>
+      <c r="I52" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>1.456</v>
+        <v>1.158</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>1.494</v>
+        <v>1.166</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="7" t="inlineStr"/>
@@ -2823,28 +2823,28 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>MRCB</t>
+          <t>IOICORP</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>0.28</v>
+        <v>4.57</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>0.0182</v>
+        <v>0.0022</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>4470500</v>
+        <v>5143700</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.63</v>
+        <v>0.54</v>
       </c>
       <c r="H53" t="n">
-        <v>37.22</v>
+        <v>40.81</v>
       </c>
       <c r="I53" s="6" t="inlineStr">
         <is>
@@ -2852,10 +2852,10 @@
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.289</v>
+        <v>4.674</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0.307</v>
+        <v>4.619</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="7" t="inlineStr"/>
@@ -2868,28 +2868,28 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0376</t>
+          <t>5326</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>IAB</t>
+          <t>99SMART</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="E54" s="8" t="n">
-        <v>-0.0222</v>
+        <v>3.27</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>0.0481</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>4385000</v>
+        <v>4816700</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>2.53</v>
+        <v>1.13</v>
       </c>
       <c r="H54" t="n">
-        <v>54.18</v>
+        <v>52.82</v>
       </c>
       <c r="I54" s="9" t="inlineStr">
         <is>
@@ -2897,10 +2897,10 @@
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>1.275</v>
+        <v>3.2</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>1.32</v>
+        <v>3.391</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="7" t="inlineStr"/>
@@ -2913,28 +2913,28 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>MRCB</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>7.25</v>
-      </c>
-      <c r="E55" s="8" t="n">
-        <v>-0.0014</v>
+        <v>0.28</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>0.0182</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>4087000</v>
+        <v>4695500</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.3</v>
+        <v>0.66</v>
       </c>
       <c r="H55" t="n">
-        <v>31.19</v>
+        <v>37.22</v>
       </c>
       <c r="I55" s="6" t="inlineStr">
         <is>
@@ -2942,10 +2942,10 @@
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>7.639</v>
+        <v>0.289</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>7.729</v>
+        <v>0.307</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="7" t="inlineStr"/>
@@ -2958,39 +2958,39 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>0376</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>IAB</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>7.12</v>
+        <v>1.31</v>
       </c>
       <c r="E56" s="8" t="n">
-        <v>-0.0042</v>
+        <v>-0.0296</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>4018500</v>
+        <v>4529200</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.42</v>
+        <v>2.61</v>
       </c>
       <c r="H56" t="n">
-        <v>18.83</v>
-      </c>
-      <c r="I56" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.07</v>
+      </c>
+      <c r="I56" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>7.596</v>
+        <v>1.274</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>8.09</v>
+        <v>1.319</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="7" t="inlineStr"/>
@@ -3003,39 +3003,39 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>0.455</v>
+        <v>7.12</v>
       </c>
       <c r="E57" s="8" t="n">
-        <v>-0.0109</v>
+        <v>-0.0042</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>3892300</v>
+        <v>4440300</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.46</v>
       </c>
       <c r="H57" t="n">
-        <v>60.71</v>
-      </c>
-      <c r="I57" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>18.83</v>
+      </c>
+      <c r="I57" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.426</v>
+        <v>7.596</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>0.413</v>
+        <v>8.09</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="7" t="inlineStr"/>
@@ -3048,28 +3048,28 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="E58" s="8" t="n">
-        <v>-0.0342</v>
+        <v>0.46</v>
+      </c>
+      <c r="E58" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>3871800</v>
+        <v>4417200</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.34</v>
+        <v>0.64</v>
       </c>
       <c r="H58" t="n">
-        <v>47.14</v>
+        <v>62.48</v>
       </c>
       <c r="I58" s="9" t="inlineStr">
         <is>
@@ -3077,10 +3077,10 @@
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>1.161</v>
+        <v>0.427</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>1.119</v>
+        <v>0.413</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="7" t="inlineStr"/>
@@ -3093,28 +3093,28 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0111</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>K1</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>0.165</v>
-      </c>
-      <c r="E59" s="3" t="n">
-        <v>0.0313</v>
+        <v>1.13</v>
+      </c>
+      <c r="E59" s="8" t="n">
+        <v>-0.0342</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>3810200</v>
+        <v>4154500</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>1.16</v>
+        <v>0.37</v>
       </c>
       <c r="H59" t="n">
-        <v>59.38</v>
+        <v>47.14</v>
       </c>
       <c r="I59" s="9" t="inlineStr">
         <is>
@@ -3122,10 +3122,10 @@
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.156</v>
+        <v>1.161</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0.145</v>
+        <v>1.119</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="7" t="inlineStr"/>
@@ -3138,28 +3138,28 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>SPSETIA</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>0.72</v>
+        <v>3.68</v>
       </c>
       <c r="E60" s="8" t="n">
-        <v>-0.0069</v>
+        <v>-0.0239</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>3694300</v>
+        <v>4146700</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.62</v>
+        <v>0.36</v>
       </c>
       <c r="H60" t="n">
-        <v>33.63</v>
+        <v>55.84</v>
       </c>
       <c r="I60" s="6" t="inlineStr">
         <is>
@@ -3167,10 +3167,10 @@
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.756</v>
+        <v>3.598</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>0.819</v>
+        <v>2.739</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="7" t="inlineStr"/>
@@ -3183,39 +3183,39 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>5326</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>99SMART</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="E61" s="3" t="n">
-        <v>0.0449</v>
+        <v>1.28</v>
+      </c>
+      <c r="E61" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>3691800</v>
+        <v>3874800</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.87</v>
+        <v>0.35</v>
       </c>
       <c r="H61" t="n">
-        <v>52.06</v>
-      </c>
-      <c r="I61" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.08</v>
+      </c>
+      <c r="I61" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>3.199</v>
+        <v>1.322</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>3.39</v>
+        <v>1.305</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="7" t="inlineStr"/>
@@ -3228,28 +3228,28 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>SPSETIA</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>3.67</v>
-      </c>
-      <c r="E62" s="8" t="n">
-        <v>-0.0265</v>
+        <v>0.725</v>
+      </c>
+      <c r="E62" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>3668400</v>
+        <v>3824000</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.32</v>
+        <v>0.64</v>
       </c>
       <c r="H62" t="n">
-        <v>55.58</v>
+        <v>34.68</v>
       </c>
       <c r="I62" s="6" t="inlineStr">
         <is>
@@ -3257,10 +3257,10 @@
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>3.597</v>
+        <v>0.757</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>2.739</v>
+        <v>0.82</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="7" t="inlineStr"/>
@@ -3273,28 +3273,28 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0345</t>
+          <t>0111</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>SUNLOGY</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>0.455</v>
+        <v>0.165</v>
       </c>
       <c r="E63" s="3" t="n">
-        <v>0.0341</v>
+        <v>0.0313</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>3581000</v>
+        <v>3815200</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.34</v>
+        <v>1.16</v>
       </c>
       <c r="H63" t="n">
-        <v>52.28</v>
+        <v>59.38</v>
       </c>
       <c r="I63" s="9" t="inlineStr">
         <is>
@@ -3302,10 +3302,10 @@
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.451</v>
+        <v>0.156</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>0.426</v>
+        <v>0.145</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="7" t="inlineStr"/>
@@ -3318,39 +3318,39 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>TANCO</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="E64" s="10" t="n">
-        <v>0</v>
+        <v>0.45</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>0.0227</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>3578900</v>
+        <v>3765600</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0.21</v>
+        <v>0.36</v>
       </c>
       <c r="H64" t="n">
-        <v>30.21</v>
-      </c>
-      <c r="I64" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.11</v>
+      </c>
+      <c r="I64" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.165</v>
+        <v>0.45</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>0.201</v>
+        <v>0.426</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="7" t="inlineStr"/>
@@ -3363,39 +3363,39 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>5253</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>ECONBHD</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>1.28</v>
+        <v>0.125</v>
       </c>
       <c r="E65" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>3559600</v>
+        <v>3696000</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>0.32</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H65" t="n">
-        <v>43.08</v>
-      </c>
-      <c r="I65" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.25</v>
+      </c>
+      <c r="I65" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>1.322</v>
+        <v>0.122</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>1.305</v>
+        <v>0.125</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="7" t="inlineStr"/>
@@ -3408,39 +3408,39 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>5253</t>
+          <t>2429</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>ECONBHD</t>
+          <t>TANCO</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>0.125</v>
+        <v>0.15</v>
       </c>
       <c r="E66" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>3421000</v>
+        <v>3650000</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>0.75</v>
+        <v>0.21</v>
       </c>
       <c r="H66" t="n">
-        <v>55.25</v>
-      </c>
-      <c r="I66" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>30.21</v>
+      </c>
+      <c r="I66" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.122</v>
+        <v>0.165</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>0.125</v>
+        <v>0.201</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="7" t="inlineStr"/>
@@ -3468,10 +3468,10 @@
         <v>-0.0052</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>3355100</v>
+        <v>3599700</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>0.41</v>
+        <v>0.44</v>
       </c>
       <c r="H67" t="n">
         <v>54.49</v>
@@ -3498,28 +3498,28 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>0.795</v>
+        <v>2.71</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>0.0127</v>
+        <v>0.0112</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>3321800</v>
+        <v>3579900</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>0.25</v>
+        <v>0.6</v>
       </c>
       <c r="H68" t="n">
-        <v>57.16</v>
+        <v>57.99</v>
       </c>
       <c r="I68" s="9" t="inlineStr">
         <is>
@@ -3527,10 +3527,10 @@
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.767</v>
+        <v>2.629</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>0.712</v>
+        <v>2.581</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="7" t="inlineStr"/>
@@ -3558,10 +3558,10 @@
         <v>0</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>3272400</v>
+        <v>3575800</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>0.28</v>
+        <v>0.3</v>
       </c>
       <c r="H69" t="n">
         <v>28.11</v>
@@ -3584,39 +3584,39 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>TENAGA</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>12.96</v>
+        <v>1.26</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>0.004699999999999999</v>
+        <v>0.0161</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>3130300</v>
+        <v>3563100</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>0.35</v>
+        <v>0.4</v>
       </c>
       <c r="H70" t="n">
-        <v>42.32</v>
-      </c>
-      <c r="I70" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.42</v>
+      </c>
+      <c r="I70" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>13.036</v>
+        <v>1.286</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>13.573</v>
+        <v>1.387</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="7" t="inlineStr"/>
@@ -3629,39 +3629,39 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>2.7</v>
+        <v>0.525</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>0.0075</v>
+        <v>0.0294</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>3087800</v>
+        <v>3556400</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>0.52</v>
+        <v>0.21</v>
       </c>
       <c r="H71" t="n">
-        <v>57.33</v>
-      </c>
-      <c r="I71" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>55.9</v>
+      </c>
+      <c r="I71" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>2.628</v>
+        <v>0.512</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>2.581</v>
+        <v>0.436</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="7" t="inlineStr"/>
@@ -3683,19 +3683,19 @@
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="E72" s="3" t="n">
-        <v>0.0182</v>
+        <v>0.0364</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>3084500</v>
+        <v>3519900</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>0.32</v>
+        <v>0.37</v>
       </c>
       <c r="H72" t="n">
-        <v>64.88</v>
+        <v>67.13</v>
       </c>
       <c r="I72" s="9" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>1.069</v>
+        <v>1.071</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>0.916</v>
+        <v>0.917</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="7" t="inlineStr"/>
@@ -3719,28 +3719,28 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>0.53</v>
+        <v>5.6</v>
       </c>
       <c r="E73" s="3" t="n">
-        <v>0.0392</v>
+        <v>0.0072</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>3084400</v>
+        <v>3465300</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>0.19</v>
+        <v>0.24</v>
       </c>
       <c r="H73" t="n">
-        <v>56.74</v>
+        <v>50.83</v>
       </c>
       <c r="I73" s="6" t="inlineStr">
         <is>
@@ -3748,10 +3748,10 @@
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.512</v>
+        <v>5.636</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>0.436</v>
+        <v>5.308</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="7" t="inlineStr"/>
@@ -3764,28 +3764,28 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="E74" s="10" t="n">
-        <v>0</v>
+        <v>0.54</v>
+      </c>
+      <c r="E74" s="8" t="n">
+        <v>-0.027</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>3074800</v>
+        <v>3464500</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>0.12</v>
+        <v>0.64</v>
       </c>
       <c r="H74" t="n">
-        <v>29.99</v>
+        <v>31.37</v>
       </c>
       <c r="I74" s="6" t="inlineStr">
         <is>
@@ -3793,10 +3793,10 @@
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.249</v>
+        <v>0.592</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>0.304</v>
+        <v>0.641</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="7" t="inlineStr"/>
@@ -3809,39 +3809,39 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>TENAGA</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>0.91</v>
+        <v>12.96</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>0.0225</v>
+        <v>0.004699999999999999</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>3045100</v>
+        <v>3385900</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>1.05</v>
+        <v>0.37</v>
       </c>
       <c r="H75" t="n">
-        <v>46.13</v>
-      </c>
-      <c r="I75" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>42.32</v>
+      </c>
+      <c r="I75" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.911</v>
+        <v>13.036</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>0.964</v>
+        <v>13.573</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="7" t="inlineStr"/>
@@ -3854,39 +3854,39 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="E76" s="8" t="n">
-        <v>-0.009000000000000001</v>
+        <v>0.79</v>
+      </c>
+      <c r="E76" s="3" t="n">
+        <v>0.0064</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>3041200</v>
+        <v>3383800</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.25</v>
       </c>
       <c r="H76" t="n">
-        <v>33.2</v>
-      </c>
-      <c r="I76" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.46</v>
+      </c>
+      <c r="I76" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.592</v>
+        <v>0.767</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>0.641</v>
+        <v>0.712</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="7" t="inlineStr"/>
@@ -3899,39 +3899,39 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0243</t>
+          <t>0296</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>CENGILD</t>
+          <t>HEGROUP</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>0.16</v>
+        <v>1.13</v>
       </c>
       <c r="E77" s="8" t="n">
-        <v>-0.1351</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>3000700</v>
+        <v>3295900</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>13.35</v>
+        <v>0.68</v>
       </c>
       <c r="H77" t="n">
-        <v>18.12</v>
-      </c>
-      <c r="I77" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>68.90000000000001</v>
+      </c>
+      <c r="I77" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.192</v>
+        <v>1.058</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>0.195</v>
+        <v>0.892</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="7" t="inlineStr"/>
@@ -3953,19 +3953,19 @@
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>2.87</v>
+        <v>2.91</v>
       </c>
       <c r="E78" s="3" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.0211</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>2977300</v>
+        <v>3285900</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>0.95</v>
+        <v>1.05</v>
       </c>
       <c r="H78" t="n">
-        <v>75.91</v>
+        <v>77.34</v>
       </c>
       <c r="I78" s="9" t="inlineStr">
         <is>
@@ -3973,10 +3973,10 @@
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>2.639</v>
+        <v>2.643</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>2.285</v>
+        <v>2.286</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="7" t="inlineStr"/>
@@ -3989,39 +3989,39 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>5210</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="E79" s="3" t="n">
-        <v>0.0165</v>
+        <v>0.33</v>
+      </c>
+      <c r="E79" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>2861600</v>
+        <v>3225000</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>0.85</v>
+        <v>0.53</v>
       </c>
       <c r="H79" t="n">
-        <v>75.64</v>
-      </c>
-      <c r="I79" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.06</v>
+      </c>
+      <c r="I79" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>1.023</v>
+        <v>0.339</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>0.86</v>
+        <v>0.345</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="7" t="inlineStr"/>
@@ -4034,39 +4034,39 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0268</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>L&amp;PBHD</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>0.235</v>
+        <v>0.225</v>
       </c>
       <c r="E80" s="3" t="n">
-        <v>0.0682</v>
+        <v>0.0227</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>2808700</v>
+        <v>3146600</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>1.41</v>
+        <v>0.12</v>
       </c>
       <c r="H80" t="n">
-        <v>76.23999999999999</v>
-      </c>
-      <c r="I80" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.07</v>
+      </c>
+      <c r="I80" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.205</v>
+        <v>0.249</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>0.171</v>
+        <v>0.304</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="7" t="inlineStr"/>
@@ -4079,39 +4079,39 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>CNERGEN</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>5.6</v>
+        <v>1.23</v>
       </c>
       <c r="E81" s="3" t="n">
-        <v>0.0072</v>
+        <v>0.0165</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>2782200</v>
+        <v>3130200</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>0.2</v>
+        <v>0.93</v>
       </c>
       <c r="H81" t="n">
-        <v>50.83</v>
-      </c>
-      <c r="I81" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>75.64</v>
+      </c>
+      <c r="I81" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J81" s="2" t="n">
-        <v>5.636</v>
+        <v>1.023</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>5.308</v>
+        <v>0.86</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="7" t="inlineStr"/>
@@ -4124,39 +4124,39 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0296</t>
+          <t>0175</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>HEGROUP</t>
+          <t>HHRG</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="E82" s="8" t="n">
-        <v>-0.0175</v>
+        <v>0.145</v>
+      </c>
+      <c r="E82" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>2707300</v>
+        <v>3118000</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="H82" t="n">
-        <v>66.73</v>
-      </c>
-      <c r="I82" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.09</v>
+      </c>
+      <c r="I82" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>1.057</v>
+        <v>0.156</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>0.891</v>
+        <v>0.148</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="7" t="inlineStr"/>
@@ -4169,39 +4169,39 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>0338</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>KOPI</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>0.975</v>
-      </c>
-      <c r="E83" s="8" t="n">
-        <v>-0.0201</v>
+        <v>0.915</v>
+      </c>
+      <c r="E83" s="3" t="n">
+        <v>0.0281</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>2649600</v>
+        <v>3046700</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>0.82</v>
+        <v>1.05</v>
       </c>
       <c r="H83" t="n">
-        <v>83.41</v>
-      </c>
-      <c r="I83" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.14</v>
+      </c>
+      <c r="I83" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.656</v>
+        <v>0.912</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>0.479</v>
+        <v>0.964</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="7" t="inlineStr"/>
@@ -4214,28 +4214,28 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>0.72</v>
+        <v>1.64</v>
       </c>
       <c r="E84" s="3" t="n">
-        <v>0.0286</v>
+        <v>0.0314</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>2642500</v>
+        <v>3024300</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>0.29</v>
+        <v>0.45</v>
       </c>
       <c r="H84" t="n">
-        <v>63.57</v>
+        <v>41.93</v>
       </c>
       <c r="I84" s="9" t="inlineStr">
         <is>
@@ -4243,10 +4243,10 @@
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.672</v>
+        <v>1.671</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>0.607</v>
+        <v>1.787</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="7" t="inlineStr"/>
@@ -4259,28 +4259,28 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>0272</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>NEXG</t>
+          <t>TTVHB</t>
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>0.295</v>
+        <v>0.265</v>
       </c>
       <c r="E85" s="3" t="n">
-        <v>0.0172</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>2558700</v>
+        <v>3006200</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>0.21</v>
+        <v>1.5</v>
       </c>
       <c r="H85" t="n">
-        <v>52.49</v>
+        <v>56.99</v>
       </c>
       <c r="I85" s="9" t="inlineStr">
         <is>
@@ -4288,10 +4288,10 @@
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.291</v>
+        <v>0.249</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>0.281</v>
+        <v>0.253</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="7" t="inlineStr"/>
@@ -4304,28 +4304,28 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>0243</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>CENGILD</t>
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="E86" s="3" t="n">
-        <v>0.0242</v>
+        <v>0.16</v>
+      </c>
+      <c r="E86" s="8" t="n">
+        <v>-0.1351</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>2556200</v>
+        <v>3002700</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>0.29</v>
+        <v>13.36</v>
       </c>
       <c r="H86" t="n">
-        <v>41.85</v>
+        <v>18.12</v>
       </c>
       <c r="I86" s="6" t="inlineStr">
         <is>
@@ -4333,10 +4333,10 @@
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>1.287</v>
+        <v>0.192</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>1.387</v>
+        <v>0.195</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="7" t="inlineStr"/>
@@ -4349,39 +4349,39 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>2.11</v>
+        <v>0.71</v>
       </c>
       <c r="E87" s="3" t="n">
-        <v>0.0048</v>
+        <v>0.0143</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v>2522600</v>
+        <v>2965500</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>0.13</v>
+        <v>0.32</v>
       </c>
       <c r="H87" t="n">
-        <v>52.16</v>
-      </c>
-      <c r="I87" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.05</v>
+      </c>
+      <c r="I87" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>2.099</v>
+        <v>0.671</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>2.081</v>
+        <v>0.607</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="7" t="inlineStr"/>
@@ -4394,28 +4394,28 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>0268</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>L&amp;PBHD</t>
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>0.795</v>
+        <v>0.24</v>
       </c>
       <c r="E88" s="3" t="n">
-        <v>0.0192</v>
+        <v>0.09089999999999999</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>2510700</v>
+        <v>2919800</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>0.36</v>
+        <v>1.46</v>
       </c>
       <c r="H88" t="n">
-        <v>64.39</v>
+        <v>77.70999999999999</v>
       </c>
       <c r="I88" s="9" t="inlineStr">
         <is>
@@ -4423,10 +4423,10 @@
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.735</v>
+        <v>0.206</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>0.652</v>
+        <v>0.171</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="7" t="inlineStr"/>
@@ -4439,39 +4439,39 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>1.64</v>
+        <v>2.11</v>
       </c>
       <c r="E89" s="3" t="n">
-        <v>0.0314</v>
+        <v>0.0048</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>2493900</v>
+        <v>2760800</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>0.37</v>
+        <v>0.14</v>
       </c>
       <c r="H89" t="n">
-        <v>41.93</v>
-      </c>
-      <c r="I89" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.16</v>
+      </c>
+      <c r="I89" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>1.671</v>
+        <v>2.099</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>1.787</v>
+        <v>2.081</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="7" t="inlineStr"/>
@@ -4484,28 +4484,28 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>ALPHA</t>
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E90" s="3" t="n">
-        <v>0.0172</v>
+        <v>0.275</v>
+      </c>
+      <c r="E90" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>2428400</v>
+        <v>2752300</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>0.27</v>
+        <v>1.15</v>
       </c>
       <c r="H90" t="n">
-        <v>57.36</v>
+        <v>63.87</v>
       </c>
       <c r="I90" s="9" t="inlineStr">
         <is>
@@ -4513,10 +4513,10 @@
         </is>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.278</v>
+        <v>0.259</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>0.303</v>
+        <v>0.257</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="7" t="inlineStr"/>
@@ -4529,28 +4529,28 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>1.05</v>
+        <v>0.985</v>
       </c>
       <c r="E91" s="8" t="n">
-        <v>-0.0187</v>
+        <v>-0.0101</v>
       </c>
       <c r="F91" s="4" t="n">
-        <v>2424300</v>
+        <v>2752300</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>0.17</v>
+        <v>0.85</v>
       </c>
       <c r="H91" t="n">
-        <v>47.46</v>
+        <v>84.86</v>
       </c>
       <c r="I91" s="9" t="inlineStr">
         <is>
@@ -4558,10 +4558,10 @@
         </is>
       </c>
       <c r="J91" s="2" t="n">
-        <v>1.07</v>
+        <v>0.657</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>1.037</v>
+        <v>0.479</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="7" t="inlineStr"/>
@@ -4574,28 +4574,28 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0272</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>TTVHB</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>0.255</v>
+        <v>0.79</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0.0408</v>
+        <v>0.0128</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v>2318600</v>
+        <v>2745500</v>
       </c>
       <c r="G92" s="5" t="n">
-        <v>1.15</v>
+        <v>0.39</v>
       </c>
       <c r="H92" t="n">
-        <v>52.98</v>
+        <v>63.79</v>
       </c>
       <c r="I92" s="9" t="inlineStr">
         <is>
@@ -4603,10 +4603,10 @@
         </is>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.248</v>
+        <v>0.735</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>0.253</v>
+        <v>0.652</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="7" t="inlineStr"/>
@@ -4619,39 +4619,39 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D93" s="2" t="n">
-        <v>0.535</v>
-      </c>
-      <c r="E93" s="3" t="n">
-        <v>0.009399999999999999</v>
+        <v>1.05</v>
+      </c>
+      <c r="E93" s="8" t="n">
+        <v>-0.0187</v>
       </c>
       <c r="F93" s="4" t="n">
-        <v>2311000</v>
+        <v>2642700</v>
       </c>
       <c r="G93" s="5" t="n">
-        <v>0.3</v>
+        <v>0.18</v>
       </c>
       <c r="H93" t="n">
-        <v>55.09</v>
-      </c>
-      <c r="I93" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.46</v>
+      </c>
+      <c r="I93" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.522</v>
+        <v>1.07</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>0.531</v>
+        <v>1.037</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="7" t="inlineStr"/>
@@ -4664,28 +4664,28 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>CPETECH</t>
+          <t>NEXG</t>
         </is>
       </c>
       <c r="D94" s="2" t="n">
-        <v>1.35</v>
+        <v>0.3</v>
       </c>
       <c r="E94" s="3" t="n">
-        <v>0.015</v>
+        <v>0.0345</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>2185500</v>
+        <v>2590500</v>
       </c>
       <c r="G94" s="5" t="n">
-        <v>0.58</v>
+        <v>0.21</v>
       </c>
       <c r="H94" t="n">
-        <v>57.71</v>
+        <v>54.14</v>
       </c>
       <c r="I94" s="9" t="inlineStr">
         <is>
@@ -4693,10 +4693,10 @@
         </is>
       </c>
       <c r="J94" s="2" t="n">
-        <v>1.294</v>
+        <v>0.292</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>1.194</v>
+        <v>0.281</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="7" t="inlineStr"/>
@@ -4709,39 +4709,39 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0239</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>ECOMATE</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D95" s="2" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E95" s="10" t="n">
-        <v>0</v>
+        <v>0.8</v>
+      </c>
+      <c r="E95" s="8" t="n">
+        <v>-0.0062</v>
       </c>
       <c r="F95" s="4" t="n">
-        <v>2152900</v>
+        <v>2508600</v>
       </c>
       <c r="G95" s="5" t="n">
-        <v>0.67</v>
+        <v>0.41</v>
       </c>
       <c r="H95" t="n">
-        <v>52.86</v>
-      </c>
-      <c r="I95" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>65.37</v>
+      </c>
+      <c r="I95" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.864</v>
+        <v>0.785</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>0.858</v>
+        <v>0.764</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="7" t="inlineStr"/>
@@ -4754,28 +4754,28 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>0388</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>SEMICO</t>
         </is>
       </c>
       <c r="D96" s="2" t="n">
-        <v>0.355</v>
-      </c>
-      <c r="E96" s="3" t="n">
-        <v>0.0143</v>
+        <v>0.615</v>
+      </c>
+      <c r="E96" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>2152100</v>
+        <v>2483900</v>
       </c>
       <c r="G96" s="5" t="n">
-        <v>0.28</v>
+        <v>0.85</v>
       </c>
       <c r="H96" t="n">
-        <v>58.58</v>
+        <v>59.01</v>
       </c>
       <c r="I96" s="9" t="inlineStr">
         <is>
@@ -4783,10 +4783,10 @@
         </is>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.344</v>
+        <v>0.612</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>0.324</v>
+        <v>0.598</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="7" t="inlineStr"/>
@@ -4799,28 +4799,28 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0045</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>SSB8</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D97" s="2" t="n">
-        <v>0.655</v>
-      </c>
-      <c r="E97" s="8" t="n">
-        <v>-0.0224</v>
+        <v>0.295</v>
+      </c>
+      <c r="E97" s="3" t="n">
+        <v>0.0172</v>
       </c>
       <c r="F97" s="4" t="n">
-        <v>2142300</v>
+        <v>2472800</v>
       </c>
       <c r="G97" s="5" t="n">
-        <v>0.52</v>
+        <v>0.28</v>
       </c>
       <c r="H97" t="n">
-        <v>58.35</v>
+        <v>57.36</v>
       </c>
       <c r="I97" s="9" t="inlineStr">
         <is>
@@ -4828,10 +4828,10 @@
         </is>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.636</v>
+        <v>0.278</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>0.601</v>
+        <v>0.303</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="7" t="inlineStr"/>
@@ -4844,39 +4844,39 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>0045</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>SSB8</t>
         </is>
       </c>
       <c r="D98" s="2" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="E98" s="3" t="n">
-        <v>0.008100000000000001</v>
+        <v>0.665</v>
+      </c>
+      <c r="E98" s="8" t="n">
+        <v>-0.0075</v>
       </c>
       <c r="F98" s="4" t="n">
-        <v>2090700</v>
+        <v>2460400</v>
       </c>
       <c r="G98" s="5" t="n">
-        <v>0.16</v>
+        <v>0.59</v>
       </c>
       <c r="H98" t="n">
-        <v>58.18</v>
-      </c>
-      <c r="I98" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62</v>
+      </c>
+      <c r="I98" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J98" s="2" t="n">
-        <v>2.463</v>
+        <v>0.637</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>2.344</v>
+        <v>0.601</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="7" t="inlineStr"/>
@@ -4889,28 +4889,28 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D99" s="2" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="E99" s="8" t="n">
-        <v>-0.0141</v>
+        <v>0.535</v>
+      </c>
+      <c r="E99" s="3" t="n">
+        <v>0.009399999999999999</v>
       </c>
       <c r="F99" s="4" t="n">
-        <v>2062200</v>
+        <v>2440000</v>
       </c>
       <c r="G99" s="5" t="n">
-        <v>0.26</v>
+        <v>0.32</v>
       </c>
       <c r="H99" t="n">
-        <v>42.46</v>
+        <v>55.09</v>
       </c>
       <c r="I99" s="6" t="inlineStr">
         <is>
@@ -4918,10 +4918,10 @@
         </is>
       </c>
       <c r="J99" s="2" t="n">
-        <v>4.366</v>
+        <v>0.522</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>4.463</v>
+        <v>0.531</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="7" t="inlineStr"/>
@@ -4934,28 +4934,28 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>0359</t>
+          <t>6947</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>HKB</t>
+          <t>CDB</t>
         </is>
       </c>
       <c r="D100" s="2" t="n">
-        <v>0.82</v>
+        <v>2.52</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0.0186</v>
+        <v>0.0202</v>
       </c>
       <c r="F100" s="4" t="n">
-        <v>2052400</v>
+        <v>2396700</v>
       </c>
       <c r="G100" s="5" t="n">
-        <v>0.92</v>
+        <v>0.77</v>
       </c>
       <c r="H100" t="n">
-        <v>82.16</v>
+        <v>37.33</v>
       </c>
       <c r="I100" s="9" t="inlineStr">
         <is>
@@ -4963,10 +4963,10 @@
         </is>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.679</v>
+        <v>2.583</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>0.622</v>
+        <v>2.731</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="7" t="inlineStr"/>
@@ -4979,28 +4979,28 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>0388</t>
+          <t>6633</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>SEMICO</t>
+          <t>LHI</t>
         </is>
       </c>
       <c r="D101" s="2" t="n">
-        <v>0.615</v>
+        <v>0.73</v>
       </c>
       <c r="E101" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F101" s="4" t="n">
-        <v>2043100</v>
+        <v>2384400</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>0.7</v>
+        <v>1.43</v>
       </c>
       <c r="H101" t="n">
-        <v>59.01</v>
+        <v>47.32</v>
       </c>
       <c r="I101" s="9" t="inlineStr">
         <is>
@@ -5008,10 +5008,10 @@
         </is>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.612</v>
+        <v>0.735</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>0.598</v>
+        <v>0.749</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="7" t="inlineStr"/>
@@ -5024,39 +5024,39 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>0267</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>ECA</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D102" s="2" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="E102" s="3" t="n">
-        <v>0.0548</v>
+        <v>4.21</v>
+      </c>
+      <c r="E102" s="8" t="n">
+        <v>-0.0117</v>
       </c>
       <c r="F102" s="4" t="n">
-        <v>2031000</v>
+        <v>2355600</v>
       </c>
       <c r="G102" s="5" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="H102" t="n">
-        <v>54.15</v>
-      </c>
-      <c r="I102" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.76</v>
+      </c>
+      <c r="I102" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.367</v>
+        <v>4.367</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>0.374</v>
+        <v>4.463</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="7" t="inlineStr"/>
@@ -5069,28 +5069,28 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>0056</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>ATECH</t>
+          <t>NCT</t>
         </is>
       </c>
       <c r="D103" s="2" t="n">
-        <v>0.805</v>
-      </c>
-      <c r="E103" s="3" t="n">
-        <v>0.019</v>
+        <v>0.57</v>
+      </c>
+      <c r="E103" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F103" s="4" t="n">
-        <v>2030000</v>
+        <v>2355400</v>
       </c>
       <c r="G103" s="5" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="H103" t="n">
-        <v>59.79</v>
+        <v>54.19</v>
       </c>
       <c r="I103" s="9" t="inlineStr">
         <is>
@@ -5098,10 +5098,10 @@
         </is>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.77</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>0.761</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="7" t="inlineStr"/>
@@ -5114,39 +5114,39 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>CMSB</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D104" s="2" t="n">
-        <v>0.92</v>
+        <v>0.355</v>
       </c>
       <c r="E104" s="3" t="n">
-        <v>0.0166</v>
+        <v>0.0143</v>
       </c>
       <c r="F104" s="4" t="n">
-        <v>2011400</v>
+        <v>2306800</v>
       </c>
       <c r="G104" s="5" t="n">
-        <v>0.98</v>
+        <v>0.3</v>
       </c>
       <c r="H104" t="n">
-        <v>33.38</v>
-      </c>
-      <c r="I104" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.58</v>
+      </c>
+      <c r="I104" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.96</v>
+        <v>0.344</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>0.993</v>
+        <v>0.324</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="7" t="inlineStr"/>
@@ -5159,39 +5159,39 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D105" s="2" t="n">
-        <v>0.545</v>
-      </c>
-      <c r="E105" s="10" t="n">
-        <v>0</v>
+        <v>7.19</v>
+      </c>
+      <c r="E105" s="3" t="n">
+        <v>0.0098</v>
       </c>
       <c r="F105" s="4" t="n">
-        <v>1983200</v>
+        <v>2300000</v>
       </c>
       <c r="G105" s="5" t="n">
-        <v>0.48</v>
+        <v>0.29</v>
       </c>
       <c r="H105" t="n">
-        <v>71.06999999999999</v>
-      </c>
-      <c r="I105" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.49</v>
+      </c>
+      <c r="I105" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.477</v>
+        <v>7.408</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>0.451</v>
+        <v>7.724</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="7" t="inlineStr"/>
@@ -5204,28 +5204,28 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>0249</t>
+          <t>0359</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>LGMS</t>
+          <t>HKB</t>
         </is>
       </c>
       <c r="D106" s="2" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="E106" s="8" t="n">
-        <v>-0.0175</v>
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="E106" s="3" t="n">
+        <v>0.0124</v>
       </c>
       <c r="F106" s="4" t="n">
-        <v>1976400</v>
+        <v>2224000</v>
       </c>
       <c r="G106" s="5" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="H106" t="n">
-        <v>66.75</v>
+        <v>81.81</v>
       </c>
       <c r="I106" s="9" t="inlineStr">
         <is>
@@ -5233,10 +5233,10 @@
         </is>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.522</v>
+        <v>0.679</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>0.504</v>
+        <v>0.622</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="7" t="inlineStr"/>
@@ -5249,28 +5249,28 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>4863</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>TM</t>
+          <t>CPETECH</t>
         </is>
       </c>
       <c r="D107" s="2" t="n">
-        <v>7.89</v>
+        <v>1.36</v>
       </c>
       <c r="E107" s="3" t="n">
-        <v>0.0025</v>
+        <v>0.0226</v>
       </c>
       <c r="F107" s="4" t="n">
-        <v>1965800</v>
+        <v>2214300</v>
       </c>
       <c r="G107" s="5" t="n">
-        <v>0.66</v>
+        <v>0.58</v>
       </c>
       <c r="H107" t="n">
-        <v>50.7</v>
+        <v>58.46</v>
       </c>
       <c r="I107" s="9" t="inlineStr">
         <is>
@@ -5278,10 +5278,10 @@
         </is>
       </c>
       <c r="J107" s="2" t="n">
-        <v>7.892</v>
+        <v>1.295</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>7.85</v>
+        <v>1.194</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="7" t="inlineStr"/>
@@ -5294,28 +5294,28 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>5210</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D108" s="2" t="n">
-        <v>0.325</v>
-      </c>
-      <c r="E108" s="8" t="n">
-        <v>-0.0152</v>
+        <v>2.5</v>
+      </c>
+      <c r="E108" s="3" t="n">
+        <v>0.008100000000000001</v>
       </c>
       <c r="F108" s="4" t="n">
-        <v>1950500</v>
+        <v>2210000</v>
       </c>
       <c r="G108" s="5" t="n">
-        <v>0.32</v>
+        <v>0.16</v>
       </c>
       <c r="H108" t="n">
-        <v>32.41</v>
+        <v>58.18</v>
       </c>
       <c r="I108" s="6" t="inlineStr">
         <is>
@@ -5323,10 +5323,10 @@
         </is>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.339</v>
+        <v>2.463</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>0.345</v>
+        <v>2.344</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="7" t="inlineStr"/>
@@ -5339,39 +5339,39 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>6633</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>LHI</t>
+          <t>CMSB</t>
         </is>
       </c>
       <c r="D109" s="2" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="E109" s="8" t="n">
-        <v>-0.0137</v>
+        <v>0.91</v>
+      </c>
+      <c r="E109" s="3" t="n">
+        <v>0.005500000000000001</v>
       </c>
       <c r="F109" s="4" t="n">
-        <v>1947400</v>
+        <v>2198300</v>
       </c>
       <c r="G109" s="5" t="n">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="H109" t="n">
-        <v>44.17</v>
-      </c>
-      <c r="I109" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>28.89</v>
+      </c>
+      <c r="I109" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.734</v>
+        <v>0.959</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>0.748</v>
+        <v>0.993</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="7" t="inlineStr"/>
@@ -5384,28 +5384,28 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>6947</t>
+          <t>0267</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>CDB</t>
+          <t>ECA</t>
         </is>
       </c>
       <c r="D110" s="2" t="n">
-        <v>2.53</v>
+        <v>0.38</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>0.0243</v>
+        <v>0.0411</v>
       </c>
       <c r="F110" s="4" t="n">
-        <v>1934000</v>
+        <v>2173100</v>
       </c>
       <c r="G110" s="5" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="H110" t="n">
-        <v>38.88</v>
+        <v>53.04</v>
       </c>
       <c r="I110" s="9" t="inlineStr">
         <is>
@@ -5413,10 +5413,10 @@
         </is>
       </c>
       <c r="J110" s="2" t="n">
-        <v>2.584</v>
+        <v>0.366</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>2.731</v>
+        <v>0.374</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="7" t="inlineStr"/>
@@ -5429,28 +5429,28 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>4863</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>TM</t>
         </is>
       </c>
       <c r="D111" s="2" t="n">
-        <v>4.24</v>
+        <v>7.88</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0.0192</v>
+        <v>0.0013</v>
       </c>
       <c r="F111" s="4" t="n">
-        <v>1930700</v>
+        <v>2162800</v>
       </c>
       <c r="G111" s="5" t="n">
-        <v>0.23</v>
+        <v>0.72</v>
       </c>
       <c r="H111" t="n">
-        <v>64.51000000000001</v>
+        <v>50.14</v>
       </c>
       <c r="I111" s="9" t="inlineStr">
         <is>
@@ -5458,10 +5458,10 @@
         </is>
       </c>
       <c r="J111" s="2" t="n">
-        <v>3.965</v>
+        <v>7.891</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>3.443</v>
+        <v>7.849</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="7" t="inlineStr"/>
@@ -5474,28 +5474,28 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>5322</t>
+          <t>0239</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>FEYTECH</t>
+          <t>ECOMATE</t>
         </is>
       </c>
       <c r="D112" s="2" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="E112" s="8" t="n">
-        <v>-0.0213</v>
+        <v>0.865</v>
+      </c>
+      <c r="E112" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F112" s="4" t="n">
-        <v>1917500</v>
+        <v>2152900</v>
       </c>
       <c r="G112" s="5" t="n">
-        <v>2.76</v>
+        <v>0.67</v>
       </c>
       <c r="H112" t="n">
-        <v>48.43</v>
+        <v>52.86</v>
       </c>
       <c r="I112" s="6" t="inlineStr">
         <is>
@@ -5503,10 +5503,10 @@
         </is>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.232</v>
+        <v>0.864</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>0.234</v>
+        <v>0.858</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="7" t="inlineStr"/>
@@ -5519,39 +5519,39 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D113" s="2" t="n">
-        <v>7.18</v>
+        <v>4.25</v>
       </c>
       <c r="E113" s="3" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.0216</v>
       </c>
       <c r="F113" s="4" t="n">
-        <v>1875900</v>
+        <v>2136700</v>
       </c>
       <c r="G113" s="5" t="n">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="H113" t="n">
-        <v>33.84</v>
-      </c>
-      <c r="I113" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.75</v>
+      </c>
+      <c r="I113" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J113" s="2" t="n">
-        <v>7.407</v>
+        <v>3.966</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>7.723</v>
+        <v>3.443</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="7" t="inlineStr"/>
@@ -5564,28 +5564,28 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>5302</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>ATECH</t>
         </is>
       </c>
       <c r="D114" s="2" t="n">
-        <v>0.805</v>
-      </c>
-      <c r="E114" s="10" t="n">
-        <v>0</v>
+        <v>0.8</v>
+      </c>
+      <c r="E114" s="3" t="n">
+        <v>0.0127</v>
       </c>
       <c r="F114" s="4" t="n">
-        <v>1870700</v>
+        <v>2096800</v>
       </c>
       <c r="G114" s="5" t="n">
-        <v>0.3</v>
+        <v>1.15</v>
       </c>
       <c r="H114" t="n">
-        <v>70.15000000000001</v>
+        <v>58.78</v>
       </c>
       <c r="I114" s="9" t="inlineStr">
         <is>
@@ -5593,10 +5593,10 @@
         </is>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.785</v>
+        <v>0.77</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>0.764</v>
+        <v>0.761</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="7" t="inlineStr"/>
@@ -5609,39 +5609,39 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>7225</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D115" s="2" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E115" s="8" t="n">
-        <v>-0.0244</v>
+        <v>0.545</v>
+      </c>
+      <c r="E115" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F115" s="4" t="n">
-        <v>1855100</v>
+        <v>2047300</v>
       </c>
       <c r="G115" s="5" t="n">
-        <v>0.4</v>
+        <v>0.49</v>
       </c>
       <c r="H115" t="n">
-        <v>42.79</v>
-      </c>
-      <c r="I115" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>71.06999999999999</v>
+      </c>
+      <c r="I115" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.207</v>
+        <v>0.477</v>
       </c>
       <c r="K115" s="2" t="n">
-        <v>0.208</v>
+        <v>0.451</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="7" t="inlineStr"/>
@@ -5654,39 +5654,39 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>0249</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>LGMS</t>
         </is>
       </c>
       <c r="D116" s="2" t="n">
-        <v>0.9350000000000001</v>
-      </c>
-      <c r="E116" s="3" t="n">
-        <v>0.0054</v>
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="E116" s="8" t="n">
+        <v>-0.008800000000000001</v>
       </c>
       <c r="F116" s="4" t="n">
-        <v>1834800</v>
+        <v>2006900</v>
       </c>
       <c r="G116" s="5" t="n">
-        <v>1.07</v>
+        <v>2.23</v>
       </c>
       <c r="H116" t="n">
-        <v>54.68</v>
-      </c>
-      <c r="I116" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>69.2</v>
+      </c>
+      <c r="I116" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.923</v>
+        <v>0.523</v>
       </c>
       <c r="K116" s="2" t="n">
-        <v>0.85</v>
+        <v>0.504</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="7" t="inlineStr"/>
@@ -5699,28 +5699,28 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>5337</t>
+          <t>7225</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>ECOSHOP</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="D117" s="2" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="E117" s="3" t="n">
-        <v>0.021</v>
+        <v>0.2</v>
+      </c>
+      <c r="E117" s="8" t="n">
+        <v>-0.0244</v>
       </c>
       <c r="F117" s="4" t="n">
-        <v>1798200</v>
+        <v>1992100</v>
       </c>
       <c r="G117" s="5" t="n">
-        <v>0.39</v>
+        <v>0.43</v>
       </c>
       <c r="H117" t="n">
-        <v>49.32</v>
+        <v>42.79</v>
       </c>
       <c r="I117" s="6" t="inlineStr">
         <is>
@@ -5728,10 +5728,10 @@
         </is>
       </c>
       <c r="J117" s="2" t="n">
-        <v>1.461</v>
+        <v>0.207</v>
       </c>
       <c r="K117" s="2" t="n">
-        <v>1.469</v>
+        <v>0.208</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="7" t="inlineStr"/>
@@ -5744,39 +5744,39 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>0056</t>
+          <t>5306</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>NCT</t>
+          <t>FFB</t>
         </is>
       </c>
       <c r="D118" s="2" t="n">
-        <v>0.5649999999999999</v>
-      </c>
-      <c r="E118" s="8" t="n">
-        <v>-0.008800000000000001</v>
+        <v>1.8</v>
+      </c>
+      <c r="E118" s="3" t="n">
+        <v>0.0286</v>
       </c>
       <c r="F118" s="4" t="n">
-        <v>1795400</v>
+        <v>1956100</v>
       </c>
       <c r="G118" s="5" t="n">
-        <v>0.83</v>
+        <v>0.67</v>
       </c>
       <c r="H118" t="n">
-        <v>51.06</v>
-      </c>
-      <c r="I118" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>32.69</v>
+      </c>
+      <c r="I118" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.5629999999999999</v>
+        <v>1.88</v>
       </c>
       <c r="K118" s="2" t="n">
-        <v>0.5620000000000001</v>
+        <v>2.017</v>
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" s="7" t="inlineStr"/>
@@ -5789,39 +5789,39 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>0328</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>3REN</t>
+          <t>AMBANK</t>
         </is>
       </c>
       <c r="D119" s="2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E119" s="3" t="n">
-        <v>0.039</v>
+        <v>6.09</v>
+      </c>
+      <c r="E119" s="8" t="n">
+        <v>-0.0016</v>
       </c>
       <c r="F119" s="4" t="n">
-        <v>1737400</v>
+        <v>1941400</v>
       </c>
       <c r="G119" s="5" t="n">
-        <v>0.88</v>
+        <v>0.42</v>
       </c>
       <c r="H119" t="n">
-        <v>56.15</v>
-      </c>
-      <c r="I119" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>22.87</v>
+      </c>
+      <c r="I119" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.386</v>
+        <v>6.473</v>
       </c>
       <c r="K119" s="2" t="n">
-        <v>0.391</v>
+        <v>6.826</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="7" t="inlineStr"/>
@@ -5834,28 +5834,28 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>5322</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>AMBANK</t>
+          <t>FEYTECH</t>
         </is>
       </c>
       <c r="D120" s="2" t="n">
-        <v>6.09</v>
+        <v>0.23</v>
       </c>
       <c r="E120" s="8" t="n">
-        <v>-0.0016</v>
+        <v>-0.0213</v>
       </c>
       <c r="F120" s="4" t="n">
-        <v>1710600</v>
+        <v>1917500</v>
       </c>
       <c r="G120" s="5" t="n">
-        <v>0.37</v>
+        <v>2.76</v>
       </c>
       <c r="H120" t="n">
-        <v>22.87</v>
+        <v>48.43</v>
       </c>
       <c r="I120" s="6" t="inlineStr">
         <is>
@@ -5863,10 +5863,10 @@
         </is>
       </c>
       <c r="J120" s="2" t="n">
-        <v>6.473</v>
+        <v>0.232</v>
       </c>
       <c r="K120" s="2" t="n">
-        <v>6.826</v>
+        <v>0.234</v>
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="7" t="inlineStr"/>
@@ -5879,28 +5879,28 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>5306</t>
+          <t>0273</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>FFB</t>
+          <t>VLB</t>
         </is>
       </c>
       <c r="D121" s="2" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="E121" s="3" t="n">
-        <v>0.0229</v>
+        <v>0.93</v>
+      </c>
+      <c r="E121" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F121" s="4" t="n">
-        <v>1702100</v>
+        <v>1884600</v>
       </c>
       <c r="G121" s="5" t="n">
-        <v>0.58</v>
+        <v>1.1</v>
       </c>
       <c r="H121" t="n">
-        <v>30.67</v>
+        <v>53.94</v>
       </c>
       <c r="I121" s="6" t="inlineStr">
         <is>
@@ -5908,10 +5908,10 @@
         </is>
       </c>
       <c r="J121" s="2" t="n">
-        <v>1.879</v>
+        <v>0.922</v>
       </c>
       <c r="K121" s="2" t="n">
-        <v>2.017</v>
+        <v>0.85</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" s="7" t="inlineStr"/>
@@ -5924,28 +5924,28 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>5337</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>ECOSHOP</t>
         </is>
       </c>
       <c r="D122" s="2" t="n">
-        <v>1.85</v>
+        <v>1.46</v>
       </c>
       <c r="E122" s="3" t="n">
-        <v>0.0054</v>
+        <v>0.021</v>
       </c>
       <c r="F122" s="4" t="n">
-        <v>1642200</v>
+        <v>1883400</v>
       </c>
       <c r="G122" s="5" t="n">
-        <v>0.39</v>
+        <v>0.41</v>
       </c>
       <c r="H122" t="n">
-        <v>38.83</v>
+        <v>49.32</v>
       </c>
       <c r="I122" s="6" t="inlineStr">
         <is>
@@ -5953,10 +5953,10 @@
         </is>
       </c>
       <c r="J122" s="2" t="n">
-        <v>1.896</v>
+        <v>1.461</v>
       </c>
       <c r="K122" s="2" t="n">
-        <v>2.026</v>
+        <v>1.469</v>
       </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="7" t="inlineStr"/>
@@ -5969,39 +5969,39 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>0172</t>
+          <t>0328</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>OCK</t>
+          <t>3REN</t>
         </is>
       </c>
       <c r="D123" s="2" t="n">
-        <v>0.455</v>
+        <v>0.4</v>
       </c>
       <c r="E123" s="3" t="n">
-        <v>0.0225</v>
+        <v>0.039</v>
       </c>
       <c r="F123" s="4" t="n">
-        <v>1609800</v>
+        <v>1837400</v>
       </c>
       <c r="G123" s="5" t="n">
-        <v>0.45</v>
+        <v>0.93</v>
       </c>
       <c r="H123" t="n">
-        <v>51.75</v>
-      </c>
-      <c r="I123" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.15</v>
+      </c>
+      <c r="I123" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J123" s="2" t="n">
-        <v>0.458</v>
+        <v>0.386</v>
       </c>
       <c r="K123" s="2" t="n">
-        <v>0.42</v>
+        <v>0.391</v>
       </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" s="7" t="inlineStr"/>
@@ -6014,28 +6014,28 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>0090</t>
+          <t>0277</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>ELSOFT</t>
+          <t>CLOUDPT</t>
         </is>
       </c>
       <c r="D124" s="2" t="n">
-        <v>0.35</v>
+        <v>0.52</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>0.09369999999999999</v>
+        <v>0.0196</v>
       </c>
       <c r="F124" s="4" t="n">
-        <v>1475300</v>
+        <v>1774500</v>
       </c>
       <c r="G124" s="5" t="n">
-        <v>2.16</v>
+        <v>1.08</v>
       </c>
       <c r="H124" t="n">
-        <v>76.87</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="I124" s="9" t="inlineStr">
         <is>
@@ -6043,10 +6043,10 @@
         </is>
       </c>
       <c r="J124" s="2" t="n">
-        <v>0.284</v>
+        <v>0.49</v>
       </c>
       <c r="K124" s="2" t="n">
-        <v>0.272</v>
+        <v>0.479</v>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" s="7" t="inlineStr"/>
@@ -6059,28 +6059,28 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>0373</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>VERDANT</t>
         </is>
       </c>
       <c r="D125" s="2" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="E125" s="8" t="n">
-        <v>-0.0108</v>
+        <v>0.28</v>
+      </c>
+      <c r="E125" s="3" t="n">
+        <v>0.0182</v>
       </c>
       <c r="F125" s="4" t="n">
-        <v>1461700</v>
+        <v>1773500</v>
       </c>
       <c r="G125" s="5" t="n">
-        <v>0.28</v>
+        <v>0.4</v>
       </c>
       <c r="H125" t="n">
-        <v>58.88</v>
+        <v>69.36</v>
       </c>
       <c r="I125" s="6" t="inlineStr">
         <is>
@@ -6088,10 +6088,10 @@
         </is>
       </c>
       <c r="J125" s="2" t="n">
-        <v>0.907</v>
+        <v>0.252</v>
       </c>
       <c r="K125" s="2" t="n">
-        <v>0.863</v>
+        <v>0.22</v>
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" s="7" t="inlineStr"/>
@@ -6104,28 +6104,28 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>AWC</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D126" s="2" t="n">
-        <v>0.64</v>
+        <v>1.85</v>
       </c>
       <c r="E126" s="3" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.0054</v>
       </c>
       <c r="F126" s="4" t="n">
-        <v>1371700</v>
+        <v>1727700</v>
       </c>
       <c r="G126" s="5" t="n">
-        <v>0.62</v>
+        <v>0.41</v>
       </c>
       <c r="H126" t="n">
-        <v>58.57</v>
+        <v>38.83</v>
       </c>
       <c r="I126" s="6" t="inlineStr">
         <is>
@@ -6133,10 +6133,10 @@
         </is>
       </c>
       <c r="J126" s="2" t="n">
-        <v>0.62</v>
+        <v>1.896</v>
       </c>
       <c r="K126" s="2" t="n">
-        <v>0.529</v>
+        <v>2.026</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="7" t="inlineStr"/>
@@ -6149,39 +6149,39 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>3662</t>
+          <t>5331</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>MFLOUR</t>
+          <t>PGLOBAL</t>
         </is>
       </c>
       <c r="D127" s="2" t="n">
-        <v>0.6</v>
+        <v>0.585</v>
       </c>
       <c r="E127" s="3" t="n">
-        <v>0.0256</v>
+        <v>0.0446</v>
       </c>
       <c r="F127" s="4" t="n">
-        <v>1370300</v>
+        <v>1703300</v>
       </c>
       <c r="G127" s="5" t="n">
-        <v>0.58</v>
+        <v>3.67</v>
       </c>
       <c r="H127" t="n">
-        <v>40.75</v>
-      </c>
-      <c r="I127" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>72.14</v>
+      </c>
+      <c r="I127" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J127" s="2" t="n">
-        <v>0.617</v>
+        <v>0.54</v>
       </c>
       <c r="K127" s="2" t="n">
-        <v>0.635</v>
+        <v>0.511</v>
       </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" s="7" t="inlineStr"/>
@@ -6194,33 +6194,40 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>0475</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>GBBOND</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D128" s="2" t="n">
-        <v>0.23</v>
+        <v>0.6</v>
       </c>
       <c r="E128" s="3" t="n">
-        <v>0.0455</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="F128" s="4" t="n">
-        <v>1365600</v>
+        <v>1694500</v>
       </c>
       <c r="G128" s="5" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="I128" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J128" s="2" t="n"/>
-      <c r="K128" s="2" t="n"/>
+        <v>0.3</v>
+      </c>
+      <c r="H128" t="n">
+        <v>69.58</v>
+      </c>
+      <c r="I128" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J128" s="2" t="n">
+        <v>0.549</v>
+      </c>
+      <c r="K128" s="2" t="n">
+        <v>0.493</v>
+      </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" s="7" t="inlineStr"/>
     </row>
@@ -6232,28 +6239,28 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>0090</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>ELSOFT</t>
         </is>
       </c>
       <c r="D129" s="2" t="n">
-        <v>0.64</v>
+        <v>0.35</v>
       </c>
       <c r="E129" s="3" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.09369999999999999</v>
       </c>
       <c r="F129" s="4" t="n">
-        <v>1342900</v>
+        <v>1630400</v>
       </c>
       <c r="G129" s="5" t="n">
-        <v>0.35</v>
+        <v>2.39</v>
       </c>
       <c r="H129" t="n">
-        <v>63.45</v>
+        <v>76.87</v>
       </c>
       <c r="I129" s="9" t="inlineStr">
         <is>
@@ -6261,10 +6268,10 @@
         </is>
       </c>
       <c r="J129" s="2" t="n">
-        <v>0.596</v>
+        <v>0.284</v>
       </c>
       <c r="K129" s="2" t="n">
-        <v>0.582</v>
+        <v>0.272</v>
       </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" s="7" t="inlineStr"/>
@@ -6277,39 +6284,39 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>0172</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>OCK</t>
         </is>
       </c>
       <c r="D130" s="2" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="E130" s="8" t="n">
-        <v>-0.0119</v>
+        <v>0.45</v>
+      </c>
+      <c r="E130" s="3" t="n">
+        <v>0.0112</v>
       </c>
       <c r="F130" s="4" t="n">
-        <v>1337500</v>
+        <v>1628600</v>
       </c>
       <c r="G130" s="5" t="n">
-        <v>0.2</v>
+        <v>0.46</v>
       </c>
       <c r="H130" t="n">
-        <v>72.09</v>
-      </c>
-      <c r="I130" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.83</v>
+      </c>
+      <c r="I130" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J130" s="2" t="n">
-        <v>0.75</v>
+        <v>0.457</v>
       </c>
       <c r="K130" s="2" t="n">
-        <v>0.663</v>
+        <v>0.42</v>
       </c>
       <c r="L130" t="inlineStr"/>
       <c r="M130" s="7" t="inlineStr"/>
@@ -6322,28 +6329,28 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>0369</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>JSSOLAR</t>
         </is>
       </c>
       <c r="D131" s="2" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="E131" s="8" t="n">
-        <v>-0.0034</v>
+        <v>0.255</v>
+      </c>
+      <c r="E131" s="3" t="n">
+        <v>0.0851</v>
       </c>
       <c r="F131" s="4" t="n">
-        <v>1330300</v>
+        <v>1602100</v>
       </c>
       <c r="G131" s="5" t="n">
-        <v>0.42</v>
+        <v>1.01</v>
       </c>
       <c r="H131" t="n">
-        <v>44.13</v>
+        <v>62.54</v>
       </c>
       <c r="I131" s="6" t="inlineStr">
         <is>
@@ -6351,10 +6358,10 @@
         </is>
       </c>
       <c r="J131" s="2" t="n">
-        <v>2.973</v>
+        <v>0.233</v>
       </c>
       <c r="K131" s="2" t="n">
-        <v>3.033</v>
+        <v>0.208</v>
       </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" s="7" t="inlineStr"/>
@@ -6367,28 +6374,28 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>0373</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>VERDANT</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D132" s="2" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="E132" s="3" t="n">
-        <v>0.0182</v>
+        <v>0.92</v>
+      </c>
+      <c r="E132" s="8" t="n">
+        <v>-0.0108</v>
       </c>
       <c r="F132" s="4" t="n">
-        <v>1324100</v>
+        <v>1570500</v>
       </c>
       <c r="G132" s="5" t="n">
         <v>0.3</v>
       </c>
       <c r="H132" t="n">
-        <v>69.36</v>
+        <v>58.88</v>
       </c>
       <c r="I132" s="6" t="inlineStr">
         <is>
@@ -6396,10 +6403,10 @@
         </is>
       </c>
       <c r="J132" s="2" t="n">
-        <v>0.252</v>
+        <v>0.907</v>
       </c>
       <c r="K132" s="2" t="n">
-        <v>0.22</v>
+        <v>0.863</v>
       </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" s="7" t="inlineStr"/>
@@ -6412,28 +6419,28 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>0277</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>CLOUDPT</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D133" s="2" t="n">
-        <v>0.515</v>
-      </c>
-      <c r="E133" s="3" t="n">
-        <v>0.0098</v>
+        <v>0.825</v>
+      </c>
+      <c r="E133" s="8" t="n">
+        <v>-0.0179</v>
       </c>
       <c r="F133" s="4" t="n">
-        <v>1316100</v>
+        <v>1551100</v>
       </c>
       <c r="G133" s="5" t="n">
-        <v>0.8</v>
+        <v>0.24</v>
       </c>
       <c r="H133" t="n">
-        <v>62.85</v>
+        <v>70.67</v>
       </c>
       <c r="I133" s="9" t="inlineStr">
         <is>
@@ -6441,10 +6448,10 @@
         </is>
       </c>
       <c r="J133" s="2" t="n">
-        <v>0.489</v>
+        <v>0.75</v>
       </c>
       <c r="K133" s="2" t="n">
-        <v>0.479</v>
+        <v>0.663</v>
       </c>
       <c r="L133" t="inlineStr"/>
       <c r="M133" s="7" t="inlineStr"/>
@@ -6457,39 +6464,39 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D134" s="2" t="n">
-        <v>0.495</v>
-      </c>
-      <c r="E134" s="3" t="n">
-        <v>0.0206</v>
+        <v>2.83</v>
+      </c>
+      <c r="E134" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F134" s="4" t="n">
-        <v>1293400</v>
+        <v>1503600</v>
       </c>
       <c r="G134" s="5" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="H134" t="n">
-        <v>31.76</v>
-      </c>
-      <c r="I134" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.14</v>
+      </c>
+      <c r="I134" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J134" s="2" t="n">
-        <v>0.524</v>
+        <v>2.775</v>
       </c>
       <c r="K134" s="2" t="n">
-        <v>0.571</v>
+        <v>2.599</v>
       </c>
       <c r="L134" t="inlineStr"/>
       <c r="M134" s="7" t="inlineStr"/>
@@ -6502,28 +6509,28 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>7081</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D135" s="2" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="E135" s="10" t="n">
-        <v>0</v>
+        <v>2.84</v>
+      </c>
+      <c r="E135" s="8" t="n">
+        <v>-0.0274</v>
       </c>
       <c r="F135" s="4" t="n">
-        <v>1258400</v>
+        <v>1495300</v>
       </c>
       <c r="G135" s="5" t="n">
-        <v>0.53</v>
+        <v>0.32</v>
       </c>
       <c r="H135" t="n">
-        <v>20.91</v>
+        <v>45.03</v>
       </c>
       <c r="I135" s="6" t="inlineStr">
         <is>
@@ -6531,10 +6538,10 @@
         </is>
       </c>
       <c r="J135" s="2" t="n">
-        <v>1.037</v>
+        <v>2.962</v>
       </c>
       <c r="K135" s="2" t="n">
-        <v>1.119</v>
+        <v>2.818</v>
       </c>
       <c r="L135" t="inlineStr"/>
       <c r="M135" s="7" t="inlineStr"/>
@@ -6547,39 +6554,39 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>5331</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>PGLOBAL</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D136" s="2" t="n">
-        <v>0.59</v>
+        <v>0.495</v>
       </c>
       <c r="E136" s="3" t="n">
-        <v>0.0536</v>
+        <v>0.0206</v>
       </c>
       <c r="F136" s="4" t="n">
-        <v>1250100</v>
+        <v>1490100</v>
       </c>
       <c r="G136" s="5" t="n">
-        <v>2.69</v>
+        <v>0.2</v>
       </c>
       <c r="H136" t="n">
-        <v>73.19</v>
-      </c>
-      <c r="I136" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>31.76</v>
+      </c>
+      <c r="I136" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J136" s="2" t="n">
-        <v>0.541</v>
+        <v>0.524</v>
       </c>
       <c r="K136" s="2" t="n">
-        <v>0.511</v>
+        <v>0.571</v>
       </c>
       <c r="L136" t="inlineStr"/>
       <c r="M136" s="7" t="inlineStr"/>
@@ -6592,39 +6599,39 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>7160</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>PENTA</t>
+          <t>AWC</t>
         </is>
       </c>
       <c r="D137" s="2" t="n">
-        <v>5.89</v>
+        <v>0.645</v>
       </c>
       <c r="E137" s="3" t="n">
-        <v>0.0051</v>
+        <v>0.0157</v>
       </c>
       <c r="F137" s="4" t="n">
-        <v>1245500</v>
+        <v>1450100</v>
       </c>
       <c r="G137" s="5" t="n">
-        <v>0.36</v>
+        <v>0.66</v>
       </c>
       <c r="H137" t="n">
-        <v>62.9</v>
-      </c>
-      <c r="I137" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>59.41</v>
+      </c>
+      <c r="I137" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J137" s="2" t="n">
-        <v>5.477</v>
+        <v>0.621</v>
       </c>
       <c r="K137" s="2" t="n">
-        <v>5.356</v>
+        <v>0.529</v>
       </c>
       <c r="L137" t="inlineStr"/>
       <c r="M137" s="7" t="inlineStr"/>
@@ -6637,39 +6644,39 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>SKYECHIP</t>
         </is>
       </c>
       <c r="D138" s="2" t="n">
-        <v>0.605</v>
+        <v>2.94</v>
       </c>
       <c r="E138" s="3" t="n">
-        <v>0.0168</v>
+        <v>0.0034</v>
       </c>
       <c r="F138" s="4" t="n">
-        <v>1233700</v>
+        <v>1446800</v>
       </c>
       <c r="G138" s="5" t="n">
-        <v>0.22</v>
+        <v>0.45</v>
       </c>
       <c r="H138" t="n">
-        <v>70.43000000000001</v>
-      </c>
-      <c r="I138" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.93</v>
+      </c>
+      <c r="I138" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J138" s="2" t="n">
-        <v>0.55</v>
+        <v>2.975</v>
       </c>
       <c r="K138" s="2" t="n">
-        <v>0.493</v>
+        <v>3.034</v>
       </c>
       <c r="L138" t="inlineStr"/>
       <c r="M138" s="7" t="inlineStr"/>
@@ -6682,39 +6689,39 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>0219</t>
+          <t>7160</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>RL</t>
+          <t>PENTA</t>
         </is>
       </c>
       <c r="D139" s="2" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E139" s="8" t="n">
-        <v>-0.0167</v>
+        <v>5.89</v>
+      </c>
+      <c r="E139" s="3" t="n">
+        <v>0.0051</v>
       </c>
       <c r="F139" s="4" t="n">
-        <v>1220800</v>
+        <v>1400900</v>
       </c>
       <c r="G139" s="5" t="n">
-        <v>0.19</v>
+        <v>0.41</v>
       </c>
       <c r="H139" t="n">
-        <v>40.45</v>
-      </c>
-      <c r="I139" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.9</v>
+      </c>
+      <c r="I139" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J139" s="2" t="n">
-        <v>0.304</v>
+        <v>5.477</v>
       </c>
       <c r="K139" s="2" t="n">
-        <v>0.299</v>
+        <v>5.356</v>
       </c>
       <c r="L139" t="inlineStr"/>
       <c r="M139" s="7" t="inlineStr"/>
@@ -6727,28 +6734,28 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>5180</t>
+          <t>3662</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>CLMT</t>
+          <t>MFLOUR</t>
         </is>
       </c>
       <c r="D140" s="2" t="n">
-        <v>0.555</v>
+        <v>0.605</v>
       </c>
       <c r="E140" s="3" t="n">
-        <v>0.0091</v>
+        <v>0.0342</v>
       </c>
       <c r="F140" s="4" t="n">
-        <v>1203100</v>
+        <v>1380300</v>
       </c>
       <c r="G140" s="5" t="n">
-        <v>0.29</v>
+        <v>0.58</v>
       </c>
       <c r="H140" t="n">
-        <v>35.64</v>
+        <v>43.16</v>
       </c>
       <c r="I140" s="6" t="inlineStr">
         <is>
@@ -6756,10 +6763,10 @@
         </is>
       </c>
       <c r="J140" s="2" t="n">
-        <v>0.571</v>
+        <v>0.617</v>
       </c>
       <c r="K140" s="2" t="n">
-        <v>0.582</v>
+        <v>0.635</v>
       </c>
       <c r="L140" t="inlineStr"/>
       <c r="M140" s="7" t="inlineStr"/>
@@ -6772,39 +6779,39 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D141" s="2" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="E141" s="8" t="n">
-        <v>-0.0205</v>
+        <v>0.645</v>
+      </c>
+      <c r="E141" s="3" t="n">
+        <v>0.0157</v>
       </c>
       <c r="F141" s="4" t="n">
-        <v>1183700</v>
+        <v>1370200</v>
       </c>
       <c r="G141" s="5" t="n">
-        <v>0.26</v>
+        <v>0.36</v>
       </c>
       <c r="H141" t="n">
-        <v>45.9</v>
-      </c>
-      <c r="I141" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.34999999999999</v>
+      </c>
+      <c r="I141" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J141" s="2" t="n">
-        <v>2.964</v>
+        <v>0.597</v>
       </c>
       <c r="K141" s="2" t="n">
-        <v>2.819</v>
+        <v>0.582</v>
       </c>
       <c r="L141" t="inlineStr"/>
       <c r="M141" s="7" t="inlineStr"/>
@@ -6817,40 +6824,33 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>0369</t>
+          <t>0475</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>JSSOLAR</t>
+          <t>GBBOND</t>
         </is>
       </c>
       <c r="D142" s="2" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="E142" s="3" t="n">
-        <v>0.0638</v>
+        <v>0.0455</v>
       </c>
       <c r="F142" s="4" t="n">
-        <v>1155900</v>
+        <v>1365600</v>
       </c>
       <c r="G142" s="5" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="H142" t="n">
-        <v>60.92</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I142" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J142" s="2" t="n">
-        <v>0.232</v>
-      </c>
-      <c r="K142" s="2" t="n">
-        <v>0.208</v>
-      </c>
+      <c r="J142" s="2" t="n"/>
+      <c r="K142" s="2" t="n"/>
       <c r="L142" t="inlineStr"/>
       <c r="M142" s="7" t="inlineStr"/>
     </row>
@@ -6862,28 +6862,28 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>0337</t>
+          <t>0185</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>SET</t>
+          <t>HSSEB</t>
         </is>
       </c>
       <c r="D143" s="2" t="n">
-        <v>0.245</v>
+        <v>0.5</v>
       </c>
       <c r="E143" s="3" t="n">
-        <v>0.0426</v>
+        <v>0.1364</v>
       </c>
       <c r="F143" s="4" t="n">
-        <v>1145000</v>
+        <v>1340100</v>
       </c>
       <c r="G143" s="5" t="n">
-        <v>0.67</v>
+        <v>9.67</v>
       </c>
       <c r="H143" t="n">
-        <v>55.55</v>
+        <v>61.28</v>
       </c>
       <c r="I143" s="9" t="inlineStr">
         <is>
@@ -6891,10 +6891,10 @@
         </is>
       </c>
       <c r="J143" s="2" t="n">
-        <v>0.237</v>
+        <v>0.469</v>
       </c>
       <c r="K143" s="2" t="n">
-        <v>0.243</v>
+        <v>0.498</v>
       </c>
       <c r="L143" t="inlineStr"/>
       <c r="M143" s="7" t="inlineStr"/>
@@ -6907,28 +6907,28 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>5053</t>
+          <t>7081</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>OSK</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D144" s="2" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="E144" s="3" t="n">
-        <v>0.0248</v>
+        <v>0.92</v>
+      </c>
+      <c r="E144" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F144" s="4" t="n">
-        <v>1127000</v>
+        <v>1297700</v>
       </c>
       <c r="G144" s="5" t="n">
-        <v>0.78</v>
+        <v>0.55</v>
       </c>
       <c r="H144" t="n">
-        <v>27.42</v>
+        <v>20.91</v>
       </c>
       <c r="I144" s="6" t="inlineStr">
         <is>
@@ -6936,10 +6936,10 @@
         </is>
       </c>
       <c r="J144" s="2" t="n">
-        <v>1.786</v>
+        <v>1.037</v>
       </c>
       <c r="K144" s="2" t="n">
-        <v>1.919</v>
+        <v>1.119</v>
       </c>
       <c r="L144" t="inlineStr"/>
       <c r="M144" s="7" t="inlineStr"/>
@@ -6952,28 +6952,28 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>0456</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>MMCS</t>
+          <t>MAHSING</t>
         </is>
       </c>
       <c r="D145" s="2" t="n">
-        <v>0.345</v>
+        <v>0.95</v>
       </c>
       <c r="E145" s="3" t="n">
-        <v>0.0299</v>
+        <v>0.0053</v>
       </c>
       <c r="F145" s="4" t="n">
-        <v>1126300</v>
+        <v>1268600</v>
       </c>
       <c r="G145" s="5" t="n">
-        <v>0.88</v>
+        <v>0.33</v>
       </c>
       <c r="H145" t="n">
-        <v>41.57</v>
+        <v>30.03</v>
       </c>
       <c r="I145" s="6" t="inlineStr">
         <is>
@@ -6981,10 +6981,10 @@
         </is>
       </c>
       <c r="J145" s="2" t="n">
-        <v>0.349</v>
+        <v>0.996</v>
       </c>
       <c r="K145" s="2" t="n">
-        <v>0.383</v>
+        <v>1.066</v>
       </c>
       <c r="L145" t="inlineStr"/>
       <c r="M145" s="7" t="inlineStr"/>
@@ -6997,28 +6997,28 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>7498</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>ALPHA</t>
+          <t>RALCO</t>
         </is>
       </c>
       <c r="D146" s="2" t="n">
-        <v>0.275</v>
+        <v>1.02</v>
       </c>
       <c r="E146" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F146" s="4" t="n">
-        <v>1122300</v>
+        <v>1251800</v>
       </c>
       <c r="G146" s="5" t="n">
-        <v>0.47</v>
+        <v>2</v>
       </c>
       <c r="H146" t="n">
-        <v>63.87</v>
+        <v>62.64</v>
       </c>
       <c r="I146" s="9" t="inlineStr">
         <is>
@@ -7026,10 +7026,10 @@
         </is>
       </c>
       <c r="J146" s="2" t="n">
-        <v>0.259</v>
+        <v>0.999</v>
       </c>
       <c r="K146" s="2" t="n">
-        <v>0.257</v>
+        <v>0.981</v>
       </c>
       <c r="L146" t="inlineStr"/>
       <c r="M146" s="7" t="inlineStr"/>
@@ -7042,28 +7042,28 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>5162</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>VSTECS</t>
         </is>
       </c>
       <c r="D147" s="2" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="E147" s="8" t="n">
-        <v>-0.0035</v>
+        <v>1.71</v>
+      </c>
+      <c r="E147" s="3" t="n">
+        <v>0.024</v>
       </c>
       <c r="F147" s="4" t="n">
-        <v>1085900</v>
+        <v>1244500</v>
       </c>
       <c r="G147" s="5" t="n">
-        <v>0.12</v>
+        <v>0.73</v>
       </c>
       <c r="H147" t="n">
-        <v>55.48</v>
+        <v>55.43</v>
       </c>
       <c r="I147" s="9" t="inlineStr">
         <is>
@@ -7071,10 +7071,10 @@
         </is>
       </c>
       <c r="J147" s="2" t="n">
-        <v>2.774</v>
+        <v>1.662</v>
       </c>
       <c r="K147" s="2" t="n">
-        <v>2.599</v>
+        <v>1.677</v>
       </c>
       <c r="L147" t="inlineStr"/>
       <c r="M147" s="7" t="inlineStr"/>
@@ -7087,28 +7087,28 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>0450</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>MFGROUP</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D148" s="2" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="E148" s="8" t="n">
-        <v>-0.0185</v>
+        <v>1.9</v>
+      </c>
+      <c r="E148" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F148" s="4" t="n">
-        <v>1082000</v>
+        <v>1241600</v>
       </c>
       <c r="G148" s="5" t="n">
-        <v>1.11</v>
+        <v>0.19</v>
       </c>
       <c r="H148" t="n">
-        <v>54.17</v>
+        <v>43.39</v>
       </c>
       <c r="I148" s="6" t="inlineStr">
         <is>
@@ -7116,10 +7116,10 @@
         </is>
       </c>
       <c r="J148" s="2" t="n">
-        <v>0.262</v>
+        <v>1.927</v>
       </c>
       <c r="K148" s="2" t="n">
-        <v>0.264</v>
+        <v>1.957</v>
       </c>
       <c r="L148" t="inlineStr"/>
       <c r="M148" s="7" t="inlineStr"/>
@@ -7132,28 +7132,28 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>5212</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>MAHSING</t>
+          <t>PAVREIT</t>
         </is>
       </c>
       <c r="D149" s="2" t="n">
-        <v>0.95</v>
+        <v>1.58</v>
       </c>
       <c r="E149" s="3" t="n">
-        <v>0.0053</v>
+        <v>0.026</v>
       </c>
       <c r="F149" s="4" t="n">
-        <v>1080400</v>
+        <v>1241400</v>
       </c>
       <c r="G149" s="5" t="n">
-        <v>0.28</v>
+        <v>0.3</v>
       </c>
       <c r="H149" t="n">
-        <v>30.03</v>
+        <v>50.99</v>
       </c>
       <c r="I149" s="6" t="inlineStr">
         <is>
@@ -7161,10 +7161,10 @@
         </is>
       </c>
       <c r="J149" s="2" t="n">
-        <v>0.996</v>
+        <v>1.565</v>
       </c>
       <c r="K149" s="2" t="n">
-        <v>1.066</v>
+        <v>1.62</v>
       </c>
       <c r="L149" t="inlineStr"/>
       <c r="M149" s="7" t="inlineStr"/>
@@ -7177,39 +7177,39 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>7233</t>
+          <t>5180</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>DUFU</t>
+          <t>CLMT</t>
         </is>
       </c>
       <c r="D150" s="2" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="E150" s="8" t="n">
-        <v>-0.0154</v>
+        <v>0.555</v>
+      </c>
+      <c r="E150" s="3" t="n">
+        <v>0.0091</v>
       </c>
       <c r="F150" s="4" t="n">
-        <v>1066600</v>
+        <v>1233100</v>
       </c>
       <c r="G150" s="5" t="n">
-        <v>0.34</v>
+        <v>0.3</v>
       </c>
       <c r="H150" t="n">
-        <v>61.36</v>
-      </c>
-      <c r="I150" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.64</v>
+      </c>
+      <c r="I150" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J150" s="2" t="n">
-        <v>3</v>
+        <v>0.571</v>
       </c>
       <c r="K150" s="2" t="n">
-        <v>2.804</v>
+        <v>0.582</v>
       </c>
       <c r="L150" t="inlineStr"/>
       <c r="M150" s="7" t="inlineStr"/>
@@ -7222,39 +7222,39 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>5162</t>
+          <t>0219</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>VSTECS</t>
+          <t>RL</t>
         </is>
       </c>
       <c r="D151" s="2" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="E151" s="3" t="n">
-        <v>0.0299</v>
+        <v>0.295</v>
+      </c>
+      <c r="E151" s="8" t="n">
+        <v>-0.0167</v>
       </c>
       <c r="F151" s="4" t="n">
-        <v>1041200</v>
+        <v>1220800</v>
       </c>
       <c r="G151" s="5" t="n">
-        <v>0.61</v>
+        <v>0.19</v>
       </c>
       <c r="H151" t="n">
-        <v>56.36</v>
-      </c>
-      <c r="I151" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.45</v>
+      </c>
+      <c r="I151" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J151" s="2" t="n">
-        <v>1.663</v>
+        <v>0.304</v>
       </c>
       <c r="K151" s="2" t="n">
-        <v>1.678</v>
+        <v>0.299</v>
       </c>
       <c r="L151" t="inlineStr"/>
       <c r="M151" s="7" t="inlineStr"/>
@@ -7267,28 +7267,28 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>5878</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>KPJ</t>
         </is>
       </c>
       <c r="D152" s="2" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="E152" s="8" t="n">
-        <v>-0.0053</v>
+        <v>2.53</v>
+      </c>
+      <c r="E152" s="3" t="n">
+        <v>0.004</v>
       </c>
       <c r="F152" s="4" t="n">
-        <v>1040400</v>
+        <v>1191300</v>
       </c>
       <c r="G152" s="5" t="n">
-        <v>0.16</v>
+        <v>0.22</v>
       </c>
       <c r="H152" t="n">
-        <v>41.98</v>
+        <v>37.16</v>
       </c>
       <c r="I152" s="6" t="inlineStr">
         <is>
@@ -7296,10 +7296,10 @@
         </is>
       </c>
       <c r="J152" s="2" t="n">
-        <v>1.927</v>
+        <v>2.615</v>
       </c>
       <c r="K152" s="2" t="n">
-        <v>1.957</v>
+        <v>2.79</v>
       </c>
       <c r="L152" t="inlineStr"/>
       <c r="M152" s="7" t="inlineStr"/>
@@ -7312,28 +7312,28 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>0185</t>
+          <t>0337</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>HSSEB</t>
+          <t>SET</t>
         </is>
       </c>
       <c r="D153" s="2" t="n">
-        <v>0.5</v>
+        <v>0.245</v>
       </c>
       <c r="E153" s="3" t="n">
-        <v>0.1364</v>
+        <v>0.0426</v>
       </c>
       <c r="F153" s="4" t="n">
-        <v>1027200</v>
+        <v>1176000</v>
       </c>
       <c r="G153" s="5" t="n">
-        <v>7.41</v>
+        <v>0.68</v>
       </c>
       <c r="H153" t="n">
-        <v>61.28</v>
+        <v>55.55</v>
       </c>
       <c r="I153" s="9" t="inlineStr">
         <is>
@@ -7341,10 +7341,10 @@
         </is>
       </c>
       <c r="J153" s="2" t="n">
-        <v>0.469</v>
+        <v>0.237</v>
       </c>
       <c r="K153" s="2" t="n">
-        <v>0.498</v>
+        <v>0.243</v>
       </c>
       <c r="L153" t="inlineStr"/>
       <c r="M153" s="7" t="inlineStr"/>
@@ -7357,28 +7357,28 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>0456</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>KPJ</t>
+          <t>MMCS</t>
         </is>
       </c>
       <c r="D154" s="2" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="E154" s="10" t="n">
-        <v>0</v>
+        <v>0.345</v>
+      </c>
+      <c r="E154" s="3" t="n">
+        <v>0.0299</v>
       </c>
       <c r="F154" s="4" t="n">
-        <v>966800</v>
+        <v>1164000</v>
       </c>
       <c r="G154" s="5" t="n">
-        <v>0.18</v>
+        <v>0.91</v>
       </c>
       <c r="H154" t="n">
-        <v>35.88</v>
+        <v>41.57</v>
       </c>
       <c r="I154" s="6" t="inlineStr">
         <is>
@@ -7386,10 +7386,10 @@
         </is>
       </c>
       <c r="J154" s="2" t="n">
-        <v>2.614</v>
+        <v>0.349</v>
       </c>
       <c r="K154" s="2" t="n">
-        <v>2.79</v>
+        <v>0.383</v>
       </c>
       <c r="L154" t="inlineStr"/>
       <c r="M154" s="7" t="inlineStr"/>
@@ -7402,39 +7402,39 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>0271</t>
+          <t>0340</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>WELLS</t>
+          <t>NORTHERN</t>
         </is>
       </c>
       <c r="D155" s="2" t="n">
-        <v>0.53</v>
+        <v>1.25</v>
       </c>
       <c r="E155" s="3" t="n">
-        <v>0.0291</v>
+        <v>0.0417</v>
       </c>
       <c r="F155" s="4" t="n">
-        <v>963600</v>
+        <v>1161400</v>
       </c>
       <c r="G155" s="5" t="n">
-        <v>0.87</v>
+        <v>0.15</v>
       </c>
       <c r="H155" t="n">
-        <v>26.64</v>
-      </c>
-      <c r="I155" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>68.3</v>
+      </c>
+      <c r="I155" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J155" s="2" t="n">
-        <v>0.582</v>
+        <v>1.083</v>
       </c>
       <c r="K155" s="2" t="n">
-        <v>0.622</v>
+        <v>0.83</v>
       </c>
       <c r="L155" t="inlineStr"/>
       <c r="M155" s="7" t="inlineStr"/>
@@ -7447,28 +7447,28 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>5053</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>OSK</t>
         </is>
       </c>
       <c r="D156" s="2" t="n">
-        <v>1.76</v>
+        <v>1.66</v>
       </c>
       <c r="E156" s="3" t="n">
-        <v>0.005699999999999999</v>
+        <v>0.0311</v>
       </c>
       <c r="F156" s="4" t="n">
-        <v>956200</v>
+        <v>1157300</v>
       </c>
       <c r="G156" s="5" t="n">
-        <v>0.19</v>
+        <v>0.8</v>
       </c>
       <c r="H156" t="n">
-        <v>50.39</v>
+        <v>29.21</v>
       </c>
       <c r="I156" s="6" t="inlineStr">
         <is>
@@ -7476,10 +7476,10 @@
         </is>
       </c>
       <c r="J156" s="2" t="n">
-        <v>1.752</v>
+        <v>1.786</v>
       </c>
       <c r="K156" s="2" t="n">
-        <v>1.778</v>
+        <v>1.919</v>
       </c>
       <c r="L156" t="inlineStr"/>
       <c r="M156" s="7" t="inlineStr"/>
@@ -7492,39 +7492,39 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>DUFU</t>
         </is>
       </c>
       <c r="D157" s="2" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="E157" s="3" t="n">
-        <v>0.0137</v>
+        <v>3.2</v>
+      </c>
+      <c r="E157" s="8" t="n">
+        <v>-0.0123</v>
       </c>
       <c r="F157" s="4" t="n">
-        <v>922600</v>
+        <v>1140700</v>
       </c>
       <c r="G157" s="5" t="n">
-        <v>0.29</v>
+        <v>0.37</v>
       </c>
       <c r="H157" t="n">
-        <v>46.05</v>
-      </c>
-      <c r="I157" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.88</v>
+      </c>
+      <c r="I157" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J157" s="2" t="n">
-        <v>0.761</v>
+        <v>3.001</v>
       </c>
       <c r="K157" s="2" t="n">
-        <v>0.747</v>
+        <v>2.804</v>
       </c>
       <c r="L157" t="inlineStr"/>
       <c r="M157" s="7" t="inlineStr"/>
@@ -7537,39 +7537,39 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>0223</t>
+          <t>0450</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>SAMAIDEN</t>
+          <t>MFGROUP</t>
         </is>
       </c>
       <c r="D158" s="2" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="E158" s="3" t="n">
-        <v>0.01</v>
+        <v>0.265</v>
+      </c>
+      <c r="E158" s="8" t="n">
+        <v>-0.0185</v>
       </c>
       <c r="F158" s="4" t="n">
-        <v>903500</v>
+        <v>1082100</v>
       </c>
       <c r="G158" s="5" t="n">
-        <v>0.22</v>
+        <v>1.11</v>
       </c>
       <c r="H158" t="n">
-        <v>69.19</v>
-      </c>
-      <c r="I158" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>54.17</v>
+      </c>
+      <c r="I158" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J158" s="2" t="n">
-        <v>2.692</v>
+        <v>0.262</v>
       </c>
       <c r="K158" s="2" t="n">
-        <v>2.042</v>
+        <v>0.264</v>
       </c>
       <c r="L158" t="inlineStr"/>
       <c r="M158" s="7" t="inlineStr"/>
@@ -7582,39 +7582,39 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>5212</t>
+          <t>5288</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>PAVREIT</t>
+          <t>SIMEPROP</t>
         </is>
       </c>
       <c r="D159" s="2" t="n">
-        <v>1.57</v>
+        <v>1.24</v>
       </c>
       <c r="E159" s="3" t="n">
-        <v>0.0195</v>
+        <v>0.0248</v>
       </c>
       <c r="F159" s="4" t="n">
-        <v>895100</v>
+        <v>1081600</v>
       </c>
       <c r="G159" s="5" t="n">
-        <v>0.22</v>
+        <v>0.19</v>
       </c>
       <c r="H159" t="n">
-        <v>49.18</v>
-      </c>
-      <c r="I159" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.82</v>
+      </c>
+      <c r="I159" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J159" s="2" t="n">
-        <v>1.564</v>
+        <v>1.247</v>
       </c>
       <c r="K159" s="2" t="n">
-        <v>1.62</v>
+        <v>1.285</v>
       </c>
       <c r="L159" t="inlineStr"/>
       <c r="M159" s="7" t="inlineStr"/>
@@ -7627,28 +7627,28 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>0217</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>PWRWELL</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D160" s="2" t="n">
-        <v>1.18</v>
+        <v>1.76</v>
       </c>
       <c r="E160" s="3" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.005699999999999999</v>
       </c>
       <c r="F160" s="4" t="n">
-        <v>870500</v>
+        <v>1070900</v>
       </c>
       <c r="G160" s="5" t="n">
         <v>0.21</v>
       </c>
       <c r="H160" t="n">
-        <v>59.85</v>
+        <v>50.39</v>
       </c>
       <c r="I160" s="6" t="inlineStr">
         <is>
@@ -7656,10 +7656,10 @@
         </is>
       </c>
       <c r="J160" s="2" t="n">
-        <v>1.153</v>
+        <v>1.752</v>
       </c>
       <c r="K160" s="2" t="n">
-        <v>1.066</v>
+        <v>1.778</v>
       </c>
       <c r="L160" t="inlineStr"/>
       <c r="M160" s="7" t="inlineStr"/>
@@ -7672,28 +7672,28 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>5284</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>MBSB</t>
+          <t>LCTITAN</t>
         </is>
       </c>
       <c r="D161" s="2" t="n">
-        <v>0.535</v>
-      </c>
-      <c r="E161" s="3" t="n">
-        <v>0.009399999999999999</v>
+        <v>0.315</v>
+      </c>
+      <c r="E161" s="8" t="n">
+        <v>-0.0156</v>
       </c>
       <c r="F161" s="4" t="n">
-        <v>866000</v>
+        <v>1059400</v>
       </c>
       <c r="G161" s="5" t="n">
-        <v>0.24</v>
+        <v>0.53</v>
       </c>
       <c r="H161" t="n">
-        <v>35.78</v>
+        <v>40.07</v>
       </c>
       <c r="I161" s="6" t="inlineStr">
         <is>
@@ -7701,10 +7701,10 @@
         </is>
       </c>
       <c r="J161" s="2" t="n">
-        <v>0.552</v>
+        <v>0.331</v>
       </c>
       <c r="K161" s="2" t="n">
-        <v>0.582</v>
+        <v>0.33</v>
       </c>
       <c r="L161" t="inlineStr"/>
       <c r="M161" s="7" t="inlineStr"/>
@@ -7717,28 +7717,28 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>5323</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>JPG</t>
+          <t>SUNREIT</t>
         </is>
       </c>
       <c r="D162" s="2" t="n">
-        <v>1.76</v>
+        <v>2.08</v>
       </c>
       <c r="E162" s="3" t="n">
-        <v>0.0115</v>
+        <v>0.0097</v>
       </c>
       <c r="F162" s="4" t="n">
-        <v>865000</v>
+        <v>1047800</v>
       </c>
       <c r="G162" s="5" t="n">
-        <v>0.14</v>
+        <v>0.31</v>
       </c>
       <c r="H162" t="n">
-        <v>38.84</v>
+        <v>53.45</v>
       </c>
       <c r="I162" s="6" t="inlineStr">
         <is>
@@ -7746,10 +7746,10 @@
         </is>
       </c>
       <c r="J162" s="2" t="n">
-        <v>1.823</v>
+        <v>2.058</v>
       </c>
       <c r="K162" s="2" t="n">
-        <v>1.927</v>
+        <v>2.086</v>
       </c>
       <c r="L162" t="inlineStr"/>
       <c r="M162" s="7" t="inlineStr"/>
@@ -7762,39 +7762,39 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>5072</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>HIAPTEK</t>
         </is>
       </c>
       <c r="D163" s="2" t="n">
-        <v>0.765</v>
+        <v>0.255</v>
       </c>
       <c r="E163" s="3" t="n">
-        <v>0.0066</v>
+        <v>0.02</v>
       </c>
       <c r="F163" s="4" t="n">
-        <v>839800</v>
+        <v>1018900</v>
       </c>
       <c r="G163" s="5" t="n">
-        <v>0.46</v>
+        <v>0.98</v>
       </c>
       <c r="H163" t="n">
-        <v>62.31</v>
-      </c>
-      <c r="I163" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.76</v>
+      </c>
+      <c r="I163" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J163" s="2" t="n">
-        <v>0.711</v>
+        <v>0.255</v>
       </c>
       <c r="K163" s="2" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.258</v>
       </c>
       <c r="L163" t="inlineStr"/>
       <c r="M163" s="7" t="inlineStr"/>
@@ -7807,39 +7807,39 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>0037</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>RGB</t>
         </is>
       </c>
       <c r="D164" s="2" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="E164" s="10" t="n">
-        <v>0</v>
+        <v>0.215</v>
+      </c>
+      <c r="E164" s="3" t="n">
+        <v>0.0238</v>
       </c>
       <c r="F164" s="4" t="n">
-        <v>839600</v>
+        <v>1014600</v>
       </c>
       <c r="G164" s="5" t="n">
-        <v>0.25</v>
+        <v>1.19</v>
       </c>
       <c r="H164" t="n">
-        <v>72.14</v>
-      </c>
-      <c r="I164" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>69.34</v>
+      </c>
+      <c r="I164" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J164" s="2" t="n">
-        <v>1.237</v>
+        <v>0.207</v>
       </c>
       <c r="K164" s="2" t="n">
-        <v>1.008</v>
+        <v>0.205</v>
       </c>
       <c r="L164" t="inlineStr"/>
       <c r="M164" s="7" t="inlineStr"/>
@@ -7852,28 +7852,28 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>5280</t>
+          <t>0146</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>KIPREIT</t>
+          <t>JFTECH</t>
         </is>
       </c>
       <c r="D165" s="2" t="n">
-        <v>0.855</v>
-      </c>
-      <c r="E165" s="8" t="n">
-        <v>-0.0058</v>
+        <v>0.77</v>
+      </c>
+      <c r="E165" s="3" t="n">
+        <v>0.0132</v>
       </c>
       <c r="F165" s="4" t="n">
-        <v>810700</v>
+        <v>1001900</v>
       </c>
       <c r="G165" s="5" t="n">
-        <v>1.31</v>
+        <v>0.54</v>
       </c>
       <c r="H165" t="n">
-        <v>50.23</v>
+        <v>62.99</v>
       </c>
       <c r="I165" s="9" t="inlineStr">
         <is>
@@ -7881,10 +7881,10 @@
         </is>
       </c>
       <c r="J165" s="2" t="n">
-        <v>0.856</v>
+        <v>0.712</v>
       </c>
       <c r="K165" s="2" t="n">
-        <v>0.851</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="L165" t="inlineStr"/>
       <c r="M165" s="7" t="inlineStr"/>
@@ -7897,39 +7897,39 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>0340</t>
+          <t>5211</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>NORTHERN</t>
+          <t>SUNWAY</t>
         </is>
       </c>
       <c r="D166" s="2" t="n">
-        <v>1.23</v>
+        <v>4.38</v>
       </c>
       <c r="E166" s="3" t="n">
-        <v>0.025</v>
+        <v>0.0162</v>
       </c>
       <c r="F166" s="4" t="n">
-        <v>785600</v>
+        <v>993100</v>
       </c>
       <c r="G166" s="5" t="n">
-        <v>0.1</v>
+        <v>0.19</v>
       </c>
       <c r="H166" t="n">
-        <v>67.31999999999999</v>
-      </c>
-      <c r="I166" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.78</v>
+      </c>
+      <c r="I166" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J166" s="2" t="n">
-        <v>1.081</v>
+        <v>4.484</v>
       </c>
       <c r="K166" s="2" t="n">
-        <v>0.83</v>
+        <v>4.817</v>
       </c>
       <c r="L166" t="inlineStr"/>
       <c r="M166" s="7" t="inlineStr"/>
@@ -7942,39 +7942,39 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>0223</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>SEG</t>
+          <t>SAMAIDEN</t>
         </is>
       </c>
       <c r="D167" s="2" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E167" s="8" t="n">
-        <v>-0.007900000000000001</v>
+        <v>3.07</v>
+      </c>
+      <c r="E167" s="3" t="n">
+        <v>0.0199</v>
       </c>
       <c r="F167" s="4" t="n">
-        <v>775100</v>
+        <v>991200</v>
       </c>
       <c r="G167" s="5" t="n">
-        <v>0.61</v>
+        <v>0.24</v>
       </c>
       <c r="H167" t="n">
-        <v>37.72</v>
-      </c>
-      <c r="I167" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>69.84999999999999</v>
+      </c>
+      <c r="I167" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J167" s="2" t="n">
-        <v>0.632</v>
+        <v>2.695</v>
       </c>
       <c r="K167" s="2" t="n">
-        <v>0.63</v>
+        <v>2.043</v>
       </c>
       <c r="L167" t="inlineStr"/>
       <c r="M167" s="7" t="inlineStr"/>
@@ -7987,28 +7987,28 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>5176</t>
+          <t>0167</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>SUNREIT</t>
+          <t>MCLEAN</t>
         </is>
       </c>
       <c r="D168" s="2" t="n">
-        <v>2.08</v>
+        <v>0.74</v>
       </c>
       <c r="E168" s="3" t="n">
-        <v>0.0097</v>
+        <v>0.0137</v>
       </c>
       <c r="F168" s="4" t="n">
-        <v>774600</v>
+        <v>981100</v>
       </c>
       <c r="G168" s="5" t="n">
-        <v>0.23</v>
+        <v>0.31</v>
       </c>
       <c r="H168" t="n">
-        <v>53.45</v>
+        <v>46.05</v>
       </c>
       <c r="I168" s="6" t="inlineStr">
         <is>
@@ -8016,10 +8016,10 @@
         </is>
       </c>
       <c r="J168" s="2" t="n">
-        <v>2.058</v>
+        <v>0.761</v>
       </c>
       <c r="K168" s="2" t="n">
-        <v>2.086</v>
+        <v>0.747</v>
       </c>
       <c r="L168" t="inlineStr"/>
       <c r="M168" s="7" t="inlineStr"/>
@@ -8032,28 +8032,28 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>5211</t>
+          <t>0271</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>SUNWAY</t>
+          <t>WELLS</t>
         </is>
       </c>
       <c r="D169" s="2" t="n">
-        <v>4.36</v>
+        <v>0.53</v>
       </c>
       <c r="E169" s="3" t="n">
-        <v>0.0116</v>
+        <v>0.0291</v>
       </c>
       <c r="F169" s="4" t="n">
-        <v>741100</v>
+        <v>968600</v>
       </c>
       <c r="G169" s="5" t="n">
-        <v>0.14</v>
+        <v>0.87</v>
       </c>
       <c r="H169" t="n">
-        <v>34.94</v>
+        <v>26.64</v>
       </c>
       <c r="I169" s="6" t="inlineStr">
         <is>
@@ -8061,10 +8061,10 @@
         </is>
       </c>
       <c r="J169" s="2" t="n">
-        <v>4.482</v>
+        <v>0.582</v>
       </c>
       <c r="K169" s="2" t="n">
-        <v>4.817</v>
+        <v>0.622</v>
       </c>
       <c r="L169" t="inlineStr"/>
       <c r="M169" s="7" t="inlineStr"/>
@@ -8077,39 +8077,39 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>5263</t>
+          <t>5323</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>SUNCON</t>
+          <t>JPG</t>
         </is>
       </c>
       <c r="D170" s="2" t="n">
-        <v>7.58</v>
+        <v>1.76</v>
       </c>
       <c r="E170" s="3" t="n">
-        <v>0.0107</v>
+        <v>0.0115</v>
       </c>
       <c r="F170" s="4" t="n">
-        <v>737400</v>
+        <v>931300</v>
       </c>
       <c r="G170" s="5" t="n">
-        <v>0.19</v>
+        <v>0.15</v>
       </c>
       <c r="H170" t="n">
-        <v>48.24</v>
-      </c>
-      <c r="I170" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.84</v>
+      </c>
+      <c r="I170" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J170" s="2" t="n">
-        <v>7.608</v>
+        <v>1.823</v>
       </c>
       <c r="K170" s="2" t="n">
-        <v>7.801</v>
+        <v>1.927</v>
       </c>
       <c r="L170" t="inlineStr"/>
       <c r="M170" s="7" t="inlineStr"/>
@@ -8122,39 +8122,39 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>0097</t>
+          <t>0217</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>VITROX</t>
+          <t>PWRWELL</t>
         </is>
       </c>
       <c r="D171" s="2" t="n">
-        <v>11.08</v>
+        <v>1.18</v>
       </c>
       <c r="E171" s="3" t="n">
-        <v>0.0073</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="F171" s="4" t="n">
-        <v>732000</v>
+        <v>930200</v>
       </c>
       <c r="G171" s="5" t="n">
         <v>0.22</v>
       </c>
       <c r="H171" t="n">
-        <v>74.28</v>
-      </c>
-      <c r="I171" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>59.85</v>
+      </c>
+      <c r="I171" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J171" s="2" t="n">
-        <v>10.242</v>
+        <v>1.153</v>
       </c>
       <c r="K171" s="2" t="n">
-        <v>9.504</v>
+        <v>1.066</v>
       </c>
       <c r="L171" t="inlineStr"/>
       <c r="M171" s="7" t="inlineStr"/>
@@ -8167,28 +8167,28 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>MBSB</t>
         </is>
       </c>
       <c r="D172" s="2" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="E172" s="8" t="n">
-        <v>-0.0225</v>
+        <v>0.54</v>
+      </c>
+      <c r="E172" s="3" t="n">
+        <v>0.0189</v>
       </c>
       <c r="F172" s="4" t="n">
-        <v>726400</v>
+        <v>914000</v>
       </c>
       <c r="G172" s="5" t="n">
-        <v>0.13</v>
+        <v>0.26</v>
       </c>
       <c r="H172" t="n">
-        <v>49.02</v>
+        <v>39.26</v>
       </c>
       <c r="I172" s="6" t="inlineStr">
         <is>
@@ -8196,10 +8196,10 @@
         </is>
       </c>
       <c r="J172" s="2" t="n">
-        <v>2.188</v>
+        <v>0.552</v>
       </c>
       <c r="K172" s="2" t="n">
-        <v>2.127</v>
+        <v>0.582</v>
       </c>
       <c r="L172" t="inlineStr"/>
       <c r="M172" s="7" t="inlineStr"/>
@@ -8212,39 +8212,39 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>0391</t>
+          <t>5263</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>AMBEST</t>
+          <t>SUNCON</t>
         </is>
       </c>
       <c r="D173" s="2" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="E173" s="8" t="n">
-        <v>-0.0149</v>
+        <v>7.62</v>
+      </c>
+      <c r="E173" s="3" t="n">
+        <v>0.016</v>
       </c>
       <c r="F173" s="4" t="n">
-        <v>698300</v>
+        <v>908500</v>
       </c>
       <c r="G173" s="5" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="H173" t="n">
-        <v>48.88</v>
-      </c>
-      <c r="I173" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.49</v>
+      </c>
+      <c r="I173" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J173" s="2" t="n">
-        <v>1.348</v>
+        <v>7.612</v>
       </c>
       <c r="K173" s="2" t="n">
-        <v>1.235</v>
+        <v>7.802</v>
       </c>
       <c r="L173" t="inlineStr"/>
       <c r="M173" s="7" t="inlineStr"/>
@@ -8257,28 +8257,28 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>3417</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>E&amp;O</t>
+          <t>HIBISCS</t>
         </is>
       </c>
       <c r="D174" s="2" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="E174" s="3" t="n">
-        <v>0.006500000000000001</v>
+        <v>2.17</v>
+      </c>
+      <c r="E174" s="8" t="n">
+        <v>-0.0225</v>
       </c>
       <c r="F174" s="4" t="n">
-        <v>677500</v>
+        <v>875000</v>
       </c>
       <c r="G174" s="5" t="n">
-        <v>0.37</v>
+        <v>0.16</v>
       </c>
       <c r="H174" t="n">
-        <v>50.06</v>
+        <v>49.02</v>
       </c>
       <c r="I174" s="6" t="inlineStr">
         <is>
@@ -8286,10 +8286,10 @@
         </is>
       </c>
       <c r="J174" s="2" t="n">
-        <v>0.771</v>
+        <v>2.188</v>
       </c>
       <c r="K174" s="2" t="n">
-        <v>0.767</v>
+        <v>2.127</v>
       </c>
       <c r="L174" t="inlineStr"/>
       <c r="M174" s="7" t="inlineStr"/>
@@ -8302,39 +8302,39 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>7293</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>YINSON</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D175" s="2" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="E175" s="3" t="n">
-        <v>0.0095</v>
+        <v>1.37</v>
+      </c>
+      <c r="E175" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F175" s="4" t="n">
-        <v>670200</v>
+        <v>869700</v>
       </c>
       <c r="G175" s="5" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="H175" t="n">
-        <v>55.63</v>
-      </c>
-      <c r="I175" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>72.14</v>
+      </c>
+      <c r="I175" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J175" s="2" t="n">
-        <v>2.09</v>
+        <v>1.237</v>
       </c>
       <c r="K175" s="2" t="n">
-        <v>2.037</v>
+        <v>1.008</v>
       </c>
       <c r="L175" t="inlineStr"/>
       <c r="M175" s="7" t="inlineStr"/>
@@ -8347,39 +8347,39 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>0097</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>VITROX</t>
         </is>
       </c>
       <c r="D176" s="2" t="n">
-        <v>1.47</v>
+        <v>11.08</v>
       </c>
       <c r="E176" s="3" t="n">
-        <v>0.0068</v>
+        <v>0.0073</v>
       </c>
       <c r="F176" s="4" t="n">
-        <v>663700</v>
+        <v>848300</v>
       </c>
       <c r="G176" s="5" t="n">
-        <v>0.35</v>
+        <v>0.26</v>
       </c>
       <c r="H176" t="n">
-        <v>34.88</v>
-      </c>
-      <c r="I176" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>74.28</v>
+      </c>
+      <c r="I176" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J176" s="2" t="n">
-        <v>1.507</v>
+        <v>10.242</v>
       </c>
       <c r="K176" s="2" t="n">
-        <v>1.621</v>
+        <v>9.504</v>
       </c>
       <c r="L176" t="inlineStr"/>
       <c r="M176" s="7" t="inlineStr"/>
@@ -8392,39 +8392,39 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>0240</t>
+          <t>0391</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>CORAZA</t>
+          <t>AMBEST</t>
         </is>
       </c>
       <c r="D177" s="2" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="E177" s="8" t="n">
-        <v>-0.0211</v>
+        <v>-0.0075</v>
       </c>
       <c r="F177" s="4" t="n">
-        <v>647600</v>
+        <v>845100</v>
       </c>
       <c r="G177" s="5" t="n">
-        <v>0.24</v>
+        <v>0.29</v>
       </c>
       <c r="H177" t="n">
-        <v>72.58</v>
-      </c>
-      <c r="I177" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.16</v>
+      </c>
+      <c r="I177" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J177" s="2" t="n">
-        <v>1.22</v>
+        <v>1.349</v>
       </c>
       <c r="K177" s="2" t="n">
-        <v>1.151</v>
+        <v>1.235</v>
       </c>
       <c r="L177" t="inlineStr"/>
       <c r="M177" s="7" t="inlineStr"/>
@@ -8437,28 +8437,28 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>5280</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>UWC</t>
+          <t>KIPREIT</t>
         </is>
       </c>
       <c r="D178" s="2" t="n">
-        <v>7.92</v>
-      </c>
-      <c r="E178" s="8" t="n">
-        <v>-0.008800000000000001</v>
+        <v>0.86</v>
+      </c>
+      <c r="E178" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F178" s="4" t="n">
-        <v>646100</v>
+        <v>813200</v>
       </c>
       <c r="G178" s="5" t="n">
-        <v>0.15</v>
+        <v>1.31</v>
       </c>
       <c r="H178" t="n">
-        <v>71.09999999999999</v>
+        <v>54.87</v>
       </c>
       <c r="I178" s="9" t="inlineStr">
         <is>
@@ -8466,10 +8466,10 @@
         </is>
       </c>
       <c r="J178" s="2" t="n">
-        <v>7.24</v>
+        <v>0.857</v>
       </c>
       <c r="K178" s="2" t="n">
-        <v>6.753</v>
+        <v>0.851</v>
       </c>
       <c r="L178" t="inlineStr"/>
       <c r="M178" s="7" t="inlineStr"/>
@@ -8482,28 +8482,28 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>5236</t>
+          <t>9792</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>MATRIX</t>
+          <t>SEG</t>
         </is>
       </c>
       <c r="D179" s="2" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="E179" s="3" t="n">
-        <v>0.019</v>
+        <v>0.625</v>
+      </c>
+      <c r="E179" s="8" t="n">
+        <v>-0.007900000000000001</v>
       </c>
       <c r="F179" s="4" t="n">
-        <v>643900</v>
+        <v>775100</v>
       </c>
       <c r="G179" s="5" t="n">
-        <v>0.58</v>
+        <v>0.61</v>
       </c>
       <c r="H179" t="n">
-        <v>38.66</v>
+        <v>37.72</v>
       </c>
       <c r="I179" s="6" t="inlineStr">
         <is>
@@ -8511,10 +8511,10 @@
         </is>
       </c>
       <c r="J179" s="2" t="n">
-        <v>1.102</v>
+        <v>0.632</v>
       </c>
       <c r="K179" s="2" t="n">
-        <v>1.147</v>
+        <v>0.63</v>
       </c>
       <c r="L179" t="inlineStr"/>
       <c r="M179" s="7" t="inlineStr"/>
@@ -8527,28 +8527,28 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>6012</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>MAXIS</t>
         </is>
       </c>
       <c r="D180" s="2" t="n">
-        <v>0.835</v>
-      </c>
-      <c r="E180" s="10" t="n">
-        <v>0</v>
+        <v>3.56</v>
+      </c>
+      <c r="E180" s="3" t="n">
+        <v>0.0142</v>
       </c>
       <c r="F180" s="4" t="n">
-        <v>637900</v>
+        <v>769600</v>
       </c>
       <c r="G180" s="5" t="n">
-        <v>0.21</v>
+        <v>0.45</v>
       </c>
       <c r="H180" t="n">
-        <v>58.39</v>
+        <v>51.11</v>
       </c>
       <c r="I180" s="6" t="inlineStr">
         <is>
@@ -8556,10 +8556,10 @@
         </is>
       </c>
       <c r="J180" s="2" t="n">
-        <v>0.819</v>
+        <v>3.543</v>
       </c>
       <c r="K180" s="2" t="n">
-        <v>0.756</v>
+        <v>3.601</v>
       </c>
       <c r="L180" t="inlineStr"/>
       <c r="M180" s="7" t="inlineStr"/>
@@ -8572,39 +8572,39 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>7293</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>YINSON</t>
         </is>
       </c>
       <c r="D181" s="2" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E181" s="8" t="n">
-        <v>-0.007800000000000001</v>
+        <v>2.13</v>
+      </c>
+      <c r="E181" s="3" t="n">
+        <v>0.0095</v>
       </c>
       <c r="F181" s="4" t="n">
-        <v>609000</v>
+        <v>756500</v>
       </c>
       <c r="G181" s="5" t="n">
-        <v>0.21</v>
+        <v>0.3</v>
       </c>
       <c r="H181" t="n">
-        <v>51.42</v>
-      </c>
-      <c r="I181" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.63</v>
+      </c>
+      <c r="I181" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J181" s="2" t="n">
-        <v>0.638</v>
+        <v>2.09</v>
       </c>
       <c r="K181" s="2" t="n">
-        <v>0.611</v>
+        <v>2.037</v>
       </c>
       <c r="L181" t="inlineStr"/>
       <c r="M181" s="7" t="inlineStr"/>
@@ -8617,28 +8617,28 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>0466</t>
+          <t>3417</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>SRKKAI</t>
+          <t>E&amp;O</t>
         </is>
       </c>
       <c r="D182" s="2" t="n">
-        <v>0.515</v>
-      </c>
-      <c r="E182" s="8" t="n">
-        <v>-0.009599999999999999</v>
+        <v>0.77</v>
+      </c>
+      <c r="E182" s="3" t="n">
+        <v>0.006500000000000001</v>
       </c>
       <c r="F182" s="4" t="n">
-        <v>600500</v>
+        <v>737700</v>
       </c>
       <c r="G182" s="5" t="n">
-        <v>0.52</v>
+        <v>0.41</v>
       </c>
       <c r="H182" t="n">
-        <v>45.34</v>
+        <v>50.06</v>
       </c>
       <c r="I182" s="6" t="inlineStr">
         <is>
@@ -8646,10 +8646,10 @@
         </is>
       </c>
       <c r="J182" s="2" t="n">
-        <v>0.524</v>
+        <v>0.771</v>
       </c>
       <c r="K182" s="2" t="n">
-        <v>0.533</v>
+        <v>0.767</v>
       </c>
       <c r="L182" t="inlineStr"/>
       <c r="M182" s="7" t="inlineStr"/>
@@ -8662,28 +8662,28 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>5227</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>IGBREIT</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="D183" s="2" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="E183" s="10" t="n">
-        <v>0</v>
+        <v>6.04</v>
+      </c>
+      <c r="E183" s="3" t="n">
+        <v>0.005</v>
       </c>
       <c r="F183" s="4" t="n">
-        <v>560900</v>
+        <v>726600</v>
       </c>
       <c r="G183" s="5" t="n">
-        <v>0.19</v>
+        <v>0.06</v>
       </c>
       <c r="H183" t="n">
-        <v>42.84</v>
+        <v>39.16</v>
       </c>
       <c r="I183" s="6" t="inlineStr">
         <is>
@@ -8691,10 +8691,10 @@
         </is>
       </c>
       <c r="J183" s="2" t="n">
-        <v>2.766</v>
+        <v>6.165</v>
       </c>
       <c r="K183" s="2" t="n">
-        <v>2.763</v>
+        <v>6.401</v>
       </c>
       <c r="L183" t="inlineStr"/>
       <c r="M183" s="7" t="inlineStr"/>
@@ -8707,28 +8707,28 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>5288</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>SIMEPROP</t>
+          <t>UWC</t>
         </is>
       </c>
       <c r="D184" s="2" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="E184" s="3" t="n">
-        <v>0.0248</v>
+        <v>7.94</v>
+      </c>
+      <c r="E184" s="8" t="n">
+        <v>-0.0063</v>
       </c>
       <c r="F184" s="4" t="n">
-        <v>558800</v>
+        <v>723700</v>
       </c>
       <c r="G184" s="5" t="n">
-        <v>0.1</v>
+        <v>0.17</v>
       </c>
       <c r="H184" t="n">
-        <v>46.82</v>
+        <v>71.79000000000001</v>
       </c>
       <c r="I184" s="9" t="inlineStr">
         <is>
@@ -8736,10 +8736,10 @@
         </is>
       </c>
       <c r="J184" s="2" t="n">
-        <v>1.247</v>
+        <v>7.242</v>
       </c>
       <c r="K184" s="2" t="n">
-        <v>1.285</v>
+        <v>6.753</v>
       </c>
       <c r="L184" t="inlineStr"/>
       <c r="M184" s="7" t="inlineStr"/>
@@ -8752,28 +8752,28 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>5271</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>PECCA</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D185" s="2" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="E185" s="10" t="n">
-        <v>0</v>
+        <v>1.47</v>
+      </c>
+      <c r="E185" s="3" t="n">
+        <v>0.0068</v>
       </c>
       <c r="F185" s="4" t="n">
-        <v>549100</v>
+        <v>717200</v>
       </c>
       <c r="G185" s="5" t="n">
-        <v>0.27</v>
+        <v>0.38</v>
       </c>
       <c r="H185" t="n">
-        <v>53.49</v>
+        <v>34.88</v>
       </c>
       <c r="I185" s="6" t="inlineStr">
         <is>
@@ -8781,10 +8781,10 @@
         </is>
       </c>
       <c r="J185" s="2" t="n">
-        <v>1.369</v>
+        <v>1.507</v>
       </c>
       <c r="K185" s="2" t="n">
-        <v>1.337</v>
+        <v>1.621</v>
       </c>
       <c r="L185" t="inlineStr"/>
       <c r="M185" s="7" t="inlineStr"/>
@@ -8797,39 +8797,39 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>7195</t>
+          <t>5227</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>BNASTRA</t>
+          <t>IGBREIT</t>
         </is>
       </c>
       <c r="D186" s="2" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="E186" s="3" t="n">
-        <v>0.0076</v>
+        <v>2.72</v>
+      </c>
+      <c r="E186" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F186" s="4" t="n">
-        <v>543700</v>
+        <v>717100</v>
       </c>
       <c r="G186" s="5" t="n">
-        <v>0.43</v>
+        <v>0.24</v>
       </c>
       <c r="H186" t="n">
-        <v>84.13</v>
-      </c>
-      <c r="I186" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.84</v>
+      </c>
+      <c r="I186" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J186" s="2" t="n">
-        <v>2.476</v>
+        <v>2.766</v>
       </c>
       <c r="K186" s="2" t="n">
-        <v>2.347</v>
+        <v>2.763</v>
       </c>
       <c r="L186" t="inlineStr"/>
       <c r="M186" s="7" t="inlineStr"/>
@@ -8842,28 +8842,28 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>0245</t>
+          <t>0240</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>MNHLDG</t>
+          <t>CORAZA</t>
         </is>
       </c>
       <c r="D187" s="2" t="n">
-        <v>3.88</v>
+        <v>1.39</v>
       </c>
       <c r="E187" s="8" t="n">
-        <v>-0.0077</v>
+        <v>-0.0211</v>
       </c>
       <c r="F187" s="4" t="n">
-        <v>543400</v>
+        <v>712900</v>
       </c>
       <c r="G187" s="5" t="n">
-        <v>0.18</v>
+        <v>0.26</v>
       </c>
       <c r="H187" t="n">
-        <v>54.53</v>
+        <v>72.58</v>
       </c>
       <c r="I187" s="9" t="inlineStr">
         <is>
@@ -8871,10 +8871,10 @@
         </is>
       </c>
       <c r="J187" s="2" t="n">
-        <v>3.859</v>
+        <v>1.22</v>
       </c>
       <c r="K187" s="2" t="n">
-        <v>3.569</v>
+        <v>1.151</v>
       </c>
       <c r="L187" t="inlineStr"/>
       <c r="M187" s="7" t="inlineStr"/>
@@ -8887,39 +8887,39 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>0291</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>CHB</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D188" s="2" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="E188" s="8" t="n">
-        <v>-0.0106</v>
+        <v>0.84</v>
+      </c>
+      <c r="E188" s="3" t="n">
+        <v>0.006</v>
       </c>
       <c r="F188" s="4" t="n">
-        <v>523100</v>
+        <v>679000</v>
       </c>
       <c r="G188" s="5" t="n">
-        <v>0.32</v>
+        <v>0.22</v>
       </c>
       <c r="H188" t="n">
-        <v>76.90000000000001</v>
-      </c>
-      <c r="I188" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>59.49</v>
+      </c>
+      <c r="I188" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J188" s="2" t="n">
-        <v>2.461</v>
+        <v>0.82</v>
       </c>
       <c r="K188" s="2" t="n">
-        <v>2.157</v>
+        <v>0.756</v>
       </c>
       <c r="L188" t="inlineStr"/>
       <c r="M188" s="7" t="inlineStr"/>
@@ -8932,28 +8932,28 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>5031</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>SDG</t>
+          <t>TIMECOM</t>
         </is>
       </c>
       <c r="D189" s="2" t="n">
-        <v>6.05</v>
+        <v>5.54</v>
       </c>
       <c r="E189" s="3" t="n">
-        <v>0.0067</v>
+        <v>0.0036</v>
       </c>
       <c r="F189" s="4" t="n">
-        <v>517600</v>
+        <v>667700</v>
       </c>
       <c r="G189" s="5" t="n">
-        <v>0.04</v>
+        <v>0.43</v>
       </c>
       <c r="H189" t="n">
-        <v>39.88</v>
+        <v>37.14</v>
       </c>
       <c r="I189" s="6" t="inlineStr">
         <is>
@@ -8961,10 +8961,10 @@
         </is>
       </c>
       <c r="J189" s="2" t="n">
-        <v>6.166</v>
+        <v>5.718</v>
       </c>
       <c r="K189" s="2" t="n">
-        <v>6.401</v>
+        <v>5.87</v>
       </c>
       <c r="L189" t="inlineStr"/>
       <c r="M189" s="7" t="inlineStr"/>
@@ -8977,28 +8977,28 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>5031</t>
+          <t>5236</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>TIMECOM</t>
+          <t>MATRIX</t>
         </is>
       </c>
       <c r="D190" s="2" t="n">
-        <v>5.56</v>
+        <v>1.07</v>
       </c>
       <c r="E190" s="3" t="n">
-        <v>0.0072</v>
+        <v>0.019</v>
       </c>
       <c r="F190" s="4" t="n">
-        <v>513100</v>
+        <v>657700</v>
       </c>
       <c r="G190" s="5" t="n">
-        <v>0.33</v>
+        <v>0.59</v>
       </c>
       <c r="H190" t="n">
-        <v>38.49</v>
+        <v>38.66</v>
       </c>
       <c r="I190" s="6" t="inlineStr">
         <is>
@@ -9006,16 +9006,556 @@
         </is>
       </c>
       <c r="J190" s="2" t="n">
-        <v>5.72</v>
+        <v>1.102</v>
       </c>
       <c r="K190" s="2" t="n">
-        <v>5.87</v>
+        <v>1.147</v>
       </c>
       <c r="L190" t="inlineStr"/>
       <c r="M190" s="7" t="inlineStr"/>
     </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>0466</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>SRKKAI</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="n">
+        <v>0.515</v>
+      </c>
+      <c r="E191" s="8" t="n">
+        <v>-0.009599999999999999</v>
+      </c>
+      <c r="F191" s="4" t="n">
+        <v>650600</v>
+      </c>
+      <c r="G191" s="5" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="H191" t="n">
+        <v>45.34</v>
+      </c>
+      <c r="I191" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J191" s="2" t="n">
+        <v>0.524</v>
+      </c>
+      <c r="K191" s="2" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="L191" t="inlineStr"/>
+      <c r="M191" s="7" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>0245</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>MNHLDG</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="E192" s="8" t="n">
+        <v>-0.0077</v>
+      </c>
+      <c r="F192" s="4" t="n">
+        <v>643100</v>
+      </c>
+      <c r="G192" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H192" t="n">
+        <v>54.53</v>
+      </c>
+      <c r="I192" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J192" s="2" t="n">
+        <v>3.859</v>
+      </c>
+      <c r="K192" s="2" t="n">
+        <v>3.569</v>
+      </c>
+      <c r="L192" t="inlineStr"/>
+      <c r="M192" s="7" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>0112</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>MIKROMB</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="E193" s="8" t="n">
+        <v>-0.007800000000000001</v>
+      </c>
+      <c r="F193" s="4" t="n">
+        <v>639100</v>
+      </c>
+      <c r="G193" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H193" t="n">
+        <v>51.42</v>
+      </c>
+      <c r="I193" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J193" s="2" t="n">
+        <v>0.638</v>
+      </c>
+      <c r="K193" s="2" t="n">
+        <v>0.611</v>
+      </c>
+      <c r="L193" t="inlineStr"/>
+      <c r="M193" s="7" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>5249</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>IOIPG</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="E194" s="8" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="F194" s="4" t="n">
+        <v>596100</v>
+      </c>
+      <c r="G194" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H194" t="n">
+        <v>37.58</v>
+      </c>
+      <c r="I194" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J194" s="2" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="K194" s="2" t="n">
+        <v>3.652</v>
+      </c>
+      <c r="L194" t="inlineStr"/>
+      <c r="M194" s="7" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>5271</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>PECCA</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="E195" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F195" s="4" t="n">
+        <v>572500</v>
+      </c>
+      <c r="G195" s="5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H195" t="n">
+        <v>53.49</v>
+      </c>
+      <c r="I195" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J195" s="2" t="n">
+        <v>1.369</v>
+      </c>
+      <c r="K195" s="2" t="n">
+        <v>1.337</v>
+      </c>
+      <c r="L195" t="inlineStr"/>
+      <c r="M195" s="7" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>0128</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>FRONTKN</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="E196" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F196" s="4" t="n">
+        <v>561200</v>
+      </c>
+      <c r="G196" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H196" t="n">
+        <v>52.79</v>
+      </c>
+      <c r="I196" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J196" s="2" t="n">
+        <v>5.049</v>
+      </c>
+      <c r="K196" s="2" t="n">
+        <v>5.057</v>
+      </c>
+      <c r="L196" t="inlineStr"/>
+      <c r="M196" s="7" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>7195</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>BNASTRA</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="E197" s="3" t="n">
+        <v>0.0076</v>
+      </c>
+      <c r="F197" s="4" t="n">
+        <v>559500</v>
+      </c>
+      <c r="G197" s="5" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="H197" t="n">
+        <v>84.13</v>
+      </c>
+      <c r="I197" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J197" s="2" t="n">
+        <v>2.476</v>
+      </c>
+      <c r="K197" s="2" t="n">
+        <v>2.347</v>
+      </c>
+      <c r="L197" t="inlineStr"/>
+      <c r="M197" s="7" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>3069</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>MFCB</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="E198" s="3" t="n">
+        <v>0.0215</v>
+      </c>
+      <c r="F198" s="4" t="n">
+        <v>550300</v>
+      </c>
+      <c r="G198" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H198" t="n">
+        <v>46.58</v>
+      </c>
+      <c r="I198" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J198" s="2" t="n">
+        <v>2.892</v>
+      </c>
+      <c r="K198" s="2" t="n">
+        <v>2.867</v>
+      </c>
+      <c r="L198" t="inlineStr"/>
+      <c r="M198" s="7" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>0291</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>CHB</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E199" s="8" t="n">
+        <v>-0.0071</v>
+      </c>
+      <c r="F199" s="4" t="n">
+        <v>531900</v>
+      </c>
+      <c r="G199" s="5" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="H199" t="n">
+        <v>77.84999999999999</v>
+      </c>
+      <c r="I199" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J199" s="2" t="n">
+        <v>2.462</v>
+      </c>
+      <c r="K199" s="2" t="n">
+        <v>2.157</v>
+      </c>
+      <c r="L199" t="inlineStr"/>
+      <c r="M199" s="7" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>7052</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>PADINI</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="E200" s="3" t="n">
+        <v>0.0192</v>
+      </c>
+      <c r="F200" s="4" t="n">
+        <v>525800</v>
+      </c>
+      <c r="G200" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H200" t="n">
+        <v>44.77</v>
+      </c>
+      <c r="I200" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J200" s="2" t="n">
+        <v>1.059</v>
+      </c>
+      <c r="K200" s="2" t="n">
+        <v>1.197</v>
+      </c>
+      <c r="L200" t="inlineStr"/>
+      <c r="M200" s="7" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>6139</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>TAKAFUL</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="E201" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F201" s="4" t="n">
+        <v>517200</v>
+      </c>
+      <c r="G201" s="5" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="H201" t="n">
+        <v>24.49</v>
+      </c>
+      <c r="I201" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J201" s="2" t="n">
+        <v>2.961</v>
+      </c>
+      <c r="K201" s="2" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="L201" t="inlineStr"/>
+      <c r="M201" s="7" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>0265</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>INFOM</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="E202" s="3" t="n">
+        <v>0.0107</v>
+      </c>
+      <c r="F202" s="4" t="n">
+        <v>507800</v>
+      </c>
+      <c r="G202" s="5" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="H202" t="n">
+        <v>83.56999999999999</v>
+      </c>
+      <c r="I202" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J202" s="2" t="n">
+        <v>1.732</v>
+      </c>
+      <c r="K202" s="2" t="n">
+        <v>1.604</v>
+      </c>
+      <c r="L202" t="inlineStr"/>
+      <c r="M202" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M190"/>
+  <autoFilter ref="A1:M202"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-09/bursa-report-2026-10-09.xlsx
+++ b/docs/downloads/2026-10-09/bursa-report-2026-10-09.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-09" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-09'!$A$1:$M$202</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-09'!$A$1:$M$207</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M202"/>
+  <dimension ref="A1:M207"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -552,19 +552,19 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.08</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0.0667</v>
+        <v>0.1333</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>172900200</v>
+        <v>174237900</v>
       </c>
       <c r="G2" s="5" t="n">
         <v>0.39</v>
       </c>
       <c r="H2" t="n">
-        <v>22.11</v>
+        <v>23.54</v>
       </c>
       <c r="I2" s="6" t="inlineStr">
         <is>
@@ -603,10 +603,10 @@
         <v>-0.0095</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>86229000</v>
+        <v>87716700</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>3.03</v>
+        <v>3.08</v>
       </c>
       <c r="H3" t="n">
         <v>62.99</v>
@@ -678,28 +678,28 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.845</v>
-      </c>
-      <c r="E5" s="8" t="n">
-        <v>-0.0343</v>
+        <v>0.335</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>0.0152</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>38921500</v>
+        <v>39429500</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="H5" t="n">
-        <v>63.57</v>
+        <v>76.77</v>
       </c>
       <c r="I5" s="9" t="inlineStr">
         <is>
@@ -707,10 +707,10 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.782</v>
+        <v>0.278</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.71</v>
+        <v>0.244</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" s="7" t="inlineStr"/>
@@ -723,28 +723,28 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.335</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>0.0152</v>
+        <v>0.84</v>
+      </c>
+      <c r="E6" s="8" t="n">
+        <v>-0.04</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>38867600</v>
+        <v>39284900</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.66</v>
+        <v>0.51</v>
       </c>
       <c r="H6" t="n">
-        <v>76.77</v>
+        <v>62.57</v>
       </c>
       <c r="I6" s="9" t="inlineStr">
         <is>
@@ -752,10 +752,10 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.278</v>
+        <v>0.782</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.244</v>
+        <v>0.71</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" s="7" t="inlineStr"/>
@@ -783,7 +783,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>31365500</v>
+        <v>31415500</v>
       </c>
       <c r="G7" s="5" t="n">
         <v>0.98</v>
@@ -828,10 +828,10 @@
         <v>0.0357</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>29980100</v>
+        <v>30383600</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="H8" t="n">
         <v>72.39</v>
@@ -918,7 +918,7 @@
         <v>0.0163</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>21869800</v>
+        <v>21878200</v>
       </c>
       <c r="G10" s="5" t="n">
         <v>0.84</v>
@@ -948,28 +948,28 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0278</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>EDELTEQ</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0.465</v>
-      </c>
-      <c r="E11" s="3" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.385</v>
+      </c>
+      <c r="E11" s="8" t="n">
+        <v>-0.0128</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>18939300</v>
+        <v>21699300</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>8.25</v>
+        <v>0.52</v>
       </c>
       <c r="H11" t="n">
-        <v>78.66</v>
+        <v>68.02</v>
       </c>
       <c r="I11" s="9" t="inlineStr">
         <is>
@@ -977,10 +977,10 @@
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.358</v>
+        <v>0.357</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0.349</v>
+        <v>0.236</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="7" t="inlineStr"/>
@@ -993,28 +993,28 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>0278</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>EDELTEQ</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="E12" s="10" t="n">
-        <v>0</v>
+        <v>0.47</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>0.0805</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>18620100</v>
+        <v>19033600</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.44</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>70.36</v>
+        <v>79.16</v>
       </c>
       <c r="I12" s="9" t="inlineStr">
         <is>
@@ -1022,10 +1022,10 @@
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.358</v>
+        <v>0.359</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0.236</v>
+        <v>0.349</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="7" t="inlineStr"/>
@@ -1047,19 +1047,19 @@
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0.185</v>
-      </c>
-      <c r="E13" s="10" t="n">
-        <v>0</v>
+        <v>0.18</v>
+      </c>
+      <c r="E13" s="8" t="n">
+        <v>-0.027</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>18528800</v>
+        <v>18581100</v>
       </c>
       <c r="G13" s="5" t="n">
         <v>0.29</v>
       </c>
       <c r="H13" t="n">
-        <v>63.02</v>
+        <v>60.1</v>
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.168</v>
+        <v>0.167</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>0.132</v>
@@ -1092,19 +1092,19 @@
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0.74</v>
+        <v>0.735</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>0.0571</v>
+        <v>0.05</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>17047600</v>
+        <v>17287600</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>2.24</v>
+        <v>2.27</v>
       </c>
       <c r="H14" t="n">
-        <v>61.01</v>
+        <v>60.21</v>
       </c>
       <c r="I14" s="9" t="inlineStr">
         <is>
@@ -1143,10 +1143,10 @@
         <v>0.0299</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>15681100</v>
+        <v>15752600</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="H15" t="n">
         <v>71.43000000000001</v>
@@ -1169,39 +1169,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>7079</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>TWL</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>0.31</v>
+        <v>0.025</v>
       </c>
       <c r="E16" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>13865000</v>
+        <v>15350000</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.72</v>
+        <v>0.82</v>
       </c>
       <c r="H16" t="n">
-        <v>57.67</v>
-      </c>
-      <c r="I16" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>51.85</v>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.305</v>
+        <v>0.025</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0.295</v>
+        <v>0.025</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="7" t="inlineStr"/>
@@ -1214,39 +1214,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E17" s="3" t="n">
-        <v>0.0959</v>
+        <v>0.31</v>
+      </c>
+      <c r="E17" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>11414600</v>
+        <v>13865000</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.96</v>
+        <v>0.72</v>
       </c>
       <c r="H17" t="n">
-        <v>56.64</v>
-      </c>
-      <c r="I17" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.67</v>
+      </c>
+      <c r="I17" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.384</v>
+        <v>0.305</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0.375</v>
+        <v>0.295</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="7" t="inlineStr"/>
@@ -1259,39 +1259,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>5.02</v>
+        <v>0.4</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>0.0141</v>
+        <v>0.0959</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>10497100</v>
+        <v>11415800</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.43</v>
+        <v>0.96</v>
       </c>
       <c r="H18" t="n">
-        <v>59</v>
-      </c>
-      <c r="I18" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>56.64</v>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>4.919</v>
+        <v>0.384</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>4.651</v>
+        <v>0.375</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="7" t="inlineStr"/>
@@ -1304,28 +1304,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>0.775</v>
+        <v>0.34</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.0149</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>10443200</v>
+        <v>10805900</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.71</v>
+        <v>1.92</v>
       </c>
       <c r="H19" t="n">
-        <v>50.25</v>
+        <v>57.06</v>
       </c>
       <c r="I19" s="9" t="inlineStr">
         <is>
@@ -1333,10 +1333,10 @@
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.775</v>
+        <v>0.327</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0.775</v>
+        <v>0.339</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="7" t="inlineStr"/>
@@ -1349,28 +1349,28 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E20" s="10" t="n">
-        <v>0</v>
+        <v>5.02</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>0.0141</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>10369400</v>
+        <v>10577200</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.55</v>
+        <v>0.43</v>
       </c>
       <c r="H20" t="n">
-        <v>46.68</v>
+        <v>59</v>
       </c>
       <c r="I20" s="9" t="inlineStr">
         <is>
@@ -1378,10 +1378,10 @@
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.868</v>
+        <v>4.919</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0.869</v>
+        <v>4.651</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="7" t="inlineStr"/>
@@ -1394,28 +1394,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0104</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>GENETEC</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>0.345</v>
+        <v>0.775</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>0.0299</v>
+        <v>0.006500000000000001</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>10242300</v>
+        <v>10443200</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>1.82</v>
+        <v>0.71</v>
       </c>
       <c r="H21" t="n">
-        <v>59.12</v>
+        <v>50.25</v>
       </c>
       <c r="I21" s="9" t="inlineStr">
         <is>
@@ -1423,10 +1423,10 @@
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.327</v>
+        <v>0.775</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0.339</v>
+        <v>0.775</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="7" t="inlineStr"/>
@@ -1439,28 +1439,28 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E22" s="3" t="n">
-        <v>0.008100000000000001</v>
+        <v>0.865</v>
+      </c>
+      <c r="E22" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>9837500</v>
+        <v>10379400</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.55</v>
       </c>
       <c r="H22" t="n">
-        <v>58.16</v>
+        <v>46.68</v>
       </c>
       <c r="I22" s="9" t="inlineStr">
         <is>
@@ -1468,10 +1468,10 @@
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.611</v>
+        <v>0.868</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0.611</v>
+        <v>0.869</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="7" t="inlineStr"/>
@@ -1484,39 +1484,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>5195</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CENSOF</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="E23" s="10" t="n">
-        <v>0</v>
+        <v>0.465</v>
+      </c>
+      <c r="E23" s="8" t="n">
+        <v>-0.0211</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>9781700</v>
+        <v>10165200</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>7.25</v>
+        <v>0.27</v>
       </c>
       <c r="H23" t="n">
-        <v>68.81</v>
-      </c>
-      <c r="I23" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>25.65</v>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.22</v>
+        <v>0.548</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0.206</v>
+        <v>0.749</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="7" t="inlineStr"/>
@@ -1529,39 +1529,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>5195</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>MALAKOF</t>
+          <t>CENSOF</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="E24" s="3" t="n">
-        <v>0.0128</v>
+        <v>0.24</v>
+      </c>
+      <c r="E24" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>9689800</v>
+        <v>9942100</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>2.62</v>
+        <v>7.37</v>
       </c>
       <c r="H24" t="n">
-        <v>48.72</v>
-      </c>
-      <c r="I24" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>68.81</v>
+      </c>
+      <c r="I24" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.791</v>
+        <v>0.22</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0.806</v>
+        <v>0.206</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="7" t="inlineStr"/>
@@ -1574,39 +1574,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="E25" s="8" t="n">
-        <v>-0.0316</v>
+        <v>0.625</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>0.008100000000000001</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>9473100</v>
+        <v>9840500</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.25</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H25" t="n">
-        <v>25.19</v>
-      </c>
-      <c r="I25" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.16</v>
+      </c>
+      <c r="I25" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.548</v>
+        <v>0.611</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0.749</v>
+        <v>0.611</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="7" t="inlineStr"/>
@@ -1628,19 +1628,19 @@
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>0.16</v>
+        <v>0.155</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>0.1034</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>9446000</v>
+        <v>9724800</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="H26" t="n">
-        <v>78.47</v>
+        <v>77.22</v>
       </c>
       <c r="I26" s="9" t="inlineStr">
         <is>
@@ -1664,39 +1664,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>MALAKOF</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="E27" s="8" t="n">
-        <v>-0.0337</v>
+        <v>0.79</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>0.0128</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>9011500</v>
+        <v>9695300</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.33</v>
+        <v>2.62</v>
       </c>
       <c r="H27" t="n">
-        <v>59.31</v>
-      </c>
-      <c r="I27" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.72</v>
+      </c>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.409</v>
+        <v>0.791</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0.346</v>
+        <v>0.806</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="7" t="inlineStr"/>
@@ -1709,28 +1709,28 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>2.81</v>
+        <v>4.57</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0.0108</v>
+        <v>0.0044</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>8691200</v>
+        <v>9094100</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.63</v>
+        <v>0.58</v>
       </c>
       <c r="H28" t="n">
-        <v>53.6</v>
+        <v>29.08</v>
       </c>
       <c r="I28" s="6" t="inlineStr">
         <is>
@@ -1738,10 +1738,10 @@
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>2.791</v>
+        <v>4.722</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>2.693</v>
+        <v>4.891</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="7" t="inlineStr"/>
@@ -1754,28 +1754,28 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>0.8149999999999999</v>
-      </c>
-      <c r="E29" s="3" t="n">
-        <v>0.0062</v>
+        <v>0.43</v>
+      </c>
+      <c r="E29" s="8" t="n">
+        <v>-0.0337</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>8538200</v>
+        <v>9032700</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.53</v>
+        <v>0.34</v>
       </c>
       <c r="H29" t="n">
-        <v>54.76</v>
+        <v>59.31</v>
       </c>
       <c r="I29" s="9" t="inlineStr">
         <is>
@@ -1783,10 +1783,10 @@
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.409</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0.806</v>
+        <v>0.346</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="7" t="inlineStr"/>
@@ -1799,39 +1799,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0050</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>SYSTECH</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>0.185</v>
+        <v>2.81</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>0.0571</v>
+        <v>0.0108</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>8237700</v>
+        <v>9016000</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>1.52</v>
+        <v>0.65</v>
       </c>
       <c r="H30" t="n">
-        <v>65.31999999999999</v>
-      </c>
-      <c r="I30" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.6</v>
+      </c>
+      <c r="I30" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.165</v>
+        <v>2.791</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0.166</v>
+        <v>2.693</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="7" t="inlineStr"/>
@@ -1844,39 +1844,39 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>4.57</v>
+        <v>0.82</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0.0044</v>
+        <v>0.0123</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>8115100</v>
+        <v>8560500</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="H31" t="n">
-        <v>29.08</v>
-      </c>
-      <c r="I31" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.28</v>
+      </c>
+      <c r="I31" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>4.722</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>4.891</v>
+        <v>0.806</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="7" t="inlineStr"/>
@@ -1889,36 +1889,40 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0470</t>
+          <t>0050</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>BFIELD</t>
+          <t>SYSTECH</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>0.475</v>
-      </c>
-      <c r="E32" s="8" t="n">
-        <v>-0.0104</v>
+        <v>0.18</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>0.0286</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>8113100</v>
+        <v>8307700</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.68</v>
+        <v>1.54</v>
       </c>
       <c r="H32" t="n">
-        <v>54.21</v>
+        <v>62.97</v>
       </c>
       <c r="I32" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J32" s="2" t="n"/>
-      <c r="K32" s="2" t="n"/>
+      <c r="J32" s="2" t="n">
+        <v>0.164</v>
+      </c>
+      <c r="K32" s="2" t="n">
+        <v>0.165</v>
+      </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="7" t="inlineStr"/>
     </row>
@@ -1930,40 +1934,36 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0358</t>
+          <t>0470</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ICTZONE</t>
+          <t>BFIELD</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="E33" s="3" t="n">
-        <v>0.0667</v>
+        <v>0.475</v>
+      </c>
+      <c r="E33" s="8" t="n">
+        <v>-0.0104</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>7663400</v>
+        <v>8113100</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>2.75</v>
+        <v>0.68</v>
       </c>
       <c r="H33" t="n">
-        <v>48.47</v>
-      </c>
-      <c r="I33" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="n">
-        <v>0.241</v>
-      </c>
-      <c r="K33" s="2" t="n">
-        <v>0.249</v>
-      </c>
+        <v>54.21</v>
+      </c>
+      <c r="I33" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="n"/>
+      <c r="K33" s="2" t="n"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="7" t="inlineStr"/>
     </row>
@@ -1975,39 +1975,39 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>0358</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>ICTZONE</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>0.7</v>
+        <v>0.24</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0.08529999999999999</v>
+        <v>0.0667</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>7575700</v>
+        <v>7663400</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>1.67</v>
+        <v>2.75</v>
       </c>
       <c r="H34" t="n">
-        <v>85.98999999999999</v>
-      </c>
-      <c r="I34" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.47</v>
+      </c>
+      <c r="I34" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.518</v>
+        <v>0.241</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0.443</v>
+        <v>0.249</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="7" t="inlineStr"/>
@@ -2020,39 +2020,39 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="E35" s="8" t="n">
-        <v>-0.0127</v>
+        <v>0.7</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>0.08529999999999999</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>7463700</v>
+        <v>7611400</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.68</v>
       </c>
       <c r="H35" t="n">
-        <v>34.12</v>
-      </c>
-      <c r="I35" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>85.98999999999999</v>
+      </c>
+      <c r="I35" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.402</v>
+        <v>0.518</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0.41</v>
+        <v>0.443</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="7" t="inlineStr"/>
@@ -2065,33 +2065,40 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0476</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>SLGC Berhad</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E36" s="10" t="n">
-        <v>0</v>
+        <v>0.39</v>
+      </c>
+      <c r="E36" s="8" t="n">
+        <v>-0.0127</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>7414600</v>
+        <v>7466200</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="I36" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="n"/>
-      <c r="K36" s="2" t="n"/>
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="H36" t="n">
+        <v>34.12</v>
+      </c>
+      <c r="I36" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="n">
+        <v>0.402</v>
+      </c>
+      <c r="K36" s="2" t="n">
+        <v>0.41</v>
+      </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="7" t="inlineStr"/>
     </row>
@@ -2103,40 +2110,33 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>0476</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>SLGC Berhad</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="E37" s="3" t="n">
-        <v>0.004699999999999999</v>
+        <v>0.25</v>
+      </c>
+      <c r="E37" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>7180700</v>
+        <v>7415200</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="H37" t="n">
-        <v>42.31</v>
-      </c>
-      <c r="I37" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="n">
-        <v>2.226</v>
-      </c>
-      <c r="K37" s="2" t="n">
-        <v>2.213</v>
-      </c>
+        <v>0.17</v>
+      </c>
+      <c r="I37" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="n"/>
+      <c r="K37" s="2" t="n"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="7" t="inlineStr"/>
     </row>
@@ -2148,28 +2148,28 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>0.365</v>
-      </c>
-      <c r="E38" s="8" t="n">
-        <v>-0.0135</v>
+        <v>2.15</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>0.004699999999999999</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>6435300</v>
+        <v>7229700</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.96</v>
+        <v>0.49</v>
       </c>
       <c r="H38" t="n">
-        <v>47.65</v>
+        <v>42.31</v>
       </c>
       <c r="I38" s="6" t="inlineStr">
         <is>
@@ -2177,10 +2177,10 @@
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.367</v>
+        <v>2.226</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>0.367</v>
+        <v>2.213</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="7" t="inlineStr"/>
@@ -2193,39 +2193,39 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0198</t>
+          <t>7020</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>GDB</t>
+          <t>ASTEEL</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="E39" s="8" t="n">
-        <v>-0.0361</v>
+        <v>-0.0476</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>6280000</v>
+        <v>6606600</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>5.57</v>
+        <v>2.98</v>
       </c>
       <c r="H39" t="n">
-        <v>32.62</v>
-      </c>
-      <c r="I39" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.45</v>
+      </c>
+      <c r="I39" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.421</v>
+        <v>0.095</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0.441</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="7" t="inlineStr"/>
@@ -2238,28 +2238,28 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>AVANGAAD</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E40" s="10" t="n">
-        <v>0</v>
+        <v>0.365</v>
+      </c>
+      <c r="E40" s="8" t="n">
+        <v>-0.0135</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>6246100</v>
+        <v>6435300</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>2.38</v>
+        <v>0.96</v>
       </c>
       <c r="H40" t="n">
-        <v>49.15</v>
+        <v>47.65</v>
       </c>
       <c r="I40" s="6" t="inlineStr">
         <is>
@@ -2267,10 +2267,10 @@
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.295</v>
+        <v>0.367</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0.296</v>
+        <v>0.367</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="7" t="inlineStr"/>
@@ -2283,39 +2283,39 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>7020</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ASTEEL</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>0.105</v>
-      </c>
-      <c r="E41" s="10" t="n">
-        <v>0</v>
+        <v>0.4</v>
+      </c>
+      <c r="E41" s="8" t="n">
+        <v>-0.0361</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>6023100</v>
+        <v>6280400</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>2.72</v>
+        <v>5.57</v>
       </c>
       <c r="H41" t="n">
-        <v>59.81</v>
-      </c>
-      <c r="I41" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>32.62</v>
+      </c>
+      <c r="I41" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.096</v>
+        <v>0.421</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.441</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="7" t="inlineStr"/>
@@ -2328,39 +2328,39 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="E42" s="3" t="n">
-        <v>0.102</v>
+        <v>0.295</v>
+      </c>
+      <c r="E42" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>5978900</v>
+        <v>6246100</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>1.33</v>
+        <v>2.38</v>
       </c>
       <c r="H42" t="n">
-        <v>65.41</v>
-      </c>
-      <c r="I42" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.15</v>
+      </c>
+      <c r="I42" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>5.832</v>
+        <v>0.295</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>5.778</v>
+        <v>0.296</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="7" t="inlineStr"/>
@@ -2388,10 +2388,10 @@
         <v>0.024</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>5877500</v>
+        <v>6206400</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.31</v>
+        <v>0.33</v>
       </c>
       <c r="H43" t="n">
         <v>64.14</v>
@@ -2418,39 +2418,39 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>7.25</v>
-      </c>
-      <c r="E44" s="8" t="n">
-        <v>-0.0014</v>
+        <v>6.69</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>0.1003</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>5737900</v>
+        <v>6008100</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.41</v>
+        <v>1.34</v>
       </c>
       <c r="H44" t="n">
-        <v>31.19</v>
-      </c>
-      <c r="I44" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>65.3</v>
+      </c>
+      <c r="I44" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>7.639</v>
+        <v>5.831</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>7.729</v>
+        <v>5.778</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="7" t="inlineStr"/>
@@ -2463,28 +2463,28 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>5141</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>DAYANG</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>1.39</v>
+        <v>7.25</v>
       </c>
       <c r="E45" s="8" t="n">
-        <v>-0.0414</v>
+        <v>-0.0014</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>5728800</v>
+        <v>5853800</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>2.61</v>
+        <v>0.42</v>
       </c>
       <c r="H45" t="n">
-        <v>33.34</v>
+        <v>31.19</v>
       </c>
       <c r="I45" s="6" t="inlineStr">
         <is>
@@ -2492,10 +2492,10 @@
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>1.456</v>
+        <v>7.639</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>1.494</v>
+        <v>7.729</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="7" t="inlineStr"/>
@@ -2508,28 +2508,28 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>7139</t>
+          <t>5141</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>NICE</t>
+          <t>DAYANG</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="E46" s="10" t="n">
-        <v>0</v>
+        <v>1.39</v>
+      </c>
+      <c r="E46" s="8" t="n">
+        <v>-0.0414</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>5705300</v>
+        <v>5736200</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>6.03</v>
+        <v>2.61</v>
       </c>
       <c r="H46" t="n">
-        <v>37.6</v>
+        <v>33.34</v>
       </c>
       <c r="I46" s="6" t="inlineStr">
         <is>
@@ -2537,10 +2537,10 @@
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.083</v>
+        <v>1.456</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>0.08699999999999999</v>
+        <v>1.494</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="7" t="inlineStr"/>
@@ -2553,28 +2553,28 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>7139</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>WCT</t>
+          <t>NICE</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>0.34</v>
+        <v>0.08</v>
       </c>
       <c r="E47" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>5657200</v>
+        <v>5705300</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>1.42</v>
+        <v>6.03</v>
       </c>
       <c r="H47" t="n">
-        <v>32.2</v>
+        <v>37.6</v>
       </c>
       <c r="I47" s="6" t="inlineStr">
         <is>
@@ -2582,10 +2582,10 @@
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.363</v>
+        <v>0.083</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0.383</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="7" t="inlineStr"/>
@@ -2598,39 +2598,39 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="E48" s="8" t="n">
-        <v>-0.0072</v>
+        <v>9.81</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>0.001</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>5593900</v>
+        <v>5672800</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.31</v>
+        <v>0.45</v>
       </c>
       <c r="H48" t="n">
-        <v>63.23</v>
-      </c>
-      <c r="I48" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>31.22</v>
+      </c>
+      <c r="I48" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>2.625</v>
+        <v>10.022</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>2.496</v>
+        <v>10.213</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="7" t="inlineStr"/>
@@ -2643,28 +2643,28 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>9.81</v>
-      </c>
-      <c r="E49" s="3" t="n">
-        <v>0.001</v>
+        <v>0.34</v>
+      </c>
+      <c r="E49" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>5545700</v>
+        <v>5662200</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.44</v>
+        <v>1.42</v>
       </c>
       <c r="H49" t="n">
-        <v>31.22</v>
+        <v>32.2</v>
       </c>
       <c r="I49" s="6" t="inlineStr">
         <is>
@@ -2672,10 +2672,10 @@
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>10.022</v>
+        <v>0.363</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>10.213</v>
+        <v>0.383</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="7" t="inlineStr"/>
@@ -2688,28 +2688,28 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>SKPRES</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="E50" s="3" t="n">
-        <v>0.04</v>
+        <v>2.75</v>
+      </c>
+      <c r="E50" s="8" t="n">
+        <v>-0.0108</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>5288500</v>
+        <v>5599900</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.64</v>
+        <v>0.31</v>
       </c>
       <c r="H50" t="n">
-        <v>70.7</v>
+        <v>62.29</v>
       </c>
       <c r="I50" s="9" t="inlineStr">
         <is>
@@ -2717,10 +2717,10 @@
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.355</v>
+        <v>2.624</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>0.322</v>
+        <v>2.496</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="7" t="inlineStr"/>
@@ -2733,28 +2733,28 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="E51" s="8" t="n">
-        <v>-0.0127</v>
+        <v>1.23</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>0.0603</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>5255200</v>
+        <v>5340400</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.66</v>
+        <v>0.93</v>
       </c>
       <c r="H51" t="n">
-        <v>51.22</v>
+        <v>60.41</v>
       </c>
       <c r="I51" s="9" t="inlineStr">
         <is>
@@ -2762,10 +2762,10 @@
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.778</v>
+        <v>1.158</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0.773</v>
+        <v>1.166</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="7" t="inlineStr"/>
@@ -2778,28 +2778,28 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>1.23</v>
+        <v>0.39</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>0.0603</v>
+        <v>0.04</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>5242000</v>
+        <v>5293500</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.91</v>
+        <v>0.64</v>
       </c>
       <c r="H52" t="n">
-        <v>60.41</v>
+        <v>70.7</v>
       </c>
       <c r="I52" s="9" t="inlineStr">
         <is>
@@ -2807,10 +2807,10 @@
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>1.158</v>
+        <v>0.355</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>1.166</v>
+        <v>0.322</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="7" t="inlineStr"/>
@@ -2823,39 +2823,39 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>IOICORP</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>4.57</v>
-      </c>
-      <c r="E53" s="3" t="n">
-        <v>0.0022</v>
+        <v>0.78</v>
+      </c>
+      <c r="E53" s="8" t="n">
+        <v>-0.0127</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>5143700</v>
+        <v>5265500</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.54</v>
+        <v>0.67</v>
       </c>
       <c r="H53" t="n">
-        <v>40.81</v>
-      </c>
-      <c r="I53" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.22</v>
+      </c>
+      <c r="I53" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>4.674</v>
+        <v>0.778</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>4.619</v>
+        <v>0.773</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="7" t="inlineStr"/>
@@ -2868,39 +2868,39 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>5326</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>99SMART</t>
+          <t>IOICORP</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="E54" s="3" t="n">
-        <v>0.0481</v>
+        <v>4.56</v>
+      </c>
+      <c r="E54" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>4816700</v>
+        <v>5152100</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>1.13</v>
+        <v>0.54</v>
       </c>
       <c r="H54" t="n">
-        <v>52.82</v>
-      </c>
-      <c r="I54" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.78</v>
+      </c>
+      <c r="I54" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>3.2</v>
+        <v>4.674</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>3.391</v>
+        <v>4.619</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="7" t="inlineStr"/>
@@ -2928,10 +2928,10 @@
         <v>0.0182</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>4695500</v>
+        <v>5095000</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.66</v>
+        <v>0.72</v>
       </c>
       <c r="H55" t="n">
         <v>37.22</v>
@@ -2958,28 +2958,28 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0376</t>
+          <t>5326</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>IAB</t>
+          <t>99SMART</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="E56" s="8" t="n">
-        <v>-0.0296</v>
+        <v>3.26</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>0.0449</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>4529200</v>
+        <v>4961100</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>2.61</v>
+        <v>1.17</v>
       </c>
       <c r="H56" t="n">
-        <v>53.07</v>
+        <v>52.06</v>
       </c>
       <c r="I56" s="9" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>1.274</v>
+        <v>3.199</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>1.319</v>
+        <v>3.39</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="7" t="inlineStr"/>
@@ -3018,10 +3018,10 @@
         <v>-0.0042</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>4440300</v>
+        <v>4671700</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.46</v>
+        <v>0.49</v>
       </c>
       <c r="H57" t="n">
         <v>18.83</v>
@@ -3048,28 +3048,28 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>0376</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>IAB</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="E58" s="10" t="n">
-        <v>0</v>
+        <v>1.32</v>
+      </c>
+      <c r="E58" s="8" t="n">
+        <v>-0.0222</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>4417200</v>
+        <v>4565400</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.64</v>
+        <v>2.64</v>
       </c>
       <c r="H58" t="n">
-        <v>62.48</v>
+        <v>54.18</v>
       </c>
       <c r="I58" s="9" t="inlineStr">
         <is>
@@ -3077,10 +3077,10 @@
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.427</v>
+        <v>1.275</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>0.413</v>
+        <v>1.32</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="7" t="inlineStr"/>
@@ -3093,28 +3093,28 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>1.13</v>
+        <v>0.455</v>
       </c>
       <c r="E59" s="8" t="n">
-        <v>-0.0342</v>
+        <v>-0.0109</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>4154500</v>
+        <v>4422200</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.37</v>
+        <v>0.64</v>
       </c>
       <c r="H59" t="n">
-        <v>47.14</v>
+        <v>60.71</v>
       </c>
       <c r="I59" s="9" t="inlineStr">
         <is>
@@ -3122,10 +3122,10 @@
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>1.161</v>
+        <v>0.426</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>1.119</v>
+        <v>0.413</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="7" t="inlineStr"/>
@@ -3147,19 +3147,19 @@
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>3.68</v>
+        <v>3.69</v>
       </c>
       <c r="E60" s="8" t="n">
-        <v>-0.0239</v>
+        <v>-0.0212</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>4146700</v>
+        <v>4167500</v>
       </c>
       <c r="G60" s="5" t="n">
         <v>0.36</v>
       </c>
       <c r="H60" t="n">
-        <v>55.84</v>
+        <v>56.09</v>
       </c>
       <c r="I60" s="6" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>3.598</v>
+        <v>3.599</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>2.739</v>
@@ -3183,39 +3183,39 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="E61" s="10" t="n">
-        <v>0</v>
+        <v>1.13</v>
+      </c>
+      <c r="E61" s="8" t="n">
+        <v>-0.0342</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>3874800</v>
+        <v>4157000</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.35</v>
+        <v>0.37</v>
       </c>
       <c r="H61" t="n">
-        <v>43.08</v>
-      </c>
-      <c r="I61" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.14</v>
+      </c>
+      <c r="I61" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>1.322</v>
+        <v>1.161</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>1.305</v>
+        <v>1.119</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="7" t="inlineStr"/>
@@ -3228,28 +3228,28 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>SPSETIA</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>0.725</v>
+        <v>1.28</v>
       </c>
       <c r="E62" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>3824000</v>
+        <v>3910400</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.64</v>
+        <v>0.36</v>
       </c>
       <c r="H62" t="n">
-        <v>34.68</v>
+        <v>43.08</v>
       </c>
       <c r="I62" s="6" t="inlineStr">
         <is>
@@ -3257,10 +3257,10 @@
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.757</v>
+        <v>1.322</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>0.82</v>
+        <v>1.305</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="7" t="inlineStr"/>
@@ -3273,39 +3273,39 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0111</t>
+          <t>2429</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>K1</t>
+          <t>TANCO</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>0.165</v>
-      </c>
-      <c r="E63" s="3" t="n">
-        <v>0.0313</v>
+        <v>0.145</v>
+      </c>
+      <c r="E63" s="8" t="n">
+        <v>-0.0333</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>3815200</v>
+        <v>3906600</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>1.16</v>
+        <v>0.22</v>
       </c>
       <c r="H63" t="n">
-        <v>59.38</v>
-      </c>
-      <c r="I63" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>28.09</v>
+      </c>
+      <c r="I63" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.156</v>
+        <v>0.164</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>0.145</v>
+        <v>0.201</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="7" t="inlineStr"/>
@@ -3318,39 +3318,39 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0345</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>SUNLOGY</t>
+          <t>SPSETIA</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="E64" s="3" t="n">
-        <v>0.0227</v>
+        <v>0.725</v>
+      </c>
+      <c r="E64" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>3765600</v>
+        <v>3829600</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0.36</v>
+        <v>0.65</v>
       </c>
       <c r="H64" t="n">
-        <v>51.11</v>
-      </c>
-      <c r="I64" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.68</v>
+      </c>
+      <c r="I64" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.45</v>
+        <v>0.757</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>0.426</v>
+        <v>0.82</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="7" t="inlineStr"/>
@@ -3363,28 +3363,28 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>5253</t>
+          <t>0111</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>ECONBHD</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="E65" s="10" t="n">
-        <v>0</v>
+        <v>0.165</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>0.0313</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>3696000</v>
+        <v>3815200</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.16</v>
       </c>
       <c r="H65" t="n">
-        <v>55.25</v>
+        <v>59.38</v>
       </c>
       <c r="I65" s="9" t="inlineStr">
         <is>
@@ -3392,10 +3392,10 @@
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.122</v>
+        <v>0.156</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>0.125</v>
+        <v>0.145</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="7" t="inlineStr"/>
@@ -3408,39 +3408,39 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>TANCO</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="E66" s="10" t="n">
-        <v>0</v>
+        <v>0.45</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>0.0227</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>3650000</v>
+        <v>3765600</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>0.21</v>
+        <v>0.36</v>
       </c>
       <c r="H66" t="n">
-        <v>30.21</v>
-      </c>
-      <c r="I66" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.11</v>
+      </c>
+      <c r="I66" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.165</v>
+        <v>0.45</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>0.201</v>
+        <v>0.426</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="7" t="inlineStr"/>
@@ -3453,28 +3453,28 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="E67" s="8" t="n">
-        <v>-0.0052</v>
+        <v>1.26</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>0.0161</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>3599700</v>
+        <v>3739500</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="H67" t="n">
-        <v>54.49</v>
+        <v>39.42</v>
       </c>
       <c r="I67" s="6" t="inlineStr">
         <is>
@@ -3482,10 +3482,10 @@
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.961</v>
+        <v>1.286</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>0.821</v>
+        <v>1.387</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="7" t="inlineStr"/>
@@ -3498,39 +3498,39 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="E68" s="3" t="n">
-        <v>0.0112</v>
+        <v>0.955</v>
+      </c>
+      <c r="E68" s="8" t="n">
+        <v>-0.0104</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>3579900</v>
+        <v>3715500</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>0.6</v>
+        <v>0.46</v>
       </c>
       <c r="H68" t="n">
-        <v>57.99</v>
-      </c>
-      <c r="I68" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.7</v>
+      </c>
+      <c r="I68" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>2.629</v>
+        <v>0.96</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>2.581</v>
+        <v>0.821</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="7" t="inlineStr"/>
@@ -3543,36 +3543,40 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0468</t>
+          <t>5253</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>UNIPAC</t>
+          <t>ECONBHD</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>0.25</v>
+        <v>0.125</v>
       </c>
       <c r="E69" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>3575800</v>
+        <v>3696000</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>0.3</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H69" t="n">
-        <v>28.11</v>
+        <v>55.25</v>
       </c>
       <c r="I69" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J69" s="2" t="n"/>
-      <c r="K69" s="2" t="n"/>
+      <c r="J69" s="2" t="n">
+        <v>0.122</v>
+      </c>
+      <c r="K69" s="2" t="n">
+        <v>0.125</v>
+      </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="7" t="inlineStr"/>
     </row>
@@ -3584,39 +3588,39 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>1.26</v>
+        <v>1.13</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>0.0161</v>
+        <v>0.0273</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>3563100</v>
+        <v>3618700</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="H70" t="n">
-        <v>39.42</v>
-      </c>
-      <c r="I70" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66.05</v>
+      </c>
+      <c r="I70" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>1.286</v>
+        <v>1.07</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>1.387</v>
+        <v>0.917</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="7" t="inlineStr"/>
@@ -3629,39 +3633,39 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>0.525</v>
+        <v>2.71</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>0.0294</v>
+        <v>0.0112</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>3556400</v>
+        <v>3580900</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>0.21</v>
+        <v>0.6</v>
       </c>
       <c r="H71" t="n">
-        <v>55.9</v>
-      </c>
-      <c r="I71" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.99</v>
+      </c>
+      <c r="I71" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.512</v>
+        <v>2.629</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>0.436</v>
+        <v>2.581</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="7" t="inlineStr"/>
@@ -3674,40 +3678,36 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>0468</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>UNIPAC</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="E72" s="3" t="n">
-        <v>0.0364</v>
+        <v>0.245</v>
+      </c>
+      <c r="E72" s="8" t="n">
+        <v>-0.02</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>3519900</v>
+        <v>3580800</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>0.37</v>
+        <v>0.3</v>
       </c>
       <c r="H72" t="n">
-        <v>67.13</v>
+        <v>27.35</v>
       </c>
       <c r="I72" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J72" s="2" t="n">
-        <v>1.071</v>
-      </c>
-      <c r="K72" s="2" t="n">
-        <v>0.917</v>
-      </c>
+      <c r="J72" s="2" t="n"/>
+      <c r="K72" s="2" t="n"/>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="7" t="inlineStr"/>
     </row>
@@ -3719,28 +3719,28 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>5.6</v>
+        <v>0.53</v>
       </c>
       <c r="E73" s="3" t="n">
-        <v>0.0072</v>
+        <v>0.0392</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>3465300</v>
+        <v>3565000</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>0.24</v>
+        <v>0.21</v>
       </c>
       <c r="H73" t="n">
-        <v>50.83</v>
+        <v>56.74</v>
       </c>
       <c r="I73" s="6" t="inlineStr">
         <is>
@@ -3748,10 +3748,10 @@
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>5.636</v>
+        <v>0.512</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>5.308</v>
+        <v>0.436</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="7" t="inlineStr"/>
@@ -3773,19 +3773,19 @@
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>0.54</v>
+        <v>0.545</v>
       </c>
       <c r="E74" s="8" t="n">
-        <v>-0.027</v>
+        <v>-0.018</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>3464500</v>
+        <v>3496200</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H74" t="n">
-        <v>31.37</v>
+        <v>32.26</v>
       </c>
       <c r="I74" s="6" t="inlineStr">
         <is>
@@ -3809,39 +3809,39 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>TENAGA</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>12.96</v>
+        <v>5.6</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>0.004699999999999999</v>
+        <v>0.0072</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>3385900</v>
+        <v>3482100</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>0.37</v>
+        <v>0.24</v>
       </c>
       <c r="H75" t="n">
-        <v>42.32</v>
-      </c>
-      <c r="I75" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.83</v>
+      </c>
+      <c r="I75" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>13.036</v>
+        <v>5.636</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>13.573</v>
+        <v>5.308</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="7" t="inlineStr"/>
@@ -3854,28 +3854,28 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>TENAGA</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>0.79</v>
+        <v>12.96</v>
       </c>
       <c r="E76" s="3" t="n">
-        <v>0.0064</v>
+        <v>0.004699999999999999</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>3383800</v>
+        <v>3478800</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>0.25</v>
+        <v>0.38</v>
       </c>
       <c r="H76" t="n">
-        <v>56.46</v>
+        <v>42.32</v>
       </c>
       <c r="I76" s="9" t="inlineStr">
         <is>
@@ -3883,10 +3883,10 @@
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.767</v>
+        <v>13.036</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>0.712</v>
+        <v>13.573</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="7" t="inlineStr"/>
@@ -3899,28 +3899,28 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0296</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>HEGROUP</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="E77" s="8" t="n">
-        <v>-0.008800000000000001</v>
+        <v>0.79</v>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>0.0064</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>3295900</v>
+        <v>3383800</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>0.68</v>
+        <v>0.25</v>
       </c>
       <c r="H77" t="n">
-        <v>68.90000000000001</v>
+        <v>56.46</v>
       </c>
       <c r="I77" s="9" t="inlineStr">
         <is>
@@ -3928,10 +3928,10 @@
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>1.058</v>
+        <v>0.767</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>0.892</v>
+        <v>0.712</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="7" t="inlineStr"/>
@@ -3944,39 +3944,39 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>5210</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="E78" s="3" t="n">
-        <v>0.0211</v>
+        <v>0.325</v>
+      </c>
+      <c r="E78" s="8" t="n">
+        <v>-0.0152</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>3285900</v>
+        <v>3361500</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>1.05</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H78" t="n">
-        <v>77.34</v>
-      </c>
-      <c r="I78" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>32.41</v>
+      </c>
+      <c r="I78" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>2.643</v>
+        <v>0.339</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>2.286</v>
+        <v>0.345</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="7" t="inlineStr"/>
@@ -3989,39 +3989,39 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>5210</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>CNERGEN</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="E79" s="10" t="n">
-        <v>0</v>
+        <v>1.24</v>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>0.0248</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>3225000</v>
+        <v>3327800</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>0.53</v>
+        <v>0.99</v>
       </c>
       <c r="H79" t="n">
-        <v>36.06</v>
-      </c>
-      <c r="I79" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>76.11</v>
+      </c>
+      <c r="I79" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.339</v>
+        <v>1.024</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>0.345</v>
+        <v>0.86</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="7" t="inlineStr"/>
@@ -4034,39 +4034,39 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>0272</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>TTVHB</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>0.225</v>
+        <v>0.265</v>
       </c>
       <c r="E80" s="3" t="n">
-        <v>0.0227</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>3146600</v>
+        <v>3309300</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>0.12</v>
+        <v>1.65</v>
       </c>
       <c r="H80" t="n">
-        <v>33.07</v>
-      </c>
-      <c r="I80" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.99</v>
+      </c>
+      <c r="I80" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J80" s="2" t="n">
         <v>0.249</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>0.304</v>
+        <v>0.253</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="7" t="inlineStr"/>
@@ -4079,39 +4079,39 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>0175</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>HHRG</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="E81" s="3" t="n">
-        <v>0.0165</v>
+        <v>0.145</v>
+      </c>
+      <c r="E81" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>3130200</v>
+        <v>3301800</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>0.93</v>
+        <v>0.11</v>
       </c>
       <c r="H81" t="n">
-        <v>75.64</v>
-      </c>
-      <c r="I81" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.09</v>
+      </c>
+      <c r="I81" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J81" s="2" t="n">
-        <v>1.023</v>
+        <v>0.156</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>0.86</v>
+        <v>0.148</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="7" t="inlineStr"/>
@@ -4124,39 +4124,39 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0175</t>
+          <t>0296</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>HHRG</t>
+          <t>HEGROUP</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>0.145</v>
-      </c>
-      <c r="E82" s="10" t="n">
-        <v>0</v>
+        <v>1.13</v>
+      </c>
+      <c r="E82" s="8" t="n">
+        <v>-0.008800000000000001</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>3118000</v>
+        <v>3295900</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>0.11</v>
+        <v>0.68</v>
       </c>
       <c r="H82" t="n">
-        <v>45.09</v>
-      </c>
-      <c r="I82" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>68.90000000000001</v>
+      </c>
+      <c r="I82" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.156</v>
+        <v>1.058</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>0.148</v>
+        <v>0.892</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="7" t="inlineStr"/>
@@ -4169,39 +4169,39 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>0.915</v>
+        <v>2.92</v>
       </c>
       <c r="E83" s="3" t="n">
-        <v>0.0281</v>
+        <v>0.0246</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>3046700</v>
+        <v>3293600</v>
       </c>
       <c r="G83" s="5" t="n">
         <v>1.05</v>
       </c>
       <c r="H83" t="n">
-        <v>48.14</v>
-      </c>
-      <c r="I83" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>77.67</v>
+      </c>
+      <c r="I83" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.912</v>
+        <v>2.644</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>0.964</v>
+        <v>2.286</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="7" t="inlineStr"/>
@@ -4214,39 +4214,39 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="E84" s="3" t="n">
-        <v>0.0314</v>
+        <v>0.22</v>
+      </c>
+      <c r="E84" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>3024300</v>
+        <v>3215400</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>0.45</v>
+        <v>0.12</v>
       </c>
       <c r="H84" t="n">
-        <v>41.93</v>
-      </c>
-      <c r="I84" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>29.99</v>
+      </c>
+      <c r="I84" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>1.671</v>
+        <v>0.249</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>1.787</v>
+        <v>0.304</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="7" t="inlineStr"/>
@@ -4259,28 +4259,28 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0272</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>TTVHB</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>0.265</v>
+        <v>1.63</v>
       </c>
       <c r="E85" s="3" t="n">
-        <v>0.08160000000000001</v>
+        <v>0.0252</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>3006200</v>
+        <v>3085900</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>1.5</v>
+        <v>0.46</v>
       </c>
       <c r="H85" t="n">
-        <v>56.99</v>
+        <v>40.34</v>
       </c>
       <c r="I85" s="9" t="inlineStr">
         <is>
@@ -4288,10 +4288,10 @@
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.249</v>
+        <v>1.67</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>0.253</v>
+        <v>1.787</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="7" t="inlineStr"/>
@@ -4304,28 +4304,28 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0243</t>
+          <t>0338</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>CENGILD</t>
+          <t>KOPI</t>
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="E86" s="8" t="n">
-        <v>-0.1351</v>
+        <v>0.915</v>
+      </c>
+      <c r="E86" s="3" t="n">
+        <v>0.0281</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>3002700</v>
+        <v>3056500</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>13.36</v>
+        <v>1.06</v>
       </c>
       <c r="H86" t="n">
-        <v>18.12</v>
+        <v>48.14</v>
       </c>
       <c r="I86" s="6" t="inlineStr">
         <is>
@@ -4333,10 +4333,10 @@
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.192</v>
+        <v>0.912</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>0.195</v>
+        <v>0.964</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="7" t="inlineStr"/>
@@ -4349,39 +4349,39 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>0243</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>CENGILD</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="E87" s="3" t="n">
-        <v>0.0143</v>
+        <v>0.16</v>
+      </c>
+      <c r="E87" s="8" t="n">
+        <v>-0.1351</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v>2965500</v>
+        <v>3002700</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>0.32</v>
+        <v>13.36</v>
       </c>
       <c r="H87" t="n">
-        <v>62.05</v>
-      </c>
-      <c r="I87" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>18.12</v>
+      </c>
+      <c r="I87" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.671</v>
+        <v>0.192</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>0.607</v>
+        <v>0.195</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="7" t="inlineStr"/>
@@ -4394,28 +4394,28 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0268</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>L&amp;PBHD</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>0.24</v>
+        <v>0.71</v>
       </c>
       <c r="E88" s="3" t="n">
-        <v>0.09089999999999999</v>
+        <v>0.0143</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>2919800</v>
+        <v>2983600</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>1.46</v>
+        <v>0.32</v>
       </c>
       <c r="H88" t="n">
-        <v>77.70999999999999</v>
+        <v>62.05</v>
       </c>
       <c r="I88" s="9" t="inlineStr">
         <is>
@@ -4423,10 +4423,10 @@
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.206</v>
+        <v>0.671</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>0.171</v>
+        <v>0.607</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="7" t="inlineStr"/>
@@ -4439,39 +4439,39 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>0268</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>L&amp;PBHD</t>
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>2.11</v>
+        <v>0.24</v>
       </c>
       <c r="E89" s="3" t="n">
-        <v>0.0048</v>
+        <v>0.09089999999999999</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>2760800</v>
+        <v>2920200</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>0.14</v>
+        <v>1.46</v>
       </c>
       <c r="H89" t="n">
-        <v>52.16</v>
-      </c>
-      <c r="I89" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>77.70999999999999</v>
+      </c>
+      <c r="I89" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>2.099</v>
+        <v>0.206</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>2.081</v>
+        <v>0.171</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="7" t="inlineStr"/>
@@ -4484,39 +4484,39 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>ALPHA</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>0.275</v>
+        <v>2.1</v>
       </c>
       <c r="E90" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>2752300</v>
+        <v>2878000</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>1.15</v>
+        <v>0.15</v>
       </c>
       <c r="H90" t="n">
-        <v>63.87</v>
-      </c>
-      <c r="I90" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.69</v>
+      </c>
+      <c r="I90" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.259</v>
+        <v>2.098</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>0.257</v>
+        <v>2.08</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="7" t="inlineStr"/>
@@ -4529,28 +4529,28 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>ALPHA</t>
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>0.985</v>
-      </c>
-      <c r="E91" s="8" t="n">
-        <v>-0.0101</v>
+        <v>0.28</v>
+      </c>
+      <c r="E91" s="3" t="n">
+        <v>0.0182</v>
       </c>
       <c r="F91" s="4" t="n">
-        <v>2752300</v>
+        <v>2852300</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>0.85</v>
+        <v>1.19</v>
       </c>
       <c r="H91" t="n">
-        <v>84.86</v>
+        <v>66.27</v>
       </c>
       <c r="I91" s="9" t="inlineStr">
         <is>
@@ -4558,10 +4558,10 @@
         </is>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.657</v>
+        <v>0.26</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>0.479</v>
+        <v>0.257</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="7" t="inlineStr"/>
@@ -4574,28 +4574,28 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="E92" s="3" t="n">
-        <v>0.0128</v>
+        <v>0.99</v>
+      </c>
+      <c r="E92" s="8" t="n">
+        <v>-0.005</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v>2745500</v>
+        <v>2772500</v>
       </c>
       <c r="G92" s="5" t="n">
-        <v>0.39</v>
+        <v>0.86</v>
       </c>
       <c r="H92" t="n">
-        <v>63.79</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="I92" s="9" t="inlineStr">
         <is>
@@ -4603,10 +4603,10 @@
         </is>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.735</v>
+        <v>0.657</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>0.652</v>
+        <v>0.479</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="7" t="inlineStr"/>
@@ -4619,28 +4619,28 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D93" s="2" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="E93" s="8" t="n">
-        <v>-0.0187</v>
+        <v>0.79</v>
+      </c>
+      <c r="E93" s="3" t="n">
+        <v>0.0128</v>
       </c>
       <c r="F93" s="4" t="n">
-        <v>2642700</v>
+        <v>2766500</v>
       </c>
       <c r="G93" s="5" t="n">
-        <v>0.18</v>
+        <v>0.39</v>
       </c>
       <c r="H93" t="n">
-        <v>47.46</v>
+        <v>63.79</v>
       </c>
       <c r="I93" s="9" t="inlineStr">
         <is>
@@ -4648,10 +4648,10 @@
         </is>
       </c>
       <c r="J93" s="2" t="n">
-        <v>1.07</v>
+        <v>0.735</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>1.037</v>
+        <v>0.652</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="7" t="inlineStr"/>
@@ -4673,19 +4673,19 @@
         </is>
       </c>
       <c r="D94" s="2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E94" s="3" t="n">
-        <v>0.0345</v>
+        <v>0.29</v>
+      </c>
+      <c r="E94" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>2590500</v>
+        <v>2747100</v>
       </c>
       <c r="G94" s="5" t="n">
-        <v>0.21</v>
+        <v>0.23</v>
       </c>
       <c r="H94" t="n">
-        <v>54.14</v>
+        <v>50.7</v>
       </c>
       <c r="I94" s="9" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.292</v>
+        <v>0.291</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0.281</v>
@@ -4709,28 +4709,28 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D95" s="2" t="n">
-        <v>0.8</v>
+        <v>1.05</v>
       </c>
       <c r="E95" s="8" t="n">
-        <v>-0.0062</v>
+        <v>-0.0187</v>
       </c>
       <c r="F95" s="4" t="n">
-        <v>2508600</v>
+        <v>2711100</v>
       </c>
       <c r="G95" s="5" t="n">
-        <v>0.41</v>
+        <v>0.19</v>
       </c>
       <c r="H95" t="n">
-        <v>65.37</v>
+        <v>47.46</v>
       </c>
       <c r="I95" s="9" t="inlineStr">
         <is>
@@ -4738,10 +4738,10 @@
         </is>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.785</v>
+        <v>1.07</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>0.764</v>
+        <v>1.037</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="7" t="inlineStr"/>
@@ -4754,28 +4754,28 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0388</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>SEMICO</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D96" s="2" t="n">
-        <v>0.615</v>
-      </c>
-      <c r="E96" s="10" t="n">
-        <v>0</v>
+        <v>0.8</v>
+      </c>
+      <c r="E96" s="8" t="n">
+        <v>-0.0062</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>2483900</v>
+        <v>2508600</v>
       </c>
       <c r="G96" s="5" t="n">
-        <v>0.85</v>
+        <v>0.41</v>
       </c>
       <c r="H96" t="n">
-        <v>59.01</v>
+        <v>65.37</v>
       </c>
       <c r="I96" s="9" t="inlineStr">
         <is>
@@ -4783,10 +4783,10 @@
         </is>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.612</v>
+        <v>0.785</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>0.598</v>
+        <v>0.764</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="7" t="inlineStr"/>
@@ -4799,28 +4799,28 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>0045</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>SSB8</t>
         </is>
       </c>
       <c r="D97" s="2" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E97" s="3" t="n">
-        <v>0.0172</v>
+        <v>0.665</v>
+      </c>
+      <c r="E97" s="8" t="n">
+        <v>-0.0075</v>
       </c>
       <c r="F97" s="4" t="n">
-        <v>2472800</v>
+        <v>2488400</v>
       </c>
       <c r="G97" s="5" t="n">
-        <v>0.28</v>
+        <v>0.6</v>
       </c>
       <c r="H97" t="n">
-        <v>57.36</v>
+        <v>62</v>
       </c>
       <c r="I97" s="9" t="inlineStr">
         <is>
@@ -4828,10 +4828,10 @@
         </is>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.278</v>
+        <v>0.637</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>0.303</v>
+        <v>0.601</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="7" t="inlineStr"/>
@@ -4844,28 +4844,28 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>0045</t>
+          <t>0388</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>SSB8</t>
+          <t>SEMICO</t>
         </is>
       </c>
       <c r="D98" s="2" t="n">
-        <v>0.665</v>
-      </c>
-      <c r="E98" s="8" t="n">
-        <v>-0.0075</v>
+        <v>0.615</v>
+      </c>
+      <c r="E98" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F98" s="4" t="n">
-        <v>2460400</v>
+        <v>2483900</v>
       </c>
       <c r="G98" s="5" t="n">
-        <v>0.59</v>
+        <v>0.85</v>
       </c>
       <c r="H98" t="n">
-        <v>62</v>
+        <v>59.01</v>
       </c>
       <c r="I98" s="9" t="inlineStr">
         <is>
@@ -4873,10 +4873,10 @@
         </is>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.637</v>
+        <v>0.612</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>0.601</v>
+        <v>0.598</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="7" t="inlineStr"/>
@@ -4889,39 +4889,39 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D99" s="2" t="n">
-        <v>0.535</v>
+        <v>0.295</v>
       </c>
       <c r="E99" s="3" t="n">
-        <v>0.009399999999999999</v>
+        <v>0.0172</v>
       </c>
       <c r="F99" s="4" t="n">
-        <v>2440000</v>
+        <v>2478100</v>
       </c>
       <c r="G99" s="5" t="n">
-        <v>0.32</v>
+        <v>0.28</v>
       </c>
       <c r="H99" t="n">
-        <v>55.09</v>
-      </c>
-      <c r="I99" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.36</v>
+      </c>
+      <c r="I99" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.522</v>
+        <v>0.278</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>0.531</v>
+        <v>0.303</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="7" t="inlineStr"/>
@@ -4934,39 +4934,39 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>6947</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>CDB</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D100" s="2" t="n">
-        <v>2.52</v>
+        <v>0.535</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0.0202</v>
+        <v>0.009399999999999999</v>
       </c>
       <c r="F100" s="4" t="n">
-        <v>2396700</v>
+        <v>2450000</v>
       </c>
       <c r="G100" s="5" t="n">
-        <v>0.77</v>
+        <v>0.32</v>
       </c>
       <c r="H100" t="n">
-        <v>37.33</v>
-      </c>
-      <c r="I100" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>55.09</v>
+      </c>
+      <c r="I100" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J100" s="2" t="n">
-        <v>2.583</v>
+        <v>0.522</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>2.731</v>
+        <v>0.531</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="7" t="inlineStr"/>
@@ -4979,39 +4979,39 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>6633</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>LHI</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D101" s="2" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="E101" s="10" t="n">
-        <v>0</v>
+        <v>4.23</v>
+      </c>
+      <c r="E101" s="8" t="n">
+        <v>-0.006999999999999999</v>
       </c>
       <c r="F101" s="4" t="n">
-        <v>2384400</v>
+        <v>2425700</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>1.43</v>
+        <v>0.31</v>
       </c>
       <c r="H101" t="n">
-        <v>47.32</v>
-      </c>
-      <c r="I101" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.38</v>
+      </c>
+      <c r="I101" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.735</v>
+        <v>4.369</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>0.749</v>
+        <v>4.464</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="7" t="inlineStr"/>
@@ -5024,39 +5024,39 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>6633</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>LHI</t>
         </is>
       </c>
       <c r="D102" s="2" t="n">
-        <v>4.21</v>
+        <v>0.725</v>
       </c>
       <c r="E102" s="8" t="n">
-        <v>-0.0117</v>
+        <v>-0.0068</v>
       </c>
       <c r="F102" s="4" t="n">
-        <v>2355600</v>
+        <v>2398500</v>
       </c>
       <c r="G102" s="5" t="n">
-        <v>0.3</v>
+        <v>1.43</v>
       </c>
       <c r="H102" t="n">
-        <v>42.76</v>
-      </c>
-      <c r="I102" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>45.69</v>
+      </c>
+      <c r="I102" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J102" s="2" t="n">
-        <v>4.367</v>
+        <v>0.734</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>4.463</v>
+        <v>0.748</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="7" t="inlineStr"/>
@@ -5069,28 +5069,28 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0056</t>
+          <t>6947</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>NCT</t>
+          <t>CDB</t>
         </is>
       </c>
       <c r="D103" s="2" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="E103" s="10" t="n">
-        <v>0</v>
+        <v>2.51</v>
+      </c>
+      <c r="E103" s="3" t="n">
+        <v>0.0162</v>
       </c>
       <c r="F103" s="4" t="n">
-        <v>2355400</v>
+        <v>2398200</v>
       </c>
       <c r="G103" s="5" t="n">
-        <v>1.08</v>
+        <v>0.77</v>
       </c>
       <c r="H103" t="n">
-        <v>54.19</v>
+        <v>35.71</v>
       </c>
       <c r="I103" s="9" t="inlineStr">
         <is>
@@ -5098,10 +5098,10 @@
         </is>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.5639999999999999</v>
+        <v>2.582</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>0.5620000000000001</v>
+        <v>2.731</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="7" t="inlineStr"/>
@@ -5114,28 +5114,28 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>0056</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>NCT</t>
         </is>
       </c>
       <c r="D104" s="2" t="n">
-        <v>0.355</v>
-      </c>
-      <c r="E104" s="3" t="n">
-        <v>0.0143</v>
+        <v>0.57</v>
+      </c>
+      <c r="E104" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F104" s="4" t="n">
-        <v>2306800</v>
+        <v>2355400</v>
       </c>
       <c r="G104" s="5" t="n">
-        <v>0.3</v>
+        <v>1.08</v>
       </c>
       <c r="H104" t="n">
-        <v>58.58</v>
+        <v>54.19</v>
       </c>
       <c r="I104" s="9" t="inlineStr">
         <is>
@@ -5143,10 +5143,10 @@
         </is>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.344</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>0.324</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="7" t="inlineStr"/>
@@ -5159,39 +5159,39 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D105" s="2" t="n">
-        <v>7.19</v>
+        <v>0.355</v>
       </c>
       <c r="E105" s="3" t="n">
-        <v>0.0098</v>
+        <v>0.0143</v>
       </c>
       <c r="F105" s="4" t="n">
-        <v>2300000</v>
+        <v>2352400</v>
       </c>
       <c r="G105" s="5" t="n">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="H105" t="n">
-        <v>34.49</v>
-      </c>
-      <c r="I105" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.58</v>
+      </c>
+      <c r="I105" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J105" s="2" t="n">
-        <v>7.408</v>
+        <v>0.344</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>7.724</v>
+        <v>0.324</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="7" t="inlineStr"/>
@@ -5204,39 +5204,39 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>0359</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>HKB</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D106" s="2" t="n">
-        <v>0.8149999999999999</v>
+        <v>2.5</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>0.0124</v>
+        <v>0.008100000000000001</v>
       </c>
       <c r="F106" s="4" t="n">
-        <v>2224000</v>
+        <v>2340100</v>
       </c>
       <c r="G106" s="5" t="n">
-        <v>1</v>
+        <v>0.17</v>
       </c>
       <c r="H106" t="n">
-        <v>81.81</v>
-      </c>
-      <c r="I106" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>58.18</v>
+      </c>
+      <c r="I106" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.679</v>
+        <v>2.463</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>0.622</v>
+        <v>2.344</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="7" t="inlineStr"/>
@@ -5249,39 +5249,39 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>CPETECH</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D107" s="2" t="n">
-        <v>1.36</v>
+        <v>7.21</v>
       </c>
       <c r="E107" s="3" t="n">
-        <v>0.0226</v>
+        <v>0.0126</v>
       </c>
       <c r="F107" s="4" t="n">
-        <v>2214300</v>
+        <v>2331400</v>
       </c>
       <c r="G107" s="5" t="n">
-        <v>0.58</v>
+        <v>0.3</v>
       </c>
       <c r="H107" t="n">
-        <v>58.46</v>
-      </c>
-      <c r="I107" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.75</v>
+      </c>
+      <c r="I107" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J107" s="2" t="n">
-        <v>1.295</v>
+        <v>7.41</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>1.194</v>
+        <v>7.724</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="7" t="inlineStr"/>
@@ -5294,39 +5294,39 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>0359</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>HKB</t>
         </is>
       </c>
       <c r="D108" s="2" t="n">
-        <v>2.5</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="E108" s="3" t="n">
-        <v>0.008100000000000001</v>
+        <v>0.0124</v>
       </c>
       <c r="F108" s="4" t="n">
-        <v>2210000</v>
+        <v>2285000</v>
       </c>
       <c r="G108" s="5" t="n">
-        <v>0.16</v>
+        <v>1.02</v>
       </c>
       <c r="H108" t="n">
-        <v>58.18</v>
-      </c>
-      <c r="I108" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>81.81</v>
+      </c>
+      <c r="I108" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J108" s="2" t="n">
-        <v>2.463</v>
+        <v>0.679</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>2.344</v>
+        <v>0.622</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="7" t="inlineStr"/>
@@ -5339,39 +5339,39 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>0267</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>CMSB</t>
+          <t>ECA</t>
         </is>
       </c>
       <c r="D109" s="2" t="n">
-        <v>0.91</v>
+        <v>0.38</v>
       </c>
       <c r="E109" s="3" t="n">
-        <v>0.005500000000000001</v>
+        <v>0.0411</v>
       </c>
       <c r="F109" s="4" t="n">
-        <v>2198300</v>
+        <v>2223100</v>
       </c>
       <c r="G109" s="5" t="n">
-        <v>1.07</v>
+        <v>0.66</v>
       </c>
       <c r="H109" t="n">
-        <v>28.89</v>
-      </c>
-      <c r="I109" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.04</v>
+      </c>
+      <c r="I109" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.959</v>
+        <v>0.366</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>0.993</v>
+        <v>0.374</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="7" t="inlineStr"/>
@@ -5384,28 +5384,28 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>0267</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>ECA</t>
+          <t>CPETECH</t>
         </is>
       </c>
       <c r="D110" s="2" t="n">
-        <v>0.38</v>
+        <v>1.36</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>0.0411</v>
+        <v>0.0226</v>
       </c>
       <c r="F110" s="4" t="n">
-        <v>2173100</v>
+        <v>2217300</v>
       </c>
       <c r="G110" s="5" t="n">
-        <v>0.65</v>
+        <v>0.59</v>
       </c>
       <c r="H110" t="n">
-        <v>53.04</v>
+        <v>58.46</v>
       </c>
       <c r="I110" s="9" t="inlineStr">
         <is>
@@ -5413,10 +5413,10 @@
         </is>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.366</v>
+        <v>1.295</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>0.374</v>
+        <v>1.194</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="7" t="inlineStr"/>
@@ -5429,28 +5429,28 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>4863</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>TM</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D111" s="2" t="n">
-        <v>7.88</v>
+        <v>4.24</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0.0013</v>
+        <v>0.0192</v>
       </c>
       <c r="F111" s="4" t="n">
-        <v>2162800</v>
+        <v>2212800</v>
       </c>
       <c r="G111" s="5" t="n">
-        <v>0.72</v>
+        <v>0.26</v>
       </c>
       <c r="H111" t="n">
-        <v>50.14</v>
+        <v>64.51000000000001</v>
       </c>
       <c r="I111" s="9" t="inlineStr">
         <is>
@@ -5458,10 +5458,10 @@
         </is>
       </c>
       <c r="J111" s="2" t="n">
-        <v>7.891</v>
+        <v>3.965</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>7.849</v>
+        <v>3.443</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="7" t="inlineStr"/>
@@ -5474,28 +5474,28 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>0239</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>ECOMATE</t>
+          <t>CMSB</t>
         </is>
       </c>
       <c r="D112" s="2" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E112" s="10" t="n">
-        <v>0</v>
+        <v>0.91</v>
+      </c>
+      <c r="E112" s="3" t="n">
+        <v>0.005500000000000001</v>
       </c>
       <c r="F112" s="4" t="n">
-        <v>2152900</v>
+        <v>2198300</v>
       </c>
       <c r="G112" s="5" t="n">
-        <v>0.67</v>
+        <v>1.07</v>
       </c>
       <c r="H112" t="n">
-        <v>52.86</v>
+        <v>28.89</v>
       </c>
       <c r="I112" s="6" t="inlineStr">
         <is>
@@ -5503,10 +5503,10 @@
         </is>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.864</v>
+        <v>0.959</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>0.858</v>
+        <v>0.993</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="7" t="inlineStr"/>
@@ -5519,28 +5519,28 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>4863</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>TM</t>
         </is>
       </c>
       <c r="D113" s="2" t="n">
-        <v>4.25</v>
+        <v>7.88</v>
       </c>
       <c r="E113" s="3" t="n">
-        <v>0.0216</v>
+        <v>0.0013</v>
       </c>
       <c r="F113" s="4" t="n">
-        <v>2136700</v>
+        <v>2163500</v>
       </c>
       <c r="G113" s="5" t="n">
-        <v>0.25</v>
+        <v>0.72</v>
       </c>
       <c r="H113" t="n">
-        <v>64.75</v>
+        <v>50.14</v>
       </c>
       <c r="I113" s="9" t="inlineStr">
         <is>
@@ -5548,10 +5548,10 @@
         </is>
       </c>
       <c r="J113" s="2" t="n">
-        <v>3.966</v>
+        <v>7.891</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>3.443</v>
+        <v>7.849</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="7" t="inlineStr"/>
@@ -5564,39 +5564,39 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>0239</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>ATECH</t>
+          <t>ECOMATE</t>
         </is>
       </c>
       <c r="D114" s="2" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E114" s="3" t="n">
-        <v>0.0127</v>
+        <v>0.865</v>
+      </c>
+      <c r="E114" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F114" s="4" t="n">
-        <v>2096800</v>
+        <v>2152900</v>
       </c>
       <c r="G114" s="5" t="n">
-        <v>1.15</v>
+        <v>0.67</v>
       </c>
       <c r="H114" t="n">
-        <v>58.78</v>
-      </c>
-      <c r="I114" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.86</v>
+      </c>
+      <c r="I114" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.77</v>
+        <v>0.864</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>0.761</v>
+        <v>0.858</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="7" t="inlineStr"/>
@@ -5609,28 +5609,28 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>5302</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>ATECH</t>
         </is>
       </c>
       <c r="D115" s="2" t="n">
-        <v>0.545</v>
-      </c>
-      <c r="E115" s="10" t="n">
-        <v>0</v>
+        <v>0.8</v>
+      </c>
+      <c r="E115" s="3" t="n">
+        <v>0.0127</v>
       </c>
       <c r="F115" s="4" t="n">
-        <v>2047300</v>
+        <v>2109200</v>
       </c>
       <c r="G115" s="5" t="n">
-        <v>0.49</v>
+        <v>1.16</v>
       </c>
       <c r="H115" t="n">
-        <v>71.06999999999999</v>
+        <v>58.78</v>
       </c>
       <c r="I115" s="9" t="inlineStr">
         <is>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.477</v>
+        <v>0.77</v>
       </c>
       <c r="K115" s="2" t="n">
-        <v>0.451</v>
+        <v>0.761</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="7" t="inlineStr"/>
@@ -5654,28 +5654,28 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>0249</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>LGMS</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D116" s="2" t="n">
-        <v>0.5649999999999999</v>
-      </c>
-      <c r="E116" s="8" t="n">
-        <v>-0.008800000000000001</v>
+        <v>0.545</v>
+      </c>
+      <c r="E116" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F116" s="4" t="n">
-        <v>2006900</v>
+        <v>2073500</v>
       </c>
       <c r="G116" s="5" t="n">
-        <v>2.23</v>
+        <v>0.5</v>
       </c>
       <c r="H116" t="n">
-        <v>69.2</v>
+        <v>71.06999999999999</v>
       </c>
       <c r="I116" s="9" t="inlineStr">
         <is>
@@ -5683,10 +5683,10 @@
         </is>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.523</v>
+        <v>0.477</v>
       </c>
       <c r="K116" s="2" t="n">
-        <v>0.504</v>
+        <v>0.451</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="7" t="inlineStr"/>
@@ -5708,19 +5708,19 @@
         </is>
       </c>
       <c r="D117" s="2" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E117" s="8" t="n">
-        <v>-0.0244</v>
+        <v>0.205</v>
+      </c>
+      <c r="E117" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F117" s="4" t="n">
-        <v>1992100</v>
+        <v>2012100</v>
       </c>
       <c r="G117" s="5" t="n">
         <v>0.43</v>
       </c>
       <c r="H117" t="n">
-        <v>42.79</v>
+        <v>47.55</v>
       </c>
       <c r="I117" s="6" t="inlineStr">
         <is>
@@ -5744,39 +5744,39 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>5306</t>
+          <t>0249</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>FFB</t>
+          <t>LGMS</t>
         </is>
       </c>
       <c r="D118" s="2" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="E118" s="3" t="n">
-        <v>0.0286</v>
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="E118" s="8" t="n">
+        <v>-0.008800000000000001</v>
       </c>
       <c r="F118" s="4" t="n">
-        <v>1956100</v>
+        <v>2006900</v>
       </c>
       <c r="G118" s="5" t="n">
-        <v>0.67</v>
+        <v>2.23</v>
       </c>
       <c r="H118" t="n">
-        <v>32.69</v>
-      </c>
-      <c r="I118" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>69.2</v>
+      </c>
+      <c r="I118" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J118" s="2" t="n">
-        <v>1.88</v>
+        <v>0.523</v>
       </c>
       <c r="K118" s="2" t="n">
-        <v>2.017</v>
+        <v>0.504</v>
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" s="7" t="inlineStr"/>
@@ -5789,28 +5789,28 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>5306</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>AMBANK</t>
+          <t>FFB</t>
         </is>
       </c>
       <c r="D119" s="2" t="n">
-        <v>6.09</v>
-      </c>
-      <c r="E119" s="8" t="n">
-        <v>-0.0016</v>
+        <v>1.81</v>
+      </c>
+      <c r="E119" s="3" t="n">
+        <v>0.0343</v>
       </c>
       <c r="F119" s="4" t="n">
-        <v>1941400</v>
+        <v>1995600</v>
       </c>
       <c r="G119" s="5" t="n">
-        <v>0.42</v>
+        <v>0.68</v>
       </c>
       <c r="H119" t="n">
-        <v>22.87</v>
+        <v>34.6</v>
       </c>
       <c r="I119" s="6" t="inlineStr">
         <is>
@@ -5818,10 +5818,10 @@
         </is>
       </c>
       <c r="J119" s="2" t="n">
-        <v>6.473</v>
+        <v>1.881</v>
       </c>
       <c r="K119" s="2" t="n">
-        <v>6.826</v>
+        <v>2.018</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="7" t="inlineStr"/>
@@ -5834,28 +5834,28 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>5322</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>FEYTECH</t>
+          <t>AMBANK</t>
         </is>
       </c>
       <c r="D120" s="2" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="E120" s="8" t="n">
-        <v>-0.0213</v>
+        <v>6.1</v>
+      </c>
+      <c r="E120" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F120" s="4" t="n">
-        <v>1917500</v>
+        <v>1962600</v>
       </c>
       <c r="G120" s="5" t="n">
-        <v>2.76</v>
+        <v>0.42</v>
       </c>
       <c r="H120" t="n">
-        <v>48.43</v>
+        <v>23.12</v>
       </c>
       <c r="I120" s="6" t="inlineStr">
         <is>
@@ -5863,10 +5863,10 @@
         </is>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.232</v>
+        <v>6.474</v>
       </c>
       <c r="K120" s="2" t="n">
-        <v>0.234</v>
+        <v>6.826</v>
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="7" t="inlineStr"/>
@@ -5894,10 +5894,10 @@
         <v>0</v>
       </c>
       <c r="F121" s="4" t="n">
-        <v>1884600</v>
+        <v>1933700</v>
       </c>
       <c r="G121" s="5" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="H121" t="n">
         <v>53.94</v>
@@ -5924,28 +5924,28 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>5337</t>
+          <t>5322</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>ECOSHOP</t>
+          <t>FEYTECH</t>
         </is>
       </c>
       <c r="D122" s="2" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="E122" s="3" t="n">
-        <v>0.021</v>
+        <v>0.23</v>
+      </c>
+      <c r="E122" s="8" t="n">
+        <v>-0.0213</v>
       </c>
       <c r="F122" s="4" t="n">
-        <v>1883400</v>
+        <v>1917500</v>
       </c>
       <c r="G122" s="5" t="n">
-        <v>0.41</v>
+        <v>2.76</v>
       </c>
       <c r="H122" t="n">
-        <v>49.32</v>
+        <v>48.43</v>
       </c>
       <c r="I122" s="6" t="inlineStr">
         <is>
@@ -5953,10 +5953,10 @@
         </is>
       </c>
       <c r="J122" s="2" t="n">
-        <v>1.461</v>
+        <v>0.232</v>
       </c>
       <c r="K122" s="2" t="n">
-        <v>1.469</v>
+        <v>0.234</v>
       </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="7" t="inlineStr"/>
@@ -5969,39 +5969,39 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>0328</t>
+          <t>5337</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>3REN</t>
+          <t>ECOSHOP</t>
         </is>
       </c>
       <c r="D123" s="2" t="n">
-        <v>0.4</v>
+        <v>1.46</v>
       </c>
       <c r="E123" s="3" t="n">
-        <v>0.039</v>
+        <v>0.021</v>
       </c>
       <c r="F123" s="4" t="n">
-        <v>1837400</v>
+        <v>1899300</v>
       </c>
       <c r="G123" s="5" t="n">
-        <v>0.93</v>
+        <v>0.41</v>
       </c>
       <c r="H123" t="n">
-        <v>56.15</v>
-      </c>
-      <c r="I123" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.32</v>
+      </c>
+      <c r="I123" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J123" s="2" t="n">
-        <v>0.386</v>
+        <v>1.461</v>
       </c>
       <c r="K123" s="2" t="n">
-        <v>0.391</v>
+        <v>1.469</v>
       </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" s="7" t="inlineStr"/>
@@ -6014,28 +6014,28 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>0277</t>
+          <t>0328</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>CLOUDPT</t>
+          <t>3REN</t>
         </is>
       </c>
       <c r="D124" s="2" t="n">
-        <v>0.52</v>
+        <v>0.4</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>0.0196</v>
+        <v>0.039</v>
       </c>
       <c r="F124" s="4" t="n">
-        <v>1774500</v>
+        <v>1837400</v>
       </c>
       <c r="G124" s="5" t="n">
-        <v>1.08</v>
+        <v>0.93</v>
       </c>
       <c r="H124" t="n">
-        <v>64.29000000000001</v>
+        <v>56.15</v>
       </c>
       <c r="I124" s="9" t="inlineStr">
         <is>
@@ -6043,10 +6043,10 @@
         </is>
       </c>
       <c r="J124" s="2" t="n">
-        <v>0.49</v>
+        <v>0.386</v>
       </c>
       <c r="K124" s="2" t="n">
-        <v>0.479</v>
+        <v>0.391</v>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" s="7" t="inlineStr"/>
@@ -6059,28 +6059,28 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>0373</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>VERDANT</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D125" s="2" t="n">
-        <v>0.28</v>
+        <v>1.86</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>0.0182</v>
+        <v>0.0109</v>
       </c>
       <c r="F125" s="4" t="n">
-        <v>1773500</v>
+        <v>1804500</v>
       </c>
       <c r="G125" s="5" t="n">
-        <v>0.4</v>
+        <v>0.43</v>
       </c>
       <c r="H125" t="n">
-        <v>69.36</v>
+        <v>40.52</v>
       </c>
       <c r="I125" s="6" t="inlineStr">
         <is>
@@ -6088,10 +6088,10 @@
         </is>
       </c>
       <c r="J125" s="2" t="n">
-        <v>0.252</v>
+        <v>1.897</v>
       </c>
       <c r="K125" s="2" t="n">
-        <v>0.22</v>
+        <v>2.026</v>
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" s="7" t="inlineStr"/>
@@ -6104,39 +6104,39 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>0277</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>CLOUDPT</t>
         </is>
       </c>
       <c r="D126" s="2" t="n">
-        <v>1.85</v>
+        <v>0.52</v>
       </c>
       <c r="E126" s="3" t="n">
-        <v>0.0054</v>
+        <v>0.0196</v>
       </c>
       <c r="F126" s="4" t="n">
-        <v>1727700</v>
+        <v>1787200</v>
       </c>
       <c r="G126" s="5" t="n">
-        <v>0.41</v>
+        <v>1.09</v>
       </c>
       <c r="H126" t="n">
-        <v>38.83</v>
-      </c>
-      <c r="I126" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.29000000000001</v>
+      </c>
+      <c r="I126" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J126" s="2" t="n">
-        <v>1.896</v>
+        <v>0.49</v>
       </c>
       <c r="K126" s="2" t="n">
-        <v>2.026</v>
+        <v>0.479</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="7" t="inlineStr"/>
@@ -6149,39 +6149,39 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>5331</t>
+          <t>0373</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>PGLOBAL</t>
+          <t>VERDANT</t>
         </is>
       </c>
       <c r="D127" s="2" t="n">
-        <v>0.585</v>
-      </c>
-      <c r="E127" s="3" t="n">
-        <v>0.0446</v>
+        <v>0.275</v>
+      </c>
+      <c r="E127" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F127" s="4" t="n">
-        <v>1703300</v>
+        <v>1783500</v>
       </c>
       <c r="G127" s="5" t="n">
-        <v>3.67</v>
+        <v>0.41</v>
       </c>
       <c r="H127" t="n">
-        <v>72.14</v>
-      </c>
-      <c r="I127" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>67.73999999999999</v>
+      </c>
+      <c r="I127" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J127" s="2" t="n">
-        <v>0.54</v>
+        <v>0.251</v>
       </c>
       <c r="K127" s="2" t="n">
-        <v>0.511</v>
+        <v>0.22</v>
       </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" s="7" t="inlineStr"/>
@@ -6194,28 +6194,28 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>5331</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>PGLOBAL</t>
         </is>
       </c>
       <c r="D128" s="2" t="n">
-        <v>0.6</v>
+        <v>0.585</v>
       </c>
       <c r="E128" s="3" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.0446</v>
       </c>
       <c r="F128" s="4" t="n">
-        <v>1694500</v>
+        <v>1703300</v>
       </c>
       <c r="G128" s="5" t="n">
-        <v>0.3</v>
+        <v>3.67</v>
       </c>
       <c r="H128" t="n">
-        <v>69.58</v>
+        <v>72.14</v>
       </c>
       <c r="I128" s="9" t="inlineStr">
         <is>
@@ -6223,10 +6223,10 @@
         </is>
       </c>
       <c r="J128" s="2" t="n">
-        <v>0.549</v>
+        <v>0.54</v>
       </c>
       <c r="K128" s="2" t="n">
-        <v>0.493</v>
+        <v>0.511</v>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" s="7" t="inlineStr"/>
@@ -6239,28 +6239,28 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>0090</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>ELSOFT</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D129" s="2" t="n">
-        <v>0.35</v>
+        <v>0.6</v>
       </c>
       <c r="E129" s="3" t="n">
-        <v>0.09369999999999999</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="F129" s="4" t="n">
-        <v>1630400</v>
+        <v>1700200</v>
       </c>
       <c r="G129" s="5" t="n">
-        <v>2.39</v>
+        <v>0.3</v>
       </c>
       <c r="H129" t="n">
-        <v>76.87</v>
+        <v>69.58</v>
       </c>
       <c r="I129" s="9" t="inlineStr">
         <is>
@@ -6268,10 +6268,10 @@
         </is>
       </c>
       <c r="J129" s="2" t="n">
-        <v>0.284</v>
+        <v>0.549</v>
       </c>
       <c r="K129" s="2" t="n">
-        <v>0.272</v>
+        <v>0.493</v>
       </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" s="7" t="inlineStr"/>
@@ -6293,19 +6293,19 @@
         </is>
       </c>
       <c r="D130" s="2" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="E130" s="3" t="n">
-        <v>0.0112</v>
+        <v>0.445</v>
+      </c>
+      <c r="E130" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F130" s="4" t="n">
-        <v>1628600</v>
+        <v>1652400</v>
       </c>
       <c r="G130" s="5" t="n">
         <v>0.46</v>
       </c>
       <c r="H130" t="n">
-        <v>49.83</v>
+        <v>47.76</v>
       </c>
       <c r="I130" s="6" t="inlineStr">
         <is>
@@ -6329,39 +6329,39 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>0369</t>
+          <t>0090</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>JSSOLAR</t>
+          <t>ELSOFT</t>
         </is>
       </c>
       <c r="D131" s="2" t="n">
-        <v>0.255</v>
+        <v>0.35</v>
       </c>
       <c r="E131" s="3" t="n">
-        <v>0.0851</v>
+        <v>0.09369999999999999</v>
       </c>
       <c r="F131" s="4" t="n">
-        <v>1602100</v>
+        <v>1630400</v>
       </c>
       <c r="G131" s="5" t="n">
-        <v>1.01</v>
+        <v>2.39</v>
       </c>
       <c r="H131" t="n">
-        <v>62.54</v>
-      </c>
-      <c r="I131" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>76.87</v>
+      </c>
+      <c r="I131" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J131" s="2" t="n">
-        <v>0.233</v>
+        <v>0.284</v>
       </c>
       <c r="K131" s="2" t="n">
-        <v>0.208</v>
+        <v>0.272</v>
       </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" s="7" t="inlineStr"/>
@@ -6374,28 +6374,28 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>0369</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>JSSOLAR</t>
         </is>
       </c>
       <c r="D132" s="2" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="E132" s="8" t="n">
-        <v>-0.0108</v>
+        <v>0.255</v>
+      </c>
+      <c r="E132" s="3" t="n">
+        <v>0.0851</v>
       </c>
       <c r="F132" s="4" t="n">
-        <v>1570500</v>
+        <v>1607100</v>
       </c>
       <c r="G132" s="5" t="n">
-        <v>0.3</v>
+        <v>1.01</v>
       </c>
       <c r="H132" t="n">
-        <v>58.88</v>
+        <v>62.54</v>
       </c>
       <c r="I132" s="6" t="inlineStr">
         <is>
@@ -6403,10 +6403,10 @@
         </is>
       </c>
       <c r="J132" s="2" t="n">
-        <v>0.907</v>
+        <v>0.233</v>
       </c>
       <c r="K132" s="2" t="n">
-        <v>0.863</v>
+        <v>0.208</v>
       </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" s="7" t="inlineStr"/>
@@ -6434,7 +6434,7 @@
         <v>-0.0179</v>
       </c>
       <c r="F133" s="4" t="n">
-        <v>1551100</v>
+        <v>1588100</v>
       </c>
       <c r="G133" s="5" t="n">
         <v>0.24</v>
@@ -6464,39 +6464,39 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D134" s="2" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="E134" s="10" t="n">
-        <v>0</v>
+        <v>0.92</v>
+      </c>
+      <c r="E134" s="8" t="n">
+        <v>-0.0108</v>
       </c>
       <c r="F134" s="4" t="n">
-        <v>1503600</v>
+        <v>1576000</v>
       </c>
       <c r="G134" s="5" t="n">
-        <v>0.16</v>
+        <v>0.3</v>
       </c>
       <c r="H134" t="n">
-        <v>56.14</v>
-      </c>
-      <c r="I134" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>58.88</v>
+      </c>
+      <c r="I134" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J134" s="2" t="n">
-        <v>2.775</v>
+        <v>0.907</v>
       </c>
       <c r="K134" s="2" t="n">
-        <v>2.599</v>
+        <v>0.863</v>
       </c>
       <c r="L134" t="inlineStr"/>
       <c r="M134" s="7" t="inlineStr"/>
@@ -6509,28 +6509,28 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D135" s="2" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="E135" s="8" t="n">
-        <v>-0.0274</v>
+        <v>0.495</v>
+      </c>
+      <c r="E135" s="3" t="n">
+        <v>0.0206</v>
       </c>
       <c r="F135" s="4" t="n">
-        <v>1495300</v>
+        <v>1563400</v>
       </c>
       <c r="G135" s="5" t="n">
-        <v>0.32</v>
+        <v>0.21</v>
       </c>
       <c r="H135" t="n">
-        <v>45.03</v>
+        <v>31.76</v>
       </c>
       <c r="I135" s="6" t="inlineStr">
         <is>
@@ -6538,10 +6538,10 @@
         </is>
       </c>
       <c r="J135" s="2" t="n">
-        <v>2.962</v>
+        <v>0.524</v>
       </c>
       <c r="K135" s="2" t="n">
-        <v>2.818</v>
+        <v>0.571</v>
       </c>
       <c r="L135" t="inlineStr"/>
       <c r="M135" s="7" t="inlineStr"/>
@@ -6554,28 +6554,28 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D136" s="2" t="n">
-        <v>0.495</v>
-      </c>
-      <c r="E136" s="3" t="n">
-        <v>0.0206</v>
+        <v>2.85</v>
+      </c>
+      <c r="E136" s="8" t="n">
+        <v>-0.024</v>
       </c>
       <c r="F136" s="4" t="n">
-        <v>1490100</v>
+        <v>1560600</v>
       </c>
       <c r="G136" s="5" t="n">
-        <v>0.2</v>
+        <v>0.34</v>
       </c>
       <c r="H136" t="n">
-        <v>31.76</v>
+        <v>45.46</v>
       </c>
       <c r="I136" s="6" t="inlineStr">
         <is>
@@ -6583,10 +6583,10 @@
         </is>
       </c>
       <c r="J136" s="2" t="n">
-        <v>0.524</v>
+        <v>2.963</v>
       </c>
       <c r="K136" s="2" t="n">
-        <v>0.571</v>
+        <v>2.818</v>
       </c>
       <c r="L136" t="inlineStr"/>
       <c r="M136" s="7" t="inlineStr"/>
@@ -6599,39 +6599,39 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>AWC</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D137" s="2" t="n">
-        <v>0.645</v>
-      </c>
-      <c r="E137" s="3" t="n">
-        <v>0.0157</v>
+        <v>2.83</v>
+      </c>
+      <c r="E137" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F137" s="4" t="n">
-        <v>1450100</v>
+        <v>1558600</v>
       </c>
       <c r="G137" s="5" t="n">
-        <v>0.66</v>
+        <v>0.17</v>
       </c>
       <c r="H137" t="n">
-        <v>59.41</v>
-      </c>
-      <c r="I137" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.14</v>
+      </c>
+      <c r="I137" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J137" s="2" t="n">
-        <v>0.621</v>
+        <v>2.775</v>
       </c>
       <c r="K137" s="2" t="n">
-        <v>0.529</v>
+        <v>2.599</v>
       </c>
       <c r="L137" t="inlineStr"/>
       <c r="M137" s="7" t="inlineStr"/>
@@ -6644,39 +6644,39 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>0185</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>HSSEB</t>
         </is>
       </c>
       <c r="D138" s="2" t="n">
-        <v>2.94</v>
+        <v>0.5</v>
       </c>
       <c r="E138" s="3" t="n">
-        <v>0.0034</v>
+        <v>0.1364</v>
       </c>
       <c r="F138" s="4" t="n">
-        <v>1446800</v>
+        <v>1521400</v>
       </c>
       <c r="G138" s="5" t="n">
-        <v>0.45</v>
+        <v>10.97</v>
       </c>
       <c r="H138" t="n">
-        <v>45.93</v>
-      </c>
-      <c r="I138" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.28</v>
+      </c>
+      <c r="I138" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J138" s="2" t="n">
-        <v>2.975</v>
+        <v>0.469</v>
       </c>
       <c r="K138" s="2" t="n">
-        <v>3.034</v>
+        <v>0.498</v>
       </c>
       <c r="L138" t="inlineStr"/>
       <c r="M138" s="7" t="inlineStr"/>
@@ -6689,39 +6689,39 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>7160</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>PENTA</t>
+          <t>SKYECHIP</t>
         </is>
       </c>
       <c r="D139" s="2" t="n">
-        <v>5.89</v>
-      </c>
-      <c r="E139" s="3" t="n">
-        <v>0.0051</v>
+        <v>2.93</v>
+      </c>
+      <c r="E139" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F139" s="4" t="n">
-        <v>1400900</v>
+        <v>1496600</v>
       </c>
       <c r="G139" s="5" t="n">
-        <v>0.41</v>
+        <v>0.47</v>
       </c>
       <c r="H139" t="n">
-        <v>62.9</v>
-      </c>
-      <c r="I139" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.94</v>
+      </c>
+      <c r="I139" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J139" s="2" t="n">
-        <v>5.477</v>
+        <v>2.974</v>
       </c>
       <c r="K139" s="2" t="n">
-        <v>5.356</v>
+        <v>3.033</v>
       </c>
       <c r="L139" t="inlineStr"/>
       <c r="M139" s="7" t="inlineStr"/>
@@ -6734,28 +6734,28 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>3662</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>MFLOUR</t>
+          <t>AWC</t>
         </is>
       </c>
       <c r="D140" s="2" t="n">
-        <v>0.605</v>
+        <v>0.645</v>
       </c>
       <c r="E140" s="3" t="n">
-        <v>0.0342</v>
+        <v>0.0157</v>
       </c>
       <c r="F140" s="4" t="n">
-        <v>1380300</v>
+        <v>1450100</v>
       </c>
       <c r="G140" s="5" t="n">
-        <v>0.58</v>
+        <v>0.66</v>
       </c>
       <c r="H140" t="n">
-        <v>43.16</v>
+        <v>59.41</v>
       </c>
       <c r="I140" s="6" t="inlineStr">
         <is>
@@ -6763,10 +6763,10 @@
         </is>
       </c>
       <c r="J140" s="2" t="n">
-        <v>0.617</v>
+        <v>0.621</v>
       </c>
       <c r="K140" s="2" t="n">
-        <v>0.635</v>
+        <v>0.529</v>
       </c>
       <c r="L140" t="inlineStr"/>
       <c r="M140" s="7" t="inlineStr"/>
@@ -6779,39 +6779,39 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>3662</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>MFLOUR</t>
         </is>
       </c>
       <c r="D141" s="2" t="n">
-        <v>0.645</v>
+        <v>0.6</v>
       </c>
       <c r="E141" s="3" t="n">
-        <v>0.0157</v>
+        <v>0.0256</v>
       </c>
       <c r="F141" s="4" t="n">
-        <v>1370200</v>
+        <v>1439300</v>
       </c>
       <c r="G141" s="5" t="n">
-        <v>0.36</v>
+        <v>0.61</v>
       </c>
       <c r="H141" t="n">
-        <v>64.34999999999999</v>
-      </c>
-      <c r="I141" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.75</v>
+      </c>
+      <c r="I141" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J141" s="2" t="n">
-        <v>0.597</v>
+        <v>0.617</v>
       </c>
       <c r="K141" s="2" t="n">
-        <v>0.582</v>
+        <v>0.635</v>
       </c>
       <c r="L141" t="inlineStr"/>
       <c r="M141" s="7" t="inlineStr"/>
@@ -6824,33 +6824,40 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>0475</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>GBBOND</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D142" s="2" t="n">
-        <v>0.23</v>
+        <v>0.64</v>
       </c>
       <c r="E142" s="3" t="n">
-        <v>0.0455</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="F142" s="4" t="n">
-        <v>1365600</v>
+        <v>1416100</v>
       </c>
       <c r="G142" s="5" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="I142" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J142" s="2" t="n"/>
-      <c r="K142" s="2" t="n"/>
+        <v>0.37</v>
+      </c>
+      <c r="H142" t="n">
+        <v>63.45</v>
+      </c>
+      <c r="I142" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J142" s="2" t="n">
+        <v>0.596</v>
+      </c>
+      <c r="K142" s="2" t="n">
+        <v>0.582</v>
+      </c>
       <c r="L142" t="inlineStr"/>
       <c r="M142" s="7" t="inlineStr"/>
     </row>
@@ -6862,28 +6869,28 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>0185</t>
+          <t>7160</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>HSSEB</t>
+          <t>PENTA</t>
         </is>
       </c>
       <c r="D143" s="2" t="n">
-        <v>0.5</v>
+        <v>5.9</v>
       </c>
       <c r="E143" s="3" t="n">
-        <v>0.1364</v>
+        <v>0.0068</v>
       </c>
       <c r="F143" s="4" t="n">
-        <v>1340100</v>
+        <v>1409800</v>
       </c>
       <c r="G143" s="5" t="n">
-        <v>9.67</v>
+        <v>0.41</v>
       </c>
       <c r="H143" t="n">
-        <v>61.28</v>
+        <v>63.09</v>
       </c>
       <c r="I143" s="9" t="inlineStr">
         <is>
@@ -6891,10 +6898,10 @@
         </is>
       </c>
       <c r="J143" s="2" t="n">
-        <v>0.469</v>
+        <v>5.478</v>
       </c>
       <c r="K143" s="2" t="n">
-        <v>0.498</v>
+        <v>5.356</v>
       </c>
       <c r="L143" t="inlineStr"/>
       <c r="M143" s="7" t="inlineStr"/>
@@ -6907,40 +6914,33 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>7081</t>
+          <t>0475</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>GBBOND</t>
         </is>
       </c>
       <c r="D144" s="2" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="E144" s="10" t="n">
-        <v>0</v>
+        <v>0.23</v>
+      </c>
+      <c r="E144" s="3" t="n">
+        <v>0.0455</v>
       </c>
       <c r="F144" s="4" t="n">
-        <v>1297700</v>
+        <v>1365800</v>
       </c>
       <c r="G144" s="5" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="H144" t="n">
-        <v>20.91</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I144" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J144" s="2" t="n">
-        <v>1.037</v>
-      </c>
-      <c r="K144" s="2" t="n">
-        <v>1.119</v>
-      </c>
+      <c r="J144" s="2" t="n"/>
+      <c r="K144" s="2" t="n"/>
       <c r="L144" t="inlineStr"/>
       <c r="M144" s="7" t="inlineStr"/>
     </row>
@@ -6967,10 +6967,10 @@
         <v>0.0053</v>
       </c>
       <c r="F145" s="4" t="n">
-        <v>1268600</v>
+        <v>1332400</v>
       </c>
       <c r="G145" s="5" t="n">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="H145" t="n">
         <v>30.03</v>
@@ -6997,39 +6997,39 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>7498</t>
+          <t>5212</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>RALCO</t>
+          <t>PAVREIT</t>
         </is>
       </c>
       <c r="D146" s="2" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="E146" s="10" t="n">
-        <v>0</v>
+        <v>1.57</v>
+      </c>
+      <c r="E146" s="3" t="n">
+        <v>0.0195</v>
       </c>
       <c r="F146" s="4" t="n">
-        <v>1251800</v>
+        <v>1305400</v>
       </c>
       <c r="G146" s="5" t="n">
-        <v>2</v>
+        <v>0.32</v>
       </c>
       <c r="H146" t="n">
-        <v>62.64</v>
-      </c>
-      <c r="I146" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.18</v>
+      </c>
+      <c r="I146" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J146" s="2" t="n">
-        <v>0.999</v>
+        <v>1.564</v>
       </c>
       <c r="K146" s="2" t="n">
-        <v>0.981</v>
+        <v>1.62</v>
       </c>
       <c r="L146" t="inlineStr"/>
       <c r="M146" s="7" t="inlineStr"/>
@@ -7042,40 +7042,38 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>5162</t>
+          <t>0469</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>VSTECS</t>
+          <t>GTA</t>
         </is>
       </c>
       <c r="D147" s="2" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="E147" s="3" t="n">
-        <v>0.024</v>
+        <v>0.265</v>
+      </c>
+      <c r="E147" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F147" s="4" t="n">
-        <v>1244500</v>
+        <v>1301000</v>
       </c>
       <c r="G147" s="5" t="n">
-        <v>0.73</v>
+        <v>0.14</v>
       </c>
       <c r="H147" t="n">
-        <v>55.43</v>
-      </c>
-      <c r="I147" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>17.22</v>
+      </c>
+      <c r="I147" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J147" s="2" t="n">
-        <v>1.662</v>
-      </c>
-      <c r="K147" s="2" t="n">
-        <v>1.677</v>
-      </c>
+        <v>0.288</v>
+      </c>
+      <c r="K147" s="2" t="n"/>
       <c r="L147" t="inlineStr"/>
       <c r="M147" s="7" t="inlineStr"/>
     </row>
@@ -7087,28 +7085,28 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>7081</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D148" s="2" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="E148" s="10" t="n">
-        <v>0</v>
+        <v>0.915</v>
+      </c>
+      <c r="E148" s="8" t="n">
+        <v>-0.0054</v>
       </c>
       <c r="F148" s="4" t="n">
-        <v>1241600</v>
+        <v>1298000</v>
       </c>
       <c r="G148" s="5" t="n">
-        <v>0.19</v>
+        <v>0.55</v>
       </c>
       <c r="H148" t="n">
-        <v>43.39</v>
+        <v>20.5</v>
       </c>
       <c r="I148" s="6" t="inlineStr">
         <is>
@@ -7116,10 +7114,10 @@
         </is>
       </c>
       <c r="J148" s="2" t="n">
-        <v>1.927</v>
+        <v>1.036</v>
       </c>
       <c r="K148" s="2" t="n">
-        <v>1.957</v>
+        <v>1.119</v>
       </c>
       <c r="L148" t="inlineStr"/>
       <c r="M148" s="7" t="inlineStr"/>
@@ -7132,28 +7130,28 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>5212</t>
+          <t>5180</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>PAVREIT</t>
+          <t>CLMT</t>
         </is>
       </c>
       <c r="D149" s="2" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="E149" s="3" t="n">
-        <v>0.026</v>
+        <v>0.55</v>
+      </c>
+      <c r="E149" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F149" s="4" t="n">
-        <v>1241400</v>
+        <v>1255600</v>
       </c>
       <c r="G149" s="5" t="n">
         <v>0.3</v>
       </c>
       <c r="H149" t="n">
-        <v>50.99</v>
+        <v>30.74</v>
       </c>
       <c r="I149" s="6" t="inlineStr">
         <is>
@@ -7161,10 +7159,10 @@
         </is>
       </c>
       <c r="J149" s="2" t="n">
-        <v>1.565</v>
+        <v>0.57</v>
       </c>
       <c r="K149" s="2" t="n">
-        <v>1.62</v>
+        <v>0.582</v>
       </c>
       <c r="L149" t="inlineStr"/>
       <c r="M149" s="7" t="inlineStr"/>
@@ -7177,39 +7175,39 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>5180</t>
+          <t>7498</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>CLMT</t>
+          <t>RALCO</t>
         </is>
       </c>
       <c r="D150" s="2" t="n">
-        <v>0.555</v>
-      </c>
-      <c r="E150" s="3" t="n">
-        <v>0.0091</v>
+        <v>1.02</v>
+      </c>
+      <c r="E150" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F150" s="4" t="n">
-        <v>1233100</v>
+        <v>1251800</v>
       </c>
       <c r="G150" s="5" t="n">
-        <v>0.3</v>
+        <v>2</v>
       </c>
       <c r="H150" t="n">
-        <v>35.64</v>
-      </c>
-      <c r="I150" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.64</v>
+      </c>
+      <c r="I150" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J150" s="2" t="n">
-        <v>0.571</v>
+        <v>0.999</v>
       </c>
       <c r="K150" s="2" t="n">
-        <v>0.582</v>
+        <v>0.981</v>
       </c>
       <c r="L150" t="inlineStr"/>
       <c r="M150" s="7" t="inlineStr"/>
@@ -7222,39 +7220,39 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>0219</t>
+          <t>5162</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>RL</t>
+          <t>VSTECS</t>
         </is>
       </c>
       <c r="D151" s="2" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E151" s="8" t="n">
-        <v>-0.0167</v>
+        <v>1.72</v>
+      </c>
+      <c r="E151" s="3" t="n">
+        <v>0.0299</v>
       </c>
       <c r="F151" s="4" t="n">
-        <v>1220800</v>
+        <v>1248900</v>
       </c>
       <c r="G151" s="5" t="n">
-        <v>0.19</v>
+        <v>0.74</v>
       </c>
       <c r="H151" t="n">
-        <v>40.45</v>
-      </c>
-      <c r="I151" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.36</v>
+      </c>
+      <c r="I151" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J151" s="2" t="n">
-        <v>0.304</v>
+        <v>1.663</v>
       </c>
       <c r="K151" s="2" t="n">
-        <v>0.299</v>
+        <v>1.678</v>
       </c>
       <c r="L151" t="inlineStr"/>
       <c r="M151" s="7" t="inlineStr"/>
@@ -7267,28 +7265,28 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>KPJ</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D152" s="2" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="E152" s="3" t="n">
-        <v>0.004</v>
+        <v>1.9</v>
+      </c>
+      <c r="E152" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F152" s="4" t="n">
-        <v>1191300</v>
+        <v>1245600</v>
       </c>
       <c r="G152" s="5" t="n">
-        <v>0.22</v>
+        <v>0.19</v>
       </c>
       <c r="H152" t="n">
-        <v>37.16</v>
+        <v>43.39</v>
       </c>
       <c r="I152" s="6" t="inlineStr">
         <is>
@@ -7296,10 +7294,10 @@
         </is>
       </c>
       <c r="J152" s="2" t="n">
-        <v>2.615</v>
+        <v>1.927</v>
       </c>
       <c r="K152" s="2" t="n">
-        <v>2.79</v>
+        <v>1.957</v>
       </c>
       <c r="L152" t="inlineStr"/>
       <c r="M152" s="7" t="inlineStr"/>
@@ -7327,10 +7325,10 @@
         <v>0.0426</v>
       </c>
       <c r="F153" s="4" t="n">
-        <v>1176000</v>
+        <v>1237000</v>
       </c>
       <c r="G153" s="5" t="n">
-        <v>0.68</v>
+        <v>0.72</v>
       </c>
       <c r="H153" t="n">
         <v>55.55</v>
@@ -7357,28 +7355,28 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>0456</t>
+          <t>5878</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>MMCS</t>
+          <t>KPJ</t>
         </is>
       </c>
       <c r="D154" s="2" t="n">
-        <v>0.345</v>
+        <v>2.53</v>
       </c>
       <c r="E154" s="3" t="n">
-        <v>0.0299</v>
+        <v>0.004</v>
       </c>
       <c r="F154" s="4" t="n">
-        <v>1164000</v>
+        <v>1221700</v>
       </c>
       <c r="G154" s="5" t="n">
-        <v>0.91</v>
+        <v>0.23</v>
       </c>
       <c r="H154" t="n">
-        <v>41.57</v>
+        <v>37.16</v>
       </c>
       <c r="I154" s="6" t="inlineStr">
         <is>
@@ -7386,10 +7384,10 @@
         </is>
       </c>
       <c r="J154" s="2" t="n">
-        <v>0.349</v>
+        <v>2.615</v>
       </c>
       <c r="K154" s="2" t="n">
-        <v>0.383</v>
+        <v>2.79</v>
       </c>
       <c r="L154" t="inlineStr"/>
       <c r="M154" s="7" t="inlineStr"/>
@@ -7402,39 +7400,39 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>0340</t>
+          <t>0219</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>NORTHERN</t>
+          <t>RL</t>
         </is>
       </c>
       <c r="D155" s="2" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="E155" s="3" t="n">
-        <v>0.0417</v>
+        <v>0.295</v>
+      </c>
+      <c r="E155" s="8" t="n">
+        <v>-0.0167</v>
       </c>
       <c r="F155" s="4" t="n">
-        <v>1161400</v>
+        <v>1220800</v>
       </c>
       <c r="G155" s="5" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="H155" t="n">
-        <v>68.3</v>
-      </c>
-      <c r="I155" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.45</v>
+      </c>
+      <c r="I155" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J155" s="2" t="n">
-        <v>1.083</v>
+        <v>0.304</v>
       </c>
       <c r="K155" s="2" t="n">
-        <v>0.83</v>
+        <v>0.299</v>
       </c>
       <c r="L155" t="inlineStr"/>
       <c r="M155" s="7" t="inlineStr"/>
@@ -7447,39 +7445,39 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>5053</t>
+          <t>0340</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>OSK</t>
+          <t>NORTHERN</t>
         </is>
       </c>
       <c r="D156" s="2" t="n">
-        <v>1.66</v>
+        <v>1.24</v>
       </c>
       <c r="E156" s="3" t="n">
-        <v>0.0311</v>
+        <v>0.0333</v>
       </c>
       <c r="F156" s="4" t="n">
-        <v>1157300</v>
+        <v>1203000</v>
       </c>
       <c r="G156" s="5" t="n">
-        <v>0.8</v>
+        <v>0.16</v>
       </c>
       <c r="H156" t="n">
-        <v>29.21</v>
-      </c>
-      <c r="I156" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>67.81999999999999</v>
+      </c>
+      <c r="I156" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J156" s="2" t="n">
-        <v>1.786</v>
+        <v>1.082</v>
       </c>
       <c r="K156" s="2" t="n">
-        <v>1.919</v>
+        <v>0.83</v>
       </c>
       <c r="L156" t="inlineStr"/>
       <c r="M156" s="7" t="inlineStr"/>
@@ -7492,39 +7490,39 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>7233</t>
+          <t>0456</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>DUFU</t>
+          <t>MMCS</t>
         </is>
       </c>
       <c r="D157" s="2" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="E157" s="8" t="n">
-        <v>-0.0123</v>
+        <v>0.34</v>
+      </c>
+      <c r="E157" s="3" t="n">
+        <v>0.0149</v>
       </c>
       <c r="F157" s="4" t="n">
-        <v>1140700</v>
+        <v>1190300</v>
       </c>
       <c r="G157" s="5" t="n">
-        <v>0.37</v>
+        <v>0.93</v>
       </c>
       <c r="H157" t="n">
-        <v>61.88</v>
-      </c>
-      <c r="I157" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.92</v>
+      </c>
+      <c r="I157" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J157" s="2" t="n">
-        <v>3.001</v>
+        <v>0.349</v>
       </c>
       <c r="K157" s="2" t="n">
-        <v>2.804</v>
+        <v>0.383</v>
       </c>
       <c r="L157" t="inlineStr"/>
       <c r="M157" s="7" t="inlineStr"/>
@@ -7537,28 +7535,28 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>0450</t>
+          <t>5053</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>MFGROUP</t>
+          <t>OSK</t>
         </is>
       </c>
       <c r="D158" s="2" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="E158" s="8" t="n">
-        <v>-0.0185</v>
+        <v>1.65</v>
+      </c>
+      <c r="E158" s="3" t="n">
+        <v>0.0248</v>
       </c>
       <c r="F158" s="4" t="n">
-        <v>1082100</v>
+        <v>1174400</v>
       </c>
       <c r="G158" s="5" t="n">
-        <v>1.11</v>
+        <v>0.82</v>
       </c>
       <c r="H158" t="n">
-        <v>54.17</v>
+        <v>27.42</v>
       </c>
       <c r="I158" s="6" t="inlineStr">
         <is>
@@ -7566,10 +7564,10 @@
         </is>
       </c>
       <c r="J158" s="2" t="n">
-        <v>0.262</v>
+        <v>1.786</v>
       </c>
       <c r="K158" s="2" t="n">
-        <v>0.264</v>
+        <v>1.919</v>
       </c>
       <c r="L158" t="inlineStr"/>
       <c r="M158" s="7" t="inlineStr"/>
@@ -7582,28 +7580,28 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>5288</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>SIMEPROP</t>
+          <t>DUFU</t>
         </is>
       </c>
       <c r="D159" s="2" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="E159" s="3" t="n">
-        <v>0.0248</v>
+        <v>3.21</v>
+      </c>
+      <c r="E159" s="8" t="n">
+        <v>-0.009300000000000001</v>
       </c>
       <c r="F159" s="4" t="n">
-        <v>1081600</v>
+        <v>1149700</v>
       </c>
       <c r="G159" s="5" t="n">
-        <v>0.19</v>
+        <v>0.37</v>
       </c>
       <c r="H159" t="n">
-        <v>46.82</v>
+        <v>62.41</v>
       </c>
       <c r="I159" s="9" t="inlineStr">
         <is>
@@ -7611,10 +7609,10 @@
         </is>
       </c>
       <c r="J159" s="2" t="n">
-        <v>1.247</v>
+        <v>3.002</v>
       </c>
       <c r="K159" s="2" t="n">
-        <v>1.285</v>
+        <v>2.804</v>
       </c>
       <c r="L159" t="inlineStr"/>
       <c r="M159" s="7" t="inlineStr"/>
@@ -7627,39 +7625,39 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>5288</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>SIMEPROP</t>
         </is>
       </c>
       <c r="D160" s="2" t="n">
-        <v>1.76</v>
+        <v>1.24</v>
       </c>
       <c r="E160" s="3" t="n">
-        <v>0.005699999999999999</v>
+        <v>0.0248</v>
       </c>
       <c r="F160" s="4" t="n">
-        <v>1070900</v>
+        <v>1111800</v>
       </c>
       <c r="G160" s="5" t="n">
-        <v>0.21</v>
+        <v>0.19</v>
       </c>
       <c r="H160" t="n">
-        <v>50.39</v>
-      </c>
-      <c r="I160" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.82</v>
+      </c>
+      <c r="I160" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J160" s="2" t="n">
-        <v>1.752</v>
+        <v>1.247</v>
       </c>
       <c r="K160" s="2" t="n">
-        <v>1.778</v>
+        <v>1.285</v>
       </c>
       <c r="L160" t="inlineStr"/>
       <c r="M160" s="7" t="inlineStr"/>
@@ -7687,10 +7685,10 @@
         <v>-0.0156</v>
       </c>
       <c r="F161" s="4" t="n">
-        <v>1059400</v>
+        <v>1104400</v>
       </c>
       <c r="G161" s="5" t="n">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
       <c r="H161" t="n">
         <v>40.07</v>
@@ -7726,19 +7724,19 @@
         </is>
       </c>
       <c r="D162" s="2" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="E162" s="3" t="n">
-        <v>0.0097</v>
+        <v>0.0049</v>
       </c>
       <c r="F162" s="4" t="n">
-        <v>1047800</v>
+        <v>1095500</v>
       </c>
       <c r="G162" s="5" t="n">
-        <v>0.31</v>
+        <v>0.33</v>
       </c>
       <c r="H162" t="n">
-        <v>53.45</v>
+        <v>51.58</v>
       </c>
       <c r="I162" s="6" t="inlineStr">
         <is>
@@ -7746,10 +7744,10 @@
         </is>
       </c>
       <c r="J162" s="2" t="n">
-        <v>2.058</v>
+        <v>2.057</v>
       </c>
       <c r="K162" s="2" t="n">
-        <v>2.086</v>
+        <v>2.085</v>
       </c>
       <c r="L162" t="inlineStr"/>
       <c r="M162" s="7" t="inlineStr"/>
@@ -7762,28 +7760,28 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>5072</t>
+          <t>0450</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>HIAPTEK</t>
+          <t>MFGROUP</t>
         </is>
       </c>
       <c r="D163" s="2" t="n">
-        <v>0.255</v>
-      </c>
-      <c r="E163" s="3" t="n">
-        <v>0.02</v>
+        <v>0.265</v>
+      </c>
+      <c r="E163" s="8" t="n">
+        <v>-0.0185</v>
       </c>
       <c r="F163" s="4" t="n">
-        <v>1018900</v>
+        <v>1082100</v>
       </c>
       <c r="G163" s="5" t="n">
-        <v>0.98</v>
+        <v>1.11</v>
       </c>
       <c r="H163" t="n">
-        <v>49.76</v>
+        <v>54.17</v>
       </c>
       <c r="I163" s="6" t="inlineStr">
         <is>
@@ -7791,10 +7789,10 @@
         </is>
       </c>
       <c r="J163" s="2" t="n">
-        <v>0.255</v>
+        <v>0.262</v>
       </c>
       <c r="K163" s="2" t="n">
-        <v>0.258</v>
+        <v>0.264</v>
       </c>
       <c r="L163" t="inlineStr"/>
       <c r="M163" s="7" t="inlineStr"/>
@@ -7807,39 +7805,39 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>0037</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>RGB</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D164" s="2" t="n">
-        <v>0.215</v>
+        <v>1.76</v>
       </c>
       <c r="E164" s="3" t="n">
-        <v>0.0238</v>
+        <v>0.005699999999999999</v>
       </c>
       <c r="F164" s="4" t="n">
-        <v>1014600</v>
+        <v>1072900</v>
       </c>
       <c r="G164" s="5" t="n">
-        <v>1.19</v>
+        <v>0.21</v>
       </c>
       <c r="H164" t="n">
-        <v>69.34</v>
-      </c>
-      <c r="I164" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.39</v>
+      </c>
+      <c r="I164" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J164" s="2" t="n">
-        <v>0.207</v>
+        <v>1.752</v>
       </c>
       <c r="K164" s="2" t="n">
-        <v>0.205</v>
+        <v>1.778</v>
       </c>
       <c r="L164" t="inlineStr"/>
       <c r="M164" s="7" t="inlineStr"/>
@@ -7852,28 +7850,28 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>0037</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>RGB</t>
         </is>
       </c>
       <c r="D165" s="2" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="E165" s="3" t="n">
-        <v>0.0132</v>
+        <v>0.21</v>
+      </c>
+      <c r="E165" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F165" s="4" t="n">
-        <v>1001900</v>
+        <v>1064800</v>
       </c>
       <c r="G165" s="5" t="n">
-        <v>0.54</v>
+        <v>1.25</v>
       </c>
       <c r="H165" t="n">
-        <v>62.99</v>
+        <v>61.14</v>
       </c>
       <c r="I165" s="9" t="inlineStr">
         <is>
@@ -7881,10 +7879,10 @@
         </is>
       </c>
       <c r="J165" s="2" t="n">
-        <v>0.712</v>
+        <v>0.207</v>
       </c>
       <c r="K165" s="2" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.205</v>
       </c>
       <c r="L165" t="inlineStr"/>
       <c r="M165" s="7" t="inlineStr"/>
@@ -7897,39 +7895,39 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>5211</t>
+          <t>0399</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>SUNWAY</t>
+          <t>AMS</t>
         </is>
       </c>
       <c r="D166" s="2" t="n">
-        <v>4.38</v>
-      </c>
-      <c r="E166" s="3" t="n">
-        <v>0.0162</v>
+        <v>0.47</v>
+      </c>
+      <c r="E166" s="8" t="n">
+        <v>-0.0105</v>
       </c>
       <c r="F166" s="4" t="n">
-        <v>993100</v>
+        <v>1061300</v>
       </c>
       <c r="G166" s="5" t="n">
-        <v>0.19</v>
+        <v>0.53</v>
       </c>
       <c r="H166" t="n">
-        <v>36.78</v>
-      </c>
-      <c r="I166" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.5</v>
+      </c>
+      <c r="I166" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J166" s="2" t="n">
-        <v>4.484</v>
+        <v>0.461</v>
       </c>
       <c r="K166" s="2" t="n">
-        <v>4.817</v>
+        <v>0.461</v>
       </c>
       <c r="L166" t="inlineStr"/>
       <c r="M166" s="7" t="inlineStr"/>
@@ -7942,28 +7940,28 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>0223</t>
+          <t>0146</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>SAMAIDEN</t>
+          <t>JFTECH</t>
         </is>
       </c>
       <c r="D167" s="2" t="n">
-        <v>3.07</v>
+        <v>0.77</v>
       </c>
       <c r="E167" s="3" t="n">
-        <v>0.0199</v>
+        <v>0.0132</v>
       </c>
       <c r="F167" s="4" t="n">
-        <v>991200</v>
+        <v>1043600</v>
       </c>
       <c r="G167" s="5" t="n">
-        <v>0.24</v>
+        <v>0.57</v>
       </c>
       <c r="H167" t="n">
-        <v>69.84999999999999</v>
+        <v>62.99</v>
       </c>
       <c r="I167" s="9" t="inlineStr">
         <is>
@@ -7971,10 +7969,10 @@
         </is>
       </c>
       <c r="J167" s="2" t="n">
-        <v>2.695</v>
+        <v>0.712</v>
       </c>
       <c r="K167" s="2" t="n">
-        <v>2.043</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="L167" t="inlineStr"/>
       <c r="M167" s="7" t="inlineStr"/>
@@ -7987,39 +7985,39 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>0223</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>SAMAIDEN</t>
         </is>
       </c>
       <c r="D168" s="2" t="n">
-        <v>0.74</v>
+        <v>3.06</v>
       </c>
       <c r="E168" s="3" t="n">
-        <v>0.0137</v>
+        <v>0.0166</v>
       </c>
       <c r="F168" s="4" t="n">
-        <v>981100</v>
+        <v>1042500</v>
       </c>
       <c r="G168" s="5" t="n">
-        <v>0.31</v>
+        <v>0.25</v>
       </c>
       <c r="H168" t="n">
-        <v>46.05</v>
-      </c>
-      <c r="I168" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>69.63</v>
+      </c>
+      <c r="I168" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J168" s="2" t="n">
-        <v>0.761</v>
+        <v>2.694</v>
       </c>
       <c r="K168" s="2" t="n">
-        <v>0.747</v>
+        <v>2.043</v>
       </c>
       <c r="L168" t="inlineStr"/>
       <c r="M168" s="7" t="inlineStr"/>
@@ -8032,28 +8030,28 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>0271</t>
+          <t>5211</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>WELLS</t>
+          <t>SUNWAY</t>
         </is>
       </c>
       <c r="D169" s="2" t="n">
-        <v>0.53</v>
+        <v>4.39</v>
       </c>
       <c r="E169" s="3" t="n">
-        <v>0.0291</v>
+        <v>0.0186</v>
       </c>
       <c r="F169" s="4" t="n">
-        <v>968600</v>
+        <v>1035500</v>
       </c>
       <c r="G169" s="5" t="n">
-        <v>0.87</v>
+        <v>0.2</v>
       </c>
       <c r="H169" t="n">
-        <v>26.64</v>
+        <v>37.66</v>
       </c>
       <c r="I169" s="6" t="inlineStr">
         <is>
@@ -8061,10 +8059,10 @@
         </is>
       </c>
       <c r="J169" s="2" t="n">
-        <v>0.582</v>
+        <v>4.485</v>
       </c>
       <c r="K169" s="2" t="n">
-        <v>0.622</v>
+        <v>4.817</v>
       </c>
       <c r="L169" t="inlineStr"/>
       <c r="M169" s="7" t="inlineStr"/>
@@ -8077,28 +8075,28 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>5323</t>
+          <t>5072</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>JPG</t>
+          <t>HIAPTEK</t>
         </is>
       </c>
       <c r="D170" s="2" t="n">
-        <v>1.76</v>
+        <v>0.255</v>
       </c>
       <c r="E170" s="3" t="n">
-        <v>0.0115</v>
+        <v>0.02</v>
       </c>
       <c r="F170" s="4" t="n">
-        <v>931300</v>
+        <v>1018900</v>
       </c>
       <c r="G170" s="5" t="n">
-        <v>0.15</v>
+        <v>0.98</v>
       </c>
       <c r="H170" t="n">
-        <v>38.84</v>
+        <v>49.76</v>
       </c>
       <c r="I170" s="6" t="inlineStr">
         <is>
@@ -8106,10 +8104,10 @@
         </is>
       </c>
       <c r="J170" s="2" t="n">
-        <v>1.823</v>
+        <v>0.255</v>
       </c>
       <c r="K170" s="2" t="n">
-        <v>1.927</v>
+        <v>0.258</v>
       </c>
       <c r="L170" t="inlineStr"/>
       <c r="M170" s="7" t="inlineStr"/>
@@ -8122,28 +8120,28 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>0217</t>
+          <t>0167</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>PWRWELL</t>
+          <t>MCLEAN</t>
         </is>
       </c>
       <c r="D171" s="2" t="n">
-        <v>1.18</v>
+        <v>0.74</v>
       </c>
       <c r="E171" s="3" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.0137</v>
       </c>
       <c r="F171" s="4" t="n">
-        <v>930200</v>
+        <v>1003200</v>
       </c>
       <c r="G171" s="5" t="n">
-        <v>0.22</v>
+        <v>0.32</v>
       </c>
       <c r="H171" t="n">
-        <v>59.85</v>
+        <v>46.05</v>
       </c>
       <c r="I171" s="6" t="inlineStr">
         <is>
@@ -8151,10 +8149,10 @@
         </is>
       </c>
       <c r="J171" s="2" t="n">
-        <v>1.153</v>
+        <v>0.761</v>
       </c>
       <c r="K171" s="2" t="n">
-        <v>1.066</v>
+        <v>0.747</v>
       </c>
       <c r="L171" t="inlineStr"/>
       <c r="M171" s="7" t="inlineStr"/>
@@ -8167,28 +8165,28 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>0271</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>MBSB</t>
+          <t>WELLS</t>
         </is>
       </c>
       <c r="D172" s="2" t="n">
-        <v>0.54</v>
+        <v>0.53</v>
       </c>
       <c r="E172" s="3" t="n">
-        <v>0.0189</v>
+        <v>0.0291</v>
       </c>
       <c r="F172" s="4" t="n">
-        <v>914000</v>
+        <v>968600</v>
       </c>
       <c r="G172" s="5" t="n">
-        <v>0.26</v>
+        <v>0.87</v>
       </c>
       <c r="H172" t="n">
-        <v>39.26</v>
+        <v>26.64</v>
       </c>
       <c r="I172" s="6" t="inlineStr">
         <is>
@@ -8196,10 +8194,10 @@
         </is>
       </c>
       <c r="J172" s="2" t="n">
-        <v>0.552</v>
+        <v>0.582</v>
       </c>
       <c r="K172" s="2" t="n">
-        <v>0.582</v>
+        <v>0.622</v>
       </c>
       <c r="L172" t="inlineStr"/>
       <c r="M172" s="7" t="inlineStr"/>
@@ -8212,39 +8210,39 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>5263</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>SUNCON</t>
+          <t>MBSB</t>
         </is>
       </c>
       <c r="D173" s="2" t="n">
-        <v>7.62</v>
+        <v>0.535</v>
       </c>
       <c r="E173" s="3" t="n">
-        <v>0.016</v>
+        <v>0.009399999999999999</v>
       </c>
       <c r="F173" s="4" t="n">
-        <v>908500</v>
+        <v>948100</v>
       </c>
       <c r="G173" s="5" t="n">
-        <v>0.23</v>
+        <v>0.27</v>
       </c>
       <c r="H173" t="n">
-        <v>49.49</v>
-      </c>
-      <c r="I173" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.78</v>
+      </c>
+      <c r="I173" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J173" s="2" t="n">
-        <v>7.612</v>
+        <v>0.552</v>
       </c>
       <c r="K173" s="2" t="n">
-        <v>7.802</v>
+        <v>0.582</v>
       </c>
       <c r="L173" t="inlineStr"/>
       <c r="M173" s="7" t="inlineStr"/>
@@ -8257,28 +8255,28 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>5323</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>JPG</t>
         </is>
       </c>
       <c r="D174" s="2" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="E174" s="8" t="n">
-        <v>-0.0225</v>
+        <v>1.76</v>
+      </c>
+      <c r="E174" s="3" t="n">
+        <v>0.0115</v>
       </c>
       <c r="F174" s="4" t="n">
-        <v>875000</v>
+        <v>940800</v>
       </c>
       <c r="G174" s="5" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="H174" t="n">
-        <v>49.02</v>
+        <v>38.84</v>
       </c>
       <c r="I174" s="6" t="inlineStr">
         <is>
@@ -8286,10 +8284,10 @@
         </is>
       </c>
       <c r="J174" s="2" t="n">
-        <v>2.188</v>
+        <v>1.823</v>
       </c>
       <c r="K174" s="2" t="n">
-        <v>2.127</v>
+        <v>1.927</v>
       </c>
       <c r="L174" t="inlineStr"/>
       <c r="M174" s="7" t="inlineStr"/>
@@ -8302,28 +8300,28 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>0217</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>PWRWELL</t>
         </is>
       </c>
       <c r="D175" s="2" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="E175" s="10" t="n">
-        <v>0</v>
+        <v>1.19</v>
+      </c>
+      <c r="E175" s="3" t="n">
+        <v>0.0171</v>
       </c>
       <c r="F175" s="4" t="n">
-        <v>869700</v>
+        <v>937900</v>
       </c>
       <c r="G175" s="5" t="n">
-        <v>0.26</v>
+        <v>0.22</v>
       </c>
       <c r="H175" t="n">
-        <v>72.14</v>
+        <v>61.35</v>
       </c>
       <c r="I175" s="6" t="inlineStr">
         <is>
@@ -8331,10 +8329,10 @@
         </is>
       </c>
       <c r="J175" s="2" t="n">
-        <v>1.237</v>
+        <v>1.154</v>
       </c>
       <c r="K175" s="2" t="n">
-        <v>1.008</v>
+        <v>1.067</v>
       </c>
       <c r="L175" t="inlineStr"/>
       <c r="M175" s="7" t="inlineStr"/>
@@ -8347,28 +8345,28 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>0097</t>
+          <t>5263</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>VITROX</t>
+          <t>SUNCON</t>
         </is>
       </c>
       <c r="D176" s="2" t="n">
-        <v>11.08</v>
+        <v>7.64</v>
       </c>
       <c r="E176" s="3" t="n">
-        <v>0.0073</v>
+        <v>0.0187</v>
       </c>
       <c r="F176" s="4" t="n">
-        <v>848300</v>
+        <v>911000</v>
       </c>
       <c r="G176" s="5" t="n">
-        <v>0.26</v>
+        <v>0.23</v>
       </c>
       <c r="H176" t="n">
-        <v>74.28</v>
+        <v>50.08</v>
       </c>
       <c r="I176" s="9" t="inlineStr">
         <is>
@@ -8376,10 +8374,10 @@
         </is>
       </c>
       <c r="J176" s="2" t="n">
-        <v>10.242</v>
+        <v>7.614</v>
       </c>
       <c r="K176" s="2" t="n">
-        <v>9.504</v>
+        <v>7.803</v>
       </c>
       <c r="L176" t="inlineStr"/>
       <c r="M176" s="7" t="inlineStr"/>
@@ -8392,28 +8390,28 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>0391</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>AMBEST</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D177" s="2" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="E177" s="8" t="n">
-        <v>-0.0075</v>
+        <v>-0.0073</v>
       </c>
       <c r="F177" s="4" t="n">
-        <v>845100</v>
+        <v>899700</v>
       </c>
       <c r="G177" s="5" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="H177" t="n">
-        <v>50.16</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="I177" s="6" t="inlineStr">
         <is>
@@ -8421,10 +8419,10 @@
         </is>
       </c>
       <c r="J177" s="2" t="n">
-        <v>1.349</v>
+        <v>1.236</v>
       </c>
       <c r="K177" s="2" t="n">
-        <v>1.235</v>
+        <v>1.008</v>
       </c>
       <c r="L177" t="inlineStr"/>
       <c r="M177" s="7" t="inlineStr"/>
@@ -8437,39 +8435,39 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>5280</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>KIPREIT</t>
+          <t>HIBISCS</t>
         </is>
       </c>
       <c r="D178" s="2" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="E178" s="10" t="n">
-        <v>0</v>
+        <v>2.18</v>
+      </c>
+      <c r="E178" s="8" t="n">
+        <v>-0.018</v>
       </c>
       <c r="F178" s="4" t="n">
-        <v>813200</v>
+        <v>875900</v>
       </c>
       <c r="G178" s="5" t="n">
-        <v>1.31</v>
+        <v>0.16</v>
       </c>
       <c r="H178" t="n">
-        <v>54.87</v>
-      </c>
-      <c r="I178" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.84</v>
+      </c>
+      <c r="I178" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J178" s="2" t="n">
-        <v>0.857</v>
+        <v>2.188</v>
       </c>
       <c r="K178" s="2" t="n">
-        <v>0.851</v>
+        <v>2.128</v>
       </c>
       <c r="L178" t="inlineStr"/>
       <c r="M178" s="7" t="inlineStr"/>
@@ -8482,39 +8480,39 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>7293</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>SEG</t>
+          <t>YINSON</t>
         </is>
       </c>
       <c r="D179" s="2" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E179" s="8" t="n">
-        <v>-0.007900000000000001</v>
+        <v>2.13</v>
+      </c>
+      <c r="E179" s="3" t="n">
+        <v>0.0095</v>
       </c>
       <c r="F179" s="4" t="n">
-        <v>775100</v>
+        <v>873200</v>
       </c>
       <c r="G179" s="5" t="n">
-        <v>0.61</v>
+        <v>0.35</v>
       </c>
       <c r="H179" t="n">
-        <v>37.72</v>
-      </c>
-      <c r="I179" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.63</v>
+      </c>
+      <c r="I179" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J179" s="2" t="n">
-        <v>0.632</v>
+        <v>2.09</v>
       </c>
       <c r="K179" s="2" t="n">
-        <v>0.63</v>
+        <v>2.037</v>
       </c>
       <c r="L179" t="inlineStr"/>
       <c r="M179" s="7" t="inlineStr"/>
@@ -8527,28 +8525,28 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>6012</t>
+          <t>0391</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>MAXIS</t>
+          <t>AMBEST</t>
         </is>
       </c>
       <c r="D180" s="2" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="E180" s="3" t="n">
-        <v>0.0142</v>
+        <v>1.33</v>
+      </c>
+      <c r="E180" s="8" t="n">
+        <v>-0.0075</v>
       </c>
       <c r="F180" s="4" t="n">
-        <v>769600</v>
+        <v>868800</v>
       </c>
       <c r="G180" s="5" t="n">
-        <v>0.45</v>
+        <v>0.3</v>
       </c>
       <c r="H180" t="n">
-        <v>51.11</v>
+        <v>50.16</v>
       </c>
       <c r="I180" s="6" t="inlineStr">
         <is>
@@ -8556,10 +8554,10 @@
         </is>
       </c>
       <c r="J180" s="2" t="n">
-        <v>3.543</v>
+        <v>1.349</v>
       </c>
       <c r="K180" s="2" t="n">
-        <v>3.601</v>
+        <v>1.235</v>
       </c>
       <c r="L180" t="inlineStr"/>
       <c r="M180" s="7" t="inlineStr"/>
@@ -8572,28 +8570,28 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>7293</t>
+          <t>0097</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>YINSON</t>
+          <t>VITROX</t>
         </is>
       </c>
       <c r="D181" s="2" t="n">
-        <v>2.13</v>
+        <v>11.08</v>
       </c>
       <c r="E181" s="3" t="n">
-        <v>0.0095</v>
+        <v>0.0073</v>
       </c>
       <c r="F181" s="4" t="n">
-        <v>756500</v>
+        <v>853600</v>
       </c>
       <c r="G181" s="5" t="n">
-        <v>0.3</v>
+        <v>0.26</v>
       </c>
       <c r="H181" t="n">
-        <v>55.63</v>
+        <v>74.28</v>
       </c>
       <c r="I181" s="9" t="inlineStr">
         <is>
@@ -8601,10 +8599,10 @@
         </is>
       </c>
       <c r="J181" s="2" t="n">
-        <v>2.09</v>
+        <v>10.242</v>
       </c>
       <c r="K181" s="2" t="n">
-        <v>2.037</v>
+        <v>9.504</v>
       </c>
       <c r="L181" t="inlineStr"/>
       <c r="M181" s="7" t="inlineStr"/>
@@ -8617,39 +8615,39 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>3417</t>
+          <t>5280</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>E&amp;O</t>
+          <t>KIPREIT</t>
         </is>
       </c>
       <c r="D182" s="2" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="E182" s="3" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.86</v>
+      </c>
+      <c r="E182" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F182" s="4" t="n">
-        <v>737700</v>
+        <v>818600</v>
       </c>
       <c r="G182" s="5" t="n">
-        <v>0.41</v>
+        <v>1.32</v>
       </c>
       <c r="H182" t="n">
-        <v>50.06</v>
-      </c>
-      <c r="I182" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.87</v>
+      </c>
+      <c r="I182" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J182" s="2" t="n">
-        <v>0.771</v>
+        <v>0.857</v>
       </c>
       <c r="K182" s="2" t="n">
-        <v>0.767</v>
+        <v>0.851</v>
       </c>
       <c r="L182" t="inlineStr"/>
       <c r="M182" s="7" t="inlineStr"/>
@@ -8662,28 +8660,28 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>9792</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>SDG</t>
+          <t>SEG</t>
         </is>
       </c>
       <c r="D183" s="2" t="n">
-        <v>6.04</v>
-      </c>
-      <c r="E183" s="3" t="n">
-        <v>0.005</v>
+        <v>0.625</v>
+      </c>
+      <c r="E183" s="8" t="n">
+        <v>-0.007900000000000001</v>
       </c>
       <c r="F183" s="4" t="n">
-        <v>726600</v>
+        <v>775100</v>
       </c>
       <c r="G183" s="5" t="n">
-        <v>0.06</v>
+        <v>0.61</v>
       </c>
       <c r="H183" t="n">
-        <v>39.16</v>
+        <v>37.72</v>
       </c>
       <c r="I183" s="6" t="inlineStr">
         <is>
@@ -8691,10 +8689,10 @@
         </is>
       </c>
       <c r="J183" s="2" t="n">
-        <v>6.165</v>
+        <v>0.632</v>
       </c>
       <c r="K183" s="2" t="n">
-        <v>6.401</v>
+        <v>0.63</v>
       </c>
       <c r="L183" t="inlineStr"/>
       <c r="M183" s="7" t="inlineStr"/>
@@ -8707,39 +8705,39 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>6012</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>UWC</t>
+          <t>MAXIS</t>
         </is>
       </c>
       <c r="D184" s="2" t="n">
-        <v>7.94</v>
-      </c>
-      <c r="E184" s="8" t="n">
-        <v>-0.0063</v>
+        <v>3.55</v>
+      </c>
+      <c r="E184" s="3" t="n">
+        <v>0.0114</v>
       </c>
       <c r="F184" s="4" t="n">
-        <v>723700</v>
+        <v>772900</v>
       </c>
       <c r="G184" s="5" t="n">
-        <v>0.17</v>
+        <v>0.45</v>
       </c>
       <c r="H184" t="n">
-        <v>71.79000000000001</v>
-      </c>
-      <c r="I184" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.99</v>
+      </c>
+      <c r="I184" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J184" s="2" t="n">
-        <v>7.242</v>
+        <v>3.542</v>
       </c>
       <c r="K184" s="2" t="n">
-        <v>6.753</v>
+        <v>3.601</v>
       </c>
       <c r="L184" t="inlineStr"/>
       <c r="M184" s="7" t="inlineStr"/>
@@ -8752,28 +8750,28 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="D185" s="2" t="n">
-        <v>1.47</v>
+        <v>6.03</v>
       </c>
       <c r="E185" s="3" t="n">
-        <v>0.0068</v>
+        <v>0.0033</v>
       </c>
       <c r="F185" s="4" t="n">
-        <v>717200</v>
+        <v>750000</v>
       </c>
       <c r="G185" s="5" t="n">
-        <v>0.38</v>
+        <v>0.06</v>
       </c>
       <c r="H185" t="n">
-        <v>34.88</v>
+        <v>38.41</v>
       </c>
       <c r="I185" s="6" t="inlineStr">
         <is>
@@ -8781,10 +8779,10 @@
         </is>
       </c>
       <c r="J185" s="2" t="n">
-        <v>1.507</v>
+        <v>6.164</v>
       </c>
       <c r="K185" s="2" t="n">
-        <v>1.621</v>
+        <v>6.401</v>
       </c>
       <c r="L185" t="inlineStr"/>
       <c r="M185" s="7" t="inlineStr"/>
@@ -8797,28 +8795,28 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>5227</t>
+          <t>0466</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>IGBREIT</t>
+          <t>SRKKAI</t>
         </is>
       </c>
       <c r="D186" s="2" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="E186" s="10" t="n">
-        <v>0</v>
+        <v>0.515</v>
+      </c>
+      <c r="E186" s="8" t="n">
+        <v>-0.009599999999999999</v>
       </c>
       <c r="F186" s="4" t="n">
-        <v>717100</v>
+        <v>749400</v>
       </c>
       <c r="G186" s="5" t="n">
-        <v>0.24</v>
+        <v>0.65</v>
       </c>
       <c r="H186" t="n">
-        <v>42.84</v>
+        <v>45.34</v>
       </c>
       <c r="I186" s="6" t="inlineStr">
         <is>
@@ -8826,10 +8824,10 @@
         </is>
       </c>
       <c r="J186" s="2" t="n">
-        <v>2.766</v>
+        <v>0.524</v>
       </c>
       <c r="K186" s="2" t="n">
-        <v>2.763</v>
+        <v>0.533</v>
       </c>
       <c r="L186" t="inlineStr"/>
       <c r="M186" s="7" t="inlineStr"/>
@@ -8842,39 +8840,39 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>0240</t>
+          <t>3417</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>CORAZA</t>
+          <t>E&amp;O</t>
         </is>
       </c>
       <c r="D187" s="2" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="E187" s="8" t="n">
-        <v>-0.0211</v>
+        <v>0.77</v>
+      </c>
+      <c r="E187" s="3" t="n">
+        <v>0.006500000000000001</v>
       </c>
       <c r="F187" s="4" t="n">
-        <v>712900</v>
+        <v>737700</v>
       </c>
       <c r="G187" s="5" t="n">
-        <v>0.26</v>
+        <v>0.41</v>
       </c>
       <c r="H187" t="n">
-        <v>72.58</v>
-      </c>
-      <c r="I187" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.06</v>
+      </c>
+      <c r="I187" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J187" s="2" t="n">
-        <v>1.22</v>
+        <v>0.771</v>
       </c>
       <c r="K187" s="2" t="n">
-        <v>1.151</v>
+        <v>0.767</v>
       </c>
       <c r="L187" t="inlineStr"/>
       <c r="M187" s="7" t="inlineStr"/>
@@ -8887,28 +8885,28 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>5227</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>IGBREIT</t>
         </is>
       </c>
       <c r="D188" s="2" t="n">
-        <v>0.84</v>
+        <v>2.73</v>
       </c>
       <c r="E188" s="3" t="n">
-        <v>0.006</v>
+        <v>0.0037</v>
       </c>
       <c r="F188" s="4" t="n">
-        <v>679000</v>
+        <v>735900</v>
       </c>
       <c r="G188" s="5" t="n">
-        <v>0.22</v>
+        <v>0.24</v>
       </c>
       <c r="H188" t="n">
-        <v>59.49</v>
+        <v>44.47</v>
       </c>
       <c r="I188" s="6" t="inlineStr">
         <is>
@@ -8916,10 +8914,10 @@
         </is>
       </c>
       <c r="J188" s="2" t="n">
-        <v>0.82</v>
+        <v>2.767</v>
       </c>
       <c r="K188" s="2" t="n">
-        <v>0.756</v>
+        <v>2.763</v>
       </c>
       <c r="L188" t="inlineStr"/>
       <c r="M188" s="7" t="inlineStr"/>
@@ -8932,39 +8930,39 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>5031</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>TIMECOM</t>
+          <t>UWC</t>
         </is>
       </c>
       <c r="D189" s="2" t="n">
-        <v>5.54</v>
-      </c>
-      <c r="E189" s="3" t="n">
-        <v>0.0036</v>
+        <v>7.95</v>
+      </c>
+      <c r="E189" s="8" t="n">
+        <v>-0.005</v>
       </c>
       <c r="F189" s="4" t="n">
-        <v>667700</v>
+        <v>731700</v>
       </c>
       <c r="G189" s="5" t="n">
-        <v>0.43</v>
+        <v>0.18</v>
       </c>
       <c r="H189" t="n">
-        <v>37.14</v>
-      </c>
-      <c r="I189" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>72.13</v>
+      </c>
+      <c r="I189" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J189" s="2" t="n">
-        <v>5.718</v>
+        <v>7.243</v>
       </c>
       <c r="K189" s="2" t="n">
-        <v>5.87</v>
+        <v>6.754</v>
       </c>
       <c r="L189" t="inlineStr"/>
       <c r="M189" s="7" t="inlineStr"/>
@@ -8977,28 +8975,28 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>5236</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>MATRIX</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D190" s="2" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="E190" s="3" t="n">
-        <v>0.019</v>
+        <v>1.46</v>
+      </c>
+      <c r="E190" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F190" s="4" t="n">
-        <v>657700</v>
+        <v>719400</v>
       </c>
       <c r="G190" s="5" t="n">
-        <v>0.59</v>
+        <v>0.38</v>
       </c>
       <c r="H190" t="n">
-        <v>38.66</v>
+        <v>31.71</v>
       </c>
       <c r="I190" s="6" t="inlineStr">
         <is>
@@ -9006,10 +9004,10 @@
         </is>
       </c>
       <c r="J190" s="2" t="n">
-        <v>1.102</v>
+        <v>1.506</v>
       </c>
       <c r="K190" s="2" t="n">
-        <v>1.147</v>
+        <v>1.621</v>
       </c>
       <c r="L190" t="inlineStr"/>
       <c r="M190" s="7" t="inlineStr"/>
@@ -9022,39 +9020,39 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>0466</t>
+          <t>0240</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>SRKKAI</t>
+          <t>CORAZA</t>
         </is>
       </c>
       <c r="D191" s="2" t="n">
-        <v>0.515</v>
+        <v>1.39</v>
       </c>
       <c r="E191" s="8" t="n">
-        <v>-0.009599999999999999</v>
+        <v>-0.0211</v>
       </c>
       <c r="F191" s="4" t="n">
-        <v>650600</v>
+        <v>718300</v>
       </c>
       <c r="G191" s="5" t="n">
-        <v>0.57</v>
+        <v>0.27</v>
       </c>
       <c r="H191" t="n">
-        <v>45.34</v>
-      </c>
-      <c r="I191" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>72.58</v>
+      </c>
+      <c r="I191" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J191" s="2" t="n">
-        <v>0.524</v>
+        <v>1.22</v>
       </c>
       <c r="K191" s="2" t="n">
-        <v>0.533</v>
+        <v>1.151</v>
       </c>
       <c r="L191" t="inlineStr"/>
       <c r="M191" s="7" t="inlineStr"/>
@@ -9067,39 +9065,39 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>0245</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>MNHLDG</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D192" s="2" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="E192" s="8" t="n">
-        <v>-0.0077</v>
+        <v>0.84</v>
+      </c>
+      <c r="E192" s="3" t="n">
+        <v>0.006</v>
       </c>
       <c r="F192" s="4" t="n">
-        <v>643100</v>
+        <v>681000</v>
       </c>
       <c r="G192" s="5" t="n">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="H192" t="n">
-        <v>54.53</v>
-      </c>
-      <c r="I192" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>59.49</v>
+      </c>
+      <c r="I192" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J192" s="2" t="n">
-        <v>3.859</v>
+        <v>0.82</v>
       </c>
       <c r="K192" s="2" t="n">
-        <v>3.569</v>
+        <v>0.756</v>
       </c>
       <c r="L192" t="inlineStr"/>
       <c r="M192" s="7" t="inlineStr"/>
@@ -9112,39 +9110,39 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>7052</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>PADINI</t>
         </is>
       </c>
       <c r="D193" s="2" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E193" s="8" t="n">
-        <v>-0.007800000000000001</v>
+        <v>1.06</v>
+      </c>
+      <c r="E193" s="3" t="n">
+        <v>0.0192</v>
       </c>
       <c r="F193" s="4" t="n">
-        <v>639100</v>
+        <v>676800</v>
       </c>
       <c r="G193" s="5" t="n">
-        <v>0.22</v>
+        <v>0.39</v>
       </c>
       <c r="H193" t="n">
-        <v>51.42</v>
-      </c>
-      <c r="I193" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>44.77</v>
+      </c>
+      <c r="I193" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J193" s="2" t="n">
-        <v>0.638</v>
+        <v>1.059</v>
       </c>
       <c r="K193" s="2" t="n">
-        <v>0.611</v>
+        <v>1.197</v>
       </c>
       <c r="L193" t="inlineStr"/>
       <c r="M193" s="7" t="inlineStr"/>
@@ -9157,28 +9155,28 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>5031</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>IOIPG</t>
+          <t>TIMECOM</t>
         </is>
       </c>
       <c r="D194" s="2" t="n">
-        <v>3.37</v>
-      </c>
-      <c r="E194" s="8" t="n">
-        <v>-0.003</v>
+        <v>5.54</v>
+      </c>
+      <c r="E194" s="3" t="n">
+        <v>0.0036</v>
       </c>
       <c r="F194" s="4" t="n">
-        <v>596100</v>
+        <v>672900</v>
       </c>
       <c r="G194" s="5" t="n">
-        <v>0.09</v>
+        <v>0.43</v>
       </c>
       <c r="H194" t="n">
-        <v>37.58</v>
+        <v>37.14</v>
       </c>
       <c r="I194" s="6" t="inlineStr">
         <is>
@@ -9186,10 +9184,10 @@
         </is>
       </c>
       <c r="J194" s="2" t="n">
-        <v>3.47</v>
+        <v>5.718</v>
       </c>
       <c r="K194" s="2" t="n">
-        <v>3.652</v>
+        <v>5.87</v>
       </c>
       <c r="L194" t="inlineStr"/>
       <c r="M194" s="7" t="inlineStr"/>
@@ -9202,39 +9200,39 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>5271</t>
+          <t>0245</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>PECCA</t>
+          <t>MNHLDG</t>
         </is>
       </c>
       <c r="D195" s="2" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="E195" s="10" t="n">
-        <v>0</v>
+        <v>3.89</v>
+      </c>
+      <c r="E195" s="8" t="n">
+        <v>-0.0051</v>
       </c>
       <c r="F195" s="4" t="n">
-        <v>572500</v>
+        <v>664300</v>
       </c>
       <c r="G195" s="5" t="n">
-        <v>0.28</v>
+        <v>0.22</v>
       </c>
       <c r="H195" t="n">
-        <v>53.49</v>
-      </c>
-      <c r="I195" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.11</v>
+      </c>
+      <c r="I195" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J195" s="2" t="n">
-        <v>1.369</v>
+        <v>3.859</v>
       </c>
       <c r="K195" s="2" t="n">
-        <v>1.337</v>
+        <v>3.569</v>
       </c>
       <c r="L195" t="inlineStr"/>
       <c r="M195" s="7" t="inlineStr"/>
@@ -9247,28 +9245,28 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>0128</t>
+          <t>5236</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>FRONTKN</t>
+          <t>MATRIX</t>
         </is>
       </c>
       <c r="D196" s="2" t="n">
-        <v>5.08</v>
-      </c>
-      <c r="E196" s="10" t="n">
-        <v>0</v>
+        <v>1.07</v>
+      </c>
+      <c r="E196" s="3" t="n">
+        <v>0.019</v>
       </c>
       <c r="F196" s="4" t="n">
-        <v>561200</v>
+        <v>658600</v>
       </c>
       <c r="G196" s="5" t="n">
-        <v>0.12</v>
+        <v>0.59</v>
       </c>
       <c r="H196" t="n">
-        <v>52.79</v>
+        <v>38.66</v>
       </c>
       <c r="I196" s="6" t="inlineStr">
         <is>
@@ -9276,10 +9274,10 @@
         </is>
       </c>
       <c r="J196" s="2" t="n">
-        <v>5.049</v>
+        <v>1.102</v>
       </c>
       <c r="K196" s="2" t="n">
-        <v>5.057</v>
+        <v>1.147</v>
       </c>
       <c r="L196" t="inlineStr"/>
       <c r="M196" s="7" t="inlineStr"/>
@@ -9292,39 +9290,39 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>7195</t>
+          <t>0112</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>BNASTRA</t>
+          <t>MIKROMB</t>
         </is>
       </c>
       <c r="D197" s="2" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="E197" s="3" t="n">
-        <v>0.0076</v>
+        <v>0.635</v>
+      </c>
+      <c r="E197" s="8" t="n">
+        <v>-0.007800000000000001</v>
       </c>
       <c r="F197" s="4" t="n">
-        <v>559500</v>
+        <v>639100</v>
       </c>
       <c r="G197" s="5" t="n">
-        <v>0.44</v>
+        <v>0.22</v>
       </c>
       <c r="H197" t="n">
-        <v>84.13</v>
-      </c>
-      <c r="I197" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>51.42</v>
+      </c>
+      <c r="I197" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J197" s="2" t="n">
-        <v>2.476</v>
+        <v>0.638</v>
       </c>
       <c r="K197" s="2" t="n">
-        <v>2.347</v>
+        <v>0.611</v>
       </c>
       <c r="L197" t="inlineStr"/>
       <c r="M197" s="7" t="inlineStr"/>
@@ -9337,28 +9335,28 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>3069</t>
+          <t>5249</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>MFCB</t>
+          <t>IOIPG</t>
         </is>
       </c>
       <c r="D198" s="2" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="E198" s="3" t="n">
-        <v>0.0215</v>
+        <v>3.37</v>
+      </c>
+      <c r="E198" s="8" t="n">
+        <v>-0.003</v>
       </c>
       <c r="F198" s="4" t="n">
-        <v>550300</v>
+        <v>637400</v>
       </c>
       <c r="G198" s="5" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="H198" t="n">
-        <v>46.58</v>
+        <v>37.58</v>
       </c>
       <c r="I198" s="6" t="inlineStr">
         <is>
@@ -9366,10 +9364,10 @@
         </is>
       </c>
       <c r="J198" s="2" t="n">
-        <v>2.892</v>
+        <v>3.47</v>
       </c>
       <c r="K198" s="2" t="n">
-        <v>2.867</v>
+        <v>3.652</v>
       </c>
       <c r="L198" t="inlineStr"/>
       <c r="M198" s="7" t="inlineStr"/>
@@ -9382,39 +9380,39 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>0291</t>
+          <t>5271</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>CHB</t>
+          <t>PECCA</t>
         </is>
       </c>
       <c r="D199" s="2" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="E199" s="8" t="n">
-        <v>-0.0071</v>
+        <v>1.37</v>
+      </c>
+      <c r="E199" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F199" s="4" t="n">
-        <v>531900</v>
+        <v>572500</v>
       </c>
       <c r="G199" s="5" t="n">
-        <v>0.33</v>
+        <v>0.28</v>
       </c>
       <c r="H199" t="n">
-        <v>77.84999999999999</v>
-      </c>
-      <c r="I199" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.49</v>
+      </c>
+      <c r="I199" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J199" s="2" t="n">
-        <v>2.462</v>
+        <v>1.369</v>
       </c>
       <c r="K199" s="2" t="n">
-        <v>2.157</v>
+        <v>1.337</v>
       </c>
       <c r="L199" t="inlineStr"/>
       <c r="M199" s="7" t="inlineStr"/>
@@ -9427,39 +9425,39 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>7052</t>
+          <t>0128</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>PADINI</t>
+          <t>FRONTKN</t>
         </is>
       </c>
       <c r="D200" s="2" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="E200" s="3" t="n">
-        <v>0.0192</v>
+        <v>5.07</v>
+      </c>
+      <c r="E200" s="8" t="n">
+        <v>-0.002</v>
       </c>
       <c r="F200" s="4" t="n">
-        <v>525800</v>
+        <v>566700</v>
       </c>
       <c r="G200" s="5" t="n">
-        <v>0.3</v>
+        <v>0.12</v>
       </c>
       <c r="H200" t="n">
-        <v>44.77</v>
-      </c>
-      <c r="I200" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.13</v>
+      </c>
+      <c r="I200" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J200" s="2" t="n">
-        <v>1.059</v>
+        <v>5.048</v>
       </c>
       <c r="K200" s="2" t="n">
-        <v>1.197</v>
+        <v>5.057</v>
       </c>
       <c r="L200" t="inlineStr"/>
       <c r="M200" s="7" t="inlineStr"/>
@@ -9472,39 +9470,39 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>7195</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>TAKAFUL</t>
+          <t>BNASTRA</t>
         </is>
       </c>
       <c r="D201" s="2" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="E201" s="10" t="n">
-        <v>0</v>
+        <v>2.65</v>
+      </c>
+      <c r="E201" s="3" t="n">
+        <v>0.0076</v>
       </c>
       <c r="F201" s="4" t="n">
-        <v>517200</v>
+        <v>561700</v>
       </c>
       <c r="G201" s="5" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="H201" t="n">
-        <v>24.49</v>
-      </c>
-      <c r="I201" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>84.13</v>
+      </c>
+      <c r="I201" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J201" s="2" t="n">
-        <v>2.961</v>
+        <v>2.476</v>
       </c>
       <c r="K201" s="2" t="n">
-        <v>3.1</v>
+        <v>2.347</v>
       </c>
       <c r="L201" t="inlineStr"/>
       <c r="M201" s="7" t="inlineStr"/>
@@ -9517,45 +9515,270 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>0265</t>
+          <t>3069</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>INFOM</t>
+          <t>MFCB</t>
         </is>
       </c>
       <c r="D202" s="2" t="n">
-        <v>1.89</v>
+        <v>2.86</v>
       </c>
       <c r="E202" s="3" t="n">
-        <v>0.0107</v>
+        <v>0.0251</v>
       </c>
       <c r="F202" s="4" t="n">
-        <v>507800</v>
+        <v>552500</v>
       </c>
       <c r="G202" s="5" t="n">
-        <v>0.73</v>
+        <v>0.51</v>
       </c>
       <c r="H202" t="n">
-        <v>83.56999999999999</v>
-      </c>
-      <c r="I202" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.44</v>
+      </c>
+      <c r="I202" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J202" s="2" t="n">
-        <v>1.732</v>
+        <v>2.892</v>
       </c>
       <c r="K202" s="2" t="n">
-        <v>1.604</v>
+        <v>2.867</v>
       </c>
       <c r="L202" t="inlineStr"/>
       <c r="M202" s="7" t="inlineStr"/>
     </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>4383</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>JTIASA</t>
+        </is>
+      </c>
+      <c r="D203" s="2" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="E203" s="8" t="n">
+        <v>-0.0108</v>
+      </c>
+      <c r="F203" s="4" t="n">
+        <v>547500</v>
+      </c>
+      <c r="G203" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H203" t="n">
+        <v>31.63</v>
+      </c>
+      <c r="I203" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J203" s="2" t="n">
+        <v>0.966</v>
+      </c>
+      <c r="K203" s="2" t="n">
+        <v>1.022</v>
+      </c>
+      <c r="L203" t="inlineStr"/>
+      <c r="M203" s="7" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>0291</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>CHB</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E204" s="8" t="n">
+        <v>-0.0071</v>
+      </c>
+      <c r="F204" s="4" t="n">
+        <v>532000</v>
+      </c>
+      <c r="G204" s="5" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="H204" t="n">
+        <v>77.84999999999999</v>
+      </c>
+      <c r="I204" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J204" s="2" t="n">
+        <v>2.462</v>
+      </c>
+      <c r="K204" s="2" t="n">
+        <v>2.157</v>
+      </c>
+      <c r="L204" t="inlineStr"/>
+      <c r="M204" s="7" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>8206</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>ECOWLD</t>
+        </is>
+      </c>
+      <c r="D205" s="2" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="E205" s="3" t="n">
+        <v>0.0164</v>
+      </c>
+      <c r="F205" s="4" t="n">
+        <v>528500</v>
+      </c>
+      <c r="G205" s="5" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="H205" t="n">
+        <v>41.35</v>
+      </c>
+      <c r="I205" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J205" s="2" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="K205" s="2" t="n">
+        <v>1.966</v>
+      </c>
+      <c r="L205" t="inlineStr"/>
+      <c r="M205" s="7" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>6139</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>TAKAFUL</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="E206" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F206" s="4" t="n">
+        <v>520500</v>
+      </c>
+      <c r="G206" s="5" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="H206" t="n">
+        <v>24.49</v>
+      </c>
+      <c r="I206" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J206" s="2" t="n">
+        <v>2.961</v>
+      </c>
+      <c r="K206" s="2" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="L206" t="inlineStr"/>
+      <c r="M206" s="7" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>0265</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>INFOM</t>
+        </is>
+      </c>
+      <c r="D207" s="2" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="E207" s="3" t="n">
+        <v>0.0107</v>
+      </c>
+      <c r="F207" s="4" t="n">
+        <v>512100</v>
+      </c>
+      <c r="G207" s="5" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="H207" t="n">
+        <v>83.56999999999999</v>
+      </c>
+      <c r="I207" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J207" s="2" t="n">
+        <v>1.732</v>
+      </c>
+      <c r="K207" s="2" t="n">
+        <v>1.604</v>
+      </c>
+      <c r="L207" t="inlineStr"/>
+      <c r="M207" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M202"/>
+  <autoFilter ref="A1:M207"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>